--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="2009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="2010">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6039,6 +6039,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.45199990272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42700004577637</t>
   </si>
 </sst>
 </file>
@@ -71039,7 +71042,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6506134259</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>25520696</v>
@@ -71060,6 +71063,32 @@
         <v>2008</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6524768519</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>20440699</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>2.44099998474121</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>2.40300011634827</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>2.43499994277954</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>2.42700004577637</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>2009</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -71068,7 +71068,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6524768519</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>20440699</v>
@@ -71089,6 +71089,32 @@
         <v>2009</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6510648148</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>23538445</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>2.43400001525879</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>2.43099999427795</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1957</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2012" uniqueCount="2012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2013" uniqueCount="2013">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6048,6 +6048,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.34299993515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29099988937378</t>
   </si>
 </sst>
 </file>
@@ -71178,7 +71181,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6514467593</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>30755679</v>
@@ -71199,6 +71202,32 @@
         <v>1968</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.65</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>34910337</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>2.2720000743866</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>2.29099988937378</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>2012</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2013" uniqueCount="2013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="2014">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6051,6 +6051,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.29099988937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32100009918213</t>
   </si>
 </sst>
 </file>
@@ -71207,7 +71210,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.65</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>34910337</v>
@@ -71228,6 +71231,32 @@
         <v>2012</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6509490741</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>45077699</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>2.35800004005432</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>2.30900001525879</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>2.30900001525879</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>2.32100009918213</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>2013</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2013" uniqueCount="2013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="2014">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6051,6 +6051,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.32100009918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25600004196167</t>
   </si>
 </sst>
 </file>
@@ -71259,7 +71262,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6500810185</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>60496004</v>
@@ -71280,6 +71283,32 @@
         <v>1978</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6500578704</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>50205321</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>2.36199998855591</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>2.25600004196167</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>2.3529999256134</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>2.25600004196167</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>2013</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -71320,7 +71320,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6912384259</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>48597798</v>
@@ -71341,6 +71341,32 @@
         <v>2015</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.693587963</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>38238104</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>2.28699994087219</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>2.24200010299683</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1974</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="2016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2017" uniqueCount="2017">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6060,6 +6060,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.27800011634827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26999998092651</t>
   </si>
 </sst>
 </file>
@@ -71424,7 +71427,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6934722222</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>27045048</v>
@@ -71445,6 +71448,32 @@
         <v>2013</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.692349537</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>19564839</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>2.29099988937378</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>2.25699996948242</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>2016</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="2018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2019" uniqueCount="2019">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6066,6 +6066,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.26999998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21499991416931</t>
   </si>
 </sst>
 </file>
@@ -71482,7 +71485,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6939814815</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>27475287</v>
@@ -71503,6 +71506,32 @@
         <v>1975</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6912268518</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>29740406</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>2.25300002098083</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>2.21099996566772</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>2.23499989509583</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>2.21499991416931</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>2018</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -6068,7 +6068,7 @@
     <t xml:space="preserve">2.26999998092651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21499991416931</t>
+    <t xml:space="preserve">2.20900011062622</t>
   </si>
 </sst>
 </file>
@@ -71511,22 +71511,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6912268518</v>
+        <v>45967.6933101852</v>
       </c>
       <c r="B2505" t="n">
-        <v>29740406</v>
+        <v>29860275</v>
       </c>
       <c r="C2505" t="n">
-        <v>2.25300002098083</v>
+        <v>2.23200011253357</v>
       </c>
       <c r="D2505" t="n">
-        <v>2.21099996566772</v>
+        <v>2.18499994277954</v>
       </c>
       <c r="E2505" t="n">
-        <v>2.23499989509583</v>
+        <v>2.21300005912781</v>
       </c>
       <c r="F2505" t="n">
-        <v>2.21499991416931</v>
+        <v>2.20900011062622</v>
       </c>
       <c r="G2505" t="s">
         <v>2018</v>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -6068,7 +6068,7 @@
     <t xml:space="preserve">2.26999998092651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20900011062622</t>
+    <t xml:space="preserve">2.20099997520447</t>
   </si>
 </sst>
 </file>
@@ -71511,22 +71511,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6933101852</v>
+        <v>45968.6915509259</v>
       </c>
       <c r="B2505" t="n">
-        <v>29860275</v>
+        <v>29225344</v>
       </c>
       <c r="C2505" t="n">
-        <v>2.23200011253357</v>
+        <v>2.21600008010864</v>
       </c>
       <c r="D2505" t="n">
-        <v>2.18499994277954</v>
+        <v>2.16599988937378</v>
       </c>
       <c r="E2505" t="n">
-        <v>2.21300005912781</v>
+        <v>2.21199989318848</v>
       </c>
       <c r="F2505" t="n">
-        <v>2.20900011062622</v>
+        <v>2.20099997520447</v>
       </c>
       <c r="G2505" t="s">
         <v>2018</v>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2019" uniqueCount="2019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2022" uniqueCount="2022">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6068,7 +6068,16 @@
     <t xml:space="preserve">2.26999998092651</t>
   </si>
   <si>
+    <t xml:space="preserve">2.21499991416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20900011062622</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.20099997520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23499989509583</t>
   </si>
 </sst>
 </file>
@@ -71511,27 +71520,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6915509259</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
-        <v>29225344</v>
+        <v>29740406</v>
       </c>
       <c r="C2505" t="n">
-        <v>2.21600008010864</v>
+        <v>2.25300002098083</v>
       </c>
       <c r="D2505" t="n">
-        <v>2.16599988937378</v>
+        <v>2.21099996566772</v>
       </c>
       <c r="E2505" t="n">
-        <v>2.21199989318848</v>
+        <v>2.23499989509583</v>
       </c>
       <c r="F2505" t="n">
-        <v>2.20099997520447</v>
+        <v>2.21499991416931</v>
       </c>
       <c r="G2505" t="s">
         <v>2018</v>
       </c>
       <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>29860275</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>2.23200011253357</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>2.18499994277954</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>2.21300005912781</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>2.20900011062622</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>2019</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
+        <v>29225344</v>
+      </c>
+      <c r="C2507" t="n">
+        <v>2.21600008010864</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>2.16599988937378</v>
+      </c>
+      <c r="E2507" t="n">
+        <v>2.21199989318848</v>
+      </c>
+      <c r="F2507" t="n">
+        <v>2.20099997520447</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>2020</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6909953704</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>24122703</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>2.24399995803833</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>2.21700000762939</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>2.22900009155273</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>2.23499989509583</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>2021</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2025" uniqueCount="2025">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="2026">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6087,6 +6087,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.29299998283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31299996376038</t>
   </si>
 </sst>
 </file>
@@ -71711,7 +71714,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6912268518</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>37949103</v>
@@ -71732,6 +71735,32 @@
         <v>2024</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6911458333</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>18406298</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>2.31699991226196</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>2.28699994087219</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>2.29099988937378</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>2.31299996376038</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>2025</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -71763,7 +71763,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6912962963</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>30068067</v>
@@ -71784,6 +71784,32 @@
         <v>2013</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6939699074</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>31960517</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>2.24900007247925</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>2.28399991989136</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>2014</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -71789,7 +71789,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6939699074</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>31960517</v>
@@ -71810,6 +71810,32 @@
         <v>2014</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6910416667</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>28220615</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>2.32399988174438</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>2.28800010681152</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>2.29200005531311</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>2.2960000038147</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>1947</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="2026">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="2027">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6090,6 +6090,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.26099991798401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35700011253357</t>
   </si>
 </sst>
 </file>
@@ -71870,7 +71873,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6918981481</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>39661261</v>
@@ -71891,6 +71894,32 @@
         <v>1990</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6918287037</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>47800820</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>2.39599990844727</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>2.32800006866455</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>2.32800006866455</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>2.35700011253357</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>2026</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="2031">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2032" uniqueCount="2032">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6105,6 +6105,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.37700009346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35800004005432</t>
   </si>
 </sst>
 </file>
@@ -72041,7 +72044,7 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.6911921296</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>53029413</v>
@@ -72062,6 +72065,32 @@
         <v>1949</v>
       </c>
       <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.6919675926</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>42560443</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>2.36400008201599</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>2.30200004577637</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>2.30699992179871</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>2.35800004005432</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>2031</v>
+      </c>
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2032" uniqueCount="2032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2033" uniqueCount="2033">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6108,6 +6108,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.35800004005432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42600011825562</t>
   </si>
 </sst>
 </file>
@@ -72070,7 +72073,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.6919675926</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>42560443</v>
@@ -72091,6 +72094,32 @@
         <v>2031</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.6944097222</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>51254051</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>2.42600011825562</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>2.35800004005432</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>2.37299990653992</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>2.42600011825562</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>2032</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -72157,7 +72157,7 @@
     </row>
     <row r="2528">
       <c r="A2528" s="1" t="n">
-        <v>45999.6915393519</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2528" t="n">
         <v>31247147</v>
@@ -72178,6 +72178,32 @@
         <v>2034</v>
       </c>
       <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.6910416667</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>29759005</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>2.48699998855591</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>2.41799998283386</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>2.46700000762939</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>2.42700004577637</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>2010</v>
+      </c>
+      <c r="H2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -72183,7 +72183,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6910416667</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>29759005</v>
@@ -72204,6 +72204,32 @@
         <v>2010</v>
       </c>
       <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.6910648148</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>22249336</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>2.37700009346008</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>2.4210000038147</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>2.39400005340576</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>1944</v>
+      </c>
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -72235,7 +72235,7 @@
     </row>
     <row r="2531">
       <c r="A2531" s="1" t="n">
-        <v>46002.6913078704</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B2531" t="n">
         <v>25805378</v>
@@ -72256,6 +72256,32 @@
         <v>2034</v>
       </c>
       <c r="H2531" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" s="1" t="n">
+        <v>46003.6939699074</v>
+      </c>
+      <c r="B2532" t="n">
+        <v>25624869</v>
+      </c>
+      <c r="C2532" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="D2532" t="n">
+        <v>2.32399988174438</v>
+      </c>
+      <c r="E2532" t="n">
+        <v>2.36700010299683</v>
+      </c>
+      <c r="F2532" t="n">
+        <v>2.32800006866455</v>
+      </c>
+      <c r="G2532" t="s">
+        <v>1965</v>
+      </c>
+      <c r="H2532" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="2035">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="2036">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6117,6 +6117,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.35500001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3289999961853</t>
   </si>
 </sst>
 </file>
@@ -72261,7 +72264,7 @@
     </row>
     <row r="2532">
       <c r="A2532" s="1" t="n">
-        <v>46003.6939699074</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2532" t="n">
         <v>25624869</v>
@@ -72282,6 +72285,32 @@
         <v>1965</v>
       </c>
       <c r="H2532" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" s="1" t="n">
+        <v>46006.6911921296</v>
+      </c>
+      <c r="B2533" t="n">
+        <v>19283516</v>
+      </c>
+      <c r="C2533" t="n">
+        <v>2.35599994659424</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>2.32699990272522</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>2.34400010108948</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>2.3289999961853</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>2035</v>
+      </c>
+      <c r="H2533" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -72319,7 +72319,7 @@
     </row>
     <row r="2534">
       <c r="A2534" s="1" t="n">
-        <v>46007.6919097222</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B2534" t="n">
         <v>35171063</v>
@@ -72340,6 +72340,32 @@
         <v>2023</v>
       </c>
       <c r="H2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46008.6917939815</v>
+      </c>
+      <c r="B2535" t="n">
+        <v>45959679</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>2.37400007247925</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>2.31800007820129</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>2.32999992370605</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>2.32299995422363</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>2022</v>
+      </c>
+      <c r="H2535" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2037" uniqueCount="2037">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2038" uniqueCount="2038">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6123,6 +6123,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.3289999961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33100008964539</t>
   </si>
 </sst>
 </file>
@@ -72345,7 +72348,7 @@
     </row>
     <row r="2535">
       <c r="A2535" s="1" t="n">
-        <v>46008.6917939815</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B2535" t="n">
         <v>45959679</v>
@@ -72366,6 +72369,32 @@
         <v>2022</v>
       </c>
       <c r="H2535" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" s="1" t="n">
+        <v>46009.691087963</v>
+      </c>
+      <c r="B2536" t="n">
+        <v>32266367</v>
+      </c>
+      <c r="C2536" t="n">
+        <v>2.34599995613098</v>
+      </c>
+      <c r="D2536" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="E2536" t="n">
+        <v>2.33800005912781</v>
+      </c>
+      <c r="F2536" t="n">
+        <v>2.33100008964539</v>
+      </c>
+      <c r="G2536" t="s">
+        <v>2037</v>
+      </c>
+      <c r="H2536" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -72374,7 +72374,7 @@
     </row>
     <row r="2536">
       <c r="A2536" s="1" t="n">
-        <v>46009.691087963</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B2536" t="n">
         <v>32266367</v>
@@ -72395,6 +72395,32 @@
         <v>2037</v>
       </c>
       <c r="H2536" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" s="1" t="n">
+        <v>46010.6917939815</v>
+      </c>
+      <c r="B2537" t="n">
+        <v>42332800</v>
+      </c>
+      <c r="C2537" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="D2537" t="n">
+        <v>2.30800008773804</v>
+      </c>
+      <c r="E2537" t="n">
+        <v>2.31200003623962</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>2.37700009346008</v>
+      </c>
+      <c r="G2537" t="s">
+        <v>2030</v>
+      </c>
+      <c r="H2537" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -72482,6 +72482,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2540">
+      <c r="A2540" s="1" t="n">
+        <v>46020.6911226852</v>
+      </c>
+      <c r="B2540" t="n">
+        <v>26209686</v>
+      </c>
+      <c r="C2540" t="n">
+        <v>2.44799995422363</v>
+      </c>
+      <c r="D2540" t="n">
+        <v>2.39499998092651</v>
+      </c>
+      <c r="E2540" t="n">
+        <v>2.42799997329712</v>
+      </c>
+      <c r="F2540" t="n">
+        <v>2.39499998092651</v>
+      </c>
+      <c r="G2540" t="s">
+        <v>1984</v>
+      </c>
+      <c r="H2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -72510,7 +72510,7 @@
     </row>
     <row r="2541">
       <c r="A2541" s="1" t="n">
-        <v>46021.6910185185</v>
+        <v>46021.3333333333</v>
       </c>
       <c r="B2541" t="n">
         <v>24319040</v>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2041" uniqueCount="2041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="2042">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6135,6 +6135,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.42499995231628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5</t>
   </si>
 </sst>
 </file>
@@ -72537,6 +72540,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2542">
+      <c r="A2542" s="1" t="n">
+        <v>46024.6911689815</v>
+      </c>
+      <c r="B2542" t="n">
+        <v>50112507</v>
+      </c>
+      <c r="C2542" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D2542" t="n">
+        <v>2.44899988174438</v>
+      </c>
+      <c r="E2542" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="F2542" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G2542" t="s">
+        <v>2041</v>
+      </c>
+      <c r="H2542" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="2042">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2043" uniqueCount="2043">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6138,6 +6138,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.58100008964539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6159999370575</t>
   </si>
 </sst>
 </file>
@@ -72568,7 +72571,7 @@
     </row>
     <row r="2543">
       <c r="A2543" s="1" t="n">
-        <v>46027.692349537</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B2543" t="n">
         <v>89838877</v>
@@ -72589,6 +72592,32 @@
         <v>2041</v>
       </c>
       <c r="H2543" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" s="1" t="n">
+        <v>46028.6917592593</v>
+      </c>
+      <c r="B2544" t="n">
+        <v>59517100</v>
+      </c>
+      <c r="C2544" t="n">
+        <v>2.64499998092651</v>
+      </c>
+      <c r="D2544" t="n">
+        <v>2.58400011062622</v>
+      </c>
+      <c r="E2544" t="n">
+        <v>2.59200000762939</v>
+      </c>
+      <c r="F2544" t="n">
+        <v>2.6159999370575</v>
+      </c>
+      <c r="G2544" t="s">
+        <v>2042</v>
+      </c>
+      <c r="H2544" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2043" uniqueCount="2043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2044" uniqueCount="2044">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6141,6 +6141,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.6159999370575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52500009536743</t>
   </si>
 </sst>
 </file>
@@ -72597,7 +72600,7 @@
     </row>
     <row r="2544">
       <c r="A2544" s="1" t="n">
-        <v>46028.6917592593</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B2544" t="n">
         <v>59517100</v>
@@ -72618,6 +72621,32 @@
         <v>2042</v>
       </c>
       <c r="H2544" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" s="1" t="n">
+        <v>46029.6913425926</v>
+      </c>
+      <c r="B2545" t="n">
+        <v>71648285</v>
+      </c>
+      <c r="C2545" t="n">
+        <v>2.59500002861023</v>
+      </c>
+      <c r="D2545" t="n">
+        <v>2.50200009346008</v>
+      </c>
+      <c r="E2545" t="n">
+        <v>2.58999991416931</v>
+      </c>
+      <c r="F2545" t="n">
+        <v>2.52500009536743</v>
+      </c>
+      <c r="G2545" t="s">
+        <v>2043</v>
+      </c>
+      <c r="H2545" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2044" uniqueCount="2044">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="2045">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6144,6 +6144,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.52500009536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53299999237061</t>
   </si>
 </sst>
 </file>
@@ -72626,7 +72629,7 @@
     </row>
     <row r="2545">
       <c r="A2545" s="1" t="n">
-        <v>46029.6913425926</v>
+        <v>46029.3333333333</v>
       </c>
       <c r="B2545" t="n">
         <v>71648285</v>
@@ -72647,6 +72650,32 @@
         <v>2043</v>
       </c>
       <c r="H2545" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2546">
+      <c r="A2546" s="1" t="n">
+        <v>46030.6912615741</v>
+      </c>
+      <c r="B2546" t="n">
+        <v>27279378</v>
+      </c>
+      <c r="C2546" t="n">
+        <v>2.55100011825562</v>
+      </c>
+      <c r="D2546" t="n">
+        <v>2.50099992752075</v>
+      </c>
+      <c r="E2546" t="n">
+        <v>2.51500010490417</v>
+      </c>
+      <c r="F2546" t="n">
+        <v>2.53299999237061</v>
+      </c>
+      <c r="G2546" t="s">
+        <v>2044</v>
+      </c>
+      <c r="H2546" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="2047">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="2048">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6153,6 +6153,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.56800007820129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59599995613098</t>
   </si>
 </sst>
 </file>
@@ -72687,7 +72690,7 @@
     </row>
     <row r="2547">
       <c r="A2547" s="1" t="n">
-        <v>46031.6912268518</v>
+        <v>46031.3333333333</v>
       </c>
       <c r="B2547" t="n">
         <v>40737827</v>
@@ -72708,6 +72711,32 @@
         <v>2046</v>
       </c>
       <c r="H2547" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2548">
+      <c r="A2548" s="1" t="n">
+        <v>46034.6912847222</v>
+      </c>
+      <c r="B2548" t="n">
+        <v>36331636</v>
+      </c>
+      <c r="C2548" t="n">
+        <v>2.59599995613098</v>
+      </c>
+      <c r="D2548" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="E2548" t="n">
+        <v>2.57500004768372</v>
+      </c>
+      <c r="F2548" t="n">
+        <v>2.59599995613098</v>
+      </c>
+      <c r="G2548" t="s">
+        <v>2047</v>
+      </c>
+      <c r="H2548" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="2050">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="2051">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6162,6 +6162,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.71199989318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71700000762939</t>
   </si>
 </sst>
 </file>
@@ -72774,7 +72777,7 @@
     </row>
     <row r="2550">
       <c r="A2550" s="1" t="n">
-        <v>46036.6911689815</v>
+        <v>46036.3333333333</v>
       </c>
       <c r="B2550" t="n">
         <v>43585162</v>
@@ -72795,6 +72798,32 @@
         <v>2049</v>
       </c>
       <c r="H2550" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2551">
+      <c r="A2551" s="1" t="n">
+        <v>46037.6918981481</v>
+      </c>
+      <c r="B2551" t="n">
+        <v>42488165</v>
+      </c>
+      <c r="C2551" t="n">
+        <v>2.71700000762939</v>
+      </c>
+      <c r="D2551" t="n">
+        <v>2.67300009727478</v>
+      </c>
+      <c r="E2551" t="n">
+        <v>2.69799995422363</v>
+      </c>
+      <c r="F2551" t="n">
+        <v>2.71700000762939</v>
+      </c>
+      <c r="G2551" t="s">
+        <v>2050</v>
+      </c>
+      <c r="H2551" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="2051">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="2052">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6165,6 +6165,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.73399996757507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68400001525879</t>
   </si>
 </sst>
 </file>
@@ -72829,7 +72832,7 @@
     </row>
     <row r="2552">
       <c r="A2552" s="1" t="n">
-        <v>46038.6910763889</v>
+        <v>46038.3333333333</v>
       </c>
       <c r="B2552" t="n">
         <v>35127739</v>
@@ -72850,6 +72853,32 @@
         <v>2050</v>
       </c>
       <c r="H2552" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2553">
+      <c r="A2553" s="1" t="n">
+        <v>46041.6912731481</v>
+      </c>
+      <c r="B2553" t="n">
+        <v>33992756</v>
+      </c>
+      <c r="C2553" t="n">
+        <v>2.70600008964539</v>
+      </c>
+      <c r="D2553" t="n">
+        <v>2.66400003433228</v>
+      </c>
+      <c r="E2553" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="F2553" t="n">
+        <v>2.68400001525879</v>
+      </c>
+      <c r="G2553" t="s">
+        <v>2051</v>
+      </c>
+      <c r="H2553" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="2052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2053" uniqueCount="2053">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6168,6 +6168,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.68400001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76399993896484</t>
   </si>
 </sst>
 </file>
@@ -72858,7 +72861,7 @@
     </row>
     <row r="2553">
       <c r="A2553" s="1" t="n">
-        <v>46041.6912731481</v>
+        <v>46041.3333333333</v>
       </c>
       <c r="B2553" t="n">
         <v>33992756</v>
@@ -72879,6 +72882,32 @@
         <v>2051</v>
       </c>
       <c r="H2553" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2554">
+      <c r="A2554" s="1" t="n">
+        <v>46042.6939930556</v>
+      </c>
+      <c r="B2554" t="n">
+        <v>46265227</v>
+      </c>
+      <c r="C2554" t="n">
+        <v>2.76399993896484</v>
+      </c>
+      <c r="D2554" t="n">
+        <v>2.63499999046326</v>
+      </c>
+      <c r="E2554" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="F2554" t="n">
+        <v>2.76399993896484</v>
+      </c>
+      <c r="G2554" t="s">
+        <v>2052</v>
+      </c>
+      <c r="H2554" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2053" uniqueCount="2053">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="2054">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6171,6 +6171,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.76399993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80999994277954</t>
   </si>
 </sst>
 </file>
@@ -72887,7 +72890,7 @@
     </row>
     <row r="2554">
       <c r="A2554" s="1" t="n">
-        <v>46042.6939930556</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B2554" t="n">
         <v>46265227</v>
@@ -72908,6 +72911,32 @@
         <v>2052</v>
       </c>
       <c r="H2554" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2555">
+      <c r="A2555" s="1" t="n">
+        <v>46043.6926157407</v>
+      </c>
+      <c r="B2555" t="n">
+        <v>42883570</v>
+      </c>
+      <c r="C2555" t="n">
+        <v>2.80800008773804</v>
+      </c>
+      <c r="D2555" t="n">
+        <v>2.73799991607666</v>
+      </c>
+      <c r="E2555" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="F2555" t="n">
+        <v>2.80999994277954</v>
+      </c>
+      <c r="G2555" t="s">
+        <v>2053</v>
+      </c>
+      <c r="H2555" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2056" uniqueCount="2056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="2057">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6180,6 +6180,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.83100008964539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95499992370605</t>
   </si>
 </sst>
 </file>
@@ -72948,7 +72951,7 @@
     </row>
     <row r="2556">
       <c r="A2556" s="1" t="n">
-        <v>46044.6933101852</v>
+        <v>46044.3333333333</v>
       </c>
       <c r="B2556" t="n">
         <v>57901929</v>
@@ -72969,6 +72972,32 @@
         <v>2055</v>
       </c>
       <c r="H2556" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" s="1" t="n">
+        <v>46045.692662037</v>
+      </c>
+      <c r="B2557" t="n">
+        <v>72947393</v>
+      </c>
+      <c r="C2557" t="n">
+        <v>2.95799994468689</v>
+      </c>
+      <c r="D2557" t="n">
+        <v>2.82999992370605</v>
+      </c>
+      <c r="E2557" t="n">
+        <v>2.84500002861023</v>
+      </c>
+      <c r="F2557" t="n">
+        <v>2.95499992370605</v>
+      </c>
+      <c r="G2557" t="s">
+        <v>2056</v>
+      </c>
+      <c r="H2557" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="2057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2058" uniqueCount="2058">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6183,6 +6183,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.95499992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96799993515015</t>
   </si>
 </sst>
 </file>
@@ -72977,7 +72980,7 @@
     </row>
     <row r="2557">
       <c r="A2557" s="1" t="n">
-        <v>46045.692662037</v>
+        <v>46045.3333333333</v>
       </c>
       <c r="B2557" t="n">
         <v>72947393</v>
@@ -72998,6 +73001,32 @@
         <v>2056</v>
       </c>
       <c r="H2557" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2558">
+      <c r="A2558" s="1" t="n">
+        <v>46048.6929166667</v>
+      </c>
+      <c r="B2558" t="n">
+        <v>39830323</v>
+      </c>
+      <c r="C2558" t="n">
+        <v>2.98099994659424</v>
+      </c>
+      <c r="D2558" t="n">
+        <v>2.92700004577637</v>
+      </c>
+      <c r="E2558" t="n">
+        <v>2.95099997520447</v>
+      </c>
+      <c r="F2558" t="n">
+        <v>2.96799993515015</v>
+      </c>
+      <c r="G2558" t="s">
+        <v>2057</v>
+      </c>
+      <c r="H2558" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="2062">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="2063">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6197,7 +6197,10 @@
     <t xml:space="preserve">3.09500002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1029999256134</t>
+    <t xml:space="preserve">3.10899996757507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16799998283386</t>
   </si>
 </sst>
 </file>
@@ -73122,10 +73125,10 @@
     </row>
     <row r="2562">
       <c r="A2562" s="1" t="n">
-        <v>46052.6388657407</v>
+        <v>46052.3333333333</v>
       </c>
       <c r="B2562" t="n">
-        <v>23994774</v>
+        <v>32688135</v>
       </c>
       <c r="C2562" t="n">
         <v>3.12199997901917</v>
@@ -73137,12 +73140,38 @@
         <v>3.08999991416931</v>
       </c>
       <c r="F2562" t="n">
-        <v>3.1029999256134</v>
+        <v>3.10899996757507</v>
       </c>
       <c r="G2562" t="s">
         <v>2061</v>
       </c>
       <c r="H2562" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2563">
+      <c r="A2563" s="1" t="n">
+        <v>46055.6912037037</v>
+      </c>
+      <c r="B2563" t="n">
+        <v>44792001</v>
+      </c>
+      <c r="C2563" t="n">
+        <v>3.16799998283386</v>
+      </c>
+      <c r="D2563" t="n">
+        <v>3.01799988746643</v>
+      </c>
+      <c r="E2563" t="n">
+        <v>3.0220000743866</v>
+      </c>
+      <c r="F2563" t="n">
+        <v>3.16799998283386</v>
+      </c>
+      <c r="G2563" t="s">
+        <v>2062</v>
+      </c>
+      <c r="H2563" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="2063">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="2064">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6201,6 +6201,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.14199995994568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10199999809265</t>
   </si>
 </sst>
 </file>
@@ -73177,7 +73180,7 @@
     </row>
     <row r="2564">
       <c r="A2564" s="1" t="n">
-        <v>46056.6929861111</v>
+        <v>46056.3333333333</v>
       </c>
       <c r="B2564" t="n">
         <v>32985747</v>
@@ -73198,6 +73201,32 @@
         <v>2062</v>
       </c>
       <c r="H2564" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2565">
+      <c r="A2565" s="1" t="n">
+        <v>46057.6940972222</v>
+      </c>
+      <c r="B2565" t="n">
+        <v>46934605</v>
+      </c>
+      <c r="C2565" t="n">
+        <v>3.20600008964539</v>
+      </c>
+      <c r="D2565" t="n">
+        <v>3.10199999809265</v>
+      </c>
+      <c r="E2565" t="n">
+        <v>3.17600011825562</v>
+      </c>
+      <c r="F2565" t="n">
+        <v>3.10199999809265</v>
+      </c>
+      <c r="G2565" t="s">
+        <v>2063</v>
+      </c>
+      <c r="H2565" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="2064">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="2065">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6204,6 +6204,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.10199999809265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10700011253357</t>
   </si>
 </sst>
 </file>
@@ -73206,7 +73209,7 @@
     </row>
     <row r="2565">
       <c r="A2565" s="1" t="n">
-        <v>46057.6940972222</v>
+        <v>46057.3333333333</v>
       </c>
       <c r="B2565" t="n">
         <v>46934605</v>
@@ -73227,6 +73230,32 @@
         <v>2063</v>
       </c>
       <c r="H2565" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2566">
+      <c r="A2566" s="1" t="n">
+        <v>46058.6911921296</v>
+      </c>
+      <c r="B2566" t="n">
+        <v>56263117</v>
+      </c>
+      <c r="C2566" t="n">
+        <v>3.1159999370575</v>
+      </c>
+      <c r="D2566" t="n">
+        <v>3.02800011634827</v>
+      </c>
+      <c r="E2566" t="n">
+        <v>3.04099988937378</v>
+      </c>
+      <c r="F2566" t="n">
+        <v>3.10700011253357</v>
+      </c>
+      <c r="G2566" t="s">
+        <v>2064</v>
+      </c>
+      <c r="H2566" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="2065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="2066">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6207,6 +6207,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.10700011253357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13800001144409</t>
   </si>
 </sst>
 </file>
@@ -73235,7 +73238,7 @@
     </row>
     <row r="2566">
       <c r="A2566" s="1" t="n">
-        <v>46058.6911921296</v>
+        <v>46058.3333333333</v>
       </c>
       <c r="B2566" t="n">
         <v>56263117</v>
@@ -73256,6 +73259,32 @@
         <v>2064</v>
       </c>
       <c r="H2566" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2567">
+      <c r="A2567" s="1" t="n">
+        <v>46059.6910648148</v>
+      </c>
+      <c r="B2567" t="n">
+        <v>42122959</v>
+      </c>
+      <c r="C2567" t="n">
+        <v>3.13800001144409</v>
+      </c>
+      <c r="D2567" t="n">
+        <v>3.06800007820129</v>
+      </c>
+      <c r="E2567" t="n">
+        <v>3.11500000953674</v>
+      </c>
+      <c r="F2567" t="n">
+        <v>3.13800001144409</v>
+      </c>
+      <c r="G2567" t="s">
+        <v>2065</v>
+      </c>
+      <c r="H2567" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2068" uniqueCount="2068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2069" uniqueCount="2069">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6216,6 +6216,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.22900009155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29299998283386</t>
   </si>
 </sst>
 </file>
@@ -73322,7 +73325,7 @@
     </row>
     <row r="2569">
       <c r="A2569" s="1" t="n">
-        <v>46063.6912152778</v>
+        <v>46063.3333333333</v>
       </c>
       <c r="B2569" t="n">
         <v>37517816</v>
@@ -73343,6 +73346,32 @@
         <v>2067</v>
       </c>
       <c r="H2569" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2570">
+      <c r="A2570" s="1" t="n">
+        <v>46064.6911342593</v>
+      </c>
+      <c r="B2570" t="n">
+        <v>28543333</v>
+      </c>
+      <c r="C2570" t="n">
+        <v>3.29399991035461</v>
+      </c>
+      <c r="D2570" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="E2570" t="n">
+        <v>3.25300002098083</v>
+      </c>
+      <c r="F2570" t="n">
+        <v>3.29299998283386</v>
+      </c>
+      <c r="G2570" t="s">
+        <v>2068</v>
+      </c>
+      <c r="H2570" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="2071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="2072">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6225,6 +6225,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.29900002479553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30900001525879</t>
   </si>
 </sst>
 </file>
@@ -73383,7 +73386,7 @@
     </row>
     <row r="2571">
       <c r="A2571" s="1" t="n">
-        <v>46065.6927893519</v>
+        <v>46065.3333333333</v>
       </c>
       <c r="B2571" t="n">
         <v>41902224</v>
@@ -73404,6 +73407,32 @@
         <v>2070</v>
       </c>
       <c r="H2571" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2572">
+      <c r="A2572" s="1" t="n">
+        <v>46066.6932407407</v>
+      </c>
+      <c r="B2572" t="n">
+        <v>35421646</v>
+      </c>
+      <c r="C2572" t="n">
+        <v>3.31299996376038</v>
+      </c>
+      <c r="D2572" t="n">
+        <v>3.23600006103516</v>
+      </c>
+      <c r="E2572" t="n">
+        <v>3.26999998092651</v>
+      </c>
+      <c r="F2572" t="n">
+        <v>3.30900001525879</v>
+      </c>
+      <c r="G2572" t="s">
+        <v>2071</v>
+      </c>
+      <c r="H2572" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="2073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="2074">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6231,6 +6231,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.38700008392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4539999961853</t>
   </si>
 </sst>
 </file>
@@ -73467,7 +73470,7 @@
     </row>
     <row r="2574">
       <c r="A2574" s="1" t="n">
-        <v>46070.6920023148</v>
+        <v>46070.3333333333</v>
       </c>
       <c r="B2574" t="n">
         <v>29786373</v>
@@ -73488,6 +73491,32 @@
         <v>2072</v>
       </c>
       <c r="H2574" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2575">
+      <c r="A2575" s="1" t="n">
+        <v>46071.6917592593</v>
+      </c>
+      <c r="B2575" t="n">
+        <v>28309588</v>
+      </c>
+      <c r="C2575" t="n">
+        <v>3.49600005149841</v>
+      </c>
+      <c r="D2575" t="n">
+        <v>3.40799999237061</v>
+      </c>
+      <c r="E2575" t="n">
+        <v>3.41199994087219</v>
+      </c>
+      <c r="F2575" t="n">
+        <v>3.4539999961853</v>
+      </c>
+      <c r="G2575" t="s">
+        <v>2073</v>
+      </c>
+      <c r="H2575" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="2076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="2077">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6240,6 +6240,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.42300009727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39599990844727</t>
   </si>
 </sst>
 </file>
@@ -73554,7 +73557,7 @@
     </row>
     <row r="2577">
       <c r="A2577" s="1" t="n">
-        <v>46073.6942013889</v>
+        <v>46073.3333333333</v>
       </c>
       <c r="B2577" t="n">
         <v>26588581</v>
@@ -73575,6 +73578,32 @@
         <v>2075</v>
       </c>
       <c r="H2577" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2578">
+      <c r="A2578" s="1" t="n">
+        <v>46076.6910069444</v>
+      </c>
+      <c r="B2578" t="n">
+        <v>26888840</v>
+      </c>
+      <c r="C2578" t="n">
+        <v>3.46900010108948</v>
+      </c>
+      <c r="D2578" t="n">
+        <v>3.37199997901917</v>
+      </c>
+      <c r="E2578" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="F2578" t="n">
+        <v>3.39599990844727</v>
+      </c>
+      <c r="G2578" t="s">
+        <v>2076</v>
+      </c>
+      <c r="H2578" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="2079">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2080" uniqueCount="2080">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6249,6 +6249,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.41899991035461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50300002098083</t>
   </si>
 </sst>
 </file>
@@ -73615,7 +73618,7 @@
     </row>
     <row r="2579">
       <c r="A2579" s="1" t="n">
-        <v>46077.6909837963</v>
+        <v>46077.3333333333</v>
       </c>
       <c r="B2579" t="n">
         <v>23614301</v>
@@ -73636,6 +73639,32 @@
         <v>2078</v>
       </c>
       <c r="H2579" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2580">
+      <c r="A2580" s="1" t="n">
+        <v>46078.6941666667</v>
+      </c>
+      <c r="B2580" t="n">
+        <v>58104169</v>
+      </c>
+      <c r="C2580" t="n">
+        <v>3.51600003242493</v>
+      </c>
+      <c r="D2580" t="n">
+        <v>3.36999988555908</v>
+      </c>
+      <c r="E2580" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="F2580" t="n">
+        <v>3.50300002098083</v>
+      </c>
+      <c r="G2580" t="s">
+        <v>2079</v>
+      </c>
+      <c r="H2580" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2080" uniqueCount="2080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="2081">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6252,6 +6252,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.48000001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57100009918213</t>
   </si>
 </sst>
 </file>
@@ -73670,7 +73673,7 @@
     </row>
     <row r="2581">
       <c r="A2581" s="1" t="n">
-        <v>46079.6910763889</v>
+        <v>46079.3333333333</v>
       </c>
       <c r="B2581" t="n">
         <v>47453089</v>
@@ -73691,6 +73694,32 @@
         <v>2079</v>
       </c>
       <c r="H2581" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2582">
+      <c r="A2582" s="1" t="n">
+        <v>46080.6928935185</v>
+      </c>
+      <c r="B2582" t="n">
+        <v>41189434</v>
+      </c>
+      <c r="C2582" t="n">
+        <v>3.6010000705719</v>
+      </c>
+      <c r="D2582" t="n">
+        <v>3.46900010108948</v>
+      </c>
+      <c r="E2582" t="n">
+        <v>3.49600005149841</v>
+      </c>
+      <c r="F2582" t="n">
+        <v>3.57100009918213</v>
+      </c>
+      <c r="G2582" t="s">
+        <v>2080</v>
+      </c>
+      <c r="H2582" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="2081">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="2082">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6255,6 +6255,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.57100009918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43300008773804</t>
   </si>
 </sst>
 </file>
@@ -73699,7 +73702,7 @@
     </row>
     <row r="2582">
       <c r="A2582" s="1" t="n">
-        <v>46080.6928935185</v>
+        <v>46080.3333333333</v>
       </c>
       <c r="B2582" t="n">
         <v>41189434</v>
@@ -73720,6 +73723,32 @@
         <v>2080</v>
       </c>
       <c r="H2582" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2583">
+      <c r="A2583" s="1" t="n">
+        <v>46083.6937847222</v>
+      </c>
+      <c r="B2583" t="n">
+        <v>73060207</v>
+      </c>
+      <c r="C2583" t="n">
+        <v>3.69099998474121</v>
+      </c>
+      <c r="D2583" t="n">
+        <v>3.40599989891052</v>
+      </c>
+      <c r="E2583" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="F2583" t="n">
+        <v>3.43300008773804</v>
+      </c>
+      <c r="G2583" t="s">
+        <v>2081</v>
+      </c>
+      <c r="H2583" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="2082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2083" uniqueCount="2083">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6258,6 +6258,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.43300008773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25600004196167</t>
   </si>
 </sst>
 </file>
@@ -73728,7 +73731,7 @@
     </row>
     <row r="2583">
       <c r="A2583" s="1" t="n">
-        <v>46083.6937847222</v>
+        <v>46083.3333333333</v>
       </c>
       <c r="B2583" t="n">
         <v>73060207</v>
@@ -73749,6 +73752,32 @@
         <v>2081</v>
       </c>
       <c r="H2583" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2584">
+      <c r="A2584" s="1" t="n">
+        <v>46084.6931481481</v>
+      </c>
+      <c r="B2584" t="n">
+        <v>90382549</v>
+      </c>
+      <c r="C2584" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="D2584" t="n">
+        <v>3.10999989509583</v>
+      </c>
+      <c r="E2584" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="F2584" t="n">
+        <v>3.25600004196167</v>
+      </c>
+      <c r="G2584" t="s">
+        <v>2082</v>
+      </c>
+      <c r="H2584" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2083" uniqueCount="2083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="2084">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6261,6 +6261,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.25600004196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34999990463257</t>
   </si>
 </sst>
 </file>
@@ -73757,7 +73760,7 @@
     </row>
     <row r="2584">
       <c r="A2584" s="1" t="n">
-        <v>46084.6931481481</v>
+        <v>46084.3333333333</v>
       </c>
       <c r="B2584" t="n">
         <v>90382549</v>
@@ -73778,6 +73781,32 @@
         <v>2082</v>
       </c>
       <c r="H2584" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2585">
+      <c r="A2585" s="1" t="n">
+        <v>46085.6909722222</v>
+      </c>
+      <c r="B2585" t="n">
+        <v>48498141</v>
+      </c>
+      <c r="C2585" t="n">
+        <v>3.36199998855591</v>
+      </c>
+      <c r="D2585" t="n">
+        <v>3.20900011062622</v>
+      </c>
+      <c r="E2585" t="n">
+        <v>3.22499990463257</v>
+      </c>
+      <c r="F2585" t="n">
+        <v>3.34999990463257</v>
+      </c>
+      <c r="G2585" t="s">
+        <v>2083</v>
+      </c>
+      <c r="H2585" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="2086">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="2087">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6270,6 +6270,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.24000000953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39499998092651</t>
   </si>
 </sst>
 </file>
@@ -73844,7 +73847,7 @@
     </row>
     <row r="2587">
       <c r="A2587" s="1" t="n">
-        <v>46087.692349537</v>
+        <v>46087.3333333333</v>
       </c>
       <c r="B2587" t="n">
         <v>30410374</v>
@@ -73865,6 +73868,32 @@
         <v>2085</v>
       </c>
       <c r="H2587" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2588">
+      <c r="A2588" s="1" t="n">
+        <v>46090.6920601852</v>
+      </c>
+      <c r="B2588" t="n">
+        <v>51250981</v>
+      </c>
+      <c r="C2588" t="n">
+        <v>3.40400004386902</v>
+      </c>
+      <c r="D2588" t="n">
+        <v>3.11400008201599</v>
+      </c>
+      <c r="E2588" t="n">
+        <v>3.13100004196167</v>
+      </c>
+      <c r="F2588" t="n">
+        <v>3.39499998092651</v>
+      </c>
+      <c r="G2588" t="s">
+        <v>2086</v>
+      </c>
+      <c r="H2588" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2089" uniqueCount="2089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="2090">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6279,6 +6279,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.39000010490417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3659999370575</t>
   </si>
 </sst>
 </file>
@@ -73905,7 +73908,7 @@
     </row>
     <row r="2589">
       <c r="A2589" s="1" t="n">
-        <v>46091.6918171296</v>
+        <v>46091.3333333333</v>
       </c>
       <c r="B2589" t="n">
         <v>27584394</v>
@@ -73926,6 +73929,32 @@
         <v>2088</v>
       </c>
       <c r="H2589" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2590">
+      <c r="A2590" s="1" t="n">
+        <v>46092.6911921296</v>
+      </c>
+      <c r="B2590" t="n">
+        <v>26791236</v>
+      </c>
+      <c r="C2590" t="n">
+        <v>3.41700005531311</v>
+      </c>
+      <c r="D2590" t="n">
+        <v>3.32699990272522</v>
+      </c>
+      <c r="E2590" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="F2590" t="n">
+        <v>3.3659999370575</v>
+      </c>
+      <c r="G2590" t="s">
+        <v>2089</v>
+      </c>
+      <c r="H2590" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="2090">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="2091">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6282,6 +6282,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.3659999370575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28800010681152</t>
   </si>
 </sst>
 </file>
@@ -73934,7 +73937,7 @@
     </row>
     <row r="2590">
       <c r="A2590" s="1" t="n">
-        <v>46092.6911921296</v>
+        <v>46092.3333333333</v>
       </c>
       <c r="B2590" t="n">
         <v>26791236</v>
@@ -73955,6 +73958,32 @@
         <v>2089</v>
       </c>
       <c r="H2590" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2591">
+      <c r="A2591" s="1" t="n">
+        <v>46093.6911574074</v>
+      </c>
+      <c r="B2591" t="n">
+        <v>22316383</v>
+      </c>
+      <c r="C2591" t="n">
+        <v>3.34800004959106</v>
+      </c>
+      <c r="D2591" t="n">
+        <v>3.24699997901917</v>
+      </c>
+      <c r="E2591" t="n">
+        <v>3.34599995613098</v>
+      </c>
+      <c r="F2591" t="n">
+        <v>3.28800010681152</v>
+      </c>
+      <c r="G2591" t="s">
+        <v>2090</v>
+      </c>
+      <c r="H2591" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="2091">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="2093">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6285,6 +6285,12 @@
   </si>
   <si>
     <t xml:space="preserve">3.28800010681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36899995803833</t>
   </si>
 </sst>
 </file>
@@ -73963,7 +73969,7 @@
     </row>
     <row r="2591">
       <c r="A2591" s="1" t="n">
-        <v>46093.6911574074</v>
+        <v>46093.3333333333</v>
       </c>
       <c r="B2591" t="n">
         <v>22316383</v>
@@ -73984,6 +73990,56 @@
         <v>2090</v>
       </c>
       <c r="H2591" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2592">
+      <c r="A2592" s="1" t="n">
+        <v>46094.3333333333</v>
+      </c>
+      <c r="B2592" t="n">
+        <v>27213187</v>
+      </c>
+      <c r="C2592" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="D2592" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="E2592" t="n">
+        <v>3.30299997329712</v>
+      </c>
+      <c r="F2592"/>
+      <c r="G2592" t="s">
+        <v>2091</v>
+      </c>
+      <c r="H2592" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2593">
+      <c r="A2593" s="1" t="n">
+        <v>46094.6922222222</v>
+      </c>
+      <c r="B2593" t="n">
+        <v>27213187</v>
+      </c>
+      <c r="C2593" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="D2593" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="E2593" t="n">
+        <v>3.30299997329712</v>
+      </c>
+      <c r="F2593" t="n">
+        <v>3.36899995803833</v>
+      </c>
+      <c r="G2593" t="s">
+        <v>2092</v>
+      </c>
+      <c r="H2593" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="2093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="2094">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6287,10 +6287,13 @@
     <t xml:space="preserve">3.28800010681152</t>
   </si>
   <si>
+    <t xml:space="preserve">3.36899995803833</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">3.36899995803833</t>
+    <t xml:space="preserve">3.38199996948242</t>
   </si>
 </sst>
 </file>
@@ -74009,7 +74012,9 @@
       <c r="E2592" t="n">
         <v>3.30299997329712</v>
       </c>
-      <c r="F2592"/>
+      <c r="F2592" t="n">
+        <v>3.36899995803833</v>
+      </c>
       <c r="G2592" t="s">
         <v>2091</v>
       </c>
@@ -74019,27 +74024,51 @@
     </row>
     <row r="2593">
       <c r="A2593" s="1" t="n">
-        <v>46094.6922222222</v>
+        <v>46097.3333333333</v>
       </c>
       <c r="B2593" t="n">
-        <v>27213187</v>
+        <v>14047404</v>
       </c>
       <c r="C2593" t="n">
-        <v>3.40000009536743</v>
+        <v>3.39499998092651</v>
       </c>
       <c r="D2593" t="n">
-        <v>3.27999997138977</v>
+        <v>3.31599998474121</v>
       </c>
       <c r="E2593" t="n">
-        <v>3.30299997329712</v>
-      </c>
-      <c r="F2593" t="n">
-        <v>3.36899995803833</v>
-      </c>
+        <v>3.39000010490417</v>
+      </c>
+      <c r="F2593"/>
       <c r="G2593" t="s">
         <v>2092</v>
       </c>
       <c r="H2593" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2594">
+      <c r="A2594" s="1" t="n">
+        <v>46097.6911689815</v>
+      </c>
+      <c r="B2594" t="n">
+        <v>14047404</v>
+      </c>
+      <c r="C2594" t="n">
+        <v>3.39499998092651</v>
+      </c>
+      <c r="D2594" t="n">
+        <v>3.31599998474121</v>
+      </c>
+      <c r="E2594" t="n">
+        <v>3.39000010490417</v>
+      </c>
+      <c r="F2594" t="n">
+        <v>3.38199996948242</v>
+      </c>
+      <c r="G2594" t="s">
+        <v>2093</v>
+      </c>
+      <c r="H2594" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="2094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2095" uniqueCount="2095">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6290,10 +6290,13 @@
     <t xml:space="preserve">3.36899995803833</t>
   </si>
   <si>
+    <t xml:space="preserve">3.38199996948242</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">3.38199996948242</t>
+    <t xml:space="preserve">3.35800004005432</t>
   </si>
 </sst>
 </file>
@@ -74038,7 +74041,9 @@
       <c r="E2593" t="n">
         <v>3.39000010490417</v>
       </c>
-      <c r="F2593"/>
+      <c r="F2593" t="n">
+        <v>3.38199996948242</v>
+      </c>
       <c r="G2593" t="s">
         <v>2092</v>
       </c>
@@ -74048,27 +74053,51 @@
     </row>
     <row r="2594">
       <c r="A2594" s="1" t="n">
-        <v>46097.6911689815</v>
+        <v>46098.3333333333</v>
       </c>
       <c r="B2594" t="n">
-        <v>14047404</v>
+        <v>20227904</v>
       </c>
       <c r="C2594" t="n">
-        <v>3.39499998092651</v>
+        <v>3.41899991035461</v>
       </c>
       <c r="D2594" t="n">
-        <v>3.31599998474121</v>
+        <v>3.34100008010864</v>
       </c>
       <c r="E2594" t="n">
-        <v>3.39000010490417</v>
-      </c>
-      <c r="F2594" t="n">
-        <v>3.38199996948242</v>
-      </c>
+        <v>3.36500000953674</v>
+      </c>
+      <c r="F2594"/>
       <c r="G2594" t="s">
         <v>2093</v>
       </c>
       <c r="H2594" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2595">
+      <c r="A2595" s="1" t="n">
+        <v>46098.6912384259</v>
+      </c>
+      <c r="B2595" t="n">
+        <v>20227904</v>
+      </c>
+      <c r="C2595" t="n">
+        <v>3.41899991035461</v>
+      </c>
+      <c r="D2595" t="n">
+        <v>3.34100008010864</v>
+      </c>
+      <c r="E2595" t="n">
+        <v>3.36500000953674</v>
+      </c>
+      <c r="F2595" t="n">
+        <v>3.35800004005432</v>
+      </c>
+      <c r="G2595" t="s">
+        <v>2094</v>
+      </c>
+      <c r="H2595" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -6293,10 +6293,10 @@
     <t xml:space="preserve">3.38199996948242</t>
   </si>
   <si>
+    <t xml:space="preserve">3.35800004005432</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35800004005432</t>
   </si>
 </sst>
 </file>
@@ -74067,7 +74067,9 @@
       <c r="E2594" t="n">
         <v>3.36500000953674</v>
       </c>
-      <c r="F2594"/>
+      <c r="F2594" t="n">
+        <v>3.35800004005432</v>
+      </c>
       <c r="G2594" t="s">
         <v>2093</v>
       </c>
@@ -74077,27 +74079,51 @@
     </row>
     <row r="2595">
       <c r="A2595" s="1" t="n">
-        <v>46098.6912384259</v>
+        <v>46099.3333333333</v>
       </c>
       <c r="B2595" t="n">
-        <v>20227904</v>
+        <v>20008767</v>
       </c>
       <c r="C2595" t="n">
-        <v>3.41899991035461</v>
+        <v>3.42000007629395</v>
       </c>
       <c r="D2595" t="n">
-        <v>3.34100008010864</v>
+        <v>3.35899996757507</v>
       </c>
       <c r="E2595" t="n">
-        <v>3.36500000953674</v>
-      </c>
-      <c r="F2595" t="n">
-        <v>3.35800004005432</v>
-      </c>
+        <v>3.38499999046326</v>
+      </c>
+      <c r="F2595"/>
       <c r="G2595" t="s">
         <v>2094</v>
       </c>
       <c r="H2595" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2596">
+      <c r="A2596" s="1" t="n">
+        <v>46099.6933564815</v>
+      </c>
+      <c r="B2596" t="n">
+        <v>20008767</v>
+      </c>
+      <c r="C2596" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="D2596" t="n">
+        <v>3.35899996757507</v>
+      </c>
+      <c r="E2596" t="n">
+        <v>3.38499999046326</v>
+      </c>
+      <c r="F2596" t="n">
+        <v>3.38199996948242</v>
+      </c>
+      <c r="G2596" t="s">
+        <v>2092</v>
+      </c>
+      <c r="H2596" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2095" uniqueCount="2095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="2096">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6297,6 +6297,9 @@
   </si>
   <si>
     <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41100001335144</t>
   </si>
 </sst>
 </file>
@@ -74093,9 +74096,11 @@
       <c r="E2595" t="n">
         <v>3.38499999046326</v>
       </c>
-      <c r="F2595"/>
+      <c r="F2595" t="n">
+        <v>3.38199996948242</v>
+      </c>
       <c r="G2595" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="H2595" t="s">
         <v>9</v>
@@ -74103,27 +74108,51 @@
     </row>
     <row r="2596">
       <c r="A2596" s="1" t="n">
-        <v>46099.6933564815</v>
+        <v>46100.3333333333</v>
       </c>
       <c r="B2596" t="n">
-        <v>20008767</v>
+        <v>28980088</v>
       </c>
       <c r="C2596" t="n">
-        <v>3.42000007629395</v>
+        <v>3.42499995231628</v>
       </c>
       <c r="D2596" t="n">
-        <v>3.35899996757507</v>
+        <v>3.33800005912781</v>
       </c>
       <c r="E2596" t="n">
-        <v>3.38499999046326</v>
-      </c>
-      <c r="F2596" t="n">
-        <v>3.38199996948242</v>
-      </c>
+        <v>3.37199997901917</v>
+      </c>
+      <c r="F2596"/>
       <c r="G2596" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="H2596" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2597">
+      <c r="A2597" s="1" t="n">
+        <v>46100.6935416667</v>
+      </c>
+      <c r="B2597" t="n">
+        <v>28980088</v>
+      </c>
+      <c r="C2597" t="n">
+        <v>3.42499995231628</v>
+      </c>
+      <c r="D2597" t="n">
+        <v>3.33800005912781</v>
+      </c>
+      <c r="E2597" t="n">
+        <v>3.37199997901917</v>
+      </c>
+      <c r="F2597" t="n">
+        <v>3.41100001335144</v>
+      </c>
+      <c r="G2597" t="s">
+        <v>2095</v>
+      </c>
+      <c r="H2597" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="2096">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2097" uniqueCount="2097">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6296,10 +6296,13 @@
     <t xml:space="preserve">3.35800004005432</t>
   </si>
   <si>
+    <t xml:space="preserve">3.41100001335144</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">3.41100001335144</t>
+    <t xml:space="preserve">3.42000007629395</t>
   </si>
 </sst>
 </file>
@@ -74122,7 +74125,9 @@
       <c r="E2596" t="n">
         <v>3.37199997901917</v>
       </c>
-      <c r="F2596"/>
+      <c r="F2596" t="n">
+        <v>3.41100001335144</v>
+      </c>
       <c r="G2596" t="s">
         <v>2094</v>
       </c>
@@ -74132,27 +74137,51 @@
     </row>
     <row r="2597">
       <c r="A2597" s="1" t="n">
-        <v>46100.6935416667</v>
+        <v>46101.3333333333</v>
       </c>
       <c r="B2597" t="n">
-        <v>28980088</v>
+        <v>45524728</v>
       </c>
       <c r="C2597" t="n">
-        <v>3.42499995231628</v>
+        <v>3.47900009155273</v>
       </c>
       <c r="D2597" t="n">
-        <v>3.33800005912781</v>
+        <v>3.38000011444092</v>
       </c>
       <c r="E2597" t="n">
-        <v>3.37199997901917</v>
-      </c>
-      <c r="F2597" t="n">
-        <v>3.41100001335144</v>
-      </c>
+        <v>3.43499994277954</v>
+      </c>
+      <c r="F2597"/>
       <c r="G2597" t="s">
         <v>2095</v>
       </c>
       <c r="H2597" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2598">
+      <c r="A2598" s="1" t="n">
+        <v>46101.6936921296</v>
+      </c>
+      <c r="B2598" t="n">
+        <v>45524728</v>
+      </c>
+      <c r="C2598" t="n">
+        <v>3.47900009155273</v>
+      </c>
+      <c r="D2598" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="E2598" t="n">
+        <v>3.43499994277954</v>
+      </c>
+      <c r="F2598" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="G2598" t="s">
+        <v>2096</v>
+      </c>
+      <c r="H2598" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2101" uniqueCount="2101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="2102">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6315,6 +6315,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.91400003433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88899993896484</t>
   </si>
 </sst>
 </file>
@@ -74355,6 +74358,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2605">
+      <c r="A2605" s="1" t="n">
+        <v>46113.2916666667</v>
+      </c>
+      <c r="B2605" t="n">
+        <v>41033860</v>
+      </c>
+      <c r="C2605" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="D2605" t="n">
+        <v>3.82999992370605</v>
+      </c>
+      <c r="E2605" t="n">
+        <v>3.92899990081787</v>
+      </c>
+      <c r="F2605" t="n">
+        <v>3.88899993896484</v>
+      </c>
+      <c r="G2605" t="s">
+        <v>2101</v>
+      </c>
+      <c r="H2605" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="2104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2105" uniqueCount="2105">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6324,6 +6324,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.02500009536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96799993515015</t>
   </si>
 </sst>
 </file>
@@ -74416,6 +74419,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2607">
+      <c r="A2607" s="1" t="n">
+        <v>46119.6508449074</v>
+      </c>
+      <c r="B2607" t="n">
+        <v>36390550</v>
+      </c>
+      <c r="C2607" t="n">
+        <v>4.07800006866455</v>
+      </c>
+      <c r="D2607" t="n">
+        <v>3.95600008964539</v>
+      </c>
+      <c r="E2607" t="n">
+        <v>4.04500007629395</v>
+      </c>
+      <c r="F2607" t="n">
+        <v>3.96799993515015</v>
+      </c>
+      <c r="G2607" t="s">
+        <v>2104</v>
+      </c>
+      <c r="H2607" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2109" uniqueCount="2109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2110" uniqueCount="2110">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6339,6 +6339,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.15500020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17600011825562</t>
   </si>
 </sst>
 </file>
@@ -74561,6 +74564,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2612">
+      <c r="A2612" s="1" t="n">
+        <v>46126.2916666667</v>
+      </c>
+      <c r="B2612" t="n">
+        <v>39125632</v>
+      </c>
+      <c r="C2612" t="n">
+        <v>4.2189998626709</v>
+      </c>
+      <c r="D2612" t="n">
+        <v>4.1230001449585</v>
+      </c>
+      <c r="E2612" t="n">
+        <v>4.19000005722046</v>
+      </c>
+      <c r="F2612" t="n">
+        <v>4.17600011825562</v>
+      </c>
+      <c r="G2612" t="s">
+        <v>2109</v>
+      </c>
+      <c r="H2612" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2110" uniqueCount="2110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2111" uniqueCount="2111">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6342,6 +6342,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.1399998664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09200000762939</t>
   </si>
 </sst>
 </file>
@@ -74616,6 +74619,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2614">
+      <c r="A2614" s="1" t="n">
+        <v>46128.2916666667</v>
+      </c>
+      <c r="B2614" t="n">
+        <v>21706104</v>
+      </c>
+      <c r="C2614" t="n">
+        <v>4.16300010681152</v>
+      </c>
+      <c r="D2614" t="n">
+        <v>4.07800006866455</v>
+      </c>
+      <c r="E2614" t="n">
+        <v>4.14499998092651</v>
+      </c>
+      <c r="F2614" t="n">
+        <v>4.09200000762939</v>
+      </c>
+      <c r="G2614" t="s">
+        <v>2110</v>
+      </c>
+      <c r="H2614" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2113" uniqueCount="2113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2114" uniqueCount="2114">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6351,6 +6351,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.99600005149841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92000007629395</t>
   </si>
 </sst>
 </file>
@@ -74703,6 +74706,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2617">
+      <c r="A2617" s="1" t="n">
+        <v>46133.2916666667</v>
+      </c>
+      <c r="B2617" t="n">
+        <v>21459103</v>
+      </c>
+      <c r="C2617" t="n">
+        <v>3.98000001907349</v>
+      </c>
+      <c r="D2617" t="n">
+        <v>3.90300011634827</v>
+      </c>
+      <c r="E2617" t="n">
+        <v>3.97000002861023</v>
+      </c>
+      <c r="F2617" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="G2617" t="s">
+        <v>2113</v>
+      </c>
+      <c r="H2617" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2114" uniqueCount="2114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2115" uniqueCount="2115">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6354,6 +6354,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.92000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1729998588562</t>
   </si>
 </sst>
 </file>
@@ -74732,6 +74735,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2618">
+      <c r="A2618" s="1" t="n">
+        <v>46134.2916666667</v>
+      </c>
+      <c r="B2618" t="n">
+        <v>69651733</v>
+      </c>
+      <c r="C2618" t="n">
+        <v>4.24599981307983</v>
+      </c>
+      <c r="D2618" t="n">
+        <v>3.89199995994568</v>
+      </c>
+      <c r="E2618" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2618" t="n">
+        <v>4.1729998588562</v>
+      </c>
+      <c r="G2618" t="s">
+        <v>2114</v>
+      </c>
+      <c r="H2618" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="2117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="2118">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6363,6 +6363,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.22200012207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33699989318848</t>
   </si>
 </sst>
 </file>
@@ -74793,6 +74796,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2620">
+      <c r="A2620" s="1" t="n">
+        <v>46136.2916666667</v>
+      </c>
+      <c r="B2620" t="n">
+        <v>43534230</v>
+      </c>
+      <c r="C2620" t="n">
+        <v>4.36499977111816</v>
+      </c>
+      <c r="D2620" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="E2620" t="n">
+        <v>4.23999977111816</v>
+      </c>
+      <c r="F2620" t="n">
+        <v>4.33699989318848</v>
+      </c>
+      <c r="G2620" t="s">
+        <v>2117</v>
+      </c>
+      <c r="H2620" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="2120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="2121">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6372,6 +6372,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.58500003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53299999237061</t>
   </si>
 </sst>
 </file>
@@ -74880,6 +74883,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2623">
+      <c r="A2623" s="1" t="n">
+        <v>46141.2916666667</v>
+      </c>
+      <c r="B2623" t="n">
+        <v>45922976</v>
+      </c>
+      <c r="C2623" t="n">
+        <v>4.79500007629395</v>
+      </c>
+      <c r="D2623" t="n">
+        <v>4.53299999237061</v>
+      </c>
+      <c r="E2623" t="n">
+        <v>4.60300016403198</v>
+      </c>
+      <c r="F2623" t="n">
+        <v>4.53299999237061</v>
+      </c>
+      <c r="G2623" t="s">
+        <v>2120</v>
+      </c>
+      <c r="H2623" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="2124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="2125">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6384,6 +6384,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.65199995040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59200000762939</t>
   </si>
 </sst>
 </file>
@@ -74996,6 +74999,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2627">
+      <c r="A2627" s="1" t="n">
+        <v>46148.2916666667</v>
+      </c>
+      <c r="B2627" t="n">
+        <v>32163076</v>
+      </c>
+      <c r="C2627" t="n">
+        <v>4.68800020217896</v>
+      </c>
+      <c r="D2627" t="n">
+        <v>4.48000001907349</v>
+      </c>
+      <c r="E2627" t="n">
+        <v>4.66200017929077</v>
+      </c>
+      <c r="F2627" t="n">
+        <v>4.59200000762939</v>
+      </c>
+      <c r="G2627" t="s">
+        <v>2124</v>
+      </c>
+      <c r="H2627" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="2125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="2126">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6387,6 +6387,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.59200000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33400011062622</t>
   </si>
 </sst>
 </file>
@@ -75025,6 +75028,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2628">
+      <c r="A2628" s="1" t="n">
+        <v>46149.2916666667</v>
+      </c>
+      <c r="B2628" t="n">
+        <v>41623155</v>
+      </c>
+      <c r="C2628" t="n">
+        <v>4.55800008773804</v>
+      </c>
+      <c r="D2628" t="n">
+        <v>4.27299976348877</v>
+      </c>
+      <c r="E2628" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="F2628" t="n">
+        <v>4.33400011062622</v>
+      </c>
+      <c r="G2628" t="s">
+        <v>2125</v>
+      </c>
+      <c r="H2628" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="2126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2127" uniqueCount="2127">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6390,6 +6390,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.33400011062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30399990081787</t>
   </si>
 </sst>
 </file>
@@ -75054,6 +75057,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2629">
+      <c r="A2629" s="1" t="n">
+        <v>46150.2916666667</v>
+      </c>
+      <c r="B2629" t="n">
+        <v>15053522</v>
+      </c>
+      <c r="C2629" t="n">
+        <v>4.40500020980835</v>
+      </c>
+      <c r="D2629" t="n">
+        <v>4.29099988937378</v>
+      </c>
+      <c r="E2629" t="n">
+        <v>4.36800003051758</v>
+      </c>
+      <c r="F2629" t="n">
+        <v>4.30399990081787</v>
+      </c>
+      <c r="G2629" t="s">
+        <v>2126</v>
+      </c>
+      <c r="H2629" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2127" uniqueCount="2127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="2128">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6393,6 +6393,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.30399990081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43499994277954</t>
   </si>
 </sst>
 </file>
@@ -75083,6 +75086,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2630">
+      <c r="A2630" s="1" t="n">
+        <v>46153.2916666667</v>
+      </c>
+      <c r="B2630" t="n">
+        <v>18653075</v>
+      </c>
+      <c r="C2630" t="n">
+        <v>4.44799995422363</v>
+      </c>
+      <c r="D2630" t="n">
+        <v>4.34100008010864</v>
+      </c>
+      <c r="E2630" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="F2630" t="n">
+        <v>4.43499994277954</v>
+      </c>
+      <c r="G2630" t="s">
+        <v>2127</v>
+      </c>
+      <c r="H2630" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="2128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2129" uniqueCount="2129">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6396,6 +6396,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.46199989318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59000015258789</t>
   </si>
 </sst>
 </file>
@@ -75138,6 +75141,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2632">
+      <c r="A2632" s="1" t="n">
+        <v>46155.2916666667</v>
+      </c>
+      <c r="B2632" t="n">
+        <v>19730914</v>
+      </c>
+      <c r="C2632" t="n">
+        <v>4.62599992752075</v>
+      </c>
+      <c r="D2632" t="n">
+        <v>4.47100019454956</v>
+      </c>
+      <c r="E2632" t="n">
+        <v>4.48999977111816</v>
+      </c>
+      <c r="F2632" t="n">
+        <v>4.59000015258789</v>
+      </c>
+      <c r="G2632" t="s">
+        <v>2128</v>
+      </c>
+      <c r="H2632" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="2131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="2132">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -6405,6 +6405,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.65799999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65500020980835</t>
   </si>
 </sst>
 </file>
@@ -75199,6 +75202,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2634">
+      <c r="A2634" s="1" t="n">
+        <v>46157.2916666667</v>
+      </c>
+      <c r="B2634" t="n">
+        <v>30280243</v>
+      </c>
+      <c r="C2634" t="n">
+        <v>4.72499990463257</v>
+      </c>
+      <c r="D2634" t="n">
+        <v>4.6230001449585</v>
+      </c>
+      <c r="E2634" t="n">
+        <v>4.65000009536743</v>
+      </c>
+      <c r="F2634" t="n">
+        <v>4.65500020980835</v>
+      </c>
+      <c r="G2634" t="s">
+        <v>2131</v>
+      </c>
+      <c r="H2634" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2133" uniqueCount="2133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2134" uniqueCount="2134">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">SPM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5791053771973</t>
+    <t xml:space="preserve">20.5791072845459</t>
   </si>
   <si>
     <t xml:space="preserve">19.7946090698242</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4443855285645</t>
+    <t xml:space="preserve">19.4443836212158</t>
   </si>
   <si>
     <t xml:space="preserve">18.9540729522705</t>
@@ -65,16 +65,16 @@
     <t xml:space="preserve">19.65452003479</t>
   </si>
   <si>
-    <t xml:space="preserve">19.668529510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5478134155273</t>
+    <t xml:space="preserve">19.6685276031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.547815322876</t>
   </si>
   <si>
     <t xml:space="preserve">17.5952072143555</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5811958312988</t>
+    <t xml:space="preserve">17.5811977386475</t>
   </si>
   <si>
     <t xml:space="preserve">15.7460279464722</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">14.8214406967163</t>
   </si>
   <si>
-    <t xml:space="preserve">11.773099899292</t>
+    <t xml:space="preserve">11.7730989456177</t>
   </si>
   <si>
     <t xml:space="preserve">13.9552736282349</t>
@@ -95,16 +95,16 @@
     <t xml:space="preserve">12.2414674758911</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6087112426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6977405548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7311267852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3082399368286</t>
+    <t xml:space="preserve">12.6087121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6977415084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7311277389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.30823802948</t>
   </si>
   <si>
     <t xml:space="preserve">11.9743804931641</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">8.64692783355713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16617202758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0571117401123</t>
+    <t xml:space="preserve">8.16617107391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05711078643799</t>
   </si>
   <si>
     <t xml:space="preserve">7.08892250061035</t>
@@ -131,13 +131,13 @@
     <t xml:space="preserve">6.70832395553589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74393558502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87747955322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51180982589722</t>
+    <t xml:space="preserve">6.74393510818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87747859954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51181030273438</t>
   </si>
   <si>
     <t xml:space="preserve">7.70322132110596</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">7.7900242805481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91243982315063</t>
+    <t xml:space="preserve">7.91243886947632</t>
   </si>
   <si>
     <t xml:space="preserve">7.67873859405518</t>
@@ -158,22 +158,22 @@
     <t xml:space="preserve">8.01259613037109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45774078369141</t>
+    <t xml:space="preserve">8.45774173736572</t>
   </si>
   <si>
     <t xml:space="preserve">8.64025020599365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58015537261963</t>
+    <t xml:space="preserve">8.58015632629395</t>
   </si>
   <si>
     <t xml:space="preserve">8.83611392974854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47712135314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07714366912842</t>
+    <t xml:space="preserve">9.47712230682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0771427154541</t>
   </si>
   <si>
     <t xml:space="preserve">8.31306934356689</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">8.56235027313232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58683395385742</t>
+    <t xml:space="preserve">8.58683204650879</t>
   </si>
   <si>
     <t xml:space="preserve">8.29526329040527</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">8.21291255950928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3175220489502</t>
+    <t xml:space="preserve">8.31752109527588</t>
   </si>
   <si>
     <t xml:space="preserve">8.44438743591309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15726947784424</t>
+    <t xml:space="preserve">8.15726852416992</t>
   </si>
   <si>
     <t xml:space="preserve">8.23071765899658</t>
@@ -215,16 +215,16 @@
     <t xml:space="preserve">7.34488010406494</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92356824874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8367657661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65870809555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32262372970581</t>
+    <t xml:space="preserve">7.92356872558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83676528930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65870714187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32262420654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.89973592758179</t>
@@ -233,28 +233,28 @@
     <t xml:space="preserve">7.03327894210815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75061273574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27365732192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5674524307251</t>
+    <t xml:space="preserve">6.75061225891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27365779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56745290756226</t>
   </si>
   <si>
     <t xml:space="preserve">7.8634729385376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09939956665039</t>
+    <t xml:space="preserve">8.09940052032471</t>
   </si>
   <si>
     <t xml:space="preserve">7.86569976806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27523136138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29303741455078</t>
+    <t xml:space="preserve">8.27523231506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2930383682251</t>
   </si>
   <si>
     <t xml:space="preserve">8.45551586151123</t>
@@ -269,19 +269,19 @@
     <t xml:space="preserve">8.33310031890869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46886920928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62912178039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68188762664795</t>
+    <t xml:space="preserve">8.46887016296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62912082672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68188858032227</t>
   </si>
   <si>
     <t xml:space="preserve">9.30351543426514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8227596282959</t>
+    <t xml:space="preserve">8.82275867462158</t>
   </si>
   <si>
     <t xml:space="preserve">8.54009246826172</t>
@@ -302,28 +302,28 @@
     <t xml:space="preserve">8.14836502075195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39542007446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31974601745605</t>
+    <t xml:space="preserve">8.26855373382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39542102813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31974697113037</t>
   </si>
   <si>
     <t xml:space="preserve">8.27968311309814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98588800430298</t>
+    <t xml:space="preserve">7.98588752746582</t>
   </si>
   <si>
     <t xml:space="preserve">7.99701690673828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9168906211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10607814788818</t>
+    <t xml:space="preserve">7.91689109802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10607719421387</t>
   </si>
   <si>
     <t xml:space="preserve">8.3976469039917</t>
@@ -335,34 +335,34 @@
     <t xml:space="preserve">8.18842887878418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02372455596924</t>
+    <t xml:space="preserve">8.02372550964355</t>
   </si>
   <si>
     <t xml:space="preserve">7.77889585494995</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44661331176758</t>
+    <t xml:space="preserve">8.44661235809326</t>
   </si>
   <si>
     <t xml:space="preserve">8.85837173461914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6736364364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22849178314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72325277328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73660755157471</t>
+    <t xml:space="preserve">8.67363548278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22849273681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72325325012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73660707473755</t>
   </si>
   <si>
     <t xml:space="preserve">7.96808242797852</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78112125396729</t>
+    <t xml:space="preserve">7.78112173080444</t>
   </si>
   <si>
     <t xml:space="preserve">8.69144153594971</t>
@@ -377,10 +377,10 @@
     <t xml:space="preserve">9.00749397277832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05933570861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59193658828735</t>
+    <t xml:space="preserve">8.05933666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5919361114502</t>
   </si>
   <si>
     <t xml:space="preserve">7.78557395935059</t>
@@ -398,25 +398,25 @@
     <t xml:space="preserve">8.51783657073975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.823410987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01704883575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37093734741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71147346496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03420448303223</t>
+    <t xml:space="preserve">7.82341051101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01704788208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37093830108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71147441864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03420257568359</t>
   </si>
   <si>
     <t xml:space="preserve">9.25454902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32577228546143</t>
+    <t xml:space="preserve">9.32577323913574</t>
   </si>
   <si>
     <t xml:space="preserve">9.20113182067871</t>
@@ -428,25 +428,25 @@
     <t xml:space="preserve">9.55947303771973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73307800292969</t>
+    <t xml:space="preserve">9.733078956604</t>
   </si>
   <si>
     <t xml:space="preserve">9.6284704208374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68856620788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18555164337158</t>
+    <t xml:space="preserve">9.68856525421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1855525970459</t>
   </si>
   <si>
     <t xml:space="preserve">9.48157215118408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78427124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82721138000488</t>
+    <t xml:space="preserve">9.78427219390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8272123336792</t>
   </si>
   <si>
     <t xml:space="preserve">8.49335289001465</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">8.52228736877441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77824592590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87172508239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7760181427002</t>
+    <t xml:space="preserve">8.778244972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87172603607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77601909637451</t>
   </si>
   <si>
     <t xml:space="preserve">9.0119457244873</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">9.25677490234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03642845153809</t>
+    <t xml:space="preserve">9.03643035888672</t>
   </si>
   <si>
     <t xml:space="preserve">8.85169410705566</t>
@@ -494,43 +494,43 @@
     <t xml:space="preserve">9.26122665405273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21671199798584</t>
+    <t xml:space="preserve">9.21671295166016</t>
   </si>
   <si>
     <t xml:space="preserve">9.09652328491211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25900077819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08094310760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16997241973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14548778533936</t>
+    <t xml:space="preserve">9.25899982452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0809440612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16997337341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14548873901367</t>
   </si>
   <si>
     <t xml:space="preserve">9.09207153320312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14771556854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27235412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2078104019165</t>
+    <t xml:space="preserve">9.14771461486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27235507965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20780944824219</t>
   </si>
   <si>
     <t xml:space="preserve">9.23451805114746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8027286529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37761497497559</t>
+    <t xml:space="preserve">8.80272769927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3776159286499</t>
   </si>
   <si>
     <t xml:space="preserve">8.38874340057373</t>
@@ -542,16 +542,16 @@
     <t xml:space="preserve">8.05043411254883</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79225015640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89463424682617</t>
+    <t xml:space="preserve">7.79225063323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89463376998901</t>
   </si>
   <si>
     <t xml:space="preserve">8.29971504211426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23516845703125</t>
+    <t xml:space="preserve">8.23516941070557</t>
   </si>
   <si>
     <t xml:space="preserve">7.90798759460449</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">7.76776790618896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73883295059204</t>
+    <t xml:space="preserve">7.7388334274292</t>
   </si>
   <si>
     <t xml:space="preserve">8.38429164886475</t>
@@ -569,16 +569,16 @@
     <t xml:space="preserve">8.42880630493164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59128379821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72482776641846</t>
+    <t xml:space="preserve">8.59128475189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72482872009277</t>
   </si>
   <si>
     <t xml:space="preserve">8.66473293304443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94294929504395</t>
+    <t xml:space="preserve">8.94294834136963</t>
   </si>
   <si>
     <t xml:space="preserve">8.92291736602783</t>
@@ -593,19 +593,19 @@
     <t xml:space="preserve">9.19445610046387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21448612213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58840847015381</t>
+    <t xml:space="preserve">9.21448516845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58840751647949</t>
   </si>
   <si>
     <t xml:space="preserve">9.71082210540771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31464385986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34645557403564</t>
+    <t xml:space="preserve">9.31464290618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34645462036133</t>
   </si>
   <si>
     <t xml:space="preserve">8.17730140686035</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">9.00304317474365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06536293029785</t>
+    <t xml:space="preserve">9.06536388397217</t>
   </si>
   <si>
     <t xml:space="preserve">8.94072246551514</t>
@@ -641,10 +641,10 @@
     <t xml:space="preserve">8.97188186645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94517421722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06313800811768</t>
+    <t xml:space="preserve">8.9451732635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06313705444336</t>
   </si>
   <si>
     <t xml:space="preserve">9.16329479217529</t>
@@ -653,10 +653,10 @@
     <t xml:space="preserve">8.92514228820801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61131477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43928527832031</t>
+    <t xml:space="preserve">8.61131572723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.439284324646</t>
   </si>
   <si>
     <t xml:space="preserve">9.72640228271484</t>
@@ -671,19 +671,19 @@
     <t xml:space="preserve">10.182674407959</t>
   </si>
   <si>
-    <t xml:space="preserve">10.316219329834</t>
+    <t xml:space="preserve">10.3162183761597</t>
   </si>
   <si>
     <t xml:space="preserve">10.1159038543701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68411445617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96677875518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4831466674805</t>
+    <t xml:space="preserve">9.68411350250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9667797088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4831476211548</t>
   </si>
   <si>
     <t xml:space="preserve">10.5721769332886</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">11.3845643997192</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3511800765991</t>
+    <t xml:space="preserve">11.3511781692505</t>
   </si>
   <si>
     <t xml:space="preserve">10.9883871078491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2844076156616</t>
+    <t xml:space="preserve">11.2844085693359</t>
   </si>
   <si>
     <t xml:space="preserve">11.417950630188</t>
@@ -716,25 +716,25 @@
     <t xml:space="preserve">11.7295513153076</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9076099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4417819976807</t>
+    <t xml:space="preserve">11.9076108932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.441782951355</t>
   </si>
   <si>
     <t xml:space="preserve">12.3972682952881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4195251464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1858253479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8074531555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3066654205322</t>
+    <t xml:space="preserve">12.4195261001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1858243942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8074522018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3066644668579</t>
   </si>
   <si>
     <t xml:space="preserve">11.6182651519775</t>
@@ -746,31 +746,31 @@
     <t xml:space="preserve">11.4068212509155</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9060344696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1397342681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1619930267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1731204986572</t>
+    <t xml:space="preserve">10.9060354232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1397352218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1619939804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1731214523315</t>
   </si>
   <si>
     <t xml:space="preserve">11.0351257324219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0840921401978</t>
+    <t xml:space="preserve">11.0840930938721</t>
   </si>
   <si>
     <t xml:space="preserve">11.7963228225708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6405220031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5960083007812</t>
+    <t xml:space="preserve">11.6405229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5960092544556</t>
   </si>
   <si>
     <t xml:space="preserve">10.817006111145</t>
@@ -782,13 +782,13 @@
     <t xml:space="preserve">10.5276622772217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2383184432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4141492843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2516717910767</t>
+    <t xml:space="preserve">10.2383193969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4141502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.251672744751</t>
   </si>
   <si>
     <t xml:space="preserve">10.2205123901367</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">10.0825185775757</t>
   </si>
   <si>
-    <t xml:space="preserve">10.39857006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3807640075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6589784622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3651847839355</t>
+    <t xml:space="preserve">10.3985710144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3807649612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6589794158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3651838302612</t>
   </si>
   <si>
     <t xml:space="preserve">10.0891952514648</t>
@@ -815,10 +815,10 @@
     <t xml:space="preserve">10.5031795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2939615249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3184432983398</t>
+    <t xml:space="preserve">10.2939624786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3184442520142</t>
   </si>
   <si>
     <t xml:space="preserve">10.3629589080811</t>
@@ -845,61 +845,61 @@
     <t xml:space="preserve">9.45486450195312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48602390289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34803009033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28125762939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98968887329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08762073516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96520519256592</t>
+    <t xml:space="preserve">9.48602485656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34802913665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28125858306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9896879196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08761978149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96520614624023</t>
   </si>
   <si>
     <t xml:space="preserve">9.06091117858887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15439224243164</t>
+    <t xml:space="preserve">9.15439128875732</t>
   </si>
   <si>
     <t xml:space="preserve">9.01639652252197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08539485931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98523712158203</t>
+    <t xml:space="preserve">9.08539390563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98523807525635</t>
   </si>
   <si>
     <t xml:space="preserve">8.97856044769287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00526809692383</t>
+    <t xml:space="preserve">9.00526714324951</t>
   </si>
   <si>
     <t xml:space="preserve">9.39254379272461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4615421295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59063243865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47044467926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77982044219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49047565460205</t>
+    <t xml:space="preserve">9.46154117584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59063339233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47044563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77981853485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49047470092773</t>
   </si>
   <si>
     <t xml:space="preserve">9.51050758361816</t>
@@ -911,19 +911,19 @@
     <t xml:space="preserve">9.32799816131592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33022403717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12990856170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10542678833008</t>
+    <t xml:space="preserve">9.33022308349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12990951538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10542583465576</t>
   </si>
   <si>
     <t xml:space="preserve">8.87617683410645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93626976013184</t>
+    <t xml:space="preserve">8.93627071380615</t>
   </si>
   <si>
     <t xml:space="preserve">8.73818206787109</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">9.20558452606201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2033576965332</t>
+    <t xml:space="preserve">9.20335865020752</t>
   </si>
   <si>
     <t xml:space="preserve">8.80495357513428</t>
@@ -950,13 +950,13 @@
     <t xml:space="preserve">8.74708557128906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87840175628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89620780944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90288543701172</t>
+    <t xml:space="preserve">8.87840270996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89620876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9028844833374</t>
   </si>
   <si>
     <t xml:space="preserve">8.90065956115723</t>
@@ -977,22 +977,22 @@
     <t xml:space="preserve">8.69366836547852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86282253265381</t>
+    <t xml:space="preserve">8.86282348632812</t>
   </si>
   <si>
     <t xml:space="preserve">8.47554683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30194091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12833499908447</t>
+    <t xml:space="preserve">8.30193996429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12833404541016</t>
   </si>
   <si>
     <t xml:space="preserve">8.0348539352417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99033880233765</t>
+    <t xml:space="preserve">7.99033975601196</t>
   </si>
   <si>
     <t xml:space="preserve">7.95472764968872</t>
@@ -1001,10 +1001,10 @@
     <t xml:space="preserve">7.66093349456787</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73215675354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69209384918213</t>
+    <t xml:space="preserve">7.73215579986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69209432601929</t>
   </si>
   <si>
     <t xml:space="preserve">7.65648126602173</t>
@@ -1022,25 +1022,25 @@
     <t xml:space="preserve">7.34042882919312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19798278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21133756637573</t>
+    <t xml:space="preserve">7.1979832649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21133708953857</t>
   </si>
   <si>
     <t xml:space="preserve">7.18017673492432</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08224534988403</t>
+    <t xml:space="preserve">7.08224582672119</t>
   </si>
   <si>
     <t xml:space="preserve">7.16237115859985</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22914218902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31817197799683</t>
+    <t xml:space="preserve">7.22914266586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31817245483398</t>
   </si>
   <si>
     <t xml:space="preserve">7.23804569244385</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">7.42055463790894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69654512405396</t>
+    <t xml:space="preserve">7.6965446472168</t>
   </si>
   <si>
     <t xml:space="preserve">7.48732662200928</t>
@@ -1058,46 +1058,46 @@
     <t xml:space="preserve">7.46061706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46952104568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43390941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74551010131836</t>
+    <t xml:space="preserve">7.46952056884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43390846252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7455096244812</t>
   </si>
   <si>
     <t xml:space="preserve">7.85679721832275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66983556747437</t>
+    <t xml:space="preserve">7.66983604431152</t>
   </si>
   <si>
     <t xml:space="preserve">7.55854988098145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54964685440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47842407226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61196708679199</t>
+    <t xml:space="preserve">7.54964637756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47842311859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61196756362915</t>
   </si>
   <si>
     <t xml:space="preserve">7.50958395004272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59416103363037</t>
+    <t xml:space="preserve">7.59416151046753</t>
   </si>
   <si>
     <t xml:space="preserve">7.70989847183228</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70099544525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64757823944092</t>
+    <t xml:space="preserve">7.70099496841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64757966995239</t>
   </si>
   <si>
     <t xml:space="preserve">7.58525800704956</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">7.6520299911499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67428731918335</t>
+    <t xml:space="preserve">7.67428636550903</t>
   </si>
   <si>
     <t xml:space="preserve">7.60306406021118</t>
@@ -1115,13 +1115,13 @@
     <t xml:space="preserve">7.57190418243408</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50513219833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24249744415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28701162338257</t>
+    <t xml:space="preserve">7.50513172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24249792098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28701210021973</t>
   </si>
   <si>
     <t xml:space="preserve">7.26475477218628</t>
@@ -1133,16 +1133,16 @@
     <t xml:space="preserve">7.30036592483521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16682243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95315408706665</t>
+    <t xml:space="preserve">7.16682195663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95315361022949</t>
   </si>
   <si>
     <t xml:space="preserve">6.75283861160278</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82851314544678</t>
+    <t xml:space="preserve">6.82851362228394</t>
   </si>
   <si>
     <t xml:space="preserve">6.8151593208313</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">6.9397988319397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86857604980469</t>
+    <t xml:space="preserve">6.86857557296753</t>
   </si>
   <si>
     <t xml:space="preserve">6.88192987442017</t>
@@ -1166,64 +1166,64 @@
     <t xml:space="preserve">7.1000509262085</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22469139099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05998802185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29591464996338</t>
+    <t xml:space="preserve">7.22469091415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05998849868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29591417312622</t>
   </si>
   <si>
     <t xml:space="preserve">7.44281196594238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55409908294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47397232055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66538381576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07491683959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07046508789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06601524353027</t>
+    <t xml:space="preserve">7.55409860610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4739727973938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6653847694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07491779327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07046604156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06601428985596</t>
   </si>
   <si>
     <t xml:space="preserve">8.1194314956665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03040218353271</t>
+    <t xml:space="preserve">8.03040313720703</t>
   </si>
   <si>
     <t xml:space="preserve">8.12388324737549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93692302703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15504264831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1149787902832</t>
+    <t xml:space="preserve">7.93692350387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15504360198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11497974395752</t>
   </si>
   <si>
     <t xml:space="preserve">7.82118511199951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77221870422363</t>
+    <t xml:space="preserve">7.77221822738647</t>
   </si>
   <si>
     <t xml:space="preserve">7.84789323806763</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91021347045898</t>
+    <t xml:space="preserve">7.91021299362183</t>
   </si>
   <si>
     <t xml:space="preserve">7.56300115585327</t>
@@ -1232,19 +1232,19 @@
     <t xml:space="preserve">7.38939476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4294581413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02150058746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71435022354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64312696456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99479150772095</t>
+    <t xml:space="preserve">7.42945718765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02149963378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7143497467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64312648773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99479198455811</t>
   </si>
   <si>
     <t xml:space="preserve">8.45328998565674</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">8.55567264556885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70256996154785</t>
+    <t xml:space="preserve">8.70257091522217</t>
   </si>
   <si>
     <t xml:space="preserve">8.59573554992676</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">8.4176778793335</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62532186508179</t>
+    <t xml:space="preserve">7.62532234191895</t>
   </si>
   <si>
     <t xml:space="preserve">7.93247127532959</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">7.90576267242432</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84344148635864</t>
+    <t xml:space="preserve">7.84344244003296</t>
   </si>
   <si>
     <t xml:space="preserve">7.62977266311646</t>
@@ -1283,22 +1283,22 @@
     <t xml:space="preserve">7.4917778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44726371765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63422441482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40274810791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7499623298645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07936763763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28858661651611</t>
+    <t xml:space="preserve">7.44726324081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6342248916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40274858474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74996280670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07936859130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2885856628418</t>
   </si>
   <si>
     <t xml:space="preserve">8.52451324462891</t>
@@ -1307,19 +1307,19 @@
     <t xml:space="preserve">8.47109508514404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50670719146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5022554397583</t>
+    <t xml:space="preserve">8.50670623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50225639343262</t>
   </si>
   <si>
     <t xml:space="preserve">8.76934242248535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7604398727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65805721282959</t>
+    <t xml:space="preserve">8.76043891906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65805625915527</t>
   </si>
   <si>
     <t xml:space="preserve">8.97410869598389</t>
@@ -1349,16 +1349,16 @@
     <t xml:space="preserve">9.04087924957275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83833980560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51560974121094</t>
+    <t xml:space="preserve">8.83833885192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51561069488525</t>
   </si>
   <si>
     <t xml:space="preserve">8.39319515228271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4199047088623</t>
+    <t xml:space="preserve">8.41990375518799</t>
   </si>
   <si>
     <t xml:space="preserve">8.24852466583252</t>
@@ -1370,58 +1370,58 @@
     <t xml:space="preserve">7.39162158966064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49622964859009</t>
+    <t xml:space="preserve">7.49623012542725</t>
   </si>
   <si>
     <t xml:space="preserve">7.5785813331604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60083818435669</t>
+    <t xml:space="preserve">7.60083866119385</t>
   </si>
   <si>
     <t xml:space="preserve">7.6409010887146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83453989028931</t>
+    <t xml:space="preserve">7.83453893661499</t>
   </si>
   <si>
     <t xml:space="preserve">7.76331663131714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50068092346191</t>
+    <t xml:space="preserve">7.50068044662476</t>
   </si>
   <si>
     <t xml:space="preserve">7.5229377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29368877410889</t>
+    <t xml:space="preserve">7.29368829727173</t>
   </si>
   <si>
     <t xml:space="preserve">7.59861183166504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75663900375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38049173355103</t>
+    <t xml:space="preserve">7.75663948059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38049268722534</t>
   </si>
   <si>
     <t xml:space="preserve">7.36936330795288</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43613433837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25585174560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37826681137085</t>
+    <t xml:space="preserve">7.43613481521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25585126876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37826633453369</t>
   </si>
   <si>
     <t xml:space="preserve">7.47619819641113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23582029342651</t>
+    <t xml:space="preserve">7.23581981658936</t>
   </si>
   <si>
     <t xml:space="preserve">7.25139999389648</t>
@@ -1433,13 +1433,13 @@
     <t xml:space="preserve">7.16459703445435</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07111740112305</t>
+    <t xml:space="preserve">7.07111692428589</t>
   </si>
   <si>
     <t xml:space="preserve">6.95537948608398</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90863943099976</t>
+    <t xml:space="preserve">6.9086389541626</t>
   </si>
   <si>
     <t xml:space="preserve">7.1111798286438</t>
@@ -1457,16 +1457,16 @@
     <t xml:space="preserve">7.19130516052246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18907976150513</t>
+    <t xml:space="preserve">7.18907928466797</t>
   </si>
   <si>
     <t xml:space="preserve">7.48064947128296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41610383987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99766778945923</t>
+    <t xml:space="preserve">7.41610431671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99766731262207</t>
   </si>
   <si>
     <t xml:space="preserve">7.00879621505737</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">7.15791940689087</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14679098129272</t>
+    <t xml:space="preserve">7.14679145812988</t>
   </si>
   <si>
     <t xml:space="preserve">7.58303260803223</t>
@@ -1499,13 +1499,13 @@
     <t xml:space="preserve">8.94740009307861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37539005279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19065380096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80115365982056</t>
+    <t xml:space="preserve">8.37538909912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19065475463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80115413665771</t>
   </si>
   <si>
     <t xml:space="preserve">8.05265998840332</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">8.15059089660645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58460807800293</t>
+    <t xml:space="preserve">8.58460712432861</t>
   </si>
   <si>
     <t xml:space="preserve">8.35090732574463</t>
@@ -1526,13 +1526,13 @@
     <t xml:space="preserve">8.26187801361084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62244510650635</t>
+    <t xml:space="preserve">8.62244415283203</t>
   </si>
   <si>
     <t xml:space="preserve">8.73595523834229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56902694702148</t>
+    <t xml:space="preserve">8.56902599334717</t>
   </si>
   <si>
     <t xml:space="preserve">8.40432357788086</t>
@@ -1547,19 +1547,19 @@
     <t xml:space="preserve">8.44883823394775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74485969543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11210155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25009822845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27903270721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88285446166992</t>
+    <t xml:space="preserve">8.74485874176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11210250854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25009727478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27903175354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88285350799561</t>
   </si>
   <si>
     <t xml:space="preserve">8.92069149017334</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">9.0564603805542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12100601196289</t>
+    <t xml:space="preserve">9.12100505828857</t>
   </si>
   <si>
     <t xml:space="preserve">9.04978275299072</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">9.92004013061523</t>
   </si>
   <si>
-    <t xml:space="preserve">9.948974609375</t>
+    <t xml:space="preserve">9.94897556304932</t>
   </si>
   <si>
     <t xml:space="preserve">10.1092262268066</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">9.95120048522949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84659099578857</t>
+    <t xml:space="preserve">9.84659194946289</t>
   </si>
   <si>
     <t xml:space="preserve">9.31686878204346</t>
@@ -1601,10 +1601,10 @@
     <t xml:space="preserve">9.71749973297119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96010398864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87107467651367</t>
+    <t xml:space="preserve">9.96010303497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87107372283936</t>
   </si>
   <si>
     <t xml:space="preserve">9.93116760253906</t>
@@ -1625,40 +1625,40 @@
     <t xml:space="preserve">10.2071580886841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3429260253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2116088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2895097732544</t>
+    <t xml:space="preserve">10.3429269790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2116098403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2895088195801</t>
   </si>
   <si>
     <t xml:space="preserve">10.0157461166382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1670961380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2449960708618</t>
+    <t xml:space="preserve">10.1670951843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2449951171875</t>
   </si>
   <si>
     <t xml:space="preserve">10.2160606384277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3740873336792</t>
+    <t xml:space="preserve">10.3740882873535</t>
   </si>
   <si>
     <t xml:space="preserve">10.3340244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99348926544189</t>
+    <t xml:space="preserve">9.99349021911621</t>
   </si>
   <si>
     <t xml:space="preserve">9.93562030792236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2694797515869</t>
+    <t xml:space="preserve">10.2694787979126</t>
   </si>
   <si>
     <t xml:space="preserve">10.1982555389404</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">10.9483232498169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.756911277771</t>
+    <t xml:space="preserve">10.7569122314453</t>
   </si>
   <si>
     <t xml:space="preserve">10.661205291748</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">11.0462560653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6360712051392</t>
+    <t xml:space="preserve">11.6360721588135</t>
   </si>
   <si>
     <t xml:space="preserve">11.7117471694946</t>
@@ -1709,13 +1709,13 @@
     <t xml:space="preserve">11.9788331985474</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1969528198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0856666564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.555944442749</t>
+    <t xml:space="preserve">12.1969537734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0856676101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5559453964233</t>
   </si>
   <si>
     <t xml:space="preserve">11.2309904098511</t>
@@ -1727,16 +1727,16 @@
     <t xml:space="preserve">11.3155670166016</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0395774841309</t>
+    <t xml:space="preserve">11.0395784378052</t>
   </si>
   <si>
     <t xml:space="preserve">11.2666025161743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2621507644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9349679946899</t>
+    <t xml:space="preserve">11.262149810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9349689483643</t>
   </si>
   <si>
     <t xml:space="preserve">10.4631156921387</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">10.670108795166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4364080429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5499200820923</t>
+    <t xml:space="preserve">10.4364070892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.549919128418</t>
   </si>
   <si>
     <t xml:space="preserve">10.4608907699585</t>
@@ -1757,16 +1757,16 @@
     <t xml:space="preserve">10.5387907028198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.76136302948</t>
+    <t xml:space="preserve">10.7613620758057</t>
   </si>
   <si>
     <t xml:space="preserve">10.3763132095337</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1604175567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3006381988525</t>
+    <t xml:space="preserve">10.160418510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3006391525269</t>
   </si>
   <si>
     <t xml:space="preserve">10.3963451385498</t>
@@ -1775,7 +1775,7 @@
     <t xml:space="preserve">9.8643970489502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87552547454834</t>
+    <t xml:space="preserve">9.87552642822266</t>
   </si>
   <si>
     <t xml:space="preserve">9.57727909088135</t>
@@ -1787,13 +1787,13 @@
     <t xml:space="preserve">9.34580421447754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29081058502197</t>
+    <t xml:space="preserve">8.29081249237061</t>
   </si>
   <si>
     <t xml:space="preserve">8.55789947509766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46219253540039</t>
+    <t xml:space="preserve">8.46219158172607</t>
   </si>
   <si>
     <t xml:space="preserve">8.5645751953125</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">8.89398288726807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25519943237305</t>
+    <t xml:space="preserve">8.25520038604736</t>
   </si>
   <si>
     <t xml:space="preserve">8.27745819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91466474533081</t>
+    <t xml:space="preserve">7.91466617584229</t>
   </si>
   <si>
     <t xml:space="preserve">7.81228160858154</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32039737701416</t>
+    <t xml:space="preserve">7.32039785385132</t>
   </si>
   <si>
     <t xml:space="preserve">7.24694871902466</t>
@@ -1829,13 +1829,13 @@
     <t xml:space="preserve">7.20688581466675</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96873378753662</t>
+    <t xml:space="preserve">6.96873331069946</t>
   </si>
   <si>
     <t xml:space="preserve">7.26698017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42500638961792</t>
+    <t xml:space="preserve">7.42500686645508</t>
   </si>
   <si>
     <t xml:space="preserve">8.09494781494141</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">8.32864952087402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39096927642822</t>
+    <t xml:space="preserve">8.39096832275391</t>
   </si>
   <si>
     <t xml:space="preserve">8.59796142578125</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">9.23896980285645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11655426025391</t>
+    <t xml:space="preserve">9.11655521392822</t>
   </si>
   <si>
     <t xml:space="preserve">9.17219829559326</t>
@@ -1871,10 +1871,10 @@
     <t xml:space="preserve">9.2478723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68476390838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6513786315918</t>
+    <t xml:space="preserve">8.68476486206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65137958526611</t>
   </si>
   <si>
     <t xml:space="preserve">8.994140625</t>
@@ -1886,13 +1886,13 @@
     <t xml:space="preserve">9.4370584487915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57282638549805</t>
+    <t xml:space="preserve">9.57282733917236</t>
   </si>
   <si>
     <t xml:space="preserve">9.48379993438721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41480159759521</t>
+    <t xml:space="preserve">9.41480255126953</t>
   </si>
   <si>
     <t xml:space="preserve">9.44818782806396</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">9.61511707305908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69746685028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96232891082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3496055603027</t>
+    <t xml:space="preserve">9.69746780395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96232986450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3496036529541</t>
   </si>
   <si>
     <t xml:space="preserve">10.5410165786743</t>
@@ -1928,22 +1928,22 @@
     <t xml:space="preserve">10.614465713501</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8681983947754</t>
+    <t xml:space="preserve">10.8681974411011</t>
   </si>
   <si>
     <t xml:space="preserve">10.9193897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7368803024292</t>
+    <t xml:space="preserve">10.7368793487549</t>
   </si>
   <si>
     <t xml:space="preserve">10.8303604125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9371957778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2828321456909</t>
+    <t xml:space="preserve">10.9371948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2828330993652</t>
   </si>
   <si>
     <t xml:space="preserve">10.2294158935547</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">10.7391052246094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8147802352905</t>
+    <t xml:space="preserve">10.8147811889648</t>
   </si>
   <si>
     <t xml:space="preserve">10.8637456893921</t>
@@ -1985,16 +1985,16 @@
     <t xml:space="preserve">10.4475355148315</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3295736312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2271900177002</t>
+    <t xml:space="preserve">10.3295726776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2271890640259</t>
   </si>
   <si>
     <t xml:space="preserve">10.3874416351318</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6901397705078</t>
+    <t xml:space="preserve">10.6901388168335</t>
   </si>
   <si>
     <t xml:space="preserve">10.4764719009399</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">10.1003246307373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0535831451416</t>
+    <t xml:space="preserve">10.0535840988159</t>
   </si>
   <si>
     <t xml:space="preserve">9.63737392425537</t>
@@ -2012,19 +2012,19 @@
     <t xml:space="preserve">9.60843944549561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33912658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99191379547119</t>
+    <t xml:space="preserve">9.33912754058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99191474914551</t>
   </si>
   <si>
     <t xml:space="preserve">8.91846561431885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04755783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22784233093262</t>
+    <t xml:space="preserve">9.04755687713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22784042358398</t>
   </si>
   <si>
     <t xml:space="preserve">9.50382995605469</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">9.27012920379639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31909561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25232315063477</t>
+    <t xml:space="preserve">9.31909465789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25232410430908</t>
   </si>
   <si>
     <t xml:space="preserve">8.77379322052002</t>
@@ -2048,34 +2048,34 @@
     <t xml:space="preserve">8.74263381958008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53118896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07203960418701</t>
+    <t xml:space="preserve">8.53118991851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07204151153564</t>
   </si>
   <si>
     <t xml:space="preserve">9.38364124298096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5483455657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58395671844482</t>
+    <t xml:space="preserve">9.54834461212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58395576477051</t>
   </si>
   <si>
     <t xml:space="preserve">9.60621356964111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81543159484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69079208374023</t>
+    <t xml:space="preserve">9.81543064117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69079113006592</t>
   </si>
   <si>
     <t xml:space="preserve">9.79762554168701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73753070831299</t>
+    <t xml:space="preserve">9.7375316619873</t>
   </si>
   <si>
     <t xml:space="preserve">9.96900653839111</t>
@@ -2096,22 +2096,22 @@
     <t xml:space="preserve">9.95565223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1070003509521</t>
+    <t xml:space="preserve">10.1070013046265</t>
   </si>
   <si>
     <t xml:space="preserve">9.96455478668213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1715459823608</t>
+    <t xml:space="preserve">10.1715469360352</t>
   </si>
   <si>
     <t xml:space="preserve">9.89555740356445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71304798126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46821880340576</t>
+    <t xml:space="preserve">9.71304893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46821784973145</t>
   </si>
   <si>
     <t xml:space="preserve">9.55057048797607</t>
@@ -2120,37 +2120,37 @@
     <t xml:space="preserve">9.79094886779785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1915788650513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2717046737671</t>
+    <t xml:space="preserve">10.191577911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2717037200928</t>
   </si>
   <si>
     <t xml:space="preserve">9.75088500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99794006347656</t>
+    <t xml:space="preserve">9.99794101715088</t>
   </si>
   <si>
     <t xml:space="preserve">9.91558837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5238618850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24342155456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19668006896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12545776367188</t>
+    <t xml:space="preserve">9.52386093139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24342060089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19668102264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12545871734619</t>
   </si>
   <si>
     <t xml:space="preserve">8.72927951812744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95185089111328</t>
+    <t xml:space="preserve">8.9518518447876</t>
   </si>
   <si>
     <t xml:space="preserve">9.21003532409668</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">9.02530002593994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26345348358154</t>
+    <t xml:space="preserve">9.26345252990723</t>
   </si>
   <si>
     <t xml:space="preserve">9.1187801361084</t>
@@ -2189,22 +2189,22 @@
     <t xml:space="preserve">10.0268754959106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.104775428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1136770248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1403865814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4230537414551</t>
+    <t xml:space="preserve">10.1047735214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1136779785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1403856277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4230527877808</t>
   </si>
   <si>
     <t xml:space="preserve">9.94452285766602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91781425476074</t>
+    <t xml:space="preserve">9.91781520843506</t>
   </si>
   <si>
     <t xml:space="preserve">9.64850234985352</t>
@@ -2222,10 +2222,10 @@
     <t xml:space="preserve">9.05868625640869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92736911773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00971984863281</t>
+    <t xml:space="preserve">8.9273681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00972080230713</t>
   </si>
   <si>
     <t xml:space="preserve">9.19000339508057</t>
@@ -2243,13 +2243,13 @@
     <t xml:space="preserve">9.65963077545166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15216541290283</t>
+    <t xml:space="preserve">9.15216636657715</t>
   </si>
   <si>
     <t xml:space="preserve">9.92226696014404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85771942138672</t>
+    <t xml:space="preserve">9.85772037506104</t>
   </si>
   <si>
     <t xml:space="preserve">9.95787811279297</t>
@@ -2267,13 +2267,13 @@
     <t xml:space="preserve">9.66853427886963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80207633972168</t>
+    <t xml:space="preserve">9.802077293396</t>
   </si>
   <si>
     <t xml:space="preserve">9.53499031066895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40812492370605</t>
+    <t xml:space="preserve">9.40812397003174</t>
   </si>
   <si>
     <t xml:space="preserve">9.51941108703613</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">9.43483257293701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4993782043457</t>
+    <t xml:space="preserve">9.49937915802002</t>
   </si>
   <si>
     <t xml:space="preserve">9.24564647674561</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">9.40144729614258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33467578887939</t>
+    <t xml:space="preserve">9.33467674255371</t>
   </si>
   <si>
     <t xml:space="preserve">9.57060146331787</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">9.55502128601074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5616979598999</t>
+    <t xml:space="preserve">9.56169891357422</t>
   </si>
   <si>
     <t xml:space="preserve">9.6952428817749</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">9.85994625091553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85326862335205</t>
+    <t xml:space="preserve">9.85326957702637</t>
   </si>
   <si>
     <t xml:space="preserve">8.9073371887207</t>
@@ -2351,22 +2351,22 @@
     <t xml:space="preserve">8.47332096099854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34868049621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4354829788208</t>
+    <t xml:space="preserve">8.34868144989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43548393249512</t>
   </si>
   <si>
     <t xml:space="preserve">8.52896404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35758399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71657657623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62754774093628</t>
+    <t xml:space="preserve">8.35758304595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71657609939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62754726409912</t>
   </si>
   <si>
     <t xml:space="preserve">8.00369453430176</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">6.30546808242798</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95000410079956</t>
+    <t xml:space="preserve">4.9500036239624</t>
   </si>
   <si>
     <t xml:space="preserve">4.88545846939087</t>
@@ -2393,31 +2393,31 @@
     <t xml:space="preserve">4.58275985717773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38912296295166</t>
+    <t xml:space="preserve">4.3891224861145</t>
   </si>
   <si>
     <t xml:space="preserve">4.57830858230591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59834003448486</t>
+    <t xml:space="preserve">4.59834051132202</t>
   </si>
   <si>
     <t xml:space="preserve">5.09022426605225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00342130661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88991022109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19260787963867</t>
+    <t xml:space="preserve">5.00342178344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88990926742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19260740280151</t>
   </si>
   <si>
     <t xml:space="preserve">5.1658992767334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22599363327026</t>
+    <t xml:space="preserve">5.22599315643311</t>
   </si>
   <si>
     <t xml:space="preserve">4.96781015396118</t>
@@ -2432,25 +2432,25 @@
     <t xml:space="preserve">5.37956809997559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28386259078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33950519561768</t>
+    <t xml:space="preserve">5.28386211395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33950567245483</t>
   </si>
   <si>
     <t xml:space="preserve">5.35063409805298</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23267126083374</t>
+    <t xml:space="preserve">5.23267078399658</t>
   </si>
   <si>
     <t xml:space="preserve">5.36398839950562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29276561737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83871793746948</t>
+    <t xml:space="preserve">5.29276514053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83871746063232</t>
   </si>
   <si>
     <t xml:space="preserve">4.85429859161377</t>
@@ -2462,46 +2462,46 @@
     <t xml:space="preserve">4.68514347076416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95445537567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03013038635254</t>
+    <t xml:space="preserve">4.95445489883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03012990951538</t>
   </si>
   <si>
     <t xml:space="preserve">4.88100624084473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92552137374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19928503036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21041393280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08354806900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1347393989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98338937759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11470794677734</t>
+    <t xml:space="preserve">4.92552089691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19928550720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21041345596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08354759216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13473892211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98338985443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11470746994019</t>
   </si>
   <si>
     <t xml:space="preserve">5.15031909942627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11248207092285</t>
+    <t xml:space="preserve">5.11248159408569</t>
   </si>
   <si>
     <t xml:space="preserve">5.02122688293457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92329549789429</t>
+    <t xml:space="preserve">4.92329597473145</t>
   </si>
   <si>
     <t xml:space="preserve">4.96113300323486</t>
@@ -6411,6 +6411,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.44700002670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36999988555908</t>
   </si>
 </sst>
 </file>
@@ -75283,6 +75286,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2637">
+      <c r="A2637" s="1" t="n">
+        <v>46162.2916666667</v>
+      </c>
+      <c r="B2637" t="n">
+        <v>26226208</v>
+      </c>
+      <c r="C2637" t="n">
+        <v>4.50799989700317</v>
+      </c>
+      <c r="D2637" t="n">
+        <v>4.36399984359741</v>
+      </c>
+      <c r="E2637" t="n">
+        <v>4.48699998855591</v>
+      </c>
+      <c r="F2637" t="n">
+        <v>4.36999988555908</v>
+      </c>
+      <c r="G2637" t="s">
+        <v>2133</v>
+      </c>
+      <c r="H2637" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2134" uniqueCount="2134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2135" uniqueCount="2135">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2849197387695</t>
+    <t xml:space="preserve">20.2849216461182</t>
   </si>
   <si>
     <t xml:space="preserve">SPM.MI</t>
@@ -50,16 +50,16 @@
     <t xml:space="preserve">19.7946090698242</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4443836212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9540729522705</t>
+    <t xml:space="preserve">19.4443855285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9540710449219</t>
   </si>
   <si>
     <t xml:space="preserve">19.0661430358887</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8786602020264</t>
+    <t xml:space="preserve">19.878662109375</t>
   </si>
   <si>
     <t xml:space="preserve">19.65452003479</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">19.6685276031494</t>
   </si>
   <si>
-    <t xml:space="preserve">18.547815322876</t>
+    <t xml:space="preserve">18.5478134155273</t>
   </si>
   <si>
     <t xml:space="preserve">17.5952072143555</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">11.7730989456177</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9552736282349</t>
+    <t xml:space="preserve">13.9552726745605</t>
   </si>
   <si>
     <t xml:space="preserve">13.810601234436</t>
@@ -95,16 +95,16 @@
     <t xml:space="preserve">12.2414674758911</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6087121963501</t>
+    <t xml:space="preserve">12.6087112426758</t>
   </si>
   <si>
     <t xml:space="preserve">12.6977415084839</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7311277389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.30823802948</t>
+    <t xml:space="preserve">12.7311267852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3082389831543</t>
   </si>
   <si>
     <t xml:space="preserve">11.9743804931641</t>
@@ -116,28 +116,28 @@
     <t xml:space="preserve">11.5737524032593</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64692783355713</t>
+    <t xml:space="preserve">8.64692687988281</t>
   </si>
   <si>
     <t xml:space="preserve">8.16617107391357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05711078643799</t>
+    <t xml:space="preserve">8.0571117401123</t>
   </si>
   <si>
     <t xml:space="preserve">7.08892250061035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70832395553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74393510818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87747859954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51181030273438</t>
+    <t xml:space="preserve">6.70832443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74393558502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8774790763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51180934906006</t>
   </si>
   <si>
     <t xml:space="preserve">7.70322132110596</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">7.7900242805481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91243886947632</t>
+    <t xml:space="preserve">7.91243982315063</t>
   </si>
   <si>
     <t xml:space="preserve">7.67873859405518</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">8.64025020599365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58015632629395</t>
+    <t xml:space="preserve">8.58015537261963</t>
   </si>
   <si>
     <t xml:space="preserve">8.83611392974854</t>
@@ -185,16 +185,16 @@
     <t xml:space="preserve">8.56235027313232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58683204650879</t>
+    <t xml:space="preserve">8.58683300018311</t>
   </si>
   <si>
     <t xml:space="preserve">8.29526329040527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21291255950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31752109527588</t>
+    <t xml:space="preserve">8.21291351318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3175220489502</t>
   </si>
   <si>
     <t xml:space="preserve">8.44438743591309</t>
@@ -221,22 +221,22 @@
     <t xml:space="preserve">7.83676528930664</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65870714187622</t>
+    <t xml:space="preserve">7.65870809555054</t>
   </si>
   <si>
     <t xml:space="preserve">7.32262420654297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89973592758179</t>
+    <t xml:space="preserve">6.89973640441895</t>
   </si>
   <si>
     <t xml:space="preserve">7.03327894210815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75061225891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27365779876709</t>
+    <t xml:space="preserve">6.75061273574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27365732192993</t>
   </si>
   <si>
     <t xml:space="preserve">7.56745290756226</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">8.27523231506348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2930383682251</t>
+    <t xml:space="preserve">8.29303741455078</t>
   </si>
   <si>
     <t xml:space="preserve">8.45551586151123</t>
@@ -269,19 +269,19 @@
     <t xml:space="preserve">8.33310031890869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46887016296387</t>
+    <t xml:space="preserve">8.46886920928955</t>
   </si>
   <si>
     <t xml:space="preserve">8.62912082672119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68188858032227</t>
+    <t xml:space="preserve">9.68188762664795</t>
   </si>
   <si>
     <t xml:space="preserve">9.30351543426514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82275867462158</t>
+    <t xml:space="preserve">8.8227596282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.54009246826172</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">8.70034408569336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30639266967773</t>
+    <t xml:space="preserve">8.30639171600342</t>
   </si>
   <si>
     <t xml:space="preserve">8.16172027587891</t>
@@ -302,28 +302,28 @@
     <t xml:space="preserve">8.14836502075195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26855373382568</t>
+    <t xml:space="preserve">8.2685546875</t>
   </si>
   <si>
     <t xml:space="preserve">8.39542102813721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31974697113037</t>
+    <t xml:space="preserve">8.31974601745605</t>
   </si>
   <si>
     <t xml:space="preserve">8.27968311309814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98588752746582</t>
+    <t xml:space="preserve">7.98588848114014</t>
   </si>
   <si>
     <t xml:space="preserve">7.99701690673828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91689109802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10607719421387</t>
+    <t xml:space="preserve">7.91689014434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10607814788818</t>
   </si>
   <si>
     <t xml:space="preserve">8.3976469039917</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">8.18842887878418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02372550964355</t>
+    <t xml:space="preserve">8.02372455596924</t>
   </si>
   <si>
     <t xml:space="preserve">7.77889585494995</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44661235809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85837173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67363548278809</t>
+    <t xml:space="preserve">8.44661331176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85837078094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6736364364624</t>
   </si>
   <si>
     <t xml:space="preserve">8.22849273681641</t>
@@ -359,25 +359,25 @@
     <t xml:space="preserve">7.73660707473755</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96808242797852</t>
+    <t xml:space="preserve">7.96808338165283</t>
   </si>
   <si>
     <t xml:space="preserve">7.78112173080444</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69144153594971</t>
+    <t xml:space="preserve">8.69144248962402</t>
   </si>
   <si>
     <t xml:space="preserve">8.98078536987305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76488971710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00749397277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05933666229248</t>
+    <t xml:space="preserve">8.76489067077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.007493019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05933570861816</t>
   </si>
   <si>
     <t xml:space="preserve">7.5919361114502</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">8.51783657073975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82341051101685</t>
+    <t xml:space="preserve">7.82341146469116</t>
   </si>
   <si>
     <t xml:space="preserve">8.01704788208008</t>
@@ -410,13 +410,13 @@
     <t xml:space="preserve">8.71147441864014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03420257568359</t>
+    <t xml:space="preserve">9.03420352935791</t>
   </si>
   <si>
     <t xml:space="preserve">9.25454902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32577323913574</t>
+    <t xml:space="preserve">9.32577228546143</t>
   </si>
   <si>
     <t xml:space="preserve">9.20113182067871</t>
@@ -425,13 +425,13 @@
     <t xml:space="preserve">9.37028789520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55947303771973</t>
+    <t xml:space="preserve">9.55947208404541</t>
   </si>
   <si>
     <t xml:space="preserve">9.733078956604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6284704208374</t>
+    <t xml:space="preserve">9.62846946716309</t>
   </si>
   <si>
     <t xml:space="preserve">9.68856525421143</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">9.48157215118408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78427219390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8272123336792</t>
+    <t xml:space="preserve">9.78427124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82721138000488</t>
   </si>
   <si>
     <t xml:space="preserve">8.49335289001465</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">8.31529426574707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52228736877441</t>
+    <t xml:space="preserve">8.5222864151001</t>
   </si>
   <si>
     <t xml:space="preserve">8.778244972229</t>
@@ -485,31 +485,31 @@
     <t xml:space="preserve">9.25677490234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03643035888672</t>
+    <t xml:space="preserve">9.0364294052124</t>
   </si>
   <si>
     <t xml:space="preserve">8.85169410705566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26122665405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21671295166016</t>
+    <t xml:space="preserve">9.26122570037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21671199798584</t>
   </si>
   <si>
     <t xml:space="preserve">9.09652328491211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25899982452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0809440612793</t>
+    <t xml:space="preserve">9.25900077819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08094310760498</t>
   </si>
   <si>
     <t xml:space="preserve">9.16997337341309</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14548873901367</t>
+    <t xml:space="preserve">9.14548778533936</t>
   </si>
   <si>
     <t xml:space="preserve">9.09207153320312</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">9.27235507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20780944824219</t>
+    <t xml:space="preserve">9.2078104019165</t>
   </si>
   <si>
     <t xml:space="preserve">9.23451805114746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80272769927979</t>
+    <t xml:space="preserve">8.8027286529541</t>
   </si>
   <si>
     <t xml:space="preserve">8.3776159286499</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">8.29971504211426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23516941070557</t>
+    <t xml:space="preserve">8.23516845703125</t>
   </si>
   <si>
     <t xml:space="preserve">7.90798759460449</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">8.42880630493164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59128475189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72482872009277</t>
+    <t xml:space="preserve">8.59128379821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72482776641846</t>
   </si>
   <si>
     <t xml:space="preserve">8.66473293304443</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">9.19445610046387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21448516845703</t>
+    <t xml:space="preserve">9.21448612213135</t>
   </si>
   <si>
     <t xml:space="preserve">9.58840751647949</t>
@@ -629,10 +629,10 @@
     <t xml:space="preserve">9.00304317474365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06536388397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94072246551514</t>
+    <t xml:space="preserve">9.06536293029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94072341918945</t>
   </si>
   <si>
     <t xml:space="preserve">8.90511131286621</t>
@@ -641,16 +641,16 @@
     <t xml:space="preserve">8.97188186645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9451732635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06313705444336</t>
+    <t xml:space="preserve">8.94517421722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06313800811768</t>
   </si>
   <si>
     <t xml:space="preserve">9.16329479217529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92514228820801</t>
+    <t xml:space="preserve">8.92514324188232</t>
   </si>
   <si>
     <t xml:space="preserve">8.61131572723389</t>
@@ -692,19 +692,19 @@
     <t xml:space="preserve">10.5788536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8837776184082</t>
+    <t xml:space="preserve">10.8837785720825</t>
   </si>
   <si>
     <t xml:space="preserve">11.3845643997192</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3511781692505</t>
+    <t xml:space="preserve">11.3511791229248</t>
   </si>
   <si>
     <t xml:space="preserve">10.9883871078491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2844085693359</t>
+    <t xml:space="preserve">11.2844076156616</t>
   </si>
   <si>
     <t xml:space="preserve">11.417950630188</t>
@@ -716,19 +716,19 @@
     <t xml:space="preserve">11.7295513153076</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9076108932495</t>
+    <t xml:space="preserve">11.9076099395752</t>
   </si>
   <si>
     <t xml:space="preserve">12.441782951355</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3972682952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4195261001587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1858243942261</t>
+    <t xml:space="preserve">12.3972692489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4195251464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1858253479004</t>
   </si>
   <si>
     <t xml:space="preserve">11.8074522018433</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">11.3066644668579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6182651519775</t>
+    <t xml:space="preserve">11.6182661056519</t>
   </si>
   <si>
     <t xml:space="preserve">11.2955369949341</t>
@@ -746,28 +746,28 @@
     <t xml:space="preserve">11.4068212509155</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9060354232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1397352218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1619939804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1731214523315</t>
+    <t xml:space="preserve">10.9060344696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1397342681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1619930267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1731204986572</t>
   </si>
   <si>
     <t xml:space="preserve">11.0351257324219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0840930938721</t>
+    <t xml:space="preserve">11.0840921401978</t>
   </si>
   <si>
     <t xml:space="preserve">11.7963228225708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6405229568481</t>
+    <t xml:space="preserve">11.6405220031738</t>
   </si>
   <si>
     <t xml:space="preserve">11.5960092544556</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">10.4141502380371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.251672744751</t>
+    <t xml:space="preserve">10.2516717910767</t>
   </si>
   <si>
     <t xml:space="preserve">10.2205123901367</t>
@@ -800,13 +800,13 @@
     <t xml:space="preserve">10.3985710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3807649612427</t>
+    <t xml:space="preserve">10.3807640075684</t>
   </si>
   <si>
     <t xml:space="preserve">10.6589794158936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3651838302612</t>
+    <t xml:space="preserve">10.3651847839355</t>
   </si>
   <si>
     <t xml:space="preserve">10.0891952514648</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">10.5031795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2939624786377</t>
+    <t xml:space="preserve">10.2939615249634</t>
   </si>
   <si>
     <t xml:space="preserve">10.3184442520142</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">10.00461769104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0469055175781</t>
+    <t xml:space="preserve">10.0469064712524</t>
   </si>
   <si>
     <t xml:space="preserve">9.36360931396484</t>
@@ -842,10 +842,10 @@
     <t xml:space="preserve">9.53053951263428</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45486450195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48602485656738</t>
+    <t xml:space="preserve">9.45486354827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48602390289307</t>
   </si>
   <si>
     <t xml:space="preserve">9.34802913665771</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">9.28125858306885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9896879196167</t>
+    <t xml:space="preserve">8.98968887329102</t>
   </si>
   <si>
     <t xml:space="preserve">9.08761978149414</t>
@@ -866,43 +866,43 @@
     <t xml:space="preserve">9.06091117858887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15439128875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01639652252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08539390563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98523807525635</t>
+    <t xml:space="preserve">9.15439224243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01639747619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08539485931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98523712158203</t>
   </si>
   <si>
     <t xml:space="preserve">8.97856044769287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00526714324951</t>
+    <t xml:space="preserve">9.00526809692383</t>
   </si>
   <si>
     <t xml:space="preserve">9.39254379272461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46154117584229</t>
+    <t xml:space="preserve">9.4615421295166</t>
   </si>
   <si>
     <t xml:space="preserve">9.59063339233398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47044563293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77981853485107</t>
+    <t xml:space="preserve">9.47044467926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77981948852539</t>
   </si>
   <si>
     <t xml:space="preserve">9.49047470092773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51050758361816</t>
+    <t xml:space="preserve">9.51050853729248</t>
   </si>
   <si>
     <t xml:space="preserve">9.51495933532715</t>
@@ -911,13 +911,13 @@
     <t xml:space="preserve">9.32799816131592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33022308349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12990951538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10542583465576</t>
+    <t xml:space="preserve">9.33022403717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12990856170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10542678833008</t>
   </si>
   <si>
     <t xml:space="preserve">8.87617683410645</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">9.20558452606201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20335865020752</t>
+    <t xml:space="preserve">9.2033576965332</t>
   </si>
   <si>
     <t xml:space="preserve">8.80495357513428</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">8.74708557128906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87840270996094</t>
+    <t xml:space="preserve">8.87840175628662</t>
   </si>
   <si>
     <t xml:space="preserve">8.89620876312256</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">8.69366836547852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86282348632812</t>
+    <t xml:space="preserve">8.86282253265381</t>
   </si>
   <si>
     <t xml:space="preserve">8.47554683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30193996429443</t>
+    <t xml:space="preserve">8.30194091796875</t>
   </si>
   <si>
     <t xml:space="preserve">8.12833404541016</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">8.0348539352417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99033975601196</t>
+    <t xml:space="preserve">7.99033880233765</t>
   </si>
   <si>
     <t xml:space="preserve">7.95472764968872</t>
@@ -1001,10 +1001,10 @@
     <t xml:space="preserve">7.66093349456787</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73215579986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69209432601929</t>
+    <t xml:space="preserve">7.73215675354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69209337234497</t>
   </si>
   <si>
     <t xml:space="preserve">7.65648126602173</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">7.58971071243286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34042882919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1979832649231</t>
+    <t xml:space="preserve">7.34042930603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19798278808594</t>
   </si>
   <si>
     <t xml:space="preserve">7.21133708953857</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">7.18017673492432</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08224582672119</t>
+    <t xml:space="preserve">7.08224534988403</t>
   </si>
   <si>
     <t xml:space="preserve">7.16237115859985</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">7.22914266586304</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31817245483398</t>
+    <t xml:space="preserve">7.31817197799683</t>
   </si>
   <si>
     <t xml:space="preserve">7.23804569244385</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">7.42055463790894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6965446472168</t>
+    <t xml:space="preserve">7.69654560089111</t>
   </si>
   <si>
     <t xml:space="preserve">7.48732662200928</t>
@@ -1061,28 +1061,28 @@
     <t xml:space="preserve">7.46952056884766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43390846252441</t>
+    <t xml:space="preserve">7.43390941619873</t>
   </si>
   <si>
     <t xml:space="preserve">7.7455096244812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85679721832275</t>
+    <t xml:space="preserve">7.85679626464844</t>
   </si>
   <si>
     <t xml:space="preserve">7.66983604431152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55854988098145</t>
+    <t xml:space="preserve">7.55854940414429</t>
   </si>
   <si>
     <t xml:space="preserve">7.54964637756348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47842311859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61196756362915</t>
+    <t xml:space="preserve">7.47842407226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61196660995483</t>
   </si>
   <si>
     <t xml:space="preserve">7.50958395004272</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">7.70989847183228</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70099496841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64757966995239</t>
+    <t xml:space="preserve">7.70099592208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64757871627808</t>
   </si>
   <si>
     <t xml:space="preserve">7.58525800704956</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">7.6520299911499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67428636550903</t>
+    <t xml:space="preserve">7.67428731918335</t>
   </si>
   <si>
     <t xml:space="preserve">7.60306406021118</t>
@@ -1115,37 +1115,37 @@
     <t xml:space="preserve">7.57190418243408</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50513172149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24249792098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28701210021973</t>
+    <t xml:space="preserve">7.5051326751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24249744415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28701162338257</t>
   </si>
   <si>
     <t xml:space="preserve">7.26475477218628</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23359441757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30036592483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16682195663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95315361022949</t>
+    <t xml:space="preserve">7.23359394073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30036640167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16682243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95315408706665</t>
   </si>
   <si>
     <t xml:space="preserve">6.75283861160278</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82851362228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8151593208313</t>
+    <t xml:space="preserve">6.82851314544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81515884399414</t>
   </si>
   <si>
     <t xml:space="preserve">6.56587791442871</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">6.56142663955688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9397988319397</t>
+    <t xml:space="preserve">6.93979930877686</t>
   </si>
   <si>
     <t xml:space="preserve">6.86857557296753</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">7.22469091415405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05998849868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29591417312622</t>
+    <t xml:space="preserve">7.05998802185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29591464996338</t>
   </si>
   <si>
     <t xml:space="preserve">7.44281196594238</t>
@@ -1181,13 +1181,13 @@
     <t xml:space="preserve">7.55409860610962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4739727973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6653847694397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07491779327393</t>
+    <t xml:space="preserve">7.47397184371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66538381576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07491683959961</t>
   </si>
   <si>
     <t xml:space="preserve">8.07046604156494</t>
@@ -1205,10 +1205,10 @@
     <t xml:space="preserve">8.12388324737549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93692350387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15504360198975</t>
+    <t xml:space="preserve">7.93692255020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15504264831543</t>
   </si>
   <si>
     <t xml:space="preserve">8.11497974395752</t>
@@ -1229,10 +1229,10 @@
     <t xml:space="preserve">7.56300115585327</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38939476013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42945718765259</t>
+    <t xml:space="preserve">7.38939523696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4294581413269</t>
   </si>
   <si>
     <t xml:space="preserve">8.02149963378906</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">7.7143497467041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64312648773193</t>
+    <t xml:space="preserve">7.64312744140625</t>
   </si>
   <si>
     <t xml:space="preserve">7.99479198455811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45328998565674</t>
+    <t xml:space="preserve">8.45328903198242</t>
   </si>
   <si>
     <t xml:space="preserve">8.54677104949951</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">8.55567264556885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70257091522217</t>
+    <t xml:space="preserve">8.70256996154785</t>
   </si>
   <si>
     <t xml:space="preserve">8.59573554992676</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">7.90576267242432</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84344244003296</t>
+    <t xml:space="preserve">7.84344148635864</t>
   </si>
   <si>
     <t xml:space="preserve">7.62977266311646</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">7.44726324081421</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6342248916626</t>
+    <t xml:space="preserve">7.63422393798828</t>
   </si>
   <si>
     <t xml:space="preserve">7.40274858474731</t>
@@ -1310,13 +1310,13 @@
     <t xml:space="preserve">8.50670623779297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50225639343262</t>
+    <t xml:space="preserve">8.5022554397583</t>
   </si>
   <si>
     <t xml:space="preserve">8.76934242248535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76043891906738</t>
+    <t xml:space="preserve">8.7604398727417</t>
   </si>
   <si>
     <t xml:space="preserve">8.65805625915527</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">8.97410869598389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02307510375977</t>
+    <t xml:space="preserve">9.02307415008545</t>
   </si>
   <si>
     <t xml:space="preserve">9.24119567871094</t>
@@ -1343,13 +1343,13 @@
     <t xml:space="preserve">9.23674297332764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16552066802979</t>
+    <t xml:space="preserve">9.16551971435547</t>
   </si>
   <si>
     <t xml:space="preserve">9.04087924957275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83833885192871</t>
+    <t xml:space="preserve">8.83833980560303</t>
   </si>
   <si>
     <t xml:space="preserve">8.51561069488525</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">8.39319515228271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41990375518799</t>
+    <t xml:space="preserve">8.4199047088623</t>
   </si>
   <si>
     <t xml:space="preserve">8.24852466583252</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">7.39162158966064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49623012542725</t>
+    <t xml:space="preserve">7.49622917175293</t>
   </si>
   <si>
     <t xml:space="preserve">7.5785813331604</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">7.6409010887146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83453893661499</t>
+    <t xml:space="preserve">7.83453989028931</t>
   </si>
   <si>
     <t xml:space="preserve">7.76331663131714</t>
@@ -1394,25 +1394,25 @@
     <t xml:space="preserve">7.5229377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29368829727173</t>
+    <t xml:space="preserve">7.29368877410889</t>
   </si>
   <si>
     <t xml:space="preserve">7.59861183166504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75663948059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38049268722534</t>
+    <t xml:space="preserve">7.7566385269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38049221038818</t>
   </si>
   <si>
     <t xml:space="preserve">7.36936330795288</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43613481521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25585126876831</t>
+    <t xml:space="preserve">7.43613386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25585174560547</t>
   </si>
   <si>
     <t xml:space="preserve">7.37826633453369</t>
@@ -1457,28 +1457,28 @@
     <t xml:space="preserve">7.19130516052246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18907928466797</t>
+    <t xml:space="preserve">7.18907976150513</t>
   </si>
   <si>
     <t xml:space="preserve">7.48064947128296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41610431671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99766731262207</t>
+    <t xml:space="preserve">7.41610336303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99766778945923</t>
   </si>
   <si>
     <t xml:space="preserve">7.00879621505737</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06443929672241</t>
+    <t xml:space="preserve">7.06443977355957</t>
   </si>
   <si>
     <t xml:space="preserve">7.14456558227539</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03105354309082</t>
+    <t xml:space="preserve">7.03105306625366</t>
   </si>
   <si>
     <t xml:space="preserve">7.05331087112427</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">8.94740009307861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37538909912109</t>
+    <t xml:space="preserve">8.37539005279541</t>
   </si>
   <si>
     <t xml:space="preserve">8.19065475463867</t>
@@ -1514,28 +1514,28 @@
     <t xml:space="preserve">8.15059089660645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58460712432861</t>
+    <t xml:space="preserve">8.58460807800293</t>
   </si>
   <si>
     <t xml:space="preserve">8.35090732574463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35535717010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26187801361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62244415283203</t>
+    <t xml:space="preserve">8.3553581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26187705993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62244510650635</t>
   </si>
   <si>
     <t xml:space="preserve">8.73595523834229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56902599334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40432357788086</t>
+    <t xml:space="preserve">8.56902694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40432453155518</t>
   </si>
   <si>
     <t xml:space="preserve">8.63579845428467</t>
@@ -1547,28 +1547,28 @@
     <t xml:space="preserve">8.44883823394775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74485874176025</t>
+    <t xml:space="preserve">8.74485969543457</t>
   </si>
   <si>
     <t xml:space="preserve">9.11210250854492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25009727478027</t>
+    <t xml:space="preserve">9.25009822845459</t>
   </si>
   <si>
     <t xml:space="preserve">9.27903175354004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88285350799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92069149017334</t>
+    <t xml:space="preserve">8.88285446166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92069053649902</t>
   </si>
   <si>
     <t xml:space="preserve">9.0564603805542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12100505828857</t>
+    <t xml:space="preserve">9.12100601196289</t>
   </si>
   <si>
     <t xml:space="preserve">9.04978275299072</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">9.92004013061523</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94897556304932</t>
+    <t xml:space="preserve">9.948974609375</t>
   </si>
   <si>
     <t xml:space="preserve">10.1092262268066</t>
@@ -1589,31 +1589,31 @@
     <t xml:space="preserve">9.95120048522949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84659194946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31686878204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79317283630371</t>
+    <t xml:space="preserve">9.84659099578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31686973571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79317378997803</t>
   </si>
   <si>
     <t xml:space="preserve">9.71749973297119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96010303497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87107372283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93116760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3139925003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1448383331299</t>
+    <t xml:space="preserve">9.96010398864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87107467651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93116855621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3139934539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1448373794556</t>
   </si>
   <si>
     <t xml:space="preserve">9.80652809143066</t>
@@ -1640,13 +1640,13 @@
     <t xml:space="preserve">10.1670951843262</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2449951171875</t>
+    <t xml:space="preserve">10.2449960708618</t>
   </si>
   <si>
     <t xml:space="preserve">10.2160606384277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3740882873535</t>
+    <t xml:space="preserve">10.3740873336792</t>
   </si>
   <si>
     <t xml:space="preserve">10.3340244293213</t>
@@ -1664,13 +1664,13 @@
     <t xml:space="preserve">10.1982555389404</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5744018554688</t>
+    <t xml:space="preserve">10.5744028091431</t>
   </si>
   <si>
     <t xml:space="preserve">10.0446805953979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.394118309021</t>
+    <t xml:space="preserve">10.3941192626953</t>
   </si>
   <si>
     <t xml:space="preserve">10.6834630966187</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">10.9483232498169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7569122314453</t>
+    <t xml:space="preserve">10.756911277771</t>
   </si>
   <si>
     <t xml:space="preserve">10.661205291748</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">11.0462560653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6360721588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7117471694946</t>
+    <t xml:space="preserve">11.6360712051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7117462158203</t>
   </si>
   <si>
     <t xml:space="preserve">11.7340040206909</t>
@@ -1727,7 +1727,7 @@
     <t xml:space="preserve">11.3155670166016</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0395784378052</t>
+    <t xml:space="preserve">11.0395774841309</t>
   </si>
   <si>
     <t xml:space="preserve">11.2666025161743</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">10.670108795166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4364070892334</t>
+    <t xml:space="preserve">10.4364080429077</t>
   </si>
   <si>
     <t xml:space="preserve">10.549919128418</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">10.5387907028198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7613620758057</t>
+    <t xml:space="preserve">10.76136302948</t>
   </si>
   <si>
     <t xml:space="preserve">10.3763132095337</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">10.160418510437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3006391525269</t>
+    <t xml:space="preserve">10.3006381988525</t>
   </si>
   <si>
     <t xml:space="preserve">10.3963451385498</t>
@@ -1775,31 +1775,31 @@
     <t xml:space="preserve">9.8643970489502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87552642822266</t>
+    <t xml:space="preserve">9.87552547454834</t>
   </si>
   <si>
     <t xml:space="preserve">9.57727909088135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45263767242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34580421447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29081249237061</t>
+    <t xml:space="preserve">9.45263862609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34580516815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29081153869629</t>
   </si>
   <si>
     <t xml:space="preserve">8.55789947509766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46219158172607</t>
+    <t xml:space="preserve">8.46219253540039</t>
   </si>
   <si>
     <t xml:space="preserve">8.5645751953125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60018634796143</t>
+    <t xml:space="preserve">8.60018730163574</t>
   </si>
   <si>
     <t xml:space="preserve">9.0742654800415</t>
@@ -1811,16 +1811,16 @@
     <t xml:space="preserve">8.25520038604736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27745819091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91466617584229</t>
+    <t xml:space="preserve">8.27745723724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91466522216797</t>
   </si>
   <si>
     <t xml:space="preserve">7.81228160858154</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32039785385132</t>
+    <t xml:space="preserve">7.32039737701416</t>
   </si>
   <si>
     <t xml:space="preserve">7.24694871902466</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">7.20688581466675</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96873331069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26698017120361</t>
+    <t xml:space="preserve">6.96873378753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26698064804077</t>
   </si>
   <si>
     <t xml:space="preserve">7.42500686645508</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">8.32864952087402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39096832275391</t>
+    <t xml:space="preserve">8.39096927642822</t>
   </si>
   <si>
     <t xml:space="preserve">8.59796142578125</t>
@@ -1910,10 +1910,10 @@
     <t xml:space="preserve">9.69746780395508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96232986450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3496036529541</t>
+    <t xml:space="preserve">9.96232891082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3496046066284</t>
   </si>
   <si>
     <t xml:space="preserve">10.5410165786743</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">10.8303604125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9371948242188</t>
+    <t xml:space="preserve">10.9371957778931</t>
   </si>
   <si>
     <t xml:space="preserve">10.2828330993652</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">10.403021812439</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4942760467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7391052246094</t>
+    <t xml:space="preserve">10.4942770004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7391061782837</t>
   </si>
   <si>
     <t xml:space="preserve">10.8147811889648</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">10.8637456893921</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0707378387451</t>
+    <t xml:space="preserve">11.0707368850708</t>
   </si>
   <si>
     <t xml:space="preserve">11.1998291015625</t>
@@ -1985,16 +1985,16 @@
     <t xml:space="preserve">10.4475355148315</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3295726776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2271890640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3874416351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6901388168335</t>
+    <t xml:space="preserve">10.3295736312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2271900177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3874425888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6901397705078</t>
   </si>
   <si>
     <t xml:space="preserve">10.4764719009399</t>
@@ -2009,10 +2009,10 @@
     <t xml:space="preserve">9.63737392425537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60843944549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33912754058838</t>
+    <t xml:space="preserve">9.60843849182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33912658691406</t>
   </si>
   <si>
     <t xml:space="preserve">8.99191474914551</t>
@@ -2021,10 +2021,10 @@
     <t xml:space="preserve">8.91846561431885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04755687713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22784042358398</t>
+    <t xml:space="preserve">9.04755783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2278413772583</t>
   </si>
   <si>
     <t xml:space="preserve">9.50382995605469</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">9.27012920379639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31909465789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25232410430908</t>
+    <t xml:space="preserve">9.31909561157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25232315063477</t>
   </si>
   <si>
     <t xml:space="preserve">8.77379322052002</t>
@@ -2051,25 +2051,25 @@
     <t xml:space="preserve">8.53118991851807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07204151153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38364124298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54834461212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58395576477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60621356964111</t>
+    <t xml:space="preserve">9.07204055786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38364028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5483455657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58395671844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60621452331543</t>
   </si>
   <si>
     <t xml:space="preserve">9.81543064117432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69079113006592</t>
+    <t xml:space="preserve">9.69079208374023</t>
   </si>
   <si>
     <t xml:space="preserve">9.79762554168701</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">9.7375316619873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96900653839111</t>
+    <t xml:space="preserve">9.9690055847168</t>
   </si>
   <si>
     <t xml:space="preserve">9.60176181793213</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">9.7775936126709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94229698181152</t>
+    <t xml:space="preserve">9.94229793548584</t>
   </si>
   <si>
     <t xml:space="preserve">9.62179470062256</t>
@@ -2099,10 +2099,10 @@
     <t xml:space="preserve">10.1070013046265</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96455478668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1715469360352</t>
+    <t xml:space="preserve">9.96455383300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1715459823608</t>
   </si>
   <si>
     <t xml:space="preserve">9.89555740356445</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">9.71304893493652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46821784973145</t>
+    <t xml:space="preserve">9.46821880340576</t>
   </si>
   <si>
     <t xml:space="preserve">9.55057048797607</t>
@@ -2120,31 +2120,31 @@
     <t xml:space="preserve">9.79094886779785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.191577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2717037200928</t>
+    <t xml:space="preserve">10.1915788650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2717046737671</t>
   </si>
   <si>
     <t xml:space="preserve">9.75088500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99794101715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91558837890625</t>
+    <t xml:space="preserve">9.99794006347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91558933258057</t>
   </si>
   <si>
     <t xml:space="preserve">9.52386093139648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24342060089111</t>
+    <t xml:space="preserve">9.24342155456543</t>
   </si>
   <si>
     <t xml:space="preserve">9.19668102264404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12545871734619</t>
+    <t xml:space="preserve">9.12545776367188</t>
   </si>
   <si>
     <t xml:space="preserve">8.72927951812744</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">9.62401962280273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6707592010498</t>
+    <t xml:space="preserve">9.67076015472412</t>
   </si>
   <si>
     <t xml:space="preserve">9.64405155181885</t>
@@ -2189,22 +2189,22 @@
     <t xml:space="preserve">10.0268754959106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1047735214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1136779785156</t>
+    <t xml:space="preserve">10.1047744750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1136770248413</t>
   </si>
   <si>
     <t xml:space="preserve">10.1403856277466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4230527877808</t>
+    <t xml:space="preserve">10.4230537414551</t>
   </si>
   <si>
     <t xml:space="preserve">9.94452285766602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91781520843506</t>
+    <t xml:space="preserve">9.91781425476074</t>
   </si>
   <si>
     <t xml:space="preserve">9.64850234985352</t>
@@ -2213,10 +2213,10 @@
     <t xml:space="preserve">9.56392574310303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26790428161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26567840576172</t>
+    <t xml:space="preserve">9.26790332794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26567935943604</t>
   </si>
   <si>
     <t xml:space="preserve">9.05868625640869</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">9.57950496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65963077545166</t>
+    <t xml:space="preserve">9.65963172912598</t>
   </si>
   <si>
     <t xml:space="preserve">9.15216636657715</t>
@@ -2249,16 +2249,16 @@
     <t xml:space="preserve">9.92226696014404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85772037506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95787811279297</t>
+    <t xml:space="preserve">9.85771942138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95787906646729</t>
   </si>
   <si>
     <t xml:space="preserve">9.87775135040283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80430221557617</t>
+    <t xml:space="preserve">9.80430126190186</t>
   </si>
   <si>
     <t xml:space="preserve">9.85549449920654</t>
@@ -2270,10 +2270,10 @@
     <t xml:space="preserve">9.802077293396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53499031066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40812397003174</t>
+    <t xml:space="preserve">9.53498935699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40812492370605</t>
   </si>
   <si>
     <t xml:space="preserve">9.51941108703613</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">9.43483257293701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49937915802002</t>
+    <t xml:space="preserve">9.4993782043457</t>
   </si>
   <si>
     <t xml:space="preserve">9.24564647674561</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">9.6952428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83546257019043</t>
+    <t xml:space="preserve">9.83546352386475</t>
   </si>
   <si>
     <t xml:space="preserve">9.9066858291626</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">9.90223407745361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85994625091553</t>
+    <t xml:space="preserve">9.85994529724121</t>
   </si>
   <si>
     <t xml:space="preserve">9.85326957702637</t>
@@ -2345,13 +2345,13 @@
     <t xml:space="preserve">8.54231834411621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43770980834961</t>
+    <t xml:space="preserve">8.43770885467529</t>
   </si>
   <si>
     <t xml:space="preserve">8.47332096099854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34868144989014</t>
+    <t xml:space="preserve">8.34868049621582</t>
   </si>
   <si>
     <t xml:space="preserve">8.43548393249512</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">8.35758304595947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71657609939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62754726409912</t>
+    <t xml:space="preserve">7.71657657623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62754821777344</t>
   </si>
   <si>
     <t xml:space="preserve">8.00369453430176</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">7.71212434768677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36268615722656</t>
+    <t xml:space="preserve">7.36268663406372</t>
   </si>
   <si>
     <t xml:space="preserve">6.30546808242798</t>
@@ -2387,10 +2387,10 @@
     <t xml:space="preserve">4.88545846939087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34126901626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58275985717773</t>
+    <t xml:space="preserve">4.34126853942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58275938034058</t>
   </si>
   <si>
     <t xml:space="preserve">4.3891224861145</t>
@@ -2405,10 +2405,10 @@
     <t xml:space="preserve">5.09022426605225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00342178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88990926742554</t>
+    <t xml:space="preserve">5.00342130661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8899097442627</t>
   </si>
   <si>
     <t xml:space="preserve">5.19260740280151</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">5.1658992767334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22599315643311</t>
+    <t xml:space="preserve">5.22599363327026</t>
   </si>
   <si>
     <t xml:space="preserve">4.96781015396118</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">5.37956809997559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28386211395264</t>
+    <t xml:space="preserve">5.28386259078979</t>
   </si>
   <si>
     <t xml:space="preserve">5.33950567245483</t>
@@ -2447,13 +2447,13 @@
     <t xml:space="preserve">5.36398839950562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29276514053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83871746063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85429859161377</t>
+    <t xml:space="preserve">5.29276561737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83871793746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85429811477661</t>
   </si>
   <si>
     <t xml:space="preserve">4.87210369110107</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">4.68514347076416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95445489883423</t>
+    <t xml:space="preserve">4.95445537567139</t>
   </si>
   <si>
     <t xml:space="preserve">5.03012990951538</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">4.88100624084473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92552089691162</t>
+    <t xml:space="preserve">4.92552137374878</t>
   </si>
   <si>
     <t xml:space="preserve">5.19928550720215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21041345596313</t>
+    <t xml:space="preserve">5.21041393280029</t>
   </si>
   <si>
     <t xml:space="preserve">5.08354759216309</t>
@@ -2489,7 +2489,7 @@
     <t xml:space="preserve">4.98338985443115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11470746994019</t>
+    <t xml:space="preserve">5.11470794677734</t>
   </si>
   <si>
     <t xml:space="preserve">5.15031909942627</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">5.02122688293457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92329597473145</t>
+    <t xml:space="preserve">4.92329549789429</t>
   </si>
   <si>
     <t xml:space="preserve">4.96113300323486</t>
@@ -6414,6 +6414,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.36999988555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32200002670288</t>
   </si>
 </sst>
 </file>
@@ -75312,6 +75315,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2638">
+      <c r="A2638" s="1" t="n">
+        <v>46163.2916666667</v>
+      </c>
+      <c r="B2638" t="n">
+        <v>20614131</v>
+      </c>
+      <c r="C2638" t="n">
+        <v>4.39400005340576</v>
+      </c>
+      <c r="D2638" t="n">
+        <v>4.30600023269653</v>
+      </c>
+      <c r="E2638" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="F2638" t="n">
+        <v>4.32200002670288</v>
+      </c>
+      <c r="G2638" t="s">
+        <v>2134</v>
+      </c>
+      <c r="H2638" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -447,7 +447,7 @@
         <v>23.2093391418457</v>
       </c>
       <c r="G3" t="n">
-        <v>20.5791053771973</v>
+        <v>20.5791072845459</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>21.9295864105225</v>
       </c>
       <c r="G5" t="n">
-        <v>19.4443855285645</v>
+        <v>19.4443836212158</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>21.3766078948975</v>
       </c>
       <c r="G6" t="n">
-        <v>18.9540729522705</v>
+        <v>18.9540748596191</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>22.4193687438965</v>
       </c>
       <c r="G8" t="n">
-        <v>19.8786602020264</v>
+        <v>19.878662109375</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811958312988</v>
+        <v>17.5811977386475</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460279464722</v>
+        <v>15.7460269927979</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>16.7157802581787</v>
       </c>
       <c r="G15" t="n">
-        <v>14.8214406967163</v>
+        <v>14.821439743042</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>13.2778282165527</v>
       </c>
       <c r="G16" t="n">
-        <v>11.773099899292</v>
+        <v>11.7730989456177</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>15.7389078140259</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9552736282349</v>
+        <v>13.9552726745605</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>13.806058883667</v>
       </c>
       <c r="G19" t="n">
-        <v>12.2414674758911</v>
+        <v>12.2414665222168</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G21" t="n">
-        <v>12.6977405548096</v>
+        <v>12.6977415084839</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.358302116394</v>
       </c>
       <c r="G22" t="n">
-        <v>12.7311267852783</v>
+        <v>12.7311277389526</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.8813648223877</v>
       </c>
       <c r="G23" t="n">
-        <v>12.3082399368286</v>
+        <v>12.30823802948</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>13.5048360824585</v>
       </c>
       <c r="G24" t="n">
-        <v>11.9743804931641</v>
+        <v>11.9743814468384</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.0530023574829</v>
       </c>
       <c r="G26" t="n">
-        <v>11.5737524032593</v>
+        <v>11.573751449585</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G29" t="n">
-        <v>8.0571117401123</v>
+        <v>8.05711078643799</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.87747955322266</v>
+        <v>6.87747859954834</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51180982589722</v>
+        <v>7.51181030273438</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.30120658874512</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36045980453491</v>
+        <v>7.36046028137207</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243982315063</v>
+        <v>7.91243934631348</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G40" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.67679214477539</v>
       </c>
       <c r="G45" t="n">
-        <v>8.58015537261963</v>
+        <v>8.58015632629395</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.96546459197998</v>
       </c>
       <c r="G46" t="n">
-        <v>8.83611392974854</v>
+        <v>8.83611297607422</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.07714366912842</v>
+        <v>8.0771427154541</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811340332031</v>
+        <v>7.98811292648315</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683395385742</v>
+        <v>8.58683300018311</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G53" t="n">
-        <v>8.29526329040527</v>
+        <v>8.29526424407959</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.3175220489502</v>
+        <v>8.31752109527588</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G57" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.34488010406494</v>
+        <v>7.34487962722778</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.93628597259521</v>
       </c>
       <c r="G62" t="n">
-        <v>7.92356824874878</v>
+        <v>7.92356872558594</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8.83838844299316</v>
       </c>
       <c r="G63" t="n">
-        <v>7.8367657661438</v>
+        <v>7.83676528930664</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870809555054</v>
+        <v>7.65870761871338</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G65" t="n">
-        <v>7.32262372970581</v>
+        <v>7.32262420654297</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.78159713745117</v>
       </c>
       <c r="G66" t="n">
-        <v>6.89973592758179</v>
+        <v>6.89973640441895</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365732192993</v>
+        <v>7.27365779876709</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G70" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.8634729385376</v>
+        <v>7.86347341537476</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09939956665039</v>
+        <v>8.09940052032471</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G75" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.25006008148193</v>
       </c>
       <c r="G79" t="n">
-        <v>8.20178318023682</v>
+        <v>8.20178413391113</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.39816093444824</v>
       </c>
       <c r="G80" t="n">
-        <v>8.33310031890869</v>
+        <v>8.33310127258301</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.55128288269043</v>
       </c>
       <c r="G81" t="n">
-        <v>8.46886920928955</v>
+        <v>8.46887016296387</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912178039551</v>
+        <v>8.62912082672119</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G83" t="n">
-        <v>9.68188762664795</v>
+        <v>9.68188858032227</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G84" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G87" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G88" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G89" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.20487594604492</v>
       </c>
       <c r="G91" t="n">
-        <v>8.16172027587891</v>
+        <v>8.16171932220459</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.2685546875</v>
+        <v>8.26855373382568</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542007446289</v>
+        <v>8.39542102813721</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G96" t="n">
-        <v>8.31974601745605</v>
+        <v>8.31974697113037</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G97" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588800430298</v>
+        <v>7.98588752746582</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701690673828</v>
+        <v>7.99701738357544</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>8.92875480651855</v>
       </c>
       <c r="G100" t="n">
-        <v>7.9168906211853</v>
+        <v>7.91689109802246</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.14212131500244</v>
       </c>
       <c r="G101" t="n">
-        <v>8.10607814788818</v>
+        <v>8.10607719421387</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.3303861618042</v>
       </c>
       <c r="G105" t="n">
-        <v>8.27300643920898</v>
+        <v>8.27300548553467</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G106" t="n">
-        <v>8.18842887878418</v>
+        <v>8.1884298324585</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.04924392700195</v>
       </c>
       <c r="G108" t="n">
-        <v>8.02372455596924</v>
+        <v>8.02372550964355</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889585494995</v>
+        <v>7.77889537811279</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701690673828</v>
+        <v>7.99701738357544</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.5261812210083</v>
       </c>
       <c r="G111" t="n">
-        <v>8.44661331176758</v>
+        <v>8.44661235809326</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G112" t="n">
-        <v>8.85837173461914</v>
+        <v>8.85837268829346</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.28018188476562</v>
       </c>
       <c r="G114" t="n">
-        <v>8.22849178314209</v>
+        <v>8.22849273681641</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325277328491</v>
+        <v>7.72325372695923</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660755157471</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808242797852</v>
+        <v>7.96808195114136</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G118" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.05933570861816</v>
+        <v>8.05933666229248</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.59193658828735</v>
+        <v>7.59193563461304</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78557395935059</v>
+        <v>7.78557348251343</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.86349010467529</v>
       </c>
       <c r="G127" t="n">
-        <v>7.85902261734009</v>
+        <v>7.85902214050293</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.60650730133057</v>
       </c>
       <c r="G130" t="n">
-        <v>8.51783657073975</v>
+        <v>8.51783561706543</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G131" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G132" t="n">
-        <v>7.823410987854</v>
+        <v>7.82341051101685</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.04171371459961</v>
       </c>
       <c r="G133" t="n">
-        <v>8.01704883575439</v>
+        <v>8.01704788208008</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.44083404541016</v>
       </c>
       <c r="G134" t="n">
-        <v>8.37093734741211</v>
+        <v>8.37093830108643</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420448303223</v>
+        <v>9.03420257568359</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G138" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>10.3771362304688</v>
       </c>
       <c r="G139" t="n">
-        <v>9.20113182067871</v>
+        <v>9.20113277435303</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>10.5679111480713</v>
       </c>
       <c r="G140" t="n">
-        <v>9.37028789520264</v>
+        <v>9.37028694152832</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>10.977071762085</v>
       </c>
       <c r="G142" t="n">
-        <v>9.73307800292969</v>
+        <v>9.733078956604</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G144" t="n">
-        <v>9.68856620788574</v>
+        <v>9.68856430053711</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>10.359564781189</v>
       </c>
       <c r="G145" t="n">
-        <v>9.18555164337158</v>
+        <v>9.1855525970459</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G149" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G151" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.37807941436768</v>
       </c>
       <c r="G153" t="n">
-        <v>8.31529426574707</v>
+        <v>8.31529521942139</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.90019989013672</v>
       </c>
       <c r="G155" t="n">
-        <v>8.77824592590332</v>
+        <v>8.778244972229</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.0056276321411</v>
       </c>
       <c r="G156" t="n">
-        <v>8.87172508239746</v>
+        <v>8.87172603607178</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G157" t="n">
-        <v>8.7760181427002</v>
+        <v>8.77601909637451</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>10.3269319534302</v>
       </c>
       <c r="G159" t="n">
-        <v>9.15661716461182</v>
+        <v>9.15661811828613</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G160" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.03642845153809</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G169" t="n">
-        <v>9.08094310760498</v>
+        <v>9.0809440612793</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G170" t="n">
-        <v>9.16997241973877</v>
+        <v>9.16997337341309</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548778533936</v>
+        <v>9.14548873901367</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>10.457462310791</v>
       </c>
       <c r="G174" t="n">
-        <v>9.27235412597656</v>
+        <v>9.27235507965088</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G175" t="n">
-        <v>9.16997241973877</v>
+        <v>9.16997337341309</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G176" t="n">
-        <v>9.2078104019165</v>
+        <v>9.20780944824219</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G177" t="n">
-        <v>9.23451805114746</v>
+        <v>9.23451900482178</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G179" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.44836521148682</v>
       </c>
       <c r="G180" t="n">
-        <v>8.37761497497559</v>
+        <v>8.3776159286499</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G182" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.95887660980225</v>
       </c>
       <c r="G183" t="n">
-        <v>7.94359874725342</v>
+        <v>7.94359827041626</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.79225015640259</v>
+        <v>7.79224967956543</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.90365314483643</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89463424682617</v>
+        <v>7.89463329315186</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.28771305084229</v>
       </c>
       <c r="G188" t="n">
-        <v>8.23516845703125</v>
+        <v>8.23516941070557</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.73883295059204</v>
+        <v>7.7388334274292</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G192" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G193" t="n">
-        <v>8.38429164886475</v>
+        <v>8.38429260253906</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G197" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.77217960357666</v>
       </c>
       <c r="G198" t="n">
-        <v>8.66473293304443</v>
+        <v>8.66473388671875</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G199" t="n">
-        <v>8.94294929504395</v>
+        <v>8.94294834136963</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.063362121582</v>
       </c>
       <c r="G200" t="n">
-        <v>8.92291736602783</v>
+        <v>8.92291641235352</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>10.1662797927856</v>
       </c>
       <c r="G202" t="n">
-        <v>9.0141716003418</v>
+        <v>9.01417064666748</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G203" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10.3696060180664</v>
       </c>
       <c r="G204" t="n">
-        <v>9.19445610046387</v>
+        <v>9.19445514678955</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.8139095306396</v>
       </c>
       <c r="G206" t="n">
-        <v>9.58840847015381</v>
+        <v>9.58840751647949</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G207" t="n">
-        <v>9.68856620788574</v>
+        <v>9.68856430053711</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>10.9519701004028</v>
       </c>
       <c r="G208" t="n">
-        <v>9.71082210540771</v>
+        <v>9.71082305908203</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G209" t="n">
-        <v>9.68188762664795</v>
+        <v>9.68188858032227</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.03642845153809</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G212" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.34645557403564</v>
+        <v>8.34645462036133</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.22244834899902</v>
       </c>
       <c r="G216" t="n">
-        <v>8.17730140686035</v>
+        <v>8.17730045318604</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G219" t="n">
-        <v>8.38429164886475</v>
+        <v>8.38429260253906</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G224" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.2240142822266</v>
       </c>
       <c r="G225" t="n">
-        <v>9.06536293029785</v>
+        <v>9.06536388397217</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.0834436416626</v>
       </c>
       <c r="G226" t="n">
-        <v>8.94072246551514</v>
+        <v>8.94072341918945</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.2215042114258</v>
       </c>
       <c r="G231" t="n">
-        <v>9.06313800811768</v>
+        <v>9.06313705444336</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G234" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.71193504333496</v>
       </c>
       <c r="G235" t="n">
-        <v>8.61131477355957</v>
+        <v>8.61131572723389</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.9695415496826</v>
       </c>
       <c r="G237" t="n">
-        <v>9.72640228271484</v>
+        <v>9.72640323638916</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>11.484130859375</v>
       </c>
       <c r="G240" t="n">
-        <v>10.182674407959</v>
+        <v>10.1826753616333</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>11.6347427368164</v>
       </c>
       <c r="G241" t="n">
-        <v>10.316219329834</v>
+        <v>10.3162183761597</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.9218482971191</v>
       </c>
       <c r="G243" t="n">
-        <v>9.68411445617676</v>
+        <v>9.68411350250244</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>11.2406415939331</v>
       </c>
       <c r="G244" t="n">
-        <v>9.96677875518799</v>
+        <v>9.9667797088623</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.9309453964233</v>
       </c>
       <c r="G247" t="n">
-        <v>10.5788536071777</v>
+        <v>10.5788545608521</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>12.8019819259644</v>
       </c>
       <c r="G250" t="n">
-        <v>11.3511800765991</v>
+        <v>11.3511781692505</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G251" t="n">
-        <v>10.9883871078491</v>
+        <v>10.9883861541748</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>13.0906553268433</v>
       </c>
       <c r="G254" t="n">
-        <v>11.6071376800537</v>
+        <v>11.607138633728</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>13.2287149429321</v>
       </c>
       <c r="G255" t="n">
-        <v>11.7295513153076</v>
+        <v>11.7295522689819</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076099395752</v>
+        <v>11.9076108932495</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.0319766998291</v>
       </c>
       <c r="G258" t="n">
-        <v>12.4417819976807</v>
+        <v>12.441782951355</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G259" t="n">
-        <v>12.6977405548096</v>
+        <v>12.6977415084839</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.3165721893311</v>
       </c>
       <c r="G263" t="n">
-        <v>11.8074531555176</v>
+        <v>11.8074522018433</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>12.7517786026001</v>
       </c>
       <c r="G264" t="n">
-        <v>11.3066654205322</v>
+        <v>11.3066644668579</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>12.8647365570068</v>
       </c>
       <c r="G267" t="n">
-        <v>11.4068212509155</v>
+        <v>11.4068222045898</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>12.2999439239502</v>
       </c>
       <c r="G268" t="n">
-        <v>10.9060344696045</v>
+        <v>10.9060354232788</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.5635137557983</v>
       </c>
       <c r="G269" t="n">
-        <v>11.1397342681885</v>
+        <v>11.1397352218628</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>12.6011667251587</v>
       </c>
       <c r="G272" t="n">
-        <v>11.1731204986572</v>
+        <v>11.1731214523315</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>12.4455347061157</v>
       </c>
       <c r="G273" t="n">
-        <v>11.0351257324219</v>
+        <v>11.0351266860962</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.5007591247559</v>
       </c>
       <c r="G274" t="n">
-        <v>11.0840921401978</v>
+        <v>11.0840930938721</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>13.3040208816528</v>
       </c>
       <c r="G275" t="n">
-        <v>11.7963228225708</v>
+        <v>11.7963237762451</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>13.1283073425293</v>
       </c>
       <c r="G276" t="n">
-        <v>11.6405220031738</v>
+        <v>11.6405229568481</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960083007812</v>
+        <v>11.5960092544556</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G280" t="n">
-        <v>10.5276622772217</v>
+        <v>10.5276613235474</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141492843628</v>
+        <v>10.4141502380371</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.39857006073</v>
+        <v>10.3985710144043</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.707537651062</v>
       </c>
       <c r="G287" t="n">
-        <v>10.3807640075684</v>
+        <v>10.3807649612427</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.0213117599487</v>
       </c>
       <c r="G288" t="n">
-        <v>10.6589784622192</v>
+        <v>10.6589794158936</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>11.6372528076172</v>
       </c>
       <c r="G293" t="n">
-        <v>10.3184432983398</v>
+        <v>10.3184442520142</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.5428085327148</v>
       </c>
       <c r="G303" t="n">
-        <v>9.34803009033203</v>
+        <v>9.34802913665771</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10.1386680603027</v>
       </c>
       <c r="G307" t="n">
-        <v>8.98968887329102</v>
+        <v>8.9896879196167</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.2491159439087</v>
       </c>
       <c r="G308" t="n">
-        <v>9.08762073516846</v>
+        <v>9.08761978149414</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520519256592</v>
+        <v>8.96520709991455</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10.218994140625</v>
       </c>
       <c r="G310" t="n">
-        <v>9.06091117858887</v>
+        <v>9.06091213226318</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.3244218826294</v>
       </c>
       <c r="G311" t="n">
-        <v>9.15439224243164</v>
+        <v>9.15439128875732</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10.1562385559082</v>
       </c>
       <c r="G317" t="n">
-        <v>9.00526809692383</v>
+        <v>9.00526714324951</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>10.8164196014404</v>
       </c>
       <c r="G321" t="n">
-        <v>9.59063243865967</v>
+        <v>9.59063339233398</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>10.6808700561523</v>
       </c>
       <c r="G322" t="n">
-        <v>9.47044467926025</v>
+        <v>9.47044563293457</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77982044219971</v>
+        <v>9.77981853485107</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>10.2691984176636</v>
       </c>
       <c r="G331" t="n">
-        <v>9.10542678833008</v>
+        <v>9.10542583465576</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10.0784225463867</v>
       </c>
       <c r="G333" t="n">
-        <v>8.93626976013184</v>
+        <v>8.93627071380615</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G339" t="n">
-        <v>8.94294929504395</v>
+        <v>8.94294834136963</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G342" t="n">
-        <v>8.85837173461914</v>
+        <v>8.85837268829346</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G344" t="n">
-        <v>8.87840175628662</v>
+        <v>8.87840270996094</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>10.0332403182983</v>
       </c>
       <c r="G345" t="n">
-        <v>8.89620780944824</v>
+        <v>8.89620876312256</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G347" t="n">
-        <v>8.87840175628662</v>
+        <v>8.87840270996094</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10.003116607666</v>
       </c>
       <c r="G349" t="n">
-        <v>8.86949920654297</v>
+        <v>8.86949825286865</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G353" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G355" t="n">
-        <v>8.86282253265381</v>
+        <v>8.86282348632812</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G357" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.36301803588867</v>
       </c>
       <c r="G359" t="n">
-        <v>8.30194091796875</v>
+        <v>8.30193996429443</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G361" t="n">
-        <v>8.12833499908447</v>
+        <v>8.12833404541016</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G362" t="n">
-        <v>8.0348539352417</v>
+        <v>8.03485488891602</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.99033880233765</v>
+        <v>7.9903392791748</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G365" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G366" t="n">
-        <v>7.66093349456787</v>
+        <v>7.66093397140503</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215675354004</v>
+        <v>7.73215627670288</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G370" t="n">
-        <v>8.0571117401123</v>
+        <v>8.05711078643799</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>8.88106060028076</v>
       </c>
       <c r="G372" t="n">
-        <v>7.8746018409729</v>
+        <v>7.87460136413574</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G373" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G374" t="n">
-        <v>7.32262372970581</v>
+        <v>7.32262420654297</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G376" t="n">
-        <v>7.19798278808594</v>
+        <v>7.1979832649231</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.13302421569824</v>
       </c>
       <c r="G377" t="n">
-        <v>7.21133756637573</v>
+        <v>7.21133661270142</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914218902588</v>
+        <v>7.22914266586304</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817197799683</v>
+        <v>7.31817245483398</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G383" t="n">
-        <v>7.23804569244385</v>
+        <v>7.23804521560669</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G384" t="n">
-        <v>7.19798278808594</v>
+        <v>7.1979832649231</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055463790894</v>
+        <v>7.42055511474609</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.44428825378418</v>
       </c>
       <c r="G387" t="n">
-        <v>7.48732662200928</v>
+        <v>7.48732709884644</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G389" t="n">
-        <v>7.32262372970581</v>
+        <v>7.32262420654297</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8.4242057800293</v>
       </c>
       <c r="G390" t="n">
-        <v>7.46952104568481</v>
+        <v>7.46952056884766</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390941619873</v>
+        <v>7.43390846252441</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G392" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.85679721832275</v>
+        <v>7.8567967414856</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>8.52461433410645</v>
       </c>
       <c r="G397" t="n">
-        <v>7.55854988098145</v>
+        <v>7.5585503578186</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842359542847</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G403" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>8.6953067779541</v>
       </c>
       <c r="G404" t="n">
-        <v>7.70989847183228</v>
+        <v>7.70989894866943</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G405" t="n">
-        <v>7.70099544525146</v>
+        <v>7.70099496841431</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757823944092</v>
+        <v>7.64757919311523</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G408" t="n">
-        <v>7.58525800704956</v>
+        <v>7.5852575302124</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428731918335</v>
+        <v>7.67428636550903</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.5748176574707</v>
       </c>
       <c r="G411" t="n">
-        <v>7.60306406021118</v>
+        <v>7.60306453704834</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G413" t="n">
-        <v>7.50513219833374</v>
+        <v>7.50513172149658</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249744415283</v>
+        <v>7.24249792098999</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701162338257</v>
+        <v>7.28701210021973</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.74645376205444</v>
       </c>
       <c r="G428" t="n">
-        <v>6.86857604980469</v>
+        <v>6.86857557296753</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.76151514053345</v>
       </c>
       <c r="G429" t="n">
-        <v>6.88192987442017</v>
+        <v>6.88193035125732</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G432" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591464996338</v>
+        <v>7.29591369628906</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409908294678</v>
+        <v>7.55409860610962</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G439" t="n">
-        <v>7.58525800704956</v>
+        <v>7.5852575302124</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G440" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.66538381576538</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G442" t="n">
-        <v>7.70099544525146</v>
+        <v>7.70099496841431</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.09693813323975</v>
       </c>
       <c r="G446" t="n">
-        <v>8.06601524353027</v>
+        <v>8.06601428985596</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G447" t="n">
-        <v>8.12833499908447</v>
+        <v>8.12833404541016</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G449" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504264831543</v>
+        <v>8.15504360198975</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.15216159820557</v>
       </c>
       <c r="G455" t="n">
-        <v>8.1149787902832</v>
+        <v>8.11497974395752</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G457" t="n">
-        <v>7.77221870422363</v>
+        <v>7.77221822738647</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.92122364044189</v>
       </c>
       <c r="G459" t="n">
-        <v>7.91021347045898</v>
+        <v>7.91021299362183</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G460" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.4294581413269</v>
+        <v>7.42945766448975</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G464" t="n">
-        <v>7.23804569244385</v>
+        <v>7.23804521560669</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>9.04673385620117</v>
       </c>
       <c r="G465" t="n">
-        <v>8.02150058746338</v>
+        <v>8.02149963378906</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.66538381576538</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G468" t="n">
-        <v>7.64312696456909</v>
+        <v>7.64312648773193</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479150772095</v>
+        <v>7.99479103088379</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G470" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.63914012908936</v>
       </c>
       <c r="G472" t="n">
-        <v>8.54677104949951</v>
+        <v>8.5467700958252</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G476" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.44836521148682</v>
       </c>
       <c r="G479" t="n">
-        <v>8.37761497497559</v>
+        <v>8.3776159286499</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G480" t="n">
-        <v>7.78557395935059</v>
+        <v>7.78557348251343</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757823944092</v>
+        <v>7.64757919311523</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576267242432</v>
+        <v>7.90576314926147</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344148635864</v>
+        <v>7.84344244003296</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G490" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G492" t="n">
-        <v>7.50513219833374</v>
+        <v>7.50513172149658</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G493" t="n">
-        <v>7.64312696456909</v>
+        <v>7.64312648773193</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G495" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>8.39910411834717</v>
       </c>
       <c r="G498" t="n">
-        <v>7.44726371765137</v>
+        <v>7.44726324081421</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G500" t="n">
-        <v>7.77221870422363</v>
+        <v>7.77221822738647</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G501" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>8.39910411834717</v>
       </c>
       <c r="G502" t="n">
-        <v>7.44726371765137</v>
+        <v>7.44726324081421</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>8.34889984130859</v>
       </c>
       <c r="G503" t="n">
-        <v>7.40274810791016</v>
+        <v>7.40274858474731</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.7499623298645</v>
+        <v>7.74996280670166</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G505" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>9.11199855804443</v>
       </c>
       <c r="G506" t="n">
-        <v>8.07936763763428</v>
+        <v>8.07936859130859</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G507" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.55379295349121</v>
       </c>
       <c r="G511" t="n">
-        <v>8.47109508514404</v>
+        <v>8.47109603881836</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.5022554397583</v>
+        <v>8.50225639343262</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.76464939117432</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65805721282959</v>
+        <v>8.65805625915527</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.03642845153809</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G527" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G529" t="n">
-        <v>9.04087924957275</v>
+        <v>9.04088020324707</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G530" t="n">
-        <v>9.04087924957275</v>
+        <v>9.04088020324707</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833980560303</v>
+        <v>8.83833885192871</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.60399723052979</v>
       </c>
       <c r="G532" t="n">
-        <v>8.51560974121094</v>
+        <v>8.51561069488525</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>9.30277442932129</v>
       </c>
       <c r="G535" t="n">
-        <v>8.24852466583252</v>
+        <v>8.2485237121582</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G537" t="n">
-        <v>7.823410987854</v>
+        <v>7.82341051101685</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G538" t="n">
-        <v>8.0348539352417</v>
+        <v>8.03485488891602</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660755157471</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519510269165</v>
+        <v>7.54519557952881</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G545" t="n">
-        <v>7.66093349456787</v>
+        <v>7.66093397140503</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G548" t="n">
-        <v>7.60083818435669</v>
+        <v>7.60083913803101</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.76331663131714</v>
+        <v>7.76331615447998</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.5229377746582</v>
+        <v>7.52293825149536</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368877410889</v>
+        <v>7.29368829727173</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>8.32379913330078</v>
       </c>
       <c r="G563" t="n">
-        <v>7.38049173355103</v>
+        <v>7.38049268722534</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.31124782562256</v>
       </c>
       <c r="G564" t="n">
-        <v>7.36936330795288</v>
+        <v>7.36936378479004</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613433837891</v>
+        <v>7.43613481521606</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585174560547</v>
+        <v>7.25585079193115</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.32128810882568</v>
       </c>
       <c r="G567" t="n">
-        <v>7.37826681137085</v>
+        <v>7.37826633453369</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>8.43173694610596</v>
       </c>
       <c r="G568" t="n">
-        <v>7.47619819641113</v>
+        <v>7.47619771957397</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>8.16063594818115</v>
       </c>
       <c r="G569" t="n">
-        <v>7.23582029342651</v>
+        <v>7.23581981658936</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G573" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.79163789749146</v>
       </c>
       <c r="G576" t="n">
-        <v>6.90863943099976</v>
+        <v>6.9086389541626</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744762420654</v>
+        <v>6.85744714736938</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G583" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G586" t="n">
-        <v>7.48064947128296</v>
+        <v>7.4806489944458</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842359542847</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G589" t="n">
-        <v>7.48064947128296</v>
+        <v>7.4806489944458</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766778945923</v>
+        <v>6.99766731262207</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443929672241</v>
+        <v>7.06443881988525</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.55222606658936</v>
       </c>
       <c r="G603" t="n">
-        <v>7.58303260803223</v>
+        <v>7.58303213119507</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065380096436</v>
+        <v>8.19065475463867</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G621" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G627" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>9.36552906036377</v>
       </c>
       <c r="G630" t="n">
-        <v>8.30416679382324</v>
+        <v>8.30416774749756</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G633" t="n">
-        <v>8.12833499908447</v>
+        <v>8.12833404541016</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G634" t="n">
-        <v>8.12833499908447</v>
+        <v>8.12833404541016</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G636" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>9.90019989013672</v>
       </c>
       <c r="G637" t="n">
-        <v>8.77824592590332</v>
+        <v>8.778244972229</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.86254692077637</v>
       </c>
       <c r="G639" t="n">
-        <v>8.74485969543457</v>
+        <v>8.74485874176025</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G640" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>10.2767276763916</v>
       </c>
       <c r="G643" t="n">
-        <v>9.11210155487061</v>
+        <v>9.11210250854492</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G644" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009822845459</v>
+        <v>9.25009727478027</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.4649925231934</v>
       </c>
       <c r="G647" t="n">
-        <v>9.27903270721436</v>
+        <v>9.27903175354004</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G651" t="n">
-        <v>9.0564603805542</v>
+        <v>9.05646133422852</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100601196289</v>
+        <v>9.12100505828857</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G660" t="n">
-        <v>9.84659099578857</v>
+        <v>9.84659194946289</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G661" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G662" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G664" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>11.2331123352051</v>
       </c>
       <c r="G666" t="n">
-        <v>9.96010398864746</v>
+        <v>9.96010303497314</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G667" t="n">
-        <v>9.87107467651367</v>
+        <v>9.87107372283936</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>11.6322326660156</v>
       </c>
       <c r="G669" t="n">
-        <v>10.3139925003052</v>
+        <v>10.3139934539795</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G671" t="n">
-        <v>9.80652809143066</v>
+        <v>9.80652904510498</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>11.6648645401001</v>
       </c>
       <c r="G674" t="n">
-        <v>10.3429260253906</v>
+        <v>10.3429269790649</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>11.5167636871338</v>
       </c>
       <c r="G675" t="n">
-        <v>10.2116088867188</v>
+        <v>10.2116098403931</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>11.4665603637695</v>
       </c>
       <c r="G680" t="n">
-        <v>10.1670961380005</v>
+        <v>10.1670951843262</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>11.700008392334</v>
       </c>
       <c r="G683" t="n">
-        <v>10.3740873336792</v>
+        <v>10.3740882873535</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G684" t="n">
-        <v>10.3340244293213</v>
+        <v>10.334023475647</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99348926544189</v>
+        <v>9.99349021911621</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694797515869</v>
+        <v>10.2694787979126</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>11.5017032623291</v>
       </c>
       <c r="G688" t="n">
-        <v>10.1982555389404</v>
+        <v>10.1982564926147</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>11.328498840332</v>
       </c>
       <c r="G690" t="n">
-        <v>10.0446805953979</v>
+        <v>10.0446796417236</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G691" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>12.0489253997803</v>
       </c>
       <c r="G692" t="n">
-        <v>10.6834630966187</v>
+        <v>10.683464050293</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G693" t="n">
-        <v>10.8259086608887</v>
+        <v>10.8259077072144</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.756911277771</v>
+        <v>10.7569122314453</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>12.4580860137939</v>
       </c>
       <c r="G697" t="n">
-        <v>11.0462560653687</v>
+        <v>11.0462551116943</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>13.1232872009277</v>
       </c>
       <c r="G698" t="n">
-        <v>11.6360712051392</v>
+        <v>11.6360721588135</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>13.7558555603027</v>
       </c>
       <c r="G704" t="n">
-        <v>12.1969528198242</v>
+        <v>12.1969537734985</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856666564941</v>
+        <v>12.0856685638428</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>13.032919883728</v>
       </c>
       <c r="G706" t="n">
-        <v>11.555944442749</v>
+        <v>11.5559453964233</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>12.7618188858032</v>
       </c>
       <c r="G709" t="n">
-        <v>11.3155670166016</v>
+        <v>11.3155679702759</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395774841309</v>
+        <v>11.0395784378052</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>12.3325757980347</v>
       </c>
       <c r="G714" t="n">
-        <v>10.9349679946899</v>
+        <v>10.9349699020386</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>11.8004150390625</v>
       </c>
       <c r="G715" t="n">
-        <v>10.4631156921387</v>
+        <v>10.463116645813</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364080429077</v>
+        <v>10.4364070892334</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G725" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>11.7025184631348</v>
       </c>
       <c r="G727" t="n">
-        <v>10.3763132095337</v>
+        <v>10.376314163208</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>11.1377248764038</v>
       </c>
       <c r="G732" t="n">
-        <v>9.87552547454834</v>
+        <v>9.87552642822266</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>10.5402994155884</v>
       </c>
       <c r="G735" t="n">
-        <v>9.34580421447754</v>
+        <v>9.34580516815186</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G736" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081058502197</v>
+        <v>8.29081249237061</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889585494995</v>
+        <v>7.77889537811279</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219253540039</v>
+        <v>8.46219158172607</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.65922069549561</v>
       </c>
       <c r="G745" t="n">
-        <v>8.5645751953125</v>
+        <v>8.56457614898682</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G749" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G750" t="n">
-        <v>8.18842887878418</v>
+        <v>8.1884298324585</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>9.33540630340576</v>
       </c>
       <c r="G753" t="n">
-        <v>8.27745819091797</v>
+        <v>8.27745723724365</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G754" t="n">
-        <v>8.29526329040527</v>
+        <v>8.29526424407959</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466474533081</v>
+        <v>7.91466569900513</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>8.81077575683594</v>
       </c>
       <c r="G756" t="n">
-        <v>7.81228160858154</v>
+        <v>7.81228256225586</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>8.25602340698242</v>
       </c>
       <c r="G758" t="n">
-        <v>7.32039737701416</v>
+        <v>7.32039785385132</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G759" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>8.17318725585938</v>
       </c>
       <c r="G760" t="n">
-        <v>7.24694871902466</v>
+        <v>7.24694919586182</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873378753662</v>
+        <v>6.96873331069946</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>8.37400245666504</v>
       </c>
       <c r="G765" t="n">
-        <v>7.42500638961792</v>
+        <v>7.42500686645508</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576267242432</v>
+        <v>7.90576314926147</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>9.12957000732422</v>
       </c>
       <c r="G767" t="n">
-        <v>8.09494781494141</v>
+        <v>8.09494876861572</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G778" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G779" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>9.71193504333496</v>
       </c>
       <c r="G780" t="n">
-        <v>8.61131477355957</v>
+        <v>8.61131572723389</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G782" t="n">
-        <v>8.86282253265381</v>
+        <v>8.86282348632812</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>10.3445043563843</v>
       </c>
       <c r="G787" t="n">
-        <v>9.17219829559326</v>
+        <v>9.17219924926758</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G788" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>9.79477119445801</v>
       </c>
       <c r="G790" t="n">
-        <v>8.68476390838623</v>
+        <v>8.68476486206055</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>9.75711917877197</v>
       </c>
       <c r="G791" t="n">
-        <v>8.6513786315918</v>
+        <v>8.65137958526611</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G795" t="n">
-        <v>9.08094310760498</v>
+        <v>9.0809440612793</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G796" t="n">
-        <v>9.4370584487915</v>
+        <v>9.43705940246582</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G804" t="n">
-        <v>9.69746685028076</v>
+        <v>9.69746875762939</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232891082764</v>
+        <v>9.96232986450195</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>11.5167636871338</v>
       </c>
       <c r="G807" t="n">
-        <v>10.2116088867188</v>
+        <v>10.2116098403931</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496055603027</v>
+        <v>10.3496036529541</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>11.8882722854614</v>
       </c>
       <c r="G809" t="n">
-        <v>10.5410165786743</v>
+        <v>10.541015625</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G812" t="n">
-        <v>10.5276622772217</v>
+        <v>10.5276613235474</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.2572708129883</v>
       </c>
       <c r="G814" t="n">
-        <v>10.8681983947754</v>
+        <v>10.8681974411011</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>12.2145967483521</v>
       </c>
       <c r="G817" t="n">
-        <v>10.8303604125977</v>
+        <v>10.8303594589233</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G819" t="n">
-        <v>10.9883871078491</v>
+        <v>10.9883861541748</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G820" t="n">
-        <v>10.8259086608887</v>
+        <v>10.8259077072144</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>11.5970897674561</v>
       </c>
       <c r="G821" t="n">
-        <v>10.2828321456909</v>
+        <v>10.2828330993652</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>11.5368452072144</v>
       </c>
       <c r="G822" t="n">
-        <v>10.2294158935547</v>
+        <v>10.2294149398804</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G825" t="n">
-        <v>10.3340244293213</v>
+        <v>10.334023475647</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147802352905</v>
+        <v>10.8147811889648</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295736312866</v>
+        <v>10.3295726776123</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>12.0564546585083</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6901397705078</v>
+        <v>10.6901388168335</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>11.3385400772095</v>
       </c>
       <c r="G846" t="n">
-        <v>10.0535831451416</v>
+        <v>10.0535840988159</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>10.977071762085</v>
       </c>
       <c r="G848" t="n">
-        <v>9.73307800292969</v>
+        <v>9.733078956604</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G851" t="n">
-        <v>9.33912658691406</v>
+        <v>9.33912754058838</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>10.1411781311035</v>
       </c>
       <c r="G852" t="n">
-        <v>8.99191379547119</v>
+        <v>8.99191474914551</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>10.203932762146</v>
       </c>
       <c r="G854" t="n">
-        <v>9.04755783081055</v>
+        <v>9.04755687713623</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G855" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>10.4072589874268</v>
       </c>
       <c r="G856" t="n">
-        <v>9.22784233093262</v>
+        <v>9.2278413772583</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>10.5101757049561</v>
       </c>
       <c r="G860" t="n">
-        <v>9.31909561157227</v>
+        <v>9.31909465789795</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G861" t="n">
-        <v>9.25232315063477</v>
+        <v>9.25232410430908</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G863" t="n">
-        <v>8.7760181427002</v>
+        <v>8.77601909637451</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>9.62156772613525</v>
       </c>
       <c r="G868" t="n">
-        <v>8.53118896484375</v>
+        <v>8.53118991851807</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G871" t="n">
-        <v>9.07203960418701</v>
+        <v>9.07204055786133</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>10.768726348877</v>
       </c>
       <c r="G874" t="n">
-        <v>9.5483455657959</v>
+        <v>9.54834461212158</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395671844482</v>
+        <v>9.58395576477051</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G876" t="n">
-        <v>9.23451805114746</v>
+        <v>9.23451900482178</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G877" t="n">
-        <v>9.33912658691406</v>
+        <v>9.33912754058838</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079208374023</v>
+        <v>9.69079113006592</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>10.9218482971191</v>
       </c>
       <c r="G886" t="n">
-        <v>9.68411445617676</v>
+        <v>9.68411350250244</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.0498676300049</v>
       </c>
       <c r="G887" t="n">
-        <v>9.79762554168701</v>
+        <v>9.79762649536133</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.2431526184082</v>
       </c>
       <c r="G889" t="n">
-        <v>9.96900653839111</v>
+        <v>9.9690055847168</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G890" t="n">
-        <v>9.69746685028076</v>
+        <v>9.69746875762939</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>11.4715795516968</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1715459823608</v>
+        <v>10.1715469360352</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304798126221</v>
+        <v>9.71304893493652</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>11.0423374176025</v>
       </c>
       <c r="G905" t="n">
-        <v>9.79094886779785</v>
+        <v>9.79094791412354</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794006347656</v>
+        <v>9.99794101715088</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G914" t="n">
-        <v>9.2078104019165</v>
+        <v>9.20780944824219</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>10.3721160888672</v>
       </c>
       <c r="G917" t="n">
-        <v>9.19668006896973</v>
+        <v>9.19668102264404</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.95185089111328</v>
+        <v>8.9518518447876</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G934" t="n">
-        <v>9.4370584487915</v>
+        <v>9.43705940246582</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G937" t="n">
-        <v>9.80652809143066</v>
+        <v>9.80652904510498</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>11.4665603637695</v>
       </c>
       <c r="G939" t="n">
-        <v>10.1670961380005</v>
+        <v>10.1670951843262</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.104775428772</v>
+        <v>10.1047744750977</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136770248413</v>
+        <v>10.1136779785156</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230537414551</v>
+        <v>10.4230527877808</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>11.1854181289673</v>
       </c>
       <c r="G945" t="n">
-        <v>9.91781425476074</v>
+        <v>9.91781520843506</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G946" t="n">
-        <v>9.87107467651367</v>
+        <v>9.87107372283936</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G947" t="n">
-        <v>9.84659099578857</v>
+        <v>9.84659194946289</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.881685256958</v>
       </c>
       <c r="G948" t="n">
-        <v>9.64850234985352</v>
+        <v>9.64850330352783</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>10.7862977981567</v>
       </c>
       <c r="G949" t="n">
-        <v>9.56392574310303</v>
+        <v>9.56392478942871</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>10.0683822631836</v>
       </c>
       <c r="G955" t="n">
-        <v>8.92736911773682</v>
+        <v>8.92736721038818</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>10.0332403182983</v>
       </c>
       <c r="G956" t="n">
-        <v>8.89620780944824</v>
+        <v>8.89620876312256</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G961" t="n">
-        <v>9.16997241973877</v>
+        <v>9.16997337341309</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G962" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G964" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G965" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65963077545166</v>
+        <v>9.65962982177734</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>10.3219118118286</v>
       </c>
       <c r="G975" t="n">
-        <v>9.15216541290283</v>
+        <v>9.15216636657715</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.03642845153809</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>11.2306022644043</v>
       </c>
       <c r="G981" t="n">
-        <v>9.95787811279297</v>
+        <v>9.95787715911865</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812492370605</v>
+        <v>9.40812397003174</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>10.8164196014404</v>
       </c>
       <c r="G993" t="n">
-        <v>9.59063243865967</v>
+        <v>9.59063339233398</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>10.7135019302368</v>
       </c>
       <c r="G996" t="n">
-        <v>9.4993782043457</v>
+        <v>9.49937915802002</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G997" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G998" t="n">
-        <v>9.07203960418701</v>
+        <v>9.07204055786133</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G999" t="n">
-        <v>9.0564603805542</v>
+        <v>9.05646133422852</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.25232315063477</v>
+        <v>9.25232410430908</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467578887939</v>
+        <v>9.33467674255371</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.5616979598999</v>
+        <v>9.56169891357422</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>10.934398651123</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.6952428817749</v>
+        <v>9.69524192810059</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>11.1678466796875</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.90223407745361</v>
+        <v>9.90223503112793</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.31974601745605</v>
+        <v>8.31974697113037</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>9.75962924957275</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.65360546112061</v>
+        <v>8.65360450744629</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.34645557403564</v>
+        <v>8.34645462036133</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>9.55630302429199</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.47332096099854</v>
+        <v>8.47332191467285</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>9.41573238372803</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.34868049621582</v>
+        <v>8.34868144989014</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>9.51362991333008</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.4354829788208</v>
+        <v>8.43548393249512</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>9.42577266693115</v>
       </c>
       <c r="G1052" t="n">
-        <v>8.35758399963379</v>
+        <v>8.35758304595947</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754774093628</v>
+        <v>7.62754726409912</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.60083818435669</v>
+        <v>7.60083913803101</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>8.3037166595459</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.36268615722656</v>
+        <v>7.36268663406372</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585174560547</v>
+        <v>7.25585079193115</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.95009994506836</v>
       </c>
       <c r="G1068" t="n">
-        <v>4.38912296295166</v>
+        <v>4.3891224861145</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>5.16346597671509</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.57830858230591</v>
+        <v>4.57830905914307</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>5.18605804443359</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.59834003448486</v>
+        <v>4.59834051132202</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342130661011</v>
+        <v>5.00342178344727</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.88991022109985</v>
+        <v>4.88990926742554</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.0219521522522</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.33950519561768</v>
+        <v>5.33950567245483</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.29276561737061</v>
+        <v>5.29276514053345</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>5.28395509719849</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.68514347076416</v>
+        <v>4.685142993927</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>5.67303514480591</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.03013038635254</v>
+        <v>5.03012990951538</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928503036499</v>
+        <v>5.19928550720215</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041393280029</v>
+        <v>5.21041345596313</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>5.73328018188477</v>
       </c>
       <c r="G1100" t="n">
-        <v>5.08354806900024</v>
+        <v>5.08354759216309</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>5.62032079696655</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.98338937759399</v>
+        <v>4.98338985443115</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470794677734</v>
+        <v>5.11470699310303</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>5.80858516693115</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15031909942627</v>
+        <v>5.15031862258911</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248207092285</v>
+        <v>5.11248159408569</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.92329549789429</v>
+        <v>4.92329597473145</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>5.57513809204102</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.9433274269104</v>
+        <v>4.94332695007324</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.79800081253052</v>
+        <v>4.79800033569336</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>5.46217918395996</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.865074634552</v>
+        <v>4.86507511138916</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>5.30905723571777</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.72869110107422</v>
+        <v>4.72869157791138</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>5.79854488372803</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.16466999053955</v>
+        <v>5.16467046737671</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>6.46876621246338</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.76162576675415</v>
+        <v>5.76162528991699</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>6.59176588058472</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.87117910385132</v>
+        <v>5.87117958068848</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>6.41354179382324</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.71243762969971</v>
+        <v>5.71243810653687</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>5.99182987213135</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.33682584762573</v>
+        <v>5.33682632446289</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>5.98680877685547</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.3323540687561</v>
+        <v>5.33235359191895</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.0841817855835</v>
+        <v>5.08418226242065</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>5.61530113220215</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.00145816802979</v>
+        <v>5.00145769119263</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.97686338424683</v>
+        <v>4.97686290740967</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>5.68558597564697</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.06405973434448</v>
+        <v>5.06405925750732</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>5.27642488479614</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.69962596893311</v>
+        <v>4.69962644577026</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>5.28897619247437</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.71080541610718</v>
+        <v>4.71080589294434</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>5.36679220199585</v>
       </c>
       <c r="G1152" t="n">
-        <v>4.78011465072632</v>
+        <v>4.78011512756348</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.47724008560181</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.87848949432373</v>
+        <v>4.87848901748657</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>4.92123222351074</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.38326215744019</v>
+        <v>4.38326168060303</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.57357120513916</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.07360553741455</v>
+        <v>4.07360601425171</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.96892595291138</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.42574214935303</v>
+        <v>4.42574167251587</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1174" t="n">
-        <v>4.34189987182617</v>
+        <v>4.34190034866333</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.66895818710327</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.15856552124023</v>
+        <v>4.15856599807739</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.50579500198364</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.01323843002319</v>
+        <v>4.01323890686035</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.39032697677612</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.91039347648621</v>
+        <v>3.91039323806763</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.29242897033691</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.82319736480713</v>
+        <v>3.82319688796997</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>4.19327592849731</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.73488283157349</v>
+        <v>3.73488306999207</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.07906293869019</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.63315534591675</v>
+        <v>3.63315558433533</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.22465419769287</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.76283097267151</v>
+        <v>3.76283121109009</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.56321811676025</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.17370080947876</v>
+        <v>3.17370057106018</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.86444091796875</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.4419949054718</v>
+        <v>3.44199514389038</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>3.79415607452393</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.3793933391571</v>
+        <v>3.37939357757568</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>3.65609502792358</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.25642466545105</v>
+        <v>3.25642490386963</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>3.59585094451904</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.20276641845703</v>
+        <v>3.20276618003845</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>3.62597298622131</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.22959566116333</v>
+        <v>3.22959542274475</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.68496203422546</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.28213620185852</v>
+        <v>3.28213596343994</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>3.78411507606506</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.37045001983643</v>
+        <v>3.370450258255</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.6940598487854</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.18092346191406</v>
+        <v>4.1809229850769</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>4.89487504959106</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.35978651046753</v>
+        <v>4.35978603363037</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.27706241607666</v>
+        <v>4.2770619392395</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.47157573699951</v>
+        <v>4.47157526016235</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>5.42201614379883</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.8293023109436</v>
+        <v>4.82930183410645</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>5.30654716491699</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.72645568847656</v>
+        <v>4.72645616531372</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>5.1333441734314</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.5721869468689</v>
+        <v>4.57218647003174</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.62584495544434</v>
+        <v>4.62584447860718</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>5.35675096511841</v>
       </c>
       <c r="G1254" t="n">
-        <v>4.77117109298706</v>
+        <v>4.77117156982422</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>5.37683200836182</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.78905773162842</v>
+        <v>4.78905725479126</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1259" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>5.46719884872437</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.86954593658447</v>
+        <v>4.86954545974731</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.86060285568237</v>
+        <v>4.86060237884521</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>5.82364702224731</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.18702840805054</v>
+        <v>5.18702793121338</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>6.17256307601929</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.49780178070068</v>
+        <v>5.49780225753784</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>6.10729789733887</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.43967151641846</v>
+        <v>5.4396710395813</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>6.08721685409546</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.42178583145142</v>
+        <v>5.42178535461426</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>6.00689077377319</v>
       </c>
       <c r="G1279" t="n">
-        <v>5.35024070739746</v>
+        <v>5.3502402305603</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.85878896713257</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.21832895278931</v>
+        <v>5.21832847595215</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>5.34169006347656</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.75775718688965</v>
+        <v>4.75775671005249</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>5.59019899368286</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.9790997505188</v>
+        <v>4.97910022735596</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>5.98178911209106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.32788276672363</v>
+        <v>5.32788324356079</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>6.55160188674927</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.83540630340576</v>
+        <v>5.8354058265686</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>6.3457670211792</v>
       </c>
       <c r="G1303" t="n">
-        <v>5.65207195281982</v>
+        <v>5.65207242965698</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>6.35078716278076</v>
       </c>
       <c r="G1304" t="n">
-        <v>5.65654373168945</v>
+        <v>5.65654325485229</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>6.40852212905884</v>
       </c>
       <c r="G1305" t="n">
-        <v>5.70796728134155</v>
+        <v>5.70796680450439</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>6.63192892074585</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.90695142745972</v>
+        <v>5.90695190429688</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>6.00940084457397</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.35247659683228</v>
+        <v>5.35247611999512</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.0841817855835</v>
+        <v>5.08418226242065</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1312" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>5.91652393341064</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.26975250244141</v>
+        <v>5.26975202560425</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>6.07215595245361</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.40837097167969</v>
+        <v>5.40837144851685</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>6.07717609405518</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.41284275054932</v>
+        <v>5.41284227371216</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>6.12486982345581</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.45532274246216</v>
+        <v>5.455322265625</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>5.97174787521362</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.31893920898438</v>
+        <v>5.31893968582153</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1324" t="n">
-        <v>5.31670379638672</v>
+        <v>5.31670331954956</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>5.69060611724854</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.06853055953979</v>
+        <v>5.06853103637695</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>5.87887096405029</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.23621559143066</v>
+        <v>5.23621511459351</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>5.83870792388916</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.20044231414795</v>
+        <v>5.20044279098511</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.97686338424683</v>
+        <v>4.97686290740967</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.94556283950806</v>
+        <v>4.94556331634521</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.87855911254883</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.34525346755981</v>
+        <v>4.34525394439697</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.82333517074585</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.29606676101685</v>
+        <v>4.29606628417969</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>5.06054782867432</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.50734806060791</v>
+        <v>4.50734853744507</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.69068288803101</v>
+        <v>4.69068336486816</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>5.1383638381958</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.57665729522705</v>
+        <v>4.57665777206421</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>5.12832307815552</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.56771421432495</v>
+        <v>4.56771469116211</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>5.11828184127808</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.55877065658569</v>
+        <v>4.55877113342285</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>5.3793420791626</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.79129266738892</v>
+        <v>4.79129314422607</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>5.56760692596436</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.95897769927979</v>
+        <v>4.95897722244263</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1390" t="n">
-        <v>4.72422027587891</v>
+        <v>4.72421979904175</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.72422027587891</v>
+        <v>4.72421979904175</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>5.29901599884033</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.71974754333496</v>
+        <v>4.71974802017212</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1396" t="n">
-        <v>4.56324338912964</v>
+        <v>4.56324291229248</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>5.22873115539551</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.65714597702026</v>
+        <v>4.65714645385742</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>5.21868991851807</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.64820241928101</v>
+        <v>4.64820289611816</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.90617084503174</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.3698468208313</v>
+        <v>4.36984729766846</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.97143602371216</v>
       </c>
       <c r="G1403" t="n">
-        <v>4.42797756195068</v>
+        <v>4.42797803878784</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>4.88483476638794</v>
       </c>
       <c r="G1405" t="n">
-        <v>4.35084295272827</v>
+        <v>4.35084342956543</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.90240621566772</v>
       </c>
       <c r="G1407" t="n">
-        <v>4.36649417877197</v>
+        <v>4.36649370193481</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.75681495666504</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.23681783676147</v>
+        <v>4.23681831359863</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1417" t="n">
-        <v>4.5297064781189</v>
+        <v>4.52970600128174</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>4.91119194030762</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.37431955337524</v>
+        <v>4.37431907653809</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.92499780654907</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.38661575317383</v>
+        <v>4.38661623001099</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.56324338912964</v>
+        <v>4.56324291229248</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>5.16597604751587</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.60125160217285</v>
+        <v>4.60125112533569</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>4.98147678375244</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.43692064285278</v>
+        <v>4.43692111968994</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1433" t="n">
-        <v>4.27706241607666</v>
+        <v>4.2770619392395</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1436" t="n">
-        <v>4.47157573699951</v>
+        <v>4.47157526016235</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>4.96139478683472</v>
       </c>
       <c r="G1443" t="n">
-        <v>4.41903400421143</v>
+        <v>4.41903448104858</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>5.01662015914917</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.46822214126587</v>
+        <v>4.46822261810303</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1449" t="n">
-        <v>4.62584495544434</v>
+        <v>4.62584447860718</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.5297064781189</v>
+        <v>4.52970600128174</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.99151802062988</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.4458646774292</v>
+        <v>4.44586420059204</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>4.91244697570801</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.37543725967407</v>
+        <v>4.37543678283691</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>5.07058906555176</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.51629161834717</v>
+        <v>4.51629209518433</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>5.55003595352173</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.9433274269104</v>
+        <v>4.94332695007324</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.69068288803101</v>
+        <v>4.69068336486816</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.79800081253052</v>
+        <v>4.79800033569336</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1470" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.91202640533447</v>
+        <v>4.91202592849731</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.94556283950806</v>
+        <v>4.94556331634521</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.87353897094727</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.3407826423645</v>
+        <v>4.34078216552734</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.81203889846802</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.28600549697876</v>
+        <v>4.2860050201416</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.34189987182617</v>
+        <v>4.34190034866333</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.39220523834229</v>
+        <v>4.39220476150513</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>4.46563196182251</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.97746610641479</v>
+        <v>3.97746634483337</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>4.50328493118286</v>
       </c>
       <c r="G1504" t="n">
-        <v>4.0110034942627</v>
+        <v>4.01100301742554</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>4.42170381546021</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.93834018707275</v>
+        <v>3.93833994865417</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>4.59365177154541</v>
       </c>
       <c r="G1509" t="n">
-        <v>4.09149169921875</v>
+        <v>4.09149122238159</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>4.56729507446289</v>
       </c>
       <c r="G1511" t="n">
-        <v>4.06801605224609</v>
+        <v>4.06801557540894</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>4.41040802001953</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.92827916145325</v>
+        <v>3.92827892303467</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>4.4455509185791</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.95958018302917</v>
+        <v>3.95958042144775</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>4.37275505065918</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.89474248886108</v>
+        <v>3.89474201202393</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.55097913742065</v>
       </c>
       <c r="G1522" t="n">
-        <v>4.05348348617554</v>
+        <v>4.0534839630127</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>4.78317213058472</v>
       </c>
       <c r="G1527" t="n">
-        <v>4.26029443740845</v>
+        <v>4.26029396057129</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>4.91495704650879</v>
       </c>
       <c r="G1531" t="n">
-        <v>4.37767267227173</v>
+        <v>4.37767314910889</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.03042602539062</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.48051929473877</v>
+        <v>4.48051881790161</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.39220523834229</v>
+        <v>4.39220476150513</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>5.01410913467407</v>
       </c>
       <c r="G1541" t="n">
-        <v>4.46598625183105</v>
+        <v>4.4659857749939</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>2.99591493606567</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.66841292381287</v>
+        <v>2.66841316223145</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>3.02854704856873</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.69747805595398</v>
+        <v>2.6974778175354</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>2.8616189956665</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.54879784584045</v>
+        <v>2.54879760742188</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.56221222877502</v>
+        <v>2.5622124671936</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.51521301269531</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.24025964736938</v>
+        <v>2.24025940895081</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>2.56165099143982</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.28162121772766</v>
+        <v>2.28162097930908</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.56792688369751</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.28721117973328</v>
+        <v>2.2872109413147</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>2.37715196609497</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.11729097366333</v>
+        <v>2.11729073524475</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.58047795295715</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.29838991165161</v>
+        <v>2.29839015007019</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>2.46450710296631</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.19509673118591</v>
+        <v>2.19509649276733</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>2.67335510253906</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.38111400604248</v>
+        <v>2.38111424446106</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>2.86287403106689</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.54991555213928</v>
+        <v>2.54991579055786</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.56221222877502</v>
+        <v>2.5622124671936</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>2.93943500518799</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.61810731887817</v>
+        <v>2.61810708045959</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>2.87919092178345</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.564448595047</v>
+        <v>2.56444883346558</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>2.84404802322388</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.53314781188965</v>
+        <v>2.53314757347107</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>2.77878308296204</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.47501730918884</v>
+        <v>2.47501707077026</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>2.80262994766235</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.49625730514526</v>
+        <v>2.49625706672668</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>2.79384398460388</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.48843169212341</v>
+        <v>2.48843145370483</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>2.75744605064392</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.45601272583008</v>
+        <v>2.4560124874115</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.43700885772705</v>
+        <v>2.43700909614563</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.84028291702271</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.52979397773743</v>
+        <v>2.52979421615601</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>2.92437410354614</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.6046929359436</v>
+        <v>2.60469269752502</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.43700885772705</v>
+        <v>2.43700909614563</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.48509001731873</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.21342945098877</v>
+        <v>2.21342968940735</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>2.53780388832092</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.26038098335266</v>
+        <v>2.26038074493408</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>2.68841600418091</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.39452886581421</v>
+        <v>2.39452862739563</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>2.90680289268494</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.58904242515564</v>
+        <v>2.58904218673706</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>2.97517991065979</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.6499445438385</v>
+        <v>2.64994478225708</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>2.72426104545593</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.42645525932312</v>
+        <v>2.4264554977417</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>2.37423992156982</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.11469721794128</v>
+        <v>2.11469697952271</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>1.96649694442749</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.75152707099915</v>
+        <v>1.75152695178986</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>2.01657509803772</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.79613077640533</v>
+        <v>1.79613089561462</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>2.21557092666626</v>
       </c>
       <c r="G1646" t="n">
-        <v>1.97337329387665</v>
+        <v>1.97337317466736</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>1.73798203468323</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.54799246788025</v>
+        <v>1.54799258708954</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.59776198863983</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.42310070991516</v>
+        <v>1.42310082912445</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>1.24932205677032</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.11275100708008</v>
+        <v>1.11275088787079</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98913478851318</v>
+        <v>2.98913502693176</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.73594284057617</v>
+        <v>1.73594272136688</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.985986948013306</v>
+        <v>0.98598700761795</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.04209995269775</v>
+        <v>1.04210007190704</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.730360686779022</v>
+        <v>0.730360746383667</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>0.71340000629425</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.635413825511932</v>
+        <v>0.635413885116577</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.659106075763702</v>
+        <v>0.659106016159058</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.692061364650726</v>
+        <v>0.692061305046082</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.751737177371979</v>
+        <v>0.751737117767334</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>0.833599984645844</v>
       </c>
       <c r="G1677" t="n">
-        <v>0.74247407913208</v>
+        <v>0.742474019527435</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>0.821799993515015</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.731963992118835</v>
+        <v>0.731963932514191</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>0.762199997901917</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.678879261016846</v>
+        <v>0.678879201412201</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>0.716400027275085</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.638085901737213</v>
+        <v>0.638085961341858</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>0.674600005149841</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.60085529088974</v>
+        <v>0.600855350494385</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>0.697399973869324</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.621162891387939</v>
+        <v>0.621162831783295</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>0.683200001716614</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.608515202999115</v>
+        <v>0.60851514339447</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>0.662199974060059</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.589810848236084</v>
+        <v>0.589810788631439</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>0.64300000667572</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.572709739208221</v>
+        <v>0.572709679603577</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.540645062923431</v>
+        <v>0.540645122528076</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>0.584800004959106</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.520871937274933</v>
+        <v>0.520871877670288</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>0.59280002117157</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.527997374534607</v>
+        <v>0.527997434139252</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>0.597199976444244</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.531916320323944</v>
+        <v>0.531916379928589</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>0.637600004673004</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.567900002002716</v>
+        <v>0.567900061607361</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>0.72759997844696</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.648061513900757</v>
+        <v>0.648061573505402</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.620806694030762</v>
+        <v>0.620806634426117</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.658215343952179</v>
+        <v>0.658215403556824</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>0.758199989795685</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.675316452980042</v>
+        <v>0.675316512584686</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>0.828599989414215</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.738020598888397</v>
+        <v>0.738020658493042</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>0.958599984645844</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.853809535503387</v>
+        <v>0.853809475898743</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.8764328956604</v>
+        <v>0.876432955265045</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.87376081943512</v>
+        <v>0.873760879039764</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.882667660713196</v>
+        <v>0.882667720317841</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.919185698032379</v>
+        <v>0.919185638427734</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.957485198974609</v>
+        <v>0.957485139369965</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>1.09650003910065</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.976634860038757</v>
+        <v>0.976634919643402</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>1.03250002861023</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.919631063938141</v>
+        <v>0.919631123542786</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.921857714653015</v>
+        <v>0.92185777425766</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>1.04649996757507</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.932100653648376</v>
+        <v>0.932100594043732</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.926311135292053</v>
+        <v>0.926311194896698</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>1.04750001430511</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.93299126625061</v>
+        <v>0.932991325855255</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.912950873374939</v>
+        <v>0.912950932979584</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>1.01950001716614</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.908052146434784</v>
+        <v>0.908052206039429</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>1.04449999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.93031919002533</v>
+        <v>0.930319249629974</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>1.00650000572205</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.896473228931427</v>
+        <v>0.896473288536072</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.04949998855591</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.934772729873657</v>
+        <v>0.934772670269012</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>1.10950005054474</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.988213777542114</v>
+        <v>0.988213717937469</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.977970957756042</v>
+        <v>0.977970898151398</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>1.12750005722046</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.00424599647522</v>
+        <v>1.00424611568451</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.05456960201263</v>
+        <v>1.05456972122192</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>1.31149995326996</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.16813182830811</v>
+        <v>1.16813170909882</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.25141072273254</v>
+        <v>1.25141084194183</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.2309250831604</v>
+        <v>1.23092496395111</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.21845555305481</v>
+        <v>1.21845543384552</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.25586414337158</v>
+        <v>1.25586426258087</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.24962949752808</v>
+        <v>1.24962937831879</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.3146493434906</v>
+        <v>1.31464922428131</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.35116744041443</v>
+        <v>1.35116732120514</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>1.53450000286102</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.36675429344177</v>
+        <v>1.36675441265106</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.31643068790436</v>
+        <v>1.31643080711365</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.35749995708466</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.20910334587097</v>
+        <v>1.20910322666168</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>1.26549994945526</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.12716031074524</v>
+        <v>1.12716042995453</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>1.14049994945526</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.01582491397858</v>
+        <v>1.01582479476929</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>1.23450005054474</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.09954929351807</v>
+        <v>1.09954917430878</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.32550001144409</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.18060147762299</v>
+        <v>1.1806013584137</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.14007532596588</v>
+        <v>1.14007520675659</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23181581497192</v>
+        <v>1.23181569576263</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>1.25049996376038</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.11380004882812</v>
+        <v>1.11380016803741</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.15076351165771</v>
+        <v>1.150763630867</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.13473129272461</v>
+        <v>1.13473117351532</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.12048017978668</v>
+        <v>1.12048029899597</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.15788900852203</v>
+        <v>1.15788888931274</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>1.25750005245209</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.1200350522995</v>
+        <v>1.12003493309021</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.12226164340973</v>
+        <v>1.12226152420044</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.07416474819183</v>
+        <v>1.07416462898254</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.13473129272461</v>
+        <v>1.13473117351532</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>1.25450003147125</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.11736297607422</v>
+        <v>1.11736285686493</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.08663427829742</v>
+        <v>1.08663439750671</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>1.16250002384186</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.03541994094849</v>
+        <v>1.03542006015778</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.04833495616913</v>
+        <v>1.04833483695984</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.07772743701935</v>
+        <v>1.07772755622864</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.30039846897125</v>
+        <v>1.30039834976196</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.3110865354538</v>
+        <v>1.31108665466309</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.32266557216644</v>
+        <v>1.32266545295715</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>1.43949997425079</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.28213942050934</v>
+        <v>1.28213930130005</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>1.43250000476837</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.27590453624725</v>
+        <v>1.27590465545654</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.30039846897125</v>
+        <v>1.30039834976196</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.328009724617</v>
+        <v>1.32800960540771</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1928" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1930" t="n">
-        <v>1.29683566093445</v>
+        <v>1.29683554172516</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.29327285289764</v>
+        <v>1.29327297210693</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.25586414337158</v>
+        <v>1.25586426258087</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1935" t="n">
-        <v>1.24339461326599</v>
+        <v>1.24339473247528</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.30485188961029</v>
+        <v>1.304851770401</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.33869779109955</v>
+        <v>1.33869791030884</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.32266557216644</v>
+        <v>1.32266545295715</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1951" t="n">
-        <v>1.4019364118576</v>
+        <v>1.40193629264832</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.328009724617</v>
+        <v>1.32800960540771</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.37566113471985</v>
+        <v>1.37566125392914</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.41975009441376</v>
+        <v>1.41974997520447</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>1.60950005054474</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.43355572223663</v>
+        <v>1.43355560302734</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.40104568004608</v>
+        <v>1.40104556083679</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>1.46249997615814</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.30262517929077</v>
+        <v>1.30262506008148</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.27679538726807</v>
+        <v>1.27679526805878</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.29683566093445</v>
+        <v>1.29683554172516</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>1.41849994659424</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.26343500614166</v>
+        <v>1.26343488693237</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>1.5275000333786</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.36051964759827</v>
+        <v>1.36051952838898</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52031,7 +52031,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.37566113471985</v>
+        <v>1.37566125392914</v>
       </c>
       <c r="H1987" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.29015564918518</v>
+        <v>1.29015552997589</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.41449999809265</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.25987231731415</v>
+        <v>1.25987219810486</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.23626923561096</v>
+        <v>1.23626911640167</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.23805046081543</v>
+        <v>1.23805058002472</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2007" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>1.44749999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>1.28926479816437</v>
+        <v>1.28926491737366</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>1.46150004863739</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.30173444747925</v>
+        <v>1.30173456668854</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.24784803390503</v>
+        <v>1.24784815311432</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2023" t="n">
-        <v>1.24784803390503</v>
+        <v>1.24784815311432</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.22647166252136</v>
+        <v>1.22647154331207</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>1.42050004005432</v>
       </c>
       <c r="G2029" t="n">
-        <v>1.26521635055542</v>
+        <v>1.26521646976471</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.29015564918518</v>
+        <v>1.29015552997589</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>1.44649994373322</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.28837406635284</v>
+        <v>1.28837418556213</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>1.48300004005432</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.3208841085434</v>
+        <v>1.32088422775269</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.30930531024933</v>
+        <v>1.30930519104004</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>1.4889999628067</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.32622814178467</v>
+        <v>1.32622826099396</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>1.50650000572205</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.34181523323059</v>
+        <v>1.3418151140213</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.27679538726807</v>
+        <v>1.27679526805878</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.31643068790436</v>
+        <v>1.31643080711365</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G2055" t="n">
-        <v>1.34315121173859</v>
+        <v>1.34315133094788</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -54189,7 +54189,7 @@
         <v>1.375</v>
       </c>
       <c r="G2070" t="n">
-        <v>1.22469019889832</v>
+        <v>1.2246903181076</v>
       </c>
       <c r="H2070" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>1.38100004196167</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.23003435134888</v>
+        <v>1.23003447055817</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.32979094982147</v>
+        <v>1.32979106903076</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>1.82149994373322</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.6223806142807</v>
+        <v>1.62238049507141</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.72347319126129</v>
+        <v>1.723473072052</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>1.97650003433228</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.76043665409088</v>
+        <v>1.76043653488159</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.87488961219788</v>
+        <v>1.87488949298859</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.88112413883209</v>
+        <v>1.88112425804138</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>2.08699989318848</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.85885715484619</v>
+        <v>1.8588570356369</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.91318881511688</v>
+        <v>1.91318893432617</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -55047,7 +55047,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.98889696598053</v>
+        <v>1.98889708518982</v>
       </c>
       <c r="H2103" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2104" t="n">
-        <v>2.00760126113892</v>
+        <v>2.0076014995575</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G2105" t="n">
-        <v>2.00849199295044</v>
+        <v>2.00849223136902</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.06994915008545</v>
+        <v>2.06994891166687</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>2.3970000743866</v>
       </c>
       <c r="G2109" t="n">
-        <v>2.13496923446655</v>
+        <v>2.13496899604797</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2110" t="n">
-        <v>2.08419990539551</v>
+        <v>2.08420014381409</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.99513185024261</v>
+        <v>1.99513173103333</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.94258141517639</v>
+        <v>1.94258153438568</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.97197389602661</v>
+        <v>1.9719740152359</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.9523788690567</v>
+        <v>1.95237898826599</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2123" t="n">
-        <v>1.94080007076263</v>
+        <v>1.94079983234406</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55645,7 +55645,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2126" t="n">
-        <v>1.91318881511688</v>
+        <v>1.91318893432617</v>
       </c>
       <c r="H2126" t="s">
         <v>8</v>
@@ -55697,7 +55697,7 @@
         <v>2.13100004196167</v>
       </c>
       <c r="G2128" t="n">
-        <v>1.8980473279953</v>
+        <v>1.89804720878601</v>
       </c>
       <c r="H2128" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G2131" t="n">
-        <v>1.97019255161285</v>
+        <v>1.97019267082214</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G2132" t="n">
-        <v>2.02541494369507</v>
+        <v>2.02541518211365</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -55853,7 +55853,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2134" t="n">
-        <v>2.11359286308289</v>
+        <v>2.11359262466431</v>
       </c>
       <c r="H2134" t="s">
         <v>8</v>
@@ -55957,7 +55957,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2138" t="n">
-        <v>2.12160897254944</v>
+        <v>2.12160873413086</v>
       </c>
       <c r="H2138" t="s">
         <v>8</v>
@@ -55983,7 +55983,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2139" t="n">
-        <v>2.11359286308289</v>
+        <v>2.11359262466431</v>
       </c>
       <c r="H2139" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2141" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56087,7 +56087,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2143" t="n">
-        <v>1.98889696598053</v>
+        <v>1.98889708518982</v>
       </c>
       <c r="H2143" t="s">
         <v>8</v>
@@ -56139,7 +56139,7 @@
         <v>2.15300011634827</v>
       </c>
       <c r="G2145" t="n">
-        <v>1.91764235496521</v>
+        <v>1.9176424741745</v>
       </c>
       <c r="H2145" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.9203143119812</v>
+        <v>1.92031419277191</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.93367457389832</v>
+        <v>1.9336746931076</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.83926212787628</v>
+        <v>1.83926224708557</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.86152911186218</v>
+        <v>1.86152923107147</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56399,7 +56399,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2155" t="n">
-        <v>1.86152911186218</v>
+        <v>1.86152923107147</v>
       </c>
       <c r="H2155" t="s">
         <v>8</v>
@@ -56425,7 +56425,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2156" t="n">
-        <v>1.89626574516296</v>
+        <v>1.89626586437225</v>
       </c>
       <c r="H2156" t="s">
         <v>8</v>
@@ -56451,7 +56451,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2157" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2157" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>2.15899991989136</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.92298626899719</v>
+        <v>1.92298638820648</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56503,7 +56503,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.99245965480804</v>
+        <v>1.99245977401733</v>
       </c>
       <c r="H2159" t="s">
         <v>8</v>
@@ -56607,7 +56607,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.1358597278595</v>
+        <v>2.13585996627808</v>
       </c>
       <c r="H2163" t="s">
         <v>8</v>
@@ -56711,7 +56711,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2167" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2167" t="s">
         <v>8</v>
@@ -56789,7 +56789,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G2170" t="n">
-        <v>2.07351183891296</v>
+        <v>2.07351207733154</v>
       </c>
       <c r="H2170" t="s">
         <v>8</v>
@@ -56815,7 +56815,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2171" t="n">
-        <v>2.06371426582336</v>
+        <v>2.06371450424194</v>
       </c>
       <c r="H2171" t="s">
         <v>8</v>
@@ -56841,7 +56841,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G2172" t="n">
-        <v>2.09666991233826</v>
+        <v>2.09666967391968</v>
       </c>
       <c r="H2172" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2174" t="n">
-        <v>2.10913920402527</v>
+        <v>2.10913944244385</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G2175" t="n">
-        <v>2.12339043617249</v>
+        <v>2.12339019775391</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -56945,7 +56945,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G2176" t="n">
-        <v>2.14476656913757</v>
+        <v>2.14476680755615</v>
       </c>
       <c r="H2176" t="s">
         <v>8</v>
@@ -57023,7 +57023,7 @@
         <v>2.41899991035461</v>
       </c>
       <c r="G2179" t="n">
-        <v>2.15456390380859</v>
+        <v>2.15456414222717</v>
       </c>
       <c r="H2179" t="s">
         <v>8</v>
@@ -57075,7 +57075,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2181" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2181" t="s">
         <v>8</v>
@@ -57101,7 +57101,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G2182" t="n">
-        <v>1.98444354534149</v>
+        <v>1.9844434261322</v>
       </c>
       <c r="H2182" t="s">
         <v>8</v>
@@ -57153,7 +57153,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2184" t="n">
-        <v>1.9461442232132</v>
+        <v>1.94614410400391</v>
       </c>
       <c r="H2184" t="s">
         <v>8</v>
@@ -57179,7 +57179,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2185" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2185" t="s">
         <v>8</v>
@@ -57205,7 +57205,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2186" t="n">
-        <v>1.94080007076263</v>
+        <v>1.94079983234406</v>
       </c>
       <c r="H2186" t="s">
         <v>8</v>
@@ -57309,7 +57309,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G2190" t="n">
-        <v>1.79294645786285</v>
+        <v>1.79294657707214</v>
       </c>
       <c r="H2190" t="s">
         <v>8</v>
@@ -57413,7 +57413,7 @@
         <v>1.98450005054474</v>
       </c>
       <c r="G2194" t="n">
-        <v>1.76756203174591</v>
+        <v>1.7675621509552</v>
       </c>
       <c r="H2194" t="s">
         <v>8</v>
@@ -57543,7 +57543,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G2199" t="n">
-        <v>1.84282493591309</v>
+        <v>1.8428248167038</v>
       </c>
       <c r="H2199" t="s">
         <v>8</v>
@@ -57621,7 +57621,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G2202" t="n">
-        <v>1.84549701213837</v>
+        <v>1.84549689292908</v>
       </c>
       <c r="H2202" t="s">
         <v>8</v>
@@ -57647,7 +57647,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G2203" t="n">
-        <v>1.81521379947662</v>
+        <v>1.81521368026733</v>
       </c>
       <c r="H2203" t="s">
         <v>8</v>
@@ -57725,7 +57725,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2206" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2206" t="s">
         <v>8</v>
@@ -57751,7 +57751,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2207" t="n">
-        <v>1.80185341835022</v>
+        <v>1.80185329914093</v>
       </c>
       <c r="H2207" t="s">
         <v>8</v>
@@ -57777,7 +57777,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2208" t="n">
-        <v>1.67448556423187</v>
+        <v>1.67448568344116</v>
       </c>
       <c r="H2208" t="s">
         <v>8</v>
@@ -57803,7 +57803,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G2209" t="n">
-        <v>1.71189427375793</v>
+        <v>1.71189439296722</v>
       </c>
       <c r="H2209" t="s">
         <v>8</v>
@@ -57907,7 +57907,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G2213" t="n">
-        <v>1.60055887699127</v>
+        <v>1.60055899620056</v>
       </c>
       <c r="H2213" t="s">
         <v>8</v>
@@ -57933,7 +57933,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G2214" t="n">
-        <v>1.6272794008255</v>
+        <v>1.62727928161621</v>
       </c>
       <c r="H2214" t="s">
         <v>8</v>
@@ -58193,7 +58193,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G2224" t="n">
-        <v>1.81343221664429</v>
+        <v>1.81343233585358</v>
       </c>
       <c r="H2224" t="s">
         <v>8</v>
@@ -58401,7 +58401,7 @@
         <v>2.05699992179871</v>
       </c>
       <c r="G2232" t="n">
-        <v>1.83213663101196</v>
+        <v>1.83213651180267</v>
       </c>
       <c r="H2232" t="s">
         <v>8</v>
@@ -58453,7 +58453,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2234" t="n">
-        <v>1.79027438163757</v>
+        <v>1.79027450084686</v>
       </c>
       <c r="H2234" t="s">
         <v>8</v>
@@ -58479,7 +58479,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2235" t="n">
-        <v>1.80185341835022</v>
+        <v>1.80185329914093</v>
       </c>
       <c r="H2235" t="s">
         <v>8</v>
@@ -58635,7 +58635,7 @@
         <v>1.99150002002716</v>
       </c>
       <c r="G2241" t="n">
-        <v>1.773796916008</v>
+        <v>1.77379679679871</v>
       </c>
       <c r="H2241" t="s">
         <v>8</v>
@@ -58687,7 +58687,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2243" t="n">
-        <v>1.83926212787628</v>
+        <v>1.83926224708557</v>
       </c>
       <c r="H2243" t="s">
         <v>8</v>
@@ -58713,7 +58713,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G2244" t="n">
-        <v>1.80630695819855</v>
+        <v>1.80630683898926</v>
       </c>
       <c r="H2244" t="s">
         <v>8</v>
@@ -58739,7 +58739,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G2245" t="n">
-        <v>1.89003121852875</v>
+        <v>1.89003109931946</v>
       </c>
       <c r="H2245" t="s">
         <v>8</v>
@@ -58765,7 +58765,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G2246" t="n">
-        <v>1.94970679283142</v>
+        <v>1.94970667362213</v>
       </c>
       <c r="H2246" t="s">
         <v>8</v>
@@ -58817,7 +58817,7 @@
         <v>2.16300010681152</v>
       </c>
       <c r="G2248" t="n">
-        <v>1.92654919624329</v>
+        <v>1.92654931545258</v>
       </c>
       <c r="H2248" t="s">
         <v>8</v>
@@ -58843,7 +58843,7 @@
         <v>2.16700005531311</v>
       </c>
       <c r="G2249" t="n">
-        <v>1.93011200428009</v>
+        <v>1.9301118850708</v>
       </c>
       <c r="H2249" t="s">
         <v>8</v>
@@ -58869,7 +58869,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2250" t="n">
-        <v>1.94525361061096</v>
+        <v>1.94525349140167</v>
       </c>
       <c r="H2250" t="s">
         <v>8</v>
@@ -58895,7 +58895,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2251" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2251" t="s">
         <v>8</v>
@@ -58921,7 +58921,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2252" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2252" t="s">
         <v>8</v>
@@ -58973,7 +58973,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2254" t="n">
-        <v>2.00314784049988</v>
+        <v>2.00314807891846</v>
       </c>
       <c r="H2254" t="s">
         <v>8</v>
@@ -59025,7 +59025,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2256" t="n">
-        <v>2.06994915008545</v>
+        <v>2.06994891166687</v>
       </c>
       <c r="H2256" t="s">
         <v>8</v>
@@ -59103,7 +59103,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2259" t="n">
-        <v>2.05302619934082</v>
+        <v>2.0530264377594</v>
       </c>
       <c r="H2259" t="s">
         <v>8</v>
@@ -59129,7 +59129,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2260" t="n">
-        <v>2.06371426582336</v>
+        <v>2.06371450424194</v>
       </c>
       <c r="H2260" t="s">
         <v>8</v>
@@ -59155,7 +59155,7 @@
         <v>2.33299994468689</v>
       </c>
       <c r="G2261" t="n">
-        <v>2.07796549797058</v>
+        <v>2.077965259552</v>
       </c>
       <c r="H2261" t="s">
         <v>8</v>
@@ -59181,7 +59181,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2262" t="n">
-        <v>2.10913920402527</v>
+        <v>2.10913944244385</v>
       </c>
       <c r="H2262" t="s">
         <v>8</v>
@@ -59363,7 +59363,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G2269" t="n">
-        <v>2.16525220870972</v>
+        <v>2.1652524471283</v>
       </c>
       <c r="H2269" t="s">
         <v>8</v>
@@ -59493,7 +59493,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G2274" t="n">
-        <v>2.26768088340759</v>
+        <v>2.26768112182617</v>
       </c>
       <c r="H2274" t="s">
         <v>8</v>
@@ -59597,7 +59597,7 @@
         <v>2.48699998855591</v>
       </c>
       <c r="G2278" t="n">
-        <v>2.21513080596924</v>
+        <v>2.21513056755066</v>
       </c>
       <c r="H2278" t="s">
         <v>8</v>
@@ -59675,7 +59675,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G2281" t="n">
-        <v>2.29261994361877</v>
+        <v>2.29262018203735</v>
       </c>
       <c r="H2281" t="s">
         <v>8</v>
@@ -59701,7 +59701,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2282" t="n">
-        <v>2.31577801704407</v>
+        <v>2.31577777862549</v>
       </c>
       <c r="H2282" t="s">
         <v>8</v>
@@ -59779,7 +59779,7 @@
         <v>2.64299988746643</v>
       </c>
       <c r="G2285" t="n">
-        <v>2.35407733917236</v>
+        <v>2.35407710075378</v>
       </c>
       <c r="H2285" t="s">
         <v>8</v>
@@ -59857,7 +59857,7 @@
         <v>2.51099991798401</v>
       </c>
       <c r="G2288" t="n">
-        <v>2.23650693893433</v>
+        <v>2.23650717735291</v>
       </c>
       <c r="H2288" t="s">
         <v>8</v>
@@ -59883,7 +59883,7 @@
         <v>2.5090000629425</v>
       </c>
       <c r="G2289" t="n">
-        <v>2.23472595214844</v>
+        <v>2.23472571372986</v>
       </c>
       <c r="H2289" t="s">
         <v>8</v>
@@ -60039,7 +60039,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G2295" t="n">
-        <v>2.45294332504272</v>
+        <v>2.45294308662415</v>
       </c>
       <c r="H2295" t="s">
         <v>8</v>
@@ -60143,7 +60143,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G2299" t="n">
-        <v>2.31221508979797</v>
+        <v>2.31221532821655</v>
       </c>
       <c r="H2299" t="s">
         <v>8</v>
@@ -60195,7 +60195,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G2301" t="n">
-        <v>2.27658772468567</v>
+        <v>2.27658796310425</v>
       </c>
       <c r="H2301" t="s">
         <v>8</v>
@@ -60221,7 +60221,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G2302" t="n">
-        <v>2.25164866447449</v>
+        <v>2.25164890289307</v>
       </c>
       <c r="H2302" t="s">
         <v>8</v>
@@ -60247,7 +60247,7 @@
         <v>2.51300001144409</v>
       </c>
       <c r="G2303" t="n">
-        <v>2.23828840255737</v>
+        <v>2.23828864097595</v>
       </c>
       <c r="H2303" t="s">
         <v>8</v>
@@ -60299,7 +60299,7 @@
         <v>2.48300004005432</v>
       </c>
       <c r="G2305" t="n">
-        <v>2.21156787872314</v>
+        <v>2.21156811714172</v>
       </c>
       <c r="H2305" t="s">
         <v>8</v>
@@ -60325,7 +60325,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G2306" t="n">
-        <v>2.14832949638367</v>
+        <v>2.14832925796509</v>
       </c>
       <c r="H2306" t="s">
         <v>8</v>
@@ -60351,7 +60351,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2307" t="n">
-        <v>2.12160897254944</v>
+        <v>2.12160873413086</v>
       </c>
       <c r="H2307" t="s">
         <v>8</v>
@@ -60559,7 +60559,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G2315" t="n">
-        <v>2.04411935806274</v>
+        <v>2.04411959648132</v>
       </c>
       <c r="H2315" t="s">
         <v>8</v>
@@ -60611,7 +60611,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G2317" t="n">
-        <v>2.04768228530884</v>
+        <v>2.04768204689026</v>
       </c>
       <c r="H2317" t="s">
         <v>8</v>
@@ -60741,7 +60741,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G2322" t="n">
-        <v>2.05658912658691</v>
+        <v>2.05658888816833</v>
       </c>
       <c r="H2322" t="s">
         <v>8</v>
@@ -60819,7 +60819,7 @@
         <v>2.28099989891052</v>
       </c>
       <c r="G2325" t="n">
-        <v>2.03164982795715</v>
+        <v>2.03164958953857</v>
       </c>
       <c r="H2325" t="s">
         <v>8</v>
@@ -60845,7 +60845,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G2326" t="n">
-        <v>2.0681676864624</v>
+        <v>2.06816792488098</v>
       </c>
       <c r="H2326" t="s">
         <v>8</v>
@@ -60923,7 +60923,7 @@
         <v>2.20300006866455</v>
       </c>
       <c r="G2329" t="n">
-        <v>1.9621764421463</v>
+        <v>1.96217656135559</v>
       </c>
       <c r="H2329" t="s">
         <v>8</v>
@@ -60949,7 +60949,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2330" t="n">
-        <v>2.00314784049988</v>
+        <v>2.00314807891846</v>
       </c>
       <c r="H2330" t="s">
         <v>8</v>
@@ -61001,7 +61001,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2332" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2332" t="s">
         <v>8</v>
@@ -61053,7 +61053,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2334" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2334" t="s">
         <v>8</v>
@@ -61183,7 +61183,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G2339" t="n">
-        <v>1.85440385341644</v>
+        <v>1.85440373420715</v>
       </c>
       <c r="H2339" t="s">
         <v>8</v>
@@ -61261,7 +61261,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2342" t="n">
-        <v>1.89626574516296</v>
+        <v>1.89626586437225</v>
       </c>
       <c r="H2342" t="s">
         <v>8</v>
@@ -61287,7 +61287,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2343" t="n">
-        <v>1.93278396129608</v>
+        <v>1.93278384208679</v>
       </c>
       <c r="H2343" t="s">
         <v>8</v>
@@ -61313,7 +61313,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2344" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2344" t="s">
         <v>8</v>
@@ -61391,7 +61391,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2347" t="n">
-        <v>1.96841132640839</v>
+        <v>1.9684112071991</v>
       </c>
       <c r="H2347" t="s">
         <v>8</v>
@@ -61417,7 +61417,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2348" t="n">
-        <v>1.94525361061096</v>
+        <v>1.94525349140167</v>
       </c>
       <c r="H2348" t="s">
         <v>8</v>
@@ -61469,7 +61469,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G2350" t="n">
-        <v>1.9586136341095</v>
+        <v>1.95861351490021</v>
       </c>
       <c r="H2350" t="s">
         <v>8</v>
@@ -61495,7 +61495,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2351" t="n">
-        <v>1.93367457389832</v>
+        <v>1.9336746931076</v>
       </c>
       <c r="H2351" t="s">
         <v>8</v>
@@ -61573,7 +61573,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G2354" t="n">
-        <v>1.89537537097931</v>
+        <v>1.89537525177002</v>
       </c>
       <c r="H2354" t="s">
         <v>8</v>
@@ -61599,7 +61599,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G2355" t="n">
-        <v>1.72436380386353</v>
+        <v>1.72436392307281</v>
       </c>
       <c r="H2355" t="s">
         <v>8</v>
@@ -61755,7 +61755,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G2361" t="n">
-        <v>1.52128803730011</v>
+        <v>1.52128791809082</v>
       </c>
       <c r="H2361" t="s">
         <v>8</v>
@@ -61781,7 +61781,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G2362" t="n">
-        <v>1.56493139266968</v>
+        <v>1.56493151187897</v>
       </c>
       <c r="H2362" t="s">
         <v>8</v>
@@ -61937,7 +61937,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G2368" t="n">
-        <v>1.74930310249329</v>
+        <v>1.749302983284</v>
       </c>
       <c r="H2368" t="s">
         <v>8</v>
@@ -62015,7 +62015,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2371" t="n">
-        <v>1.82590174674988</v>
+        <v>1.82590186595917</v>
       </c>
       <c r="H2371" t="s">
         <v>8</v>
@@ -62067,7 +62067,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2373" t="n">
-        <v>1.85262227058411</v>
+        <v>1.8526223897934</v>
       </c>
       <c r="H2373" t="s">
         <v>8</v>
@@ -62093,7 +62093,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G2374" t="n">
-        <v>1.83302748203278</v>
+        <v>1.83302736282349</v>
       </c>
       <c r="H2374" t="s">
         <v>8</v>
@@ -62119,7 +62119,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G2375" t="n">
-        <v>1.82768332958221</v>
+        <v>1.82768321037292</v>
       </c>
       <c r="H2375" t="s">
         <v>8</v>
@@ -62145,7 +62145,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G2376" t="n">
-        <v>1.83837139606476</v>
+        <v>1.83837127685547</v>
       </c>
       <c r="H2376" t="s">
         <v>8</v>
@@ -62197,7 +62197,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G2378" t="n">
-        <v>1.9399094581604</v>
+        <v>1.93990933895111</v>
       </c>
       <c r="H2378" t="s">
         <v>8</v>
@@ -68986,6 +68986,32 @@
         <v>4.23000001907349</v>
       </c>
       <c r="H2639" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2640">
+      <c r="A2640" s="1" t="n">
+        <v>46167.2916666667</v>
+      </c>
+      <c r="B2640" t="n">
+        <v>12346784</v>
+      </c>
+      <c r="C2640" t="n">
+        <v>4.24100017547607</v>
+      </c>
+      <c r="D2640" t="n">
+        <v>4.17700004577637</v>
+      </c>
+      <c r="E2640" t="n">
+        <v>4.19000005722046</v>
+      </c>
+      <c r="F2640" t="n">
+        <v>4.21799993515015</v>
+      </c>
+      <c r="G2640" t="n">
+        <v>4.21799993515015</v>
+      </c>
+      <c r="H2640" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -447,7 +447,7 @@
         <v>23.2093391418457</v>
       </c>
       <c r="G3" t="n">
-        <v>20.5791072845459</v>
+        <v>20.5791053771973</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>21.9295864105225</v>
       </c>
       <c r="G5" t="n">
-        <v>19.4443836212158</v>
+        <v>19.4443855285645</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>21.3766078948975</v>
       </c>
       <c r="G6" t="n">
-        <v>18.9540748596191</v>
+        <v>18.9540729522705</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>22.4193687438965</v>
       </c>
       <c r="G8" t="n">
-        <v>19.878662109375</v>
+        <v>19.8786602020264</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811977386475</v>
+        <v>17.5811958312988</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460269927979</v>
+        <v>15.7460279464722</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>16.7157802581787</v>
       </c>
       <c r="G15" t="n">
-        <v>14.821439743042</v>
+        <v>14.8214406967163</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>13.2778282165527</v>
       </c>
       <c r="G16" t="n">
-        <v>11.7730989456177</v>
+        <v>11.773099899292</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>15.7389078140259</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9552726745605</v>
+        <v>13.9552736282349</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>13.806058883667</v>
       </c>
       <c r="G19" t="n">
-        <v>12.2414665222168</v>
+        <v>12.2414674758911</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G21" t="n">
-        <v>12.6977415084839</v>
+        <v>12.6977405548096</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.358302116394</v>
       </c>
       <c r="G22" t="n">
-        <v>12.7311277389526</v>
+        <v>12.7311267852783</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.8813648223877</v>
       </c>
       <c r="G23" t="n">
-        <v>12.30823802948</v>
+        <v>12.3082399368286</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>13.5048360824585</v>
       </c>
       <c r="G24" t="n">
-        <v>11.9743814468384</v>
+        <v>11.9743804931641</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.0530023574829</v>
       </c>
       <c r="G26" t="n">
-        <v>11.573751449585</v>
+        <v>11.5737524032593</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617107391357</v>
+        <v>8.16617202758789</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G29" t="n">
-        <v>8.05711078643799</v>
+        <v>8.0571117401123</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.87747859954834</v>
+        <v>6.87747955322266</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51181030273438</v>
+        <v>7.51180982589722</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.30120658874512</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36046028137207</v>
+        <v>7.36045980453491</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243934631348</v>
+        <v>7.91243982315063</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G40" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.67679214477539</v>
       </c>
       <c r="G45" t="n">
-        <v>8.58015632629395</v>
+        <v>8.58015537261963</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.96546459197998</v>
       </c>
       <c r="G46" t="n">
-        <v>8.83611297607422</v>
+        <v>8.83611392974854</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.0771427154541</v>
+        <v>8.07714366912842</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811292648315</v>
+        <v>7.98811340332031</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683300018311</v>
+        <v>8.58683395385742</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G53" t="n">
-        <v>8.29526424407959</v>
+        <v>8.29526329040527</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.31752109527588</v>
+        <v>8.3175220489502</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G57" t="n">
-        <v>8.15726852416992</v>
+        <v>8.15726947784424</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.34487962722778</v>
+        <v>7.34488010406494</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.93628597259521</v>
       </c>
       <c r="G62" t="n">
-        <v>7.92356872558594</v>
+        <v>7.92356824874878</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8.83838844299316</v>
       </c>
       <c r="G63" t="n">
-        <v>7.83676528930664</v>
+        <v>7.8367657661438</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870761871338</v>
+        <v>7.65870809555054</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G65" t="n">
-        <v>7.32262420654297</v>
+        <v>7.32262372970581</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.78159713745117</v>
       </c>
       <c r="G66" t="n">
-        <v>6.89973640441895</v>
+        <v>6.89973592758179</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365779876709</v>
+        <v>7.27365732192993</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G70" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.86347341537476</v>
+        <v>7.8634729385376</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09940052032471</v>
+        <v>8.09939956665039</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G75" t="n">
-        <v>8.27523231506348</v>
+        <v>8.27523136138916</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.25006008148193</v>
       </c>
       <c r="G79" t="n">
-        <v>8.20178413391113</v>
+        <v>8.20178318023682</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.39816093444824</v>
       </c>
       <c r="G80" t="n">
-        <v>8.33310127258301</v>
+        <v>8.33310031890869</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.55128288269043</v>
       </c>
       <c r="G81" t="n">
-        <v>8.46887016296387</v>
+        <v>8.46886920928955</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912082672119</v>
+        <v>8.62912178039551</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G83" t="n">
-        <v>9.68188858032227</v>
+        <v>9.68188762664795</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G84" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G87" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G88" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G89" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.20487594604492</v>
       </c>
       <c r="G91" t="n">
-        <v>8.16171932220459</v>
+        <v>8.16172027587891</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.26855373382568</v>
+        <v>8.2685546875</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542102813721</v>
+        <v>8.39542007446289</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G96" t="n">
-        <v>8.31974697113037</v>
+        <v>8.31974601745605</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G97" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588752746582</v>
+        <v>7.98588800430298</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701738357544</v>
+        <v>7.99701690673828</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>8.92875480651855</v>
       </c>
       <c r="G100" t="n">
-        <v>7.91689109802246</v>
+        <v>7.9168906211853</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.14212131500244</v>
       </c>
       <c r="G101" t="n">
-        <v>8.10607719421387</v>
+        <v>8.10607814788818</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.3303861618042</v>
       </c>
       <c r="G105" t="n">
-        <v>8.27300548553467</v>
+        <v>8.27300643920898</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G106" t="n">
-        <v>8.1884298324585</v>
+        <v>8.18842887878418</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.04924392700195</v>
       </c>
       <c r="G108" t="n">
-        <v>8.02372550964355</v>
+        <v>8.02372455596924</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889537811279</v>
+        <v>7.77889585494995</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701738357544</v>
+        <v>7.99701690673828</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.5261812210083</v>
       </c>
       <c r="G111" t="n">
-        <v>8.44661235809326</v>
+        <v>8.44661331176758</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G112" t="n">
-        <v>8.85837268829346</v>
+        <v>8.85837173461914</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.28018188476562</v>
       </c>
       <c r="G114" t="n">
-        <v>8.22849273681641</v>
+        <v>8.22849178314209</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325372695923</v>
+        <v>7.72325277328491</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660707473755</v>
+        <v>7.73660755157471</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808195114136</v>
+        <v>7.96808242797852</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G118" t="n">
-        <v>7.78112173080444</v>
+        <v>7.78112125396729</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.05933666229248</v>
+        <v>8.05933570861816</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.59193563461304</v>
+        <v>7.59193658828735</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78557348251343</v>
+        <v>7.78557395935059</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.86349010467529</v>
       </c>
       <c r="G127" t="n">
-        <v>7.85902214050293</v>
+        <v>7.85902261734009</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.60650730133057</v>
       </c>
       <c r="G130" t="n">
-        <v>8.51783561706543</v>
+        <v>8.51783657073975</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G131" t="n">
-        <v>8.15726852416992</v>
+        <v>8.15726947784424</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G132" t="n">
-        <v>7.82341051101685</v>
+        <v>7.823410987854</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.04171371459961</v>
       </c>
       <c r="G133" t="n">
-        <v>8.01704788208008</v>
+        <v>8.01704883575439</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.44083404541016</v>
       </c>
       <c r="G134" t="n">
-        <v>8.37093830108643</v>
+        <v>8.37093734741211</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420257568359</v>
+        <v>9.03420448303223</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G138" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>10.3771362304688</v>
       </c>
       <c r="G139" t="n">
-        <v>9.20113277435303</v>
+        <v>9.20113182067871</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>10.5679111480713</v>
       </c>
       <c r="G140" t="n">
-        <v>9.37028694152832</v>
+        <v>9.37028789520264</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>10.977071762085</v>
       </c>
       <c r="G142" t="n">
-        <v>9.733078956604</v>
+        <v>9.73307800292969</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G144" t="n">
-        <v>9.68856430053711</v>
+        <v>9.68856620788574</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>10.359564781189</v>
       </c>
       <c r="G145" t="n">
-        <v>9.1855525970459</v>
+        <v>9.18555164337158</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G149" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G151" t="n">
-        <v>8.27523231506348</v>
+        <v>8.27523136138916</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.37807941436768</v>
       </c>
       <c r="G153" t="n">
-        <v>8.31529521942139</v>
+        <v>8.31529426574707</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.90019989013672</v>
       </c>
       <c r="G155" t="n">
-        <v>8.778244972229</v>
+        <v>8.77824592590332</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.0056276321411</v>
       </c>
       <c r="G156" t="n">
-        <v>8.87172603607178</v>
+        <v>8.87172508239746</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G157" t="n">
-        <v>8.77601909637451</v>
+        <v>8.7760181427002</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>10.3269319534302</v>
       </c>
       <c r="G159" t="n">
-        <v>9.15661811828613</v>
+        <v>9.15661716461182</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G160" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03642845153809</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G169" t="n">
-        <v>9.0809440612793</v>
+        <v>9.08094310760498</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G170" t="n">
-        <v>9.16997337341309</v>
+        <v>9.16997241973877</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548873901367</v>
+        <v>9.14548778533936</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>10.457462310791</v>
       </c>
       <c r="G174" t="n">
-        <v>9.27235507965088</v>
+        <v>9.27235412597656</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G175" t="n">
-        <v>9.16997337341309</v>
+        <v>9.16997241973877</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G176" t="n">
-        <v>9.20780944824219</v>
+        <v>9.2078104019165</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G177" t="n">
-        <v>9.23451900482178</v>
+        <v>9.23451805114746</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G179" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.44836521148682</v>
       </c>
       <c r="G180" t="n">
-        <v>8.3776159286499</v>
+        <v>8.37761497497559</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G182" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.95887660980225</v>
       </c>
       <c r="G183" t="n">
-        <v>7.94359827041626</v>
+        <v>7.94359874725342</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.79224967956543</v>
+        <v>7.79225015640259</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.90365314483643</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89463329315186</v>
+        <v>7.89463424682617</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.28771305084229</v>
       </c>
       <c r="G188" t="n">
-        <v>8.23516941070557</v>
+        <v>8.23516845703125</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.7388334274292</v>
+        <v>7.73883295059204</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G192" t="n">
-        <v>8.15726852416992</v>
+        <v>8.15726947784424</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G193" t="n">
-        <v>8.38429260253906</v>
+        <v>8.38429164886475</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G197" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.77217960357666</v>
       </c>
       <c r="G198" t="n">
-        <v>8.66473388671875</v>
+        <v>8.66473293304443</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G199" t="n">
-        <v>8.94294834136963</v>
+        <v>8.94294929504395</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.063362121582</v>
       </c>
       <c r="G200" t="n">
-        <v>8.92291641235352</v>
+        <v>8.92291736602783</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>10.1662797927856</v>
       </c>
       <c r="G202" t="n">
-        <v>9.01417064666748</v>
+        <v>9.0141716003418</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G203" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10.3696060180664</v>
       </c>
       <c r="G204" t="n">
-        <v>9.19445514678955</v>
+        <v>9.19445610046387</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.8139095306396</v>
       </c>
       <c r="G206" t="n">
-        <v>9.58840751647949</v>
+        <v>9.58840847015381</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G207" t="n">
-        <v>9.68856430053711</v>
+        <v>9.68856620788574</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>10.9519701004028</v>
       </c>
       <c r="G208" t="n">
-        <v>9.71082305908203</v>
+        <v>9.71082210540771</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G209" t="n">
-        <v>9.68188858032227</v>
+        <v>9.68188762664795</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03642845153809</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G212" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.34645462036133</v>
+        <v>8.34645557403564</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.22244834899902</v>
       </c>
       <c r="G216" t="n">
-        <v>8.17730045318604</v>
+        <v>8.17730140686035</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G219" t="n">
-        <v>8.38429260253906</v>
+        <v>8.38429164886475</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G224" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.2240142822266</v>
       </c>
       <c r="G225" t="n">
-        <v>9.06536388397217</v>
+        <v>9.06536293029785</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.0834436416626</v>
       </c>
       <c r="G226" t="n">
-        <v>8.94072341918945</v>
+        <v>8.94072246551514</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.2215042114258</v>
       </c>
       <c r="G231" t="n">
-        <v>9.06313705444336</v>
+        <v>9.06313800811768</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G234" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.71193504333496</v>
       </c>
       <c r="G235" t="n">
-        <v>8.61131572723389</v>
+        <v>8.61131477355957</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.9695415496826</v>
       </c>
       <c r="G237" t="n">
-        <v>9.72640323638916</v>
+        <v>9.72640228271484</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>11.484130859375</v>
       </c>
       <c r="G240" t="n">
-        <v>10.1826753616333</v>
+        <v>10.182674407959</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>11.6347427368164</v>
       </c>
       <c r="G241" t="n">
-        <v>10.3162183761597</v>
+        <v>10.316219329834</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.9218482971191</v>
       </c>
       <c r="G243" t="n">
-        <v>9.68411350250244</v>
+        <v>9.68411445617676</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>11.2406415939331</v>
       </c>
       <c r="G244" t="n">
-        <v>9.9667797088623</v>
+        <v>9.96677875518799</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.9309453964233</v>
       </c>
       <c r="G247" t="n">
-        <v>10.5788545608521</v>
+        <v>10.5788536071777</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>12.8019819259644</v>
       </c>
       <c r="G250" t="n">
-        <v>11.3511781692505</v>
+        <v>11.3511800765991</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G251" t="n">
-        <v>10.9883861541748</v>
+        <v>10.9883871078491</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>13.0906553268433</v>
       </c>
       <c r="G254" t="n">
-        <v>11.607138633728</v>
+        <v>11.6071376800537</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>13.2287149429321</v>
       </c>
       <c r="G255" t="n">
-        <v>11.7295522689819</v>
+        <v>11.7295513153076</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076108932495</v>
+        <v>11.9076099395752</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.0319766998291</v>
       </c>
       <c r="G258" t="n">
-        <v>12.441782951355</v>
+        <v>12.4417819976807</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G259" t="n">
-        <v>12.6977415084839</v>
+        <v>12.6977405548096</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.3165721893311</v>
       </c>
       <c r="G263" t="n">
-        <v>11.8074522018433</v>
+        <v>11.8074531555176</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>12.7517786026001</v>
       </c>
       <c r="G264" t="n">
-        <v>11.3066644668579</v>
+        <v>11.3066654205322</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>12.8647365570068</v>
       </c>
       <c r="G267" t="n">
-        <v>11.4068222045898</v>
+        <v>11.4068212509155</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>12.2999439239502</v>
       </c>
       <c r="G268" t="n">
-        <v>10.9060354232788</v>
+        <v>10.9060344696045</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.5635137557983</v>
       </c>
       <c r="G269" t="n">
-        <v>11.1397352218628</v>
+        <v>11.1397342681885</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>12.6011667251587</v>
       </c>
       <c r="G272" t="n">
-        <v>11.1731214523315</v>
+        <v>11.1731204986572</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>12.4455347061157</v>
       </c>
       <c r="G273" t="n">
-        <v>11.0351266860962</v>
+        <v>11.0351257324219</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.5007591247559</v>
       </c>
       <c r="G274" t="n">
-        <v>11.0840930938721</v>
+        <v>11.0840921401978</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>13.3040208816528</v>
       </c>
       <c r="G275" t="n">
-        <v>11.7963237762451</v>
+        <v>11.7963228225708</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>13.1283073425293</v>
       </c>
       <c r="G276" t="n">
-        <v>11.6405229568481</v>
+        <v>11.6405220031738</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960092544556</v>
+        <v>11.5960083007812</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G280" t="n">
-        <v>10.5276613235474</v>
+        <v>10.5276622772217</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141502380371</v>
+        <v>10.4141492843628</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.3985710144043</v>
+        <v>10.39857006073</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.707537651062</v>
       </c>
       <c r="G287" t="n">
-        <v>10.3807649612427</v>
+        <v>10.3807640075684</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.0213117599487</v>
       </c>
       <c r="G288" t="n">
-        <v>10.6589794158936</v>
+        <v>10.6589784622192</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>11.6372528076172</v>
       </c>
       <c r="G293" t="n">
-        <v>10.3184442520142</v>
+        <v>10.3184432983398</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.5428085327148</v>
       </c>
       <c r="G303" t="n">
-        <v>9.34802913665771</v>
+        <v>9.34803009033203</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10.1386680603027</v>
       </c>
       <c r="G307" t="n">
-        <v>8.9896879196167</v>
+        <v>8.98968887329102</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.2491159439087</v>
       </c>
       <c r="G308" t="n">
-        <v>9.08761978149414</v>
+        <v>9.08762073516846</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520709991455</v>
+        <v>8.96520519256592</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10.218994140625</v>
       </c>
       <c r="G310" t="n">
-        <v>9.06091213226318</v>
+        <v>9.06091117858887</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.3244218826294</v>
       </c>
       <c r="G311" t="n">
-        <v>9.15439128875732</v>
+        <v>9.15439224243164</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10.1562385559082</v>
       </c>
       <c r="G317" t="n">
-        <v>9.00526714324951</v>
+        <v>9.00526809692383</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>10.8164196014404</v>
       </c>
       <c r="G321" t="n">
-        <v>9.59063339233398</v>
+        <v>9.59063243865967</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>10.6808700561523</v>
       </c>
       <c r="G322" t="n">
-        <v>9.47044563293457</v>
+        <v>9.47044467926025</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77981853485107</v>
+        <v>9.77982044219971</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>10.2691984176636</v>
       </c>
       <c r="G331" t="n">
-        <v>9.10542583465576</v>
+        <v>9.10542678833008</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10.0784225463867</v>
       </c>
       <c r="G333" t="n">
-        <v>8.93627071380615</v>
+        <v>8.93626976013184</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G339" t="n">
-        <v>8.94294834136963</v>
+        <v>8.94294929504395</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G342" t="n">
-        <v>8.85837268829346</v>
+        <v>8.85837173461914</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G344" t="n">
-        <v>8.87840270996094</v>
+        <v>8.87840175628662</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>10.0332403182983</v>
       </c>
       <c r="G345" t="n">
-        <v>8.89620876312256</v>
+        <v>8.89620780944824</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G347" t="n">
-        <v>8.87840270996094</v>
+        <v>8.87840175628662</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10.003116607666</v>
       </c>
       <c r="G349" t="n">
-        <v>8.86949825286865</v>
+        <v>8.86949920654297</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G353" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G355" t="n">
-        <v>8.86282348632812</v>
+        <v>8.86282253265381</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G357" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.36301803588867</v>
       </c>
       <c r="G359" t="n">
-        <v>8.30193996429443</v>
+        <v>8.30194091796875</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G361" t="n">
-        <v>8.12833404541016</v>
+        <v>8.12833499908447</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G362" t="n">
-        <v>8.03485488891602</v>
+        <v>8.0348539352417</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.9903392791748</v>
+        <v>7.99033880233765</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G365" t="n">
-        <v>7.78112173080444</v>
+        <v>7.78112125396729</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G366" t="n">
-        <v>7.66093397140503</v>
+        <v>7.66093349456787</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215627670288</v>
+        <v>7.73215675354004</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G370" t="n">
-        <v>8.05711078643799</v>
+        <v>8.0571117401123</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>8.88106060028076</v>
       </c>
       <c r="G372" t="n">
-        <v>7.87460136413574</v>
+        <v>7.8746018409729</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G373" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G374" t="n">
-        <v>7.32262420654297</v>
+        <v>7.32262372970581</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G376" t="n">
-        <v>7.1979832649231</v>
+        <v>7.19798278808594</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.13302421569824</v>
       </c>
       <c r="G377" t="n">
-        <v>7.21133661270142</v>
+        <v>7.21133756637573</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914266586304</v>
+        <v>7.22914218902588</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817245483398</v>
+        <v>7.31817197799683</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G383" t="n">
-        <v>7.23804521560669</v>
+        <v>7.23804569244385</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G384" t="n">
-        <v>7.1979832649231</v>
+        <v>7.19798278808594</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055511474609</v>
+        <v>7.42055463790894</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.44428825378418</v>
       </c>
       <c r="G387" t="n">
-        <v>7.48732709884644</v>
+        <v>7.48732662200928</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G389" t="n">
-        <v>7.32262420654297</v>
+        <v>7.32262372970581</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8.4242057800293</v>
       </c>
       <c r="G390" t="n">
-        <v>7.46952056884766</v>
+        <v>7.46952104568481</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390846252441</v>
+        <v>7.43390941619873</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G392" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.8567967414856</v>
+        <v>7.85679721832275</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>8.52461433410645</v>
       </c>
       <c r="G397" t="n">
-        <v>7.5585503578186</v>
+        <v>7.55854988098145</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842359542847</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G403" t="n">
-        <v>7.59416151046753</v>
+        <v>7.59416103363037</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>8.6953067779541</v>
       </c>
       <c r="G404" t="n">
-        <v>7.70989894866943</v>
+        <v>7.70989847183228</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G405" t="n">
-        <v>7.70099496841431</v>
+        <v>7.70099544525146</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757919311523</v>
+        <v>7.64757823944092</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G408" t="n">
-        <v>7.5852575302124</v>
+        <v>7.58525800704956</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428636550903</v>
+        <v>7.67428731918335</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.5748176574707</v>
       </c>
       <c r="G411" t="n">
-        <v>7.60306453704834</v>
+        <v>7.60306406021118</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G413" t="n">
-        <v>7.50513172149658</v>
+        <v>7.50513219833374</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249792098999</v>
+        <v>7.24249744415283</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701210021973</v>
+        <v>7.28701162338257</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.74645376205444</v>
       </c>
       <c r="G428" t="n">
-        <v>6.86857557296753</v>
+        <v>6.86857604980469</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.76151514053345</v>
       </c>
       <c r="G429" t="n">
-        <v>6.88193035125732</v>
+        <v>6.88192987442017</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G432" t="n">
-        <v>7.22469091415405</v>
+        <v>7.22469139099121</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591369628906</v>
+        <v>7.29591464996338</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409860610962</v>
+        <v>7.55409908294678</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G439" t="n">
-        <v>7.5852575302124</v>
+        <v>7.58525800704956</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G440" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538381576538</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G442" t="n">
-        <v>7.70099496841431</v>
+        <v>7.70099544525146</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.09693813323975</v>
       </c>
       <c r="G446" t="n">
-        <v>8.06601428985596</v>
+        <v>8.06601524353027</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G447" t="n">
-        <v>8.12833404541016</v>
+        <v>8.12833499908447</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G449" t="n">
-        <v>8.03040313720703</v>
+        <v>8.03040218353271</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504360198975</v>
+        <v>8.15504264831543</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.15216159820557</v>
       </c>
       <c r="G455" t="n">
-        <v>8.11497974395752</v>
+        <v>8.1149787902832</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G457" t="n">
-        <v>7.77221822738647</v>
+        <v>7.77221870422363</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.92122364044189</v>
       </c>
       <c r="G459" t="n">
-        <v>7.91021299362183</v>
+        <v>7.91021347045898</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G460" t="n">
-        <v>7.78112173080444</v>
+        <v>7.78112125396729</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.42945766448975</v>
+        <v>7.4294581413269</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G464" t="n">
-        <v>7.23804521560669</v>
+        <v>7.23804569244385</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>9.04673385620117</v>
       </c>
       <c r="G465" t="n">
-        <v>8.02149963378906</v>
+        <v>8.02150058746338</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538381576538</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G468" t="n">
-        <v>7.64312648773193</v>
+        <v>7.64312696456909</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479103088379</v>
+        <v>7.99479150772095</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G470" t="n">
-        <v>8.03040313720703</v>
+        <v>8.03040218353271</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.63914012908936</v>
       </c>
       <c r="G472" t="n">
-        <v>8.5467700958252</v>
+        <v>8.54677104949951</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G476" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.44836521148682</v>
       </c>
       <c r="G479" t="n">
-        <v>8.3776159286499</v>
+        <v>8.37761497497559</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G480" t="n">
-        <v>7.78557348251343</v>
+        <v>7.78557395935059</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757919311523</v>
+        <v>7.64757823944092</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576314926147</v>
+        <v>7.90576267242432</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344244003296</v>
+        <v>7.84344148635864</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G490" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G492" t="n">
-        <v>7.50513172149658</v>
+        <v>7.50513219833374</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G493" t="n">
-        <v>7.64312648773193</v>
+        <v>7.64312696456909</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G495" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>8.39910411834717</v>
       </c>
       <c r="G498" t="n">
-        <v>7.44726324081421</v>
+        <v>7.44726371765137</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G500" t="n">
-        <v>7.77221822738647</v>
+        <v>7.77221870422363</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G501" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>8.39910411834717</v>
       </c>
       <c r="G502" t="n">
-        <v>7.44726324081421</v>
+        <v>7.44726371765137</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>8.34889984130859</v>
       </c>
       <c r="G503" t="n">
-        <v>7.40274858474731</v>
+        <v>7.40274810791016</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.74996280670166</v>
+        <v>7.7499623298645</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G505" t="n">
-        <v>8.03040313720703</v>
+        <v>8.03040218353271</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>9.11199855804443</v>
       </c>
       <c r="G506" t="n">
-        <v>8.07936859130859</v>
+        <v>8.07936763763428</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G507" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.55379295349121</v>
       </c>
       <c r="G511" t="n">
-        <v>8.47109603881836</v>
+        <v>8.47109508514404</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.50225639343262</v>
+        <v>8.5022554397583</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.76464939117432</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65805625915527</v>
+        <v>8.65805721282959</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03642845153809</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G527" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G529" t="n">
-        <v>9.04088020324707</v>
+        <v>9.04087924957275</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G530" t="n">
-        <v>9.04088020324707</v>
+        <v>9.04087924957275</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833885192871</v>
+        <v>8.83833980560303</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.60399723052979</v>
       </c>
       <c r="G532" t="n">
-        <v>8.51561069488525</v>
+        <v>8.51560974121094</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>9.30277442932129</v>
       </c>
       <c r="G535" t="n">
-        <v>8.2485237121582</v>
+        <v>8.24852466583252</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617107391357</v>
+        <v>8.16617202758789</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G537" t="n">
-        <v>7.82341051101685</v>
+        <v>7.823410987854</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G538" t="n">
-        <v>8.03485488891602</v>
+        <v>8.0348539352417</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660707473755</v>
+        <v>7.73660755157471</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519557952881</v>
+        <v>7.54519510269165</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G545" t="n">
-        <v>7.66093397140503</v>
+        <v>7.66093349456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G548" t="n">
-        <v>7.60083913803101</v>
+        <v>7.60083818435669</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.76331615447998</v>
+        <v>7.76331663131714</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.52293825149536</v>
+        <v>7.5229377746582</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368829727173</v>
+        <v>7.29368877410889</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>8.32379913330078</v>
       </c>
       <c r="G563" t="n">
-        <v>7.38049268722534</v>
+        <v>7.38049173355103</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.31124782562256</v>
       </c>
       <c r="G564" t="n">
-        <v>7.36936378479004</v>
+        <v>7.36936330795288</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613481521606</v>
+        <v>7.43613433837891</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585079193115</v>
+        <v>7.25585174560547</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.32128810882568</v>
       </c>
       <c r="G567" t="n">
-        <v>7.37826633453369</v>
+        <v>7.37826681137085</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>8.43173694610596</v>
       </c>
       <c r="G568" t="n">
-        <v>7.47619771957397</v>
+        <v>7.47619819641113</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>8.16063594818115</v>
       </c>
       <c r="G569" t="n">
-        <v>7.23581981658936</v>
+        <v>7.23582029342651</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G573" t="n">
-        <v>7.07111692428589</v>
+        <v>7.07111740112305</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.79163789749146</v>
       </c>
       <c r="G576" t="n">
-        <v>6.9086389541626</v>
+        <v>6.90863943099976</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744714736938</v>
+        <v>6.85744762420654</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G583" t="n">
-        <v>7.22469091415405</v>
+        <v>7.22469139099121</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G586" t="n">
-        <v>7.4806489944458</v>
+        <v>7.48064947128296</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842359542847</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G589" t="n">
-        <v>7.4806489944458</v>
+        <v>7.48064947128296</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766731262207</v>
+        <v>6.99766778945923</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443881988525</v>
+        <v>7.06443929672241</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.55222606658936</v>
       </c>
       <c r="G603" t="n">
-        <v>7.58303213119507</v>
+        <v>7.58303260803223</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065475463867</v>
+        <v>8.19065380096436</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G621" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G627" t="n">
-        <v>8.27523231506348</v>
+        <v>8.27523136138916</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>9.36552906036377</v>
       </c>
       <c r="G630" t="n">
-        <v>8.30416774749756</v>
+        <v>8.30416679382324</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G633" t="n">
-        <v>8.12833404541016</v>
+        <v>8.12833499908447</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G634" t="n">
-        <v>8.12833404541016</v>
+        <v>8.12833499908447</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G636" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>9.90019989013672</v>
       </c>
       <c r="G637" t="n">
-        <v>8.778244972229</v>
+        <v>8.77824592590332</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.86254692077637</v>
       </c>
       <c r="G639" t="n">
-        <v>8.74485874176025</v>
+        <v>8.74485969543457</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G640" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>10.2767276763916</v>
       </c>
       <c r="G643" t="n">
-        <v>9.11210250854492</v>
+        <v>9.11210155487061</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G644" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009727478027</v>
+        <v>9.25009822845459</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.4649925231934</v>
       </c>
       <c r="G647" t="n">
-        <v>9.27903175354004</v>
+        <v>9.27903270721436</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G651" t="n">
-        <v>9.05646133422852</v>
+        <v>9.0564603805542</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100505828857</v>
+        <v>9.12100601196289</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G660" t="n">
-        <v>9.84659194946289</v>
+        <v>9.84659099578857</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G661" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G662" t="n">
-        <v>9.31686973571777</v>
+        <v>9.31686878204346</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G664" t="n">
-        <v>9.79317378997803</v>
+        <v>9.79317283630371</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>11.2331123352051</v>
       </c>
       <c r="G666" t="n">
-        <v>9.96010303497314</v>
+        <v>9.96010398864746</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G667" t="n">
-        <v>9.87107372283936</v>
+        <v>9.87107467651367</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>11.6322326660156</v>
       </c>
       <c r="G669" t="n">
-        <v>10.3139934539795</v>
+        <v>10.3139925003052</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G671" t="n">
-        <v>9.80652904510498</v>
+        <v>9.80652809143066</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>11.6648645401001</v>
       </c>
       <c r="G674" t="n">
-        <v>10.3429269790649</v>
+        <v>10.3429260253906</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>11.5167636871338</v>
       </c>
       <c r="G675" t="n">
-        <v>10.2116098403931</v>
+        <v>10.2116088867188</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>11.4665603637695</v>
       </c>
       <c r="G680" t="n">
-        <v>10.1670951843262</v>
+        <v>10.1670961380005</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>11.700008392334</v>
       </c>
       <c r="G683" t="n">
-        <v>10.3740882873535</v>
+        <v>10.3740873336792</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G684" t="n">
-        <v>10.334023475647</v>
+        <v>10.3340244293213</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99349021911621</v>
+        <v>9.99348926544189</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694787979126</v>
+        <v>10.2694797515869</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>11.5017032623291</v>
       </c>
       <c r="G688" t="n">
-        <v>10.1982564926147</v>
+        <v>10.1982555389404</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>11.328498840332</v>
       </c>
       <c r="G690" t="n">
-        <v>10.0446796417236</v>
+        <v>10.0446805953979</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G691" t="n">
-        <v>10.3941192626953</v>
+        <v>10.394118309021</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>12.0489253997803</v>
       </c>
       <c r="G692" t="n">
-        <v>10.683464050293</v>
+        <v>10.6834630966187</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G693" t="n">
-        <v>10.8259077072144</v>
+        <v>10.8259086608887</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.7569122314453</v>
+        <v>10.756911277771</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>12.4580860137939</v>
       </c>
       <c r="G697" t="n">
-        <v>11.0462551116943</v>
+        <v>11.0462560653687</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>13.1232872009277</v>
       </c>
       <c r="G698" t="n">
-        <v>11.6360721588135</v>
+        <v>11.6360712051392</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>13.7558555603027</v>
       </c>
       <c r="G704" t="n">
-        <v>12.1969537734985</v>
+        <v>12.1969528198242</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856685638428</v>
+        <v>12.0856666564941</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>13.032919883728</v>
       </c>
       <c r="G706" t="n">
-        <v>11.5559453964233</v>
+        <v>11.555944442749</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>12.7618188858032</v>
       </c>
       <c r="G709" t="n">
-        <v>11.3155679702759</v>
+        <v>11.3155670166016</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395784378052</v>
+        <v>11.0395774841309</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>12.3325757980347</v>
       </c>
       <c r="G714" t="n">
-        <v>10.9349699020386</v>
+        <v>10.9349679946899</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>11.8004150390625</v>
       </c>
       <c r="G715" t="n">
-        <v>10.463116645813</v>
+        <v>10.4631156921387</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364070892334</v>
+        <v>10.4364080429077</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G725" t="n">
-        <v>10.3941192626953</v>
+        <v>10.394118309021</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>11.7025184631348</v>
       </c>
       <c r="G727" t="n">
-        <v>10.376314163208</v>
+        <v>10.3763132095337</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>11.1377248764038</v>
       </c>
       <c r="G732" t="n">
-        <v>9.87552642822266</v>
+        <v>9.87552547454834</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>10.5402994155884</v>
       </c>
       <c r="G735" t="n">
-        <v>9.34580516815186</v>
+        <v>9.34580421447754</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G736" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081249237061</v>
+        <v>8.29081058502197</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889537811279</v>
+        <v>7.77889585494995</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219158172607</v>
+        <v>8.46219253540039</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.65922069549561</v>
       </c>
       <c r="G745" t="n">
-        <v>8.56457614898682</v>
+        <v>8.5645751953125</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G749" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G750" t="n">
-        <v>8.1884298324585</v>
+        <v>8.18842887878418</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>9.33540630340576</v>
       </c>
       <c r="G753" t="n">
-        <v>8.27745723724365</v>
+        <v>8.27745819091797</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G754" t="n">
-        <v>8.29526424407959</v>
+        <v>8.29526329040527</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466569900513</v>
+        <v>7.91466474533081</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>8.81077575683594</v>
       </c>
       <c r="G756" t="n">
-        <v>7.81228256225586</v>
+        <v>7.81228160858154</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>8.25602340698242</v>
       </c>
       <c r="G758" t="n">
-        <v>7.32039785385132</v>
+        <v>7.32039737701416</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G759" t="n">
-        <v>7.59416151046753</v>
+        <v>7.59416103363037</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>8.17318725585938</v>
       </c>
       <c r="G760" t="n">
-        <v>7.24694919586182</v>
+        <v>7.24694871902466</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873331069946</v>
+        <v>6.96873378753662</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>8.37400245666504</v>
       </c>
       <c r="G765" t="n">
-        <v>7.42500686645508</v>
+        <v>7.42500638961792</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576314926147</v>
+        <v>7.90576267242432</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>9.12957000732422</v>
       </c>
       <c r="G767" t="n">
-        <v>8.09494876861572</v>
+        <v>8.09494781494141</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G778" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G779" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>9.71193504333496</v>
       </c>
       <c r="G780" t="n">
-        <v>8.61131572723389</v>
+        <v>8.61131477355957</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G782" t="n">
-        <v>8.86282348632812</v>
+        <v>8.86282253265381</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>10.3445043563843</v>
       </c>
       <c r="G787" t="n">
-        <v>9.17219924926758</v>
+        <v>9.17219829559326</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G788" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>9.79477119445801</v>
       </c>
       <c r="G790" t="n">
-        <v>8.68476486206055</v>
+        <v>8.68476390838623</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>9.75711917877197</v>
       </c>
       <c r="G791" t="n">
-        <v>8.65137958526611</v>
+        <v>8.6513786315918</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G795" t="n">
-        <v>9.0809440612793</v>
+        <v>9.08094310760498</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G796" t="n">
-        <v>9.43705940246582</v>
+        <v>9.4370584487915</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G804" t="n">
-        <v>9.69746875762939</v>
+        <v>9.69746685028076</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232986450195</v>
+        <v>9.96232891082764</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>11.5167636871338</v>
       </c>
       <c r="G807" t="n">
-        <v>10.2116098403931</v>
+        <v>10.2116088867188</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496036529541</v>
+        <v>10.3496055603027</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>11.8882722854614</v>
       </c>
       <c r="G809" t="n">
-        <v>10.541015625</v>
+        <v>10.5410165786743</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G812" t="n">
-        <v>10.5276613235474</v>
+        <v>10.5276622772217</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.2572708129883</v>
       </c>
       <c r="G814" t="n">
-        <v>10.8681974411011</v>
+        <v>10.8681983947754</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>12.2145967483521</v>
       </c>
       <c r="G817" t="n">
-        <v>10.8303594589233</v>
+        <v>10.8303604125977</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G819" t="n">
-        <v>10.9883861541748</v>
+        <v>10.9883871078491</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G820" t="n">
-        <v>10.8259077072144</v>
+        <v>10.8259086608887</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>11.5970897674561</v>
       </c>
       <c r="G821" t="n">
-        <v>10.2828330993652</v>
+        <v>10.2828321456909</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>11.5368452072144</v>
       </c>
       <c r="G822" t="n">
-        <v>10.2294149398804</v>
+        <v>10.2294158935547</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G825" t="n">
-        <v>10.334023475647</v>
+        <v>10.3340244293213</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147811889648</v>
+        <v>10.8147802352905</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295726776123</v>
+        <v>10.3295736312866</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>12.0564546585083</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6901388168335</v>
+        <v>10.6901397705078</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>11.3385400772095</v>
       </c>
       <c r="G846" t="n">
-        <v>10.0535840988159</v>
+        <v>10.0535831451416</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>10.977071762085</v>
       </c>
       <c r="G848" t="n">
-        <v>9.733078956604</v>
+        <v>9.73307800292969</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G851" t="n">
-        <v>9.33912754058838</v>
+        <v>9.33912658691406</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>10.1411781311035</v>
       </c>
       <c r="G852" t="n">
-        <v>8.99191474914551</v>
+        <v>8.99191379547119</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>10.203932762146</v>
       </c>
       <c r="G854" t="n">
-        <v>9.04755687713623</v>
+        <v>9.04755783081055</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G855" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>10.4072589874268</v>
       </c>
       <c r="G856" t="n">
-        <v>9.2278413772583</v>
+        <v>9.22784233093262</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>10.5101757049561</v>
       </c>
       <c r="G860" t="n">
-        <v>9.31909465789795</v>
+        <v>9.31909561157227</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G861" t="n">
-        <v>9.25232410430908</v>
+        <v>9.25232315063477</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G863" t="n">
-        <v>8.77601909637451</v>
+        <v>8.7760181427002</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>9.62156772613525</v>
       </c>
       <c r="G868" t="n">
-        <v>8.53118991851807</v>
+        <v>8.53118896484375</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G871" t="n">
-        <v>9.07204055786133</v>
+        <v>9.07203960418701</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>10.768726348877</v>
       </c>
       <c r="G874" t="n">
-        <v>9.54834461212158</v>
+        <v>9.5483455657959</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395576477051</v>
+        <v>9.58395671844482</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G876" t="n">
-        <v>9.23451900482178</v>
+        <v>9.23451805114746</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G877" t="n">
-        <v>9.33912754058838</v>
+        <v>9.33912658691406</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079113006592</v>
+        <v>9.69079208374023</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>10.9218482971191</v>
       </c>
       <c r="G886" t="n">
-        <v>9.68411350250244</v>
+        <v>9.68411445617676</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.0498676300049</v>
       </c>
       <c r="G887" t="n">
-        <v>9.79762649536133</v>
+        <v>9.79762554168701</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.2431526184082</v>
       </c>
       <c r="G889" t="n">
-        <v>9.9690055847168</v>
+        <v>9.96900653839111</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G890" t="n">
-        <v>9.69746875762939</v>
+        <v>9.69746685028076</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>11.4715795516968</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1715469360352</v>
+        <v>10.1715459823608</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304893493652</v>
+        <v>9.71304798126221</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>11.0423374176025</v>
       </c>
       <c r="G905" t="n">
-        <v>9.79094791412354</v>
+        <v>9.79094886779785</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794101715088</v>
+        <v>9.99794006347656</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G914" t="n">
-        <v>9.20780944824219</v>
+        <v>9.2078104019165</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>10.3721160888672</v>
       </c>
       <c r="G917" t="n">
-        <v>9.19668102264404</v>
+        <v>9.19668006896973</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.9518518447876</v>
+        <v>8.95185089111328</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G934" t="n">
-        <v>9.43705940246582</v>
+        <v>9.4370584487915</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G937" t="n">
-        <v>9.80652904510498</v>
+        <v>9.80652809143066</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>11.4665603637695</v>
       </c>
       <c r="G939" t="n">
-        <v>10.1670951843262</v>
+        <v>10.1670961380005</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.1047744750977</v>
+        <v>10.104775428772</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136779785156</v>
+        <v>10.1136770248413</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230527877808</v>
+        <v>10.4230537414551</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>11.1854181289673</v>
       </c>
       <c r="G945" t="n">
-        <v>9.91781520843506</v>
+        <v>9.91781425476074</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G946" t="n">
-        <v>9.87107372283936</v>
+        <v>9.87107467651367</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G947" t="n">
-        <v>9.84659194946289</v>
+        <v>9.84659099578857</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.881685256958</v>
       </c>
       <c r="G948" t="n">
-        <v>9.64850330352783</v>
+        <v>9.64850234985352</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>10.7862977981567</v>
       </c>
       <c r="G949" t="n">
-        <v>9.56392478942871</v>
+        <v>9.56392574310303</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>10.0683822631836</v>
       </c>
       <c r="G955" t="n">
-        <v>8.92736721038818</v>
+        <v>8.92736911773682</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>10.0332403182983</v>
       </c>
       <c r="G956" t="n">
-        <v>8.89620876312256</v>
+        <v>8.89620780944824</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G961" t="n">
-        <v>9.16997337341309</v>
+        <v>9.16997241973877</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G962" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G964" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G965" t="n">
-        <v>9.31686973571777</v>
+        <v>9.31686878204346</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65962982177734</v>
+        <v>9.65963077545166</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>10.3219118118286</v>
       </c>
       <c r="G975" t="n">
-        <v>9.15216636657715</v>
+        <v>9.15216541290283</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03642845153809</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>11.2306022644043</v>
       </c>
       <c r="G981" t="n">
-        <v>9.95787715911865</v>
+        <v>9.95787811279297</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.802077293396</v>
+        <v>9.80207633972168</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812397003174</v>
+        <v>9.40812492370605</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>10.8164196014404</v>
       </c>
       <c r="G993" t="n">
-        <v>9.59063339233398</v>
+        <v>9.59063243865967</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>10.7135019302368</v>
       </c>
       <c r="G996" t="n">
-        <v>9.49937915802002</v>
+        <v>9.4993782043457</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G997" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G998" t="n">
-        <v>9.07204055786133</v>
+        <v>9.07203960418701</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G999" t="n">
-        <v>9.05646133422852</v>
+        <v>9.0564603805542</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.25232410430908</v>
+        <v>9.25232315063477</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467674255371</v>
+        <v>9.33467578887939</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.56169891357422</v>
+        <v>9.5616979598999</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>10.934398651123</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.69524192810059</v>
+        <v>9.6952428817749</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>11.1678466796875</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.90223503112793</v>
+        <v>9.90223407745361</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.79317378997803</v>
+        <v>9.79317283630371</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.802077293396</v>
+        <v>9.80207633972168</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.31974697113037</v>
+        <v>8.31974601745605</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>9.75962924957275</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.65360450744629</v>
+        <v>8.65360546112061</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.34645462036133</v>
+        <v>8.34645557403564</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>9.55630302429199</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.47332191467285</v>
+        <v>8.47332096099854</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>9.41573238372803</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.34868144989014</v>
+        <v>8.34868049621582</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>9.51362991333008</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.43548393249512</v>
+        <v>8.4354829788208</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>9.42577266693115</v>
       </c>
       <c r="G1052" t="n">
-        <v>8.35758304595947</v>
+        <v>8.35758399963379</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754726409912</v>
+        <v>7.62754774093628</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.60083913803101</v>
+        <v>7.60083818435669</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>8.3037166595459</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.36268663406372</v>
+        <v>7.36268615722656</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585079193115</v>
+        <v>7.25585174560547</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.07111692428589</v>
+        <v>7.07111740112305</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.95009994506836</v>
       </c>
       <c r="G1068" t="n">
-        <v>4.3891224861145</v>
+        <v>4.38912296295166</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>5.16346597671509</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.57830905914307</v>
+        <v>4.57830858230591</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>5.18605804443359</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.59834051132202</v>
+        <v>4.59834003448486</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342178344727</v>
+        <v>5.00342130661011</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.88990926742554</v>
+        <v>4.88991022109985</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.0219521522522</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.33950567245483</v>
+        <v>5.33950519561768</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.29276514053345</v>
+        <v>5.29276561737061</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>5.28395509719849</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.685142993927</v>
+        <v>4.68514347076416</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>5.67303514480591</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.03012990951538</v>
+        <v>5.03013038635254</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928550720215</v>
+        <v>5.19928503036499</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041345596313</v>
+        <v>5.21041393280029</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>5.73328018188477</v>
       </c>
       <c r="G1100" t="n">
-        <v>5.08354759216309</v>
+        <v>5.08354806900024</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>5.62032079696655</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.98338985443115</v>
+        <v>4.98338937759399</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470699310303</v>
+        <v>5.11470794677734</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>5.80858516693115</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15031862258911</v>
+        <v>5.15031909942627</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248159408569</v>
+        <v>5.11248207092285</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.92329597473145</v>
+        <v>4.92329549789429</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>5.57513809204102</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.94332695007324</v>
+        <v>4.9433274269104</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.79800033569336</v>
+        <v>4.79800081253052</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>5.46217918395996</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.86507511138916</v>
+        <v>4.865074634552</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>5.30905723571777</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.72869157791138</v>
+        <v>4.72869110107422</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>5.79854488372803</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.16467046737671</v>
+        <v>5.16466999053955</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>6.46876621246338</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.76162528991699</v>
+        <v>5.76162576675415</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>6.59176588058472</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.87117958068848</v>
+        <v>5.87117910385132</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>6.41354179382324</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.71243810653687</v>
+        <v>5.71243762969971</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>5.99182987213135</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.33682632446289</v>
+        <v>5.33682584762573</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>5.98680877685547</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.33235359191895</v>
+        <v>5.3323540687561</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.08418226242065</v>
+        <v>5.0841817855835</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>5.61530113220215</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.00145769119263</v>
+        <v>5.00145816802979</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.97686290740967</v>
+        <v>4.97686338424683</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>5.68558597564697</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.06405925750732</v>
+        <v>5.06405973434448</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>5.27642488479614</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.69962644577026</v>
+        <v>4.69962596893311</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>5.28897619247437</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.71080589294434</v>
+        <v>4.71080541610718</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>5.36679220199585</v>
       </c>
       <c r="G1152" t="n">
-        <v>4.78011512756348</v>
+        <v>4.78011465072632</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.47724008560181</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.87848901748657</v>
+        <v>4.87848949432373</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>4.92123222351074</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.38326168060303</v>
+        <v>4.38326215744019</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.57357120513916</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.07360601425171</v>
+        <v>4.07360553741455</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.96892595291138</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.42574167251587</v>
+        <v>4.42574214935303</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1174" t="n">
-        <v>4.34190034866333</v>
+        <v>4.34189987182617</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.66895818710327</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.15856599807739</v>
+        <v>4.15856552124023</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.50579500198364</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.01323890686035</v>
+        <v>4.01323843002319</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.39032697677612</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.91039323806763</v>
+        <v>3.91039347648621</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.29242897033691</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.82319688796997</v>
+        <v>3.82319736480713</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>4.19327592849731</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.73488306999207</v>
+        <v>3.73488283157349</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.07906293869019</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.63315558433533</v>
+        <v>3.63315534591675</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.22465419769287</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.76283121109009</v>
+        <v>3.76283097267151</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.56321811676025</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.17370057106018</v>
+        <v>3.17370080947876</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.86444091796875</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.44199514389038</v>
+        <v>3.4419949054718</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>3.79415607452393</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.37939357757568</v>
+        <v>3.3793933391571</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>3.65609502792358</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.25642490386963</v>
+        <v>3.25642466545105</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>3.59585094451904</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.20276618003845</v>
+        <v>3.20276641845703</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>3.62597298622131</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.22959542274475</v>
+        <v>3.22959566116333</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.68496203422546</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.28213596343994</v>
+        <v>3.28213620185852</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>3.78411507606506</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.370450258255</v>
+        <v>3.37045001983643</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.6940598487854</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.1809229850769</v>
+        <v>4.18092346191406</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>4.89487504959106</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.35978603363037</v>
+        <v>4.35978651046753</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.2770619392395</v>
+        <v>4.27706241607666</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.47157526016235</v>
+        <v>4.47157573699951</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>5.42201614379883</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.82930183410645</v>
+        <v>4.8293023109436</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>5.30654716491699</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.72645616531372</v>
+        <v>4.72645568847656</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>5.1333441734314</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.57218647003174</v>
+        <v>4.5721869468689</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.62584447860718</v>
+        <v>4.62584495544434</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>5.35675096511841</v>
       </c>
       <c r="G1254" t="n">
-        <v>4.77117156982422</v>
+        <v>4.77117109298706</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>5.37683200836182</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.78905725479126</v>
+        <v>4.78905773162842</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1259" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>5.46719884872437</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.86954545974731</v>
+        <v>4.86954593658447</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.86060237884521</v>
+        <v>4.86060285568237</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>5.82364702224731</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.18702793121338</v>
+        <v>5.18702840805054</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>6.17256307601929</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.49780225753784</v>
+        <v>5.49780178070068</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>6.10729789733887</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.4396710395813</v>
+        <v>5.43967151641846</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>6.08721685409546</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.42178535461426</v>
+        <v>5.42178583145142</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>6.00689077377319</v>
       </c>
       <c r="G1279" t="n">
-        <v>5.3502402305603</v>
+        <v>5.35024070739746</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.85878896713257</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.21832847595215</v>
+        <v>5.21832895278931</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>5.34169006347656</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.75775671005249</v>
+        <v>4.75775718688965</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>5.59019899368286</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.97910022735596</v>
+        <v>4.9790997505188</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>5.98178911209106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.32788324356079</v>
+        <v>5.32788276672363</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>6.55160188674927</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.8354058265686</v>
+        <v>5.83540630340576</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>6.3457670211792</v>
       </c>
       <c r="G1303" t="n">
-        <v>5.65207242965698</v>
+        <v>5.65207195281982</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>6.35078716278076</v>
       </c>
       <c r="G1304" t="n">
-        <v>5.65654325485229</v>
+        <v>5.65654373168945</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>6.40852212905884</v>
       </c>
       <c r="G1305" t="n">
-        <v>5.70796680450439</v>
+        <v>5.70796728134155</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>6.63192892074585</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.90695190429688</v>
+        <v>5.90695142745972</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>6.00940084457397</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.35247611999512</v>
+        <v>5.35247659683228</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.08418226242065</v>
+        <v>5.0841817855835</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1312" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>5.91652393341064</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.26975202560425</v>
+        <v>5.26975250244141</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>6.07215595245361</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.40837144851685</v>
+        <v>5.40837097167969</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>6.07717609405518</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.41284227371216</v>
+        <v>5.41284275054932</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>6.12486982345581</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.455322265625</v>
+        <v>5.45532274246216</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>5.97174787521362</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.31893968582153</v>
+        <v>5.31893920898438</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1324" t="n">
-        <v>5.31670331954956</v>
+        <v>5.31670379638672</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>5.69060611724854</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.06853103637695</v>
+        <v>5.06853055953979</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>5.87887096405029</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.23621511459351</v>
+        <v>5.23621559143066</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>5.83870792388916</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.20044279098511</v>
+        <v>5.20044231414795</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.97686290740967</v>
+        <v>4.97686338424683</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.94556331634521</v>
+        <v>4.94556283950806</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.87855911254883</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.34525394439697</v>
+        <v>4.34525346755981</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.82333517074585</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.29606628417969</v>
+        <v>4.29606676101685</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>5.06054782867432</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.50734853744507</v>
+        <v>4.50734806060791</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.69068336486816</v>
+        <v>4.69068288803101</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>5.1383638381958</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.57665777206421</v>
+        <v>4.57665729522705</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>5.12832307815552</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.56771469116211</v>
+        <v>4.56771421432495</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>5.11828184127808</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.55877113342285</v>
+        <v>4.55877065658569</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>5.3793420791626</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.79129314422607</v>
+        <v>4.79129266738892</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>5.56760692596436</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.95897722244263</v>
+        <v>4.95897769927979</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1390" t="n">
-        <v>4.72421979904175</v>
+        <v>4.72422027587891</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.72421979904175</v>
+        <v>4.72422027587891</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>5.29901599884033</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.71974802017212</v>
+        <v>4.71974754333496</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1396" t="n">
-        <v>4.56324291229248</v>
+        <v>4.56324338912964</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>5.22873115539551</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.65714645385742</v>
+        <v>4.65714597702026</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>5.21868991851807</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.64820289611816</v>
+        <v>4.64820241928101</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.90617084503174</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.36984729766846</v>
+        <v>4.3698468208313</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.97143602371216</v>
       </c>
       <c r="G1403" t="n">
-        <v>4.42797803878784</v>
+        <v>4.42797756195068</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>4.88483476638794</v>
       </c>
       <c r="G1405" t="n">
-        <v>4.35084342956543</v>
+        <v>4.35084295272827</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.90240621566772</v>
       </c>
       <c r="G1407" t="n">
-        <v>4.36649370193481</v>
+        <v>4.36649417877197</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.75681495666504</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.23681831359863</v>
+        <v>4.23681783676147</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1417" t="n">
-        <v>4.52970600128174</v>
+        <v>4.5297064781189</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>4.91119194030762</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.37431907653809</v>
+        <v>4.37431955337524</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.92499780654907</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.38661623001099</v>
+        <v>4.38661575317383</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.56324291229248</v>
+        <v>4.56324338912964</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>5.16597604751587</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.60125112533569</v>
+        <v>4.60125160217285</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>4.98147678375244</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.43692111968994</v>
+        <v>4.43692064285278</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1433" t="n">
-        <v>4.2770619392395</v>
+        <v>4.27706241607666</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1436" t="n">
-        <v>4.47157526016235</v>
+        <v>4.47157573699951</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>4.96139478683472</v>
       </c>
       <c r="G1443" t="n">
-        <v>4.41903448104858</v>
+        <v>4.41903400421143</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>5.01662015914917</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.46822261810303</v>
+        <v>4.46822214126587</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1449" t="n">
-        <v>4.62584447860718</v>
+        <v>4.62584495544434</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.52970600128174</v>
+        <v>4.5297064781189</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.99151802062988</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.44586420059204</v>
+        <v>4.4458646774292</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>4.91244697570801</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.37543678283691</v>
+        <v>4.37543725967407</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>5.07058906555176</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.51629209518433</v>
+        <v>4.51629161834717</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>5.55003595352173</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.94332695007324</v>
+        <v>4.9433274269104</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.69068336486816</v>
+        <v>4.69068288803101</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.79800033569336</v>
+        <v>4.79800081253052</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1470" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.91202592849731</v>
+        <v>4.91202640533447</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.94556331634521</v>
+        <v>4.94556283950806</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.87353897094727</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.34078216552734</v>
+        <v>4.3407826423645</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.81203889846802</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.2860050201416</v>
+        <v>4.28600549697876</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.34190034866333</v>
+        <v>4.34189987182617</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.39220476150513</v>
+        <v>4.39220523834229</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>4.46563196182251</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.97746634483337</v>
+        <v>3.97746610641479</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>4.50328493118286</v>
       </c>
       <c r="G1504" t="n">
-        <v>4.01100301742554</v>
+        <v>4.0110034942627</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>4.42170381546021</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.93833994865417</v>
+        <v>3.93834018707275</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>4.59365177154541</v>
       </c>
       <c r="G1509" t="n">
-        <v>4.09149122238159</v>
+        <v>4.09149169921875</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>4.56729507446289</v>
       </c>
       <c r="G1511" t="n">
-        <v>4.06801557540894</v>
+        <v>4.06801605224609</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>4.41040802001953</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.92827892303467</v>
+        <v>3.92827916145325</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>4.4455509185791</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.95958042144775</v>
+        <v>3.95958018302917</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>4.37275505065918</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.89474201202393</v>
+        <v>3.89474248886108</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.55097913742065</v>
       </c>
       <c r="G1522" t="n">
-        <v>4.0534839630127</v>
+        <v>4.05348348617554</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>4.78317213058472</v>
       </c>
       <c r="G1527" t="n">
-        <v>4.26029396057129</v>
+        <v>4.26029443740845</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>4.91495704650879</v>
       </c>
       <c r="G1531" t="n">
-        <v>4.37767314910889</v>
+        <v>4.37767267227173</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.03042602539062</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.48051881790161</v>
+        <v>4.48051929473877</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.39220476150513</v>
+        <v>4.39220523834229</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>5.01410913467407</v>
       </c>
       <c r="G1541" t="n">
-        <v>4.4659857749939</v>
+        <v>4.46598625183105</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>2.99591493606567</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.66841316223145</v>
+        <v>2.66841292381287</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>3.02854704856873</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.6974778175354</v>
+        <v>2.69747805595398</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>2.8616189956665</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.54879760742188</v>
+        <v>2.54879784584045</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.5622124671936</v>
+        <v>2.56221222877502</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.51521301269531</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.24025940895081</v>
+        <v>2.24025964736938</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>2.56165099143982</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.28162097930908</v>
+        <v>2.28162121772766</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.56792688369751</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.2872109413147</v>
+        <v>2.28721117973328</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>2.37715196609497</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.11729073524475</v>
+        <v>2.11729097366333</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.58047795295715</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.29839015007019</v>
+        <v>2.29838991165161</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>2.46450710296631</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.19509649276733</v>
+        <v>2.19509673118591</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>2.67335510253906</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.38111424446106</v>
+        <v>2.38111400604248</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>2.86287403106689</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.54991579055786</v>
+        <v>2.54991555213928</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.5622124671936</v>
+        <v>2.56221222877502</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>2.93943500518799</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.61810708045959</v>
+        <v>2.61810731887817</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>2.87919092178345</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.56444883346558</v>
+        <v>2.564448595047</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>2.84404802322388</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.53314757347107</v>
+        <v>2.53314781188965</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>2.77878308296204</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.47501707077026</v>
+        <v>2.47501730918884</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>2.80262994766235</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.49625706672668</v>
+        <v>2.49625730514526</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>2.79384398460388</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.48843145370483</v>
+        <v>2.48843169212341</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>2.75744605064392</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.4560124874115</v>
+        <v>2.45601272583008</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.43700909614563</v>
+        <v>2.43700885772705</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.84028291702271</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.52979421615601</v>
+        <v>2.52979397773743</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>2.92437410354614</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.60469269752502</v>
+        <v>2.6046929359436</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.43700909614563</v>
+        <v>2.43700885772705</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.48509001731873</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.21342968940735</v>
+        <v>2.21342945098877</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>2.53780388832092</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.26038074493408</v>
+        <v>2.26038098335266</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>2.68841600418091</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.39452862739563</v>
+        <v>2.39452886581421</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>2.90680289268494</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.58904218673706</v>
+        <v>2.58904242515564</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>2.97517991065979</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.64994478225708</v>
+        <v>2.6499445438385</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>2.72426104545593</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.4264554977417</v>
+        <v>2.42645525932312</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>2.37423992156982</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.11469697952271</v>
+        <v>2.11469721794128</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>1.96649694442749</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.75152695178986</v>
+        <v>1.75152707099915</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>2.01657509803772</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.79613089561462</v>
+        <v>1.79613077640533</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>2.21557092666626</v>
       </c>
       <c r="G1646" t="n">
-        <v>1.97337317466736</v>
+        <v>1.97337329387665</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>1.73798203468323</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.54799258708954</v>
+        <v>1.54799246788025</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.59776198863983</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.42310082912445</v>
+        <v>1.42310070991516</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>1.24932205677032</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.11275088787079</v>
+        <v>1.11275100708008</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98913502693176</v>
+        <v>2.98913478851318</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.73594272136688</v>
+        <v>1.73594284057617</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.98598700761795</v>
+        <v>0.985986948013306</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.04210007190704</v>
+        <v>1.04209995269775</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.730360746383667</v>
+        <v>0.730360686779022</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>0.71340000629425</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.635413885116577</v>
+        <v>0.635413825511932</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.659106016159058</v>
+        <v>0.659106075763702</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.692061305046082</v>
+        <v>0.692061364650726</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.751737117767334</v>
+        <v>0.751737177371979</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>0.833599984645844</v>
       </c>
       <c r="G1677" t="n">
-        <v>0.742474019527435</v>
+        <v>0.74247407913208</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>0.821799993515015</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.731963932514191</v>
+        <v>0.731963992118835</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>0.762199997901917</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.678879201412201</v>
+        <v>0.678879261016846</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>0.716400027275085</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.638085961341858</v>
+        <v>0.638085901737213</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>0.674600005149841</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.600855350494385</v>
+        <v>0.60085529088974</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>0.697399973869324</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.621162831783295</v>
+        <v>0.621162891387939</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>0.683200001716614</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.60851514339447</v>
+        <v>0.608515202999115</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>0.662199974060059</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.589810788631439</v>
+        <v>0.589810848236084</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>0.64300000667572</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.572709679603577</v>
+        <v>0.572709739208221</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.540645122528076</v>
+        <v>0.540645062923431</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>0.584800004959106</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.520871877670288</v>
+        <v>0.520871937274933</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>0.59280002117157</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.527997434139252</v>
+        <v>0.527997374534607</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>0.597199976444244</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.531916379928589</v>
+        <v>0.531916320323944</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>0.637600004673004</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.567900061607361</v>
+        <v>0.567900002002716</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>0.72759997844696</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.648061573505402</v>
+        <v>0.648061513900757</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.620806634426117</v>
+        <v>0.620806694030762</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.658215403556824</v>
+        <v>0.658215343952179</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>0.758199989795685</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.675316512584686</v>
+        <v>0.675316452980042</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>0.828599989414215</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.738020658493042</v>
+        <v>0.738020598888397</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>0.958599984645844</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.853809475898743</v>
+        <v>0.853809535503387</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.876432955265045</v>
+        <v>0.8764328956604</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.873760879039764</v>
+        <v>0.87376081943512</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.882667720317841</v>
+        <v>0.882667660713196</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.919185638427734</v>
+        <v>0.919185698032379</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.957485139369965</v>
+        <v>0.957485198974609</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>1.09650003910065</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.976634919643402</v>
+        <v>0.976634860038757</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>1.03250002861023</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.919631123542786</v>
+        <v>0.919631063938141</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.92185777425766</v>
+        <v>0.921857714653015</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>1.04649996757507</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.932100594043732</v>
+        <v>0.932100653648376</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.926311194896698</v>
+        <v>0.926311135292053</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>1.04750001430511</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.932991325855255</v>
+        <v>0.93299126625061</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.912950932979584</v>
+        <v>0.912950873374939</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>1.01950001716614</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.908052206039429</v>
+        <v>0.908052146434784</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>1.04449999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.930319249629974</v>
+        <v>0.93031919002533</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>1.00650000572205</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.896473288536072</v>
+        <v>0.896473228931427</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.04949998855591</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.934772670269012</v>
+        <v>0.934772729873657</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>1.10950005054474</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.988213717937469</v>
+        <v>0.988213777542114</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.977970898151398</v>
+        <v>0.977970957756042</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>1.12750005722046</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.00424611568451</v>
+        <v>1.00424599647522</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.05456972122192</v>
+        <v>1.05456960201263</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>1.31149995326996</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.16813170909882</v>
+        <v>1.16813182830811</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.25141084194183</v>
+        <v>1.25141072273254</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.23092496395111</v>
+        <v>1.2309250831604</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.21845543384552</v>
+        <v>1.21845555305481</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.26031768321991</v>
+        <v>1.26031756401062</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.25586426258087</v>
+        <v>1.25586414337158</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.24962937831879</v>
+        <v>1.24962949752808</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.31464922428131</v>
+        <v>1.3146493434906</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.35116732120514</v>
+        <v>1.35116744041443</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>1.53450000286102</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.36675441265106</v>
+        <v>1.36675429344177</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.31643080711365</v>
+        <v>1.31643068790436</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.35749995708466</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.20910322666168</v>
+        <v>1.20910334587097</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>1.26549994945526</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.12716042995453</v>
+        <v>1.12716031074524</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>1.14049994945526</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.01582479476929</v>
+        <v>1.01582491397858</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>1.23450005054474</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.09954917430878</v>
+        <v>1.09954929351807</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.32550001144409</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.1806013584137</v>
+        <v>1.18060147762299</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.14007520675659</v>
+        <v>1.14007532596588</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23181569576263</v>
+        <v>1.23181581497192</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.31821203231812</v>
+        <v>1.3182121515274</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>1.25049996376038</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.11380016803741</v>
+        <v>1.11380004882812</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.150763630867</v>
+        <v>1.15076351165771</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.13473117351532</v>
+        <v>1.13473129272461</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.12048029899597</v>
+        <v>1.12048017978668</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.15788888931274</v>
+        <v>1.15788900852203</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>1.25750005245209</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.12003493309021</v>
+        <v>1.1200350522995</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.12226152420044</v>
+        <v>1.12226164340973</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.07416462898254</v>
+        <v>1.07416474819183</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.13473117351532</v>
+        <v>1.13473129272461</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>1.25450003147125</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.11736285686493</v>
+        <v>1.11736297607422</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.08663439750671</v>
+        <v>1.08663427829742</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>1.16250002384186</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.03542006015778</v>
+        <v>1.03541994094849</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.04833483695984</v>
+        <v>1.04833495616913</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.07772755622864</v>
+        <v>1.07772743701935</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.30039834976196</v>
+        <v>1.30039846897125</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.31108665466309</v>
+        <v>1.3110865354538</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.32266545295715</v>
+        <v>1.32266557216644</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>1.43949997425079</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.28213930130005</v>
+        <v>1.28213942050934</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>1.43250000476837</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.27590465545654</v>
+        <v>1.27590453624725</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.30039834976196</v>
+        <v>1.30039846897125</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.32800960540771</v>
+        <v>1.328009724617</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1928" t="n">
-        <v>1.31821203231812</v>
+        <v>1.3182121515274</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.31821203231812</v>
+        <v>1.3182121515274</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1930" t="n">
-        <v>1.29683554172516</v>
+        <v>1.29683566093445</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.29327297210693</v>
+        <v>1.29327285289764</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.25586426258087</v>
+        <v>1.25586414337158</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1935" t="n">
-        <v>1.24339473247528</v>
+        <v>1.24339461326599</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.304851770401</v>
+        <v>1.30485188961029</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.31019580364227</v>
+        <v>1.31019592285156</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.33869791030884</v>
+        <v>1.33869779109955</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.32266545295715</v>
+        <v>1.32266557216644</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1951" t="n">
-        <v>1.40193629264832</v>
+        <v>1.4019364118576</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.32800960540771</v>
+        <v>1.328009724617</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.31019580364227</v>
+        <v>1.31019592285156</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.37566125392914</v>
+        <v>1.37566113471985</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.41974997520447</v>
+        <v>1.41975009441376</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>1.60950005054474</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.43355560302734</v>
+        <v>1.43355572223663</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.40104556083679</v>
+        <v>1.40104568004608</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>1.46249997615814</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.30262506008148</v>
+        <v>1.30262517929077</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.27679526805878</v>
+        <v>1.27679538726807</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.29683554172516</v>
+        <v>1.29683566093445</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>1.41849994659424</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.26343488693237</v>
+        <v>1.26343500614166</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>1.5275000333786</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.36051952838898</v>
+        <v>1.36051964759827</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52031,7 +52031,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.37566125392914</v>
+        <v>1.37566113471985</v>
       </c>
       <c r="H1987" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.29015552997589</v>
+        <v>1.29015564918518</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.41449999809265</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.25987219810486</v>
+        <v>1.25987231731415</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.23626911640167</v>
+        <v>1.23626923561096</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.26031768321991</v>
+        <v>1.26031756401062</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.23805058002472</v>
+        <v>1.23805046081543</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2007" t="n">
-        <v>1.26031768321991</v>
+        <v>1.26031756401062</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>1.44749999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>1.28926491737366</v>
+        <v>1.28926479816437</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.31019580364227</v>
+        <v>1.31019592285156</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>1.46150004863739</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.30173456668854</v>
+        <v>1.30173444747925</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.24784815311432</v>
+        <v>1.24784803390503</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2023" t="n">
-        <v>1.24784815311432</v>
+        <v>1.24784803390503</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.22647154331207</v>
+        <v>1.22647166252136</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>1.42050004005432</v>
       </c>
       <c r="G2029" t="n">
-        <v>1.26521646976471</v>
+        <v>1.26521635055542</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.29015552997589</v>
+        <v>1.29015564918518</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>1.44649994373322</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.28837418556213</v>
+        <v>1.28837406635284</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>1.48300004005432</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.32088422775269</v>
+        <v>1.3208841085434</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.30930519104004</v>
+        <v>1.30930531024933</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>1.4889999628067</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.32622826099396</v>
+        <v>1.32622814178467</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>1.50650000572205</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.3418151140213</v>
+        <v>1.34181523323059</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.27679526805878</v>
+        <v>1.27679538726807</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.31643080711365</v>
+        <v>1.31643068790436</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G2055" t="n">
-        <v>1.34315133094788</v>
+        <v>1.34315121173859</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -54189,7 +54189,7 @@
         <v>1.375</v>
       </c>
       <c r="G2070" t="n">
-        <v>1.2246903181076</v>
+        <v>1.22469019889832</v>
       </c>
       <c r="H2070" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>1.38100004196167</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.23003447055817</v>
+        <v>1.23003435134888</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.32979106903076</v>
+        <v>1.32979094982147</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>1.82149994373322</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.62238049507141</v>
+        <v>1.6223806142807</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.723473072052</v>
+        <v>1.72347319126129</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>1.97650003433228</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.76043653488159</v>
+        <v>1.76043665409088</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.87488949298859</v>
+        <v>1.87488961219788</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.88112425804138</v>
+        <v>1.88112413883209</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>2.08699989318848</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.8588570356369</v>
+        <v>1.85885715484619</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.91318893432617</v>
+        <v>1.91318881511688</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -55047,7 +55047,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.98889708518982</v>
+        <v>1.98889696598053</v>
       </c>
       <c r="H2103" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2104" t="n">
-        <v>2.0076014995575</v>
+        <v>2.00760126113892</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G2105" t="n">
-        <v>2.00849223136902</v>
+        <v>2.00849199295044</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.06994891166687</v>
+        <v>2.06994915008545</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>2.3970000743866</v>
       </c>
       <c r="G2109" t="n">
-        <v>2.13496899604797</v>
+        <v>2.13496923446655</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2110" t="n">
-        <v>2.08420014381409</v>
+        <v>2.08419990539551</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.99513173103333</v>
+        <v>1.99513185024261</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.97909951210022</v>
+        <v>1.97909939289093</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.94258153438568</v>
+        <v>1.94258141517639</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.9719740152359</v>
+        <v>1.97197389602661</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.95237898826599</v>
+        <v>1.9523788690567</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2123" t="n">
-        <v>1.94079983234406</v>
+        <v>1.94080007076263</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55645,7 +55645,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2126" t="n">
-        <v>1.91318893432617</v>
+        <v>1.91318881511688</v>
       </c>
       <c r="H2126" t="s">
         <v>8</v>
@@ -55697,7 +55697,7 @@
         <v>2.13100004196167</v>
       </c>
       <c r="G2128" t="n">
-        <v>1.89804720878601</v>
+        <v>1.8980473279953</v>
       </c>
       <c r="H2128" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.95683240890503</v>
+        <v>1.95683228969574</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G2131" t="n">
-        <v>1.97019267082214</v>
+        <v>1.97019255161285</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G2132" t="n">
-        <v>2.02541518211365</v>
+        <v>2.02541494369507</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -55853,7 +55853,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2134" t="n">
-        <v>2.11359262466431</v>
+        <v>2.11359286308289</v>
       </c>
       <c r="H2134" t="s">
         <v>8</v>
@@ -55957,7 +55957,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2138" t="n">
-        <v>2.12160873413086</v>
+        <v>2.12160897254944</v>
       </c>
       <c r="H2138" t="s">
         <v>8</v>
@@ -55983,7 +55983,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2139" t="n">
-        <v>2.11359262466431</v>
+        <v>2.11359286308289</v>
       </c>
       <c r="H2139" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2141" t="n">
-        <v>2.07084012031555</v>
+        <v>2.07083988189697</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56087,7 +56087,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2143" t="n">
-        <v>1.98889708518982</v>
+        <v>1.98889696598053</v>
       </c>
       <c r="H2143" t="s">
         <v>8</v>
@@ -56139,7 +56139,7 @@
         <v>2.15300011634827</v>
       </c>
       <c r="G2145" t="n">
-        <v>1.9176424741745</v>
+        <v>1.91764235496521</v>
       </c>
       <c r="H2145" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.92031419277191</v>
+        <v>1.9203143119812</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.9336746931076</v>
+        <v>1.93367457389832</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91853308677673</v>
+        <v>1.91853296756744</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.83926224708557</v>
+        <v>1.83926212787628</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.80808818340302</v>
+        <v>1.80808806419373</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.86152923107147</v>
+        <v>1.86152911186218</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56399,7 +56399,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2155" t="n">
-        <v>1.86152923107147</v>
+        <v>1.86152911186218</v>
       </c>
       <c r="H2155" t="s">
         <v>8</v>
@@ -56425,7 +56425,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2156" t="n">
-        <v>1.89626586437225</v>
+        <v>1.89626574516296</v>
       </c>
       <c r="H2156" t="s">
         <v>8</v>
@@ -56451,7 +56451,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2157" t="n">
-        <v>1.91853308677673</v>
+        <v>1.91853296756744</v>
       </c>
       <c r="H2157" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>2.15899991989136</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.92298638820648</v>
+        <v>1.92298626899719</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56503,7 +56503,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.99245977401733</v>
+        <v>1.99245965480804</v>
       </c>
       <c r="H2159" t="s">
         <v>8</v>
@@ -56607,7 +56607,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.13585996627808</v>
+        <v>2.1358597278595</v>
       </c>
       <c r="H2163" t="s">
         <v>8</v>
@@ -56711,7 +56711,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2167" t="n">
-        <v>2.07084012031555</v>
+        <v>2.07083988189697</v>
       </c>
       <c r="H2167" t="s">
         <v>8</v>
@@ -56789,7 +56789,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G2170" t="n">
-        <v>2.07351207733154</v>
+        <v>2.07351183891296</v>
       </c>
       <c r="H2170" t="s">
         <v>8</v>
@@ -56815,7 +56815,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2171" t="n">
-        <v>2.06371450424194</v>
+        <v>2.06371426582336</v>
       </c>
       <c r="H2171" t="s">
         <v>8</v>
@@ -56841,7 +56841,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G2172" t="n">
-        <v>2.09666967391968</v>
+        <v>2.09666991233826</v>
       </c>
       <c r="H2172" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2174" t="n">
-        <v>2.10913944244385</v>
+        <v>2.10913920402527</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G2175" t="n">
-        <v>2.12339019775391</v>
+        <v>2.12339043617249</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -56945,7 +56945,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G2176" t="n">
-        <v>2.14476680755615</v>
+        <v>2.14476656913757</v>
       </c>
       <c r="H2176" t="s">
         <v>8</v>
@@ -57023,7 +57023,7 @@
         <v>2.41899991035461</v>
       </c>
       <c r="G2179" t="n">
-        <v>2.15456414222717</v>
+        <v>2.15456390380859</v>
       </c>
       <c r="H2179" t="s">
         <v>8</v>
@@ -57075,7 +57075,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2181" t="n">
-        <v>2.07084012031555</v>
+        <v>2.07083988189697</v>
       </c>
       <c r="H2181" t="s">
         <v>8</v>
@@ -57101,7 +57101,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G2182" t="n">
-        <v>1.9844434261322</v>
+        <v>1.98444354534149</v>
       </c>
       <c r="H2182" t="s">
         <v>8</v>
@@ -57153,7 +57153,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2184" t="n">
-        <v>1.94614410400391</v>
+        <v>1.9461442232132</v>
       </c>
       <c r="H2184" t="s">
         <v>8</v>
@@ -57179,7 +57179,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2185" t="n">
-        <v>1.95683240890503</v>
+        <v>1.95683228969574</v>
       </c>
       <c r="H2185" t="s">
         <v>8</v>
@@ -57205,7 +57205,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2186" t="n">
-        <v>1.94079983234406</v>
+        <v>1.94080007076263</v>
       </c>
       <c r="H2186" t="s">
         <v>8</v>
@@ -57309,7 +57309,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G2190" t="n">
-        <v>1.79294657707214</v>
+        <v>1.79294645786285</v>
       </c>
       <c r="H2190" t="s">
         <v>8</v>
@@ -57413,7 +57413,7 @@
         <v>1.98450005054474</v>
       </c>
       <c r="G2194" t="n">
-        <v>1.7675621509552</v>
+        <v>1.76756203174591</v>
       </c>
       <c r="H2194" t="s">
         <v>8</v>
@@ -57543,7 +57543,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G2199" t="n">
-        <v>1.8428248167038</v>
+        <v>1.84282493591309</v>
       </c>
       <c r="H2199" t="s">
         <v>8</v>
@@ -57621,7 +57621,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G2202" t="n">
-        <v>1.84549689292908</v>
+        <v>1.84549701213837</v>
       </c>
       <c r="H2202" t="s">
         <v>8</v>
@@ -57647,7 +57647,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G2203" t="n">
-        <v>1.81521368026733</v>
+        <v>1.81521379947662</v>
       </c>
       <c r="H2203" t="s">
         <v>8</v>
@@ -57725,7 +57725,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2206" t="n">
-        <v>1.80808818340302</v>
+        <v>1.80808806419373</v>
       </c>
       <c r="H2206" t="s">
         <v>8</v>
@@ -57751,7 +57751,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2207" t="n">
-        <v>1.80185329914093</v>
+        <v>1.80185341835022</v>
       </c>
       <c r="H2207" t="s">
         <v>8</v>
@@ -57777,7 +57777,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2208" t="n">
-        <v>1.67448568344116</v>
+        <v>1.67448556423187</v>
       </c>
       <c r="H2208" t="s">
         <v>8</v>
@@ -57803,7 +57803,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G2209" t="n">
-        <v>1.71189439296722</v>
+        <v>1.71189427375793</v>
       </c>
       <c r="H2209" t="s">
         <v>8</v>
@@ -57907,7 +57907,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G2213" t="n">
-        <v>1.60055899620056</v>
+        <v>1.60055887699127</v>
       </c>
       <c r="H2213" t="s">
         <v>8</v>
@@ -57933,7 +57933,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G2214" t="n">
-        <v>1.62727928161621</v>
+        <v>1.6272794008255</v>
       </c>
       <c r="H2214" t="s">
         <v>8</v>
@@ -58193,7 +58193,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G2224" t="n">
-        <v>1.81343233585358</v>
+        <v>1.81343221664429</v>
       </c>
       <c r="H2224" t="s">
         <v>8</v>
@@ -58401,7 +58401,7 @@
         <v>2.05699992179871</v>
       </c>
       <c r="G2232" t="n">
-        <v>1.83213651180267</v>
+        <v>1.83213663101196</v>
       </c>
       <c r="H2232" t="s">
         <v>8</v>
@@ -58453,7 +58453,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2234" t="n">
-        <v>1.79027450084686</v>
+        <v>1.79027438163757</v>
       </c>
       <c r="H2234" t="s">
         <v>8</v>
@@ -58479,7 +58479,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2235" t="n">
-        <v>1.80185329914093</v>
+        <v>1.80185341835022</v>
       </c>
       <c r="H2235" t="s">
         <v>8</v>
@@ -58635,7 +58635,7 @@
         <v>1.99150002002716</v>
       </c>
       <c r="G2241" t="n">
-        <v>1.77379679679871</v>
+        <v>1.773796916008</v>
       </c>
       <c r="H2241" t="s">
         <v>8</v>
@@ -58687,7 +58687,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2243" t="n">
-        <v>1.83926224708557</v>
+        <v>1.83926212787628</v>
       </c>
       <c r="H2243" t="s">
         <v>8</v>
@@ -58713,7 +58713,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G2244" t="n">
-        <v>1.80630683898926</v>
+        <v>1.80630695819855</v>
       </c>
       <c r="H2244" t="s">
         <v>8</v>
@@ -58739,7 +58739,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G2245" t="n">
-        <v>1.89003109931946</v>
+        <v>1.89003121852875</v>
       </c>
       <c r="H2245" t="s">
         <v>8</v>
@@ -58765,7 +58765,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G2246" t="n">
-        <v>1.94970667362213</v>
+        <v>1.94970679283142</v>
       </c>
       <c r="H2246" t="s">
         <v>8</v>
@@ -58817,7 +58817,7 @@
         <v>2.16300010681152</v>
       </c>
       <c r="G2248" t="n">
-        <v>1.92654931545258</v>
+        <v>1.92654919624329</v>
       </c>
       <c r="H2248" t="s">
         <v>8</v>
@@ -58843,7 +58843,7 @@
         <v>2.16700005531311</v>
       </c>
       <c r="G2249" t="n">
-        <v>1.9301118850708</v>
+        <v>1.93011200428009</v>
       </c>
       <c r="H2249" t="s">
         <v>8</v>
@@ -58869,7 +58869,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2250" t="n">
-        <v>1.94525349140167</v>
+        <v>1.94525361061096</v>
       </c>
       <c r="H2250" t="s">
         <v>8</v>
@@ -58895,7 +58895,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2251" t="n">
-        <v>1.97909951210022</v>
+        <v>1.97909939289093</v>
       </c>
       <c r="H2251" t="s">
         <v>8</v>
@@ -58921,7 +58921,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2252" t="n">
-        <v>1.97909951210022</v>
+        <v>1.97909939289093</v>
       </c>
       <c r="H2252" t="s">
         <v>8</v>
@@ -58973,7 +58973,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2254" t="n">
-        <v>2.00314807891846</v>
+        <v>2.00314784049988</v>
       </c>
       <c r="H2254" t="s">
         <v>8</v>
@@ -59025,7 +59025,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2256" t="n">
-        <v>2.06994891166687</v>
+        <v>2.06994915008545</v>
       </c>
       <c r="H2256" t="s">
         <v>8</v>
@@ -59103,7 +59103,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2259" t="n">
-        <v>2.0530264377594</v>
+        <v>2.05302619934082</v>
       </c>
       <c r="H2259" t="s">
         <v>8</v>
@@ -59129,7 +59129,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2260" t="n">
-        <v>2.06371450424194</v>
+        <v>2.06371426582336</v>
       </c>
       <c r="H2260" t="s">
         <v>8</v>
@@ -59155,7 +59155,7 @@
         <v>2.33299994468689</v>
       </c>
       <c r="G2261" t="n">
-        <v>2.077965259552</v>
+        <v>2.07796549797058</v>
       </c>
       <c r="H2261" t="s">
         <v>8</v>
@@ -59181,7 +59181,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2262" t="n">
-        <v>2.10913944244385</v>
+        <v>2.10913920402527</v>
       </c>
       <c r="H2262" t="s">
         <v>8</v>
@@ -59363,7 +59363,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G2269" t="n">
-        <v>2.1652524471283</v>
+        <v>2.16525220870972</v>
       </c>
       <c r="H2269" t="s">
         <v>8</v>
@@ -59493,7 +59493,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G2274" t="n">
-        <v>2.26768112182617</v>
+        <v>2.26768088340759</v>
       </c>
       <c r="H2274" t="s">
         <v>8</v>
@@ -59597,7 +59597,7 @@
         <v>2.48699998855591</v>
       </c>
       <c r="G2278" t="n">
-        <v>2.21513056755066</v>
+        <v>2.21513080596924</v>
       </c>
       <c r="H2278" t="s">
         <v>8</v>
@@ -59675,7 +59675,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G2281" t="n">
-        <v>2.29262018203735</v>
+        <v>2.29261994361877</v>
       </c>
       <c r="H2281" t="s">
         <v>8</v>
@@ -59701,7 +59701,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2282" t="n">
-        <v>2.31577777862549</v>
+        <v>2.31577801704407</v>
       </c>
       <c r="H2282" t="s">
         <v>8</v>
@@ -59779,7 +59779,7 @@
         <v>2.64299988746643</v>
       </c>
       <c r="G2285" t="n">
-        <v>2.35407710075378</v>
+        <v>2.35407733917236</v>
       </c>
       <c r="H2285" t="s">
         <v>8</v>
@@ -59857,7 +59857,7 @@
         <v>2.51099991798401</v>
       </c>
       <c r="G2288" t="n">
-        <v>2.23650717735291</v>
+        <v>2.23650693893433</v>
       </c>
       <c r="H2288" t="s">
         <v>8</v>
@@ -59883,7 +59883,7 @@
         <v>2.5090000629425</v>
       </c>
       <c r="G2289" t="n">
-        <v>2.23472571372986</v>
+        <v>2.23472595214844</v>
       </c>
       <c r="H2289" t="s">
         <v>8</v>
@@ -60039,7 +60039,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G2295" t="n">
-        <v>2.45294308662415</v>
+        <v>2.45294332504272</v>
       </c>
       <c r="H2295" t="s">
         <v>8</v>
@@ -60143,7 +60143,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G2299" t="n">
-        <v>2.31221532821655</v>
+        <v>2.31221508979797</v>
       </c>
       <c r="H2299" t="s">
         <v>8</v>
@@ -60195,7 +60195,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G2301" t="n">
-        <v>2.27658796310425</v>
+        <v>2.27658772468567</v>
       </c>
       <c r="H2301" t="s">
         <v>8</v>
@@ -60221,7 +60221,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G2302" t="n">
-        <v>2.25164890289307</v>
+        <v>2.25164866447449</v>
       </c>
       <c r="H2302" t="s">
         <v>8</v>
@@ -60247,7 +60247,7 @@
         <v>2.51300001144409</v>
       </c>
       <c r="G2303" t="n">
-        <v>2.23828864097595</v>
+        <v>2.23828840255737</v>
       </c>
       <c r="H2303" t="s">
         <v>8</v>
@@ -60299,7 +60299,7 @@
         <v>2.48300004005432</v>
       </c>
       <c r="G2305" t="n">
-        <v>2.21156811714172</v>
+        <v>2.21156787872314</v>
       </c>
       <c r="H2305" t="s">
         <v>8</v>
@@ -60325,7 +60325,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G2306" t="n">
-        <v>2.14832925796509</v>
+        <v>2.14832949638367</v>
       </c>
       <c r="H2306" t="s">
         <v>8</v>
@@ -60351,7 +60351,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2307" t="n">
-        <v>2.12160873413086</v>
+        <v>2.12160897254944</v>
       </c>
       <c r="H2307" t="s">
         <v>8</v>
@@ -60559,7 +60559,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G2315" t="n">
-        <v>2.04411959648132</v>
+        <v>2.04411935806274</v>
       </c>
       <c r="H2315" t="s">
         <v>8</v>
@@ -60611,7 +60611,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G2317" t="n">
-        <v>2.04768204689026</v>
+        <v>2.04768228530884</v>
       </c>
       <c r="H2317" t="s">
         <v>8</v>
@@ -60741,7 +60741,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G2322" t="n">
-        <v>2.05658888816833</v>
+        <v>2.05658912658691</v>
       </c>
       <c r="H2322" t="s">
         <v>8</v>
@@ -60819,7 +60819,7 @@
         <v>2.28099989891052</v>
       </c>
       <c r="G2325" t="n">
-        <v>2.03164958953857</v>
+        <v>2.03164982795715</v>
       </c>
       <c r="H2325" t="s">
         <v>8</v>
@@ -60845,7 +60845,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G2326" t="n">
-        <v>2.06816792488098</v>
+        <v>2.0681676864624</v>
       </c>
       <c r="H2326" t="s">
         <v>8</v>
@@ -60923,7 +60923,7 @@
         <v>2.20300006866455</v>
       </c>
       <c r="G2329" t="n">
-        <v>1.96217656135559</v>
+        <v>1.9621764421463</v>
       </c>
       <c r="H2329" t="s">
         <v>8</v>
@@ -60949,7 +60949,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2330" t="n">
-        <v>2.00314807891846</v>
+        <v>2.00314784049988</v>
       </c>
       <c r="H2330" t="s">
         <v>8</v>
@@ -61001,7 +61001,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2332" t="n">
-        <v>1.91853308677673</v>
+        <v>1.91853296756744</v>
       </c>
       <c r="H2332" t="s">
         <v>8</v>
@@ -61053,7 +61053,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2334" t="n">
-        <v>1.80808818340302</v>
+        <v>1.80808806419373</v>
       </c>
       <c r="H2334" t="s">
         <v>8</v>
@@ -61183,7 +61183,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G2339" t="n">
-        <v>1.85440373420715</v>
+        <v>1.85440385341644</v>
       </c>
       <c r="H2339" t="s">
         <v>8</v>
@@ -61261,7 +61261,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2342" t="n">
-        <v>1.89626586437225</v>
+        <v>1.89626574516296</v>
       </c>
       <c r="H2342" t="s">
         <v>8</v>
@@ -61287,7 +61287,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2343" t="n">
-        <v>1.93278384208679</v>
+        <v>1.93278396129608</v>
       </c>
       <c r="H2343" t="s">
         <v>8</v>
@@ -61313,7 +61313,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2344" t="n">
-        <v>1.95683240890503</v>
+        <v>1.95683228969574</v>
       </c>
       <c r="H2344" t="s">
         <v>8</v>
@@ -61391,7 +61391,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2347" t="n">
-        <v>1.9684112071991</v>
+        <v>1.96841132640839</v>
       </c>
       <c r="H2347" t="s">
         <v>8</v>
@@ -61417,7 +61417,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2348" t="n">
-        <v>1.94525349140167</v>
+        <v>1.94525361061096</v>
       </c>
       <c r="H2348" t="s">
         <v>8</v>
@@ -61469,7 +61469,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G2350" t="n">
-        <v>1.95861351490021</v>
+        <v>1.9586136341095</v>
       </c>
       <c r="H2350" t="s">
         <v>8</v>
@@ -61495,7 +61495,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2351" t="n">
-        <v>1.9336746931076</v>
+        <v>1.93367457389832</v>
       </c>
       <c r="H2351" t="s">
         <v>8</v>
@@ -61573,7 +61573,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G2354" t="n">
-        <v>1.89537525177002</v>
+        <v>1.89537537097931</v>
       </c>
       <c r="H2354" t="s">
         <v>8</v>
@@ -61599,7 +61599,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G2355" t="n">
-        <v>1.72436392307281</v>
+        <v>1.72436380386353</v>
       </c>
       <c r="H2355" t="s">
         <v>8</v>
@@ -61755,7 +61755,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G2361" t="n">
-        <v>1.52128791809082</v>
+        <v>1.52128803730011</v>
       </c>
       <c r="H2361" t="s">
         <v>8</v>
@@ -61781,7 +61781,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G2362" t="n">
-        <v>1.56493151187897</v>
+        <v>1.56493139266968</v>
       </c>
       <c r="H2362" t="s">
         <v>8</v>
@@ -61937,7 +61937,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G2368" t="n">
-        <v>1.749302983284</v>
+        <v>1.74930310249329</v>
       </c>
       <c r="H2368" t="s">
         <v>8</v>
@@ -62015,7 +62015,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2371" t="n">
-        <v>1.82590186595917</v>
+        <v>1.82590174674988</v>
       </c>
       <c r="H2371" t="s">
         <v>8</v>
@@ -62067,7 +62067,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2373" t="n">
-        <v>1.8526223897934</v>
+        <v>1.85262227058411</v>
       </c>
       <c r="H2373" t="s">
         <v>8</v>
@@ -62093,7 +62093,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G2374" t="n">
-        <v>1.83302736282349</v>
+        <v>1.83302748203278</v>
       </c>
       <c r="H2374" t="s">
         <v>8</v>
@@ -62119,7 +62119,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G2375" t="n">
-        <v>1.82768321037292</v>
+        <v>1.82768332958221</v>
       </c>
       <c r="H2375" t="s">
         <v>8</v>
@@ -62145,7 +62145,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G2376" t="n">
-        <v>1.83837127685547</v>
+        <v>1.83837139606476</v>
       </c>
       <c r="H2376" t="s">
         <v>8</v>
@@ -62197,7 +62197,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G2378" t="n">
-        <v>1.93990933895111</v>
+        <v>1.9399094581604</v>
       </c>
       <c r="H2378" t="s">
         <v>8</v>
@@ -69012,6 +69012,32 @@
         <v>4.21799993515015</v>
       </c>
       <c r="H2640" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2641">
+      <c r="A2641" s="1" t="n">
+        <v>46168.2916666667</v>
+      </c>
+      <c r="B2641" t="n">
+        <v>16851538</v>
+      </c>
+      <c r="C2641" t="n">
+        <v>4.34200000762939</v>
+      </c>
+      <c r="D2641" t="n">
+        <v>4.22900009155273</v>
+      </c>
+      <c r="E2641" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="F2641" t="n">
+        <v>4.27600002288818</v>
+      </c>
+      <c r="G2641" t="n">
+        <v>4.27600002288818</v>
+      </c>
+      <c r="H2641" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -69041,6 +69041,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2642">
+      <c r="A2642" s="1" t="n">
+        <v>46169.2916666667</v>
+      </c>
+      <c r="B2642" t="n">
+        <v>34442905</v>
+      </c>
+      <c r="C2642" t="n">
+        <v>4.26200008392334</v>
+      </c>
+      <c r="D2642" t="n">
+        <v>4.0149998664856</v>
+      </c>
+      <c r="E2642" t="n">
+        <v>4.25600004196167</v>
+      </c>
+      <c r="F2642" t="n">
+        <v>4.09600019454956</v>
+      </c>
+      <c r="G2642" t="n">
+        <v>4.09600019454956</v>
+      </c>
+      <c r="H2642" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -447,7 +447,7 @@
         <v>23.2093391418457</v>
       </c>
       <c r="G3" t="n">
-        <v>20.5791053771973</v>
+        <v>20.5791072845459</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>21.9295864105225</v>
       </c>
       <c r="G5" t="n">
-        <v>19.4443855285645</v>
+        <v>19.4443836212158</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>22.1823787689209</v>
       </c>
       <c r="G10" t="n">
-        <v>19.668529510498</v>
+        <v>19.6685276031494</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>20.9184246063232</v>
       </c>
       <c r="G11" t="n">
-        <v>18.5478134155273</v>
+        <v>18.547815322876</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811958312988</v>
+        <v>17.5811977386475</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>13.2778282165527</v>
       </c>
       <c r="G16" t="n">
-        <v>11.773099899292</v>
+        <v>11.7730989456177</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087112426758</v>
+        <v>12.6087121963501</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G21" t="n">
-        <v>12.6977405548096</v>
+        <v>12.6977415084839</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.358302116394</v>
       </c>
       <c r="G22" t="n">
-        <v>12.7311267852783</v>
+        <v>12.7311277389526</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.8813648223877</v>
       </c>
       <c r="G23" t="n">
-        <v>12.3082399368286</v>
+        <v>12.30823802948</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G29" t="n">
-        <v>8.0571117401123</v>
+        <v>8.05711078643799</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393558502197</v>
+        <v>6.74393510818481</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.87747955322266</v>
+        <v>6.87747859954834</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51180982589722</v>
+        <v>7.51181030273438</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243982315063</v>
+        <v>7.91243886947632</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.67679214477539</v>
       </c>
       <c r="G45" t="n">
-        <v>8.58015537261963</v>
+        <v>8.58015632629395</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>10.6884002685547</v>
       </c>
       <c r="G47" t="n">
-        <v>9.47712135314941</v>
+        <v>9.47712230682373</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.07714366912842</v>
+        <v>8.0771427154541</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683395385742</v>
+        <v>8.58683204650879</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.3175220489502</v>
+        <v>8.31752109527588</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G57" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.93628597259521</v>
       </c>
       <c r="G62" t="n">
-        <v>7.92356824874878</v>
+        <v>7.92356872558594</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8.83838844299316</v>
       </c>
       <c r="G63" t="n">
-        <v>7.8367657661438</v>
+        <v>7.83676528930664</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870809555054</v>
+        <v>7.65870714187622</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G65" t="n">
-        <v>7.32262372970581</v>
+        <v>7.32262420654297</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.61341381072998</v>
       </c>
       <c r="G68" t="n">
-        <v>6.75061273574829</v>
+        <v>6.75061225891113</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365732192993</v>
+        <v>7.27365779876709</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G71" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09939956665039</v>
+        <v>8.09940052032471</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G75" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.55128288269043</v>
       </c>
       <c r="G81" t="n">
-        <v>8.46886920928955</v>
+        <v>8.46887016296387</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912178039551</v>
+        <v>8.62912082672119</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G83" t="n">
-        <v>9.68188762664795</v>
+        <v>9.68188858032227</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.2685546875</v>
+        <v>8.26855373382568</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542007446289</v>
+        <v>8.39542102813721</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G96" t="n">
-        <v>8.31974601745605</v>
+        <v>8.31974697113037</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588800430298</v>
+        <v>7.98588752746582</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>8.92875480651855</v>
       </c>
       <c r="G100" t="n">
-        <v>7.9168906211853</v>
+        <v>7.91689109802246</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.14212131500244</v>
       </c>
       <c r="G101" t="n">
-        <v>8.10607814788818</v>
+        <v>8.10607719421387</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.04924392700195</v>
       </c>
       <c r="G108" t="n">
-        <v>8.02372455596924</v>
+        <v>8.02372550964355</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.5261812210083</v>
       </c>
       <c r="G111" t="n">
-        <v>8.44661331176758</v>
+        <v>8.44661235809326</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G113" t="n">
-        <v>8.6736364364624</v>
+        <v>8.67363548278809</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.28018188476562</v>
       </c>
       <c r="G114" t="n">
-        <v>8.22849178314209</v>
+        <v>8.22849273681641</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325277328491</v>
+        <v>7.72325325012207</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660755157471</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G118" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.05933570861816</v>
+        <v>8.05933666229248</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.59193658828735</v>
+        <v>7.5919361114502</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G131" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G132" t="n">
-        <v>7.823410987854</v>
+        <v>7.82341051101685</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.04171371459961</v>
       </c>
       <c r="G133" t="n">
-        <v>8.01704883575439</v>
+        <v>8.01704788208008</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.44083404541016</v>
       </c>
       <c r="G134" t="n">
-        <v>8.37093734741211</v>
+        <v>8.37093830108643</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.71147346496582</v>
+        <v>8.71147441864014</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420448303223</v>
+        <v>9.03420257568359</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G138" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>10.977071762085</v>
       </c>
       <c r="G142" t="n">
-        <v>9.73307800292969</v>
+        <v>9.733078956604</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G144" t="n">
-        <v>9.68856620788574</v>
+        <v>9.68856525421143</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>10.359564781189</v>
       </c>
       <c r="G145" t="n">
-        <v>9.18555164337158</v>
+        <v>9.1855525970459</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427124023438</v>
+        <v>9.78427219390869</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G148" t="n">
-        <v>8.82721138000488</v>
+        <v>8.8272123336792</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G151" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.90019989013672</v>
       </c>
       <c r="G155" t="n">
-        <v>8.77824592590332</v>
+        <v>8.778244972229</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.0056276321411</v>
       </c>
       <c r="G156" t="n">
-        <v>8.87172508239746</v>
+        <v>8.87172603607178</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G157" t="n">
-        <v>8.7760181427002</v>
+        <v>8.77601909637451</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.03642845153809</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G166" t="n">
-        <v>9.21671199798584</v>
+        <v>9.21671295166016</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>10.442400932312</v>
       </c>
       <c r="G168" t="n">
-        <v>9.25900077819824</v>
+        <v>9.25899982452393</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G169" t="n">
-        <v>9.08094310760498</v>
+        <v>9.0809440612793</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G170" t="n">
-        <v>9.16997241973877</v>
+        <v>9.16997337341309</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548778533936</v>
+        <v>9.14548873901367</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>10.457462310791</v>
       </c>
       <c r="G174" t="n">
-        <v>9.27235412597656</v>
+        <v>9.27235507965088</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G175" t="n">
-        <v>9.16997241973877</v>
+        <v>9.16997337341309</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G176" t="n">
-        <v>9.2078104019165</v>
+        <v>9.20780944824219</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G178" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G179" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.44836521148682</v>
       </c>
       <c r="G180" t="n">
-        <v>8.37761497497559</v>
+        <v>8.3776159286499</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.79225015640259</v>
+        <v>7.79225063323975</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.90365314483643</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89463424682617</v>
+        <v>7.89463376998901</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.28771305084229</v>
       </c>
       <c r="G188" t="n">
-        <v>8.23516845703125</v>
+        <v>8.23516941070557</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.73883295059204</v>
+        <v>7.7388334274292</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G192" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G196" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G197" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G199" t="n">
-        <v>8.94294929504395</v>
+        <v>8.94294834136963</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.8139095306396</v>
       </c>
       <c r="G206" t="n">
-        <v>9.58840847015381</v>
+        <v>9.58840751647949</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G207" t="n">
-        <v>9.68856620788574</v>
+        <v>9.68856525421143</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G209" t="n">
-        <v>9.68188762664795</v>
+        <v>9.68188858032227</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G210" t="n">
-        <v>9.31464385986328</v>
+        <v>9.31464290618896</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.03642845153809</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G212" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.34645557403564</v>
+        <v>8.34645462036133</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.2240142822266</v>
       </c>
       <c r="G225" t="n">
-        <v>9.06536293029785</v>
+        <v>9.06536388397217</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G228" t="n">
-        <v>8.6736364364624</v>
+        <v>8.67363548278809</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G230" t="n">
-        <v>8.94517421722412</v>
+        <v>8.9451732635498</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.2215042114258</v>
       </c>
       <c r="G231" t="n">
-        <v>9.06313800811768</v>
+        <v>9.06313705444336</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.71193504333496</v>
       </c>
       <c r="G235" t="n">
-        <v>8.61131477355957</v>
+        <v>8.61131572723389</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.6457271575928</v>
       </c>
       <c r="G236" t="n">
-        <v>9.43928527832031</v>
+        <v>9.439284324646</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>11.6347427368164</v>
       </c>
       <c r="G241" t="n">
-        <v>10.316219329834</v>
+        <v>10.3162183761597</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.9218482971191</v>
       </c>
       <c r="G243" t="n">
-        <v>9.68411445617676</v>
+        <v>9.68411350250244</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>11.2406415939331</v>
       </c>
       <c r="G244" t="n">
-        <v>9.96677875518799</v>
+        <v>9.9667797088623</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.8230066299438</v>
       </c>
       <c r="G245" t="n">
-        <v>10.4831466674805</v>
+        <v>10.4831476211548</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>12.8019819259644</v>
       </c>
       <c r="G250" t="n">
-        <v>11.3511800765991</v>
+        <v>11.3511781692505</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G252" t="n">
-        <v>11.2844076156616</v>
+        <v>11.2844085693359</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076099395752</v>
+        <v>11.9076108932495</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.0319766998291</v>
       </c>
       <c r="G258" t="n">
-        <v>12.4417819976807</v>
+        <v>12.441782951355</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G259" t="n">
-        <v>12.6977405548096</v>
+        <v>12.6977415084839</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195251464844</v>
+        <v>12.4195261001587</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858253479004</v>
+        <v>12.1858243942261</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.3165721893311</v>
       </c>
       <c r="G263" t="n">
-        <v>11.8074531555176</v>
+        <v>11.8074522018433</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>12.7517786026001</v>
       </c>
       <c r="G264" t="n">
-        <v>11.3066654205322</v>
+        <v>11.3066644668579</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>12.2999439239502</v>
       </c>
       <c r="G268" t="n">
-        <v>10.9060344696045</v>
+        <v>10.9060354232788</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.5635137557983</v>
       </c>
       <c r="G269" t="n">
-        <v>11.1397342681885</v>
+        <v>11.1397352218628</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G270" t="n">
-        <v>11.2844076156616</v>
+        <v>11.2844085693359</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619930267334</v>
+        <v>11.1619939804077</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>12.6011667251587</v>
       </c>
       <c r="G272" t="n">
-        <v>11.1731204986572</v>
+        <v>11.1731214523315</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.5007591247559</v>
       </c>
       <c r="G274" t="n">
-        <v>11.0840921401978</v>
+        <v>11.0840930938721</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>13.1283073425293</v>
       </c>
       <c r="G276" t="n">
-        <v>11.6405220031738</v>
+        <v>11.6405229568481</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960083007812</v>
+        <v>11.5960092544556</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G281" t="n">
-        <v>10.2383184432983</v>
+        <v>10.2383193969727</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141492843628</v>
+        <v>10.4141502380371</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.2516717910767</v>
+        <v>10.251672744751</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.39857006073</v>
+        <v>10.3985710144043</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.707537651062</v>
       </c>
       <c r="G287" t="n">
-        <v>10.3807640075684</v>
+        <v>10.3807649612427</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.0213117599487</v>
       </c>
       <c r="G288" t="n">
-        <v>10.6589784622192</v>
+        <v>10.6589794158936</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651847839355</v>
+        <v>10.3651838302612</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>11.6372528076172</v>
       </c>
       <c r="G293" t="n">
-        <v>10.3184432983398</v>
+        <v>10.3184442520142</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10.6984405517578</v>
       </c>
       <c r="G302" t="n">
-        <v>9.48602390289307</v>
+        <v>9.48602485656738</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.5428085327148</v>
       </c>
       <c r="G303" t="n">
-        <v>9.34803009033203</v>
+        <v>9.34802913665771</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10.4675025939941</v>
       </c>
       <c r="G304" t="n">
-        <v>9.28125762939453</v>
+        <v>9.28125858306885</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10.1386680603027</v>
       </c>
       <c r="G307" t="n">
-        <v>8.98968887329102</v>
+        <v>8.9896879196167</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.2491159439087</v>
       </c>
       <c r="G308" t="n">
-        <v>9.08762073516846</v>
+        <v>9.08761978149414</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520519256592</v>
+        <v>8.96520614624023</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.3244218826294</v>
       </c>
       <c r="G311" t="n">
-        <v>9.15439224243164</v>
+        <v>9.15439128875732</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539485931396</v>
+        <v>9.08539390563965</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.1336479187012</v>
       </c>
       <c r="G315" t="n">
-        <v>8.98523712158203</v>
+        <v>8.98523807525635</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10.1562385559082</v>
       </c>
       <c r="G317" t="n">
-        <v>9.00526809692383</v>
+        <v>9.00526714324951</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G320" t="n">
-        <v>9.4615421295166</v>
+        <v>9.46154117584229</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>10.8164196014404</v>
       </c>
       <c r="G321" t="n">
-        <v>9.59063243865967</v>
+        <v>9.59063339233398</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>10.6808700561523</v>
       </c>
       <c r="G322" t="n">
-        <v>9.47044467926025</v>
+        <v>9.47044563293457</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77982044219971</v>
+        <v>9.77981853485107</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G324" t="n">
-        <v>9.49047565460205</v>
+        <v>9.49047470092773</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>10.5227270126343</v>
       </c>
       <c r="G328" t="n">
-        <v>9.33022403717041</v>
+        <v>9.33022308349609</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G330" t="n">
-        <v>9.12990856170654</v>
+        <v>9.12990951538086</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>10.2691984176636</v>
       </c>
       <c r="G331" t="n">
-        <v>9.10542678833008</v>
+        <v>9.10542583465576</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10.0784225463867</v>
       </c>
       <c r="G333" t="n">
-        <v>8.93626976013184</v>
+        <v>8.93627071380615</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.2033576965332</v>
+        <v>9.20335865020752</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G339" t="n">
-        <v>8.94294929504395</v>
+        <v>8.94294834136963</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G344" t="n">
-        <v>8.87840175628662</v>
+        <v>8.87840270996094</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>10.0332403182983</v>
       </c>
       <c r="G345" t="n">
-        <v>8.89620780944824</v>
+        <v>8.89620876312256</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G346" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G347" t="n">
-        <v>8.87840175628662</v>
+        <v>8.87840270996094</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G355" t="n">
-        <v>8.86282253265381</v>
+        <v>8.86282348632812</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.36301803588867</v>
       </c>
       <c r="G359" t="n">
-        <v>8.30194091796875</v>
+        <v>8.30193996429443</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G361" t="n">
-        <v>8.12833499908447</v>
+        <v>8.12833404541016</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.99033880233765</v>
+        <v>7.99033975601196</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G365" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215675354004</v>
+        <v>7.73215579986572</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G368" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G370" t="n">
-        <v>8.0571117401123</v>
+        <v>8.05711078643799</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G374" t="n">
-        <v>7.32262372970581</v>
+        <v>7.32262420654297</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G376" t="n">
-        <v>7.19798278808594</v>
+        <v>7.1979832649231</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.13302421569824</v>
       </c>
       <c r="G377" t="n">
-        <v>7.21133756637573</v>
+        <v>7.21133708953857</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914218902588</v>
+        <v>7.22914266586304</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817197799683</v>
+        <v>7.31817245483398</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G384" t="n">
-        <v>7.19798278808594</v>
+        <v>7.1979832649231</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.68024635314941</v>
       </c>
       <c r="G386" t="n">
-        <v>7.69654512405396</v>
+        <v>7.6965446472168</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G389" t="n">
-        <v>7.32262372970581</v>
+        <v>7.32262420654297</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8.4242057800293</v>
       </c>
       <c r="G390" t="n">
-        <v>7.46952104568481</v>
+        <v>7.46952056884766</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390941619873</v>
+        <v>7.43390846252441</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G393" t="n">
-        <v>7.74551010131836</v>
+        <v>7.7455096244812</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.514573097229</v>
       </c>
       <c r="G398" t="n">
-        <v>7.54964685440063</v>
+        <v>7.54964637756348</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842311859131</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G400" t="n">
-        <v>7.61196708679199</v>
+        <v>7.61196756362915</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G403" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G405" t="n">
-        <v>7.70099544525146</v>
+        <v>7.70099496841431</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G406" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757823944092</v>
+        <v>7.64757966995239</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428731918335</v>
+        <v>7.67428636550903</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G413" t="n">
-        <v>7.50513219833374</v>
+        <v>7.50513172149658</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249744415283</v>
+        <v>7.24249792098999</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701162338257</v>
+        <v>7.28701210021973</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>8.08281993865967</v>
       </c>
       <c r="G419" t="n">
-        <v>7.16682243347168</v>
+        <v>7.16682195663452</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>7.84184217453003</v>
       </c>
       <c r="G421" t="n">
-        <v>6.95315408706665</v>
+        <v>6.95315361022949</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>7.70127105712891</v>
       </c>
       <c r="G423" t="n">
-        <v>6.82851314544678</v>
+        <v>6.82851362228394</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.74645376205444</v>
       </c>
       <c r="G428" t="n">
-        <v>6.86857604980469</v>
+        <v>6.86857557296753</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G432" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.96233081817627</v>
       </c>
       <c r="G433" t="n">
-        <v>7.05998802185059</v>
+        <v>7.05998849868774</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591464996338</v>
+        <v>7.29591417312622</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409908294678</v>
+        <v>7.55409860610962</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.42922687530518</v>
       </c>
       <c r="G438" t="n">
-        <v>7.47397232055664</v>
+        <v>7.4739727973938</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.66538381576538</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G442" t="n">
-        <v>7.70099544525146</v>
+        <v>7.70099496841431</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.10697937011719</v>
       </c>
       <c r="G444" t="n">
-        <v>8.07491683959961</v>
+        <v>8.07491779327393</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.10195827484131</v>
       </c>
       <c r="G445" t="n">
-        <v>8.07046508789062</v>
+        <v>8.07046604156494</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.09693813323975</v>
       </c>
       <c r="G446" t="n">
-        <v>8.06601524353027</v>
+        <v>8.06601428985596</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G447" t="n">
-        <v>8.12833499908447</v>
+        <v>8.12833404541016</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G449" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692302703857</v>
+        <v>7.93692350387573</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504264831543</v>
+        <v>8.15504360198975</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.15216159820557</v>
       </c>
       <c r="G455" t="n">
-        <v>8.1149787902832</v>
+        <v>8.11497974395752</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G457" t="n">
-        <v>7.77221870422363</v>
+        <v>7.77221822738647</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.92122364044189</v>
       </c>
       <c r="G459" t="n">
-        <v>7.91021347045898</v>
+        <v>7.91021299362183</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G460" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.4294581413269</v>
+        <v>7.42945718765259</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>9.04673385620117</v>
       </c>
       <c r="G465" t="n">
-        <v>8.02150058746338</v>
+        <v>8.02149963378906</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.66538381576538</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G468" t="n">
-        <v>7.64312696456909</v>
+        <v>7.64312648773193</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479150772095</v>
+        <v>7.99479198455811</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G470" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.44836521148682</v>
       </c>
       <c r="G479" t="n">
-        <v>8.37761497497559</v>
+        <v>8.3776159286499</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757823944092</v>
+        <v>7.64757966995239</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G482" t="n">
-        <v>7.62532186508179</v>
+        <v>7.62532234191895</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G483" t="n">
-        <v>7.62532186508179</v>
+        <v>7.62532234191895</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G484" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344148635864</v>
+        <v>7.84344244003296</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G491" t="n">
-        <v>7.74551010131836</v>
+        <v>7.7455096244812</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G492" t="n">
-        <v>7.50513219833374</v>
+        <v>7.50513172149658</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G493" t="n">
-        <v>7.64312696456909</v>
+        <v>7.64312648773193</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>8.39910411834717</v>
       </c>
       <c r="G498" t="n">
-        <v>7.44726371765137</v>
+        <v>7.44726324081421</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>8.60996055603027</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63422441482544</v>
+        <v>7.6342248916626</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G500" t="n">
-        <v>7.77221870422363</v>
+        <v>7.77221822738647</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>8.39910411834717</v>
       </c>
       <c r="G502" t="n">
-        <v>7.44726371765137</v>
+        <v>7.44726324081421</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>8.34889984130859</v>
       </c>
       <c r="G503" t="n">
-        <v>7.40274810791016</v>
+        <v>7.40274858474731</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.7499623298645</v>
+        <v>7.74996280670166</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G505" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>9.11199855804443</v>
       </c>
       <c r="G506" t="n">
-        <v>8.07936763763428</v>
+        <v>8.07936859130859</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>9.34795665740967</v>
       </c>
       <c r="G508" t="n">
-        <v>8.28858661651611</v>
+        <v>8.2885856628418</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.50670719146729</v>
+        <v>8.50670623779297</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.5022554397583</v>
+        <v>8.50225639343262</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G517" t="n">
-        <v>8.7604398727417</v>
+        <v>8.76043891906738</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.76464939117432</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65805721282959</v>
+        <v>8.65805625915527</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G522" t="n">
-        <v>9.12990856170654</v>
+        <v>9.12990951538086</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.03642845153809</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833980560303</v>
+        <v>8.83833885192871</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.60399723052979</v>
       </c>
       <c r="G532" t="n">
-        <v>8.51560974121094</v>
+        <v>8.51561069488525</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.4199047088623</v>
+        <v>8.41990375518799</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G537" t="n">
-        <v>7.823410987854</v>
+        <v>7.82341051101685</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660755157471</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G540" t="n">
-        <v>7.61196708679199</v>
+        <v>7.61196756362915</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>8.4543285369873</v>
       </c>
       <c r="G543" t="n">
-        <v>7.49622964859009</v>
+        <v>7.49623012542725</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G548" t="n">
-        <v>7.60083818435669</v>
+        <v>7.60083866119385</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.83587837219238</v>
       </c>
       <c r="G550" t="n">
-        <v>7.83453989028931</v>
+        <v>7.83453893661499</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G553" t="n">
-        <v>7.50068092346191</v>
+        <v>7.50068044662476</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368877410889</v>
+        <v>7.29368829727173</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G557" t="n">
-        <v>7.50068092346191</v>
+        <v>7.50068044662476</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663900375366</v>
+        <v>7.75663948059082</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>8.32379913330078</v>
       </c>
       <c r="G563" t="n">
-        <v>7.38049173355103</v>
+        <v>7.38049268722534</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613433837891</v>
+        <v>7.43613481521606</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585174560547</v>
+        <v>7.25585126876831</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.32128810882568</v>
       </c>
       <c r="G567" t="n">
-        <v>7.37826681137085</v>
+        <v>7.37826633453369</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>8.16063594818115</v>
       </c>
       <c r="G569" t="n">
-        <v>7.23582029342651</v>
+        <v>7.23581981658936</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G573" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.79163789749146</v>
       </c>
       <c r="G576" t="n">
-        <v>6.90863943099976</v>
+        <v>6.9086389541626</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G583" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>8.1079216003418</v>
       </c>
       <c r="G584" t="n">
-        <v>7.18907976150513</v>
+        <v>7.18907928466797</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842311859131</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610383987427</v>
+        <v>7.41610431671143</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766778945923</v>
+        <v>6.99766731262207</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.06022834777832</v>
       </c>
       <c r="G599" t="n">
-        <v>7.14679098129272</v>
+        <v>7.14679145812988</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G600" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G602" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G608" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37539005279541</v>
+        <v>8.37538909912109</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065380096436</v>
+        <v>8.19065475463867</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>8.79822540283203</v>
       </c>
       <c r="G613" t="n">
-        <v>7.80115365982056</v>
+        <v>7.80115413665771</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>9.72448635101318</v>
       </c>
       <c r="G622" t="n">
-        <v>8.62244510650635</v>
+        <v>8.62244415283203</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902694702148</v>
+        <v>8.56902599334717</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G627" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G633" t="n">
-        <v>8.12833499908447</v>
+        <v>8.12833404541016</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G634" t="n">
-        <v>8.12833499908447</v>
+        <v>8.12833404541016</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>9.90019989013672</v>
       </c>
       <c r="G637" t="n">
-        <v>8.77824592590332</v>
+        <v>8.778244972229</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.86254692077637</v>
       </c>
       <c r="G639" t="n">
-        <v>8.74485969543457</v>
+        <v>8.74485874176025</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.71147346496582</v>
+        <v>8.71147441864014</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>10.2767276763916</v>
       </c>
       <c r="G643" t="n">
-        <v>9.11210155487061</v>
+        <v>9.11210250854492</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009822845459</v>
+        <v>9.25009727478027</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.4649925231934</v>
       </c>
       <c r="G647" t="n">
-        <v>9.27903270721436</v>
+        <v>9.27903175354004</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>10.0181789398193</v>
       </c>
       <c r="G648" t="n">
-        <v>8.88285446166992</v>
+        <v>8.88285350799561</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100601196289</v>
+        <v>9.12100505828857</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G654" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.948974609375</v>
+        <v>9.94897556304932</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G660" t="n">
-        <v>9.84659099578857</v>
+        <v>9.84659194946289</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G661" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>11.2331123352051</v>
       </c>
       <c r="G666" t="n">
-        <v>9.96010398864746</v>
+        <v>9.96010303497314</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G667" t="n">
-        <v>9.87107467651367</v>
+        <v>9.87107372283936</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>11.6648645401001</v>
       </c>
       <c r="G674" t="n">
-        <v>10.3429260253906</v>
+        <v>10.3429269790649</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>11.5167636871338</v>
       </c>
       <c r="G675" t="n">
-        <v>10.2116088867188</v>
+        <v>10.2116098403931</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>11.6046199798584</v>
       </c>
       <c r="G676" t="n">
-        <v>10.2895097732544</v>
+        <v>10.2895088195801</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>11.4665603637695</v>
       </c>
       <c r="G680" t="n">
-        <v>10.1670961380005</v>
+        <v>10.1670951843262</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>11.700008392334</v>
       </c>
       <c r="G683" t="n">
-        <v>10.3740873336792</v>
+        <v>10.3740882873535</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99348926544189</v>
+        <v>9.99349021911621</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694797515869</v>
+        <v>10.2694787979126</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.756911277771</v>
+        <v>10.7569122314453</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>13.1232872009277</v>
       </c>
       <c r="G698" t="n">
-        <v>11.6360712051392</v>
+        <v>11.6360721588135</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>13.7558555603027</v>
       </c>
       <c r="G704" t="n">
-        <v>12.1969528198242</v>
+        <v>12.1969537734985</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856666564941</v>
+        <v>12.0856676101685</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>13.032919883728</v>
       </c>
       <c r="G706" t="n">
-        <v>11.555944442749</v>
+        <v>11.5559453964233</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395774841309</v>
+        <v>11.0395784378052</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>12.7015752792358</v>
       </c>
       <c r="G713" t="n">
-        <v>11.2621507644653</v>
+        <v>11.262149810791</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>12.3325757980347</v>
       </c>
       <c r="G714" t="n">
-        <v>10.9349679946899</v>
+        <v>10.9349689483643</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364080429077</v>
+        <v>10.4364070892334</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G719" t="n">
-        <v>10.5499200820923</v>
+        <v>10.549919128418</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G724" t="n">
-        <v>10.76136302948</v>
+        <v>10.7613620758057</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G728" t="n">
-        <v>10.1604175567627</v>
+        <v>10.160418510437</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006381988525</v>
+        <v>10.3006391525269</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>11.1377248764038</v>
       </c>
       <c r="G732" t="n">
-        <v>9.87552547454834</v>
+        <v>9.87552642822266</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G737" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081058502197</v>
+        <v>8.29081249237061</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219253540039</v>
+        <v>8.46219158172607</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G744" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G752" t="n">
-        <v>8.25519943237305</v>
+        <v>8.25520038604736</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466474533081</v>
+        <v>7.91466617584229</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>8.25602340698242</v>
       </c>
       <c r="G758" t="n">
-        <v>7.32039737701416</v>
+        <v>7.32039785385132</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G759" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873378753662</v>
+        <v>6.96873331069946</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>8.37400245666504</v>
       </c>
       <c r="G765" t="n">
-        <v>7.42500638961792</v>
+        <v>7.42500686645508</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G772" t="n">
-        <v>8.25519943237305</v>
+        <v>8.25520038604736</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096927642822</v>
+        <v>8.39096832275391</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>9.71193504333496</v>
       </c>
       <c r="G780" t="n">
-        <v>8.61131477355957</v>
+        <v>8.61131572723389</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G781" t="n">
-        <v>8.82721138000488</v>
+        <v>8.8272123336792</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G782" t="n">
-        <v>8.86282253265381</v>
+        <v>8.86282348632812</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G783" t="n">
-        <v>8.94517421722412</v>
+        <v>8.9451732635498</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>10.2817487716675</v>
       </c>
       <c r="G786" t="n">
-        <v>9.11655426025391</v>
+        <v>9.11655521392822</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>9.79477119445801</v>
       </c>
       <c r="G790" t="n">
-        <v>8.68476390838623</v>
+        <v>8.68476486206055</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>9.75711917877197</v>
       </c>
       <c r="G791" t="n">
-        <v>8.6513786315918</v>
+        <v>8.65137958526611</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G792" t="n">
-        <v>8.82721138000488</v>
+        <v>8.8272123336792</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G795" t="n">
-        <v>9.08094310760498</v>
+        <v>9.0809440612793</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>10.7963380813599</v>
       </c>
       <c r="G797" t="n">
-        <v>9.57282638549805</v>
+        <v>9.57282733917236</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G799" t="n">
-        <v>9.41480159759521</v>
+        <v>9.41480255126953</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G804" t="n">
-        <v>9.69746685028076</v>
+        <v>9.69746780395508</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G805" t="n">
-        <v>10.1604175567627</v>
+        <v>10.160418510437</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232891082764</v>
+        <v>9.96232986450195</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>11.5167636871338</v>
       </c>
       <c r="G807" t="n">
-        <v>10.2116088867188</v>
+        <v>10.2116098403931</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496055603027</v>
+        <v>10.3496036529541</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.2572708129883</v>
       </c>
       <c r="G814" t="n">
-        <v>10.8681983947754</v>
+        <v>10.8681974411011</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>12.1091690063477</v>
       </c>
       <c r="G816" t="n">
-        <v>10.7368803024292</v>
+        <v>10.7368793487549</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.3350868225098</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9371957778931</v>
+        <v>10.9371948242188</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>11.5970897674561</v>
       </c>
       <c r="G821" t="n">
-        <v>10.2828321456909</v>
+        <v>10.2828330993652</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147802352905</v>
+        <v>10.8147811889648</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G830" t="n">
-        <v>10.76136302948</v>
+        <v>10.7613620758057</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295736312866</v>
+        <v>10.3295726776123</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>11.5343351364136</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2271900177002</v>
+        <v>10.2271890640259</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>12.0564546585083</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6901397705078</v>
+        <v>10.6901388168335</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G842" t="n">
-        <v>10.5499200820923</v>
+        <v>10.549919128418</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G845" t="n">
-        <v>10.2383184432983</v>
+        <v>10.2383193969727</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>11.3385400772095</v>
       </c>
       <c r="G846" t="n">
-        <v>10.0535831451416</v>
+        <v>10.0535840988159</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>10.977071762085</v>
       </c>
       <c r="G848" t="n">
-        <v>9.73307800292969</v>
+        <v>9.733078956604</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G851" t="n">
-        <v>9.33912658691406</v>
+        <v>9.33912754058838</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>10.1411781311035</v>
       </c>
       <c r="G852" t="n">
-        <v>8.99191379547119</v>
+        <v>8.99191474914551</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>10.203932762146</v>
       </c>
       <c r="G854" t="n">
-        <v>9.04755783081055</v>
+        <v>9.04755687713623</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G855" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>10.4072589874268</v>
       </c>
       <c r="G856" t="n">
-        <v>9.22784233093262</v>
+        <v>9.22784042358398</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>10.5101757049561</v>
       </c>
       <c r="G860" t="n">
-        <v>9.31909561157227</v>
+        <v>9.31909465789795</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G861" t="n">
-        <v>9.25232315063477</v>
+        <v>9.25232410430908</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G863" t="n">
-        <v>8.7760181427002</v>
+        <v>8.77601909637451</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G864" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G867" t="n">
-        <v>8.7604398727417</v>
+        <v>8.76043891906738</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>9.62156772613525</v>
       </c>
       <c r="G868" t="n">
-        <v>8.53118896484375</v>
+        <v>8.53118991851807</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G869" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G871" t="n">
-        <v>9.07203960418701</v>
+        <v>9.07204151153564</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>10.768726348877</v>
       </c>
       <c r="G874" t="n">
-        <v>9.5483455657959</v>
+        <v>9.54834461212158</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395671844482</v>
+        <v>9.58395576477051</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G877" t="n">
-        <v>9.33912658691406</v>
+        <v>9.33912754058838</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G879" t="n">
-        <v>9.21671199798584</v>
+        <v>9.21671295166016</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>11.0699491500854</v>
       </c>
       <c r="G883" t="n">
-        <v>9.81543159484863</v>
+        <v>9.81543064117432</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079208374023</v>
+        <v>9.69079113006592</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G885" t="n">
-        <v>9.49047565460205</v>
+        <v>9.49047470092773</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>10.9218482971191</v>
       </c>
       <c r="G886" t="n">
-        <v>9.68411445617676</v>
+        <v>9.68411350250244</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>10.9820928573608</v>
       </c>
       <c r="G888" t="n">
-        <v>9.73753070831299</v>
+        <v>9.7375316619873</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G890" t="n">
-        <v>9.69746685028076</v>
+        <v>9.69746780395508</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.948974609375</v>
+        <v>9.94897556304932</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>11.3987846374512</v>
       </c>
       <c r="G898" t="n">
-        <v>10.1070003509521</v>
+        <v>10.1070013046265</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>11.4715795516968</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1715459823608</v>
+        <v>10.1715469360352</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304798126221</v>
+        <v>9.71304893493652</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>11.4941720962524</v>
       </c>
       <c r="G907" t="n">
-        <v>10.1915788650513</v>
+        <v>10.191577911377</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>11.5845394134521</v>
       </c>
       <c r="G908" t="n">
-        <v>10.2717046737671</v>
+        <v>10.2717037200928</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794006347656</v>
+        <v>9.99794101715088</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>10.7411136627197</v>
       </c>
       <c r="G913" t="n">
-        <v>9.5238618850708</v>
+        <v>9.52386093139648</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G914" t="n">
-        <v>9.2078104019165</v>
+        <v>9.20780944824219</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>10.4248304367065</v>
       </c>
       <c r="G915" t="n">
-        <v>9.24342155456543</v>
+        <v>9.24342060089111</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>10.3721160888672</v>
       </c>
       <c r="G917" t="n">
-        <v>9.19668006896973</v>
+        <v>9.19668102264404</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G918" t="n">
-        <v>9.12545776367188</v>
+        <v>9.12545871734619</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G919" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G920" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.95185089111328</v>
+        <v>8.9518518447876</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>10.4474220275879</v>
       </c>
       <c r="G925" t="n">
-        <v>9.26345348358154</v>
+        <v>9.26345252990723</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G926" t="n">
-        <v>9.31464385986328</v>
+        <v>9.31464290618896</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G929" t="n">
-        <v>9.41480159759521</v>
+        <v>9.41480255126953</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>11.4665603637695</v>
       </c>
       <c r="G939" t="n">
-        <v>10.1670961380005</v>
+        <v>10.1670951843262</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.104775428772</v>
+        <v>10.1047735214233</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136770248413</v>
+        <v>10.1136779785156</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403865814209</v>
+        <v>10.1403856277466</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230537414551</v>
+        <v>10.4230527877808</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>11.1854181289673</v>
       </c>
       <c r="G945" t="n">
-        <v>9.91781425476074</v>
+        <v>9.91781520843506</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G946" t="n">
-        <v>9.87107467651367</v>
+        <v>9.87107372283936</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G947" t="n">
-        <v>9.84659099578857</v>
+        <v>9.84659194946289</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>10.0683822631836</v>
       </c>
       <c r="G955" t="n">
-        <v>8.92736911773682</v>
+        <v>8.9273681640625</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>10.0332403182983</v>
       </c>
       <c r="G956" t="n">
-        <v>8.89620780944824</v>
+        <v>8.89620876312256</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>10.1612596511841</v>
       </c>
       <c r="G960" t="n">
-        <v>9.00971984863281</v>
+        <v>9.00972080230713</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G961" t="n">
-        <v>9.16997241973877</v>
+        <v>9.16997337341309</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>10.3219118118286</v>
       </c>
       <c r="G975" t="n">
-        <v>9.15216541290283</v>
+        <v>9.15216636657715</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.03642845153809</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812492370605</v>
+        <v>9.40812397003174</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>10.8164196014404</v>
       </c>
       <c r="G993" t="n">
-        <v>9.59063243865967</v>
+        <v>9.59063339233398</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>10.7135019302368</v>
       </c>
       <c r="G996" t="n">
-        <v>9.4993782043457</v>
+        <v>9.49937915802002</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G998" t="n">
-        <v>9.07203960418701</v>
+        <v>9.07204151153564</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.25232315063477</v>
+        <v>9.25232410430908</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.21671199798584</v>
+        <v>9.21671295166016</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467578887939</v>
+        <v>9.33467674255371</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.5616979598999</v>
+        <v>9.56169891357422</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>11.1126232147217</v>
       </c>
       <c r="G1029" t="n">
-        <v>9.85326862335205</v>
+        <v>9.85326957702637</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G1030" t="n">
-        <v>9.4615421295166</v>
+        <v>9.46154117584229</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G1032" t="n">
-        <v>9.12545776367188</v>
+        <v>9.12545871734619</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.31974601745605</v>
+        <v>8.31974697113037</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.34645557403564</v>
+        <v>8.34645462036133</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>9.41573238372803</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.34868049621582</v>
+        <v>8.34868144989014</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>9.51362991333008</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.4354829788208</v>
+        <v>8.43548393249512</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>9.42577266693115</v>
       </c>
       <c r="G1052" t="n">
-        <v>8.35758399963379</v>
+        <v>8.35758304595947</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657657623291</v>
+        <v>7.71657609939575</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754774093628</v>
+        <v>7.62754726409912</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.60083818435669</v>
+        <v>7.60083866119385</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585174560547</v>
+        <v>7.25585126876831</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.95000410079956</v>
+        <v>4.9500036239624</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.95000410079956</v>
+        <v>4.9500036239624</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.95009994506836</v>
       </c>
       <c r="G1068" t="n">
-        <v>4.38912296295166</v>
+        <v>4.3891224861145</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>5.18605804443359</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.59834003448486</v>
+        <v>4.59834051132202</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342130661011</v>
+        <v>5.00342178344727</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.88991022109985</v>
+        <v>4.88990926742554</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>5.85627889633179</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.19260787963867</v>
+        <v>5.19260740280151</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>5.89393186569214</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.22599363327026</v>
+        <v>5.22599315643311</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>5.95919704437256</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.28386259078979</v>
+        <v>5.28386211395264</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.0219521522522</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.33950519561768</v>
+        <v>5.33950567245483</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>5.9014630317688</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.23267126083374</v>
+        <v>5.23267078399658</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.29276561737061</v>
+        <v>5.29276514053345</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.95445537567139</v>
+        <v>4.95445489883423</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>5.67303514480591</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.03013038635254</v>
+        <v>5.03012990951538</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>5.55505609512329</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.92552137374878</v>
+        <v>4.92552089691162</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928503036499</v>
+        <v>5.19928550720215</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041393280029</v>
+        <v>5.21041345596313</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>5.73328018188477</v>
       </c>
       <c r="G1100" t="n">
-        <v>5.08354806900024</v>
+        <v>5.08354759216309</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>5.79101419448853</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.1347393989563</v>
+        <v>5.13473892211914</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>5.62032079696655</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.98338937759399</v>
+        <v>4.98338985443115</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470794677734</v>
+        <v>5.11470746994019</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248207092285</v>
+        <v>5.11248159408569</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.92329549789429</v>
+        <v>4.92329597473145</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -69064,6 +69064,32 @@
         <v>4.09600019454956</v>
       </c>
       <c r="H2642" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2643">
+      <c r="A2643" s="1" t="n">
+        <v>46170.2916666667</v>
+      </c>
+      <c r="B2643" t="n">
+        <v>25078079</v>
+      </c>
+      <c r="C2643" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="D2643" t="n">
+        <v>4.09000015258789</v>
+      </c>
+      <c r="E2643" t="n">
+        <v>4.1269998550415</v>
+      </c>
+      <c r="F2643" t="n">
+        <v>4.16699981689453</v>
+      </c>
+      <c r="G2643" t="n">
+        <v>4.16699981689453</v>
+      </c>
+      <c r="H2643" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -447,7 +447,7 @@
         <v>23.2093391418457</v>
       </c>
       <c r="G3" t="n">
-        <v>20.5791072845459</v>
+        <v>20.5791053771973</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>21.9295864105225</v>
       </c>
       <c r="G5" t="n">
-        <v>19.4443836212158</v>
+        <v>19.4443855285645</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>22.1823787689209</v>
       </c>
       <c r="G10" t="n">
-        <v>19.6685276031494</v>
+        <v>19.668529510498</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>20.9184246063232</v>
       </c>
       <c r="G11" t="n">
-        <v>18.547815322876</v>
+        <v>18.5478134155273</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811977386475</v>
+        <v>17.5811958312988</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>13.2778282165527</v>
       </c>
       <c r="G16" t="n">
-        <v>11.7730989456177</v>
+        <v>11.773099899292</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087121963501</v>
+        <v>12.6087112426758</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G21" t="n">
-        <v>12.6977415084839</v>
+        <v>12.6977405548096</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.358302116394</v>
       </c>
       <c r="G22" t="n">
-        <v>12.7311277389526</v>
+        <v>12.7311267852783</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.8813648223877</v>
       </c>
       <c r="G23" t="n">
-        <v>12.30823802948</v>
+        <v>12.3082399368286</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617107391357</v>
+        <v>8.16617202758789</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G29" t="n">
-        <v>8.05711078643799</v>
+        <v>8.0571117401123</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393510818481</v>
+        <v>6.74393558502197</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.87747859954834</v>
+        <v>6.87747955322266</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51181030273438</v>
+        <v>7.51180982589722</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243886947632</v>
+        <v>7.91243982315063</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.67679214477539</v>
       </c>
       <c r="G45" t="n">
-        <v>8.58015632629395</v>
+        <v>8.58015537261963</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>10.6884002685547</v>
       </c>
       <c r="G47" t="n">
-        <v>9.47712230682373</v>
+        <v>9.47712135314941</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.0771427154541</v>
+        <v>8.07714366912842</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683204650879</v>
+        <v>8.58683395385742</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.31752109527588</v>
+        <v>8.3175220489502</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G57" t="n">
-        <v>8.15726852416992</v>
+        <v>8.15726947784424</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.93628597259521</v>
       </c>
       <c r="G62" t="n">
-        <v>7.92356872558594</v>
+        <v>7.92356824874878</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8.83838844299316</v>
       </c>
       <c r="G63" t="n">
-        <v>7.83676528930664</v>
+        <v>7.8367657661438</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870714187622</v>
+        <v>7.65870809555054</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G65" t="n">
-        <v>7.32262420654297</v>
+        <v>7.32262372970581</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.61341381072998</v>
       </c>
       <c r="G68" t="n">
-        <v>6.75061225891113</v>
+        <v>6.75061273574829</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365779876709</v>
+        <v>7.27365732192993</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G71" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09940052032471</v>
+        <v>8.09939956665039</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G75" t="n">
-        <v>8.27523231506348</v>
+        <v>8.27523136138916</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.55128288269043</v>
       </c>
       <c r="G81" t="n">
-        <v>8.46887016296387</v>
+        <v>8.46886920928955</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912082672119</v>
+        <v>8.62912178039551</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G83" t="n">
-        <v>9.68188858032227</v>
+        <v>9.68188762664795</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.26855373382568</v>
+        <v>8.2685546875</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542102813721</v>
+        <v>8.39542007446289</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G96" t="n">
-        <v>8.31974697113037</v>
+        <v>8.31974601745605</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588752746582</v>
+        <v>7.98588800430298</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>8.92875480651855</v>
       </c>
       <c r="G100" t="n">
-        <v>7.91689109802246</v>
+        <v>7.9168906211853</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.14212131500244</v>
       </c>
       <c r="G101" t="n">
-        <v>8.10607719421387</v>
+        <v>8.10607814788818</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.04924392700195</v>
       </c>
       <c r="G108" t="n">
-        <v>8.02372550964355</v>
+        <v>8.02372455596924</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.5261812210083</v>
       </c>
       <c r="G111" t="n">
-        <v>8.44661235809326</v>
+        <v>8.44661331176758</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G113" t="n">
-        <v>8.67363548278809</v>
+        <v>8.6736364364624</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.28018188476562</v>
       </c>
       <c r="G114" t="n">
-        <v>8.22849273681641</v>
+        <v>8.22849178314209</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325325012207</v>
+        <v>7.72325277328491</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660707473755</v>
+        <v>7.73660755157471</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G118" t="n">
-        <v>7.78112173080444</v>
+        <v>7.78112125396729</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.05933666229248</v>
+        <v>8.05933570861816</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.5919361114502</v>
+        <v>7.59193658828735</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G131" t="n">
-        <v>8.15726852416992</v>
+        <v>8.15726947784424</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G132" t="n">
-        <v>7.82341051101685</v>
+        <v>7.823410987854</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.04171371459961</v>
       </c>
       <c r="G133" t="n">
-        <v>8.01704788208008</v>
+        <v>8.01704883575439</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.44083404541016</v>
       </c>
       <c r="G134" t="n">
-        <v>8.37093830108643</v>
+        <v>8.37093734741211</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.71147441864014</v>
+        <v>8.71147346496582</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420257568359</v>
+        <v>9.03420448303223</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G138" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>10.977071762085</v>
       </c>
       <c r="G142" t="n">
-        <v>9.733078956604</v>
+        <v>9.73307800292969</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G144" t="n">
-        <v>9.68856525421143</v>
+        <v>9.68856620788574</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>10.359564781189</v>
       </c>
       <c r="G145" t="n">
-        <v>9.1855525970459</v>
+        <v>9.18555164337158</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427219390869</v>
+        <v>9.78427124023438</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G148" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G151" t="n">
-        <v>8.27523231506348</v>
+        <v>8.27523136138916</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.90019989013672</v>
       </c>
       <c r="G155" t="n">
-        <v>8.778244972229</v>
+        <v>8.77824592590332</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.0056276321411</v>
       </c>
       <c r="G156" t="n">
-        <v>8.87172603607178</v>
+        <v>8.87172508239746</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G157" t="n">
-        <v>8.77601909637451</v>
+        <v>8.7760181427002</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.03643035888672</v>
+        <v>9.03642845153809</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G166" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>10.442400932312</v>
       </c>
       <c r="G168" t="n">
-        <v>9.25899982452393</v>
+        <v>9.25900077819824</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G169" t="n">
-        <v>9.0809440612793</v>
+        <v>9.08094310760498</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G170" t="n">
-        <v>9.16997337341309</v>
+        <v>9.16997241973877</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548873901367</v>
+        <v>9.14548778533936</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>10.457462310791</v>
       </c>
       <c r="G174" t="n">
-        <v>9.27235507965088</v>
+        <v>9.27235412597656</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G175" t="n">
-        <v>9.16997337341309</v>
+        <v>9.16997241973877</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G176" t="n">
-        <v>9.20780944824219</v>
+        <v>9.2078104019165</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G178" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G179" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.44836521148682</v>
       </c>
       <c r="G180" t="n">
-        <v>8.3776159286499</v>
+        <v>8.37761497497559</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.79225063323975</v>
+        <v>7.79225015640259</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.90365314483643</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89463376998901</v>
+        <v>7.89463424682617</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.28771305084229</v>
       </c>
       <c r="G188" t="n">
-        <v>8.23516941070557</v>
+        <v>8.23516845703125</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.7388334274292</v>
+        <v>7.73883295059204</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G192" t="n">
-        <v>8.15726852416992</v>
+        <v>8.15726947784424</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G196" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G197" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G199" t="n">
-        <v>8.94294834136963</v>
+        <v>8.94294929504395</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.8139095306396</v>
       </c>
       <c r="G206" t="n">
-        <v>9.58840751647949</v>
+        <v>9.58840847015381</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G207" t="n">
-        <v>9.68856525421143</v>
+        <v>9.68856620788574</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G209" t="n">
-        <v>9.68188858032227</v>
+        <v>9.68188762664795</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G210" t="n">
-        <v>9.31464290618896</v>
+        <v>9.31464385986328</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.03643035888672</v>
+        <v>9.03642845153809</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G212" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.34645462036133</v>
+        <v>8.34645557403564</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.2240142822266</v>
       </c>
       <c r="G225" t="n">
-        <v>9.06536388397217</v>
+        <v>9.06536293029785</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G228" t="n">
-        <v>8.67363548278809</v>
+        <v>8.6736364364624</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G230" t="n">
-        <v>8.9451732635498</v>
+        <v>8.94517421722412</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.2215042114258</v>
       </c>
       <c r="G231" t="n">
-        <v>9.06313705444336</v>
+        <v>9.06313800811768</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.71193504333496</v>
       </c>
       <c r="G235" t="n">
-        <v>8.61131572723389</v>
+        <v>8.61131477355957</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.6457271575928</v>
       </c>
       <c r="G236" t="n">
-        <v>9.439284324646</v>
+        <v>9.43928527832031</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>11.6347427368164</v>
       </c>
       <c r="G241" t="n">
-        <v>10.3162183761597</v>
+        <v>10.316219329834</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.9218482971191</v>
       </c>
       <c r="G243" t="n">
-        <v>9.68411350250244</v>
+        <v>9.68411445617676</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>11.2406415939331</v>
       </c>
       <c r="G244" t="n">
-        <v>9.9667797088623</v>
+        <v>9.96677875518799</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.8230066299438</v>
       </c>
       <c r="G245" t="n">
-        <v>10.4831476211548</v>
+        <v>10.4831466674805</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>12.8019819259644</v>
       </c>
       <c r="G250" t="n">
-        <v>11.3511781692505</v>
+        <v>11.3511800765991</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G252" t="n">
-        <v>11.2844085693359</v>
+        <v>11.2844076156616</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076108932495</v>
+        <v>11.9076099395752</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.0319766998291</v>
       </c>
       <c r="G258" t="n">
-        <v>12.441782951355</v>
+        <v>12.4417819976807</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G259" t="n">
-        <v>12.6977415084839</v>
+        <v>12.6977405548096</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195261001587</v>
+        <v>12.4195251464844</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858243942261</v>
+        <v>12.1858253479004</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.3165721893311</v>
       </c>
       <c r="G263" t="n">
-        <v>11.8074522018433</v>
+        <v>11.8074531555176</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>12.7517786026001</v>
       </c>
       <c r="G264" t="n">
-        <v>11.3066644668579</v>
+        <v>11.3066654205322</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>12.2999439239502</v>
       </c>
       <c r="G268" t="n">
-        <v>10.9060354232788</v>
+        <v>10.9060344696045</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.5635137557983</v>
       </c>
       <c r="G269" t="n">
-        <v>11.1397352218628</v>
+        <v>11.1397342681885</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G270" t="n">
-        <v>11.2844085693359</v>
+        <v>11.2844076156616</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619939804077</v>
+        <v>11.1619930267334</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>12.6011667251587</v>
       </c>
       <c r="G272" t="n">
-        <v>11.1731214523315</v>
+        <v>11.1731204986572</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.5007591247559</v>
       </c>
       <c r="G274" t="n">
-        <v>11.0840930938721</v>
+        <v>11.0840921401978</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>13.1283073425293</v>
       </c>
       <c r="G276" t="n">
-        <v>11.6405229568481</v>
+        <v>11.6405220031738</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960092544556</v>
+        <v>11.5960083007812</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G281" t="n">
-        <v>10.2383193969727</v>
+        <v>10.2383184432983</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141502380371</v>
+        <v>10.4141492843628</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.251672744751</v>
+        <v>10.2516717910767</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.3985710144043</v>
+        <v>10.39857006073</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.707537651062</v>
       </c>
       <c r="G287" t="n">
-        <v>10.3807649612427</v>
+        <v>10.3807640075684</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.0213117599487</v>
       </c>
       <c r="G288" t="n">
-        <v>10.6589794158936</v>
+        <v>10.6589784622192</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651838302612</v>
+        <v>10.3651847839355</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>11.6372528076172</v>
       </c>
       <c r="G293" t="n">
-        <v>10.3184442520142</v>
+        <v>10.3184432983398</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10.6984405517578</v>
       </c>
       <c r="G302" t="n">
-        <v>9.48602485656738</v>
+        <v>9.48602390289307</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.5428085327148</v>
       </c>
       <c r="G303" t="n">
-        <v>9.34802913665771</v>
+        <v>9.34803009033203</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10.4675025939941</v>
       </c>
       <c r="G304" t="n">
-        <v>9.28125858306885</v>
+        <v>9.28125762939453</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10.1386680603027</v>
       </c>
       <c r="G307" t="n">
-        <v>8.9896879196167</v>
+        <v>8.98968887329102</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.2491159439087</v>
       </c>
       <c r="G308" t="n">
-        <v>9.08761978149414</v>
+        <v>9.08762073516846</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520614624023</v>
+        <v>8.96520519256592</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.3244218826294</v>
       </c>
       <c r="G311" t="n">
-        <v>9.15439128875732</v>
+        <v>9.15439224243164</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539390563965</v>
+        <v>9.08539485931396</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.1336479187012</v>
       </c>
       <c r="G315" t="n">
-        <v>8.98523807525635</v>
+        <v>8.98523712158203</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10.1562385559082</v>
       </c>
       <c r="G317" t="n">
-        <v>9.00526714324951</v>
+        <v>9.00526809692383</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G320" t="n">
-        <v>9.46154117584229</v>
+        <v>9.4615421295166</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>10.8164196014404</v>
       </c>
       <c r="G321" t="n">
-        <v>9.59063339233398</v>
+        <v>9.59063243865967</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>10.6808700561523</v>
       </c>
       <c r="G322" t="n">
-        <v>9.47044563293457</v>
+        <v>9.47044467926025</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77981853485107</v>
+        <v>9.77982044219971</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G324" t="n">
-        <v>9.49047470092773</v>
+        <v>9.49047565460205</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>10.5227270126343</v>
       </c>
       <c r="G328" t="n">
-        <v>9.33022308349609</v>
+        <v>9.33022403717041</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G330" t="n">
-        <v>9.12990951538086</v>
+        <v>9.12990856170654</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>10.2691984176636</v>
       </c>
       <c r="G331" t="n">
-        <v>9.10542583465576</v>
+        <v>9.10542678833008</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10.0784225463867</v>
       </c>
       <c r="G333" t="n">
-        <v>8.93627071380615</v>
+        <v>8.93626976013184</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.20335865020752</v>
+        <v>9.2033576965332</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G339" t="n">
-        <v>8.94294834136963</v>
+        <v>8.94294929504395</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G344" t="n">
-        <v>8.87840270996094</v>
+        <v>8.87840175628662</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>10.0332403182983</v>
       </c>
       <c r="G345" t="n">
-        <v>8.89620876312256</v>
+        <v>8.89620780944824</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G346" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G347" t="n">
-        <v>8.87840270996094</v>
+        <v>8.87840175628662</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G355" t="n">
-        <v>8.86282348632812</v>
+        <v>8.86282253265381</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.36301803588867</v>
       </c>
       <c r="G359" t="n">
-        <v>8.30193996429443</v>
+        <v>8.30194091796875</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G361" t="n">
-        <v>8.12833404541016</v>
+        <v>8.12833499908447</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.99033975601196</v>
+        <v>7.99033880233765</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G365" t="n">
-        <v>7.78112173080444</v>
+        <v>7.78112125396729</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215579986572</v>
+        <v>7.73215675354004</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G368" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G370" t="n">
-        <v>8.05711078643799</v>
+        <v>8.0571117401123</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G374" t="n">
-        <v>7.32262420654297</v>
+        <v>7.32262372970581</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G376" t="n">
-        <v>7.1979832649231</v>
+        <v>7.19798278808594</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.13302421569824</v>
       </c>
       <c r="G377" t="n">
-        <v>7.21133708953857</v>
+        <v>7.21133756637573</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914266586304</v>
+        <v>7.22914218902588</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817245483398</v>
+        <v>7.31817197799683</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G384" t="n">
-        <v>7.1979832649231</v>
+        <v>7.19798278808594</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.68024635314941</v>
       </c>
       <c r="G386" t="n">
-        <v>7.6965446472168</v>
+        <v>7.69654512405396</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G389" t="n">
-        <v>7.32262420654297</v>
+        <v>7.32262372970581</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8.4242057800293</v>
       </c>
       <c r="G390" t="n">
-        <v>7.46952056884766</v>
+        <v>7.46952104568481</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390846252441</v>
+        <v>7.43390941619873</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G393" t="n">
-        <v>7.7455096244812</v>
+        <v>7.74551010131836</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.514573097229</v>
       </c>
       <c r="G398" t="n">
-        <v>7.54964637756348</v>
+        <v>7.54964685440063</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842311859131</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G400" t="n">
-        <v>7.61196756362915</v>
+        <v>7.61196708679199</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G403" t="n">
-        <v>7.59416151046753</v>
+        <v>7.59416103363037</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G405" t="n">
-        <v>7.70099496841431</v>
+        <v>7.70099544525146</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G406" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757966995239</v>
+        <v>7.64757823944092</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428636550903</v>
+        <v>7.67428731918335</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G413" t="n">
-        <v>7.50513172149658</v>
+        <v>7.50513219833374</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249792098999</v>
+        <v>7.24249744415283</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701210021973</v>
+        <v>7.28701162338257</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>8.08281993865967</v>
       </c>
       <c r="G419" t="n">
-        <v>7.16682195663452</v>
+        <v>7.16682243347168</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>7.84184217453003</v>
       </c>
       <c r="G421" t="n">
-        <v>6.95315361022949</v>
+        <v>6.95315408706665</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>7.70127105712891</v>
       </c>
       <c r="G423" t="n">
-        <v>6.82851362228394</v>
+        <v>6.82851314544678</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.74645376205444</v>
       </c>
       <c r="G428" t="n">
-        <v>6.86857557296753</v>
+        <v>6.86857604980469</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G432" t="n">
-        <v>7.22469091415405</v>
+        <v>7.22469139099121</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.96233081817627</v>
       </c>
       <c r="G433" t="n">
-        <v>7.05998849868774</v>
+        <v>7.05998802185059</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591417312622</v>
+        <v>7.29591464996338</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409860610962</v>
+        <v>7.55409908294678</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.42922687530518</v>
       </c>
       <c r="G438" t="n">
-        <v>7.4739727973938</v>
+        <v>7.47397232055664</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538381576538</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G442" t="n">
-        <v>7.70099496841431</v>
+        <v>7.70099544525146</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.10697937011719</v>
       </c>
       <c r="G444" t="n">
-        <v>8.07491779327393</v>
+        <v>8.07491683959961</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.10195827484131</v>
       </c>
       <c r="G445" t="n">
-        <v>8.07046604156494</v>
+        <v>8.07046508789062</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.09693813323975</v>
       </c>
       <c r="G446" t="n">
-        <v>8.06601428985596</v>
+        <v>8.06601524353027</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G447" t="n">
-        <v>8.12833404541016</v>
+        <v>8.12833499908447</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G449" t="n">
-        <v>8.03040313720703</v>
+        <v>8.03040218353271</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692350387573</v>
+        <v>7.93692302703857</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504360198975</v>
+        <v>8.15504264831543</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.15216159820557</v>
       </c>
       <c r="G455" t="n">
-        <v>8.11497974395752</v>
+        <v>8.1149787902832</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G457" t="n">
-        <v>7.77221822738647</v>
+        <v>7.77221870422363</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.92122364044189</v>
       </c>
       <c r="G459" t="n">
-        <v>7.91021299362183</v>
+        <v>7.91021347045898</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G460" t="n">
-        <v>7.78112173080444</v>
+        <v>7.78112125396729</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.42945718765259</v>
+        <v>7.4294581413269</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>9.04673385620117</v>
       </c>
       <c r="G465" t="n">
-        <v>8.02149963378906</v>
+        <v>8.02150058746338</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.7143497467041</v>
+        <v>7.71435022354126</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538381576538</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G468" t="n">
-        <v>7.64312648773193</v>
+        <v>7.64312696456909</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479198455811</v>
+        <v>7.99479150772095</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G470" t="n">
-        <v>8.03040313720703</v>
+        <v>8.03040218353271</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.44836521148682</v>
       </c>
       <c r="G479" t="n">
-        <v>8.3776159286499</v>
+        <v>8.37761497497559</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757966995239</v>
+        <v>7.64757823944092</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G482" t="n">
-        <v>7.62532234191895</v>
+        <v>7.62532186508179</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G483" t="n">
-        <v>7.62532234191895</v>
+        <v>7.62532186508179</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G484" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344244003296</v>
+        <v>7.84344148635864</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G491" t="n">
-        <v>7.7455096244812</v>
+        <v>7.74551010131836</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G492" t="n">
-        <v>7.50513172149658</v>
+        <v>7.50513219833374</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G493" t="n">
-        <v>7.64312648773193</v>
+        <v>7.64312696456909</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>8.39910411834717</v>
       </c>
       <c r="G498" t="n">
-        <v>7.44726324081421</v>
+        <v>7.44726371765137</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>8.60996055603027</v>
       </c>
       <c r="G499" t="n">
-        <v>7.6342248916626</v>
+        <v>7.63422441482544</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G500" t="n">
-        <v>7.77221822738647</v>
+        <v>7.77221870422363</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>8.39910411834717</v>
       </c>
       <c r="G502" t="n">
-        <v>7.44726324081421</v>
+        <v>7.44726371765137</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>8.34889984130859</v>
       </c>
       <c r="G503" t="n">
-        <v>7.40274858474731</v>
+        <v>7.40274810791016</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.74996280670166</v>
+        <v>7.7499623298645</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G505" t="n">
-        <v>8.03040313720703</v>
+        <v>8.03040218353271</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>9.11199855804443</v>
       </c>
       <c r="G506" t="n">
-        <v>8.07936859130859</v>
+        <v>8.07936763763428</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>9.34795665740967</v>
       </c>
       <c r="G508" t="n">
-        <v>8.2885856628418</v>
+        <v>8.28858661651611</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.50670623779297</v>
+        <v>8.50670719146729</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.50225639343262</v>
+        <v>8.5022554397583</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G517" t="n">
-        <v>8.76043891906738</v>
+        <v>8.7604398727417</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.76464939117432</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65805625915527</v>
+        <v>8.65805721282959</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G522" t="n">
-        <v>9.12990951538086</v>
+        <v>9.12990856170654</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.03643035888672</v>
+        <v>9.03642845153809</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833885192871</v>
+        <v>8.83833980560303</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.60399723052979</v>
       </c>
       <c r="G532" t="n">
-        <v>8.51561069488525</v>
+        <v>8.51560974121094</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.41990375518799</v>
+        <v>8.4199047088623</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617107391357</v>
+        <v>8.16617202758789</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G537" t="n">
-        <v>7.82341051101685</v>
+        <v>7.823410987854</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660707473755</v>
+        <v>7.73660755157471</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G540" t="n">
-        <v>7.61196756362915</v>
+        <v>7.61196708679199</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>8.4543285369873</v>
       </c>
       <c r="G543" t="n">
-        <v>7.49623012542725</v>
+        <v>7.49622964859009</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.7143497467041</v>
+        <v>7.71435022354126</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G548" t="n">
-        <v>7.60083866119385</v>
+        <v>7.60083818435669</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.83587837219238</v>
       </c>
       <c r="G550" t="n">
-        <v>7.83453893661499</v>
+        <v>7.83453989028931</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G553" t="n">
-        <v>7.50068044662476</v>
+        <v>7.50068092346191</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368829727173</v>
+        <v>7.29368877410889</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G557" t="n">
-        <v>7.50068044662476</v>
+        <v>7.50068092346191</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663948059082</v>
+        <v>7.75663900375366</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>8.32379913330078</v>
       </c>
       <c r="G563" t="n">
-        <v>7.38049268722534</v>
+        <v>7.38049173355103</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613481521606</v>
+        <v>7.43613433837891</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585126876831</v>
+        <v>7.25585174560547</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.32128810882568</v>
       </c>
       <c r="G567" t="n">
-        <v>7.37826633453369</v>
+        <v>7.37826681137085</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>8.16063594818115</v>
       </c>
       <c r="G569" t="n">
-        <v>7.23581981658936</v>
+        <v>7.23582029342651</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G573" t="n">
-        <v>7.07111692428589</v>
+        <v>7.07111740112305</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.79163789749146</v>
       </c>
       <c r="G576" t="n">
-        <v>6.9086389541626</v>
+        <v>6.90863943099976</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G583" t="n">
-        <v>7.22469091415405</v>
+        <v>7.22469139099121</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>8.1079216003418</v>
       </c>
       <c r="G584" t="n">
-        <v>7.18907928466797</v>
+        <v>7.18907976150513</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842311859131</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610431671143</v>
+        <v>7.41610383987427</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766731262207</v>
+        <v>6.99766778945923</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.06022834777832</v>
       </c>
       <c r="G599" t="n">
-        <v>7.14679145812988</v>
+        <v>7.14679098129272</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G602" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G608" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37538909912109</v>
+        <v>8.37539005279541</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065475463867</v>
+        <v>8.19065380096436</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>8.79822540283203</v>
       </c>
       <c r="G613" t="n">
-        <v>7.80115413665771</v>
+        <v>7.80115365982056</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>9.72448635101318</v>
       </c>
       <c r="G622" t="n">
-        <v>8.62244415283203</v>
+        <v>8.62244510650635</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902599334717</v>
+        <v>8.56902694702148</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G627" t="n">
-        <v>8.27523231506348</v>
+        <v>8.27523136138916</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G633" t="n">
-        <v>8.12833404541016</v>
+        <v>8.12833499908447</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G634" t="n">
-        <v>8.12833404541016</v>
+        <v>8.12833499908447</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>9.90019989013672</v>
       </c>
       <c r="G637" t="n">
-        <v>8.778244972229</v>
+        <v>8.77824592590332</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.86254692077637</v>
       </c>
       <c r="G639" t="n">
-        <v>8.74485874176025</v>
+        <v>8.74485969543457</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.71147441864014</v>
+        <v>8.71147346496582</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>10.2767276763916</v>
       </c>
       <c r="G643" t="n">
-        <v>9.11210250854492</v>
+        <v>9.11210155487061</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009727478027</v>
+        <v>9.25009822845459</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.4649925231934</v>
       </c>
       <c r="G647" t="n">
-        <v>9.27903175354004</v>
+        <v>9.27903270721436</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>10.0181789398193</v>
       </c>
       <c r="G648" t="n">
-        <v>8.88285350799561</v>
+        <v>8.88285446166992</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100505828857</v>
+        <v>9.12100601196289</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G654" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G660" t="n">
-        <v>9.84659194946289</v>
+        <v>9.84659099578857</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G661" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>11.2331123352051</v>
       </c>
       <c r="G666" t="n">
-        <v>9.96010303497314</v>
+        <v>9.96010398864746</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G667" t="n">
-        <v>9.87107372283936</v>
+        <v>9.87107467651367</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>11.6648645401001</v>
       </c>
       <c r="G674" t="n">
-        <v>10.3429269790649</v>
+        <v>10.3429260253906</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>11.5167636871338</v>
       </c>
       <c r="G675" t="n">
-        <v>10.2116098403931</v>
+        <v>10.2116088867188</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>11.6046199798584</v>
       </c>
       <c r="G676" t="n">
-        <v>10.2895088195801</v>
+        <v>10.2895097732544</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>11.4665603637695</v>
       </c>
       <c r="G680" t="n">
-        <v>10.1670951843262</v>
+        <v>10.1670961380005</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>11.700008392334</v>
       </c>
       <c r="G683" t="n">
-        <v>10.3740882873535</v>
+        <v>10.3740873336792</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99349021911621</v>
+        <v>9.99348926544189</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694787979126</v>
+        <v>10.2694797515869</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.7569122314453</v>
+        <v>10.756911277771</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>13.1232872009277</v>
       </c>
       <c r="G698" t="n">
-        <v>11.6360721588135</v>
+        <v>11.6360712051392</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>13.7558555603027</v>
       </c>
       <c r="G704" t="n">
-        <v>12.1969537734985</v>
+        <v>12.1969528198242</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856676101685</v>
+        <v>12.0856666564941</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>13.032919883728</v>
       </c>
       <c r="G706" t="n">
-        <v>11.5559453964233</v>
+        <v>11.555944442749</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395784378052</v>
+        <v>11.0395774841309</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>12.7015752792358</v>
       </c>
       <c r="G713" t="n">
-        <v>11.262149810791</v>
+        <v>11.2621507644653</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>12.3325757980347</v>
       </c>
       <c r="G714" t="n">
-        <v>10.9349689483643</v>
+        <v>10.9349679946899</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364070892334</v>
+        <v>10.4364080429077</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G719" t="n">
-        <v>10.549919128418</v>
+        <v>10.5499200820923</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G724" t="n">
-        <v>10.7613620758057</v>
+        <v>10.76136302948</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G728" t="n">
-        <v>10.160418510437</v>
+        <v>10.1604175567627</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006391525269</v>
+        <v>10.3006381988525</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>11.1377248764038</v>
       </c>
       <c r="G732" t="n">
-        <v>9.87552642822266</v>
+        <v>9.87552547454834</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G737" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081249237061</v>
+        <v>8.29081058502197</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219158172607</v>
+        <v>8.46219253540039</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G744" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G752" t="n">
-        <v>8.25520038604736</v>
+        <v>8.25519943237305</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466617584229</v>
+        <v>7.91466474533081</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>8.25602340698242</v>
       </c>
       <c r="G758" t="n">
-        <v>7.32039785385132</v>
+        <v>7.32039737701416</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G759" t="n">
-        <v>7.59416151046753</v>
+        <v>7.59416103363037</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873331069946</v>
+        <v>6.96873378753662</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>8.37400245666504</v>
       </c>
       <c r="G765" t="n">
-        <v>7.42500686645508</v>
+        <v>7.42500638961792</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G772" t="n">
-        <v>8.25520038604736</v>
+        <v>8.25519943237305</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096832275391</v>
+        <v>8.39096927642822</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>9.71193504333496</v>
       </c>
       <c r="G780" t="n">
-        <v>8.61131572723389</v>
+        <v>8.61131477355957</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G781" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G782" t="n">
-        <v>8.86282348632812</v>
+        <v>8.86282253265381</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G783" t="n">
-        <v>8.9451732635498</v>
+        <v>8.94517421722412</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>10.2817487716675</v>
       </c>
       <c r="G786" t="n">
-        <v>9.11655521392822</v>
+        <v>9.11655426025391</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>9.79477119445801</v>
       </c>
       <c r="G790" t="n">
-        <v>8.68476486206055</v>
+        <v>8.68476390838623</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>9.75711917877197</v>
       </c>
       <c r="G791" t="n">
-        <v>8.65137958526611</v>
+        <v>8.6513786315918</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G792" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G795" t="n">
-        <v>9.0809440612793</v>
+        <v>9.08094310760498</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>10.7963380813599</v>
       </c>
       <c r="G797" t="n">
-        <v>9.57282733917236</v>
+        <v>9.57282638549805</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G799" t="n">
-        <v>9.41480255126953</v>
+        <v>9.41480159759521</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G804" t="n">
-        <v>9.69746780395508</v>
+        <v>9.69746685028076</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G805" t="n">
-        <v>10.160418510437</v>
+        <v>10.1604175567627</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232986450195</v>
+        <v>9.96232891082764</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>11.5167636871338</v>
       </c>
       <c r="G807" t="n">
-        <v>10.2116098403931</v>
+        <v>10.2116088867188</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496036529541</v>
+        <v>10.3496055603027</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.2572708129883</v>
       </c>
       <c r="G814" t="n">
-        <v>10.8681974411011</v>
+        <v>10.8681983947754</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>12.1091690063477</v>
       </c>
       <c r="G816" t="n">
-        <v>10.7368793487549</v>
+        <v>10.7368803024292</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.3350868225098</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9371948242188</v>
+        <v>10.9371957778931</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>11.5970897674561</v>
       </c>
       <c r="G821" t="n">
-        <v>10.2828330993652</v>
+        <v>10.2828321456909</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147811889648</v>
+        <v>10.8147802352905</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G830" t="n">
-        <v>10.7613620758057</v>
+        <v>10.76136302948</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295726776123</v>
+        <v>10.3295736312866</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>11.5343351364136</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2271890640259</v>
+        <v>10.2271900177002</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>12.0564546585083</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6901388168335</v>
+        <v>10.6901397705078</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G842" t="n">
-        <v>10.549919128418</v>
+        <v>10.5499200820923</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G845" t="n">
-        <v>10.2383193969727</v>
+        <v>10.2383184432983</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>11.3385400772095</v>
       </c>
       <c r="G846" t="n">
-        <v>10.0535840988159</v>
+        <v>10.0535831451416</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>10.977071762085</v>
       </c>
       <c r="G848" t="n">
-        <v>9.733078956604</v>
+        <v>9.73307800292969</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G851" t="n">
-        <v>9.33912754058838</v>
+        <v>9.33912658691406</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>10.1411781311035</v>
       </c>
       <c r="G852" t="n">
-        <v>8.99191474914551</v>
+        <v>8.99191379547119</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>10.203932762146</v>
       </c>
       <c r="G854" t="n">
-        <v>9.04755687713623</v>
+        <v>9.04755783081055</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G855" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>10.4072589874268</v>
       </c>
       <c r="G856" t="n">
-        <v>9.22784042358398</v>
+        <v>9.22784233093262</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>10.5101757049561</v>
       </c>
       <c r="G860" t="n">
-        <v>9.31909465789795</v>
+        <v>9.31909561157227</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G861" t="n">
-        <v>9.25232410430908</v>
+        <v>9.25232315063477</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G863" t="n">
-        <v>8.77601909637451</v>
+        <v>8.7760181427002</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G864" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G867" t="n">
-        <v>8.76043891906738</v>
+        <v>8.7604398727417</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>9.62156772613525</v>
       </c>
       <c r="G868" t="n">
-        <v>8.53118991851807</v>
+        <v>8.53118896484375</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G869" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G871" t="n">
-        <v>9.07204151153564</v>
+        <v>9.07203960418701</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>10.768726348877</v>
       </c>
       <c r="G874" t="n">
-        <v>9.54834461212158</v>
+        <v>9.5483455657959</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395576477051</v>
+        <v>9.58395671844482</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G877" t="n">
-        <v>9.33912754058838</v>
+        <v>9.33912658691406</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G879" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>11.0699491500854</v>
       </c>
       <c r="G883" t="n">
-        <v>9.81543064117432</v>
+        <v>9.81543159484863</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079113006592</v>
+        <v>9.69079208374023</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G885" t="n">
-        <v>9.49047470092773</v>
+        <v>9.49047565460205</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>10.9218482971191</v>
       </c>
       <c r="G886" t="n">
-        <v>9.68411350250244</v>
+        <v>9.68411445617676</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>10.9820928573608</v>
       </c>
       <c r="G888" t="n">
-        <v>9.7375316619873</v>
+        <v>9.73753070831299</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G890" t="n">
-        <v>9.69746780395508</v>
+        <v>9.69746685028076</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>11.3987846374512</v>
       </c>
       <c r="G898" t="n">
-        <v>10.1070013046265</v>
+        <v>10.1070003509521</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>11.4715795516968</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1715469360352</v>
+        <v>10.1715459823608</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304893493652</v>
+        <v>9.71304798126221</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>11.4941720962524</v>
       </c>
       <c r="G907" t="n">
-        <v>10.191577911377</v>
+        <v>10.1915788650513</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>11.5845394134521</v>
       </c>
       <c r="G908" t="n">
-        <v>10.2717037200928</v>
+        <v>10.2717046737671</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794101715088</v>
+        <v>9.99794006347656</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>10.7411136627197</v>
       </c>
       <c r="G913" t="n">
-        <v>9.52386093139648</v>
+        <v>9.5238618850708</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G914" t="n">
-        <v>9.20780944824219</v>
+        <v>9.2078104019165</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>10.4248304367065</v>
       </c>
       <c r="G915" t="n">
-        <v>9.24342060089111</v>
+        <v>9.24342155456543</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>10.3721160888672</v>
       </c>
       <c r="G917" t="n">
-        <v>9.19668102264404</v>
+        <v>9.19668006896973</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G918" t="n">
-        <v>9.12545871734619</v>
+        <v>9.12545776367188</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G919" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G920" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.9518518447876</v>
+        <v>8.95185089111328</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>10.4474220275879</v>
       </c>
       <c r="G925" t="n">
-        <v>9.26345252990723</v>
+        <v>9.26345348358154</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G926" t="n">
-        <v>9.31464290618896</v>
+        <v>9.31464385986328</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G929" t="n">
-        <v>9.41480255126953</v>
+        <v>9.41480159759521</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>11.4665603637695</v>
       </c>
       <c r="G939" t="n">
-        <v>10.1670951843262</v>
+        <v>10.1670961380005</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.1047735214233</v>
+        <v>10.104775428772</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136779785156</v>
+        <v>10.1136770248413</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403856277466</v>
+        <v>10.1403865814209</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230527877808</v>
+        <v>10.4230537414551</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>11.1854181289673</v>
       </c>
       <c r="G945" t="n">
-        <v>9.91781520843506</v>
+        <v>9.91781425476074</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G946" t="n">
-        <v>9.87107372283936</v>
+        <v>9.87107467651367</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G947" t="n">
-        <v>9.84659194946289</v>
+        <v>9.84659099578857</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>10.0683822631836</v>
       </c>
       <c r="G955" t="n">
-        <v>8.9273681640625</v>
+        <v>8.92736911773682</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>10.0332403182983</v>
       </c>
       <c r="G956" t="n">
-        <v>8.89620876312256</v>
+        <v>8.89620780944824</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>10.1612596511841</v>
       </c>
       <c r="G960" t="n">
-        <v>9.00972080230713</v>
+        <v>9.00971984863281</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G961" t="n">
-        <v>9.16997337341309</v>
+        <v>9.16997241973877</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>10.3219118118286</v>
       </c>
       <c r="G975" t="n">
-        <v>9.15216636657715</v>
+        <v>9.15216541290283</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.03643035888672</v>
+        <v>9.03642845153809</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.802077293396</v>
+        <v>9.80207633972168</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812397003174</v>
+        <v>9.40812492370605</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>10.8164196014404</v>
       </c>
       <c r="G993" t="n">
-        <v>9.59063339233398</v>
+        <v>9.59063243865967</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>10.7135019302368</v>
       </c>
       <c r="G996" t="n">
-        <v>9.49937915802002</v>
+        <v>9.4993782043457</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G998" t="n">
-        <v>9.07204151153564</v>
+        <v>9.07203960418701</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.25232410430908</v>
+        <v>9.25232315063477</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467674255371</v>
+        <v>9.33467578887939</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.56169891357422</v>
+        <v>9.5616979598999</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.802077293396</v>
+        <v>9.80207633972168</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>11.1126232147217</v>
       </c>
       <c r="G1029" t="n">
-        <v>9.85326957702637</v>
+        <v>9.85326862335205</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G1030" t="n">
-        <v>9.46154117584229</v>
+        <v>9.4615421295166</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G1032" t="n">
-        <v>9.12545871734619</v>
+        <v>9.12545776367188</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.31974697113037</v>
+        <v>8.31974601745605</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.34645462036133</v>
+        <v>8.34645557403564</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>9.41573238372803</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.34868144989014</v>
+        <v>8.34868049621582</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>9.51362991333008</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.43548393249512</v>
+        <v>8.4354829788208</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>9.42577266693115</v>
       </c>
       <c r="G1052" t="n">
-        <v>8.35758304595947</v>
+        <v>8.35758399963379</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657609939575</v>
+        <v>7.71657657623291</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754726409912</v>
+        <v>7.62754774093628</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.60083866119385</v>
+        <v>7.60083818435669</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585126876831</v>
+        <v>7.25585174560547</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.07111692428589</v>
+        <v>7.07111740112305</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.9500036239624</v>
+        <v>4.95000410079956</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.9500036239624</v>
+        <v>4.95000410079956</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.95009994506836</v>
       </c>
       <c r="G1068" t="n">
-        <v>4.3891224861145</v>
+        <v>4.38912296295166</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>5.18605804443359</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.59834051132202</v>
+        <v>4.59834003448486</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342178344727</v>
+        <v>5.00342130661011</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.88990926742554</v>
+        <v>4.88991022109985</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>5.85627889633179</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.19260740280151</v>
+        <v>5.19260787963867</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>5.89393186569214</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.22599315643311</v>
+        <v>5.22599363327026</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>5.95919704437256</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.28386211395264</v>
+        <v>5.28386259078979</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.0219521522522</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.33950567245483</v>
+        <v>5.33950519561768</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>5.9014630317688</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.23267078399658</v>
+        <v>5.23267126083374</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.29276514053345</v>
+        <v>5.29276561737061</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.95445489883423</v>
+        <v>4.95445537567139</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>5.67303514480591</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.03012990951538</v>
+        <v>5.03013038635254</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>5.55505609512329</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.92552089691162</v>
+        <v>4.92552137374878</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928550720215</v>
+        <v>5.19928503036499</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041345596313</v>
+        <v>5.21041393280029</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>5.73328018188477</v>
       </c>
       <c r="G1100" t="n">
-        <v>5.08354759216309</v>
+        <v>5.08354806900024</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>5.79101419448853</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.13473892211914</v>
+        <v>5.1347393989563</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>5.62032079696655</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.98338985443115</v>
+        <v>4.98338937759399</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470746994019</v>
+        <v>5.11470794677734</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248159408569</v>
+        <v>5.11248207092285</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.92329597473145</v>
+        <v>4.92329549789429</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -69090,6 +69090,32 @@
         <v>4.16699981689453</v>
       </c>
       <c r="H2643" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2644">
+      <c r="A2644" s="1" t="n">
+        <v>46171.2916666667</v>
+      </c>
+      <c r="B2644" t="n">
+        <v>15980176</v>
+      </c>
+      <c r="C2644" t="n">
+        <v>4.22499990463257</v>
+      </c>
+      <c r="D2644" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="E2644" t="n">
+        <v>4.15399980545044</v>
+      </c>
+      <c r="F2644" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="G2644" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="H2644" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -447,7 +447,7 @@
         <v>23.2093391418457</v>
       </c>
       <c r="G3" t="n">
-        <v>20.5791053771973</v>
+        <v>20.5791072845459</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>21.9295864105225</v>
       </c>
       <c r="G5" t="n">
-        <v>19.4443855285645</v>
+        <v>19.4443836212158</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>22.1823787689209</v>
       </c>
       <c r="G10" t="n">
-        <v>19.668529510498</v>
+        <v>19.6685276031494</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>20.9184246063232</v>
       </c>
       <c r="G11" t="n">
-        <v>18.5478134155273</v>
+        <v>18.547815322876</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811958312988</v>
+        <v>17.5811977386475</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>13.2778282165527</v>
       </c>
       <c r="G16" t="n">
-        <v>11.773099899292</v>
+        <v>11.7730989456177</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087112426758</v>
+        <v>12.6087121963501</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G21" t="n">
-        <v>12.6977405548096</v>
+        <v>12.6977415084839</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.358302116394</v>
       </c>
       <c r="G22" t="n">
-        <v>12.7311267852783</v>
+        <v>12.7311277389526</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.8813648223877</v>
       </c>
       <c r="G23" t="n">
-        <v>12.3082399368286</v>
+        <v>12.30823802948</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G29" t="n">
-        <v>8.0571117401123</v>
+        <v>8.05711078643799</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393558502197</v>
+        <v>6.74393510818481</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.87747955322266</v>
+        <v>6.87747859954834</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51180982589722</v>
+        <v>7.51181030273438</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243982315063</v>
+        <v>7.91243886947632</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.67679214477539</v>
       </c>
       <c r="G45" t="n">
-        <v>8.58015537261963</v>
+        <v>8.58015632629395</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>10.6884002685547</v>
       </c>
       <c r="G47" t="n">
-        <v>9.47712135314941</v>
+        <v>9.47712230682373</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.07714366912842</v>
+        <v>8.0771427154541</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683395385742</v>
+        <v>8.58683204650879</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.3175220489502</v>
+        <v>8.31752109527588</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G57" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.93628597259521</v>
       </c>
       <c r="G62" t="n">
-        <v>7.92356824874878</v>
+        <v>7.92356872558594</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8.83838844299316</v>
       </c>
       <c r="G63" t="n">
-        <v>7.8367657661438</v>
+        <v>7.83676528930664</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870809555054</v>
+        <v>7.65870714187622</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G65" t="n">
-        <v>7.32262372970581</v>
+        <v>7.32262420654297</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.61341381072998</v>
       </c>
       <c r="G68" t="n">
-        <v>6.75061273574829</v>
+        <v>6.75061225891113</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365732192993</v>
+        <v>7.27365779876709</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G71" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09939956665039</v>
+        <v>8.09940052032471</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G75" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.55128288269043</v>
       </c>
       <c r="G81" t="n">
-        <v>8.46886920928955</v>
+        <v>8.46887016296387</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912178039551</v>
+        <v>8.62912082672119</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G83" t="n">
-        <v>9.68188762664795</v>
+        <v>9.68188858032227</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.2685546875</v>
+        <v>8.26855373382568</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542007446289</v>
+        <v>8.39542102813721</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G96" t="n">
-        <v>8.31974601745605</v>
+        <v>8.31974697113037</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588800430298</v>
+        <v>7.98588752746582</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>8.92875480651855</v>
       </c>
       <c r="G100" t="n">
-        <v>7.9168906211853</v>
+        <v>7.91689109802246</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.14212131500244</v>
       </c>
       <c r="G101" t="n">
-        <v>8.10607814788818</v>
+        <v>8.10607719421387</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.04924392700195</v>
       </c>
       <c r="G108" t="n">
-        <v>8.02372455596924</v>
+        <v>8.02372550964355</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.5261812210083</v>
       </c>
       <c r="G111" t="n">
-        <v>8.44661331176758</v>
+        <v>8.44661235809326</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G113" t="n">
-        <v>8.6736364364624</v>
+        <v>8.67363548278809</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.28018188476562</v>
       </c>
       <c r="G114" t="n">
-        <v>8.22849178314209</v>
+        <v>8.22849273681641</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325277328491</v>
+        <v>7.72325325012207</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660755157471</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G118" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.05933570861816</v>
+        <v>8.05933666229248</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.59193658828735</v>
+        <v>7.5919361114502</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G131" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G132" t="n">
-        <v>7.823410987854</v>
+        <v>7.82341051101685</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.04171371459961</v>
       </c>
       <c r="G133" t="n">
-        <v>8.01704883575439</v>
+        <v>8.01704788208008</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.44083404541016</v>
       </c>
       <c r="G134" t="n">
-        <v>8.37093734741211</v>
+        <v>8.37093830108643</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.71147346496582</v>
+        <v>8.71147441864014</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420448303223</v>
+        <v>9.03420257568359</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G138" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>10.977071762085</v>
       </c>
       <c r="G142" t="n">
-        <v>9.73307800292969</v>
+        <v>9.733078956604</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G144" t="n">
-        <v>9.68856620788574</v>
+        <v>9.68856525421143</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>10.359564781189</v>
       </c>
       <c r="G145" t="n">
-        <v>9.18555164337158</v>
+        <v>9.1855525970459</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427124023438</v>
+        <v>9.78427219390869</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G148" t="n">
-        <v>8.82721138000488</v>
+        <v>8.8272123336792</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G151" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.90019989013672</v>
       </c>
       <c r="G155" t="n">
-        <v>8.77824592590332</v>
+        <v>8.778244972229</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.0056276321411</v>
       </c>
       <c r="G156" t="n">
-        <v>8.87172508239746</v>
+        <v>8.87172603607178</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G157" t="n">
-        <v>8.7760181427002</v>
+        <v>8.77601909637451</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.03642845153809</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G166" t="n">
-        <v>9.21671199798584</v>
+        <v>9.21671295166016</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>10.442400932312</v>
       </c>
       <c r="G168" t="n">
-        <v>9.25900077819824</v>
+        <v>9.25899982452393</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G169" t="n">
-        <v>9.08094310760498</v>
+        <v>9.0809440612793</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G170" t="n">
-        <v>9.16997241973877</v>
+        <v>9.16997337341309</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548778533936</v>
+        <v>9.14548873901367</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>10.457462310791</v>
       </c>
       <c r="G174" t="n">
-        <v>9.27235412597656</v>
+        <v>9.27235507965088</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G175" t="n">
-        <v>9.16997241973877</v>
+        <v>9.16997337341309</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G176" t="n">
-        <v>9.2078104019165</v>
+        <v>9.20780944824219</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G178" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G179" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.44836521148682</v>
       </c>
       <c r="G180" t="n">
-        <v>8.37761497497559</v>
+        <v>8.3776159286499</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.79225015640259</v>
+        <v>7.79225063323975</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.90365314483643</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89463424682617</v>
+        <v>7.89463376998901</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.28771305084229</v>
       </c>
       <c r="G188" t="n">
-        <v>8.23516845703125</v>
+        <v>8.23516941070557</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.73883295059204</v>
+        <v>7.7388334274292</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G192" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G196" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G197" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G199" t="n">
-        <v>8.94294929504395</v>
+        <v>8.94294834136963</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.8139095306396</v>
       </c>
       <c r="G206" t="n">
-        <v>9.58840847015381</v>
+        <v>9.58840751647949</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G207" t="n">
-        <v>9.68856620788574</v>
+        <v>9.68856525421143</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G209" t="n">
-        <v>9.68188762664795</v>
+        <v>9.68188858032227</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G210" t="n">
-        <v>9.31464385986328</v>
+        <v>9.31464290618896</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.03642845153809</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G212" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.34645557403564</v>
+        <v>8.34645462036133</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.2240142822266</v>
       </c>
       <c r="G225" t="n">
-        <v>9.06536293029785</v>
+        <v>9.06536388397217</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G228" t="n">
-        <v>8.6736364364624</v>
+        <v>8.67363548278809</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G230" t="n">
-        <v>8.94517421722412</v>
+        <v>8.9451732635498</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.2215042114258</v>
       </c>
       <c r="G231" t="n">
-        <v>9.06313800811768</v>
+        <v>9.06313705444336</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.71193504333496</v>
       </c>
       <c r="G235" t="n">
-        <v>8.61131477355957</v>
+        <v>8.61131572723389</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.6457271575928</v>
       </c>
       <c r="G236" t="n">
-        <v>9.43928527832031</v>
+        <v>9.439284324646</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>11.6347427368164</v>
       </c>
       <c r="G241" t="n">
-        <v>10.316219329834</v>
+        <v>10.3162183761597</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.9218482971191</v>
       </c>
       <c r="G243" t="n">
-        <v>9.68411445617676</v>
+        <v>9.68411350250244</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>11.2406415939331</v>
       </c>
       <c r="G244" t="n">
-        <v>9.96677875518799</v>
+        <v>9.9667797088623</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.8230066299438</v>
       </c>
       <c r="G245" t="n">
-        <v>10.4831466674805</v>
+        <v>10.4831476211548</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>12.8019819259644</v>
       </c>
       <c r="G250" t="n">
-        <v>11.3511800765991</v>
+        <v>11.3511781692505</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G252" t="n">
-        <v>11.2844076156616</v>
+        <v>11.2844085693359</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076099395752</v>
+        <v>11.9076108932495</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.0319766998291</v>
       </c>
       <c r="G258" t="n">
-        <v>12.4417819976807</v>
+        <v>12.441782951355</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G259" t="n">
-        <v>12.6977405548096</v>
+        <v>12.6977415084839</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195251464844</v>
+        <v>12.4195261001587</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858253479004</v>
+        <v>12.1858243942261</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.3165721893311</v>
       </c>
       <c r="G263" t="n">
-        <v>11.8074531555176</v>
+        <v>11.8074522018433</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>12.7517786026001</v>
       </c>
       <c r="G264" t="n">
-        <v>11.3066654205322</v>
+        <v>11.3066644668579</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>12.2999439239502</v>
       </c>
       <c r="G268" t="n">
-        <v>10.9060344696045</v>
+        <v>10.9060354232788</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.5635137557983</v>
       </c>
       <c r="G269" t="n">
-        <v>11.1397342681885</v>
+        <v>11.1397352218628</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G270" t="n">
-        <v>11.2844076156616</v>
+        <v>11.2844085693359</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619930267334</v>
+        <v>11.1619939804077</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>12.6011667251587</v>
       </c>
       <c r="G272" t="n">
-        <v>11.1731204986572</v>
+        <v>11.1731214523315</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.5007591247559</v>
       </c>
       <c r="G274" t="n">
-        <v>11.0840921401978</v>
+        <v>11.0840930938721</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>13.1283073425293</v>
       </c>
       <c r="G276" t="n">
-        <v>11.6405220031738</v>
+        <v>11.6405229568481</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960083007812</v>
+        <v>11.5960092544556</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G281" t="n">
-        <v>10.2383184432983</v>
+        <v>10.2383193969727</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141492843628</v>
+        <v>10.4141502380371</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.2516717910767</v>
+        <v>10.251672744751</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.39857006073</v>
+        <v>10.3985710144043</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.707537651062</v>
       </c>
       <c r="G287" t="n">
-        <v>10.3807640075684</v>
+        <v>10.3807649612427</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>12.0213117599487</v>
       </c>
       <c r="G288" t="n">
-        <v>10.6589784622192</v>
+        <v>10.6589794158936</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651847839355</v>
+        <v>10.3651838302612</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>11.6372528076172</v>
       </c>
       <c r="G293" t="n">
-        <v>10.3184432983398</v>
+        <v>10.3184442520142</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10.6984405517578</v>
       </c>
       <c r="G302" t="n">
-        <v>9.48602390289307</v>
+        <v>9.48602485656738</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.5428085327148</v>
       </c>
       <c r="G303" t="n">
-        <v>9.34803009033203</v>
+        <v>9.34802913665771</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10.4675025939941</v>
       </c>
       <c r="G304" t="n">
-        <v>9.28125762939453</v>
+        <v>9.28125858306885</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10.1386680603027</v>
       </c>
       <c r="G307" t="n">
-        <v>8.98968887329102</v>
+        <v>8.9896879196167</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.2491159439087</v>
       </c>
       <c r="G308" t="n">
-        <v>9.08762073516846</v>
+        <v>9.08761978149414</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520519256592</v>
+        <v>8.96520614624023</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.3244218826294</v>
       </c>
       <c r="G311" t="n">
-        <v>9.15439224243164</v>
+        <v>9.15439128875732</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539485931396</v>
+        <v>9.08539390563965</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.1336479187012</v>
       </c>
       <c r="G315" t="n">
-        <v>8.98523712158203</v>
+        <v>8.98523807525635</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10.1562385559082</v>
       </c>
       <c r="G317" t="n">
-        <v>9.00526809692383</v>
+        <v>9.00526714324951</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G320" t="n">
-        <v>9.4615421295166</v>
+        <v>9.46154117584229</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>10.8164196014404</v>
       </c>
       <c r="G321" t="n">
-        <v>9.59063243865967</v>
+        <v>9.59063339233398</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>10.6808700561523</v>
       </c>
       <c r="G322" t="n">
-        <v>9.47044467926025</v>
+        <v>9.47044563293457</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77982044219971</v>
+        <v>9.77981853485107</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G324" t="n">
-        <v>9.49047565460205</v>
+        <v>9.49047470092773</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>10.5227270126343</v>
       </c>
       <c r="G328" t="n">
-        <v>9.33022403717041</v>
+        <v>9.33022308349609</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G330" t="n">
-        <v>9.12990856170654</v>
+        <v>9.12990951538086</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>10.2691984176636</v>
       </c>
       <c r="G331" t="n">
-        <v>9.10542678833008</v>
+        <v>9.10542583465576</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10.0784225463867</v>
       </c>
       <c r="G333" t="n">
-        <v>8.93626976013184</v>
+        <v>8.93627071380615</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.2033576965332</v>
+        <v>9.20335865020752</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G339" t="n">
-        <v>8.94294929504395</v>
+        <v>8.94294834136963</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G344" t="n">
-        <v>8.87840175628662</v>
+        <v>8.87840270996094</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>10.0332403182983</v>
       </c>
       <c r="G345" t="n">
-        <v>8.89620780944824</v>
+        <v>8.89620876312256</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G346" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G347" t="n">
-        <v>8.87840175628662</v>
+        <v>8.87840270996094</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G355" t="n">
-        <v>8.86282253265381</v>
+        <v>8.86282348632812</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.36301803588867</v>
       </c>
       <c r="G359" t="n">
-        <v>8.30194091796875</v>
+        <v>8.30193996429443</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G361" t="n">
-        <v>8.12833499908447</v>
+        <v>8.12833404541016</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.99033880233765</v>
+        <v>7.99033975601196</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G365" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215675354004</v>
+        <v>7.73215579986572</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G368" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G370" t="n">
-        <v>8.0571117401123</v>
+        <v>8.05711078643799</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G374" t="n">
-        <v>7.32262372970581</v>
+        <v>7.32262420654297</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G376" t="n">
-        <v>7.19798278808594</v>
+        <v>7.1979832649231</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.13302421569824</v>
       </c>
       <c r="G377" t="n">
-        <v>7.21133756637573</v>
+        <v>7.21133708953857</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914218902588</v>
+        <v>7.22914266586304</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817197799683</v>
+        <v>7.31817245483398</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G384" t="n">
-        <v>7.19798278808594</v>
+        <v>7.1979832649231</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.68024635314941</v>
       </c>
       <c r="G386" t="n">
-        <v>7.69654512405396</v>
+        <v>7.6965446472168</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.25853443145752</v>
       </c>
       <c r="G389" t="n">
-        <v>7.32262372970581</v>
+        <v>7.32262420654297</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8.4242057800293</v>
       </c>
       <c r="G390" t="n">
-        <v>7.46952104568481</v>
+        <v>7.46952056884766</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390941619873</v>
+        <v>7.43390846252441</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G393" t="n">
-        <v>7.74551010131836</v>
+        <v>7.7455096244812</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.514573097229</v>
       </c>
       <c r="G398" t="n">
-        <v>7.54964685440063</v>
+        <v>7.54964637756348</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842311859131</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G400" t="n">
-        <v>7.61196708679199</v>
+        <v>7.61196756362915</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G403" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G405" t="n">
-        <v>7.70099544525146</v>
+        <v>7.70099496841431</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G406" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757823944092</v>
+        <v>7.64757966995239</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428731918335</v>
+        <v>7.67428636550903</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G413" t="n">
-        <v>7.50513219833374</v>
+        <v>7.50513172149658</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249744415283</v>
+        <v>7.24249792098999</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701162338257</v>
+        <v>7.28701210021973</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>8.08281993865967</v>
       </c>
       <c r="G419" t="n">
-        <v>7.16682243347168</v>
+        <v>7.16682195663452</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>7.84184217453003</v>
       </c>
       <c r="G421" t="n">
-        <v>6.95315408706665</v>
+        <v>6.95315361022949</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>7.70127105712891</v>
       </c>
       <c r="G423" t="n">
-        <v>6.82851314544678</v>
+        <v>6.82851362228394</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.74645376205444</v>
       </c>
       <c r="G428" t="n">
-        <v>6.86857604980469</v>
+        <v>6.86857557296753</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G432" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.96233081817627</v>
       </c>
       <c r="G433" t="n">
-        <v>7.05998802185059</v>
+        <v>7.05998849868774</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591464996338</v>
+        <v>7.29591417312622</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409908294678</v>
+        <v>7.55409860610962</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.42922687530518</v>
       </c>
       <c r="G438" t="n">
-        <v>7.47397232055664</v>
+        <v>7.4739727973938</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.66538381576538</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G442" t="n">
-        <v>7.70099544525146</v>
+        <v>7.70099496841431</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.10697937011719</v>
       </c>
       <c r="G444" t="n">
-        <v>8.07491683959961</v>
+        <v>8.07491779327393</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.10195827484131</v>
       </c>
       <c r="G445" t="n">
-        <v>8.07046508789062</v>
+        <v>8.07046604156494</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.09693813323975</v>
       </c>
       <c r="G446" t="n">
-        <v>8.06601524353027</v>
+        <v>8.06601428985596</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G447" t="n">
-        <v>8.12833499908447</v>
+        <v>8.12833404541016</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G449" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692302703857</v>
+        <v>7.93692350387573</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504264831543</v>
+        <v>8.15504360198975</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.15216159820557</v>
       </c>
       <c r="G455" t="n">
-        <v>8.1149787902832</v>
+        <v>8.11497974395752</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G457" t="n">
-        <v>7.77221870422363</v>
+        <v>7.77221822738647</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.92122364044189</v>
       </c>
       <c r="G459" t="n">
-        <v>7.91021347045898</v>
+        <v>7.91021299362183</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G460" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.4294581413269</v>
+        <v>7.42945718765259</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>9.04673385620117</v>
       </c>
       <c r="G465" t="n">
-        <v>8.02150058746338</v>
+        <v>8.02149963378906</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.66538381576538</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G468" t="n">
-        <v>7.64312696456909</v>
+        <v>7.64312648773193</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479150772095</v>
+        <v>7.99479198455811</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G470" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.44836521148682</v>
       </c>
       <c r="G479" t="n">
-        <v>8.37761497497559</v>
+        <v>8.3776159286499</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757823944092</v>
+        <v>7.64757966995239</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G482" t="n">
-        <v>7.62532186508179</v>
+        <v>7.62532234191895</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G483" t="n">
-        <v>7.62532186508179</v>
+        <v>7.62532234191895</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G484" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344148635864</v>
+        <v>7.84344244003296</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G491" t="n">
-        <v>7.74551010131836</v>
+        <v>7.7455096244812</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G492" t="n">
-        <v>7.50513219833374</v>
+        <v>7.50513172149658</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G493" t="n">
-        <v>7.64312696456909</v>
+        <v>7.64312648773193</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>8.39910411834717</v>
       </c>
       <c r="G498" t="n">
-        <v>7.44726371765137</v>
+        <v>7.44726324081421</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>8.60996055603027</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63422441482544</v>
+        <v>7.6342248916626</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G500" t="n">
-        <v>7.77221870422363</v>
+        <v>7.77221822738647</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>8.39910411834717</v>
       </c>
       <c r="G502" t="n">
-        <v>7.44726371765137</v>
+        <v>7.44726324081421</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>8.34889984130859</v>
       </c>
       <c r="G503" t="n">
-        <v>7.40274810791016</v>
+        <v>7.40274858474731</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.7499623298645</v>
+        <v>7.74996280670166</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G505" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>9.11199855804443</v>
       </c>
       <c r="G506" t="n">
-        <v>8.07936763763428</v>
+        <v>8.07936859130859</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>9.34795665740967</v>
       </c>
       <c r="G508" t="n">
-        <v>8.28858661651611</v>
+        <v>8.2885856628418</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.50670719146729</v>
+        <v>8.50670623779297</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.5022554397583</v>
+        <v>8.50225639343262</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G517" t="n">
-        <v>8.7604398727417</v>
+        <v>8.76043891906738</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.76464939117432</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65805721282959</v>
+        <v>8.65805625915527</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G522" t="n">
-        <v>9.12990856170654</v>
+        <v>9.12990951538086</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.03642845153809</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833980560303</v>
+        <v>8.83833885192871</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.60399723052979</v>
       </c>
       <c r="G532" t="n">
-        <v>8.51560974121094</v>
+        <v>8.51561069488525</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.4199047088623</v>
+        <v>8.41990375518799</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G537" t="n">
-        <v>7.823410987854</v>
+        <v>7.82341051101685</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660755157471</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G540" t="n">
-        <v>7.61196708679199</v>
+        <v>7.61196756362915</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>8.4543285369873</v>
       </c>
       <c r="G543" t="n">
-        <v>7.49622964859009</v>
+        <v>7.49623012542725</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G548" t="n">
-        <v>7.60083818435669</v>
+        <v>7.60083866119385</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.83587837219238</v>
       </c>
       <c r="G550" t="n">
-        <v>7.83453989028931</v>
+        <v>7.83453893661499</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G553" t="n">
-        <v>7.50068092346191</v>
+        <v>7.50068044662476</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368877410889</v>
+        <v>7.29368829727173</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G557" t="n">
-        <v>7.50068092346191</v>
+        <v>7.50068044662476</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663900375366</v>
+        <v>7.75663948059082</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>8.32379913330078</v>
       </c>
       <c r="G563" t="n">
-        <v>7.38049173355103</v>
+        <v>7.38049268722534</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613433837891</v>
+        <v>7.43613481521606</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585174560547</v>
+        <v>7.25585126876831</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.32128810882568</v>
       </c>
       <c r="G567" t="n">
-        <v>7.37826681137085</v>
+        <v>7.37826633453369</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>8.16063594818115</v>
       </c>
       <c r="G569" t="n">
-        <v>7.23582029342651</v>
+        <v>7.23581981658936</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G573" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.79163789749146</v>
       </c>
       <c r="G576" t="n">
-        <v>6.90863943099976</v>
+        <v>6.9086389541626</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G583" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>8.1079216003418</v>
       </c>
       <c r="G584" t="n">
-        <v>7.18907976150513</v>
+        <v>7.18907928466797</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842311859131</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610383987427</v>
+        <v>7.41610431671143</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766778945923</v>
+        <v>6.99766731262207</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.06022834777832</v>
       </c>
       <c r="G599" t="n">
-        <v>7.14679098129272</v>
+        <v>7.14679145812988</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G600" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G602" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G608" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37539005279541</v>
+        <v>8.37538909912109</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065380096436</v>
+        <v>8.19065475463867</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>8.79822540283203</v>
       </c>
       <c r="G613" t="n">
-        <v>7.80115365982056</v>
+        <v>7.80115413665771</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>9.72448635101318</v>
       </c>
       <c r="G622" t="n">
-        <v>8.62244510650635</v>
+        <v>8.62244415283203</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902694702148</v>
+        <v>8.56902599334717</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G627" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G633" t="n">
-        <v>8.12833499908447</v>
+        <v>8.12833404541016</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>9.16722297668457</v>
       </c>
       <c r="G634" t="n">
-        <v>8.12833499908447</v>
+        <v>8.12833404541016</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>9.90019989013672</v>
       </c>
       <c r="G637" t="n">
-        <v>8.77824592590332</v>
+        <v>8.778244972229</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.86254692077637</v>
       </c>
       <c r="G639" t="n">
-        <v>8.74485969543457</v>
+        <v>8.74485874176025</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.71147346496582</v>
+        <v>8.71147441864014</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>10.2767276763916</v>
       </c>
       <c r="G643" t="n">
-        <v>9.11210155487061</v>
+        <v>9.11210250854492</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009822845459</v>
+        <v>9.25009727478027</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.4649925231934</v>
       </c>
       <c r="G647" t="n">
-        <v>9.27903270721436</v>
+        <v>9.27903175354004</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>10.0181789398193</v>
       </c>
       <c r="G648" t="n">
-        <v>8.88285446166992</v>
+        <v>8.88285350799561</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100601196289</v>
+        <v>9.12100505828857</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G654" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.948974609375</v>
+        <v>9.94897556304932</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G660" t="n">
-        <v>9.84659099578857</v>
+        <v>9.84659194946289</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G661" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>11.2331123352051</v>
       </c>
       <c r="G666" t="n">
-        <v>9.96010398864746</v>
+        <v>9.96010303497314</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G667" t="n">
-        <v>9.87107467651367</v>
+        <v>9.87107372283936</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>11.6648645401001</v>
       </c>
       <c r="G674" t="n">
-        <v>10.3429260253906</v>
+        <v>10.3429269790649</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>11.5167636871338</v>
       </c>
       <c r="G675" t="n">
-        <v>10.2116088867188</v>
+        <v>10.2116098403931</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>11.6046199798584</v>
       </c>
       <c r="G676" t="n">
-        <v>10.2895097732544</v>
+        <v>10.2895088195801</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>11.4665603637695</v>
       </c>
       <c r="G680" t="n">
-        <v>10.1670961380005</v>
+        <v>10.1670951843262</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>11.700008392334</v>
       </c>
       <c r="G683" t="n">
-        <v>10.3740873336792</v>
+        <v>10.3740882873535</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99348926544189</v>
+        <v>9.99349021911621</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694797515869</v>
+        <v>10.2694787979126</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.756911277771</v>
+        <v>10.7569122314453</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>13.1232872009277</v>
       </c>
       <c r="G698" t="n">
-        <v>11.6360712051392</v>
+        <v>11.6360721588135</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>13.7558555603027</v>
       </c>
       <c r="G704" t="n">
-        <v>12.1969528198242</v>
+        <v>12.1969537734985</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856666564941</v>
+        <v>12.0856676101685</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>13.032919883728</v>
       </c>
       <c r="G706" t="n">
-        <v>11.555944442749</v>
+        <v>11.5559453964233</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395774841309</v>
+        <v>11.0395784378052</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>12.7015752792358</v>
       </c>
       <c r="G713" t="n">
-        <v>11.2621507644653</v>
+        <v>11.262149810791</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>12.3325757980347</v>
       </c>
       <c r="G714" t="n">
-        <v>10.9349679946899</v>
+        <v>10.9349689483643</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364080429077</v>
+        <v>10.4364070892334</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G719" t="n">
-        <v>10.5499200820923</v>
+        <v>10.549919128418</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G724" t="n">
-        <v>10.76136302948</v>
+        <v>10.7613620758057</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G728" t="n">
-        <v>10.1604175567627</v>
+        <v>10.160418510437</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006381988525</v>
+        <v>10.3006391525269</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>11.1377248764038</v>
       </c>
       <c r="G732" t="n">
-        <v>9.87552547454834</v>
+        <v>9.87552642822266</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G737" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081058502197</v>
+        <v>8.29081249237061</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219253540039</v>
+        <v>8.46219158172607</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G744" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G752" t="n">
-        <v>8.25519943237305</v>
+        <v>8.25520038604736</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466474533081</v>
+        <v>7.91466617584229</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>8.25602340698242</v>
       </c>
       <c r="G758" t="n">
-        <v>7.32039737701416</v>
+        <v>7.32039785385132</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G759" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873378753662</v>
+        <v>6.96873331069946</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>8.37400245666504</v>
       </c>
       <c r="G765" t="n">
-        <v>7.42500638961792</v>
+        <v>7.42500686645508</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G772" t="n">
-        <v>8.25519943237305</v>
+        <v>8.25520038604736</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096927642822</v>
+        <v>8.39096832275391</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>9.71193504333496</v>
       </c>
       <c r="G780" t="n">
-        <v>8.61131477355957</v>
+        <v>8.61131572723389</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G781" t="n">
-        <v>8.82721138000488</v>
+        <v>8.8272123336792</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G782" t="n">
-        <v>8.86282253265381</v>
+        <v>8.86282348632812</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G783" t="n">
-        <v>8.94517421722412</v>
+        <v>8.9451732635498</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>10.2817487716675</v>
       </c>
       <c r="G786" t="n">
-        <v>9.11655426025391</v>
+        <v>9.11655521392822</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>9.79477119445801</v>
       </c>
       <c r="G790" t="n">
-        <v>8.68476390838623</v>
+        <v>8.68476486206055</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>9.75711917877197</v>
       </c>
       <c r="G791" t="n">
-        <v>8.6513786315918</v>
+        <v>8.65137958526611</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G792" t="n">
-        <v>8.82721138000488</v>
+        <v>8.8272123336792</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G795" t="n">
-        <v>9.08094310760498</v>
+        <v>9.0809440612793</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>10.7963380813599</v>
       </c>
       <c r="G797" t="n">
-        <v>9.57282638549805</v>
+        <v>9.57282733917236</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G799" t="n">
-        <v>9.41480159759521</v>
+        <v>9.41480255126953</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G804" t="n">
-        <v>9.69746685028076</v>
+        <v>9.69746780395508</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G805" t="n">
-        <v>10.1604175567627</v>
+        <v>10.160418510437</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232891082764</v>
+        <v>9.96232986450195</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>11.5167636871338</v>
       </c>
       <c r="G807" t="n">
-        <v>10.2116088867188</v>
+        <v>10.2116098403931</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496055603027</v>
+        <v>10.3496036529541</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.2572708129883</v>
       </c>
       <c r="G814" t="n">
-        <v>10.8681983947754</v>
+        <v>10.8681974411011</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>12.1091690063477</v>
       </c>
       <c r="G816" t="n">
-        <v>10.7368803024292</v>
+        <v>10.7368793487549</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.3350868225098</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9371957778931</v>
+        <v>10.9371948242188</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>11.5970897674561</v>
       </c>
       <c r="G821" t="n">
-        <v>10.2828321456909</v>
+        <v>10.2828330993652</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147802352905</v>
+        <v>10.8147811889648</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G830" t="n">
-        <v>10.76136302948</v>
+        <v>10.7613620758057</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295736312866</v>
+        <v>10.3295726776123</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>11.5343351364136</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2271900177002</v>
+        <v>10.2271890640259</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>12.0564546585083</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6901397705078</v>
+        <v>10.6901388168335</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G842" t="n">
-        <v>10.5499200820923</v>
+        <v>10.549919128418</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G845" t="n">
-        <v>10.2383184432983</v>
+        <v>10.2383193969727</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>11.3385400772095</v>
       </c>
       <c r="G846" t="n">
-        <v>10.0535831451416</v>
+        <v>10.0535840988159</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>10.977071762085</v>
       </c>
       <c r="G848" t="n">
-        <v>9.73307800292969</v>
+        <v>9.733078956604</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G851" t="n">
-        <v>9.33912658691406</v>
+        <v>9.33912754058838</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>10.1411781311035</v>
       </c>
       <c r="G852" t="n">
-        <v>8.99191379547119</v>
+        <v>8.99191474914551</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>10.203932762146</v>
       </c>
       <c r="G854" t="n">
-        <v>9.04755783081055</v>
+        <v>9.04755687713623</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G855" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>10.4072589874268</v>
       </c>
       <c r="G856" t="n">
-        <v>9.22784233093262</v>
+        <v>9.22784042358398</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>10.5101757049561</v>
       </c>
       <c r="G860" t="n">
-        <v>9.31909561157227</v>
+        <v>9.31909465789795</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G861" t="n">
-        <v>9.25232315063477</v>
+        <v>9.25232410430908</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G863" t="n">
-        <v>8.7760181427002</v>
+        <v>8.77601909637451</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G864" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G867" t="n">
-        <v>8.7604398727417</v>
+        <v>8.76043891906738</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>9.62156772613525</v>
       </c>
       <c r="G868" t="n">
-        <v>8.53118896484375</v>
+        <v>8.53118991851807</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G869" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G871" t="n">
-        <v>9.07203960418701</v>
+        <v>9.07204151153564</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>10.768726348877</v>
       </c>
       <c r="G874" t="n">
-        <v>9.5483455657959</v>
+        <v>9.54834461212158</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395671844482</v>
+        <v>9.58395576477051</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G877" t="n">
-        <v>9.33912658691406</v>
+        <v>9.33912754058838</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G879" t="n">
-        <v>9.21671199798584</v>
+        <v>9.21671295166016</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>11.0699491500854</v>
       </c>
       <c r="G883" t="n">
-        <v>9.81543159484863</v>
+        <v>9.81543064117432</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079208374023</v>
+        <v>9.69079113006592</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G885" t="n">
-        <v>9.49047565460205</v>
+        <v>9.49047470092773</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>10.9218482971191</v>
       </c>
       <c r="G886" t="n">
-        <v>9.68411445617676</v>
+        <v>9.68411350250244</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>10.9820928573608</v>
       </c>
       <c r="G888" t="n">
-        <v>9.73753070831299</v>
+        <v>9.7375316619873</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G890" t="n">
-        <v>9.69746685028076</v>
+        <v>9.69746780395508</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.948974609375</v>
+        <v>9.94897556304932</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>11.3987846374512</v>
       </c>
       <c r="G898" t="n">
-        <v>10.1070003509521</v>
+        <v>10.1070013046265</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>11.4715795516968</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1715459823608</v>
+        <v>10.1715469360352</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304798126221</v>
+        <v>9.71304893493652</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>11.4941720962524</v>
       </c>
       <c r="G907" t="n">
-        <v>10.1915788650513</v>
+        <v>10.191577911377</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>11.5845394134521</v>
       </c>
       <c r="G908" t="n">
-        <v>10.2717046737671</v>
+        <v>10.2717037200928</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794006347656</v>
+        <v>9.99794101715088</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>10.7411136627197</v>
       </c>
       <c r="G913" t="n">
-        <v>9.5238618850708</v>
+        <v>9.52386093139648</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G914" t="n">
-        <v>9.2078104019165</v>
+        <v>9.20780944824219</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>10.4248304367065</v>
       </c>
       <c r="G915" t="n">
-        <v>9.24342155456543</v>
+        <v>9.24342060089111</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>10.3721160888672</v>
       </c>
       <c r="G917" t="n">
-        <v>9.19668006896973</v>
+        <v>9.19668102264404</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G918" t="n">
-        <v>9.12545776367188</v>
+        <v>9.12545871734619</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G919" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G920" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.95185089111328</v>
+        <v>8.9518518447876</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>10.4474220275879</v>
       </c>
       <c r="G925" t="n">
-        <v>9.26345348358154</v>
+        <v>9.26345252990723</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G926" t="n">
-        <v>9.31464385986328</v>
+        <v>9.31464290618896</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G929" t="n">
-        <v>9.41480159759521</v>
+        <v>9.41480255126953</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>11.4665603637695</v>
       </c>
       <c r="G939" t="n">
-        <v>10.1670961380005</v>
+        <v>10.1670951843262</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.104775428772</v>
+        <v>10.1047735214233</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136770248413</v>
+        <v>10.1136779785156</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403865814209</v>
+        <v>10.1403856277466</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230537414551</v>
+        <v>10.4230527877808</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>11.1854181289673</v>
       </c>
       <c r="G945" t="n">
-        <v>9.91781425476074</v>
+        <v>9.91781520843506</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G946" t="n">
-        <v>9.87107467651367</v>
+        <v>9.87107372283936</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G947" t="n">
-        <v>9.84659099578857</v>
+        <v>9.84659194946289</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>10.0683822631836</v>
       </c>
       <c r="G955" t="n">
-        <v>8.92736911773682</v>
+        <v>8.9273681640625</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>10.0332403182983</v>
       </c>
       <c r="G956" t="n">
-        <v>8.89620780944824</v>
+        <v>8.89620876312256</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>10.1612596511841</v>
       </c>
       <c r="G960" t="n">
-        <v>9.00971984863281</v>
+        <v>9.00972080230713</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>10.3419942855835</v>
       </c>
       <c r="G961" t="n">
-        <v>9.16997241973877</v>
+        <v>9.16997337341309</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>10.3219118118286</v>
       </c>
       <c r="G975" t="n">
-        <v>9.15216541290283</v>
+        <v>9.15216636657715</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.03642845153809</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812492370605</v>
+        <v>9.40812397003174</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>10.8164196014404</v>
       </c>
       <c r="G993" t="n">
-        <v>9.59063243865967</v>
+        <v>9.59063339233398</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>10.7135019302368</v>
       </c>
       <c r="G996" t="n">
-        <v>9.4993782043457</v>
+        <v>9.49937915802002</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G998" t="n">
-        <v>9.07203960418701</v>
+        <v>9.07204151153564</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.25232315063477</v>
+        <v>9.25232410430908</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.21671199798584</v>
+        <v>9.21671295166016</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467578887939</v>
+        <v>9.33467674255371</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.5616979598999</v>
+        <v>9.56169891357422</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>11.1126232147217</v>
       </c>
       <c r="G1029" t="n">
-        <v>9.85326862335205</v>
+        <v>9.85326957702637</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G1030" t="n">
-        <v>9.4615421295166</v>
+        <v>9.46154117584229</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G1032" t="n">
-        <v>9.12545776367188</v>
+        <v>9.12545871734619</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.31974601745605</v>
+        <v>8.31974697113037</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.34645557403564</v>
+        <v>8.34645462036133</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>9.41573238372803</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.34868049621582</v>
+        <v>8.34868144989014</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>9.51362991333008</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.4354829788208</v>
+        <v>8.43548393249512</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>9.42577266693115</v>
       </c>
       <c r="G1052" t="n">
-        <v>8.35758399963379</v>
+        <v>8.35758304595947</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657657623291</v>
+        <v>7.71657609939575</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754774093628</v>
+        <v>7.62754726409912</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.60083818435669</v>
+        <v>7.60083866119385</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585174560547</v>
+        <v>7.25585126876831</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.95000410079956</v>
+        <v>4.9500036239624</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.95000410079956</v>
+        <v>4.9500036239624</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.95009994506836</v>
       </c>
       <c r="G1068" t="n">
-        <v>4.38912296295166</v>
+        <v>4.3891224861145</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>5.18605804443359</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.59834003448486</v>
+        <v>4.59834051132202</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342130661011</v>
+        <v>5.00342178344727</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.88991022109985</v>
+        <v>4.88990926742554</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>5.85627889633179</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.19260787963867</v>
+        <v>5.19260740280151</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>5.89393186569214</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.22599363327026</v>
+        <v>5.22599315643311</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>5.95919704437256</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.28386259078979</v>
+        <v>5.28386211395264</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.0219521522522</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.33950519561768</v>
+        <v>5.33950567245483</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>5.9014630317688</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.23267126083374</v>
+        <v>5.23267078399658</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.29276561737061</v>
+        <v>5.29276514053345</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.95445537567139</v>
+        <v>4.95445489883423</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>5.67303514480591</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.03013038635254</v>
+        <v>5.03012990951538</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>5.55505609512329</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.92552137374878</v>
+        <v>4.92552089691162</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928503036499</v>
+        <v>5.19928550720215</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041393280029</v>
+        <v>5.21041345596313</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>5.73328018188477</v>
       </c>
       <c r="G1100" t="n">
-        <v>5.08354806900024</v>
+        <v>5.08354759216309</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>5.79101419448853</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.1347393989563</v>
+        <v>5.13473892211914</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>5.62032079696655</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.98338937759399</v>
+        <v>4.98338985443115</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470794677734</v>
+        <v>5.11470746994019</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248207092285</v>
+        <v>5.11248159408569</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.92329549789429</v>
+        <v>4.92329597473145</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -69116,6 +69116,32 @@
         <v>4.11999988555908</v>
       </c>
       <c r="H2644" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2645">
+      <c r="A2645" s="1" t="n">
+        <v>46174.2916666667</v>
+      </c>
+      <c r="B2645" t="n">
+        <v>17668746</v>
+      </c>
+      <c r="C2645" t="n">
+        <v>4.2519998550415</v>
+      </c>
+      <c r="D2645" t="n">
+        <v>4.17600011825562</v>
+      </c>
+      <c r="E2645" t="n">
+        <v>4.17799997329712</v>
+      </c>
+      <c r="F2645" t="n">
+        <v>4.23400020599365</v>
+      </c>
+      <c r="G2645" t="n">
+        <v>4.23400020599365</v>
+      </c>
+      <c r="H2645" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -473,7 +473,7 @@
         <v>22.3245735168457</v>
       </c>
       <c r="G4" t="n">
-        <v>19.7946090698242</v>
+        <v>19.7946071624756</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>22.4193687438965</v>
       </c>
       <c r="G8" t="n">
-        <v>19.8786602020264</v>
+        <v>19.878662109375</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>22.1665782928467</v>
       </c>
       <c r="G9" t="n">
-        <v>19.65452003479</v>
+        <v>19.6545181274414</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>22.1823787689209</v>
       </c>
       <c r="G10" t="n">
-        <v>19.6685276031494</v>
+        <v>19.668529510498</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>20.9184246063232</v>
       </c>
       <c r="G11" t="n">
-        <v>18.547815322876</v>
+        <v>18.5478134155273</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>19.8440647125244</v>
       </c>
       <c r="G12" t="n">
-        <v>17.5952072143555</v>
+        <v>17.5952091217041</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811977386475</v>
+        <v>17.5811958312988</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460279464722</v>
+        <v>15.7460289001465</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>16.7157802581787</v>
       </c>
       <c r="G15" t="n">
-        <v>14.8214406967163</v>
+        <v>14.821439743042</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>15.7389078140259</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9552736282349</v>
+        <v>13.9552726745605</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087121963501</v>
+        <v>12.6087112426758</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.0530023574829</v>
       </c>
       <c r="G26" t="n">
-        <v>11.5737524032593</v>
+        <v>11.573751449585</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617107391357</v>
+        <v>8.16617202758789</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G30" t="n">
-        <v>7.08892250061035</v>
+        <v>7.08892202377319</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G31" t="n">
-        <v>6.70832395553589</v>
+        <v>6.70832347869873</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393510818481</v>
+        <v>6.74393558502197</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.87747859954834</v>
+        <v>6.8774790763855</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51181030273438</v>
+        <v>7.51180982589722</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.30120658874512</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36045980453491</v>
+        <v>7.36046028137207</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243886947632</v>
+        <v>7.91243934631348</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G40" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>10.6884002685547</v>
       </c>
       <c r="G47" t="n">
-        <v>9.47712230682373</v>
+        <v>9.47712135314941</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.0771427154541</v>
+        <v>8.07714366912842</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811340332031</v>
+        <v>7.98811388015747</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683204650879</v>
+        <v>8.58683300018311</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.26261138916016</v>
       </c>
       <c r="G54" t="n">
-        <v>8.21291255950928</v>
+        <v>8.21291351318359</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.31752109527588</v>
+        <v>8.3175220489502</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G59" t="n">
-        <v>8.2062349319458</v>
+        <v>8.20623397827148</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G60" t="n">
-        <v>7.75218820571899</v>
+        <v>7.75218725204468</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.34488010406494</v>
+        <v>7.3448805809021</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870714187622</v>
+        <v>7.65870809555054</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.78159713745117</v>
       </c>
       <c r="G66" t="n">
-        <v>6.89973592758179</v>
+        <v>6.89973640441895</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.61341381072998</v>
       </c>
       <c r="G68" t="n">
-        <v>6.75061225891113</v>
+        <v>6.75061273574829</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365779876709</v>
+        <v>7.27365732192993</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G70" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G71" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.8634729385376</v>
+        <v>7.86347436904907</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09940052032471</v>
+        <v>8.09939956665039</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.87102127075195</v>
       </c>
       <c r="G74" t="n">
-        <v>7.86569976806641</v>
+        <v>7.86570072174072</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.39816093444824</v>
       </c>
       <c r="G80" t="n">
-        <v>8.33310031890869</v>
+        <v>8.33310127258301</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912082672119</v>
+        <v>8.62912178039551</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G84" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G86" t="n">
-        <v>8.54009246826172</v>
+        <v>8.54009342193604</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G87" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G88" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G89" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.36803913116455</v>
       </c>
       <c r="G90" t="n">
-        <v>8.30639266967773</v>
+        <v>8.30639171600342</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.26855373382568</v>
+        <v>8.2685546875</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542102813721</v>
+        <v>8.39542007446289</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G97" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588752746582</v>
+        <v>7.98588848114014</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701690673828</v>
+        <v>7.99701642990112</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G103" t="n">
-        <v>8.3976469039917</v>
+        <v>8.39764595031738</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889585494995</v>
+        <v>7.77889633178711</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701690673828</v>
+        <v>7.99701642990112</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G113" t="n">
-        <v>8.67363548278809</v>
+        <v>8.6736364364624</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325325012207</v>
+        <v>7.72325372695923</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660707473755</v>
+        <v>7.73660612106323</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808242797852</v>
+        <v>7.96808290481567</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G119" t="n">
-        <v>8.2062349319458</v>
+        <v>8.20623397827148</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.8851375579834</v>
       </c>
       <c r="G122" t="n">
-        <v>8.76488971710205</v>
+        <v>8.76489067077637</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.05933666229248</v>
+        <v>8.0593376159668</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.5919361114502</v>
+        <v>7.59193563461304</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78557395935059</v>
+        <v>7.78557348251343</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.86349010467529</v>
       </c>
       <c r="G127" t="n">
-        <v>7.85902261734009</v>
+        <v>7.85902214050293</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.60650730133057</v>
       </c>
       <c r="G130" t="n">
-        <v>8.51783657073975</v>
+        <v>8.51783561706543</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.71147441864014</v>
+        <v>8.7114725112915</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420257568359</v>
+        <v>9.03420352935791</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>10.3771362304688</v>
       </c>
       <c r="G139" t="n">
-        <v>9.20113182067871</v>
+        <v>9.20113277435303</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>10.5679111480713</v>
       </c>
       <c r="G140" t="n">
-        <v>9.37028789520264</v>
+        <v>9.37028694152832</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G141" t="n">
-        <v>9.55947303771973</v>
+        <v>9.55947208404541</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>10.6934204101562</v>
       </c>
       <c r="G146" t="n">
-        <v>9.48157215118408</v>
+        <v>9.4815731048584</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427219390869</v>
+        <v>9.78427124023438</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G148" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G149" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.37807941436768</v>
       </c>
       <c r="G153" t="n">
-        <v>8.31529426574707</v>
+        <v>8.31529521942139</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.52228736877441</v>
+        <v>8.52228832244873</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G160" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.98303604125977</v>
       </c>
       <c r="G164" t="n">
-        <v>8.85169410705566</v>
+        <v>8.85169315338135</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>10.4449110031128</v>
       </c>
       <c r="G165" t="n">
-        <v>9.26122665405273</v>
+        <v>9.26122570037842</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G166" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>10.442400932312</v>
       </c>
       <c r="G168" t="n">
-        <v>9.25899982452393</v>
+        <v>9.25900077819824</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548873901367</v>
+        <v>9.14548778533936</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>10.457462310791</v>
       </c>
       <c r="G174" t="n">
-        <v>9.27235507965088</v>
+        <v>9.2723560333252</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G177" t="n">
-        <v>9.23451805114746</v>
+        <v>9.23451900482178</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G178" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G182" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.95887660980225</v>
       </c>
       <c r="G183" t="n">
-        <v>7.94359874725342</v>
+        <v>7.94359827041626</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.90365314483643</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89463376998901</v>
+        <v>7.89463329315186</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.91871356964111</v>
       </c>
       <c r="G189" t="n">
-        <v>7.90798759460449</v>
+        <v>7.90798664093018</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.7388334274292</v>
+        <v>7.73883247375488</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G193" t="n">
-        <v>8.38429164886475</v>
+        <v>8.38429260253906</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G196" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.77217960357666</v>
       </c>
       <c r="G198" t="n">
-        <v>8.66473293304443</v>
+        <v>8.66473388671875</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G203" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10.3696060180664</v>
       </c>
       <c r="G204" t="n">
-        <v>9.19445610046387</v>
+        <v>9.19445514678955</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G210" t="n">
-        <v>9.31464290618896</v>
+        <v>9.31464385986328</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G219" t="n">
-        <v>8.38429164886475</v>
+        <v>8.38429260253906</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G220" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G221" t="n">
-        <v>8.73373031616211</v>
+        <v>8.73373126983643</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G224" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.0834436416626</v>
       </c>
       <c r="G226" t="n">
-        <v>8.94072246551514</v>
+        <v>8.94072341918945</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G228" t="n">
-        <v>8.67363548278809</v>
+        <v>8.6736364364624</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G230" t="n">
-        <v>8.9451732635498</v>
+        <v>8.94517421722412</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G232" t="n">
-        <v>9.16329479217529</v>
+        <v>9.16329383850098</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G233" t="n">
-        <v>8.92514228820801</v>
+        <v>8.92514324188232</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G234" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.9695415496826</v>
       </c>
       <c r="G237" t="n">
-        <v>9.72640228271484</v>
+        <v>9.72640323638916</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>11.484130859375</v>
       </c>
       <c r="G240" t="n">
-        <v>10.182674407959</v>
+        <v>10.1826753616333</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.4088249206543</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1159038543701</v>
+        <v>10.1159029006958</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.8230066299438</v>
       </c>
       <c r="G245" t="n">
-        <v>10.4831476211548</v>
+        <v>10.4831466674805</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.9309453964233</v>
       </c>
       <c r="G247" t="n">
-        <v>10.5788536071777</v>
+        <v>10.5788545608521</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G251" t="n">
-        <v>10.9883871078491</v>
+        <v>10.9883861541748</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G252" t="n">
-        <v>11.2844085693359</v>
+        <v>11.2844076156616</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>12.8772878646851</v>
       </c>
       <c r="G253" t="n">
-        <v>11.417950630188</v>
+        <v>11.4179496765137</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>13.2287149429321</v>
       </c>
       <c r="G255" t="n">
-        <v>11.7295513153076</v>
+        <v>11.7295522689819</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076108932495</v>
+        <v>11.9076099395752</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>13.9817733764648</v>
       </c>
       <c r="G260" t="n">
-        <v>12.3972682952881</v>
+        <v>12.3972692489624</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195261001587</v>
+        <v>12.4195251464844</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858243942261</v>
+        <v>12.1858253479004</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>12.8647365570068</v>
       </c>
       <c r="G267" t="n">
-        <v>11.4068212509155</v>
+        <v>11.4068222045898</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G270" t="n">
-        <v>11.2844085693359</v>
+        <v>11.2844076156616</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619939804077</v>
+        <v>11.1619920730591</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>12.4455347061157</v>
       </c>
       <c r="G273" t="n">
-        <v>11.0351257324219</v>
+        <v>11.0351266860962</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>13.3040208816528</v>
       </c>
       <c r="G275" t="n">
-        <v>11.7963228225708</v>
+        <v>11.7963237762451</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960092544556</v>
+        <v>11.5960083007812</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G281" t="n">
-        <v>10.2383193969727</v>
+        <v>10.2383184432983</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141502380371</v>
+        <v>10.4141492843628</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.251672744751</v>
+        <v>10.2516717910767</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.3985710144043</v>
+        <v>10.39857006073</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651838302612</v>
+        <v>10.3651847839355</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.6874570846558</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3629589080811</v>
+        <v>10.3629579544067</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>10.5754413604736</v>
       </c>
       <c r="G298" t="n">
-        <v>9.37696361541748</v>
+        <v>9.3769645690918</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.6632976531982</v>
       </c>
       <c r="G301" t="n">
-        <v>9.45486450195312</v>
+        <v>9.45486354827881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10.6984405517578</v>
       </c>
       <c r="G302" t="n">
-        <v>9.48602485656738</v>
+        <v>9.48602390289307</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10.4675025939941</v>
       </c>
       <c r="G304" t="n">
-        <v>9.28125858306885</v>
+        <v>9.28125762939453</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520614624023</v>
+        <v>8.96520709991455</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10.218994140625</v>
       </c>
       <c r="G310" t="n">
-        <v>9.06091117858887</v>
+        <v>9.06091213226318</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G313" t="n">
-        <v>9.01639652252197</v>
+        <v>9.01639747619629</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539390563965</v>
+        <v>9.08539485931396</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.1336479187012</v>
       </c>
       <c r="G315" t="n">
-        <v>8.98523807525635</v>
+        <v>8.98523712158203</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G319" t="n">
-        <v>9.39254379272461</v>
+        <v>9.39254474639893</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G320" t="n">
-        <v>9.46154117584229</v>
+        <v>9.4615421295166</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77981853485107</v>
+        <v>9.77981948852539</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G324" t="n">
-        <v>9.49047470092773</v>
+        <v>9.49047565460205</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G325" t="n">
-        <v>9.51050758361816</v>
+        <v>9.51050662994385</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>10.7310733795166</v>
       </c>
       <c r="G326" t="n">
-        <v>9.51495933532715</v>
+        <v>9.51495838165283</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>10.5227270126343</v>
       </c>
       <c r="G328" t="n">
-        <v>9.33022308349609</v>
+        <v>9.33022403717041</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G330" t="n">
-        <v>9.12990951538086</v>
+        <v>9.12990856170654</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.7671594619751</v>
       </c>
       <c r="G335" t="n">
-        <v>8.66028213500977</v>
+        <v>8.66028118133545</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.20335865020752</v>
+        <v>9.2033576965332</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G353" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.80481243133545</v>
       </c>
       <c r="G354" t="n">
-        <v>8.69366836547852</v>
+        <v>8.6936674118042</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G357" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.99033975601196</v>
+        <v>7.9903392791748</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215579986572</v>
+        <v>7.73215627670288</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G368" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>8.88106060028076</v>
       </c>
       <c r="G372" t="n">
-        <v>7.8746018409729</v>
+        <v>7.87460136413574</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G373" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G378" t="n">
-        <v>7.18017673492432</v>
+        <v>7.18017721176147</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>8.07779979705811</v>
       </c>
       <c r="G380" t="n">
-        <v>7.16237115859985</v>
+        <v>7.16237163543701</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914266586304</v>
+        <v>7.22914218902588</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817245483398</v>
+        <v>7.31817150115967</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G383" t="n">
-        <v>7.23804569244385</v>
+        <v>7.23804521560669</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055463790894</v>
+        <v>7.42055559158325</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.68024635314941</v>
       </c>
       <c r="G386" t="n">
-        <v>7.6965446472168</v>
+        <v>7.69654512405396</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.44428825378418</v>
       </c>
       <c r="G387" t="n">
-        <v>7.48732662200928</v>
+        <v>7.48732709884644</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390846252441</v>
+        <v>7.43390893936157</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G392" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G393" t="n">
-        <v>7.7455096244812</v>
+        <v>7.74551010131836</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.85679721832275</v>
+        <v>7.85679578781128</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.514573097229</v>
       </c>
       <c r="G398" t="n">
-        <v>7.54964637756348</v>
+        <v>7.54964685440063</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842311859131</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G400" t="n">
-        <v>7.61196756362915</v>
+        <v>7.61196708679199</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G403" t="n">
-        <v>7.59416151046753</v>
+        <v>7.59416103363037</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>8.6953067779541</v>
       </c>
       <c r="G404" t="n">
-        <v>7.70989847183228</v>
+        <v>7.70989894866943</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G406" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757966995239</v>
+        <v>7.64757871627808</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428636550903</v>
+        <v>7.67428731918335</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249792098999</v>
+        <v>7.24249744415283</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701210021973</v>
+        <v>7.28701162338257</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G416" t="n">
-        <v>7.26475477218628</v>
+        <v>7.26475429534912</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>8.08281993865967</v>
       </c>
       <c r="G419" t="n">
-        <v>7.16682195663452</v>
+        <v>7.16682243347168</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>7.84184217453003</v>
       </c>
       <c r="G421" t="n">
-        <v>6.95315361022949</v>
+        <v>6.95315408706665</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.61592388153076</v>
       </c>
       <c r="G422" t="n">
-        <v>6.75283861160278</v>
+        <v>6.75283813476562</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>7.70127105712891</v>
       </c>
       <c r="G423" t="n">
-        <v>6.82851362228394</v>
+        <v>6.82851314544678</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>7.68621015548706</v>
       </c>
       <c r="G424" t="n">
-        <v>6.8151593208313</v>
+        <v>6.81515884399414</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.40004777908325</v>
       </c>
       <c r="G426" t="n">
-        <v>6.56142663955688</v>
+        <v>6.56142616271973</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.9397988319397</v>
+        <v>6.93979835510254</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.74645376205444</v>
       </c>
       <c r="G428" t="n">
-        <v>6.86857557296753</v>
+        <v>6.86857604980469</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G432" t="n">
-        <v>7.22469091415405</v>
+        <v>7.22469139099121</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.96233081817627</v>
       </c>
       <c r="G433" t="n">
-        <v>7.05998849868774</v>
+        <v>7.05998802185059</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409860610962</v>
+        <v>7.55409908294678</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.42922687530518</v>
       </c>
       <c r="G438" t="n">
-        <v>7.4739727973938</v>
+        <v>7.47397232055664</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G440" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538429260254</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692350387573</v>
+        <v>7.93692302703857</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504360198975</v>
+        <v>8.15504264831543</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G462" t="n">
-        <v>7.38939476013184</v>
+        <v>7.38939523696899</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.42945718765259</v>
+        <v>7.42945766448975</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G464" t="n">
-        <v>7.23804569244385</v>
+        <v>7.23804521560669</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.7143497467041</v>
+        <v>7.71435022354126</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538429260254</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479198455811</v>
+        <v>7.99479103088379</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.63914012908936</v>
       </c>
       <c r="G472" t="n">
-        <v>8.54677104949951</v>
+        <v>8.5467700958252</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G476" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.49354839324951</v>
       </c>
       <c r="G478" t="n">
-        <v>8.4176778793335</v>
+        <v>8.41767883300781</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G480" t="n">
-        <v>7.78557395935059</v>
+        <v>7.78557348251343</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757966995239</v>
+        <v>7.64757871627808</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G482" t="n">
-        <v>7.62532234191895</v>
+        <v>7.62532186508179</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G483" t="n">
-        <v>7.62532234191895</v>
+        <v>7.62532186508179</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G484" t="n">
-        <v>7.69209432601929</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576267242432</v>
+        <v>7.90576219558716</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344244003296</v>
+        <v>7.84344148635864</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>8.60494041442871</v>
       </c>
       <c r="G488" t="n">
-        <v>7.62977266311646</v>
+        <v>7.62977313995361</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G490" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G491" t="n">
-        <v>7.7455096244812</v>
+        <v>7.74551010131836</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G495" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>8.60996055603027</v>
       </c>
       <c r="G499" t="n">
-        <v>7.6342248916626</v>
+        <v>7.63422441482544</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G501" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.74996280670166</v>
+        <v>7.74996185302734</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G507" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.61403846740723</v>
       </c>
       <c r="G510" t="n">
-        <v>8.52451324462891</v>
+        <v>8.52451419830322</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.55379295349121</v>
       </c>
       <c r="G511" t="n">
-        <v>8.47109508514404</v>
+        <v>8.47109603881836</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.50670623779297</v>
+        <v>8.50670719146729</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.50225639343262</v>
+        <v>8.5022554397583</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G514" t="n">
-        <v>8.73373031616211</v>
+        <v>8.73373126983643</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.76464939117432</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65805625915527</v>
+        <v>8.65805530548096</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>10.1210966110229</v>
       </c>
       <c r="G519" t="n">
-        <v>8.97410869598389</v>
+        <v>8.9741096496582</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G522" t="n">
-        <v>9.12990951538086</v>
+        <v>9.12990856170654</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>10.1813411712646</v>
       </c>
       <c r="G524" t="n">
-        <v>9.02752590179443</v>
+        <v>9.02752685546875</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G527" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G528" t="n">
-        <v>9.16552066802979</v>
+        <v>9.1655216217041</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833885192871</v>
+        <v>8.83833980560303</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>9.46593570709229</v>
       </c>
       <c r="G533" t="n">
-        <v>8.39319515228271</v>
+        <v>8.3931941986084</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.41990375518799</v>
+        <v>8.41990566253662</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>9.30277442932129</v>
       </c>
       <c r="G535" t="n">
-        <v>8.24852466583252</v>
+        <v>8.2485237121582</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617107391357</v>
+        <v>8.16617202758789</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660707473755</v>
+        <v>7.73660612106323</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G540" t="n">
-        <v>7.61196756362915</v>
+        <v>7.61196708679199</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519510269165</v>
+        <v>7.54519605636597</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>8.4543285369873</v>
       </c>
       <c r="G543" t="n">
-        <v>7.49623012542725</v>
+        <v>7.49622964859009</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.7143497467041</v>
+        <v>7.71435022354126</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.83587837219238</v>
       </c>
       <c r="G550" t="n">
-        <v>7.83453893661499</v>
+        <v>7.83453989028931</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.76331663131714</v>
+        <v>7.7633171081543</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G553" t="n">
-        <v>7.50068044662476</v>
+        <v>7.50068092346191</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.5229377746582</v>
+        <v>7.52293872833252</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368829727173</v>
+        <v>7.29368877410889</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G557" t="n">
-        <v>7.50068044662476</v>
+        <v>7.50068092346191</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.56979656219482</v>
       </c>
       <c r="G558" t="n">
-        <v>7.59861183166504</v>
+        <v>7.5986123085022</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663948059082</v>
+        <v>7.75663805007935</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G560" t="n">
-        <v>7.75218820571899</v>
+        <v>7.75218725204468</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.31124782562256</v>
       </c>
       <c r="G564" t="n">
-        <v>7.36936330795288</v>
+        <v>7.36936378479004</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613481521606</v>
+        <v>7.43613433837891</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.32128810882568</v>
       </c>
       <c r="G567" t="n">
-        <v>7.37826633453369</v>
+        <v>7.37826585769653</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>8.17820739746094</v>
       </c>
       <c r="G570" t="n">
-        <v>7.25139999389648</v>
+        <v>7.25140047073364</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G573" t="n">
-        <v>7.07111692428589</v>
+        <v>7.07111740112305</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G578" t="n">
-        <v>6.98876571655273</v>
+        <v>6.98876523971558</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744762420654</v>
+        <v>6.85744667053223</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G581" t="n">
-        <v>7.08892250061035</v>
+        <v>7.08892202377319</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G583" t="n">
-        <v>7.22469091415405</v>
+        <v>7.22469139099121</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>8.1079216003418</v>
       </c>
       <c r="G584" t="n">
-        <v>7.18907928466797</v>
+        <v>7.18907976150513</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G585" t="n">
-        <v>7.18017673492432</v>
+        <v>7.18017721176147</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842311859131</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610431671143</v>
+        <v>7.41610383987427</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G590" t="n">
-        <v>7.26475477218628</v>
+        <v>7.26475429534912</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G591" t="n">
-        <v>6.98876571655273</v>
+        <v>6.98876523971558</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766731262207</v>
+        <v>6.99766778945923</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443929672241</v>
+        <v>7.06443881988525</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>7.92969799041748</v>
       </c>
       <c r="G596" t="n">
-        <v>7.03105354309082</v>
+        <v>7.03105306625366</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G601" t="n">
-        <v>7.38939476013184</v>
+        <v>7.38939523696899</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G602" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.83242416381836</v>
       </c>
       <c r="G605" t="n">
-        <v>8.71815013885498</v>
+        <v>8.7181510925293</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G607" t="n">
-        <v>8.54009246826172</v>
+        <v>8.54009342193604</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G608" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>10.0909738540649</v>
       </c>
       <c r="G609" t="n">
-        <v>8.94740009307861</v>
+        <v>8.9473991394043</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37538909912109</v>
+        <v>8.37539005279541</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065475463867</v>
+        <v>8.19065380096436</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>8.79822540283203</v>
       </c>
       <c r="G613" t="n">
-        <v>7.80115413665771</v>
+        <v>7.80115365982056</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.31783485412598</v>
       </c>
       <c r="G620" t="n">
-        <v>8.26187801361084</v>
+        <v>8.26187896728516</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G621" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>9.72448635101318</v>
       </c>
       <c r="G622" t="n">
-        <v>8.62244415283203</v>
+        <v>8.62244510650635</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>9.85250568389893</v>
       </c>
       <c r="G623" t="n">
-        <v>8.73595523834229</v>
+        <v>8.7359561920166</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902599334717</v>
+        <v>8.56902694702148</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G629" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G636" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G640" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.71147441864014</v>
+        <v>8.7114725112915</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G644" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009727478027</v>
+        <v>9.25009632110596</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G646" t="n">
-        <v>9.39254379272461</v>
+        <v>9.39254474639893</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>10.0181789398193</v>
       </c>
       <c r="G648" t="n">
-        <v>8.88285350799561</v>
+        <v>8.88285446166992</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G650" t="n">
-        <v>9.01639652252197</v>
+        <v>9.01639747619629</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100505828857</v>
+        <v>9.12100601196289</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G654" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G662" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G664" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>11.200478553772</v>
       </c>
       <c r="G668" t="n">
-        <v>9.93116760253906</v>
+        <v>9.93116855621338</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>11.6322326660156</v>
       </c>
       <c r="G669" t="n">
-        <v>10.3139925003052</v>
+        <v>10.3139934539795</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>11.6046199798584</v>
       </c>
       <c r="G676" t="n">
-        <v>10.2895088195801</v>
+        <v>10.2895097732544</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G678" t="n">
-        <v>10.0157461166382</v>
+        <v>10.0157451629639</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99349021911621</v>
+        <v>9.99348926544189</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694787979126</v>
+        <v>10.2694797515869</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>11.5017032623291</v>
       </c>
       <c r="G688" t="n">
-        <v>10.1982555389404</v>
+        <v>10.1982564926147</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>11.9259252548218</v>
       </c>
       <c r="G689" t="n">
-        <v>10.5744018554688</v>
+        <v>10.5744028091431</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>11.328498840332</v>
       </c>
       <c r="G690" t="n">
-        <v>10.0446805953979</v>
+        <v>10.0446796417236</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G691" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>12.0489253997803</v>
       </c>
       <c r="G692" t="n">
-        <v>10.6834630966187</v>
+        <v>10.683464050293</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.7569122314453</v>
+        <v>10.756911277771</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>12.4580860137939</v>
       </c>
       <c r="G697" t="n">
-        <v>11.0462560653687</v>
+        <v>11.0462551116943</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>13.2086343765259</v>
       </c>
       <c r="G699" t="n">
-        <v>11.7117471694946</v>
+        <v>11.7117462158203</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>13.5500202178955</v>
       </c>
       <c r="G702" t="n">
-        <v>12.0144443511963</v>
+        <v>12.014443397522</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856676101685</v>
+        <v>12.0856685638428</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395784378052</v>
+        <v>11.0395774841309</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>12.7065954208374</v>
       </c>
       <c r="G712" t="n">
-        <v>11.2666025161743</v>
+        <v>11.2666015625</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>12.7015752792358</v>
       </c>
       <c r="G713" t="n">
-        <v>11.262149810791</v>
+        <v>11.2621507644653</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364070892334</v>
+        <v>10.4364080429077</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>11.7979049682617</v>
       </c>
       <c r="G721" t="n">
-        <v>10.4608907699585</v>
+        <v>10.4608898162842</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>11.8857622146606</v>
       </c>
       <c r="G723" t="n">
-        <v>10.5387907028198</v>
+        <v>10.5387916564941</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G725" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>11.7025184631348</v>
       </c>
       <c r="G727" t="n">
-        <v>10.3763132095337</v>
+        <v>10.376314163208</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G728" t="n">
-        <v>10.160418510437</v>
+        <v>10.1604175567627</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006391525269</v>
+        <v>10.3006381988525</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>11.7251100540161</v>
       </c>
       <c r="G730" t="n">
-        <v>10.3963451385498</v>
+        <v>10.3963441848755</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>10.5402994155884</v>
       </c>
       <c r="G735" t="n">
-        <v>9.34580421447754</v>
+        <v>9.34580516815186</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G736" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G738" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081249237061</v>
+        <v>8.29081153869629</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889585494995</v>
+        <v>7.77889633178711</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219158172607</v>
+        <v>8.46219253540039</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G744" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.65922069549561</v>
       </c>
       <c r="G745" t="n">
-        <v>8.5645751953125</v>
+        <v>8.56457614898682</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G749" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G752" t="n">
-        <v>8.25520038604736</v>
+        <v>8.25519943237305</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>9.33540630340576</v>
       </c>
       <c r="G753" t="n">
-        <v>8.27745819091797</v>
+        <v>8.27745723724365</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466617584229</v>
+        <v>7.91466569900513</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>8.81077575683594</v>
       </c>
       <c r="G756" t="n">
-        <v>7.81228160858154</v>
+        <v>7.81228256225586</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G759" t="n">
-        <v>7.59416151046753</v>
+        <v>7.59416103363037</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>8.17318725585938</v>
       </c>
       <c r="G760" t="n">
-        <v>7.24694871902466</v>
+        <v>7.24694919586182</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>8.12800407409668</v>
       </c>
       <c r="G761" t="n">
-        <v>7.20688581466675</v>
+        <v>7.20688629150391</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873331069946</v>
+        <v>6.96873378753662</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576267242432</v>
+        <v>7.90576219558716</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G771" t="n">
-        <v>8.3976469039917</v>
+        <v>8.39764595031738</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G772" t="n">
-        <v>8.25520038604736</v>
+        <v>8.25519943237305</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096832275391</v>
+        <v>8.39096927642822</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G778" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G779" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G781" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G783" t="n">
-        <v>8.9451732635498</v>
+        <v>8.94517421722412</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>10.3445043563843</v>
       </c>
       <c r="G787" t="n">
-        <v>9.17219829559326</v>
+        <v>9.17219924926758</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G788" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>10.4298496246338</v>
       </c>
       <c r="G789" t="n">
-        <v>9.2478723526001</v>
+        <v>9.24787139892578</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G792" t="n">
-        <v>8.8272123336792</v>
+        <v>8.82721138000488</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G796" t="n">
-        <v>9.4370584487915</v>
+        <v>9.43705940246582</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G799" t="n">
-        <v>9.41480255126953</v>
+        <v>9.41480159759521</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>10.8440322875977</v>
       </c>
       <c r="G803" t="n">
-        <v>9.61511707305908</v>
+        <v>9.61511611938477</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G805" t="n">
-        <v>10.160418510437</v>
+        <v>10.1604175567627</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232986450195</v>
+        <v>9.96232891082764</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496036529541</v>
+        <v>10.3496046066284</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>12.3150053024292</v>
       </c>
       <c r="G815" t="n">
-        <v>10.9193897247314</v>
+        <v>10.9193887710571</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>12.1091690063477</v>
       </c>
       <c r="G816" t="n">
-        <v>10.7368793487549</v>
+        <v>10.7368803024292</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>12.2145967483521</v>
       </c>
       <c r="G817" t="n">
-        <v>10.8303604125977</v>
+        <v>10.8303594589233</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G819" t="n">
-        <v>10.9883871078491</v>
+        <v>10.9883861541748</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147811889648</v>
+        <v>10.8147802352905</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>12.2522497177124</v>
       </c>
       <c r="G829" t="n">
-        <v>10.8637456893921</v>
+        <v>10.8637447357178</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>12.4856977462769</v>
       </c>
       <c r="G831" t="n">
-        <v>11.0707378387451</v>
+        <v>11.0707368850708</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>12.6312885284424</v>
       </c>
       <c r="G832" t="n">
-        <v>11.1998291015625</v>
+        <v>11.1998300552368</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>12.0991277694702</v>
       </c>
       <c r="G834" t="n">
-        <v>10.7279767990112</v>
+        <v>10.7279777526855</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G835" t="n">
-        <v>10.4386329650879</v>
+        <v>10.4386339187622</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295726776123</v>
+        <v>10.3295736312866</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>11.5343351364136</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2271890640259</v>
+        <v>10.2271909713745</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G839" t="n">
-        <v>10.4386329650879</v>
+        <v>10.4386339187622</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>11.3912544250488</v>
       </c>
       <c r="G844" t="n">
-        <v>10.1003246307373</v>
+        <v>10.100323677063</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G845" t="n">
-        <v>10.2383193969727</v>
+        <v>10.2383184432983</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>10.836501121521</v>
       </c>
       <c r="G849" t="n">
-        <v>9.60843944549561</v>
+        <v>9.60843849182129</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>10.4072589874268</v>
       </c>
       <c r="G856" t="n">
-        <v>9.22784042358398</v>
+        <v>9.2278413772583</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G858" t="n">
-        <v>9.27012920379639</v>
+        <v>9.2701301574707</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G859" t="n">
-        <v>9.16329479217529</v>
+        <v>9.16329383850098</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G864" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G869" t="n">
-        <v>8.72482872009277</v>
+        <v>8.72482776641846</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G871" t="n">
-        <v>9.07204151153564</v>
+        <v>9.07204055786133</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395576477051</v>
+        <v>9.58395671844482</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G876" t="n">
-        <v>9.23451805114746</v>
+        <v>9.23451900482178</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G878" t="n">
-        <v>9.27012920379639</v>
+        <v>9.2701301574707</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G879" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G880" t="n">
-        <v>9.55947303771973</v>
+        <v>9.55947208404541</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G881" t="n">
-        <v>9.60621356964111</v>
+        <v>9.6062126159668</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079113006592</v>
+        <v>9.69079208374023</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G885" t="n">
-        <v>9.49047470092773</v>
+        <v>9.49047565460205</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>10.9820928573608</v>
       </c>
       <c r="G888" t="n">
-        <v>9.7375316619873</v>
+        <v>9.73753070831299</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>11.0272760391235</v>
       </c>
       <c r="G893" t="n">
-        <v>9.7775936126709</v>
+        <v>9.77759456634521</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>11.3987846374512</v>
       </c>
       <c r="G898" t="n">
-        <v>10.1070013046265</v>
+        <v>10.1070003509521</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304893493652</v>
+        <v>9.71304798126221</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G906" t="n">
-        <v>10.0157461166382</v>
+        <v>10.0157451629639</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>11.4941720962524</v>
       </c>
       <c r="G907" t="n">
-        <v>10.191577911377</v>
+        <v>10.1915788650513</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>11.5845394134521</v>
       </c>
       <c r="G908" t="n">
-        <v>10.2717037200928</v>
+        <v>10.2717046737671</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794101715088</v>
+        <v>9.99794006347656</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>10.7411136627197</v>
       </c>
       <c r="G913" t="n">
-        <v>9.52386093139648</v>
+        <v>9.5238618850708</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>10.4248304367065</v>
       </c>
       <c r="G915" t="n">
-        <v>9.24342060089111</v>
+        <v>9.24342155456543</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G916" t="n">
-        <v>8.92514228820801</v>
+        <v>8.92514324188232</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G918" t="n">
-        <v>9.12545871734619</v>
+        <v>9.12545776367188</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G920" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.9518518447876</v>
+        <v>8.95185089111328</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G926" t="n">
-        <v>9.31464290618896</v>
+        <v>9.31464385986328</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>10.2842588424683</v>
       </c>
       <c r="G927" t="n">
-        <v>9.1187801361084</v>
+        <v>9.11878108978271</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>10.3545436859131</v>
       </c>
       <c r="G928" t="n">
-        <v>9.1810998916626</v>
+        <v>9.18110084533691</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G929" t="n">
-        <v>9.41480255126953</v>
+        <v>9.41480159759521</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>10.9092969894409</v>
       </c>
       <c r="G931" t="n">
-        <v>9.6729850769043</v>
+        <v>9.67298603057861</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>10.9067869186401</v>
       </c>
       <c r="G933" t="n">
-        <v>9.6707592010498</v>
+        <v>9.67076015472412</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G934" t="n">
-        <v>9.4370584487915</v>
+        <v>9.43705940246582</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.1047735214233</v>
+        <v>10.1047744750977</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136779785156</v>
+        <v>10.1136770248413</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403856277466</v>
+        <v>10.1403875350952</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230527877808</v>
+        <v>10.4230537414551</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>10.7862977981567</v>
       </c>
       <c r="G949" t="n">
-        <v>9.56392574310303</v>
+        <v>9.56392383575439</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>10.2164840698242</v>
       </c>
       <c r="G954" t="n">
-        <v>9.05868625640869</v>
+        <v>9.05868530273438</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G958" t="n">
-        <v>9.16552066802979</v>
+        <v>9.1655216217041</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>10.1612596511841</v>
       </c>
       <c r="G960" t="n">
-        <v>9.00972080230713</v>
+        <v>9.00971984863281</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G962" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G964" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G965" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>10.3294429779053</v>
       </c>
       <c r="G968" t="n">
-        <v>9.15884399414062</v>
+        <v>9.15884304046631</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>10.2792387008667</v>
       </c>
       <c r="G969" t="n">
-        <v>9.11432933807373</v>
+        <v>9.11433029174805</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65963077545166</v>
+        <v>9.65962982177734</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G974" t="n">
-        <v>9.51050758361816</v>
+        <v>9.51050662994385</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.03643035888672</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G978" t="n">
-        <v>9.60621356964111</v>
+        <v>9.6062126159668</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>11.2306022644043</v>
       </c>
       <c r="G981" t="n">
-        <v>9.95787811279297</v>
+        <v>9.95787715911865</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>11.1402349472046</v>
       </c>
       <c r="G982" t="n">
-        <v>9.87775135040283</v>
+        <v>9.87775230407715</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>11.0573978424072</v>
       </c>
       <c r="G983" t="n">
-        <v>9.80430221557617</v>
+        <v>9.80430126190186</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.802077293396</v>
+        <v>9.80207633972168</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812397003174</v>
+        <v>9.40812492370605</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G994" t="n">
-        <v>9.45931625366211</v>
+        <v>9.45931529998779</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G997" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>10.2315454483032</v>
       </c>
       <c r="G998" t="n">
-        <v>9.07204151153564</v>
+        <v>9.07204055786133</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>10.427339553833</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.24564647674561</v>
+        <v>9.24564552307129</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.39254379272461</v>
+        <v>9.39254474639893</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.21671295166016</v>
+        <v>9.21671199798584</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467674255371</v>
+        <v>9.33467578887939</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G1008" t="n">
-        <v>9.45931625366211</v>
+        <v>9.45931529998779</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>10.7938280105591</v>
       </c>
       <c r="G1009" t="n">
-        <v>9.57060146331787</v>
+        <v>9.57060241699219</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.56169891357422</v>
+        <v>9.5616979598999</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>10.934398651123</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.6952428817749</v>
+        <v>9.69524192810059</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>11.1728668212891</v>
       </c>
       <c r="G1019" t="n">
-        <v>9.9066858291626</v>
+        <v>9.90668487548828</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.802077293396</v>
+        <v>9.80207633972168</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>11.1126232147217</v>
       </c>
       <c r="G1029" t="n">
-        <v>9.85326957702637</v>
+        <v>9.85326862335205</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G1030" t="n">
-        <v>9.46154117584229</v>
+        <v>9.4615421295166</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>10.2917900085449</v>
       </c>
       <c r="G1032" t="n">
-        <v>9.12545871734619</v>
+        <v>9.12545776367188</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.2062349319458</v>
+        <v>8.20623397827148</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>9.75962924957275</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.65360546112061</v>
+        <v>8.65360450744629</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>9.55630302429199</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.47332096099854</v>
+        <v>8.47332191467285</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>9.51362991333008</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.43548393249512</v>
+        <v>8.43548488616943</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657609939575</v>
+        <v>7.71657657623291</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754726409912</v>
+        <v>7.62754774093628</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.07111692428589</v>
+        <v>7.07111740112305</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.70832395553589</v>
+        <v>6.70832347869873</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.9500036239624</v>
+        <v>4.95000410079956</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.9500036239624</v>
+        <v>4.95000410079956</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>5.16848611831665</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.58275985717773</v>
+        <v>4.58276033401489</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342178344727</v>
+        <v>5.00342130661011</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.88990926742554</v>
+        <v>4.8899097442627</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>5.85627889633179</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.19260740280151</v>
+        <v>5.19260787963867</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>5.8261570930481</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.1658992767334</v>
+        <v>5.16589975357056</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>5.89393186569214</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.22599315643311</v>
+        <v>5.22599363327026</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1078" t="n">
-        <v>4.98561525344849</v>
+        <v>4.98561573028564</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1079" t="n">
-        <v>4.98561525344849</v>
+        <v>4.98561573028564</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.06713485717773</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.37956809997559</v>
+        <v>5.37956762313843</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.0219521522522</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.33950567245483</v>
+        <v>5.33950614929199</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>6.04956388473511</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.36398839950562</v>
+        <v>5.36398887634277</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>5.47473001480103</v>
       </c>
       <c r="G1089" t="n">
-        <v>4.85429859161377</v>
+        <v>4.85429811477661</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>5.28395509719849</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.68514347076416</v>
+        <v>4.685142993927</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>5.55505609512329</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.92552089691162</v>
+        <v>4.92552137374878</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928550720215</v>
+        <v>5.19928503036499</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041345596313</v>
+        <v>5.21041393280029</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>5.79101419448853</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.13473892211914</v>
+        <v>5.1347393989563</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>5.80858516693115</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15031909942627</v>
+        <v>5.15031862258911</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248159408569</v>
+        <v>5.11248207092285</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.79800081253052</v>
+        <v>4.79800033569336</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>5.46217918395996</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.865074634552</v>
+        <v>4.86507511138916</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>5.30905723571777</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.72869110107422</v>
+        <v>4.72869157791138</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>5.79854488372803</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.16466999053955</v>
+        <v>5.16467046737671</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>6.46876621246338</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.76162576675415</v>
+        <v>5.76162528991699</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>6.59176588058472</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.87117910385132</v>
+        <v>5.87117958068848</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>6.41354179382324</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.71243762969971</v>
+        <v>5.71243810653687</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>5.99182987213135</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.33682584762573</v>
+        <v>5.33682632446289</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>5.98680877685547</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.3323540687561</v>
+        <v>5.33235359191895</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.0841817855835</v>
+        <v>5.08418226242065</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>5.61530113220215</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.00145816802979</v>
+        <v>5.00145769119263</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.97686338424683</v>
+        <v>4.97686290740967</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>5.68558597564697</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.06405973434448</v>
+        <v>5.06405925750732</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>5.27642488479614</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.69962596893311</v>
+        <v>4.69962644577026</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>5.28897619247437</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.71080541610718</v>
+        <v>4.71080589294434</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>5.36679220199585</v>
       </c>
       <c r="G1152" t="n">
-        <v>4.78011465072632</v>
+        <v>4.78011512756348</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.47724008560181</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.87848949432373</v>
+        <v>4.87848901748657</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>4.92123222351074</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.38326215744019</v>
+        <v>4.38326168060303</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.57357120513916</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.07360553741455</v>
+        <v>4.07360601425171</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.96892595291138</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.42574214935303</v>
+        <v>4.42574167251587</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1174" t="n">
-        <v>4.34189987182617</v>
+        <v>4.34190034866333</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.66895818710327</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.15856552124023</v>
+        <v>4.15856599807739</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.50579500198364</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.01323843002319</v>
+        <v>4.01323890686035</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.39032697677612</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.91039347648621</v>
+        <v>3.91039323806763</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.29242897033691</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.82319736480713</v>
+        <v>3.82319688796997</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>4.19327592849731</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.73488283157349</v>
+        <v>3.73488306999207</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.07906293869019</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.63315534591675</v>
+        <v>3.63315558433533</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.22465419769287</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.76283097267151</v>
+        <v>3.76283121109009</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.56321811676025</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.17370080947876</v>
+        <v>3.17370057106018</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.86444091796875</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.4419949054718</v>
+        <v>3.44199514389038</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>3.79415607452393</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.3793933391571</v>
+        <v>3.37939357757568</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>3.65609502792358</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.25642466545105</v>
+        <v>3.25642490386963</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>3.59585094451904</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.20276641845703</v>
+        <v>3.20276618003845</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>3.62597298622131</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.22959566116333</v>
+        <v>3.22959542274475</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.68496203422546</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.28213620185852</v>
+        <v>3.28213596343994</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>3.78411507606506</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.37045001983643</v>
+        <v>3.370450258255</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.6940598487854</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.18092346191406</v>
+        <v>4.1809229850769</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>4.89487504959106</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.35978651046753</v>
+        <v>4.35978603363037</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.27706241607666</v>
+        <v>4.2770619392395</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.47157573699951</v>
+        <v>4.47157526016235</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>5.42201614379883</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.8293023109436</v>
+        <v>4.82930183410645</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>5.30654716491699</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.72645568847656</v>
+        <v>4.72645616531372</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>5.1333441734314</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.5721869468689</v>
+        <v>4.57218647003174</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.62584495544434</v>
+        <v>4.62584447860718</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>5.35675096511841</v>
       </c>
       <c r="G1254" t="n">
-        <v>4.77117109298706</v>
+        <v>4.77117156982422</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>5.37683200836182</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.78905773162842</v>
+        <v>4.78905725479126</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1259" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>5.46719884872437</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.86954593658447</v>
+        <v>4.86954545974731</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.86060285568237</v>
+        <v>4.86060237884521</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>5.82364702224731</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.18702840805054</v>
+        <v>5.18702793121338</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>6.17256307601929</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.49780178070068</v>
+        <v>5.49780225753784</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>6.10729789733887</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.43967151641846</v>
+        <v>5.4396710395813</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>6.08721685409546</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.42178583145142</v>
+        <v>5.42178535461426</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>6.00689077377319</v>
       </c>
       <c r="G1279" t="n">
-        <v>5.35024070739746</v>
+        <v>5.3502402305603</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.85878896713257</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.21832895278931</v>
+        <v>5.21832847595215</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>5.34169006347656</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.75775718688965</v>
+        <v>4.75775671005249</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>5.59019899368286</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.9790997505188</v>
+        <v>4.97910022735596</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>5.98178911209106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.32788276672363</v>
+        <v>5.32788324356079</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>6.55160188674927</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.83540630340576</v>
+        <v>5.8354058265686</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>6.3457670211792</v>
       </c>
       <c r="G1303" t="n">
-        <v>5.65207195281982</v>
+        <v>5.65207242965698</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>6.35078716278076</v>
       </c>
       <c r="G1304" t="n">
-        <v>5.65654373168945</v>
+        <v>5.65654325485229</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>6.40852212905884</v>
       </c>
       <c r="G1305" t="n">
-        <v>5.70796728134155</v>
+        <v>5.70796680450439</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>6.63192892074585</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.90695142745972</v>
+        <v>5.90695190429688</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>6.00940084457397</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.35247659683228</v>
+        <v>5.35247611999512</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.0841817855835</v>
+        <v>5.08418226242065</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1312" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>5.91652393341064</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.26975250244141</v>
+        <v>5.26975202560425</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>6.07215595245361</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.40837097167969</v>
+        <v>5.40837144851685</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>6.07717609405518</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.41284275054932</v>
+        <v>5.41284227371216</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>6.12486982345581</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.45532274246216</v>
+        <v>5.455322265625</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>5.97174787521362</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.31893920898438</v>
+        <v>5.31893968582153</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1324" t="n">
-        <v>5.31670379638672</v>
+        <v>5.31670331954956</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>5.69060611724854</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.06853055953979</v>
+        <v>5.06853103637695</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>5.87887096405029</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.23621559143066</v>
+        <v>5.23621511459351</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>5.83870792388916</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.20044231414795</v>
+        <v>5.20044279098511</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.97686338424683</v>
+        <v>4.97686290740967</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.94556283950806</v>
+        <v>4.94556331634521</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.87855911254883</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.34525346755981</v>
+        <v>4.34525394439697</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.82333517074585</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.29606676101685</v>
+        <v>4.29606628417969</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>5.06054782867432</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.50734806060791</v>
+        <v>4.50734853744507</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.69068288803101</v>
+        <v>4.69068336486816</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>5.1383638381958</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.57665729522705</v>
+        <v>4.57665777206421</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>5.12832307815552</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.56771421432495</v>
+        <v>4.56771469116211</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>5.11828184127808</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.55877065658569</v>
+        <v>4.55877113342285</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>5.3793420791626</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.79129266738892</v>
+        <v>4.79129314422607</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>5.56760692596436</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.95897769927979</v>
+        <v>4.95897722244263</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1390" t="n">
-        <v>4.72422027587891</v>
+        <v>4.72421979904175</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.72422027587891</v>
+        <v>4.72421979904175</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>5.29901599884033</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.71974754333496</v>
+        <v>4.71974802017212</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1396" t="n">
-        <v>4.56324338912964</v>
+        <v>4.56324291229248</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>5.22873115539551</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.65714597702026</v>
+        <v>4.65714645385742</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>5.21868991851807</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.64820241928101</v>
+        <v>4.64820289611816</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.90617084503174</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.3698468208313</v>
+        <v>4.36984729766846</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.97143602371216</v>
       </c>
       <c r="G1403" t="n">
-        <v>4.42797756195068</v>
+        <v>4.42797803878784</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>4.88483476638794</v>
       </c>
       <c r="G1405" t="n">
-        <v>4.35084295272827</v>
+        <v>4.35084342956543</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.90240621566772</v>
       </c>
       <c r="G1407" t="n">
-        <v>4.36649417877197</v>
+        <v>4.36649370193481</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.75681495666504</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.23681783676147</v>
+        <v>4.23681831359863</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1417" t="n">
-        <v>4.5297064781189</v>
+        <v>4.52970600128174</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>4.91119194030762</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.37431955337524</v>
+        <v>4.37431907653809</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.92499780654907</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.38661575317383</v>
+        <v>4.38661623001099</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.56324338912964</v>
+        <v>4.56324291229248</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>5.16597604751587</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.60125160217285</v>
+        <v>4.60125112533569</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>4.98147678375244</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.43692064285278</v>
+        <v>4.43692111968994</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1433" t="n">
-        <v>4.27706241607666</v>
+        <v>4.2770619392395</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1436" t="n">
-        <v>4.47157573699951</v>
+        <v>4.47157526016235</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>4.96139478683472</v>
       </c>
       <c r="G1443" t="n">
-        <v>4.41903400421143</v>
+        <v>4.41903448104858</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>5.01662015914917</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.46822214126587</v>
+        <v>4.46822261810303</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1449" t="n">
-        <v>4.62584495544434</v>
+        <v>4.62584447860718</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.5297064781189</v>
+        <v>4.52970600128174</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.99151802062988</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.4458646774292</v>
+        <v>4.44586420059204</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>4.91244697570801</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.37543725967407</v>
+        <v>4.37543678283691</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>5.07058906555176</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.51629161834717</v>
+        <v>4.51629209518433</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>5.55003595352173</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.9433274269104</v>
+        <v>4.94332695007324</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.69068288803101</v>
+        <v>4.69068336486816</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.79800081253052</v>
+        <v>4.79800033569336</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1470" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.91202640533447</v>
+        <v>4.91202592849731</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.94556283950806</v>
+        <v>4.94556331634521</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.87353897094727</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.3407826423645</v>
+        <v>4.34078216552734</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.81203889846802</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.28600549697876</v>
+        <v>4.2860050201416</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.34189987182617</v>
+        <v>4.34190034866333</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.39220523834229</v>
+        <v>4.39220476150513</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>4.46563196182251</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.97746610641479</v>
+        <v>3.97746634483337</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>4.50328493118286</v>
       </c>
       <c r="G1504" t="n">
-        <v>4.0110034942627</v>
+        <v>4.01100301742554</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>4.42170381546021</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.93834018707275</v>
+        <v>3.93833994865417</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>4.59365177154541</v>
       </c>
       <c r="G1509" t="n">
-        <v>4.09149169921875</v>
+        <v>4.09149122238159</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>4.56729507446289</v>
       </c>
       <c r="G1511" t="n">
-        <v>4.06801605224609</v>
+        <v>4.06801557540894</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>4.41040802001953</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.92827916145325</v>
+        <v>3.92827892303467</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>4.4455509185791</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.95958018302917</v>
+        <v>3.95958042144775</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>4.37275505065918</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.89474248886108</v>
+        <v>3.89474201202393</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.55097913742065</v>
       </c>
       <c r="G1522" t="n">
-        <v>4.05348348617554</v>
+        <v>4.0534839630127</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>4.78317213058472</v>
       </c>
       <c r="G1527" t="n">
-        <v>4.26029443740845</v>
+        <v>4.26029396057129</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>4.91495704650879</v>
       </c>
       <c r="G1531" t="n">
-        <v>4.37767267227173</v>
+        <v>4.37767314910889</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.03042602539062</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.48051929473877</v>
+        <v>4.48051881790161</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.39220523834229</v>
+        <v>4.39220476150513</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>5.01410913467407</v>
       </c>
       <c r="G1541" t="n">
-        <v>4.46598625183105</v>
+        <v>4.4659857749939</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>2.99591493606567</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.66841292381287</v>
+        <v>2.66841316223145</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>3.02854704856873</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.69747805595398</v>
+        <v>2.6974778175354</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>2.8616189956665</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.54879784584045</v>
+        <v>2.54879760742188</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.56221222877502</v>
+        <v>2.5622124671936</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.51521301269531</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.24025964736938</v>
+        <v>2.24025940895081</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>2.56165099143982</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.28162121772766</v>
+        <v>2.28162097930908</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.56792688369751</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.28721117973328</v>
+        <v>2.2872109413147</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>2.37715196609497</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.11729097366333</v>
+        <v>2.11729073524475</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.58047795295715</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.29838991165161</v>
+        <v>2.29839015007019</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>2.46450710296631</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.19509673118591</v>
+        <v>2.19509649276733</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>2.67335510253906</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.38111400604248</v>
+        <v>2.38111424446106</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>2.86287403106689</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.54991555213928</v>
+        <v>2.54991579055786</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.56221222877502</v>
+        <v>2.5622124671936</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>2.93943500518799</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.61810731887817</v>
+        <v>2.61810708045959</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>2.87919092178345</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.564448595047</v>
+        <v>2.56444883346558</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>2.84404802322388</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.53314781188965</v>
+        <v>2.53314757347107</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>2.77878308296204</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.47501730918884</v>
+        <v>2.47501707077026</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>2.80262994766235</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.49625730514526</v>
+        <v>2.49625706672668</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>2.79384398460388</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.48843169212341</v>
+        <v>2.48843145370483</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>2.75744605064392</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.45601272583008</v>
+        <v>2.4560124874115</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.43700885772705</v>
+        <v>2.43700909614563</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.84028291702271</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.52979397773743</v>
+        <v>2.52979421615601</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>2.92437410354614</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.6046929359436</v>
+        <v>2.60469269752502</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.43700885772705</v>
+        <v>2.43700909614563</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.48509001731873</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.21342945098877</v>
+        <v>2.21342968940735</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>2.53780388832092</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.26038098335266</v>
+        <v>2.26038074493408</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>2.68841600418091</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.39452886581421</v>
+        <v>2.39452862739563</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>2.90680289268494</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.58904242515564</v>
+        <v>2.58904218673706</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>2.97517991065979</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.6499445438385</v>
+        <v>2.64994478225708</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>2.72426104545593</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.42645525932312</v>
+        <v>2.4264554977417</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>2.37423992156982</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.11469721794128</v>
+        <v>2.11469697952271</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>1.96649694442749</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.75152707099915</v>
+        <v>1.75152695178986</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>2.01657509803772</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.79613077640533</v>
+        <v>1.79613089561462</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>2.21557092666626</v>
       </c>
       <c r="G1646" t="n">
-        <v>1.97337329387665</v>
+        <v>1.97337317466736</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>1.73798203468323</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.54799246788025</v>
+        <v>1.54799258708954</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.59776198863983</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.42310070991516</v>
+        <v>1.42310082912445</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>1.24932205677032</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.11275100708008</v>
+        <v>1.11275088787079</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98913478851318</v>
+        <v>2.98913502693176</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.73594284057617</v>
+        <v>1.73594272136688</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.985986948013306</v>
+        <v>0.98598700761795</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.04209995269775</v>
+        <v>1.04210007190704</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.730360686779022</v>
+        <v>0.730360746383667</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>0.71340000629425</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.635413825511932</v>
+        <v>0.635413885116577</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.659106075763702</v>
+        <v>0.659106016159058</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.692061364650726</v>
+        <v>0.692061305046082</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.751737177371979</v>
+        <v>0.751737117767334</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>0.833599984645844</v>
       </c>
       <c r="G1677" t="n">
-        <v>0.74247407913208</v>
+        <v>0.742474019527435</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>0.821799993515015</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.731963992118835</v>
+        <v>0.731963932514191</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>0.762199997901917</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.678879261016846</v>
+        <v>0.678879201412201</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>0.716400027275085</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.638085901737213</v>
+        <v>0.638085961341858</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>0.674600005149841</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.60085529088974</v>
+        <v>0.600855350494385</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>0.697399973869324</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.621162891387939</v>
+        <v>0.621162831783295</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>0.683200001716614</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.608515202999115</v>
+        <v>0.60851514339447</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>0.662199974060059</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.589810848236084</v>
+        <v>0.589810788631439</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>0.64300000667572</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.572709739208221</v>
+        <v>0.572709679603577</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.540645062923431</v>
+        <v>0.540645122528076</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>0.584800004959106</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.520871937274933</v>
+        <v>0.520871877670288</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>0.59280002117157</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.527997374534607</v>
+        <v>0.527997434139252</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>0.597199976444244</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.531916320323944</v>
+        <v>0.531916379928589</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>0.637600004673004</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.567900002002716</v>
+        <v>0.567900061607361</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>0.72759997844696</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.648061513900757</v>
+        <v>0.648061573505402</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.620806694030762</v>
+        <v>0.620806634426117</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.658215343952179</v>
+        <v>0.658215403556824</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>0.758199989795685</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.675316452980042</v>
+        <v>0.675316512584686</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>0.828599989414215</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.738020598888397</v>
+        <v>0.738020658493042</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>0.958599984645844</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.853809535503387</v>
+        <v>0.853809475898743</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.8764328956604</v>
+        <v>0.876432955265045</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.87376081943512</v>
+        <v>0.873760879039764</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.882667660713196</v>
+        <v>0.882667720317841</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.919185698032379</v>
+        <v>0.919185638427734</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.957485198974609</v>
+        <v>0.957485139369965</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>1.09650003910065</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.976634860038757</v>
+        <v>0.976634919643402</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>1.03250002861023</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.919631063938141</v>
+        <v>0.919631123542786</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.921857714653015</v>
+        <v>0.92185777425766</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>1.04649996757507</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.932100653648376</v>
+        <v>0.932100594043732</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.926311135292053</v>
+        <v>0.926311194896698</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>1.04750001430511</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.93299126625061</v>
+        <v>0.932991325855255</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.912950873374939</v>
+        <v>0.912950932979584</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>1.01950001716614</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.908052146434784</v>
+        <v>0.908052206039429</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>1.04449999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.93031919002533</v>
+        <v>0.930319249629974</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>1.00650000572205</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.896473228931427</v>
+        <v>0.896473288536072</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.04949998855591</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.934772729873657</v>
+        <v>0.934772670269012</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>1.10950005054474</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.988213777542114</v>
+        <v>0.988213717937469</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.977970957756042</v>
+        <v>0.977970898151398</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>1.12750005722046</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.00424599647522</v>
+        <v>1.00424611568451</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.05456960201263</v>
+        <v>1.05456972122192</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>1.31149995326996</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.16813182830811</v>
+        <v>1.16813170909882</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.25141072273254</v>
+        <v>1.25141084194183</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.2309250831604</v>
+        <v>1.23092496395111</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.21845555305481</v>
+        <v>1.21845543384552</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.25586414337158</v>
+        <v>1.25586426258087</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.24962949752808</v>
+        <v>1.24962937831879</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.3146493434906</v>
+        <v>1.31464922428131</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.35116744041443</v>
+        <v>1.35116732120514</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>1.53450000286102</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.36675429344177</v>
+        <v>1.36675441265106</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.31643068790436</v>
+        <v>1.31643080711365</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.35749995708466</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.20910334587097</v>
+        <v>1.20910322666168</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>1.26549994945526</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.12716031074524</v>
+        <v>1.12716042995453</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>1.14049994945526</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.01582491397858</v>
+        <v>1.01582479476929</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>1.23450005054474</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.09954929351807</v>
+        <v>1.09954917430878</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.32550001144409</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.18060147762299</v>
+        <v>1.1806013584137</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.14007532596588</v>
+        <v>1.14007520675659</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23181581497192</v>
+        <v>1.23181569576263</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>1.25049996376038</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.11380004882812</v>
+        <v>1.11380016803741</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.15076351165771</v>
+        <v>1.150763630867</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.13473129272461</v>
+        <v>1.13473117351532</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.12048017978668</v>
+        <v>1.12048029899597</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.15788900852203</v>
+        <v>1.15788888931274</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>1.25750005245209</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.1200350522995</v>
+        <v>1.12003493309021</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.12226164340973</v>
+        <v>1.12226152420044</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.07416474819183</v>
+        <v>1.07416462898254</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.13473129272461</v>
+        <v>1.13473117351532</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>1.25450003147125</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.11736297607422</v>
+        <v>1.11736285686493</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.08663427829742</v>
+        <v>1.08663439750671</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>1.16250002384186</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.03541994094849</v>
+        <v>1.03542006015778</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.04833495616913</v>
+        <v>1.04833483695984</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.07772743701935</v>
+        <v>1.07772755622864</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.30039846897125</v>
+        <v>1.30039834976196</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.3110865354538</v>
+        <v>1.31108665466309</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.32266557216644</v>
+        <v>1.32266545295715</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>1.43949997425079</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.28213942050934</v>
+        <v>1.28213930130005</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>1.43250000476837</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.27590453624725</v>
+        <v>1.27590465545654</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.30039846897125</v>
+        <v>1.30039834976196</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.328009724617</v>
+        <v>1.32800960540771</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1928" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1930" t="n">
-        <v>1.29683566093445</v>
+        <v>1.29683554172516</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.29327285289764</v>
+        <v>1.29327297210693</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.25586414337158</v>
+        <v>1.25586426258087</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1935" t="n">
-        <v>1.24339461326599</v>
+        <v>1.24339473247528</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.30485188961029</v>
+        <v>1.304851770401</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.33869779109955</v>
+        <v>1.33869791030884</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.32266557216644</v>
+        <v>1.32266545295715</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1951" t="n">
-        <v>1.4019364118576</v>
+        <v>1.40193629264832</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.328009724617</v>
+        <v>1.32800960540771</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.37566113471985</v>
+        <v>1.37566125392914</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.41975009441376</v>
+        <v>1.41974997520447</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>1.60950005054474</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.43355572223663</v>
+        <v>1.43355560302734</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.40104568004608</v>
+        <v>1.40104556083679</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>1.46249997615814</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.30262517929077</v>
+        <v>1.30262506008148</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.27679538726807</v>
+        <v>1.27679526805878</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.29683566093445</v>
+        <v>1.29683554172516</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>1.41849994659424</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.26343500614166</v>
+        <v>1.26343488693237</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>1.5275000333786</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.36051964759827</v>
+        <v>1.36051952838898</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52031,7 +52031,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.37566113471985</v>
+        <v>1.37566125392914</v>
       </c>
       <c r="H1987" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.29015564918518</v>
+        <v>1.29015552997589</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.41449999809265</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.25987231731415</v>
+        <v>1.25987219810486</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.23626923561096</v>
+        <v>1.23626911640167</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.23805046081543</v>
+        <v>1.23805058002472</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2007" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>1.44749999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>1.28926479816437</v>
+        <v>1.28926491737366</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>1.46150004863739</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.30173444747925</v>
+        <v>1.30173456668854</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.24784803390503</v>
+        <v>1.24784815311432</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2023" t="n">
-        <v>1.24784803390503</v>
+        <v>1.24784815311432</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.22647166252136</v>
+        <v>1.22647154331207</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>1.42050004005432</v>
       </c>
       <c r="G2029" t="n">
-        <v>1.26521635055542</v>
+        <v>1.26521646976471</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.29015564918518</v>
+        <v>1.29015552997589</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>1.44649994373322</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.28837406635284</v>
+        <v>1.28837418556213</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>1.48300004005432</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.3208841085434</v>
+        <v>1.32088422775269</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.30930531024933</v>
+        <v>1.30930519104004</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>1.4889999628067</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.32622814178467</v>
+        <v>1.32622826099396</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>1.50650000572205</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.34181523323059</v>
+        <v>1.3418151140213</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.27679538726807</v>
+        <v>1.27679526805878</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.31643068790436</v>
+        <v>1.31643080711365</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G2055" t="n">
-        <v>1.34315121173859</v>
+        <v>1.34315133094788</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -54189,7 +54189,7 @@
         <v>1.375</v>
       </c>
       <c r="G2070" t="n">
-        <v>1.22469019889832</v>
+        <v>1.2246903181076</v>
       </c>
       <c r="H2070" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>1.38100004196167</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.23003435134888</v>
+        <v>1.23003447055817</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.32979094982147</v>
+        <v>1.32979106903076</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>1.82149994373322</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.6223806142807</v>
+        <v>1.62238049507141</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.72347319126129</v>
+        <v>1.723473072052</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>1.97650003433228</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.76043665409088</v>
+        <v>1.76043653488159</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.87488961219788</v>
+        <v>1.87488949298859</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.88112413883209</v>
+        <v>1.88112425804138</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>2.08699989318848</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.85885715484619</v>
+        <v>1.8588570356369</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.91318881511688</v>
+        <v>1.91318893432617</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -55047,7 +55047,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.98889696598053</v>
+        <v>1.98889708518982</v>
       </c>
       <c r="H2103" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2104" t="n">
-        <v>2.00760126113892</v>
+        <v>2.0076014995575</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G2105" t="n">
-        <v>2.00849199295044</v>
+        <v>2.00849223136902</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.06994915008545</v>
+        <v>2.06994891166687</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>2.3970000743866</v>
       </c>
       <c r="G2109" t="n">
-        <v>2.13496923446655</v>
+        <v>2.13496899604797</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2110" t="n">
-        <v>2.08419990539551</v>
+        <v>2.08420014381409</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.99513185024261</v>
+        <v>1.99513173103333</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.94258141517639</v>
+        <v>1.94258153438568</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.97197389602661</v>
+        <v>1.9719740152359</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.9523788690567</v>
+        <v>1.95237898826599</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2123" t="n">
-        <v>1.94080007076263</v>
+        <v>1.94079983234406</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55645,7 +55645,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2126" t="n">
-        <v>1.91318881511688</v>
+        <v>1.91318893432617</v>
       </c>
       <c r="H2126" t="s">
         <v>8</v>
@@ -55697,7 +55697,7 @@
         <v>2.13100004196167</v>
       </c>
       <c r="G2128" t="n">
-        <v>1.8980473279953</v>
+        <v>1.89804720878601</v>
       </c>
       <c r="H2128" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G2131" t="n">
-        <v>1.97019255161285</v>
+        <v>1.97019267082214</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G2132" t="n">
-        <v>2.02541494369507</v>
+        <v>2.02541518211365</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -55853,7 +55853,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2134" t="n">
-        <v>2.11359286308289</v>
+        <v>2.11359262466431</v>
       </c>
       <c r="H2134" t="s">
         <v>8</v>
@@ -55957,7 +55957,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2138" t="n">
-        <v>2.12160897254944</v>
+        <v>2.12160873413086</v>
       </c>
       <c r="H2138" t="s">
         <v>8</v>
@@ -55983,7 +55983,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2139" t="n">
-        <v>2.11359286308289</v>
+        <v>2.11359262466431</v>
       </c>
       <c r="H2139" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2141" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56087,7 +56087,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2143" t="n">
-        <v>1.98889696598053</v>
+        <v>1.98889708518982</v>
       </c>
       <c r="H2143" t="s">
         <v>8</v>
@@ -56139,7 +56139,7 @@
         <v>2.15300011634827</v>
       </c>
       <c r="G2145" t="n">
-        <v>1.91764235496521</v>
+        <v>1.9176424741745</v>
       </c>
       <c r="H2145" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.9203143119812</v>
+        <v>1.92031419277191</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.93367457389832</v>
+        <v>1.9336746931076</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.83926212787628</v>
+        <v>1.83926224708557</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.86152911186218</v>
+        <v>1.86152923107147</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56399,7 +56399,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2155" t="n">
-        <v>1.86152911186218</v>
+        <v>1.86152923107147</v>
       </c>
       <c r="H2155" t="s">
         <v>8</v>
@@ -56425,7 +56425,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2156" t="n">
-        <v>1.89626574516296</v>
+        <v>1.89626586437225</v>
       </c>
       <c r="H2156" t="s">
         <v>8</v>
@@ -56451,7 +56451,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2157" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2157" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>2.15899991989136</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.92298626899719</v>
+        <v>1.92298638820648</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56503,7 +56503,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.99245965480804</v>
+        <v>1.99245977401733</v>
       </c>
       <c r="H2159" t="s">
         <v>8</v>
@@ -56607,7 +56607,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.1358597278595</v>
+        <v>2.13585996627808</v>
       </c>
       <c r="H2163" t="s">
         <v>8</v>
@@ -56711,7 +56711,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2167" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2167" t="s">
         <v>8</v>
@@ -56789,7 +56789,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G2170" t="n">
-        <v>2.07351183891296</v>
+        <v>2.07351207733154</v>
       </c>
       <c r="H2170" t="s">
         <v>8</v>
@@ -56815,7 +56815,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2171" t="n">
-        <v>2.06371426582336</v>
+        <v>2.06371450424194</v>
       </c>
       <c r="H2171" t="s">
         <v>8</v>
@@ -56841,7 +56841,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G2172" t="n">
-        <v>2.09666991233826</v>
+        <v>2.09666967391968</v>
       </c>
       <c r="H2172" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2174" t="n">
-        <v>2.10913920402527</v>
+        <v>2.10913944244385</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G2175" t="n">
-        <v>2.12339043617249</v>
+        <v>2.12339019775391</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -56945,7 +56945,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G2176" t="n">
-        <v>2.14476656913757</v>
+        <v>2.14476680755615</v>
       </c>
       <c r="H2176" t="s">
         <v>8</v>
@@ -57023,7 +57023,7 @@
         <v>2.41899991035461</v>
       </c>
       <c r="G2179" t="n">
-        <v>2.15456390380859</v>
+        <v>2.15456414222717</v>
       </c>
       <c r="H2179" t="s">
         <v>8</v>
@@ -57075,7 +57075,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2181" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2181" t="s">
         <v>8</v>
@@ -57101,7 +57101,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G2182" t="n">
-        <v>1.98444354534149</v>
+        <v>1.9844434261322</v>
       </c>
       <c r="H2182" t="s">
         <v>8</v>
@@ -57153,7 +57153,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2184" t="n">
-        <v>1.9461442232132</v>
+        <v>1.94614410400391</v>
       </c>
       <c r="H2184" t="s">
         <v>8</v>
@@ -57179,7 +57179,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2185" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2185" t="s">
         <v>8</v>
@@ -57205,7 +57205,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2186" t="n">
-        <v>1.94080007076263</v>
+        <v>1.94079983234406</v>
       </c>
       <c r="H2186" t="s">
         <v>8</v>
@@ -57309,7 +57309,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G2190" t="n">
-        <v>1.79294645786285</v>
+        <v>1.79294657707214</v>
       </c>
       <c r="H2190" t="s">
         <v>8</v>
@@ -57413,7 +57413,7 @@
         <v>1.98450005054474</v>
       </c>
       <c r="G2194" t="n">
-        <v>1.76756203174591</v>
+        <v>1.7675621509552</v>
       </c>
       <c r="H2194" t="s">
         <v>8</v>
@@ -57543,7 +57543,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G2199" t="n">
-        <v>1.84282493591309</v>
+        <v>1.8428248167038</v>
       </c>
       <c r="H2199" t="s">
         <v>8</v>
@@ -57621,7 +57621,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G2202" t="n">
-        <v>1.84549701213837</v>
+        <v>1.84549689292908</v>
       </c>
       <c r="H2202" t="s">
         <v>8</v>
@@ -57647,7 +57647,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G2203" t="n">
-        <v>1.81521379947662</v>
+        <v>1.81521368026733</v>
       </c>
       <c r="H2203" t="s">
         <v>8</v>
@@ -57725,7 +57725,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2206" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2206" t="s">
         <v>8</v>
@@ -57751,7 +57751,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2207" t="n">
-        <v>1.80185341835022</v>
+        <v>1.80185329914093</v>
       </c>
       <c r="H2207" t="s">
         <v>8</v>
@@ -57777,7 +57777,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2208" t="n">
-        <v>1.67448556423187</v>
+        <v>1.67448568344116</v>
       </c>
       <c r="H2208" t="s">
         <v>8</v>
@@ -57803,7 +57803,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G2209" t="n">
-        <v>1.71189427375793</v>
+        <v>1.71189439296722</v>
       </c>
       <c r="H2209" t="s">
         <v>8</v>
@@ -57907,7 +57907,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G2213" t="n">
-        <v>1.60055887699127</v>
+        <v>1.60055899620056</v>
       </c>
       <c r="H2213" t="s">
         <v>8</v>
@@ -57933,7 +57933,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G2214" t="n">
-        <v>1.6272794008255</v>
+        <v>1.62727928161621</v>
       </c>
       <c r="H2214" t="s">
         <v>8</v>
@@ -58193,7 +58193,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G2224" t="n">
-        <v>1.81343221664429</v>
+        <v>1.81343233585358</v>
       </c>
       <c r="H2224" t="s">
         <v>8</v>
@@ -58401,7 +58401,7 @@
         <v>2.05699992179871</v>
       </c>
       <c r="G2232" t="n">
-        <v>1.83213663101196</v>
+        <v>1.83213651180267</v>
       </c>
       <c r="H2232" t="s">
         <v>8</v>
@@ -58453,7 +58453,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2234" t="n">
-        <v>1.79027438163757</v>
+        <v>1.79027450084686</v>
       </c>
       <c r="H2234" t="s">
         <v>8</v>
@@ -58479,7 +58479,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2235" t="n">
-        <v>1.80185341835022</v>
+        <v>1.80185329914093</v>
       </c>
       <c r="H2235" t="s">
         <v>8</v>
@@ -58635,7 +58635,7 @@
         <v>1.99150002002716</v>
       </c>
       <c r="G2241" t="n">
-        <v>1.773796916008</v>
+        <v>1.77379679679871</v>
       </c>
       <c r="H2241" t="s">
         <v>8</v>
@@ -58687,7 +58687,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2243" t="n">
-        <v>1.83926212787628</v>
+        <v>1.83926224708557</v>
       </c>
       <c r="H2243" t="s">
         <v>8</v>
@@ -58713,7 +58713,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G2244" t="n">
-        <v>1.80630695819855</v>
+        <v>1.80630683898926</v>
       </c>
       <c r="H2244" t="s">
         <v>8</v>
@@ -58739,7 +58739,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G2245" t="n">
-        <v>1.89003121852875</v>
+        <v>1.89003109931946</v>
       </c>
       <c r="H2245" t="s">
         <v>8</v>
@@ -58765,7 +58765,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G2246" t="n">
-        <v>1.94970679283142</v>
+        <v>1.94970667362213</v>
       </c>
       <c r="H2246" t="s">
         <v>8</v>
@@ -58817,7 +58817,7 @@
         <v>2.16300010681152</v>
       </c>
       <c r="G2248" t="n">
-        <v>1.92654919624329</v>
+        <v>1.92654931545258</v>
       </c>
       <c r="H2248" t="s">
         <v>8</v>
@@ -58843,7 +58843,7 @@
         <v>2.16700005531311</v>
       </c>
       <c r="G2249" t="n">
-        <v>1.93011200428009</v>
+        <v>1.9301118850708</v>
       </c>
       <c r="H2249" t="s">
         <v>8</v>
@@ -58869,7 +58869,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2250" t="n">
-        <v>1.94525361061096</v>
+        <v>1.94525349140167</v>
       </c>
       <c r="H2250" t="s">
         <v>8</v>
@@ -58895,7 +58895,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2251" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2251" t="s">
         <v>8</v>
@@ -58921,7 +58921,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2252" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2252" t="s">
         <v>8</v>
@@ -58973,7 +58973,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2254" t="n">
-        <v>2.00314784049988</v>
+        <v>2.00314807891846</v>
       </c>
       <c r="H2254" t="s">
         <v>8</v>
@@ -59025,7 +59025,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2256" t="n">
-        <v>2.06994915008545</v>
+        <v>2.06994891166687</v>
       </c>
       <c r="H2256" t="s">
         <v>8</v>
@@ -59103,7 +59103,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2259" t="n">
-        <v>2.05302619934082</v>
+        <v>2.0530264377594</v>
       </c>
       <c r="H2259" t="s">
         <v>8</v>
@@ -59129,7 +59129,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2260" t="n">
-        <v>2.06371426582336</v>
+        <v>2.06371450424194</v>
       </c>
       <c r="H2260" t="s">
         <v>8</v>
@@ -59155,7 +59155,7 @@
         <v>2.33299994468689</v>
       </c>
       <c r="G2261" t="n">
-        <v>2.07796549797058</v>
+        <v>2.077965259552</v>
       </c>
       <c r="H2261" t="s">
         <v>8</v>
@@ -59181,7 +59181,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2262" t="n">
-        <v>2.10913920402527</v>
+        <v>2.10913944244385</v>
       </c>
       <c r="H2262" t="s">
         <v>8</v>
@@ -59363,7 +59363,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G2269" t="n">
-        <v>2.16525220870972</v>
+        <v>2.1652524471283</v>
       </c>
       <c r="H2269" t="s">
         <v>8</v>
@@ -59493,7 +59493,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G2274" t="n">
-        <v>2.26768088340759</v>
+        <v>2.26768112182617</v>
       </c>
       <c r="H2274" t="s">
         <v>8</v>
@@ -59597,7 +59597,7 @@
         <v>2.48699998855591</v>
       </c>
       <c r="G2278" t="n">
-        <v>2.21513080596924</v>
+        <v>2.21513056755066</v>
       </c>
       <c r="H2278" t="s">
         <v>8</v>
@@ -59675,7 +59675,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G2281" t="n">
-        <v>2.29261994361877</v>
+        <v>2.29262018203735</v>
       </c>
       <c r="H2281" t="s">
         <v>8</v>
@@ -59701,7 +59701,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2282" t="n">
-        <v>2.31577801704407</v>
+        <v>2.31577777862549</v>
       </c>
       <c r="H2282" t="s">
         <v>8</v>
@@ -59779,7 +59779,7 @@
         <v>2.64299988746643</v>
       </c>
       <c r="G2285" t="n">
-        <v>2.35407733917236</v>
+        <v>2.35407710075378</v>
       </c>
       <c r="H2285" t="s">
         <v>8</v>
@@ -59857,7 +59857,7 @@
         <v>2.51099991798401</v>
       </c>
       <c r="G2288" t="n">
-        <v>2.23650693893433</v>
+        <v>2.23650717735291</v>
       </c>
       <c r="H2288" t="s">
         <v>8</v>
@@ -59883,7 +59883,7 @@
         <v>2.5090000629425</v>
       </c>
       <c r="G2289" t="n">
-        <v>2.23472595214844</v>
+        <v>2.23472571372986</v>
       </c>
       <c r="H2289" t="s">
         <v>8</v>
@@ -60039,7 +60039,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G2295" t="n">
-        <v>2.45294332504272</v>
+        <v>2.45294308662415</v>
       </c>
       <c r="H2295" t="s">
         <v>8</v>
@@ -60143,7 +60143,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G2299" t="n">
-        <v>2.31221508979797</v>
+        <v>2.31221532821655</v>
       </c>
       <c r="H2299" t="s">
         <v>8</v>
@@ -60195,7 +60195,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G2301" t="n">
-        <v>2.27658772468567</v>
+        <v>2.27658796310425</v>
       </c>
       <c r="H2301" t="s">
         <v>8</v>
@@ -60221,7 +60221,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G2302" t="n">
-        <v>2.25164866447449</v>
+        <v>2.25164890289307</v>
       </c>
       <c r="H2302" t="s">
         <v>8</v>
@@ -60247,7 +60247,7 @@
         <v>2.51300001144409</v>
       </c>
       <c r="G2303" t="n">
-        <v>2.23828840255737</v>
+        <v>2.23828864097595</v>
       </c>
       <c r="H2303" t="s">
         <v>8</v>
@@ -60299,7 +60299,7 @@
         <v>2.48300004005432</v>
       </c>
       <c r="G2305" t="n">
-        <v>2.21156787872314</v>
+        <v>2.21156811714172</v>
       </c>
       <c r="H2305" t="s">
         <v>8</v>
@@ -60325,7 +60325,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G2306" t="n">
-        <v>2.14832949638367</v>
+        <v>2.14832925796509</v>
       </c>
       <c r="H2306" t="s">
         <v>8</v>
@@ -60351,7 +60351,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2307" t="n">
-        <v>2.12160897254944</v>
+        <v>2.12160873413086</v>
       </c>
       <c r="H2307" t="s">
         <v>8</v>
@@ -60559,7 +60559,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G2315" t="n">
-        <v>2.04411935806274</v>
+        <v>2.04411959648132</v>
       </c>
       <c r="H2315" t="s">
         <v>8</v>
@@ -60611,7 +60611,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G2317" t="n">
-        <v>2.04768228530884</v>
+        <v>2.04768204689026</v>
       </c>
       <c r="H2317" t="s">
         <v>8</v>
@@ -60741,7 +60741,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G2322" t="n">
-        <v>2.05658912658691</v>
+        <v>2.05658888816833</v>
       </c>
       <c r="H2322" t="s">
         <v>8</v>
@@ -60819,7 +60819,7 @@
         <v>2.28099989891052</v>
       </c>
       <c r="G2325" t="n">
-        <v>2.03164982795715</v>
+        <v>2.03164958953857</v>
       </c>
       <c r="H2325" t="s">
         <v>8</v>
@@ -60845,7 +60845,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G2326" t="n">
-        <v>2.0681676864624</v>
+        <v>2.06816792488098</v>
       </c>
       <c r="H2326" t="s">
         <v>8</v>
@@ -60923,7 +60923,7 @@
         <v>2.20300006866455</v>
       </c>
       <c r="G2329" t="n">
-        <v>1.9621764421463</v>
+        <v>1.96217656135559</v>
       </c>
       <c r="H2329" t="s">
         <v>8</v>
@@ -60949,7 +60949,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2330" t="n">
-        <v>2.00314784049988</v>
+        <v>2.00314807891846</v>
       </c>
       <c r="H2330" t="s">
         <v>8</v>
@@ -61001,7 +61001,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2332" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2332" t="s">
         <v>8</v>
@@ -61053,7 +61053,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2334" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2334" t="s">
         <v>8</v>
@@ -61183,7 +61183,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G2339" t="n">
-        <v>1.85440385341644</v>
+        <v>1.85440373420715</v>
       </c>
       <c r="H2339" t="s">
         <v>8</v>
@@ -61261,7 +61261,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2342" t="n">
-        <v>1.89626574516296</v>
+        <v>1.89626586437225</v>
       </c>
       <c r="H2342" t="s">
         <v>8</v>
@@ -61287,7 +61287,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2343" t="n">
-        <v>1.93278396129608</v>
+        <v>1.93278384208679</v>
       </c>
       <c r="H2343" t="s">
         <v>8</v>
@@ -61313,7 +61313,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2344" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2344" t="s">
         <v>8</v>
@@ -61391,7 +61391,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2347" t="n">
-        <v>1.96841132640839</v>
+        <v>1.9684112071991</v>
       </c>
       <c r="H2347" t="s">
         <v>8</v>
@@ -61417,7 +61417,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2348" t="n">
-        <v>1.94525361061096</v>
+        <v>1.94525349140167</v>
       </c>
       <c r="H2348" t="s">
         <v>8</v>
@@ -61469,7 +61469,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G2350" t="n">
-        <v>1.9586136341095</v>
+        <v>1.95861351490021</v>
       </c>
       <c r="H2350" t="s">
         <v>8</v>
@@ -61495,7 +61495,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2351" t="n">
-        <v>1.93367457389832</v>
+        <v>1.9336746931076</v>
       </c>
       <c r="H2351" t="s">
         <v>8</v>
@@ -61573,7 +61573,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G2354" t="n">
-        <v>1.89537537097931</v>
+        <v>1.89537525177002</v>
       </c>
       <c r="H2354" t="s">
         <v>8</v>
@@ -61599,7 +61599,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G2355" t="n">
-        <v>1.72436380386353</v>
+        <v>1.72436392307281</v>
       </c>
       <c r="H2355" t="s">
         <v>8</v>
@@ -61755,7 +61755,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G2361" t="n">
-        <v>1.52128803730011</v>
+        <v>1.52128791809082</v>
       </c>
       <c r="H2361" t="s">
         <v>8</v>
@@ -61781,7 +61781,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G2362" t="n">
-        <v>1.56493139266968</v>
+        <v>1.56493151187897</v>
       </c>
       <c r="H2362" t="s">
         <v>8</v>
@@ -61937,7 +61937,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G2368" t="n">
-        <v>1.74930310249329</v>
+        <v>1.749302983284</v>
       </c>
       <c r="H2368" t="s">
         <v>8</v>
@@ -62015,7 +62015,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2371" t="n">
-        <v>1.82590174674988</v>
+        <v>1.82590186595917</v>
       </c>
       <c r="H2371" t="s">
         <v>8</v>
@@ -62067,7 +62067,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2373" t="n">
-        <v>1.85262227058411</v>
+        <v>1.8526223897934</v>
       </c>
       <c r="H2373" t="s">
         <v>8</v>
@@ -62093,7 +62093,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G2374" t="n">
-        <v>1.83302748203278</v>
+        <v>1.83302736282349</v>
       </c>
       <c r="H2374" t="s">
         <v>8</v>
@@ -62119,7 +62119,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G2375" t="n">
-        <v>1.82768332958221</v>
+        <v>1.82768321037292</v>
       </c>
       <c r="H2375" t="s">
         <v>8</v>
@@ -62145,7 +62145,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G2376" t="n">
-        <v>1.83837139606476</v>
+        <v>1.83837127685547</v>
       </c>
       <c r="H2376" t="s">
         <v>8</v>
@@ -62197,7 +62197,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G2378" t="n">
-        <v>1.9399094581604</v>
+        <v>1.93990933895111</v>
       </c>
       <c r="H2378" t="s">
         <v>8</v>
@@ -69142,6 +69142,32 @@
         <v>4.23400020599365</v>
       </c>
       <c r="H2645" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2646">
+      <c r="A2646" s="1" t="n">
+        <v>46175.2916666667</v>
+      </c>
+      <c r="B2646" t="n">
+        <v>17067359</v>
+      </c>
+      <c r="C2646" t="n">
+        <v>4.3439998626709</v>
+      </c>
+      <c r="D2646" t="n">
+        <v>4.20499992370605</v>
+      </c>
+      <c r="E2646" t="n">
+        <v>4.23400020599365</v>
+      </c>
+      <c r="F2646" t="n">
+        <v>4.3289999961853</v>
+      </c>
+      <c r="G2646" t="n">
+        <v>4.3289999961853</v>
+      </c>
+      <c r="H2646" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -447,7 +447,7 @@
         <v>23.2093391418457</v>
       </c>
       <c r="G3" t="n">
-        <v>20.5791072845459</v>
+        <v>20.5791053771973</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>22.3245735168457</v>
       </c>
       <c r="G4" t="n">
-        <v>19.7946071624756</v>
+        <v>19.7946090698242</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>22.4193687438965</v>
       </c>
       <c r="G8" t="n">
-        <v>19.878662109375</v>
+        <v>19.8786602020264</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>19.8440647125244</v>
       </c>
       <c r="G12" t="n">
-        <v>17.5952091217041</v>
+        <v>17.5952072143555</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>16.7157802581787</v>
       </c>
       <c r="G15" t="n">
-        <v>14.821439743042</v>
+        <v>14.8214406967163</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>15.7389078140259</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9552726745605</v>
+        <v>13.9552736282349</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087112426758</v>
+        <v>12.6087121963501</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G21" t="n">
-        <v>12.6977415084839</v>
+        <v>12.6977405548096</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.358302116394</v>
       </c>
       <c r="G22" t="n">
-        <v>12.7311277389526</v>
+        <v>12.7311267852783</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.8813648223877</v>
       </c>
       <c r="G23" t="n">
-        <v>12.30823802948</v>
+        <v>12.3082389831543</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G29" t="n">
-        <v>8.05711078643799</v>
+        <v>8.0571117401123</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G30" t="n">
-        <v>7.08892202377319</v>
+        <v>7.08892250061035</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G31" t="n">
-        <v>6.70832347869873</v>
+        <v>6.70832395553589</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393558502197</v>
+        <v>6.74393510818481</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.30120658874512</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36046028137207</v>
+        <v>7.36045980453491</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G40" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.67679214477539</v>
       </c>
       <c r="G45" t="n">
-        <v>8.58015632629395</v>
+        <v>8.58015537261963</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811388015747</v>
+        <v>7.98811340332031</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683300018311</v>
+        <v>8.58683395385742</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.26261138916016</v>
       </c>
       <c r="G54" t="n">
-        <v>8.21291351318359</v>
+        <v>8.21291255950928</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G57" t="n">
-        <v>8.15726852416992</v>
+        <v>8.15726947784424</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G59" t="n">
-        <v>8.20623397827148</v>
+        <v>8.2062349319458</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G60" t="n">
-        <v>7.75218725204468</v>
+        <v>7.75218772888184</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.3448805809021</v>
+        <v>7.34488010406494</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.93628597259521</v>
       </c>
       <c r="G62" t="n">
-        <v>7.92356872558594</v>
+        <v>7.92356824874878</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.78159713745117</v>
       </c>
       <c r="G66" t="n">
-        <v>6.89973640441895</v>
+        <v>6.89973592758179</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.93220806121826</v>
       </c>
       <c r="G67" t="n">
-        <v>7.03327894210815</v>
+        <v>7.03327941894531</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G70" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.86347436904907</v>
+        <v>7.86347389221191</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.87102127075195</v>
       </c>
       <c r="G74" t="n">
-        <v>7.86570072174072</v>
+        <v>7.86570024490356</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G75" t="n">
-        <v>8.27523231506348</v>
+        <v>8.27523136138916</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.25006008148193</v>
       </c>
       <c r="G79" t="n">
-        <v>8.20178318023682</v>
+        <v>8.20178413391113</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.55128288269043</v>
       </c>
       <c r="G81" t="n">
-        <v>8.46887016296387</v>
+        <v>8.46886920928955</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G83" t="n">
-        <v>9.68188858032227</v>
+        <v>9.68188762664795</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G84" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G87" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.36803913116455</v>
       </c>
       <c r="G90" t="n">
-        <v>8.30639171600342</v>
+        <v>8.30639266967773</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G96" t="n">
-        <v>8.31974697113037</v>
+        <v>8.31974601745605</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588848114014</v>
+        <v>7.98588800430298</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701642990112</v>
+        <v>7.99701690673828</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.14212131500244</v>
       </c>
       <c r="G101" t="n">
-        <v>8.10607719421387</v>
+        <v>8.10607814788818</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G103" t="n">
-        <v>8.39764595031738</v>
+        <v>8.3976469039917</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701642990112</v>
+        <v>7.99701690673828</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.5261812210083</v>
       </c>
       <c r="G111" t="n">
-        <v>8.44661235809326</v>
+        <v>8.44661331176758</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.28018188476562</v>
       </c>
       <c r="G114" t="n">
-        <v>8.22849273681641</v>
+        <v>8.22849178314209</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325372695923</v>
+        <v>7.72325325012207</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660612106323</v>
+        <v>7.73660659790039</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808290481567</v>
+        <v>7.96808242797852</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G118" t="n">
-        <v>7.78112173080444</v>
+        <v>7.78112125396729</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G119" t="n">
-        <v>8.20623397827148</v>
+        <v>8.2062349319458</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G123" t="n">
-        <v>9.00749397277832</v>
+        <v>9.00749492645264</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.0593376159668</v>
+        <v>8.05933666229248</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.59193563461304</v>
+        <v>7.5919361114502</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G131" t="n">
-        <v>8.15726852416992</v>
+        <v>8.15726947784424</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.44083404541016</v>
       </c>
       <c r="G134" t="n">
-        <v>8.37093830108643</v>
+        <v>8.37093734741211</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G137" t="n">
-        <v>9.25454902648926</v>
+        <v>9.25454998016357</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G138" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G141" t="n">
-        <v>9.55947208404541</v>
+        <v>9.55947303771973</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G144" t="n">
-        <v>9.68856525421143</v>
+        <v>9.68856620788574</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427124023438</v>
+        <v>9.78427219390869</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G151" t="n">
-        <v>8.27523231506348</v>
+        <v>8.27523136138916</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>9.3881196975708</v>
       </c>
       <c r="G152" t="n">
-        <v>8.32419776916504</v>
+        <v>8.32419681549072</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.0056276321411</v>
       </c>
       <c r="G156" t="n">
-        <v>8.87172603607178</v>
+        <v>8.87172508239746</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G157" t="n">
-        <v>8.77601909637451</v>
+        <v>8.7760181427002</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G160" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03642845153809</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G169" t="n">
-        <v>9.0809440612793</v>
+        <v>9.08094310760498</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>10.457462310791</v>
       </c>
       <c r="G174" t="n">
-        <v>9.2723560333252</v>
+        <v>9.27235507965088</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G176" t="n">
-        <v>9.20780944824219</v>
+        <v>9.2078104019165</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G179" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.95887660980225</v>
       </c>
       <c r="G183" t="n">
-        <v>7.94359827041626</v>
+        <v>7.94359874725342</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.07936668395996</v>
       </c>
       <c r="G184" t="n">
-        <v>8.05043411254883</v>
+        <v>8.05043315887451</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.79225063323975</v>
+        <v>7.7922511100769</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.91871356964111</v>
       </c>
       <c r="G189" t="n">
-        <v>7.90798664093018</v>
+        <v>7.90798711776733</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.73883247375488</v>
+        <v>7.73883295059204</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G192" t="n">
-        <v>8.15726852416992</v>
+        <v>8.15726947784424</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G197" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.77217960357666</v>
       </c>
       <c r="G198" t="n">
-        <v>8.66473388671875</v>
+        <v>8.66473293304443</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G199" t="n">
-        <v>8.94294834136963</v>
+        <v>8.94294929504395</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G203" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.8139095306396</v>
       </c>
       <c r="G206" t="n">
-        <v>9.58840751647949</v>
+        <v>9.58840847015381</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G207" t="n">
-        <v>9.68856525421143</v>
+        <v>9.68856620788574</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G209" t="n">
-        <v>9.68188858032227</v>
+        <v>9.68188762664795</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03642845153809</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G212" t="n">
-        <v>8.80272769927979</v>
+        <v>8.8027286529541</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.34645462036133</v>
+        <v>8.34645557403564</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G224" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.2240142822266</v>
       </c>
       <c r="G225" t="n">
-        <v>9.06536388397217</v>
+        <v>9.06536293029785</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.0834436416626</v>
       </c>
       <c r="G226" t="n">
-        <v>8.94072341918945</v>
+        <v>8.94072246551514</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.1185855865479</v>
       </c>
       <c r="G229" t="n">
-        <v>8.97188186645508</v>
+        <v>8.97188091278076</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.2215042114258</v>
       </c>
       <c r="G231" t="n">
-        <v>9.06313705444336</v>
+        <v>9.06313800811768</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G232" t="n">
-        <v>9.16329383850098</v>
+        <v>9.16329479217529</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G233" t="n">
-        <v>8.92514324188232</v>
+        <v>8.92514228820801</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.9695415496826</v>
       </c>
       <c r="G237" t="n">
-        <v>9.72640323638916</v>
+        <v>9.72640228271484</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.6507472991943</v>
       </c>
       <c r="G238" t="n">
-        <v>9.44373607635498</v>
+        <v>9.4437370300293</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>11.484130859375</v>
       </c>
       <c r="G240" t="n">
-        <v>10.1826753616333</v>
+        <v>10.182674407959</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>11.6347427368164</v>
       </c>
       <c r="G241" t="n">
-        <v>10.3162183761597</v>
+        <v>10.316219329834</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G246" t="n">
-        <v>10.5721769332886</v>
+        <v>10.5721759796143</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.9309453964233</v>
       </c>
       <c r="G247" t="n">
-        <v>10.5788545608521</v>
+        <v>10.5788536071777</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>12.8019819259644</v>
       </c>
       <c r="G250" t="n">
-        <v>11.3511781692505</v>
+        <v>11.3511791229248</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>12.8772878646851</v>
       </c>
       <c r="G253" t="n">
-        <v>11.4179496765137</v>
+        <v>11.417950630188</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>13.2287149429321</v>
       </c>
       <c r="G255" t="n">
-        <v>11.7295522689819</v>
+        <v>11.7295513153076</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.0319766998291</v>
       </c>
       <c r="G258" t="n">
-        <v>12.441782951355</v>
+        <v>12.4417819976807</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G259" t="n">
-        <v>12.6977415084839</v>
+        <v>12.6977405548096</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>13.9817733764648</v>
       </c>
       <c r="G260" t="n">
-        <v>12.3972692489624</v>
+        <v>12.3972682952881</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195251464844</v>
+        <v>12.4195261001587</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858253479004</v>
+        <v>12.1858243942261</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.3165721893311</v>
       </c>
       <c r="G263" t="n">
-        <v>11.8074522018433</v>
+        <v>11.8074531555176</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>12.7517786026001</v>
       </c>
       <c r="G264" t="n">
-        <v>11.3066644668579</v>
+        <v>11.3066654205322</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>12.7392282485962</v>
       </c>
       <c r="G266" t="n">
-        <v>11.2955369949341</v>
+        <v>11.2955360412598</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619920730591</v>
+        <v>11.1619930267334</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>12.4455347061157</v>
       </c>
       <c r="G273" t="n">
-        <v>11.0351266860962</v>
+        <v>11.0351257324219</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.5007591247559</v>
       </c>
       <c r="G274" t="n">
-        <v>11.0840930938721</v>
+        <v>11.0840921401978</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>13.3040208816528</v>
       </c>
       <c r="G275" t="n">
-        <v>11.7963237762451</v>
+        <v>11.7963228225708</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>12.1995363235474</v>
       </c>
       <c r="G278" t="n">
-        <v>10.817006111145</v>
+        <v>10.8170070648193</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.2516717910767</v>
+        <v>10.251672744751</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>11.3711729049683</v>
       </c>
       <c r="G285" t="n">
-        <v>10.0825185775757</v>
+        <v>10.0825176239014</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651847839355</v>
+        <v>10.3651857376099</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>11.3787031173706</v>
       </c>
       <c r="G290" t="n">
-        <v>10.0891952514648</v>
+        <v>10.0891962051392</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939605712891</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G297" t="n">
-        <v>9.36360931396484</v>
+        <v>9.36361026763916</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>10.5754413604736</v>
       </c>
       <c r="G298" t="n">
-        <v>9.3769645690918</v>
+        <v>9.37696361541748</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.5428085327148</v>
       </c>
       <c r="G303" t="n">
-        <v>9.34802913665771</v>
+        <v>9.34803009033203</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G305" t="n">
-        <v>9.25454902648926</v>
+        <v>9.25454998016357</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G306" t="n">
-        <v>9.00749397277832</v>
+        <v>9.00749492645264</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.2491159439087</v>
       </c>
       <c r="G308" t="n">
-        <v>9.08761978149414</v>
+        <v>9.08762073516846</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520709991455</v>
+        <v>8.96520614624023</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.3244218826294</v>
       </c>
       <c r="G311" t="n">
-        <v>9.15439128875732</v>
+        <v>9.15439224243164</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G313" t="n">
-        <v>9.01639747619629</v>
+        <v>9.01639652252197</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539485931396</v>
+        <v>9.08539390563965</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G319" t="n">
-        <v>9.39254474639893</v>
+        <v>9.39254379272461</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>10.6808700561523</v>
       </c>
       <c r="G322" t="n">
-        <v>9.47044563293457</v>
+        <v>9.47044467926025</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G325" t="n">
-        <v>9.51050662994385</v>
+        <v>9.51050758361816</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>10.7310733795166</v>
       </c>
       <c r="G326" t="n">
-        <v>9.51495838165283</v>
+        <v>9.51495933532715</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>10.2691984176636</v>
       </c>
       <c r="G331" t="n">
-        <v>9.10542583465576</v>
+        <v>9.10542678833008</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>10.0106477737427</v>
       </c>
       <c r="G332" t="n">
-        <v>8.87617683410645</v>
+        <v>8.87617588043213</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10.0784225463867</v>
       </c>
       <c r="G333" t="n">
-        <v>8.93627071380615</v>
+        <v>8.93626976013184</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.2033576965332</v>
+        <v>9.20335865020752</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G339" t="n">
-        <v>8.94294834136963</v>
+        <v>8.94294929504395</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.36301803588867</v>
       </c>
       <c r="G359" t="n">
-        <v>8.30193996429443</v>
+        <v>8.30194091796875</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G362" t="n">
-        <v>8.0348539352417</v>
+        <v>8.03485298156738</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.9903392791748</v>
+        <v>7.99033975601196</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>8.97142791748047</v>
       </c>
       <c r="G364" t="n">
-        <v>7.95472764968872</v>
+        <v>7.95472812652588</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G365" t="n">
-        <v>7.78112173080444</v>
+        <v>7.78112125396729</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G366" t="n">
-        <v>7.66093349456787</v>
+        <v>7.66093301773071</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G370" t="n">
-        <v>8.05711078643799</v>
+        <v>8.0571117401123</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G373" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.13302421569824</v>
       </c>
       <c r="G377" t="n">
-        <v>7.21133708953857</v>
+        <v>7.21133756637573</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817150115967</v>
+        <v>7.31817197799683</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G383" t="n">
-        <v>7.23804521560669</v>
+        <v>7.23804569244385</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055559158325</v>
+        <v>7.42055511474609</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G392" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.85679578781128</v>
+        <v>7.8567967414856</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>8.52461433410645</v>
       </c>
       <c r="G397" t="n">
-        <v>7.55854988098145</v>
+        <v>7.5585503578186</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G403" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.5748176574707</v>
       </c>
       <c r="G411" t="n">
-        <v>7.60306406021118</v>
+        <v>7.60306358337402</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>8.53967475891113</v>
       </c>
       <c r="G412" t="n">
-        <v>7.57190418243408</v>
+        <v>7.57190370559692</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249744415283</v>
+        <v>7.24249792098999</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.15812587738037</v>
       </c>
       <c r="G417" t="n">
-        <v>7.23359441757202</v>
+        <v>7.23359489440918</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7.93220806121826</v>
       </c>
       <c r="G420" t="n">
-        <v>7.03327894210815</v>
+        <v>7.03327941894531</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>7.68621015548706</v>
       </c>
       <c r="G424" t="n">
-        <v>6.81515884399414</v>
+        <v>6.8151593208313</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.74645376205444</v>
       </c>
       <c r="G428" t="n">
-        <v>6.86857604980469</v>
+        <v>6.86857557296753</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.00751399993896</v>
       </c>
       <c r="G430" t="n">
-        <v>7.1000509262085</v>
+        <v>7.10005044937134</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G432" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G440" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G449" t="n">
-        <v>8.03040313720703</v>
+        <v>8.03040218353271</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692302703857</v>
+        <v>7.93692350387573</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.15216159820557</v>
       </c>
       <c r="G455" t="n">
-        <v>8.11497974395752</v>
+        <v>8.1149787902832</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.82081699371338</v>
       </c>
       <c r="G456" t="n">
-        <v>7.82118511199951</v>
+        <v>7.82118463516235</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G457" t="n">
-        <v>7.77221822738647</v>
+        <v>7.77221775054932</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.85093879699707</v>
       </c>
       <c r="G458" t="n">
-        <v>7.84789323806763</v>
+        <v>7.84789371490479</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.92122364044189</v>
       </c>
       <c r="G459" t="n">
-        <v>7.91021299362183</v>
+        <v>7.91021251678467</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G460" t="n">
-        <v>7.78112173080444</v>
+        <v>7.78112125396729</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G464" t="n">
-        <v>7.23804521560669</v>
+        <v>7.23804569244385</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>9.04673385620117</v>
       </c>
       <c r="G465" t="n">
-        <v>8.02149963378906</v>
+        <v>8.02150058746338</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479103088379</v>
+        <v>7.99479150772095</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G470" t="n">
-        <v>8.03040313720703</v>
+        <v>8.03040218353271</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.63914012908936</v>
       </c>
       <c r="G472" t="n">
-        <v>8.5467700958252</v>
+        <v>8.54677104949951</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G476" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576219558716</v>
+        <v>7.90576267242432</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G490" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G495" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>8.44930839538574</v>
       </c>
       <c r="G497" t="n">
-        <v>7.4917778968811</v>
+        <v>7.49177837371826</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G500" t="n">
-        <v>7.77221822738647</v>
+        <v>7.77221775054932</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G501" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G505" t="n">
-        <v>8.03040313720703</v>
+        <v>8.03040218353271</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>9.11199855804443</v>
       </c>
       <c r="G506" t="n">
-        <v>8.07936859130859</v>
+        <v>8.07936763763428</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.55379295349121</v>
       </c>
       <c r="G511" t="n">
-        <v>8.47109603881836</v>
+        <v>8.47109508514404</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.50670719146729</v>
+        <v>8.5067081451416</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.76464939117432</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65805530548096</v>
+        <v>8.65805625915527</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>10.1210966110229</v>
       </c>
       <c r="G519" t="n">
-        <v>8.9741096496582</v>
+        <v>8.97410869598389</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03642845153809</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G528" t="n">
-        <v>9.1655216217041</v>
+        <v>9.16552066802979</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.60399723052979</v>
       </c>
       <c r="G532" t="n">
-        <v>8.51561069488525</v>
+        <v>8.51560974121094</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>9.46593570709229</v>
       </c>
       <c r="G533" t="n">
-        <v>8.3931941986084</v>
+        <v>8.39319515228271</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.41990566253662</v>
+        <v>8.4199047088623</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>9.30277442932129</v>
       </c>
       <c r="G535" t="n">
-        <v>8.2485237121582</v>
+        <v>8.24852466583252</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G538" t="n">
-        <v>8.0348539352417</v>
+        <v>8.03485298156738</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660612106323</v>
+        <v>7.73660659790039</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519605636597</v>
+        <v>7.54519557952881</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G545" t="n">
-        <v>7.66093349456787</v>
+        <v>7.66093301773071</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G548" t="n">
-        <v>7.60083866119385</v>
+        <v>7.60083818435669</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.7633171081543</v>
+        <v>7.76331663131714</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.52293872833252</v>
+        <v>7.52293825149536</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663805007935</v>
+        <v>7.7566385269165</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G560" t="n">
-        <v>7.75218725204468</v>
+        <v>7.75218772888184</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.31124782562256</v>
       </c>
       <c r="G564" t="n">
-        <v>7.36936378479004</v>
+        <v>7.36936330795288</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613433837891</v>
+        <v>7.43613481521606</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.32128810882568</v>
       </c>
       <c r="G567" t="n">
-        <v>7.37826585769653</v>
+        <v>7.37826633453369</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>8.43173694610596</v>
       </c>
       <c r="G568" t="n">
-        <v>7.47619819641113</v>
+        <v>7.47619867324829</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>8.16063594818115</v>
       </c>
       <c r="G569" t="n">
-        <v>7.23581981658936</v>
+        <v>7.23582029342651</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>8.03512573242188</v>
       </c>
       <c r="G571" t="n">
-        <v>7.12453365325928</v>
+        <v>7.12453317642212</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G573" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744667053223</v>
+        <v>6.85744714736938</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G581" t="n">
-        <v>7.08892202377319</v>
+        <v>7.08892250061035</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G583" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G586" t="n">
-        <v>7.48064947128296</v>
+        <v>7.4806489944458</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610383987427</v>
+        <v>7.41610431671143</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G589" t="n">
-        <v>7.48064947128296</v>
+        <v>7.4806489944458</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443881988525</v>
+        <v>7.06443929672241</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>7.92969799041748</v>
       </c>
       <c r="G596" t="n">
-        <v>7.03105306625366</v>
+        <v>7.03105354309082</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>10.0909738540649</v>
       </c>
       <c r="G609" t="n">
-        <v>8.9473991394043</v>
+        <v>8.94740009307861</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37539005279541</v>
+        <v>8.37538909912109</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.31783485412598</v>
       </c>
       <c r="G620" t="n">
-        <v>8.26187896728516</v>
+        <v>8.26187801361084</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G621" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902694702148</v>
+        <v>8.56902599334717</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G627" t="n">
-        <v>8.27523231506348</v>
+        <v>8.27523136138916</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G636" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009632110596</v>
+        <v>9.25009727478027</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G646" t="n">
-        <v>9.39254474639893</v>
+        <v>9.39254379272461</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>10.0608520507812</v>
       </c>
       <c r="G649" t="n">
-        <v>8.92069149017334</v>
+        <v>8.92069053649902</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G650" t="n">
-        <v>9.01639747619629</v>
+        <v>9.01639652252197</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.948974609375</v>
+        <v>9.94897556304932</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>11.401294708252</v>
       </c>
       <c r="G658" t="n">
-        <v>10.1092262268066</v>
+        <v>10.109227180481</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G661" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G662" t="n">
-        <v>9.31686973571777</v>
+        <v>9.31686878204346</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G664" t="n">
-        <v>9.79317378997803</v>
+        <v>9.79317283630371</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>11.2331123352051</v>
       </c>
       <c r="G666" t="n">
-        <v>9.96010303497314</v>
+        <v>9.96010398864746</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>11.6322326660156</v>
       </c>
       <c r="G669" t="n">
-        <v>10.3139934539795</v>
+        <v>10.3139925003052</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>11.6648645401001</v>
       </c>
       <c r="G674" t="n">
-        <v>10.3429269790649</v>
+        <v>10.3429260253906</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939605712891</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G678" t="n">
-        <v>10.0157451629639</v>
+        <v>10.0157461166382</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>11.3711729049683</v>
       </c>
       <c r="G679" t="n">
-        <v>10.0825185775757</v>
+        <v>10.0825176239014</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>11.700008392334</v>
       </c>
       <c r="G683" t="n">
-        <v>10.3740882873535</v>
+        <v>10.3740873336792</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>11.5017032623291</v>
       </c>
       <c r="G688" t="n">
-        <v>10.1982564926147</v>
+        <v>10.1982555389404</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>11.328498840332</v>
       </c>
       <c r="G690" t="n">
-        <v>10.0446796417236</v>
+        <v>10.0446805953979</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G691" t="n">
-        <v>10.3941192626953</v>
+        <v>10.394118309021</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>12.0489253997803</v>
       </c>
       <c r="G692" t="n">
-        <v>10.683464050293</v>
+        <v>10.6834630966187</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>12.0238227844238</v>
       </c>
       <c r="G696" t="n">
-        <v>10.661205291748</v>
+        <v>10.6612062454224</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>12.4580860137939</v>
       </c>
       <c r="G697" t="n">
-        <v>11.0462551116943</v>
+        <v>11.0462560653687</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>13.1232872009277</v>
       </c>
       <c r="G698" t="n">
-        <v>11.6360721588135</v>
+        <v>11.6360712051392</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>13.2086343765259</v>
       </c>
       <c r="G699" t="n">
-        <v>11.7117462158203</v>
+        <v>11.7117471694946</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>13.233736038208</v>
       </c>
       <c r="G700" t="n">
-        <v>11.7340040206909</v>
+        <v>11.7340030670166</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>13.5500202178955</v>
       </c>
       <c r="G702" t="n">
-        <v>12.014443397522</v>
+        <v>12.0144443511963</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>13.7558555603027</v>
       </c>
       <c r="G704" t="n">
-        <v>12.1969537734985</v>
+        <v>12.1969528198242</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856685638428</v>
+        <v>12.0856676101685</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>13.032919883728</v>
       </c>
       <c r="G706" t="n">
-        <v>11.5559453964233</v>
+        <v>11.555944442749</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>12.7618188858032</v>
       </c>
       <c r="G709" t="n">
-        <v>11.3155670166016</v>
+        <v>11.3155660629272</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395774841309</v>
+        <v>11.0395765304565</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>12.3325757980347</v>
       </c>
       <c r="G714" t="n">
-        <v>10.9349689483643</v>
+        <v>10.9349679946899</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G720" t="n">
-        <v>10.5721769332886</v>
+        <v>10.5721759796143</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>11.7979049682617</v>
       </c>
       <c r="G721" t="n">
-        <v>10.4608898162842</v>
+        <v>10.4608907699585</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G722" t="n">
-        <v>10.5721769332886</v>
+        <v>10.5721759796143</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>11.8857622146606</v>
       </c>
       <c r="G723" t="n">
-        <v>10.5387916564941</v>
+        <v>10.5387907028198</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G725" t="n">
-        <v>10.3941192626953</v>
+        <v>10.394118309021</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>11.7025184631348</v>
       </c>
       <c r="G727" t="n">
-        <v>10.376314163208</v>
+        <v>10.3763132095337</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G728" t="n">
-        <v>10.1604175567627</v>
+        <v>10.160418510437</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006381988525</v>
+        <v>10.3006391525269</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>11.7251100540161</v>
       </c>
       <c r="G730" t="n">
-        <v>10.3963441848755</v>
+        <v>10.3963451385498</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>11.1251735687256</v>
       </c>
       <c r="G731" t="n">
-        <v>9.8643970489502</v>
+        <v>9.86439800262451</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>11.1377248764038</v>
       </c>
       <c r="G732" t="n">
-        <v>9.87552642822266</v>
+        <v>9.87552547454834</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>10.5402994155884</v>
       </c>
       <c r="G735" t="n">
-        <v>9.34580516815186</v>
+        <v>9.34580421447754</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081153869629</v>
+        <v>8.29081058502197</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>9.65169143676758</v>
       </c>
       <c r="G742" t="n">
-        <v>8.55789947509766</v>
+        <v>8.55790042877197</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G744" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.65922069549561</v>
       </c>
       <c r="G745" t="n">
-        <v>8.56457614898682</v>
+        <v>8.5645751953125</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>10.0307302474976</v>
       </c>
       <c r="G748" t="n">
-        <v>8.89398288726807</v>
+        <v>8.89398384094238</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>8.81077575683594</v>
       </c>
       <c r="G756" t="n">
-        <v>7.81228256225586</v>
+        <v>7.8122820854187</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>8.25602340698242</v>
       </c>
       <c r="G758" t="n">
-        <v>7.32039785385132</v>
+        <v>7.32039737701416</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G759" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>8.17318725585938</v>
       </c>
       <c r="G760" t="n">
-        <v>7.24694919586182</v>
+        <v>7.24694871902466</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>8.19577884674072</v>
       </c>
       <c r="G763" t="n">
-        <v>7.26698017120361</v>
+        <v>7.26698064804077</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>8.37400245666504</v>
       </c>
       <c r="G765" t="n">
-        <v>7.42500686645508</v>
+        <v>7.42500638961792</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576219558716</v>
+        <v>7.90576267242432</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G771" t="n">
-        <v>8.39764595031738</v>
+        <v>8.3976469039917</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096927642822</v>
+        <v>8.39096832275391</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G778" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G779" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>10.2817487716675</v>
       </c>
       <c r="G786" t="n">
-        <v>9.11655521392822</v>
+        <v>9.11655426025391</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>10.3445043563843</v>
       </c>
       <c r="G787" t="n">
-        <v>9.17219924926758</v>
+        <v>9.17219829559326</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G788" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G795" t="n">
-        <v>9.0809440612793</v>
+        <v>9.08094310760498</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G796" t="n">
-        <v>9.43705940246582</v>
+        <v>9.4370584487915</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G799" t="n">
-        <v>9.41480159759521</v>
+        <v>9.41480255126953</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>10.6557683944702</v>
       </c>
       <c r="G800" t="n">
-        <v>9.44818782806396</v>
+        <v>9.44818878173828</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>10.6833801269531</v>
       </c>
       <c r="G801" t="n">
-        <v>9.47267055511475</v>
+        <v>9.47266960144043</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G804" t="n">
-        <v>9.69746780395508</v>
+        <v>9.69746685028076</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G805" t="n">
-        <v>10.1604175567627</v>
+        <v>10.160418510437</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496046066284</v>
+        <v>10.3496055603027</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.2572708129883</v>
       </c>
       <c r="G814" t="n">
-        <v>10.8681974411011</v>
+        <v>10.8681983947754</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147802352905</v>
+        <v>10.8147792816162</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>12.2522497177124</v>
       </c>
       <c r="G829" t="n">
-        <v>10.8637447357178</v>
+        <v>10.8637456893921</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>12.4856977462769</v>
       </c>
       <c r="G831" t="n">
-        <v>11.0707368850708</v>
+        <v>11.0707378387451</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>12.6312885284424</v>
       </c>
       <c r="G832" t="n">
-        <v>11.1998300552368</v>
+        <v>11.1998291015625</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>12.0991277694702</v>
       </c>
       <c r="G834" t="n">
-        <v>10.7279777526855</v>
+        <v>10.7279767990112</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G835" t="n">
-        <v>10.4386339187622</v>
+        <v>10.4386329650879</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>11.5343351364136</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2271909713745</v>
+        <v>10.2271900177002</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G839" t="n">
-        <v>10.4386339187622</v>
+        <v>10.4386329650879</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>12.0564546585083</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6901388168335</v>
+        <v>10.6901397705078</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>11.8154773712158</v>
       </c>
       <c r="G843" t="n">
-        <v>10.4764719009399</v>
+        <v>10.4764709472656</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>11.3385400772095</v>
       </c>
       <c r="G846" t="n">
-        <v>10.0535840988159</v>
+        <v>10.0535831451416</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>10.836501121521</v>
       </c>
       <c r="G849" t="n">
-        <v>9.60843849182129</v>
+        <v>9.60843944549561</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>10.203932762146</v>
       </c>
       <c r="G854" t="n">
-        <v>9.04755687713623</v>
+        <v>9.04755783081055</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G855" t="n">
-        <v>9.32577323913574</v>
+        <v>9.32577228546143</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G859" t="n">
-        <v>9.16329383850098</v>
+        <v>9.16329479217529</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G863" t="n">
-        <v>8.77601909637451</v>
+        <v>8.7760181427002</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>9.62156772613525</v>
       </c>
       <c r="G868" t="n">
-        <v>8.53118991851807</v>
+        <v>8.53118896484375</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>10.768726348877</v>
       </c>
       <c r="G874" t="n">
-        <v>9.54834461212158</v>
+        <v>9.5483455657959</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G880" t="n">
-        <v>9.55947208404541</v>
+        <v>9.55947303771973</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G881" t="n">
-        <v>9.6062126159668</v>
+        <v>9.60621356964111</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>11.0699491500854</v>
       </c>
       <c r="G883" t="n">
-        <v>9.81543064117432</v>
+        <v>9.81543159484863</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.0498676300049</v>
       </c>
       <c r="G887" t="n">
-        <v>9.79762554168701</v>
+        <v>9.7976245880127</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G890" t="n">
-        <v>9.69746780395508</v>
+        <v>9.69746685028076</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>11.0272760391235</v>
       </c>
       <c r="G893" t="n">
-        <v>9.77759456634521</v>
+        <v>9.7775936126709</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>11.2130298614502</v>
       </c>
       <c r="G894" t="n">
-        <v>9.94229698181152</v>
+        <v>9.94229602813721</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.948974609375</v>
+        <v>9.94897556304932</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>11.3987846374512</v>
       </c>
       <c r="G898" t="n">
-        <v>10.1070003509521</v>
+        <v>10.1070013046265</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>11.2381324768066</v>
       </c>
       <c r="G899" t="n">
-        <v>9.96455478668213</v>
+        <v>9.96455574035645</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>11.1603164672852</v>
       </c>
       <c r="G901" t="n">
-        <v>9.89555740356445</v>
+        <v>9.89555835723877</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G906" t="n">
-        <v>10.0157451629639</v>
+        <v>10.0157461166382</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G910" t="n">
-        <v>9.75088500976562</v>
+        <v>9.75088596343994</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>11.1829080581665</v>
       </c>
       <c r="G912" t="n">
-        <v>9.91558837890625</v>
+        <v>9.91558933258057</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G914" t="n">
-        <v>9.20780944824219</v>
+        <v>9.2078104019165</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G916" t="n">
-        <v>8.92514324188232</v>
+        <v>8.92514228820801</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>10.3721160888672</v>
       </c>
       <c r="G917" t="n">
-        <v>9.19668102264404</v>
+        <v>9.19668006896973</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>9.84497547149658</v>
       </c>
       <c r="G921" t="n">
-        <v>8.72927951812744</v>
+        <v>8.72927856445312</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>10.2842588424683</v>
       </c>
       <c r="G927" t="n">
-        <v>9.11878108978271</v>
+        <v>9.1187801361084</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>10.3545436859131</v>
       </c>
       <c r="G928" t="n">
-        <v>9.18110084533691</v>
+        <v>9.1810998916626</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G929" t="n">
-        <v>9.41480159759521</v>
+        <v>9.41480255126953</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>10.7586851119995</v>
       </c>
       <c r="G930" t="n">
-        <v>9.53944110870361</v>
+        <v>9.53944206237793</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>10.9092969894409</v>
       </c>
       <c r="G931" t="n">
-        <v>9.67298603057861</v>
+        <v>9.6729850769043</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G934" t="n">
-        <v>9.43705940246582</v>
+        <v>9.4370584487915</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.1047744750977</v>
+        <v>10.104775428772</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230537414551</v>
+        <v>10.4230527877808</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>11.2155408859253</v>
       </c>
       <c r="G944" t="n">
-        <v>9.94452285766602</v>
+        <v>9.94452381134033</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>11.1854181289673</v>
       </c>
       <c r="G945" t="n">
-        <v>9.91781520843506</v>
+        <v>9.91781425476074</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>10.7862977981567</v>
       </c>
       <c r="G949" t="n">
-        <v>9.56392383575439</v>
+        <v>9.56392478942871</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G950" t="n">
-        <v>9.36360931396484</v>
+        <v>9.36361026763916</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>10.2164840698242</v>
       </c>
       <c r="G954" t="n">
-        <v>9.05868530273438</v>
+        <v>9.05868625640869</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>10.0683822631836</v>
       </c>
       <c r="G955" t="n">
-        <v>8.9273681640625</v>
+        <v>8.92736911773682</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G958" t="n">
-        <v>9.1655216217041</v>
+        <v>9.16552066802979</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>10.1612596511841</v>
       </c>
       <c r="G960" t="n">
-        <v>9.00971984863281</v>
+        <v>9.00972080230713</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G962" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G964" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G965" t="n">
-        <v>9.31686973571777</v>
+        <v>9.31686878204346</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>10.3294429779053</v>
       </c>
       <c r="G968" t="n">
-        <v>9.15884304046631</v>
+        <v>9.15884399414062</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>10.2792387008667</v>
       </c>
       <c r="G969" t="n">
-        <v>9.11433029174805</v>
+        <v>9.11432933807373</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>10.6557683944702</v>
       </c>
       <c r="G971" t="n">
-        <v>9.44818782806396</v>
+        <v>9.44818878173828</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65962982177734</v>
+        <v>9.65963077545166</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G974" t="n">
-        <v>9.51050662994385</v>
+        <v>9.51050758361816</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03642845153809</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G978" t="n">
-        <v>9.6062126159668</v>
+        <v>9.60621356964111</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>11.1904392242432</v>
       </c>
       <c r="G979" t="n">
-        <v>9.92226696014404</v>
+        <v>9.92226600646973</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>11.1402349472046</v>
       </c>
       <c r="G982" t="n">
-        <v>9.87775230407715</v>
+        <v>9.87775135040283</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>11.0573978424072</v>
       </c>
       <c r="G983" t="n">
-        <v>9.80430126190186</v>
+        <v>9.80430221557617</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G994" t="n">
-        <v>9.45931529998779</v>
+        <v>9.45931625366211</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.39254474639893</v>
+        <v>9.39254379272461</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G1004" t="n">
-        <v>9.36360931396484</v>
+        <v>9.36361026763916</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G1008" t="n">
-        <v>9.45931529998779</v>
+        <v>9.45931625366211</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>10.7938280105591</v>
       </c>
       <c r="G1009" t="n">
-        <v>9.57060241699219</v>
+        <v>9.57060146331787</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G1014" t="n">
-        <v>9.75088500976562</v>
+        <v>9.75088596343994</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G1016" t="n">
-        <v>9.75088500976562</v>
+        <v>9.75088596343994</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.79317378997803</v>
+        <v>9.79317283630371</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>11.1251735687256</v>
       </c>
       <c r="G1028" t="n">
-        <v>9.8643970489502</v>
+        <v>9.86439800262451</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G1031" t="n">
-        <v>9.25454902648926</v>
+        <v>9.25454998016357</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.20623397827148</v>
+        <v>8.2062349319458</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.31974697113037</v>
+        <v>8.31974601745605</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>9.75962924957275</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.65360450744629</v>
+        <v>8.65360546112061</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.34645462036133</v>
+        <v>8.34645557403564</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>9.63411903381348</v>
       </c>
       <c r="G1046" t="n">
-        <v>8.54231834411621</v>
+        <v>8.54231929779053</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>9.51362991333008</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.43548488616943</v>
+        <v>8.43548393249512</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657657623291</v>
+        <v>7.71657609939575</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754774093628</v>
+        <v>7.62754726409912</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.60083866119385</v>
+        <v>7.60083818435669</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.70832347869873</v>
+        <v>6.70832395553589</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>4.89613008499146</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.34126901626587</v>
+        <v>4.34126949310303</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>5.16848611831665</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.58276033401489</v>
+        <v>4.58275985717773</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>5.18605804443359</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.59834051132202</v>
+        <v>4.59834003448486</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1078" t="n">
-        <v>4.98561573028564</v>
+        <v>4.98561525344849</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1079" t="n">
-        <v>4.98561573028564</v>
+        <v>4.98561525344849</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.0219521522522</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.33950614929199</v>
+        <v>5.33950567245483</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>5.9014630317688</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.23267078399658</v>
+        <v>5.23267126083374</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>6.04956388473511</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.36398887634277</v>
+        <v>5.36398839950562</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>5.47473001480103</v>
       </c>
       <c r="G1089" t="n">
-        <v>4.85429811477661</v>
+        <v>4.85429859161377</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>5.67303514480591</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.03012990951538</v>
+        <v>5.03013038635254</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>5.80858516693115</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15031862258911</v>
+        <v>5.15031909942627</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>5.59521913528442</v>
       </c>
       <c r="G1108" t="n">
-        <v>4.96113300323486</v>
+        <v>4.96113252639771</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -69168,6 +69168,32 @@
         <v>4.3289999961853</v>
       </c>
       <c r="H2646" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2647">
+      <c r="A2647" s="1" t="n">
+        <v>46176.2916666667</v>
+      </c>
+      <c r="B2647" t="n">
+        <v>17803818</v>
+      </c>
+      <c r="C2647" t="n">
+        <v>4.39099979400635</v>
+      </c>
+      <c r="D2647" t="n">
+        <v>4.30900001525879</v>
+      </c>
+      <c r="E2647" t="n">
+        <v>4.34800004959106</v>
+      </c>
+      <c r="F2647" t="n">
+        <v>4.30900001525879</v>
+      </c>
+      <c r="G2647" t="n">
+        <v>4.30900001525879</v>
+      </c>
+      <c r="H2647" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>22.8775520324707</v>
       </c>
       <c r="G2" t="n">
-        <v>20.2849197387695</v>
+        <v>20.2849216461182</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>23.2093391418457</v>
       </c>
       <c r="G3" t="n">
-        <v>20.5791053771973</v>
+        <v>20.5791072845459</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>21.9295864105225</v>
       </c>
       <c r="G5" t="n">
-        <v>19.4443836212158</v>
+        <v>19.4443855285645</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>21.3766078948975</v>
       </c>
       <c r="G6" t="n">
-        <v>18.9540729522705</v>
+        <v>18.9540710449219</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>22.4193687438965</v>
       </c>
       <c r="G8" t="n">
-        <v>19.8786602020264</v>
+        <v>19.878662109375</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>22.1665782928467</v>
       </c>
       <c r="G9" t="n">
-        <v>19.6545181274414</v>
+        <v>19.65452003479</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>22.1823787689209</v>
       </c>
       <c r="G10" t="n">
-        <v>19.668529510498</v>
+        <v>19.6685276031494</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811958312988</v>
+        <v>17.5811977386475</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460289001465</v>
+        <v>15.7460279464722</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>15.7389078140259</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9552736282349</v>
+        <v>13.9552726745605</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087121963501</v>
+        <v>12.6087112426758</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G21" t="n">
-        <v>12.6977405548096</v>
+        <v>12.6977415084839</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.0530023574829</v>
       </c>
       <c r="G26" t="n">
-        <v>11.573751449585</v>
+        <v>11.5737524032593</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>9.75209808349609</v>
       </c>
       <c r="G27" t="n">
-        <v>8.64692783355713</v>
+        <v>8.64692687988281</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G31" t="n">
-        <v>6.70832395553589</v>
+        <v>6.70832443237305</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393510818481</v>
+        <v>6.74393558502197</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51180982589722</v>
+        <v>7.51180934906006</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243934631348</v>
+        <v>7.91243982315063</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>10.6884002685547</v>
       </c>
       <c r="G47" t="n">
-        <v>9.47712135314941</v>
+        <v>9.47712230682373</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.07714366912842</v>
+        <v>8.0771427154541</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683395385742</v>
+        <v>8.58683300018311</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.26261138916016</v>
       </c>
       <c r="G54" t="n">
-        <v>8.21291255950928</v>
+        <v>8.21291351318359</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G57" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G60" t="n">
-        <v>7.75218772888184</v>
+        <v>7.75218820571899</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.93628597259521</v>
       </c>
       <c r="G62" t="n">
-        <v>7.92356824874878</v>
+        <v>7.92356872558594</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.78159713745117</v>
       </c>
       <c r="G66" t="n">
-        <v>6.89973592758179</v>
+        <v>6.89973640441895</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.93220806121826</v>
       </c>
       <c r="G67" t="n">
-        <v>7.03327941894531</v>
+        <v>7.03327894210815</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G71" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.86347389221191</v>
+        <v>7.8634729385376</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09939956665039</v>
+        <v>8.09940052032471</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.87102127075195</v>
       </c>
       <c r="G74" t="n">
-        <v>7.86570024490356</v>
+        <v>7.86569976806641</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G75" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.25006008148193</v>
       </c>
       <c r="G79" t="n">
-        <v>8.20178413391113</v>
+        <v>8.20178318023682</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.39816093444824</v>
       </c>
       <c r="G80" t="n">
-        <v>8.33310127258301</v>
+        <v>8.33310031890869</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912178039551</v>
+        <v>8.62912082672119</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G86" t="n">
-        <v>8.54009342193604</v>
+        <v>8.54009246826172</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G88" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G89" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.36803913116455</v>
       </c>
       <c r="G90" t="n">
-        <v>8.30639266967773</v>
+        <v>8.30639171600342</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542007446289</v>
+        <v>8.39542102813721</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G97" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588800430298</v>
+        <v>7.98588848114014</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>8.92875480651855</v>
       </c>
       <c r="G100" t="n">
-        <v>7.91689109802246</v>
+        <v>7.91689014434814</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.04924392700195</v>
       </c>
       <c r="G108" t="n">
-        <v>8.02372550964355</v>
+        <v>8.02372455596924</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889633178711</v>
+        <v>7.77889585494995</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G112" t="n">
-        <v>8.85837173461914</v>
+        <v>8.85837078094482</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.28018188476562</v>
       </c>
       <c r="G114" t="n">
-        <v>8.22849178314209</v>
+        <v>8.22849273681641</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660659790039</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808242797852</v>
+        <v>7.96808338165283</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G118" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.80230236053467</v>
       </c>
       <c r="G120" t="n">
-        <v>8.69144153594971</v>
+        <v>8.69144248962402</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G123" t="n">
-        <v>9.00749492645264</v>
+        <v>9.007493019104</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.05933666229248</v>
+        <v>8.05933570861816</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78557348251343</v>
+        <v>7.78557395935059</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.86349010467529</v>
       </c>
       <c r="G127" t="n">
-        <v>7.85902214050293</v>
+        <v>7.85902261734009</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.60650730133057</v>
       </c>
       <c r="G130" t="n">
-        <v>8.51783561706543</v>
+        <v>8.51783657073975</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G131" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G132" t="n">
-        <v>7.82341051101685</v>
+        <v>7.82341146469116</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.44083404541016</v>
       </c>
       <c r="G134" t="n">
-        <v>8.37093734741211</v>
+        <v>8.37093830108643</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.7114725112915</v>
+        <v>8.71147441864014</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G137" t="n">
-        <v>9.25454998016357</v>
+        <v>9.25454902648926</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>10.3771362304688</v>
       </c>
       <c r="G139" t="n">
-        <v>9.20113277435303</v>
+        <v>9.20113182067871</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>10.5679111480713</v>
       </c>
       <c r="G140" t="n">
-        <v>9.37028694152832</v>
+        <v>9.37028789520264</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G141" t="n">
-        <v>9.55947303771973</v>
+        <v>9.55947208404541</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>10.8590927124023</v>
       </c>
       <c r="G143" t="n">
-        <v>9.6284704208374</v>
+        <v>9.62846946716309</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G144" t="n">
-        <v>9.68856620788574</v>
+        <v>9.68856525421143</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>10.6934204101562</v>
       </c>
       <c r="G146" t="n">
-        <v>9.4815731048584</v>
+        <v>9.48157215118408</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427219390869</v>
+        <v>9.78427124023438</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G149" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G151" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>9.3881196975708</v>
       </c>
       <c r="G152" t="n">
-        <v>8.32419681549072</v>
+        <v>8.32419776916504</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.37807941436768</v>
       </c>
       <c r="G153" t="n">
-        <v>8.31529521942139</v>
+        <v>8.31529426574707</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.52228832244873</v>
+        <v>8.5222864151001</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10.0056276321411</v>
       </c>
       <c r="G156" t="n">
-        <v>8.87172508239746</v>
+        <v>8.87172603607178</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G157" t="n">
-        <v>8.7760181427002</v>
+        <v>8.77601909637451</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.03642845153809</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.98303604125977</v>
       </c>
       <c r="G164" t="n">
-        <v>8.85169315338135</v>
+        <v>8.85169410705566</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G177" t="n">
-        <v>9.23451900482178</v>
+        <v>9.23451805114746</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G178" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G182" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.07936668395996</v>
       </c>
       <c r="G184" t="n">
-        <v>8.05043315887451</v>
+        <v>8.05043411254883</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.7922511100769</v>
+        <v>7.79225063323975</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.90365314483643</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89463329315186</v>
+        <v>7.89463376998901</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.28771305084229</v>
       </c>
       <c r="G188" t="n">
-        <v>8.23516941070557</v>
+        <v>8.23516845703125</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.91871356964111</v>
       </c>
       <c r="G189" t="n">
-        <v>7.90798711776733</v>
+        <v>7.90798759460449</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.73883295059204</v>
+        <v>7.7388334274292</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.19985580444336</v>
       </c>
       <c r="G192" t="n">
-        <v>8.15726947784424</v>
+        <v>8.15726852416992</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G193" t="n">
-        <v>8.38429260253906</v>
+        <v>8.38429164886475</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G199" t="n">
-        <v>8.94294929504395</v>
+        <v>8.94294834136963</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10.3696060180664</v>
       </c>
       <c r="G204" t="n">
-        <v>9.19445514678955</v>
+        <v>9.19445610046387</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.8139095306396</v>
       </c>
       <c r="G206" t="n">
-        <v>9.58840847015381</v>
+        <v>9.58840751647949</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G207" t="n">
-        <v>9.68856620788574</v>
+        <v>9.68856525421143</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G210" t="n">
-        <v>9.31464385986328</v>
+        <v>9.31464290618896</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.03642845153809</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.34645557403564</v>
+        <v>8.34645462036133</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G219" t="n">
-        <v>8.38429260253906</v>
+        <v>8.38429164886475</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G220" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G221" t="n">
-        <v>8.73373126983643</v>
+        <v>8.73373031616211</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.0834436416626</v>
       </c>
       <c r="G226" t="n">
-        <v>8.94072246551514</v>
+        <v>8.94072341918945</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.1185855865479</v>
       </c>
       <c r="G229" t="n">
-        <v>8.97188091278076</v>
+        <v>8.97188186645508</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G233" t="n">
-        <v>8.92514228820801</v>
+        <v>8.92514324188232</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G234" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.6507472991943</v>
       </c>
       <c r="G238" t="n">
-        <v>9.4437370300293</v>
+        <v>9.44373607635498</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>11.6347427368164</v>
       </c>
       <c r="G241" t="n">
-        <v>10.316219329834</v>
+        <v>10.3162183761597</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.4088249206543</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1159029006958</v>
+        <v>10.1159038543701</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.8230066299438</v>
       </c>
       <c r="G245" t="n">
-        <v>10.4831466674805</v>
+        <v>10.4831476211548</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G246" t="n">
-        <v>10.5721759796143</v>
+        <v>10.5721769332886</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>12.2748422622681</v>
       </c>
       <c r="G248" t="n">
-        <v>10.8837776184082</v>
+        <v>10.8837785720825</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G251" t="n">
-        <v>10.9883861541748</v>
+        <v>10.9883871078491</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.0319766998291</v>
       </c>
       <c r="G258" t="n">
-        <v>12.4417819976807</v>
+        <v>12.441782951355</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>14.3206491470337</v>
       </c>
       <c r="G259" t="n">
-        <v>12.6977405548096</v>
+        <v>12.6977415084839</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>13.9817733764648</v>
       </c>
       <c r="G260" t="n">
-        <v>12.3972682952881</v>
+        <v>12.3972692489624</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195261001587</v>
+        <v>12.4195251464844</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858243942261</v>
+        <v>12.1858253479004</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.3165721893311</v>
       </c>
       <c r="G263" t="n">
-        <v>11.8074531555176</v>
+        <v>11.8074522018433</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>12.7517786026001</v>
       </c>
       <c r="G264" t="n">
-        <v>11.3066654205322</v>
+        <v>11.3066644668579</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>13.1032047271729</v>
       </c>
       <c r="G265" t="n">
-        <v>11.6182651519775</v>
+        <v>11.6182661056519</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>12.7392282485962</v>
       </c>
       <c r="G266" t="n">
-        <v>11.2955360412598</v>
+        <v>11.2955369949341</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>12.8647365570068</v>
       </c>
       <c r="G267" t="n">
-        <v>11.4068222045898</v>
+        <v>11.4068212509155</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>12.2999439239502</v>
       </c>
       <c r="G268" t="n">
-        <v>10.9060354232788</v>
+        <v>10.9060344696045</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.5635137557983</v>
       </c>
       <c r="G269" t="n">
-        <v>11.1397352218628</v>
+        <v>11.1397342681885</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>12.6011667251587</v>
       </c>
       <c r="G272" t="n">
-        <v>11.1731214523315</v>
+        <v>11.1731204986572</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>13.1283073425293</v>
       </c>
       <c r="G276" t="n">
-        <v>11.6405229568481</v>
+        <v>11.6405220031738</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960083007812</v>
+        <v>11.5960092544556</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>12.1995363235474</v>
       </c>
       <c r="G278" t="n">
-        <v>10.8170070648193</v>
+        <v>10.817006111145</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G281" t="n">
-        <v>10.2383184432983</v>
+        <v>10.2383193969727</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141492843628</v>
+        <v>10.4141502380371</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.251672744751</v>
+        <v>10.2516717910767</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>11.3711729049683</v>
       </c>
       <c r="G285" t="n">
-        <v>10.0825176239014</v>
+        <v>10.0825185775757</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.39857006073</v>
+        <v>10.3985710144043</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.707537651062</v>
       </c>
       <c r="G287" t="n">
-        <v>10.3807649612427</v>
+        <v>10.3807640075684</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651857376099</v>
+        <v>10.3651847839355</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>11.3787031173706</v>
       </c>
       <c r="G290" t="n">
-        <v>10.0891962051392</v>
+        <v>10.0891952514648</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939605712891</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.6874570846558</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3629579544067</v>
+        <v>10.3629589080811</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>11.3310089111328</v>
       </c>
       <c r="G296" t="n">
-        <v>10.0469055175781</v>
+        <v>10.0469064712524</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G297" t="n">
-        <v>9.36361026763916</v>
+        <v>9.36360931396484</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.5428085327148</v>
       </c>
       <c r="G303" t="n">
-        <v>9.34803009033203</v>
+        <v>9.34802913665771</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10.4675025939941</v>
       </c>
       <c r="G304" t="n">
-        <v>9.28125762939453</v>
+        <v>9.28125858306885</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G305" t="n">
-        <v>9.25454998016357</v>
+        <v>9.25454902648926</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G306" t="n">
-        <v>9.00749492645264</v>
+        <v>9.007493019104</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10.1386680603027</v>
       </c>
       <c r="G307" t="n">
-        <v>8.9896879196167</v>
+        <v>8.98968887329102</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.2491159439087</v>
       </c>
       <c r="G308" t="n">
-        <v>9.08762073516846</v>
+        <v>9.08761978149414</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10.218994140625</v>
       </c>
       <c r="G310" t="n">
-        <v>9.06091213226318</v>
+        <v>9.06091117858887</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G313" t="n">
-        <v>9.01639652252197</v>
+        <v>9.01639747619629</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539390563965</v>
+        <v>9.08539485931396</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10.1562385559082</v>
       </c>
       <c r="G317" t="n">
-        <v>9.00526714324951</v>
+        <v>9.00526809692383</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G324" t="n">
-        <v>9.49047565460205</v>
+        <v>9.49047470092773</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G325" t="n">
-        <v>9.51050758361816</v>
+        <v>9.51050853729248</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>10.0106477737427</v>
       </c>
       <c r="G332" t="n">
-        <v>8.87617588043213</v>
+        <v>8.87617683410645</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10.0784225463867</v>
       </c>
       <c r="G333" t="n">
-        <v>8.93626976013184</v>
+        <v>8.93627071380615</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.7671594619751</v>
       </c>
       <c r="G335" t="n">
-        <v>8.66028118133545</v>
+        <v>8.66028213500977</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.20335865020752</v>
+        <v>9.2033576965332</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>10.0859537124634</v>
       </c>
       <c r="G339" t="n">
-        <v>8.94294929504395</v>
+        <v>8.94294834136963</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G342" t="n">
-        <v>8.85837173461914</v>
+        <v>8.85837078094482</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G344" t="n">
-        <v>8.87840270996094</v>
+        <v>8.87840175628662</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G347" t="n">
-        <v>8.87840270996094</v>
+        <v>8.87840175628662</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G353" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.80481243133545</v>
       </c>
       <c r="G354" t="n">
-        <v>8.6936674118042</v>
+        <v>8.69366836547852</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G355" t="n">
-        <v>8.86282348632812</v>
+        <v>8.86282253265381</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G357" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G362" t="n">
-        <v>8.03485298156738</v>
+        <v>8.0348539352417</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.99033975601196</v>
+        <v>7.99033880233765</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>8.97142791748047</v>
       </c>
       <c r="G364" t="n">
-        <v>7.95472812652588</v>
+        <v>7.95472764968872</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G365" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G366" t="n">
-        <v>7.66093301773071</v>
+        <v>7.66093349456787</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215627670288</v>
+        <v>7.73215675354004</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G368" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209337234497</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>8.88106060028076</v>
       </c>
       <c r="G372" t="n">
-        <v>7.87460136413574</v>
+        <v>7.8746018409729</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>8.27861499786377</v>
       </c>
       <c r="G375" t="n">
-        <v>7.34042882919312</v>
+        <v>7.34042930603027</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G376" t="n">
-        <v>7.1979832649231</v>
+        <v>7.19798278808594</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.13302421569824</v>
       </c>
       <c r="G377" t="n">
-        <v>7.21133756637573</v>
+        <v>7.21133708953857</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G378" t="n">
-        <v>7.18017721176147</v>
+        <v>7.18017673492432</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>8.07779979705811</v>
       </c>
       <c r="G380" t="n">
-        <v>7.16237163543701</v>
+        <v>7.16237115859985</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914218902588</v>
+        <v>7.22914266586304</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G384" t="n">
-        <v>7.1979832649231</v>
+        <v>7.19798278808594</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055511474609</v>
+        <v>7.42055463790894</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.68024635314941</v>
       </c>
       <c r="G386" t="n">
-        <v>7.69654512405396</v>
+        <v>7.69654560089111</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.44428825378418</v>
       </c>
       <c r="G387" t="n">
-        <v>7.48732709884644</v>
+        <v>7.48732662200928</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390893936157</v>
+        <v>7.43390941619873</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G393" t="n">
-        <v>7.74551010131836</v>
+        <v>7.7455096244812</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.8567967414856</v>
+        <v>7.85679626464844</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>8.52461433410645</v>
       </c>
       <c r="G397" t="n">
-        <v>7.5585503578186</v>
+        <v>7.55854940414429</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.514573097229</v>
       </c>
       <c r="G398" t="n">
-        <v>7.54964685440063</v>
+        <v>7.54964637756348</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G400" t="n">
-        <v>7.61196708679199</v>
+        <v>7.61196660995483</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>8.6953067779541</v>
       </c>
       <c r="G404" t="n">
-        <v>7.70989894866943</v>
+        <v>7.70989847183228</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G405" t="n">
-        <v>7.70099496841431</v>
+        <v>7.70099592208862</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G406" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209337234497</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.5748176574707</v>
       </c>
       <c r="G411" t="n">
-        <v>7.60306358337402</v>
+        <v>7.60306406021118</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>8.53967475891113</v>
       </c>
       <c r="G412" t="n">
-        <v>7.57190370559692</v>
+        <v>7.57190418243408</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G413" t="n">
-        <v>7.50513172149658</v>
+        <v>7.5051326751709</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249792098999</v>
+        <v>7.24249744415283</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G416" t="n">
-        <v>7.26475429534912</v>
+        <v>7.26475477218628</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.15812587738037</v>
       </c>
       <c r="G417" t="n">
-        <v>7.23359489440918</v>
+        <v>7.23359394073486</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G418" t="n">
-        <v>7.30036592483521</v>
+        <v>7.30036640167236</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7.93220806121826</v>
       </c>
       <c r="G420" t="n">
-        <v>7.03327941894531</v>
+        <v>7.03327894210815</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.61592388153076</v>
       </c>
       <c r="G422" t="n">
-        <v>6.75283813476562</v>
+        <v>6.75283861160278</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>7.68621015548706</v>
       </c>
       <c r="G424" t="n">
-        <v>6.8151593208313</v>
+        <v>6.81515884399414</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.40004777908325</v>
       </c>
       <c r="G426" t="n">
-        <v>6.56142616271973</v>
+        <v>6.56142663955688</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.93979835510254</v>
+        <v>6.93979930877686</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.00751399993896</v>
       </c>
       <c r="G430" t="n">
-        <v>7.10005044937134</v>
+        <v>7.1000509262085</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G431" t="n">
-        <v>7.30036592483521</v>
+        <v>7.30036640167236</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591417312622</v>
+        <v>7.29591464996338</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409908294678</v>
+        <v>7.55409860610962</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.42922687530518</v>
       </c>
       <c r="G438" t="n">
-        <v>7.47397232055664</v>
+        <v>7.47397184371948</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.66538429260254</v>
+        <v>7.66538381576538</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G442" t="n">
-        <v>7.70099496841431</v>
+        <v>7.70099592208862</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.10697937011719</v>
       </c>
       <c r="G444" t="n">
-        <v>8.07491779327393</v>
+        <v>8.07491683959961</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G449" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692350387573</v>
+        <v>7.93692255020142</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.15216159820557</v>
       </c>
       <c r="G455" t="n">
-        <v>8.1149787902832</v>
+        <v>8.11497974395752</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.82081699371338</v>
       </c>
       <c r="G456" t="n">
-        <v>7.82118463516235</v>
+        <v>7.82118511199951</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G457" t="n">
-        <v>7.77221775054932</v>
+        <v>7.77221822738647</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.85093879699707</v>
       </c>
       <c r="G458" t="n">
-        <v>7.84789371490479</v>
+        <v>7.84789323806763</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.92122364044189</v>
       </c>
       <c r="G459" t="n">
-        <v>7.91021251678467</v>
+        <v>7.91021299362183</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.77563285827637</v>
       </c>
       <c r="G460" t="n">
-        <v>7.78112125396729</v>
+        <v>7.78112173080444</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.42945766448975</v>
+        <v>7.4294581413269</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>9.04673385620117</v>
       </c>
       <c r="G465" t="n">
-        <v>8.02150058746338</v>
+        <v>8.02149963378906</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.66538429260254</v>
+        <v>7.66538381576538</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G468" t="n">
-        <v>7.64312648773193</v>
+        <v>7.64312744140625</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479150772095</v>
+        <v>7.99479198455811</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G470" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>9.53371143341064</v>
       </c>
       <c r="G471" t="n">
-        <v>8.45328998565674</v>
+        <v>8.45328903198242</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.49354839324951</v>
       </c>
       <c r="G478" t="n">
-        <v>8.41767883300781</v>
+        <v>8.4176778793335</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G480" t="n">
-        <v>7.78557348251343</v>
+        <v>7.78557395935059</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G482" t="n">
-        <v>7.62532186508179</v>
+        <v>7.62532234191895</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G483" t="n">
-        <v>7.62532186508179</v>
+        <v>7.62532234191895</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G484" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209337234497</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>8.60494041442871</v>
       </c>
       <c r="G488" t="n">
-        <v>7.62977313995361</v>
+        <v>7.62977266311646</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G491" t="n">
-        <v>7.74551010131836</v>
+        <v>7.7455096244812</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G492" t="n">
-        <v>7.50513172149658</v>
+        <v>7.5051326751709</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G493" t="n">
-        <v>7.64312648773193</v>
+        <v>7.64312744140625</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>8.44930839538574</v>
       </c>
       <c r="G497" t="n">
-        <v>7.49177837371826</v>
+        <v>7.4917778968811</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>8.60996055603027</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63422441482544</v>
+        <v>7.63422393798828</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.76559162139893</v>
       </c>
       <c r="G500" t="n">
-        <v>7.77221775054932</v>
+        <v>7.77221822738647</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.74996185302734</v>
+        <v>7.74996280670166</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.05677509307861</v>
       </c>
       <c r="G505" t="n">
-        <v>8.03040218353271</v>
+        <v>8.03040313720703</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>9.11199855804443</v>
       </c>
       <c r="G506" t="n">
-        <v>8.07936763763428</v>
+        <v>8.07936859130859</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G507" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.61403846740723</v>
       </c>
       <c r="G510" t="n">
-        <v>8.52451419830322</v>
+        <v>8.52451324462891</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.5067081451416</v>
+        <v>8.50670623779297</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G514" t="n">
-        <v>8.73373126983643</v>
+        <v>8.73373031616211</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G517" t="n">
-        <v>8.76043891906738</v>
+        <v>8.7604398727417</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>10.1763210296631</v>
       </c>
       <c r="G520" t="n">
-        <v>9.02307510375977</v>
+        <v>9.02307415008545</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.03642845153809</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>10.1813411712646</v>
       </c>
       <c r="G524" t="n">
-        <v>9.02752685546875</v>
+        <v>9.02752590179443</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G527" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G528" t="n">
-        <v>9.16552066802979</v>
+        <v>9.16551971435547</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.60399723052979</v>
       </c>
       <c r="G532" t="n">
-        <v>8.51560974121094</v>
+        <v>8.51561069488525</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G537" t="n">
-        <v>7.82341051101685</v>
+        <v>7.82341146469116</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G538" t="n">
-        <v>8.03485298156738</v>
+        <v>8.0348539352417</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660659790039</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G540" t="n">
-        <v>7.61196708679199</v>
+        <v>7.61196660995483</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519557952881</v>
+        <v>7.54519510269165</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>8.4543285369873</v>
       </c>
       <c r="G543" t="n">
-        <v>7.49622964859009</v>
+        <v>7.49622917175293</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G545" t="n">
-        <v>7.66093301773071</v>
+        <v>7.66093349456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G548" t="n">
-        <v>7.60083818435669</v>
+        <v>7.60083866119385</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G553" t="n">
-        <v>7.50068092346191</v>
+        <v>7.50068044662476</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.52293825149536</v>
+        <v>7.5229377746582</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G556" t="n">
-        <v>7.30036592483521</v>
+        <v>7.30036640167236</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G557" t="n">
-        <v>7.50068092346191</v>
+        <v>7.50068044662476</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.56979656219482</v>
       </c>
       <c r="G558" t="n">
-        <v>7.5986123085022</v>
+        <v>7.59861183166504</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G560" t="n">
-        <v>7.75218772888184</v>
+        <v>7.75218820571899</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>8.32379913330078</v>
       </c>
       <c r="G563" t="n">
-        <v>7.38049268722534</v>
+        <v>7.38049221038818</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613481521606</v>
+        <v>7.43613386154175</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585126876831</v>
+        <v>7.25585174560547</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>8.43173694610596</v>
       </c>
       <c r="G568" t="n">
-        <v>7.47619867324829</v>
+        <v>7.47619819641113</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>8.16063594818115</v>
       </c>
       <c r="G569" t="n">
-        <v>7.23582029342651</v>
+        <v>7.23581981658936</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>8.17820739746094</v>
       </c>
       <c r="G570" t="n">
-        <v>7.25140047073364</v>
+        <v>7.25139999389648</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>8.03512573242188</v>
       </c>
       <c r="G571" t="n">
-        <v>7.12453317642212</v>
+        <v>7.12453365325928</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G578" t="n">
-        <v>6.98876523971558</v>
+        <v>6.98876571655273</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744714736938</v>
+        <v>6.85744762420654</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G585" t="n">
-        <v>7.18017721176147</v>
+        <v>7.18017673492432</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G586" t="n">
-        <v>7.4806489944458</v>
+        <v>7.48064947128296</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610431671143</v>
+        <v>7.41610336303711</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G589" t="n">
-        <v>7.4806489944458</v>
+        <v>7.48064947128296</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G590" t="n">
-        <v>7.26475429534912</v>
+        <v>7.26475477218628</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G591" t="n">
-        <v>6.98876523971558</v>
+        <v>6.98876571655273</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443929672241</v>
+        <v>7.06443977355957</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>7.92969799041748</v>
       </c>
       <c r="G596" t="n">
-        <v>7.03105354309082</v>
+        <v>7.03105306625366</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G600" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G602" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.83242416381836</v>
       </c>
       <c r="G605" t="n">
-        <v>8.7181510925293</v>
+        <v>8.71815013885498</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G607" t="n">
-        <v>8.54009342193604</v>
+        <v>8.54009246826172</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37538909912109</v>
+        <v>8.37539005279541</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065380096436</v>
+        <v>8.19065475463867</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>8.79822540283203</v>
       </c>
       <c r="G613" t="n">
-        <v>7.80115365982056</v>
+        <v>7.80115413665771</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>9.42326259613037</v>
       </c>
       <c r="G619" t="n">
-        <v>8.35535717010498</v>
+        <v>8.3553581237793</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.31783485412598</v>
       </c>
       <c r="G620" t="n">
-        <v>8.26187801361084</v>
+        <v>8.26187705993652</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>9.85250568389893</v>
       </c>
       <c r="G623" t="n">
-        <v>8.7359561920166</v>
+        <v>8.73595523834229</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902599334717</v>
+        <v>8.56902694702148</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>9.47848701477051</v>
       </c>
       <c r="G625" t="n">
-        <v>8.40432357788086</v>
+        <v>8.40432453155518</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.33289623260498</v>
       </c>
       <c r="G627" t="n">
-        <v>8.27523136138916</v>
+        <v>8.27523231506348</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G629" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G638" t="n">
-        <v>8.70257091522217</v>
+        <v>8.70256996154785</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.86254692077637</v>
       </c>
       <c r="G639" t="n">
-        <v>8.74485874176025</v>
+        <v>8.74485969543457</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G640" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.7114725112915</v>
+        <v>8.71147441864014</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G644" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009727478027</v>
+        <v>9.25009822845459</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G650" t="n">
-        <v>9.01639652252197</v>
+        <v>9.01639747619629</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G654" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G657" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>11.401294708252</v>
       </c>
       <c r="G658" t="n">
-        <v>10.109227180481</v>
+        <v>10.1092262268066</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G660" t="n">
-        <v>9.84659194946289</v>
+        <v>9.84659099578857</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G662" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G664" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G667" t="n">
-        <v>9.87107372283936</v>
+        <v>9.87107467651367</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>11.6322326660156</v>
       </c>
       <c r="G669" t="n">
-        <v>10.3139925003052</v>
+        <v>10.3139934539795</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>11.4414577484131</v>
       </c>
       <c r="G670" t="n">
-        <v>10.1448383331299</v>
+        <v>10.1448373794556</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>11.6648645401001</v>
       </c>
       <c r="G674" t="n">
-        <v>10.3429260253906</v>
+        <v>10.3429269790649</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>11.6046199798584</v>
       </c>
       <c r="G676" t="n">
-        <v>10.2895097732544</v>
+        <v>10.2895088195801</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939605712891</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>11.3711729049683</v>
       </c>
       <c r="G679" t="n">
-        <v>10.0825176239014</v>
+        <v>10.0825185775757</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99348926544189</v>
+        <v>9.99349021911621</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694797515869</v>
+        <v>10.2694787979126</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G691" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>12.0238227844238</v>
       </c>
       <c r="G696" t="n">
-        <v>10.6612062454224</v>
+        <v>10.661205291748</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>13.2086343765259</v>
       </c>
       <c r="G699" t="n">
-        <v>11.7117471694946</v>
+        <v>11.7117462158203</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>13.233736038208</v>
       </c>
       <c r="G700" t="n">
-        <v>11.7340030670166</v>
+        <v>11.7340040206909</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>13.7558555603027</v>
       </c>
       <c r="G704" t="n">
-        <v>12.1969528198242</v>
+        <v>12.1969537734985</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>13.032919883728</v>
       </c>
       <c r="G706" t="n">
-        <v>11.555944442749</v>
+        <v>11.5559453964233</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>12.7618188858032</v>
       </c>
       <c r="G709" t="n">
-        <v>11.3155660629272</v>
+        <v>11.3155670166016</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395765304565</v>
+        <v>11.0395774841309</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>12.7065954208374</v>
       </c>
       <c r="G712" t="n">
-        <v>11.2666015625</v>
+        <v>11.2666025161743</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>12.7015752792358</v>
       </c>
       <c r="G713" t="n">
-        <v>11.2621507644653</v>
+        <v>11.262149810791</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>12.3325757980347</v>
       </c>
       <c r="G714" t="n">
-        <v>10.9349679946899</v>
+        <v>10.9349689483643</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G720" t="n">
-        <v>10.5721759796143</v>
+        <v>10.5721769332886</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>11.923415184021</v>
       </c>
       <c r="G722" t="n">
-        <v>10.5721759796143</v>
+        <v>10.5721769332886</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G724" t="n">
-        <v>10.7613620758057</v>
+        <v>10.76136302948</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>11.7225999832153</v>
       </c>
       <c r="G725" t="n">
-        <v>10.394118309021</v>
+        <v>10.3941192626953</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>11.6171712875366</v>
       </c>
       <c r="G729" t="n">
-        <v>10.3006391525269</v>
+        <v>10.3006381988525</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>11.1251735687256</v>
       </c>
       <c r="G731" t="n">
-        <v>9.86439800262451</v>
+        <v>9.8643970489502</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>10.6607875823975</v>
       </c>
       <c r="G734" t="n">
-        <v>9.45263767242432</v>
+        <v>9.45263862609863</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>10.5402994155884</v>
       </c>
       <c r="G735" t="n">
-        <v>9.34580421447754</v>
+        <v>9.34580516815186</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G736" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G738" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081058502197</v>
+        <v>8.29081153869629</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889633178711</v>
+        <v>7.77889585494995</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>9.65169143676758</v>
       </c>
       <c r="G742" t="n">
-        <v>8.55790042877197</v>
+        <v>8.55789947509766</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>9.69938373565674</v>
       </c>
       <c r="G746" t="n">
-        <v>8.60018634796143</v>
+        <v>8.60018730163574</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>10.0307302474976</v>
       </c>
       <c r="G748" t="n">
-        <v>8.89398384094238</v>
+        <v>8.89398288726807</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G749" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>9.75209808349609</v>
       </c>
       <c r="G751" t="n">
-        <v>8.64692783355713</v>
+        <v>8.64692687988281</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G752" t="n">
-        <v>8.25519943237305</v>
+        <v>8.25520038604736</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466569900513</v>
+        <v>7.91466522216797</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>8.81077575683594</v>
       </c>
       <c r="G756" t="n">
-        <v>7.8122820854187</v>
+        <v>7.81228160858154</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G757" t="n">
-        <v>7.30036592483521</v>
+        <v>7.30036640167236</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>8.12800407409668</v>
       </c>
       <c r="G761" t="n">
-        <v>7.20688629150391</v>
+        <v>7.20688581466675</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G764" t="n">
-        <v>7.30036592483521</v>
+        <v>7.30036640167236</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>8.37400245666504</v>
       </c>
       <c r="G765" t="n">
-        <v>7.42500638961792</v>
+        <v>7.42500686645508</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G772" t="n">
-        <v>8.25519943237305</v>
+        <v>8.25520038604736</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.4634256362915</v>
       </c>
       <c r="G773" t="n">
-        <v>8.39096832275391</v>
+        <v>8.39096927642822</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G782" t="n">
-        <v>8.86282348632812</v>
+        <v>8.86282253265381</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>10.1763210296631</v>
       </c>
       <c r="G784" t="n">
-        <v>9.02307510375977</v>
+        <v>9.02307415008545</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>10.2817487716675</v>
       </c>
       <c r="G786" t="n">
-        <v>9.11655426025391</v>
+        <v>9.11655521392822</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>10.4298496246338</v>
       </c>
       <c r="G789" t="n">
-        <v>9.24787139892578</v>
+        <v>9.2478723526001</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>10.6557683944702</v>
       </c>
       <c r="G800" t="n">
-        <v>9.44818878173828</v>
+        <v>9.44818782806396</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>10.6833801269531</v>
       </c>
       <c r="G801" t="n">
-        <v>9.47266960144043</v>
+        <v>9.47267055511475</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>10.8440322875977</v>
       </c>
       <c r="G803" t="n">
-        <v>9.61511611938477</v>
+        <v>9.61511707305908</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G804" t="n">
-        <v>9.69746685028076</v>
+        <v>9.69746780395508</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496055603027</v>
+        <v>10.3496046066284</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.2572708129883</v>
       </c>
       <c r="G814" t="n">
-        <v>10.8681983947754</v>
+        <v>10.8681974411011</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>12.3150053024292</v>
       </c>
       <c r="G815" t="n">
-        <v>10.9193887710571</v>
+        <v>10.9193897247314</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>12.1091690063477</v>
       </c>
       <c r="G816" t="n">
-        <v>10.7368803024292</v>
+        <v>10.7368793487549</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>12.2145967483521</v>
       </c>
       <c r="G817" t="n">
-        <v>10.8303594589233</v>
+        <v>10.8303604125977</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.3350868225098</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9371948242188</v>
+        <v>10.9371957778931</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G819" t="n">
-        <v>10.9883861541748</v>
+        <v>10.9883871078491</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>11.8355579376221</v>
       </c>
       <c r="G826" t="n">
-        <v>10.4942760467529</v>
+        <v>10.4942770004272</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>12.1116790771484</v>
       </c>
       <c r="G827" t="n">
-        <v>10.7391052246094</v>
+        <v>10.7391061782837</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147792816162</v>
+        <v>10.8147811889648</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G830" t="n">
-        <v>10.7613620758057</v>
+        <v>10.76136302948</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>12.4856977462769</v>
       </c>
       <c r="G831" t="n">
-        <v>11.0707378387451</v>
+        <v>11.0707368850708</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>11.7150688171387</v>
       </c>
       <c r="G840" t="n">
-        <v>10.3874416351318</v>
+        <v>10.3874425888062</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>11.8154773712158</v>
       </c>
       <c r="G843" t="n">
-        <v>10.4764709472656</v>
+        <v>10.4764719009399</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>11.3912544250488</v>
       </c>
       <c r="G844" t="n">
-        <v>10.100323677063</v>
+        <v>10.1003246307373</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G845" t="n">
-        <v>10.2383184432983</v>
+        <v>10.2383193969727</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>11.3385400772095</v>
       </c>
       <c r="G846" t="n">
-        <v>10.0535831451416</v>
+        <v>10.0535840988159</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>10.836501121521</v>
       </c>
       <c r="G849" t="n">
-        <v>9.60843944549561</v>
+        <v>9.60843849182129</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G851" t="n">
-        <v>9.33912754058838</v>
+        <v>9.33912658691406</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G858" t="n">
-        <v>9.2701301574707</v>
+        <v>9.27012920379639</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>10.5101757049561</v>
       </c>
       <c r="G860" t="n">
-        <v>9.31909465789795</v>
+        <v>9.31909561157227</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G861" t="n">
-        <v>9.25232410430908</v>
+        <v>9.25232315063477</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>9.89768886566162</v>
       </c>
       <c r="G863" t="n">
-        <v>8.7760181427002</v>
+        <v>8.77601909637451</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G867" t="n">
-        <v>8.76043891906738</v>
+        <v>8.7604398727417</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>9.62156772613525</v>
       </c>
       <c r="G868" t="n">
-        <v>8.53118896484375</v>
+        <v>8.53118991851807</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>10.582971572876</v>
       </c>
       <c r="G873" t="n">
-        <v>9.38364124298096</v>
+        <v>9.38364028930664</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G876" t="n">
-        <v>9.23451900482178</v>
+        <v>9.23451805114746</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G877" t="n">
-        <v>9.33912754058838</v>
+        <v>9.33912658691406</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G878" t="n">
-        <v>9.2701301574707</v>
+        <v>9.27012920379639</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G880" t="n">
-        <v>9.55947303771973</v>
+        <v>9.55947208404541</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G881" t="n">
-        <v>9.60621356964111</v>
+        <v>9.60621452331543</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>11.0699491500854</v>
       </c>
       <c r="G883" t="n">
-        <v>9.81543159484863</v>
+        <v>9.81543064117432</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G885" t="n">
-        <v>9.49047565460205</v>
+        <v>9.49047470092773</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.0498676300049</v>
       </c>
       <c r="G887" t="n">
-        <v>9.7976245880127</v>
+        <v>9.79762554168701</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>10.9820928573608</v>
       </c>
       <c r="G888" t="n">
-        <v>9.73753070831299</v>
+        <v>9.7375316619873</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.2431526184082</v>
       </c>
       <c r="G889" t="n">
-        <v>9.96900653839111</v>
+        <v>9.9690055847168</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G890" t="n">
-        <v>9.69746685028076</v>
+        <v>9.69746780395508</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>11.2130298614502</v>
       </c>
       <c r="G894" t="n">
-        <v>9.94229602813721</v>
+        <v>9.94229793548584</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.2205610275269</v>
       </c>
       <c r="G896" t="n">
-        <v>9.94897556304932</v>
+        <v>9.948974609375</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>11.2381324768066</v>
       </c>
       <c r="G899" t="n">
-        <v>9.96455574035645</v>
+        <v>9.96455383300781</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>11.4715795516968</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1715469360352</v>
+        <v>10.1715459823608</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>11.1603164672852</v>
       </c>
       <c r="G901" t="n">
-        <v>9.89555835723877</v>
+        <v>9.89555740356445</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304798126221</v>
+        <v>9.71304893493652</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G910" t="n">
-        <v>9.75088596343994</v>
+        <v>9.75088500976562</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>10.7411136627197</v>
       </c>
       <c r="G913" t="n">
-        <v>9.5238618850708</v>
+        <v>9.52386093139648</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G916" t="n">
-        <v>8.92514228820801</v>
+        <v>8.92514324188232</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>10.3721160888672</v>
       </c>
       <c r="G917" t="n">
-        <v>9.19668006896973</v>
+        <v>9.19668102264404</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G920" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>9.84497547149658</v>
       </c>
       <c r="G921" t="n">
-        <v>8.72927856445312</v>
+        <v>8.72927951812744</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.95185089111328</v>
+        <v>8.9518518447876</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G926" t="n">
-        <v>9.31464385986328</v>
+        <v>9.31464290618896</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>10.7586851119995</v>
       </c>
       <c r="G930" t="n">
-        <v>9.53944206237793</v>
+        <v>9.53944110870361</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>11.3962736129761</v>
       </c>
       <c r="G940" t="n">
-        <v>10.104775428772</v>
+        <v>10.1047744750977</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403875350952</v>
+        <v>10.1403856277466</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230527877808</v>
+        <v>10.4230537414551</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>11.2155408859253</v>
       </c>
       <c r="G944" t="n">
-        <v>9.94452381134033</v>
+        <v>9.94452285766602</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G946" t="n">
-        <v>9.87107372283936</v>
+        <v>9.87107467651367</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G947" t="n">
-        <v>9.84659194946289</v>
+        <v>9.84659099578857</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>10.7862977981567</v>
       </c>
       <c r="G949" t="n">
-        <v>9.56392478942871</v>
+        <v>9.56392574310303</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G950" t="n">
-        <v>9.36361026763916</v>
+        <v>9.36360931396484</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>10.4524421691895</v>
       </c>
       <c r="G951" t="n">
-        <v>9.26790428161621</v>
+        <v>9.26790332794189</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>10.4499320983887</v>
       </c>
       <c r="G952" t="n">
-        <v>9.26567840576172</v>
+        <v>9.26567935943604</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>10.0683822631836</v>
       </c>
       <c r="G955" t="n">
-        <v>8.92736911773682</v>
+        <v>8.9273681640625</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G958" t="n">
-        <v>9.16552066802979</v>
+        <v>9.16551971435547</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>10.5076656341553</v>
       </c>
       <c r="G965" t="n">
-        <v>9.31686878204346</v>
+        <v>9.31686973571777</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>10.6557683944702</v>
       </c>
       <c r="G971" t="n">
-        <v>9.44818878173828</v>
+        <v>9.44818782806396</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65963077545166</v>
+        <v>9.65963172912598</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G974" t="n">
-        <v>9.51050758361816</v>
+        <v>9.51050853729248</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G976" t="n">
-        <v>9.03642845153809</v>
+        <v>9.0364294052124</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G978" t="n">
-        <v>9.60621356964111</v>
+        <v>9.60621452331543</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>11.1904392242432</v>
       </c>
       <c r="G979" t="n">
-        <v>9.92226600646973</v>
+        <v>9.92226696014404</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>11.2306022644043</v>
       </c>
       <c r="G981" t="n">
-        <v>9.95787715911865</v>
+        <v>9.95787906646729</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>11.0573978424072</v>
       </c>
       <c r="G983" t="n">
-        <v>9.80430221557617</v>
+        <v>9.80430126190186</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>10.7536649703979</v>
       </c>
       <c r="G988" t="n">
-        <v>9.53499031066895</v>
+        <v>9.53498935699463</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>10.7536649703979</v>
       </c>
       <c r="G992" t="n">
-        <v>9.53499031066895</v>
+        <v>9.53498935699463</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>10.7135019302368</v>
       </c>
       <c r="G996" t="n">
-        <v>9.49937915802002</v>
+        <v>9.4993782043457</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G997" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.25232410430908</v>
+        <v>9.25232315063477</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>10.427339553833</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.24564552307129</v>
+        <v>9.24564647674561</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>10.5603799819946</v>
       </c>
       <c r="G1004" t="n">
-        <v>9.36361026763916</v>
+        <v>9.36360931396484</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>10.582971572876</v>
       </c>
       <c r="G1006" t="n">
-        <v>9.38364124298096</v>
+        <v>9.38364028930664</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467578887939</v>
+        <v>9.33467674255371</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.5616979598999</v>
+        <v>9.56169891357422</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G1014" t="n">
-        <v>9.75088596343994</v>
+        <v>9.75088500976562</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>10.934398651123</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.69524192810059</v>
+        <v>9.6952428817749</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>10.9971542358398</v>
       </c>
       <c r="G1016" t="n">
-        <v>9.75088596343994</v>
+        <v>9.75088500976562</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>11.0925407409668</v>
       </c>
       <c r="G1017" t="n">
-        <v>9.83546257019043</v>
+        <v>9.83546352386475</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>11.1728668212891</v>
       </c>
       <c r="G1019" t="n">
-        <v>9.90668487548828</v>
+        <v>9.9066858291626</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>11.120153427124</v>
       </c>
       <c r="G1023" t="n">
-        <v>9.85994625091553</v>
+        <v>9.85994529724121</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>11.044846534729</v>
       </c>
       <c r="G1024" t="n">
-        <v>9.79317283630371</v>
+        <v>9.79317378997803</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>11.1251735687256</v>
       </c>
       <c r="G1028" t="n">
-        <v>9.86439800262451</v>
+        <v>9.8643970489502</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>11.1126232147217</v>
       </c>
       <c r="G1029" t="n">
-        <v>9.85326862335205</v>
+        <v>9.85326957702637</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>10.4373807907104</v>
       </c>
       <c r="G1031" t="n">
-        <v>9.25454998016357</v>
+        <v>9.25454902648926</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.58460712432861</v>
+        <v>8.58460807800293</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>9.41322231292725</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.34645557403564</v>
+        <v>8.34645462036133</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>9.63411903381348</v>
       </c>
       <c r="G1046" t="n">
-        <v>8.54231929779053</v>
+        <v>8.54231834411621</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>9.51613998413086</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.43770980834961</v>
+        <v>8.43770885467529</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>9.55630302429199</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.47332191467285</v>
+        <v>8.47332096099854</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>9.41573238372803</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.34868144989014</v>
+        <v>8.34868049621582</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>8.70283794403076</v>
       </c>
       <c r="G1053" t="n">
-        <v>7.71657609939575</v>
+        <v>7.71657657623291</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754726409912</v>
+        <v>7.62754821777344</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.60083818435669</v>
+        <v>7.60083866119385</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>8.3037166595459</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.36268615722656</v>
+        <v>7.36268663406372</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585126876831</v>
+        <v>7.25585174560547</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.70832395553589</v>
+        <v>6.70832443237305</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.95000410079956</v>
+        <v>4.9500036239624</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.95000410079956</v>
+        <v>4.9500036239624</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>4.89613008499146</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.34126949310303</v>
+        <v>4.34126853942871</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>5.16848611831665</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.58275985717773</v>
+        <v>4.58275938034058</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>5.18605804443359</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.59834003448486</v>
+        <v>4.59834051132202</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>5.85627889633179</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.19260787963867</v>
+        <v>5.19260740280151</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>5.8261570930481</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.16589975357056</v>
+        <v>5.1658992767334</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.06713485717773</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.37956762313843</v>
+        <v>5.37956809997559</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>5.95919704437256</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.28386211395264</v>
+        <v>5.28386259078979</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>5.9014630317688</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.23267126083374</v>
+        <v>5.23267078399658</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.29276514053345</v>
+        <v>5.29276561737061</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>5.47473001480103</v>
       </c>
       <c r="G1089" t="n">
-        <v>4.85429859161377</v>
+        <v>4.85429811477661</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>5.28395509719849</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.685142993927</v>
+        <v>4.68514347076416</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.95445489883423</v>
+        <v>4.95445537567139</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>5.67303514480591</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.03013038635254</v>
+        <v>5.03012990951538</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928503036499</v>
+        <v>5.19928550720215</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>5.79101419448853</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.1347393989563</v>
+        <v>5.13473892211914</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470746994019</v>
+        <v>5.11470794677734</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248207092285</v>
+        <v>5.11248159408569</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.92329597473145</v>
+        <v>4.92329549789429</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>5.59521913528442</v>
       </c>
       <c r="G1108" t="n">
-        <v>4.96113252639771</v>
+        <v>4.96113300323486</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.79800033569336</v>
+        <v>4.79800081253052</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>5.46217918395996</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.86507511138916</v>
+        <v>4.865074634552</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>5.30905723571777</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.72869157791138</v>
+        <v>4.72869110107422</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>5.79854488372803</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.16467046737671</v>
+        <v>5.16466999053955</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>6.46876621246338</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.76162528991699</v>
+        <v>5.76162576675415</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>6.59176588058472</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.87117958068848</v>
+        <v>5.87117910385132</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>6.41354179382324</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.71243810653687</v>
+        <v>5.71243762969971</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>5.99182987213135</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.33682632446289</v>
+        <v>5.33682584762573</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>5.98680877685547</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.33235359191895</v>
+        <v>5.3323540687561</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.08418226242065</v>
+        <v>5.0841817855835</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>5.61530113220215</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.00145769119263</v>
+        <v>5.00145816802979</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.97686290740967</v>
+        <v>4.97686338424683</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>5.68558597564697</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.06405925750732</v>
+        <v>5.06405973434448</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>5.27642488479614</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.69962644577026</v>
+        <v>4.69962596893311</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>5.28897619247437</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.71080589294434</v>
+        <v>4.71080541610718</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>5.36679220199585</v>
       </c>
       <c r="G1152" t="n">
-        <v>4.78011512756348</v>
+        <v>4.78011465072632</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.47724008560181</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.87848901748657</v>
+        <v>4.87848949432373</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>4.92123222351074</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.38326168060303</v>
+        <v>4.38326215744019</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.57357120513916</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.07360601425171</v>
+        <v>4.07360553741455</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.96892595291138</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.42574167251587</v>
+        <v>4.42574214935303</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1174" t="n">
-        <v>4.34190034866333</v>
+        <v>4.34189987182617</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.66895818710327</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.15856599807739</v>
+        <v>4.15856552124023</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.50579500198364</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.01323890686035</v>
+        <v>4.01323843002319</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.39032697677612</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.91039323806763</v>
+        <v>3.91039347648621</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.29242897033691</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.82319688796997</v>
+        <v>3.82319736480713</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>4.19327592849731</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.73488306999207</v>
+        <v>3.73488283157349</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.07906293869019</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.63315558433533</v>
+        <v>3.63315534591675</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.22465419769287</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.76283121109009</v>
+        <v>3.76283097267151</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.56321811676025</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.17370057106018</v>
+        <v>3.17370080947876</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.86444091796875</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.44199514389038</v>
+        <v>3.4419949054718</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>3.79415607452393</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.37939357757568</v>
+        <v>3.3793933391571</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>3.65609502792358</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.25642490386963</v>
+        <v>3.25642466545105</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>3.59585094451904</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.20276618003845</v>
+        <v>3.20276641845703</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>3.62597298622131</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.22959542274475</v>
+        <v>3.22959566116333</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.68496203422546</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.28213596343994</v>
+        <v>3.28213620185852</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>3.78411507606506</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.370450258255</v>
+        <v>3.37045001983643</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.6940598487854</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.1809229850769</v>
+        <v>4.18092346191406</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>4.89487504959106</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.35978603363037</v>
+        <v>4.35978651046753</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.2770619392395</v>
+        <v>4.27706241607666</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.47157526016235</v>
+        <v>4.47157573699951</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>5.42201614379883</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.82930183410645</v>
+        <v>4.8293023109436</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>5.30654716491699</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.72645616531372</v>
+        <v>4.72645568847656</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>5.1333441734314</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.57218647003174</v>
+        <v>4.5721869468689</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.62584447860718</v>
+        <v>4.62584495544434</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>5.35675096511841</v>
       </c>
       <c r="G1254" t="n">
-        <v>4.77117156982422</v>
+        <v>4.77117109298706</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>5.37683200836182</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.78905725479126</v>
+        <v>4.78905773162842</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1259" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>5.46719884872437</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.86954545974731</v>
+        <v>4.86954593658447</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.86060237884521</v>
+        <v>4.86060285568237</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>5.82364702224731</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.18702793121338</v>
+        <v>5.18702840805054</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>6.17256307601929</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.49780225753784</v>
+        <v>5.49780178070068</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>6.10729789733887</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.4396710395813</v>
+        <v>5.43967151641846</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>6.08721685409546</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.42178535461426</v>
+        <v>5.42178583145142</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>6.00689077377319</v>
       </c>
       <c r="G1279" t="n">
-        <v>5.3502402305603</v>
+        <v>5.35024070739746</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.85878896713257</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.21832847595215</v>
+        <v>5.21832895278931</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>5.34169006347656</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.75775671005249</v>
+        <v>4.75775718688965</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>5.59019899368286</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.97910022735596</v>
+        <v>4.9790997505188</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>5.98178911209106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.32788324356079</v>
+        <v>5.32788276672363</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>6.55160188674927</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.8354058265686</v>
+        <v>5.83540630340576</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>6.3457670211792</v>
       </c>
       <c r="G1303" t="n">
-        <v>5.65207242965698</v>
+        <v>5.65207195281982</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>6.35078716278076</v>
       </c>
       <c r="G1304" t="n">
-        <v>5.65654325485229</v>
+        <v>5.65654373168945</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>6.40852212905884</v>
       </c>
       <c r="G1305" t="n">
-        <v>5.70796680450439</v>
+        <v>5.70796728134155</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>6.63192892074585</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.90695190429688</v>
+        <v>5.90695142745972</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>6.00940084457397</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.35247611999512</v>
+        <v>5.35247659683228</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.08418226242065</v>
+        <v>5.0841817855835</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1312" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>5.91652393341064</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.26975202560425</v>
+        <v>5.26975250244141</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>6.07215595245361</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.40837144851685</v>
+        <v>5.40837097167969</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>6.07717609405518</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.41284227371216</v>
+        <v>5.41284275054932</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>6.12486982345581</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.455322265625</v>
+        <v>5.45532274246216</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>5.97174787521362</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.31893968582153</v>
+        <v>5.31893920898438</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1324" t="n">
-        <v>5.31670331954956</v>
+        <v>5.31670379638672</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>5.69060611724854</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.06853103637695</v>
+        <v>5.06853055953979</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>5.87887096405029</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.23621511459351</v>
+        <v>5.23621559143066</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>5.83870792388916</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.20044279098511</v>
+        <v>5.20044231414795</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.97686290740967</v>
+        <v>4.97686338424683</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.94556331634521</v>
+        <v>4.94556283950806</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.87855911254883</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.34525394439697</v>
+        <v>4.34525346755981</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.82333517074585</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.29606628417969</v>
+        <v>4.29606676101685</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>5.06054782867432</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.50734853744507</v>
+        <v>4.50734806060791</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.69068336486816</v>
+        <v>4.69068288803101</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>5.1383638381958</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.57665777206421</v>
+        <v>4.57665729522705</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>5.12832307815552</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.56771469116211</v>
+        <v>4.56771421432495</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>5.11828184127808</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.55877113342285</v>
+        <v>4.55877065658569</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>5.3793420791626</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.79129314422607</v>
+        <v>4.79129266738892</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.83824491500854</v>
+        <v>4.8382453918457</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>5.56760692596436</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.95897722244263</v>
+        <v>4.95897769927979</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1390" t="n">
-        <v>4.72421979904175</v>
+        <v>4.72422027587891</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.72421979904175</v>
+        <v>4.72422027587891</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>5.29901599884033</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.71974802017212</v>
+        <v>4.71974754333496</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1396" t="n">
-        <v>4.56324291229248</v>
+        <v>4.56324338912964</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>5.22873115539551</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.65714645385742</v>
+        <v>4.65714597702026</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>5.21868991851807</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.64820289611816</v>
+        <v>4.64820241928101</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.90617084503174</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.36984729766846</v>
+        <v>4.3698468208313</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.97143602371216</v>
       </c>
       <c r="G1403" t="n">
-        <v>4.42797803878784</v>
+        <v>4.42797756195068</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>4.88483476638794</v>
       </c>
       <c r="G1405" t="n">
-        <v>4.35084342956543</v>
+        <v>4.35084295272827</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.90240621566772</v>
       </c>
       <c r="G1407" t="n">
-        <v>4.36649370193481</v>
+        <v>4.36649417877197</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.75681495666504</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.23681831359863</v>
+        <v>4.23681783676147</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1417" t="n">
-        <v>4.52970600128174</v>
+        <v>4.5297064781189</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>4.91119194030762</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.37431907653809</v>
+        <v>4.37431955337524</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.92499780654907</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.38661623001099</v>
+        <v>4.38661575317383</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.56324291229248</v>
+        <v>4.56324338912964</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>5.16597604751587</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.60125112533569</v>
+        <v>4.60125160217285</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>4.98147678375244</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.43692111968994</v>
+        <v>4.43692064285278</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1433" t="n">
-        <v>4.2770619392395</v>
+        <v>4.27706241607666</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1436" t="n">
-        <v>4.47157526016235</v>
+        <v>4.47157573699951</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>4.96139478683472</v>
       </c>
       <c r="G1443" t="n">
-        <v>4.41903448104858</v>
+        <v>4.41903400421143</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>5.01662015914917</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.46822261810303</v>
+        <v>4.46822214126587</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1449" t="n">
-        <v>4.62584447860718</v>
+        <v>4.62584495544434</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.52970600128174</v>
+        <v>4.5297064781189</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.99151802062988</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.44586420059204</v>
+        <v>4.4458646774292</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>4.91244697570801</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.37543678283691</v>
+        <v>4.37543725967407</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>5.07058906555176</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.51629209518433</v>
+        <v>4.51629161834717</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>5.55003595352173</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.94332695007324</v>
+        <v>4.9433274269104</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.69068336486816</v>
+        <v>4.69068288803101</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.79800033569336</v>
+        <v>4.79800081253052</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1470" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.91202592849731</v>
+        <v>4.91202640533447</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.95003414154053</v>
+        <v>4.95003461837769</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.94556331634521</v>
+        <v>4.94556283950806</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.87353897094727</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.34078216552734</v>
+        <v>4.3407826423645</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.81203889846802</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.2860050201416</v>
+        <v>4.28600549697876</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.34190034866333</v>
+        <v>4.34189987182617</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.39220476150513</v>
+        <v>4.39220523834229</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>4.46563196182251</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.97746634483337</v>
+        <v>3.97746610641479</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>4.50328493118286</v>
       </c>
       <c r="G1504" t="n">
-        <v>4.01100301742554</v>
+        <v>4.0110034942627</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>4.42170381546021</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.93833994865417</v>
+        <v>3.93834018707275</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>4.59365177154541</v>
       </c>
       <c r="G1509" t="n">
-        <v>4.09149122238159</v>
+        <v>4.09149169921875</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>4.56729507446289</v>
       </c>
       <c r="G1511" t="n">
-        <v>4.06801557540894</v>
+        <v>4.06801605224609</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>4.41040802001953</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.92827892303467</v>
+        <v>3.92827916145325</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>4.4455509185791</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.95958042144775</v>
+        <v>3.95958018302917</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>4.37275505065918</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.89474201202393</v>
+        <v>3.89474248886108</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.55097913742065</v>
       </c>
       <c r="G1522" t="n">
-        <v>4.0534839630127</v>
+        <v>4.05348348617554</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>4.78317213058472</v>
       </c>
       <c r="G1527" t="n">
-        <v>4.26029396057129</v>
+        <v>4.26029443740845</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>4.91495704650879</v>
       </c>
       <c r="G1531" t="n">
-        <v>4.37767314910889</v>
+        <v>4.37767267227173</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.03042602539062</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.48051881790161</v>
+        <v>4.48051929473877</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.39220476150513</v>
+        <v>4.39220523834229</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>5.01410913467407</v>
       </c>
       <c r="G1541" t="n">
-        <v>4.4659857749939</v>
+        <v>4.46598625183105</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>2.99591493606567</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.66841316223145</v>
+        <v>2.66841292381287</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>3.02854704856873</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.6974778175354</v>
+        <v>2.69747805595398</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>2.8616189956665</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.54879760742188</v>
+        <v>2.54879784584045</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.5622124671936</v>
+        <v>2.56221222877502</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.51521301269531</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.24025940895081</v>
+        <v>2.24025964736938</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>2.56165099143982</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.28162097930908</v>
+        <v>2.28162121772766</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.56792688369751</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.2872109413147</v>
+        <v>2.28721117973328</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>2.37715196609497</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.11729073524475</v>
+        <v>2.11729097366333</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.58047795295715</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.29839015007019</v>
+        <v>2.29838991165161</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>2.46450710296631</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.19509649276733</v>
+        <v>2.19509673118591</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>2.67335510253906</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.38111424446106</v>
+        <v>2.38111400604248</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>2.86287403106689</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.54991579055786</v>
+        <v>2.54991555213928</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.5622124671936</v>
+        <v>2.56221222877502</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>2.93943500518799</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.61810708045959</v>
+        <v>2.61810731887817</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>2.87919092178345</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.56444883346558</v>
+        <v>2.564448595047</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>2.84404802322388</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.53314757347107</v>
+        <v>2.53314781188965</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>2.77878308296204</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.47501707077026</v>
+        <v>2.47501730918884</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>2.80262994766235</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.49625706672668</v>
+        <v>2.49625730514526</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>2.79384398460388</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.48843145370483</v>
+        <v>2.48843169212341</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>2.75744605064392</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.4560124874115</v>
+        <v>2.45601272583008</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.43700909614563</v>
+        <v>2.43700885772705</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.84028291702271</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.52979421615601</v>
+        <v>2.52979397773743</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>2.92437410354614</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.60469269752502</v>
+        <v>2.6046929359436</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.43700909614563</v>
+        <v>2.43700885772705</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.48509001731873</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.21342968940735</v>
+        <v>2.21342945098877</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>2.53780388832092</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.26038074493408</v>
+        <v>2.26038098335266</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>2.68841600418091</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.39452862739563</v>
+        <v>2.39452886581421</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>2.90680289268494</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.58904218673706</v>
+        <v>2.58904242515564</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>2.97517991065979</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.64994478225708</v>
+        <v>2.6499445438385</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>2.72426104545593</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.4264554977417</v>
+        <v>2.42645525932312</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>2.37423992156982</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.11469697952271</v>
+        <v>2.11469721794128</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>1.96649694442749</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.75152695178986</v>
+        <v>1.75152707099915</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>2.01657509803772</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.79613089561462</v>
+        <v>1.79613077640533</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>2.21557092666626</v>
       </c>
       <c r="G1646" t="n">
-        <v>1.97337317466736</v>
+        <v>1.97337329387665</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>1.73798203468323</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.54799258708954</v>
+        <v>1.54799246788025</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.59776198863983</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.42310082912445</v>
+        <v>1.42310070991516</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>1.24932205677032</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.11275088787079</v>
+        <v>1.11275100708008</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98913502693176</v>
+        <v>2.98913478851318</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.73594272136688</v>
+        <v>1.73594284057617</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.98598700761795</v>
+        <v>0.985986948013306</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.04210007190704</v>
+        <v>1.04209995269775</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.730360746383667</v>
+        <v>0.730360686779022</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>0.71340000629425</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.635413885116577</v>
+        <v>0.635413825511932</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.659106016159058</v>
+        <v>0.659106075763702</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.692061305046082</v>
+        <v>0.692061364650726</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.751737117767334</v>
+        <v>0.751737177371979</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>0.833599984645844</v>
       </c>
       <c r="G1677" t="n">
-        <v>0.742474019527435</v>
+        <v>0.74247407913208</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>0.821799993515015</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.731963932514191</v>
+        <v>0.731963992118835</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>0.762199997901917</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.678879201412201</v>
+        <v>0.678879261016846</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>0.716400027275085</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.638085961341858</v>
+        <v>0.638085901737213</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>0.674600005149841</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.600855350494385</v>
+        <v>0.60085529088974</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>0.697399973869324</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.621162831783295</v>
+        <v>0.621162891387939</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>0.683200001716614</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.60851514339447</v>
+        <v>0.608515202999115</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>0.662199974060059</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.589810788631439</v>
+        <v>0.589810848236084</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>0.64300000667572</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.572709679603577</v>
+        <v>0.572709739208221</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.540645122528076</v>
+        <v>0.540645062923431</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>0.584800004959106</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.520871877670288</v>
+        <v>0.520871937274933</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>0.59280002117157</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.527997434139252</v>
+        <v>0.527997374534607</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>0.597199976444244</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.531916379928589</v>
+        <v>0.531916320323944</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>0.637600004673004</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.567900061607361</v>
+        <v>0.567900002002716</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>0.72759997844696</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.648061573505402</v>
+        <v>0.648061513900757</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.620806634426117</v>
+        <v>0.620806694030762</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.658215403556824</v>
+        <v>0.658215343952179</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>0.758199989795685</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.675316512584686</v>
+        <v>0.675316452980042</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>0.828599989414215</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.738020658493042</v>
+        <v>0.738020598888397</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>0.958599984645844</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.853809475898743</v>
+        <v>0.853809535503387</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.876432955265045</v>
+        <v>0.8764328956604</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.873760879039764</v>
+        <v>0.87376081943512</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.882667720317841</v>
+        <v>0.882667660713196</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.919185638427734</v>
+        <v>0.919185698032379</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.957485139369965</v>
+        <v>0.957485198974609</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>1.09650003910065</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.976634919643402</v>
+        <v>0.976634860038757</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>1.03250002861023</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.919631123542786</v>
+        <v>0.919631063938141</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.92185777425766</v>
+        <v>0.921857714653015</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>1.04649996757507</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.932100594043732</v>
+        <v>0.932100653648376</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.926311194896698</v>
+        <v>0.926311135292053</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>1.04750001430511</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.932991325855255</v>
+        <v>0.93299126625061</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.912950932979584</v>
+        <v>0.912950873374939</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>1.01950001716614</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.908052206039429</v>
+        <v>0.908052146434784</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>1.04449999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.930319249629974</v>
+        <v>0.93031919002533</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>1.00650000572205</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.896473288536072</v>
+        <v>0.896473228931427</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.04949998855591</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.934772670269012</v>
+        <v>0.934772729873657</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>1.10950005054474</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.988213717937469</v>
+        <v>0.988213777542114</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.977970898151398</v>
+        <v>0.977970957756042</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>1.12750005722046</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.00424611568451</v>
+        <v>1.00424599647522</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.05456972122192</v>
+        <v>1.05456960201263</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>1.31149995326996</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.16813170909882</v>
+        <v>1.16813182830811</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.25141084194183</v>
+        <v>1.25141072273254</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.23092496395111</v>
+        <v>1.2309250831604</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.21845543384552</v>
+        <v>1.21845555305481</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.26031768321991</v>
+        <v>1.26031756401062</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.25586426258087</v>
+        <v>1.25586414337158</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.24962937831879</v>
+        <v>1.24962949752808</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.31464922428131</v>
+        <v>1.3146493434906</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.35116732120514</v>
+        <v>1.35116744041443</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>1.53450000286102</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.36675441265106</v>
+        <v>1.36675429344177</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.31643080711365</v>
+        <v>1.31643068790436</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.35749995708466</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.20910322666168</v>
+        <v>1.20910334587097</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>1.26549994945526</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.12716042995453</v>
+        <v>1.12716031074524</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>1.14049994945526</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.01582479476929</v>
+        <v>1.01582491397858</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>1.23450005054474</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.09954917430878</v>
+        <v>1.09954929351807</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.32550001144409</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.1806013584137</v>
+        <v>1.18060147762299</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.14007520675659</v>
+        <v>1.14007532596588</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23181569576263</v>
+        <v>1.23181581497192</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.31821203231812</v>
+        <v>1.3182121515274</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>1.25049996376038</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.11380016803741</v>
+        <v>1.11380004882812</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.150763630867</v>
+        <v>1.15076351165771</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.13473117351532</v>
+        <v>1.13473129272461</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.12048029899597</v>
+        <v>1.12048017978668</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.15788888931274</v>
+        <v>1.15788900852203</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>1.25750005245209</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.12003493309021</v>
+        <v>1.1200350522995</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.12226152420044</v>
+        <v>1.12226164340973</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.07416462898254</v>
+        <v>1.07416474819183</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.13473117351532</v>
+        <v>1.13473129272461</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>1.25450003147125</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.11736285686493</v>
+        <v>1.11736297607422</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.08663439750671</v>
+        <v>1.08663427829742</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>1.16250002384186</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.03542006015778</v>
+        <v>1.03541994094849</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.04833483695984</v>
+        <v>1.04833495616913</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.07772755622864</v>
+        <v>1.07772743701935</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.30039834976196</v>
+        <v>1.30039846897125</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.31108665466309</v>
+        <v>1.3110865354538</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.32266545295715</v>
+        <v>1.32266557216644</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>1.43949997425079</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.28213930130005</v>
+        <v>1.28213942050934</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>1.43250000476837</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.27590465545654</v>
+        <v>1.27590453624725</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.30039834976196</v>
+        <v>1.30039846897125</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.32800960540771</v>
+        <v>1.328009724617</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1928" t="n">
-        <v>1.31821203231812</v>
+        <v>1.3182121515274</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.31821203231812</v>
+        <v>1.3182121515274</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1930" t="n">
-        <v>1.29683554172516</v>
+        <v>1.29683566093445</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.29327297210693</v>
+        <v>1.29327285289764</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.25586426258087</v>
+        <v>1.25586414337158</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1935" t="n">
-        <v>1.24339473247528</v>
+        <v>1.24339461326599</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.304851770401</v>
+        <v>1.30485188961029</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.31019580364227</v>
+        <v>1.31019592285156</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.33869791030884</v>
+        <v>1.33869779109955</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.32266545295715</v>
+        <v>1.32266557216644</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1951" t="n">
-        <v>1.40193629264832</v>
+        <v>1.4019364118576</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.32800960540771</v>
+        <v>1.328009724617</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.31019580364227</v>
+        <v>1.31019592285156</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.37566125392914</v>
+        <v>1.37566113471985</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.41974997520447</v>
+        <v>1.41975009441376</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>1.60950005054474</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.43355560302734</v>
+        <v>1.43355572223663</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.40104556083679</v>
+        <v>1.40104568004608</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>1.46249997615814</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.30262506008148</v>
+        <v>1.30262517929077</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.27679526805878</v>
+        <v>1.27679538726807</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.29683554172516</v>
+        <v>1.29683566093445</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>1.41849994659424</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.26343488693237</v>
+        <v>1.26343500614166</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>1.5275000333786</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.36051952838898</v>
+        <v>1.36051964759827</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52031,7 +52031,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.37566125392914</v>
+        <v>1.37566113471985</v>
       </c>
       <c r="H1987" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.29015552997589</v>
+        <v>1.29015564918518</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.41449999809265</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.25987219810486</v>
+        <v>1.25987231731415</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.23626911640167</v>
+        <v>1.23626923561096</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.26031768321991</v>
+        <v>1.26031756401062</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.23805058002472</v>
+        <v>1.23805046081543</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2007" t="n">
-        <v>1.26031768321991</v>
+        <v>1.26031756401062</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>1.44749999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>1.28926491737366</v>
+        <v>1.28926479816437</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.31019580364227</v>
+        <v>1.31019592285156</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>1.46150004863739</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.30173456668854</v>
+        <v>1.30173444747925</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.24784815311432</v>
+        <v>1.24784803390503</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2023" t="n">
-        <v>1.24784815311432</v>
+        <v>1.24784803390503</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.22647154331207</v>
+        <v>1.22647166252136</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>1.42050004005432</v>
       </c>
       <c r="G2029" t="n">
-        <v>1.26521646976471</v>
+        <v>1.26521635055542</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.29015552997589</v>
+        <v>1.29015564918518</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>1.44649994373322</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.28837418556213</v>
+        <v>1.28837406635284</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>1.48300004005432</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.32088422775269</v>
+        <v>1.3208841085434</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.30930519104004</v>
+        <v>1.30930531024933</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>1.4889999628067</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.32622826099396</v>
+        <v>1.32622814178467</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>1.50650000572205</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.3418151140213</v>
+        <v>1.34181523323059</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.27679526805878</v>
+        <v>1.27679538726807</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.31643080711365</v>
+        <v>1.31643068790436</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G2055" t="n">
-        <v>1.34315133094788</v>
+        <v>1.34315121173859</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -54189,7 +54189,7 @@
         <v>1.375</v>
       </c>
       <c r="G2070" t="n">
-        <v>1.2246903181076</v>
+        <v>1.22469019889832</v>
       </c>
       <c r="H2070" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>1.38100004196167</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.23003447055817</v>
+        <v>1.23003435134888</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.32979106903076</v>
+        <v>1.32979094982147</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>1.82149994373322</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.62238049507141</v>
+        <v>1.6223806142807</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.723473072052</v>
+        <v>1.72347319126129</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>1.97650003433228</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.76043653488159</v>
+        <v>1.76043665409088</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.87488949298859</v>
+        <v>1.87488961219788</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.88112425804138</v>
+        <v>1.88112413883209</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>2.08699989318848</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.8588570356369</v>
+        <v>1.85885715484619</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.91318893432617</v>
+        <v>1.91318881511688</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -55047,7 +55047,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.98889708518982</v>
+        <v>1.98889696598053</v>
       </c>
       <c r="H2103" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2104" t="n">
-        <v>2.0076014995575</v>
+        <v>2.00760126113892</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G2105" t="n">
-        <v>2.00849223136902</v>
+        <v>2.00849199295044</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.06994891166687</v>
+        <v>2.06994915008545</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>2.3970000743866</v>
       </c>
       <c r="G2109" t="n">
-        <v>2.13496899604797</v>
+        <v>2.13496923446655</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2110" t="n">
-        <v>2.08420014381409</v>
+        <v>2.08419990539551</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.99513173103333</v>
+        <v>1.99513185024261</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.97909951210022</v>
+        <v>1.97909939289093</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.94258153438568</v>
+        <v>1.94258141517639</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.9719740152359</v>
+        <v>1.97197389602661</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.95237898826599</v>
+        <v>1.9523788690567</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2123" t="n">
-        <v>1.94079983234406</v>
+        <v>1.94080007076263</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55645,7 +55645,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2126" t="n">
-        <v>1.91318893432617</v>
+        <v>1.91318881511688</v>
       </c>
       <c r="H2126" t="s">
         <v>8</v>
@@ -55697,7 +55697,7 @@
         <v>2.13100004196167</v>
       </c>
       <c r="G2128" t="n">
-        <v>1.89804720878601</v>
+        <v>1.8980473279953</v>
       </c>
       <c r="H2128" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.95683240890503</v>
+        <v>1.95683228969574</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G2131" t="n">
-        <v>1.97019267082214</v>
+        <v>1.97019255161285</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G2132" t="n">
-        <v>2.02541518211365</v>
+        <v>2.02541494369507</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -55853,7 +55853,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2134" t="n">
-        <v>2.11359262466431</v>
+        <v>2.11359286308289</v>
       </c>
       <c r="H2134" t="s">
         <v>8</v>
@@ -55957,7 +55957,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2138" t="n">
-        <v>2.12160873413086</v>
+        <v>2.12160897254944</v>
       </c>
       <c r="H2138" t="s">
         <v>8</v>
@@ -55983,7 +55983,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2139" t="n">
-        <v>2.11359262466431</v>
+        <v>2.11359286308289</v>
       </c>
       <c r="H2139" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2141" t="n">
-        <v>2.07084012031555</v>
+        <v>2.07083988189697</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56087,7 +56087,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2143" t="n">
-        <v>1.98889708518982</v>
+        <v>1.98889696598053</v>
       </c>
       <c r="H2143" t="s">
         <v>8</v>
@@ -56139,7 +56139,7 @@
         <v>2.15300011634827</v>
       </c>
       <c r="G2145" t="n">
-        <v>1.9176424741745</v>
+        <v>1.91764235496521</v>
       </c>
       <c r="H2145" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.92031419277191</v>
+        <v>1.9203143119812</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.9336746931076</v>
+        <v>1.93367457389832</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91853308677673</v>
+        <v>1.91853296756744</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.83926224708557</v>
+        <v>1.83926212787628</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.80808818340302</v>
+        <v>1.80808806419373</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.86152923107147</v>
+        <v>1.86152911186218</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56399,7 +56399,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2155" t="n">
-        <v>1.86152923107147</v>
+        <v>1.86152911186218</v>
       </c>
       <c r="H2155" t="s">
         <v>8</v>
@@ -56425,7 +56425,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2156" t="n">
-        <v>1.89626586437225</v>
+        <v>1.89626574516296</v>
       </c>
       <c r="H2156" t="s">
         <v>8</v>
@@ -56451,7 +56451,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2157" t="n">
-        <v>1.91853308677673</v>
+        <v>1.91853296756744</v>
       </c>
       <c r="H2157" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>2.15899991989136</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.92298638820648</v>
+        <v>1.92298626899719</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56503,7 +56503,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.99245977401733</v>
+        <v>1.99245965480804</v>
       </c>
       <c r="H2159" t="s">
         <v>8</v>
@@ -56607,7 +56607,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.13585996627808</v>
+        <v>2.1358597278595</v>
       </c>
       <c r="H2163" t="s">
         <v>8</v>
@@ -56711,7 +56711,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2167" t="n">
-        <v>2.07084012031555</v>
+        <v>2.07083988189697</v>
       </c>
       <c r="H2167" t="s">
         <v>8</v>
@@ -56789,7 +56789,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G2170" t="n">
-        <v>2.07351207733154</v>
+        <v>2.07351183891296</v>
       </c>
       <c r="H2170" t="s">
         <v>8</v>
@@ -56815,7 +56815,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2171" t="n">
-        <v>2.06371450424194</v>
+        <v>2.06371426582336</v>
       </c>
       <c r="H2171" t="s">
         <v>8</v>
@@ -56841,7 +56841,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G2172" t="n">
-        <v>2.09666967391968</v>
+        <v>2.09666991233826</v>
       </c>
       <c r="H2172" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2174" t="n">
-        <v>2.10913944244385</v>
+        <v>2.10913920402527</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G2175" t="n">
-        <v>2.12339019775391</v>
+        <v>2.12339043617249</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -56945,7 +56945,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G2176" t="n">
-        <v>2.14476680755615</v>
+        <v>2.14476656913757</v>
       </c>
       <c r="H2176" t="s">
         <v>8</v>
@@ -57023,7 +57023,7 @@
         <v>2.41899991035461</v>
       </c>
       <c r="G2179" t="n">
-        <v>2.15456414222717</v>
+        <v>2.15456390380859</v>
       </c>
       <c r="H2179" t="s">
         <v>8</v>
@@ -57075,7 +57075,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2181" t="n">
-        <v>2.07084012031555</v>
+        <v>2.07083988189697</v>
       </c>
       <c r="H2181" t="s">
         <v>8</v>
@@ -57101,7 +57101,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G2182" t="n">
-        <v>1.9844434261322</v>
+        <v>1.98444354534149</v>
       </c>
       <c r="H2182" t="s">
         <v>8</v>
@@ -57153,7 +57153,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2184" t="n">
-        <v>1.94614410400391</v>
+        <v>1.9461442232132</v>
       </c>
       <c r="H2184" t="s">
         <v>8</v>
@@ -57179,7 +57179,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2185" t="n">
-        <v>1.95683240890503</v>
+        <v>1.95683228969574</v>
       </c>
       <c r="H2185" t="s">
         <v>8</v>
@@ -57205,7 +57205,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2186" t="n">
-        <v>1.94079983234406</v>
+        <v>1.94080007076263</v>
       </c>
       <c r="H2186" t="s">
         <v>8</v>
@@ -57309,7 +57309,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G2190" t="n">
-        <v>1.79294657707214</v>
+        <v>1.79294645786285</v>
       </c>
       <c r="H2190" t="s">
         <v>8</v>
@@ -57413,7 +57413,7 @@
         <v>1.98450005054474</v>
       </c>
       <c r="G2194" t="n">
-        <v>1.7675621509552</v>
+        <v>1.76756203174591</v>
       </c>
       <c r="H2194" t="s">
         <v>8</v>
@@ -57543,7 +57543,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G2199" t="n">
-        <v>1.8428248167038</v>
+        <v>1.84282493591309</v>
       </c>
       <c r="H2199" t="s">
         <v>8</v>
@@ -57621,7 +57621,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G2202" t="n">
-        <v>1.84549689292908</v>
+        <v>1.84549701213837</v>
       </c>
       <c r="H2202" t="s">
         <v>8</v>
@@ -57647,7 +57647,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G2203" t="n">
-        <v>1.81521368026733</v>
+        <v>1.81521379947662</v>
       </c>
       <c r="H2203" t="s">
         <v>8</v>
@@ -57725,7 +57725,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2206" t="n">
-        <v>1.80808818340302</v>
+        <v>1.80808806419373</v>
       </c>
       <c r="H2206" t="s">
         <v>8</v>
@@ -57751,7 +57751,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2207" t="n">
-        <v>1.80185329914093</v>
+        <v>1.80185341835022</v>
       </c>
       <c r="H2207" t="s">
         <v>8</v>
@@ -57777,7 +57777,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2208" t="n">
-        <v>1.67448568344116</v>
+        <v>1.67448556423187</v>
       </c>
       <c r="H2208" t="s">
         <v>8</v>
@@ -57803,7 +57803,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G2209" t="n">
-        <v>1.71189439296722</v>
+        <v>1.71189427375793</v>
       </c>
       <c r="H2209" t="s">
         <v>8</v>
@@ -57907,7 +57907,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G2213" t="n">
-        <v>1.60055899620056</v>
+        <v>1.60055887699127</v>
       </c>
       <c r="H2213" t="s">
         <v>8</v>
@@ -57933,7 +57933,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G2214" t="n">
-        <v>1.62727928161621</v>
+        <v>1.6272794008255</v>
       </c>
       <c r="H2214" t="s">
         <v>8</v>
@@ -58193,7 +58193,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G2224" t="n">
-        <v>1.81343233585358</v>
+        <v>1.81343221664429</v>
       </c>
       <c r="H2224" t="s">
         <v>8</v>
@@ -58401,7 +58401,7 @@
         <v>2.05699992179871</v>
       </c>
       <c r="G2232" t="n">
-        <v>1.83213651180267</v>
+        <v>1.83213663101196</v>
       </c>
       <c r="H2232" t="s">
         <v>8</v>
@@ -58453,7 +58453,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2234" t="n">
-        <v>1.79027450084686</v>
+        <v>1.79027438163757</v>
       </c>
       <c r="H2234" t="s">
         <v>8</v>
@@ -58479,7 +58479,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2235" t="n">
-        <v>1.80185329914093</v>
+        <v>1.80185341835022</v>
       </c>
       <c r="H2235" t="s">
         <v>8</v>
@@ -58635,7 +58635,7 @@
         <v>1.99150002002716</v>
       </c>
       <c r="G2241" t="n">
-        <v>1.77379679679871</v>
+        <v>1.773796916008</v>
       </c>
       <c r="H2241" t="s">
         <v>8</v>
@@ -58687,7 +58687,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2243" t="n">
-        <v>1.83926224708557</v>
+        <v>1.83926212787628</v>
       </c>
       <c r="H2243" t="s">
         <v>8</v>
@@ -58713,7 +58713,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G2244" t="n">
-        <v>1.80630683898926</v>
+        <v>1.80630695819855</v>
       </c>
       <c r="H2244" t="s">
         <v>8</v>
@@ -58739,7 +58739,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G2245" t="n">
-        <v>1.89003109931946</v>
+        <v>1.89003121852875</v>
       </c>
       <c r="H2245" t="s">
         <v>8</v>
@@ -58765,7 +58765,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G2246" t="n">
-        <v>1.94970667362213</v>
+        <v>1.94970679283142</v>
       </c>
       <c r="H2246" t="s">
         <v>8</v>
@@ -58817,7 +58817,7 @@
         <v>2.16300010681152</v>
       </c>
       <c r="G2248" t="n">
-        <v>1.92654931545258</v>
+        <v>1.92654919624329</v>
       </c>
       <c r="H2248" t="s">
         <v>8</v>
@@ -58843,7 +58843,7 @@
         <v>2.16700005531311</v>
       </c>
       <c r="G2249" t="n">
-        <v>1.9301118850708</v>
+        <v>1.93011200428009</v>
       </c>
       <c r="H2249" t="s">
         <v>8</v>
@@ -58869,7 +58869,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2250" t="n">
-        <v>1.94525349140167</v>
+        <v>1.94525361061096</v>
       </c>
       <c r="H2250" t="s">
         <v>8</v>
@@ -58895,7 +58895,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2251" t="n">
-        <v>1.97909951210022</v>
+        <v>1.97909939289093</v>
       </c>
       <c r="H2251" t="s">
         <v>8</v>
@@ -58921,7 +58921,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2252" t="n">
-        <v>1.97909951210022</v>
+        <v>1.97909939289093</v>
       </c>
       <c r="H2252" t="s">
         <v>8</v>
@@ -58973,7 +58973,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2254" t="n">
-        <v>2.00314807891846</v>
+        <v>2.00314784049988</v>
       </c>
       <c r="H2254" t="s">
         <v>8</v>
@@ -59025,7 +59025,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2256" t="n">
-        <v>2.06994891166687</v>
+        <v>2.06994915008545</v>
       </c>
       <c r="H2256" t="s">
         <v>8</v>
@@ -59103,7 +59103,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2259" t="n">
-        <v>2.0530264377594</v>
+        <v>2.05302619934082</v>
       </c>
       <c r="H2259" t="s">
         <v>8</v>
@@ -59129,7 +59129,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2260" t="n">
-        <v>2.06371450424194</v>
+        <v>2.06371426582336</v>
       </c>
       <c r="H2260" t="s">
         <v>8</v>
@@ -59155,7 +59155,7 @@
         <v>2.33299994468689</v>
       </c>
       <c r="G2261" t="n">
-        <v>2.077965259552</v>
+        <v>2.07796549797058</v>
       </c>
       <c r="H2261" t="s">
         <v>8</v>
@@ -59181,7 +59181,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2262" t="n">
-        <v>2.10913944244385</v>
+        <v>2.10913920402527</v>
       </c>
       <c r="H2262" t="s">
         <v>8</v>
@@ -59363,7 +59363,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G2269" t="n">
-        <v>2.1652524471283</v>
+        <v>2.16525220870972</v>
       </c>
       <c r="H2269" t="s">
         <v>8</v>
@@ -59493,7 +59493,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G2274" t="n">
-        <v>2.26768112182617</v>
+        <v>2.26768088340759</v>
       </c>
       <c r="H2274" t="s">
         <v>8</v>
@@ -59597,7 +59597,7 @@
         <v>2.48699998855591</v>
       </c>
       <c r="G2278" t="n">
-        <v>2.21513056755066</v>
+        <v>2.21513080596924</v>
       </c>
       <c r="H2278" t="s">
         <v>8</v>
@@ -59675,7 +59675,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G2281" t="n">
-        <v>2.29262018203735</v>
+        <v>2.29261994361877</v>
       </c>
       <c r="H2281" t="s">
         <v>8</v>
@@ -59701,7 +59701,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2282" t="n">
-        <v>2.31577777862549</v>
+        <v>2.31577801704407</v>
       </c>
       <c r="H2282" t="s">
         <v>8</v>
@@ -59779,7 +59779,7 @@
         <v>2.64299988746643</v>
       </c>
       <c r="G2285" t="n">
-        <v>2.35407710075378</v>
+        <v>2.35407733917236</v>
       </c>
       <c r="H2285" t="s">
         <v>8</v>
@@ -59857,7 +59857,7 @@
         <v>2.51099991798401</v>
       </c>
       <c r="G2288" t="n">
-        <v>2.23650717735291</v>
+        <v>2.23650693893433</v>
       </c>
       <c r="H2288" t="s">
         <v>8</v>
@@ -59883,7 +59883,7 @@
         <v>2.5090000629425</v>
       </c>
       <c r="G2289" t="n">
-        <v>2.23472571372986</v>
+        <v>2.23472595214844</v>
       </c>
       <c r="H2289" t="s">
         <v>8</v>
@@ -60039,7 +60039,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G2295" t="n">
-        <v>2.45294308662415</v>
+        <v>2.45294332504272</v>
       </c>
       <c r="H2295" t="s">
         <v>8</v>
@@ -60143,7 +60143,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G2299" t="n">
-        <v>2.31221532821655</v>
+        <v>2.31221508979797</v>
       </c>
       <c r="H2299" t="s">
         <v>8</v>
@@ -60195,7 +60195,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G2301" t="n">
-        <v>2.27658796310425</v>
+        <v>2.27658772468567</v>
       </c>
       <c r="H2301" t="s">
         <v>8</v>
@@ -60221,7 +60221,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G2302" t="n">
-        <v>2.25164890289307</v>
+        <v>2.25164866447449</v>
       </c>
       <c r="H2302" t="s">
         <v>8</v>
@@ -60247,7 +60247,7 @@
         <v>2.51300001144409</v>
       </c>
       <c r="G2303" t="n">
-        <v>2.23828864097595</v>
+        <v>2.23828840255737</v>
       </c>
       <c r="H2303" t="s">
         <v>8</v>
@@ -60299,7 +60299,7 @@
         <v>2.48300004005432</v>
       </c>
       <c r="G2305" t="n">
-        <v>2.21156811714172</v>
+        <v>2.21156787872314</v>
       </c>
       <c r="H2305" t="s">
         <v>8</v>
@@ -60325,7 +60325,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G2306" t="n">
-        <v>2.14832925796509</v>
+        <v>2.14832949638367</v>
       </c>
       <c r="H2306" t="s">
         <v>8</v>
@@ -60351,7 +60351,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2307" t="n">
-        <v>2.12160873413086</v>
+        <v>2.12160897254944</v>
       </c>
       <c r="H2307" t="s">
         <v>8</v>
@@ -60559,7 +60559,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G2315" t="n">
-        <v>2.04411959648132</v>
+        <v>2.04411935806274</v>
       </c>
       <c r="H2315" t="s">
         <v>8</v>
@@ -60611,7 +60611,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G2317" t="n">
-        <v>2.04768204689026</v>
+        <v>2.04768228530884</v>
       </c>
       <c r="H2317" t="s">
         <v>8</v>
@@ -60741,7 +60741,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G2322" t="n">
-        <v>2.05658888816833</v>
+        <v>2.05658912658691</v>
       </c>
       <c r="H2322" t="s">
         <v>8</v>
@@ -60819,7 +60819,7 @@
         <v>2.28099989891052</v>
       </c>
       <c r="G2325" t="n">
-        <v>2.03164958953857</v>
+        <v>2.03164982795715</v>
       </c>
       <c r="H2325" t="s">
         <v>8</v>
@@ -60845,7 +60845,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G2326" t="n">
-        <v>2.06816792488098</v>
+        <v>2.0681676864624</v>
       </c>
       <c r="H2326" t="s">
         <v>8</v>
@@ -60923,7 +60923,7 @@
         <v>2.20300006866455</v>
       </c>
       <c r="G2329" t="n">
-        <v>1.96217656135559</v>
+        <v>1.9621764421463</v>
       </c>
       <c r="H2329" t="s">
         <v>8</v>
@@ -60949,7 +60949,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2330" t="n">
-        <v>2.00314807891846</v>
+        <v>2.00314784049988</v>
       </c>
       <c r="H2330" t="s">
         <v>8</v>
@@ -61001,7 +61001,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2332" t="n">
-        <v>1.91853308677673</v>
+        <v>1.91853296756744</v>
       </c>
       <c r="H2332" t="s">
         <v>8</v>
@@ -61053,7 +61053,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2334" t="n">
-        <v>1.80808818340302</v>
+        <v>1.80808806419373</v>
       </c>
       <c r="H2334" t="s">
         <v>8</v>
@@ -61183,7 +61183,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G2339" t="n">
-        <v>1.85440373420715</v>
+        <v>1.85440385341644</v>
       </c>
       <c r="H2339" t="s">
         <v>8</v>
@@ -61261,7 +61261,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2342" t="n">
-        <v>1.89626586437225</v>
+        <v>1.89626574516296</v>
       </c>
       <c r="H2342" t="s">
         <v>8</v>
@@ -61287,7 +61287,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2343" t="n">
-        <v>1.93278384208679</v>
+        <v>1.93278396129608</v>
       </c>
       <c r="H2343" t="s">
         <v>8</v>
@@ -61313,7 +61313,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2344" t="n">
-        <v>1.95683240890503</v>
+        <v>1.95683228969574</v>
       </c>
       <c r="H2344" t="s">
         <v>8</v>
@@ -61391,7 +61391,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2347" t="n">
-        <v>1.9684112071991</v>
+        <v>1.96841132640839</v>
       </c>
       <c r="H2347" t="s">
         <v>8</v>
@@ -61417,7 +61417,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2348" t="n">
-        <v>1.94525349140167</v>
+        <v>1.94525361061096</v>
       </c>
       <c r="H2348" t="s">
         <v>8</v>
@@ -61469,7 +61469,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G2350" t="n">
-        <v>1.95861351490021</v>
+        <v>1.9586136341095</v>
       </c>
       <c r="H2350" t="s">
         <v>8</v>
@@ -61495,7 +61495,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2351" t="n">
-        <v>1.9336746931076</v>
+        <v>1.93367457389832</v>
       </c>
       <c r="H2351" t="s">
         <v>8</v>
@@ -61573,7 +61573,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G2354" t="n">
-        <v>1.89537525177002</v>
+        <v>1.89537537097931</v>
       </c>
       <c r="H2354" t="s">
         <v>8</v>
@@ -61599,7 +61599,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G2355" t="n">
-        <v>1.72436392307281</v>
+        <v>1.72436380386353</v>
       </c>
       <c r="H2355" t="s">
         <v>8</v>
@@ -61755,7 +61755,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G2361" t="n">
-        <v>1.52128791809082</v>
+        <v>1.52128803730011</v>
       </c>
       <c r="H2361" t="s">
         <v>8</v>
@@ -61781,7 +61781,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G2362" t="n">
-        <v>1.56493151187897</v>
+        <v>1.56493139266968</v>
       </c>
       <c r="H2362" t="s">
         <v>8</v>
@@ -61937,7 +61937,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G2368" t="n">
-        <v>1.749302983284</v>
+        <v>1.74930310249329</v>
       </c>
       <c r="H2368" t="s">
         <v>8</v>
@@ -62015,7 +62015,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2371" t="n">
-        <v>1.82590186595917</v>
+        <v>1.82590174674988</v>
       </c>
       <c r="H2371" t="s">
         <v>8</v>
@@ -62067,7 +62067,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2373" t="n">
-        <v>1.8526223897934</v>
+        <v>1.85262227058411</v>
       </c>
       <c r="H2373" t="s">
         <v>8</v>
@@ -62093,7 +62093,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G2374" t="n">
-        <v>1.83302736282349</v>
+        <v>1.83302748203278</v>
       </c>
       <c r="H2374" t="s">
         <v>8</v>
@@ -62119,7 +62119,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G2375" t="n">
-        <v>1.82768321037292</v>
+        <v>1.82768332958221</v>
       </c>
       <c r="H2375" t="s">
         <v>8</v>
@@ -62145,7 +62145,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G2376" t="n">
-        <v>1.83837127685547</v>
+        <v>1.83837139606476</v>
       </c>
       <c r="H2376" t="s">
         <v>8</v>
@@ -62197,7 +62197,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G2378" t="n">
-        <v>1.93990933895111</v>
+        <v>1.9399094581604</v>
       </c>
       <c r="H2378" t="s">
         <v>8</v>
@@ -69194,6 +69194,32 @@
         <v>4.30900001525879</v>
       </c>
       <c r="H2647" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2648">
+      <c r="A2648" s="1" t="n">
+        <v>46177.2916666667</v>
+      </c>
+      <c r="B2648" t="n">
+        <v>10424965</v>
+      </c>
+      <c r="C2648" t="n">
+        <v>4.34299993515015</v>
+      </c>
+      <c r="D2648" t="n">
+        <v>4.17000007629395</v>
+      </c>
+      <c r="E2648" t="n">
+        <v>4.29300022125244</v>
+      </c>
+      <c r="F2648" t="n">
+        <v>4.3289999961853</v>
+      </c>
+      <c r="G2648" t="n">
+        <v>4.3289999961853</v>
+      </c>
+      <c r="H2648" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>22.8775520324707</v>
       </c>
       <c r="G2" t="n">
-        <v>20.2849216461182</v>
+        <v>20.2849197387695</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>21.9295864105225</v>
       </c>
       <c r="G5" t="n">
-        <v>19.4443855285645</v>
+        <v>19.4443836212158</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>21.3766078948975</v>
       </c>
       <c r="G6" t="n">
-        <v>18.9540710449219</v>
+        <v>18.9540748596191</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>22.1823787689209</v>
       </c>
       <c r="G10" t="n">
-        <v>19.6685276031494</v>
+        <v>19.668529510498</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460279464722</v>
+        <v>15.7460269927979</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>16.7157802581787</v>
       </c>
       <c r="G15" t="n">
-        <v>14.8214406967163</v>
+        <v>14.821439743042</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>13.806058883667</v>
       </c>
       <c r="G19" t="n">
-        <v>12.2414674758911</v>
+        <v>12.2414665222168</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.358302116394</v>
       </c>
       <c r="G22" t="n">
-        <v>12.7311267852783</v>
+        <v>12.7311277389526</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.8813648223877</v>
       </c>
       <c r="G23" t="n">
-        <v>12.3082389831543</v>
+        <v>12.30823802948</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>13.5048360824585</v>
       </c>
       <c r="G24" t="n">
-        <v>11.9743804931641</v>
+        <v>11.9743814468384</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.0530023574829</v>
       </c>
       <c r="G26" t="n">
-        <v>11.5737524032593</v>
+        <v>11.573751449585</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>9.75209808349609</v>
       </c>
       <c r="G27" t="n">
-        <v>8.64692687988281</v>
+        <v>8.64692783355713</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G29" t="n">
-        <v>8.0571117401123</v>
+        <v>8.05711078643799</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G31" t="n">
-        <v>6.70832443237305</v>
+        <v>6.70832395553589</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.8774790763855</v>
+        <v>6.87747859954834</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51180934906006</v>
+        <v>7.51181030273438</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.30120658874512</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36045980453491</v>
+        <v>7.36046028137207</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243982315063</v>
+        <v>7.91243934631348</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G40" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.67679214477539</v>
       </c>
       <c r="G45" t="n">
-        <v>8.58015537261963</v>
+        <v>8.58015632629395</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.96546459197998</v>
       </c>
       <c r="G46" t="n">
-        <v>8.83611392974854</v>
+        <v>8.83611297607422</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>10.6884002685547</v>
       </c>
       <c r="G47" t="n">
-        <v>9.47712230682373</v>
+        <v>9.47712135314941</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811340332031</v>
+        <v>7.98811292648315</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G53" t="n">
-        <v>8.29526329040527</v>
+        <v>8.29526424407959</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.26261138916016</v>
       </c>
       <c r="G54" t="n">
-        <v>8.21291351318359</v>
+        <v>8.21291255950928</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.3175220489502</v>
+        <v>8.31752109527588</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.34488010406494</v>
+        <v>7.34487962722778</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870809555054</v>
+        <v>7.65870761871338</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365732192993</v>
+        <v>7.27365779876709</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G70" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G71" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.8634729385376</v>
+        <v>7.86347341537476</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.25006008148193</v>
       </c>
       <c r="G79" t="n">
-        <v>8.20178318023682</v>
+        <v>8.20178413391113</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.39816093444824</v>
       </c>
       <c r="G80" t="n">
-        <v>8.33310031890869</v>
+        <v>8.33310127258301</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.55128288269043</v>
       </c>
       <c r="G81" t="n">
-        <v>8.46886920928955</v>
+        <v>8.46887016296387</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G83" t="n">
-        <v>9.68188762664795</v>
+        <v>9.68188858032227</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G84" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G87" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G88" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G89" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.36803913116455</v>
       </c>
       <c r="G90" t="n">
-        <v>8.30639171600342</v>
+        <v>8.30639266967773</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.20487594604492</v>
       </c>
       <c r="G91" t="n">
-        <v>8.16172027587891</v>
+        <v>8.16171932220459</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.2685546875</v>
+        <v>8.26855373382568</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G96" t="n">
-        <v>8.31974601745605</v>
+        <v>8.31974697113037</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G97" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588848114014</v>
+        <v>7.98588752746582</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701690673828</v>
+        <v>7.99701738357544</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>8.92875480651855</v>
       </c>
       <c r="G100" t="n">
-        <v>7.91689014434814</v>
+        <v>7.91689109802246</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.14212131500244</v>
       </c>
       <c r="G101" t="n">
-        <v>8.10607814788818</v>
+        <v>8.10607719421387</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.3303861618042</v>
       </c>
       <c r="G105" t="n">
-        <v>8.27300643920898</v>
+        <v>8.27300548553467</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G106" t="n">
-        <v>8.18842887878418</v>
+        <v>8.1884298324585</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.04924392700195</v>
       </c>
       <c r="G108" t="n">
-        <v>8.02372455596924</v>
+        <v>8.02372550964355</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889585494995</v>
+        <v>7.77889537811279</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701690673828</v>
+        <v>7.99701738357544</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.5261812210083</v>
       </c>
       <c r="G111" t="n">
-        <v>8.44661331176758</v>
+        <v>8.44661235809326</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G112" t="n">
-        <v>8.85837078094482</v>
+        <v>8.85837268829346</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325325012207</v>
+        <v>7.72325372695923</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808338165283</v>
+        <v>7.96808195114136</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.80230236053467</v>
       </c>
       <c r="G120" t="n">
-        <v>8.69144248962402</v>
+        <v>8.69144153594971</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.8851375579834</v>
       </c>
       <c r="G122" t="n">
-        <v>8.76489067077637</v>
+        <v>8.76488971710205</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G123" t="n">
-        <v>9.007493019104</v>
+        <v>9.00749397277832</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.05933570861816</v>
+        <v>8.05933666229248</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.5919361114502</v>
+        <v>7.59193563461304</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78557395935059</v>
+        <v>7.78557348251343</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.86349010467529</v>
       </c>
       <c r="G127" t="n">
-        <v>7.85902261734009</v>
+        <v>7.85902214050293</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.60650730133057</v>
       </c>
       <c r="G130" t="n">
-        <v>8.51783657073975</v>
+        <v>8.51783561706543</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G132" t="n">
-        <v>7.82341146469116</v>
+        <v>7.82341051101685</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.71147441864014</v>
+        <v>8.71147346496582</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420352935791</v>
+        <v>9.03420257568359</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G138" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>10.3771362304688</v>
       </c>
       <c r="G139" t="n">
-        <v>9.20113182067871</v>
+        <v>9.20113277435303</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>10.5679111480713</v>
       </c>
       <c r="G140" t="n">
-        <v>9.37028789520264</v>
+        <v>9.37028694152832</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G141" t="n">
-        <v>9.55947208404541</v>
+        <v>9.55947303771973</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>10.8590927124023</v>
       </c>
       <c r="G143" t="n">
-        <v>9.62846946716309</v>
+        <v>9.6284704208374</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G144" t="n">
-        <v>9.68856525421143</v>
+        <v>9.68856430053711</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G149" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.37807941436768</v>
       </c>
       <c r="G153" t="n">
-        <v>8.31529426574707</v>
+        <v>8.31529521942139</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.5222864151001</v>
+        <v>8.52228736877441</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>10.3269319534302</v>
       </c>
       <c r="G159" t="n">
-        <v>9.15661716461182</v>
+        <v>9.15661811828613</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G160" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>10.4449110031128</v>
       </c>
       <c r="G165" t="n">
-        <v>9.26122570037842</v>
+        <v>9.26122665405273</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G169" t="n">
-        <v>9.08094310760498</v>
+        <v>9.0809440612793</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548778533936</v>
+        <v>9.14548873901367</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G176" t="n">
-        <v>9.2078104019165</v>
+        <v>9.20780944824219</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G177" t="n">
-        <v>9.23451805114746</v>
+        <v>9.23451900482178</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G178" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G179" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G182" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.95887660980225</v>
       </c>
       <c r="G183" t="n">
-        <v>7.94359874725342</v>
+        <v>7.94359827041626</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.79225063323975</v>
+        <v>7.79224967956543</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.90365314483643</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89463376998901</v>
+        <v>7.89463329315186</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.28771305084229</v>
       </c>
       <c r="G188" t="n">
-        <v>8.23516845703125</v>
+        <v>8.23516941070557</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G193" t="n">
-        <v>8.38429164886475</v>
+        <v>8.38429260253906</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G197" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.77217960357666</v>
       </c>
       <c r="G198" t="n">
-        <v>8.66473293304443</v>
+        <v>8.66473388671875</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.063362121582</v>
       </c>
       <c r="G200" t="n">
-        <v>8.92291736602783</v>
+        <v>8.92291641235352</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>10.1662797927856</v>
       </c>
       <c r="G202" t="n">
-        <v>9.0141716003418</v>
+        <v>9.01417064666748</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G203" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10.3696060180664</v>
       </c>
       <c r="G204" t="n">
-        <v>9.19445610046387</v>
+        <v>9.19445514678955</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G207" t="n">
-        <v>9.68856525421143</v>
+        <v>9.68856430053711</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>10.9519701004028</v>
       </c>
       <c r="G208" t="n">
-        <v>9.71082210540771</v>
+        <v>9.71082305908203</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.9193382263184</v>
       </c>
       <c r="G209" t="n">
-        <v>9.68188762664795</v>
+        <v>9.68188858032227</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G210" t="n">
-        <v>9.31464290618896</v>
+        <v>9.31464385986328</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.92781162261963</v>
       </c>
       <c r="G212" t="n">
-        <v>8.8027286529541</v>
+        <v>8.80272769927979</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.22244834899902</v>
       </c>
       <c r="G216" t="n">
-        <v>8.17730140686035</v>
+        <v>8.17730045318604</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G219" t="n">
-        <v>8.38429164886475</v>
+        <v>8.38429260253906</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G224" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.2240142822266</v>
       </c>
       <c r="G225" t="n">
-        <v>9.06536293029785</v>
+        <v>9.06536388397217</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.2215042114258</v>
       </c>
       <c r="G231" t="n">
-        <v>9.06313800811768</v>
+        <v>9.06313705444336</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G233" t="n">
-        <v>8.92514324188232</v>
+        <v>8.92514228820801</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G234" t="n">
-        <v>8.70034408569336</v>
+        <v>8.70034503936768</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.6457271575928</v>
       </c>
       <c r="G236" t="n">
-        <v>9.439284324646</v>
+        <v>9.43928527832031</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.9695415496826</v>
       </c>
       <c r="G237" t="n">
-        <v>9.72640228271484</v>
+        <v>9.72640323638916</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>11.484130859375</v>
       </c>
       <c r="G240" t="n">
-        <v>10.182674407959</v>
+        <v>10.1826753616333</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.8230066299438</v>
       </c>
       <c r="G245" t="n">
-        <v>10.4831476211548</v>
+        <v>10.4831466674805</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.9309453964233</v>
       </c>
       <c r="G247" t="n">
-        <v>10.5788536071777</v>
+        <v>10.5788545608521</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>12.2748422622681</v>
       </c>
       <c r="G248" t="n">
-        <v>10.8837785720825</v>
+        <v>10.8837776184082</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>12.8019819259644</v>
       </c>
       <c r="G250" t="n">
-        <v>11.3511791229248</v>
+        <v>11.3511781692505</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G251" t="n">
-        <v>10.9883871078491</v>
+        <v>10.9883861541748</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>13.0906553268433</v>
       </c>
       <c r="G254" t="n">
-        <v>11.6071376800537</v>
+        <v>11.607138633728</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>13.2287149429321</v>
       </c>
       <c r="G255" t="n">
-        <v>11.7295513153076</v>
+        <v>11.7295522689819</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076099395752</v>
+        <v>11.9076108932495</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>13.9817733764648</v>
       </c>
       <c r="G260" t="n">
-        <v>12.3972692489624</v>
+        <v>12.3972682952881</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>13.1032047271729</v>
       </c>
       <c r="G265" t="n">
-        <v>11.6182661056519</v>
+        <v>11.6182651519775</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>12.8647365570068</v>
       </c>
       <c r="G267" t="n">
-        <v>11.4068212509155</v>
+        <v>11.4068222045898</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>12.2999439239502</v>
       </c>
       <c r="G268" t="n">
-        <v>10.9060344696045</v>
+        <v>10.9060354232788</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.5635137557983</v>
       </c>
       <c r="G269" t="n">
-        <v>11.1397342681885</v>
+        <v>11.1397352218628</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>12.6011667251587</v>
       </c>
       <c r="G272" t="n">
-        <v>11.1731204986572</v>
+        <v>11.1731214523315</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>12.4455347061157</v>
       </c>
       <c r="G273" t="n">
-        <v>11.0351257324219</v>
+        <v>11.0351266860962</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.5007591247559</v>
       </c>
       <c r="G274" t="n">
-        <v>11.0840921401978</v>
+        <v>11.0840930938721</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>13.3040208816528</v>
       </c>
       <c r="G275" t="n">
-        <v>11.7963228225708</v>
+        <v>11.7963237762451</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>13.1283073425293</v>
       </c>
       <c r="G276" t="n">
-        <v>11.6405220031738</v>
+        <v>11.6405229568481</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G280" t="n">
-        <v>10.5276622772217</v>
+        <v>10.5276613235474</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G281" t="n">
-        <v>10.2383193969727</v>
+        <v>10.2383184432983</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.707537651062</v>
       </c>
       <c r="G287" t="n">
-        <v>10.3807640075684</v>
+        <v>10.3807649612427</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>11.3310089111328</v>
       </c>
       <c r="G296" t="n">
-        <v>10.0469064712524</v>
+        <v>10.0469055175781</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.6632976531982</v>
       </c>
       <c r="G301" t="n">
-        <v>9.45486354827881</v>
+        <v>9.45486450195312</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10.4675025939941</v>
       </c>
       <c r="G304" t="n">
-        <v>9.28125858306885</v>
+        <v>9.28125762939453</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10.158748626709</v>
       </c>
       <c r="G306" t="n">
-        <v>9.007493019104</v>
+        <v>9.00749397277832</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10.1386680603027</v>
       </c>
       <c r="G307" t="n">
-        <v>8.98968887329102</v>
+        <v>8.9896879196167</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520614624023</v>
+        <v>8.96520709991455</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10.218994140625</v>
       </c>
       <c r="G310" t="n">
-        <v>9.06091117858887</v>
+        <v>9.06091213226318</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.3244218826294</v>
       </c>
       <c r="G311" t="n">
-        <v>9.15439224243164</v>
+        <v>9.15439128875732</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G313" t="n">
-        <v>9.01639747619629</v>
+        <v>9.01639652252197</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10.1562385559082</v>
       </c>
       <c r="G317" t="n">
-        <v>9.00526809692383</v>
+        <v>9.00526714324951</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>10.6808700561523</v>
       </c>
       <c r="G322" t="n">
-        <v>9.47044467926025</v>
+        <v>9.47044563293457</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77981948852539</v>
+        <v>9.77981853485107</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G324" t="n">
-        <v>9.49047470092773</v>
+        <v>9.49047565460205</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G325" t="n">
-        <v>9.51050853729248</v>
+        <v>9.51050758361816</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>10.2691984176636</v>
       </c>
       <c r="G331" t="n">
-        <v>9.10542678833008</v>
+        <v>9.10542583465576</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G342" t="n">
-        <v>8.85837078094482</v>
+        <v>8.85837268829346</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G344" t="n">
-        <v>8.87840175628662</v>
+        <v>8.87840270996094</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G346" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10.0131578445435</v>
       </c>
       <c r="G347" t="n">
-        <v>8.87840175628662</v>
+        <v>8.87840270996094</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10.003116607666</v>
       </c>
       <c r="G349" t="n">
-        <v>8.86949920654297</v>
+        <v>8.86949825286865</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G353" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G355" t="n">
-        <v>8.86282253265381</v>
+        <v>8.86282348632812</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G357" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.36301803588867</v>
       </c>
       <c r="G359" t="n">
-        <v>8.30194091796875</v>
+        <v>8.30193996429443</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G362" t="n">
-        <v>8.0348539352417</v>
+        <v>8.03485488891602</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.99033880233765</v>
+        <v>7.9903392791748</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G366" t="n">
-        <v>7.66093349456787</v>
+        <v>7.66093397140503</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215675354004</v>
+        <v>7.73215627670288</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G368" t="n">
-        <v>7.69209337234497</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.0868968963623</v>
       </c>
       <c r="G370" t="n">
-        <v>8.0571117401123</v>
+        <v>8.05711078643799</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>8.88106060028076</v>
       </c>
       <c r="G372" t="n">
-        <v>7.8746018409729</v>
+        <v>7.87460136413574</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G373" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>8.27861499786377</v>
       </c>
       <c r="G375" t="n">
-        <v>7.34042930603027</v>
+        <v>7.34042882919312</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G376" t="n">
-        <v>7.19798278808594</v>
+        <v>7.1979832649231</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.13302421569824</v>
       </c>
       <c r="G377" t="n">
-        <v>7.21133708953857</v>
+        <v>7.21133661270142</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817197799683</v>
+        <v>7.31817245483398</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G383" t="n">
-        <v>7.23804569244385</v>
+        <v>7.23804521560669</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>8.11796283721924</v>
       </c>
       <c r="G384" t="n">
-        <v>7.19798278808594</v>
+        <v>7.1979832649231</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055463790894</v>
+        <v>7.42055511474609</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.68024635314941</v>
       </c>
       <c r="G386" t="n">
-        <v>7.69654560089111</v>
+        <v>7.69654512405396</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.44428825378418</v>
       </c>
       <c r="G387" t="n">
-        <v>7.48732662200928</v>
+        <v>7.48732709884644</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390941619873</v>
+        <v>7.43390846252441</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G392" t="n">
-        <v>7.67873859405518</v>
+        <v>7.67873811721802</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G393" t="n">
-        <v>7.7455096244812</v>
+        <v>7.74551010131836</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.85679626464844</v>
+        <v>7.8567967414856</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>8.52461433410645</v>
       </c>
       <c r="G397" t="n">
-        <v>7.55854940414429</v>
+        <v>7.5585503578186</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.514573097229</v>
       </c>
       <c r="G398" t="n">
-        <v>7.54964637756348</v>
+        <v>7.54964685440063</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842359542847</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G400" t="n">
-        <v>7.61196660995483</v>
+        <v>7.61196708679199</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>8.6953067779541</v>
       </c>
       <c r="G404" t="n">
-        <v>7.70989847183228</v>
+        <v>7.70989894866943</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G405" t="n">
-        <v>7.70099592208862</v>
+        <v>7.70099496841431</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G406" t="n">
-        <v>7.69209337234497</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757871627808</v>
+        <v>7.64757919311523</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G408" t="n">
-        <v>7.58525800704956</v>
+        <v>7.5852575302124</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428731918335</v>
+        <v>7.67428636550903</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.5748176574707</v>
       </c>
       <c r="G411" t="n">
-        <v>7.60306406021118</v>
+        <v>7.60306453704834</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G413" t="n">
-        <v>7.5051326751709</v>
+        <v>7.50513172149658</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249744415283</v>
+        <v>7.24249792098999</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701162338257</v>
+        <v>7.28701210021973</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.15812587738037</v>
       </c>
       <c r="G417" t="n">
-        <v>7.23359394073486</v>
+        <v>7.23359441757202</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G418" t="n">
-        <v>7.30036640167236</v>
+        <v>7.30036592483521</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>7.68621015548706</v>
       </c>
       <c r="G424" t="n">
-        <v>6.81515884399414</v>
+        <v>6.8151593208313</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.93979930877686</v>
+        <v>6.9397988319397</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.76151514053345</v>
       </c>
       <c r="G429" t="n">
-        <v>6.88192987442017</v>
+        <v>6.88193035125732</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G431" t="n">
-        <v>7.30036640167236</v>
+        <v>7.30036592483521</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591464996338</v>
+        <v>7.29591369628906</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.42922687530518</v>
       </c>
       <c r="G438" t="n">
-        <v>7.47397184371948</v>
+        <v>7.47397232055664</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G439" t="n">
-        <v>7.58525800704956</v>
+        <v>7.5852575302124</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G440" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.66538381576538</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>8.68526554107666</v>
       </c>
       <c r="G442" t="n">
-        <v>7.70099592208862</v>
+        <v>7.70099496841431</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.10195827484131</v>
       </c>
       <c r="G445" t="n">
-        <v>8.07046604156494</v>
+        <v>8.07046508789062</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692255020142</v>
+        <v>7.93692302703857</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504264831543</v>
+        <v>8.15504360198975</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G462" t="n">
-        <v>7.38939523696899</v>
+        <v>7.38939476013184</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.4294581413269</v>
+        <v>7.42945766448975</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G464" t="n">
-        <v>7.23804569244385</v>
+        <v>7.23804521560669</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.7143497467041</v>
+        <v>7.71435022354126</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.66538381576538</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G468" t="n">
-        <v>7.64312744140625</v>
+        <v>7.64312648773193</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479198455811</v>
+        <v>7.99479103088379</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>9.53371143341064</v>
       </c>
       <c r="G471" t="n">
-        <v>8.45328903198242</v>
+        <v>8.45328998565674</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.63914012908936</v>
       </c>
       <c r="G472" t="n">
-        <v>8.54677104949951</v>
+        <v>8.5467700958252</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G476" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G480" t="n">
-        <v>7.78557395935059</v>
+        <v>7.78557348251343</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757871627808</v>
+        <v>7.64757919311523</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G482" t="n">
-        <v>7.62532234191895</v>
+        <v>7.62532186508179</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G483" t="n">
-        <v>7.62532234191895</v>
+        <v>7.62532186508179</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G484" t="n">
-        <v>7.69209337234497</v>
+        <v>7.69209384918213</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576267242432</v>
+        <v>7.90576314926147</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344148635864</v>
+        <v>7.84344244003296</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G490" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G491" t="n">
-        <v>7.7455096244812</v>
+        <v>7.74551010131836</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>8.46436882019043</v>
       </c>
       <c r="G492" t="n">
-        <v>7.5051326751709</v>
+        <v>7.50513172149658</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>8.6200008392334</v>
       </c>
       <c r="G493" t="n">
-        <v>7.64312744140625</v>
+        <v>7.64312648773193</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G495" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>8.60996055603027</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63422393798828</v>
+        <v>7.63422441482544</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G501" t="n">
-        <v>7.58971071243286</v>
+        <v>7.5897102355957</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G507" t="n">
-        <v>8.27968311309814</v>
+        <v>8.27968406677246</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>9.34795665740967</v>
       </c>
       <c r="G508" t="n">
-        <v>8.2885856628418</v>
+        <v>8.28858661651611</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.55379295349121</v>
       </c>
       <c r="G511" t="n">
-        <v>8.47109508514404</v>
+        <v>8.47109603881836</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.50670623779297</v>
+        <v>8.50670719146729</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.5022554397583</v>
+        <v>8.50225639343262</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>10.1763210296631</v>
       </c>
       <c r="G520" t="n">
-        <v>9.02307415008545</v>
+        <v>9.02307510375977</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G527" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G528" t="n">
-        <v>9.16551971435547</v>
+        <v>9.16552066802979</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G529" t="n">
-        <v>9.04087924957275</v>
+        <v>9.04088020324707</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G530" t="n">
-        <v>9.04087924957275</v>
+        <v>9.04088020324707</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833980560303</v>
+        <v>8.83833885192871</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>9.30277442932129</v>
       </c>
       <c r="G535" t="n">
-        <v>8.24852466583252</v>
+        <v>8.2485237121582</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>8.82332706451416</v>
       </c>
       <c r="G537" t="n">
-        <v>7.82341146469116</v>
+        <v>7.82341051101685</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G538" t="n">
-        <v>8.0348539352417</v>
+        <v>8.03485488891602</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G540" t="n">
-        <v>7.61196660995483</v>
+        <v>7.61196708679199</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519510269165</v>
+        <v>7.54519557952881</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>8.4543285369873</v>
       </c>
       <c r="G543" t="n">
-        <v>7.49622917175293</v>
+        <v>7.49622964859009</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G545" t="n">
-        <v>7.66093349456787</v>
+        <v>7.66093397140503</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.7143497467041</v>
+        <v>7.71435022354126</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G548" t="n">
-        <v>7.60083866119385</v>
+        <v>7.60083913803101</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.76331663131714</v>
+        <v>7.76331615447998</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983604431152</v>
+        <v>7.66983556747437</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G553" t="n">
-        <v>7.50068044662476</v>
+        <v>7.50068092346191</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.5229377746582</v>
+        <v>7.52293825149536</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368877410889</v>
+        <v>7.29368829727173</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G556" t="n">
-        <v>7.30036640167236</v>
+        <v>7.30036592483521</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G557" t="n">
-        <v>7.50068044662476</v>
+        <v>7.50068092346191</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.7566385269165</v>
+        <v>7.75663900375366</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>8.32379913330078</v>
       </c>
       <c r="G563" t="n">
-        <v>7.38049221038818</v>
+        <v>7.38049268722534</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.31124782562256</v>
       </c>
       <c r="G564" t="n">
-        <v>7.36936330795288</v>
+        <v>7.36936378479004</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613386154175</v>
+        <v>7.43613481521606</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585174560547</v>
+        <v>7.25585079193115</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>8.43173694610596</v>
       </c>
       <c r="G568" t="n">
-        <v>7.47619819641113</v>
+        <v>7.47619771957397</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744762420654</v>
+        <v>6.85744714736938</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G586" t="n">
-        <v>7.48064947128296</v>
+        <v>7.4806489944458</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842359542847</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610336303711</v>
+        <v>7.41610383987427</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G589" t="n">
-        <v>7.48064947128296</v>
+        <v>7.4806489944458</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766778945923</v>
+        <v>6.99766731262207</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443977355957</v>
+        <v>7.06443881988525</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>7.92969799041748</v>
       </c>
       <c r="G596" t="n">
-        <v>7.03105306625366</v>
+        <v>7.03105354309082</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.06022834777832</v>
       </c>
       <c r="G599" t="n">
-        <v>7.14679145812988</v>
+        <v>7.14679098129272</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G601" t="n">
-        <v>7.38939523696899</v>
+        <v>7.38939476013184</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G602" t="n">
-        <v>7.56745290756226</v>
+        <v>7.5674524307251</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.55222606658936</v>
       </c>
       <c r="G603" t="n">
-        <v>7.58303260803223</v>
+        <v>7.58303213119507</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>8.79822540283203</v>
       </c>
       <c r="G613" t="n">
-        <v>7.80115413665771</v>
+        <v>7.80115365982056</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>9.42326259613037</v>
       </c>
       <c r="G619" t="n">
-        <v>8.3553581237793</v>
+        <v>8.35535717010498</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.31783485412598</v>
       </c>
       <c r="G620" t="n">
-        <v>8.26187705993652</v>
+        <v>8.26187801361084</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G621" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>9.47848701477051</v>
       </c>
       <c r="G625" t="n">
-        <v>8.40432453155518</v>
+        <v>8.40432357788086</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>9.36552906036377</v>
       </c>
       <c r="G630" t="n">
-        <v>8.30416679382324</v>
+        <v>8.30416774749756</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G636" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.86254692077637</v>
       </c>
       <c r="G639" t="n">
-        <v>8.74485969543457</v>
+        <v>8.74485874176025</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G640" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.71147441864014</v>
+        <v>8.71147346496582</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G644" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009822845459</v>
+        <v>9.25009727478027</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>10.0608520507812</v>
       </c>
       <c r="G649" t="n">
-        <v>8.92069053649902</v>
+        <v>8.92069149017334</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G650" t="n">
-        <v>9.01639747619629</v>
+        <v>9.01639652252197</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G651" t="n">
-        <v>9.0564603805542</v>
+        <v>9.05646133422852</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100601196289</v>
+        <v>9.12100505828857</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G654" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G660" t="n">
-        <v>9.84659099578857</v>
+        <v>9.84659194946289</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G661" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>11.2331123352051</v>
       </c>
       <c r="G666" t="n">
-        <v>9.96010398864746</v>
+        <v>9.96010303497314</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G667" t="n">
-        <v>9.87107467651367</v>
+        <v>9.87107372283936</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>11.200478553772</v>
       </c>
       <c r="G668" t="n">
-        <v>9.93116855621338</v>
+        <v>9.93116760253906</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>11.4414577484131</v>
       </c>
       <c r="G670" t="n">
-        <v>10.1448373794556</v>
+        <v>10.1448383331299</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G671" t="n">
-        <v>9.80652809143066</v>
+        <v>9.80652904510498</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>11.6046199798584</v>
       </c>
       <c r="G676" t="n">
-        <v>10.2895088195801</v>
+        <v>10.2895097732544</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>11.700008392334</v>
       </c>
       <c r="G683" t="n">
-        <v>10.3740873336792</v>
+        <v>10.3740882873535</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G684" t="n">
-        <v>10.3340244293213</v>
+        <v>10.334023475647</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>11.5017032623291</v>
       </c>
       <c r="G688" t="n">
-        <v>10.1982555389404</v>
+        <v>10.1982564926147</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>11.9259252548218</v>
       </c>
       <c r="G689" t="n">
-        <v>10.5744028091431</v>
+        <v>10.5744018554688</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>11.328498840332</v>
       </c>
       <c r="G690" t="n">
-        <v>10.0446805953979</v>
+        <v>10.0446796417236</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>12.0489253997803</v>
       </c>
       <c r="G692" t="n">
-        <v>10.6834630966187</v>
+        <v>10.683464050293</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G693" t="n">
-        <v>10.8259086608887</v>
+        <v>10.8259077072144</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.756911277771</v>
+        <v>10.7569122314453</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>12.4580860137939</v>
       </c>
       <c r="G697" t="n">
-        <v>11.0462560653687</v>
+        <v>11.0462551116943</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>13.1232872009277</v>
       </c>
       <c r="G698" t="n">
-        <v>11.6360712051392</v>
+        <v>11.6360721588135</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>13.2086343765259</v>
       </c>
       <c r="G699" t="n">
-        <v>11.7117462158203</v>
+        <v>11.7117471694946</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>13.6303462982178</v>
       </c>
       <c r="G705" t="n">
-        <v>12.0856676101685</v>
+        <v>12.0856685638428</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>12.7618188858032</v>
       </c>
       <c r="G709" t="n">
-        <v>11.3155670166016</v>
+        <v>11.3155679702759</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395774841309</v>
+        <v>11.0395784378052</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>12.7015752792358</v>
       </c>
       <c r="G713" t="n">
-        <v>11.262149810791</v>
+        <v>11.2621507644653</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>12.3325757980347</v>
       </c>
       <c r="G714" t="n">
-        <v>10.9349689483643</v>
+        <v>10.9349699020386</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>11.8004150390625</v>
       </c>
       <c r="G715" t="n">
-        <v>10.4631156921387</v>
+        <v>10.463116645813</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364080429077</v>
+        <v>10.4364070892334</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G719" t="n">
-        <v>10.549919128418</v>
+        <v>10.5499200820923</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>11.7025184631348</v>
       </c>
       <c r="G727" t="n">
-        <v>10.3763132095337</v>
+        <v>10.376314163208</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G728" t="n">
-        <v>10.160418510437</v>
+        <v>10.1604175567627</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>11.1377248764038</v>
       </c>
       <c r="G732" t="n">
-        <v>9.87552547454834</v>
+        <v>9.87552642822266</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>10.6607875823975</v>
       </c>
       <c r="G734" t="n">
-        <v>9.45263862609863</v>
+        <v>9.45263767242432</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G736" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G737" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081153869629</v>
+        <v>8.29081249237061</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889585494995</v>
+        <v>7.77889537811279</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219253540039</v>
+        <v>8.46219158172607</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G744" t="n">
-        <v>8.45774173736572</v>
+        <v>8.45774078369141</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.65922069549561</v>
       </c>
       <c r="G745" t="n">
-        <v>8.5645751953125</v>
+        <v>8.56457614898682</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>9.69938373565674</v>
       </c>
       <c r="G746" t="n">
-        <v>8.60018730163574</v>
+        <v>8.60018634796143</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G749" t="n">
-        <v>8.74708557128906</v>
+        <v>8.74708461761475</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G750" t="n">
-        <v>8.18842887878418</v>
+        <v>8.1884298324585</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>9.75209808349609</v>
       </c>
       <c r="G751" t="n">
-        <v>8.64692687988281</v>
+        <v>8.64692783355713</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G752" t="n">
-        <v>8.25520038604736</v>
+        <v>8.25519943237305</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G754" t="n">
-        <v>8.29526329040527</v>
+        <v>8.29526424407959</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>8.92624473571777</v>
       </c>
       <c r="G755" t="n">
-        <v>7.91466522216797</v>
+        <v>7.91466569900513</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>8.81077575683594</v>
       </c>
       <c r="G756" t="n">
-        <v>7.81228160858154</v>
+        <v>7.81228256225586</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G757" t="n">
-        <v>7.30036640167236</v>
+        <v>7.30036592483521</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>8.25602340698242</v>
       </c>
       <c r="G758" t="n">
-        <v>7.32039737701416</v>
+        <v>7.32039785385132</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>8.17318725585938</v>
       </c>
       <c r="G760" t="n">
-        <v>7.24694871902466</v>
+        <v>7.24694919586182</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873378753662</v>
+        <v>6.96873331069946</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>8.19577884674072</v>
       </c>
       <c r="G763" t="n">
-        <v>7.26698064804077</v>
+        <v>7.26698017120361</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>8.23343181610107</v>
       </c>
       <c r="G764" t="n">
-        <v>7.30036640167236</v>
+        <v>7.30036592483521</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576267242432</v>
+        <v>7.90576314926147</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>9.12957000732422</v>
       </c>
       <c r="G767" t="n">
-        <v>8.09494781494141</v>
+        <v>8.09494876861572</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>9.31030368804932</v>
       </c>
       <c r="G772" t="n">
-        <v>8.25520038604736</v>
+        <v>8.25519943237305</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G778" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G779" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>9.99558734893799</v>
       </c>
       <c r="G782" t="n">
-        <v>8.86282253265381</v>
+        <v>8.86282348632812</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>10.1763210296631</v>
       </c>
       <c r="G784" t="n">
-        <v>9.02307415008545</v>
+        <v>9.02307510375977</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>10.2817487716675</v>
       </c>
       <c r="G786" t="n">
-        <v>9.11655521392822</v>
+        <v>9.11655426025391</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>10.3445043563843</v>
       </c>
       <c r="G787" t="n">
-        <v>9.17219829559326</v>
+        <v>9.17219924926758</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G788" t="n">
-        <v>9.22561454772949</v>
+        <v>9.22561550140381</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>10.2415857315063</v>
       </c>
       <c r="G795" t="n">
-        <v>9.08094310760498</v>
+        <v>9.0809440612793</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G796" t="n">
-        <v>9.4370584487915</v>
+        <v>9.43705940246582</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>10.7963380813599</v>
       </c>
       <c r="G797" t="n">
-        <v>9.57282733917236</v>
+        <v>9.57282638549805</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G799" t="n">
-        <v>9.41480255126953</v>
+        <v>9.41480159759521</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G804" t="n">
-        <v>9.69746780395508</v>
+        <v>9.69746875762939</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>11.4590291976929</v>
       </c>
       <c r="G805" t="n">
-        <v>10.160418510437</v>
+        <v>10.1604175567627</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232891082764</v>
+        <v>9.96232986450195</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496046066284</v>
+        <v>10.3496036529541</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>11.8882722854614</v>
       </c>
       <c r="G809" t="n">
-        <v>10.5410165786743</v>
+        <v>10.541015625</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G812" t="n">
-        <v>10.5276622772217</v>
+        <v>10.5276613235474</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>12.1091690063477</v>
       </c>
       <c r="G816" t="n">
-        <v>10.7368793487549</v>
+        <v>10.7368803024292</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>12.2145967483521</v>
       </c>
       <c r="G817" t="n">
-        <v>10.8303604125977</v>
+        <v>10.8303594589233</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G819" t="n">
-        <v>10.9883871078491</v>
+        <v>10.9883861541748</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G820" t="n">
-        <v>10.8259086608887</v>
+        <v>10.8259077072144</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>11.5368452072144</v>
       </c>
       <c r="G822" t="n">
-        <v>10.2294158935547</v>
+        <v>10.2294149398804</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G825" t="n">
-        <v>10.3340244293213</v>
+        <v>10.334023475647</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>11.8355579376221</v>
       </c>
       <c r="G826" t="n">
-        <v>10.4942770004272</v>
+        <v>10.4942760467529</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>12.1116790771484</v>
       </c>
       <c r="G827" t="n">
-        <v>10.7391061782837</v>
+        <v>10.7391052246094</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>12.4856977462769</v>
       </c>
       <c r="G831" t="n">
-        <v>11.0707368850708</v>
+        <v>11.0707378387451</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295736312866</v>
+        <v>10.3295726776123</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>11.7150688171387</v>
       </c>
       <c r="G840" t="n">
-        <v>10.3874425888062</v>
+        <v>10.3874416351318</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>12.0564546585083</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6901397705078</v>
+        <v>10.6901388168335</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G842" t="n">
-        <v>10.549919128418</v>
+        <v>10.5499200820923</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G845" t="n">
-        <v>10.2383193969727</v>
+        <v>10.2383184432983</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>10.836501121521</v>
       </c>
       <c r="G849" t="n">
-        <v>9.60843849182129</v>
+        <v>9.60843944549561</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G851" t="n">
-        <v>9.33912658691406</v>
+        <v>9.33912754058838</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>10.203932762146</v>
       </c>
       <c r="G854" t="n">
-        <v>9.04755783081055</v>
+        <v>9.04755687713623</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>10.5177068710327</v>
       </c>
       <c r="G855" t="n">
-        <v>9.32577228546143</v>
+        <v>9.32577323913574</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>10.5101757049561</v>
       </c>
       <c r="G860" t="n">
-        <v>9.31909561157227</v>
+        <v>9.31909465789795</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G861" t="n">
-        <v>9.25232315063477</v>
+        <v>9.25232410430908</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>10.582971572876</v>
       </c>
       <c r="G873" t="n">
-        <v>9.38364028930664</v>
+        <v>9.38364124298096</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>10.768726348877</v>
       </c>
       <c r="G874" t="n">
-        <v>9.5483455657959</v>
+        <v>9.54834461212158</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395671844482</v>
+        <v>9.58395576477051</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G876" t="n">
-        <v>9.23451805114746</v>
+        <v>9.23451900482178</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>10.5327682495117</v>
       </c>
       <c r="G877" t="n">
-        <v>9.33912658691406</v>
+        <v>9.33912754058838</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G880" t="n">
-        <v>9.55947208404541</v>
+        <v>9.55947303771973</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G881" t="n">
-        <v>9.60621452331543</v>
+        <v>9.60621356964111</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>11.0699491500854</v>
       </c>
       <c r="G883" t="n">
-        <v>9.81543064117432</v>
+        <v>9.81543159484863</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079208374023</v>
+        <v>9.69079113006592</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G885" t="n">
-        <v>9.49047470092773</v>
+        <v>9.49047565460205</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.0498676300049</v>
       </c>
       <c r="G887" t="n">
-        <v>9.79762554168701</v>
+        <v>9.79762649536133</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>10.9820928573608</v>
       </c>
       <c r="G888" t="n">
-        <v>9.7375316619873</v>
+        <v>9.73753070831299</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G890" t="n">
-        <v>9.69746780395508</v>
+        <v>9.69746875762939</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>11.2130298614502</v>
       </c>
       <c r="G894" t="n">
-        <v>9.94229793548584</v>
+        <v>9.94229698181152</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>11.3987846374512</v>
       </c>
       <c r="G898" t="n">
-        <v>10.1070013046265</v>
+        <v>10.1070003509521</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>11.2381324768066</v>
       </c>
       <c r="G899" t="n">
-        <v>9.96455383300781</v>
+        <v>9.96455478668213</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>11.4715795516968</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1715459823608</v>
+        <v>10.1715469360352</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>11.0423374176025</v>
       </c>
       <c r="G905" t="n">
-        <v>9.79094886779785</v>
+        <v>9.79094791412354</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794006347656</v>
+        <v>9.99794101715088</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>11.1829080581665</v>
       </c>
       <c r="G912" t="n">
-        <v>9.91558933258057</v>
+        <v>9.91558837890625</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>10.7411136627197</v>
       </c>
       <c r="G913" t="n">
-        <v>9.52386093139648</v>
+        <v>9.5238618850708</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>10.3846673965454</v>
       </c>
       <c r="G914" t="n">
-        <v>9.2078104019165</v>
+        <v>9.20780944824219</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G916" t="n">
-        <v>8.92514324188232</v>
+        <v>8.92514228820801</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G919" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G920" t="n">
-        <v>9.14771461486816</v>
+        <v>9.14771556854248</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>10.4474220275879</v>
       </c>
       <c r="G925" t="n">
-        <v>9.26345252990723</v>
+        <v>9.26345348358154</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G926" t="n">
-        <v>9.31464290618896</v>
+        <v>9.31464385986328</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>10.6181154251099</v>
       </c>
       <c r="G929" t="n">
-        <v>9.41480255126953</v>
+        <v>9.41480159759521</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>10.9067869186401</v>
       </c>
       <c r="G933" t="n">
-        <v>9.67076015472412</v>
+        <v>9.6707592010498</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>10.643217086792</v>
       </c>
       <c r="G934" t="n">
-        <v>9.4370584487915</v>
+        <v>9.43705940246582</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G937" t="n">
-        <v>9.80652809143066</v>
+        <v>9.80652904510498</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136770248413</v>
+        <v>10.1136779785156</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403856277466</v>
+        <v>10.1403865814209</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230537414551</v>
+        <v>10.4230527877808</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>11.1854181289673</v>
       </c>
       <c r="G945" t="n">
-        <v>9.91781425476074</v>
+        <v>9.91781520843506</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>11.1327037811279</v>
       </c>
       <c r="G946" t="n">
-        <v>9.87107467651367</v>
+        <v>9.87107372283936</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>11.105092048645</v>
       </c>
       <c r="G947" t="n">
-        <v>9.84659099578857</v>
+        <v>9.84659194946289</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.881685256958</v>
       </c>
       <c r="G948" t="n">
-        <v>9.64850234985352</v>
+        <v>9.64850330352783</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>10.7862977981567</v>
       </c>
       <c r="G949" t="n">
-        <v>9.56392574310303</v>
+        <v>9.56392478942871</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>10.4524421691895</v>
       </c>
       <c r="G951" t="n">
-        <v>9.26790332794189</v>
+        <v>9.26790428161621</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>10.4499320983887</v>
       </c>
       <c r="G952" t="n">
-        <v>9.26567935943604</v>
+        <v>9.26567840576172</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>10.0683822631836</v>
       </c>
       <c r="G955" t="n">
-        <v>8.9273681640625</v>
+        <v>8.92736721038818</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G958" t="n">
-        <v>9.16551971435547</v>
+        <v>9.16552066802979</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>10.1612596511841</v>
       </c>
       <c r="G960" t="n">
-        <v>9.00972080230713</v>
+        <v>9.00971984863281</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G962" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G964" t="n">
-        <v>9.30351543426514</v>
+        <v>9.30351448059082</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>10.8942356109619</v>
       </c>
       <c r="G973" t="n">
-        <v>9.65963172912598</v>
+        <v>9.65962982177734</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G974" t="n">
-        <v>9.51050853729248</v>
+        <v>9.51050758361816</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G978" t="n">
-        <v>9.60621452331543</v>
+        <v>9.60621356964111</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>11.2306022644043</v>
       </c>
       <c r="G981" t="n">
-        <v>9.95787906646729</v>
+        <v>9.95787715911865</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>11.0573978424072</v>
       </c>
       <c r="G983" t="n">
-        <v>9.80430126190186</v>
+        <v>9.80430221557617</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>10.7536649703979</v>
       </c>
       <c r="G988" t="n">
-        <v>9.53498935699463</v>
+        <v>9.53499031066895</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812492370605</v>
+        <v>9.40812397003174</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>10.7536649703979</v>
       </c>
       <c r="G992" t="n">
-        <v>9.53498935699463</v>
+        <v>9.53499031066895</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>10.7135019302368</v>
       </c>
       <c r="G996" t="n">
-        <v>9.4993782043457</v>
+        <v>9.49937915802002</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G997" t="n">
-        <v>9.23674297332764</v>
+        <v>9.23674392700195</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G999" t="n">
-        <v>9.0564603805542</v>
+        <v>9.05646133422852</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>10.4348707199097</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.25232315063477</v>
+        <v>9.25232410430908</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>10.582971572876</v>
       </c>
       <c r="G1006" t="n">
-        <v>9.38364028930664</v>
+        <v>9.38364124298096</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>10.934398651123</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.6952428817749</v>
+        <v>9.69524192810059</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>11.0925407409668</v>
       </c>
       <c r="G1017" t="n">
-        <v>9.83546352386475</v>
+        <v>9.83546257019043</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>11.1678466796875</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.90223407745361</v>
+        <v>9.90223503112793</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>11.120153427124</v>
       </c>
       <c r="G1023" t="n">
-        <v>9.85994529724121</v>
+        <v>9.85994625091553</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>11.1126232147217</v>
       </c>
       <c r="G1029" t="n">
-        <v>9.85326957702637</v>
+        <v>9.85326862335205</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>9.38309955596924</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.31974601745605</v>
+        <v>8.31974697113037</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>9.75962924957275</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.65360546112061</v>
+        <v>8.65360450744629</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.68031311035156</v>
+        <v>8.68031406402588</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>9.51613998413086</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.43770885467529</v>
+        <v>8.43770980834961</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>9.55630302429199</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.47332096099854</v>
+        <v>8.47332191467285</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>9.41573238372803</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.34868049621582</v>
+        <v>8.34868144989014</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754821777344</v>
+        <v>7.62754726409912</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.60083866119385</v>
+        <v>7.60083913803101</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585174560547</v>
+        <v>7.25585079193115</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.70832443237305</v>
+        <v>6.70832395553589</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.9500036239624</v>
+        <v>4.95000410079956</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>5.5826678276062</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.9500036239624</v>
+        <v>4.95000410079956</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>4.89613008499146</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.34126853942871</v>
+        <v>4.34126901626587</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>5.16848611831665</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.58275938034058</v>
+        <v>4.58275985717773</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>5.16346597671509</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.57830858230591</v>
+        <v>4.57830905914307</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342130661011</v>
+        <v>5.00342178344727</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.8899097442627</v>
+        <v>4.88990926742554</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>5.85627889633179</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.19260740280151</v>
+        <v>5.19260787963867</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>5.9014630317688</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.23267078399658</v>
+        <v>5.23267126083374</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.29276561737061</v>
+        <v>5.29276514053345</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>5.47473001480103</v>
       </c>
       <c r="G1089" t="n">
-        <v>4.85429811477661</v>
+        <v>4.85429859161377</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>5.28395509719849</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.68514347076416</v>
+        <v>4.685142993927</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041393280029</v>
+        <v>5.21041345596313</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>5.79101419448853</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.13473892211914</v>
+        <v>5.1347393989563</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470794677734</v>
+        <v>5.11470699310303</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>5.80858516693115</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15031909942627</v>
+        <v>5.15031862258911</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.92329549789429</v>
+        <v>4.92329597473145</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>5.57513809204102</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.9433274269104</v>
+        <v>4.94332695007324</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.79800081253052</v>
+        <v>4.79800033569336</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>5.46217918395996</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.865074634552</v>
+        <v>4.86507511138916</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>5.30905723571777</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.72869110107422</v>
+        <v>4.72869157791138</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>5.79854488372803</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.16466999053955</v>
+        <v>5.16467046737671</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>6.46876621246338</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.76162576675415</v>
+        <v>5.76162528991699</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>6.59176588058472</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.87117910385132</v>
+        <v>5.87117958068848</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>6.41354179382324</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.71243762969971</v>
+        <v>5.71243810653687</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>5.99182987213135</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.33682584762573</v>
+        <v>5.33682632446289</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>5.98680877685547</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.3323540687561</v>
+        <v>5.33235359191895</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.0841817855835</v>
+        <v>5.08418226242065</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>5.61530113220215</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.00145816802979</v>
+        <v>5.00145769119263</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.97686338424683</v>
+        <v>4.97686290740967</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>5.68558597564697</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.06405973434448</v>
+        <v>5.06405925750732</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>5.27642488479614</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.69962596893311</v>
+        <v>4.69962644577026</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>5.28897619247437</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.71080541610718</v>
+        <v>4.71080589294434</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>5.36679220199585</v>
       </c>
       <c r="G1152" t="n">
-        <v>4.78011465072632</v>
+        <v>4.78011512756348</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.47724008560181</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.87848949432373</v>
+        <v>4.87848901748657</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>4.92123222351074</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.38326215744019</v>
+        <v>4.38326168060303</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.57357120513916</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.07360553741455</v>
+        <v>4.07360601425171</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.96892595291138</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.42574214935303</v>
+        <v>4.42574167251587</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1174" t="n">
-        <v>4.34189987182617</v>
+        <v>4.34190034866333</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.66895818710327</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.15856552124023</v>
+        <v>4.15856599807739</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.50579500198364</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.01323843002319</v>
+        <v>4.01323890686035</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.39032697677612</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.91039347648621</v>
+        <v>3.91039323806763</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.29242897033691</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.82319736480713</v>
+        <v>3.82319688796997</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>4.19327592849731</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.73488283157349</v>
+        <v>3.73488306999207</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.07906293869019</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.63315534591675</v>
+        <v>3.63315558433533</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.22465419769287</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.76283097267151</v>
+        <v>3.76283121109009</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.56321811676025</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.17370080947876</v>
+        <v>3.17370057106018</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.86444091796875</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.4419949054718</v>
+        <v>3.44199514389038</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>3.79415607452393</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.3793933391571</v>
+        <v>3.37939357757568</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>3.65609502792358</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.25642466545105</v>
+        <v>3.25642490386963</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>3.59585094451904</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.20276641845703</v>
+        <v>3.20276618003845</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>3.62597298622131</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.22959566116333</v>
+        <v>3.22959542274475</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.68496203422546</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.28213620185852</v>
+        <v>3.28213596343994</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>3.78411507606506</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.37045001983643</v>
+        <v>3.370450258255</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.6940598487854</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.18092346191406</v>
+        <v>4.1809229850769</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>4.89487504959106</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.35978651046753</v>
+        <v>4.35978603363037</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.27706241607666</v>
+        <v>4.2770619392395</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.47157573699951</v>
+        <v>4.47157526016235</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>5.42201614379883</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.8293023109436</v>
+        <v>4.82930183410645</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>5.30654716491699</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.72645568847656</v>
+        <v>4.72645616531372</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>5.1333441734314</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.5721869468689</v>
+        <v>4.57218647003174</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.62584495544434</v>
+        <v>4.62584447860718</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>5.35675096511841</v>
       </c>
       <c r="G1254" t="n">
-        <v>4.77117109298706</v>
+        <v>4.77117156982422</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>5.37683200836182</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.78905773162842</v>
+        <v>4.78905725479126</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1259" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>5.46719884872437</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.86954593658447</v>
+        <v>4.86954545974731</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.86060285568237</v>
+        <v>4.86060237884521</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>5.82364702224731</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.18702840805054</v>
+        <v>5.18702793121338</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>6.17256307601929</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.49780178070068</v>
+        <v>5.49780225753784</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>6.10729789733887</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.43967151641846</v>
+        <v>5.4396710395813</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>6.08721685409546</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.42178583145142</v>
+        <v>5.42178535461426</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>6.00689077377319</v>
       </c>
       <c r="G1279" t="n">
-        <v>5.35024070739746</v>
+        <v>5.3502402305603</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.85878896713257</v>
       </c>
       <c r="G1282" t="n">
-        <v>5.21832895278931</v>
+        <v>5.21832847595215</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>5.34169006347656</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.75775718688965</v>
+        <v>4.75775671005249</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>5.59019899368286</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.9790997505188</v>
+        <v>4.97910022735596</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>5.98178911209106</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.32788276672363</v>
+        <v>5.32788324356079</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>6.55160188674927</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.83540630340576</v>
+        <v>5.8354058265686</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>6.3457670211792</v>
       </c>
       <c r="G1303" t="n">
-        <v>5.65207195281982</v>
+        <v>5.65207242965698</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>6.35078716278076</v>
       </c>
       <c r="G1304" t="n">
-        <v>5.65654373168945</v>
+        <v>5.65654325485229</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>6.40852212905884</v>
       </c>
       <c r="G1305" t="n">
-        <v>5.70796728134155</v>
+        <v>5.70796680450439</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>6.63192892074585</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.90695142745972</v>
+        <v>5.90695190429688</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>6.00940084457397</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.35247659683228</v>
+        <v>5.35247611999512</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>5.70817804336548</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.0841817855835</v>
+        <v>5.08418226242065</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1312" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>5.91652393341064</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.26975250244141</v>
+        <v>5.26975202560425</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>6.07215595245361</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.40837097167969</v>
+        <v>5.40837144851685</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>6.07717609405518</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.41284275054932</v>
+        <v>5.41284227371216</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>6.12486982345581</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.45532274246216</v>
+        <v>5.455322265625</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>5.97174787521362</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.31893920898438</v>
+        <v>5.31893968582153</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>5.96923780441284</v>
       </c>
       <c r="G1324" t="n">
-        <v>5.31670379638672</v>
+        <v>5.31670331954956</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>5.69060611724854</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.06853055953979</v>
+        <v>5.06853103637695</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>5.87887096405029</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.23621559143066</v>
+        <v>5.23621511459351</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>5.83870792388916</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.20044231414795</v>
+        <v>5.20044279098511</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.97686338424683</v>
+        <v>4.97686290740967</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.94556283950806</v>
+        <v>4.94556331634521</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.87855911254883</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.34525346755981</v>
+        <v>4.34525394439697</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.82333517074585</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.29606676101685</v>
+        <v>4.29606628417969</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>5.06054782867432</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.50734806060791</v>
+        <v>4.50734853744507</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.69068288803101</v>
+        <v>4.69068336486816</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>5.1383638381958</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.57665729522705</v>
+        <v>4.57665777206421</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>5.12832307815552</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.56771421432495</v>
+        <v>4.56771469116211</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>5.11828184127808</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.55877065658569</v>
+        <v>4.55877113342285</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>5.3793420791626</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.79129266738892</v>
+        <v>4.79129314422607</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>5.43205690383911</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.8382453918457</v>
+        <v>4.83824491500854</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>5.56760692596436</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.95897769927979</v>
+        <v>4.95897722244263</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1390" t="n">
-        <v>4.72422027587891</v>
+        <v>4.72421979904175</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>5.30403709411621</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.72422027587891</v>
+        <v>4.72421979904175</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>5.29901599884033</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.71974754333496</v>
+        <v>4.71974802017212</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1396" t="n">
-        <v>4.56324338912964</v>
+        <v>4.56324291229248</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>5.22873115539551</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.65714597702026</v>
+        <v>4.65714645385742</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>5.21868991851807</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.64820241928101</v>
+        <v>4.64820289611816</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.90617084503174</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.3698468208313</v>
+        <v>4.36984729766846</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.97143602371216</v>
       </c>
       <c r="G1403" t="n">
-        <v>4.42797756195068</v>
+        <v>4.42797803878784</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>4.88483476638794</v>
       </c>
       <c r="G1405" t="n">
-        <v>4.35084295272827</v>
+        <v>4.35084342956543</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.90240621566772</v>
       </c>
       <c r="G1407" t="n">
-        <v>4.36649417877197</v>
+        <v>4.36649370193481</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.75681495666504</v>
       </c>
       <c r="G1411" t="n">
-        <v>4.23681783676147</v>
+        <v>4.23681831359863</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1417" t="n">
-        <v>4.5297064781189</v>
+        <v>4.52970600128174</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>4.91119194030762</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.37431955337524</v>
+        <v>4.37431907653809</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.92499780654907</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.38661575317383</v>
+        <v>4.38661623001099</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>5.12330293655396</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.56324338912964</v>
+        <v>4.56324291229248</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>5.16597604751587</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.60125160217285</v>
+        <v>4.60125112533569</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>4.98147678375244</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.43692064285278</v>
+        <v>4.43692111968994</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>4.80199813842773</v>
       </c>
       <c r="G1433" t="n">
-        <v>4.27706241607666</v>
+        <v>4.2770619392395</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>5.02038478851318</v>
       </c>
       <c r="G1436" t="n">
-        <v>4.47157573699951</v>
+        <v>4.47157526016235</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>4.96139478683472</v>
       </c>
       <c r="G1443" t="n">
-        <v>4.41903400421143</v>
+        <v>4.41903448104858</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>5.01662015914917</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.46822214126587</v>
+        <v>4.46822261810303</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>5.19358777999878</v>
       </c>
       <c r="G1449" t="n">
-        <v>4.62584495544434</v>
+        <v>4.62584447860718</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>5.0856499671936</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.5297064781189</v>
+        <v>4.52970600128174</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.99151802062988</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.4458646774292</v>
+        <v>4.44586420059204</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>4.91244697570801</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.37543725967407</v>
+        <v>4.37543678283691</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>5.07058906555176</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.51629161834717</v>
+        <v>4.51629209518433</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>5.55003595352173</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.9433274269104</v>
+        <v>4.94332695007324</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>5.26638412475586</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.69068288803101</v>
+        <v>4.69068336486816</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>5.3868727684021</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.79800081253052</v>
+        <v>4.79800033569336</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1470" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.91202640533447</v>
+        <v>4.91202592849731</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>5.55756616592407</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.95003461837769</v>
+        <v>4.95003414154053</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>5.55254602432251</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.94556283950806</v>
+        <v>4.94556331634521</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.87353897094727</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.3407826423645</v>
+        <v>4.34078216552734</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.81203889846802</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.28600549697876</v>
+        <v>4.2860050201416</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.87479400634766</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.34189987182617</v>
+        <v>4.34190034866333</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.39220523834229</v>
+        <v>4.39220476150513</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>4.46563196182251</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.97746610641479</v>
+        <v>3.97746634483337</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>4.50328493118286</v>
       </c>
       <c r="G1504" t="n">
-        <v>4.0110034942627</v>
+        <v>4.01100301742554</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>4.42170381546021</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.93834018707275</v>
+        <v>3.93833994865417</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>4.59365177154541</v>
       </c>
       <c r="G1509" t="n">
-        <v>4.09149169921875</v>
+        <v>4.09149122238159</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>4.56729507446289</v>
       </c>
       <c r="G1511" t="n">
-        <v>4.06801605224609</v>
+        <v>4.06801557540894</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>4.41040802001953</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.92827916145325</v>
+        <v>3.92827892303467</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>4.4455509185791</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.95958018302917</v>
+        <v>3.95958042144775</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>4.37275505065918</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.89474248886108</v>
+        <v>3.89474201202393</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.55097913742065</v>
       </c>
       <c r="G1522" t="n">
-        <v>4.05348348617554</v>
+        <v>4.0534839630127</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>4.78317213058472</v>
       </c>
       <c r="G1527" t="n">
-        <v>4.26029443740845</v>
+        <v>4.26029396057129</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>4.91495704650879</v>
       </c>
       <c r="G1531" t="n">
-        <v>4.37767267227173</v>
+        <v>4.37767314910889</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.03042602539062</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.48051929473877</v>
+        <v>4.48051881790161</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>4.93127298355103</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.39220523834229</v>
+        <v>4.39220476150513</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>5.01410913467407</v>
       </c>
       <c r="G1541" t="n">
-        <v>4.46598625183105</v>
+        <v>4.4659857749939</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>2.99591493606567</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.66841292381287</v>
+        <v>2.66841316223145</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>3.02854704856873</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.69747805595398</v>
+        <v>2.6974778175354</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>2.8616189956665</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.54879784584045</v>
+        <v>2.54879760742188</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.56221222877502</v>
+        <v>2.5622124671936</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.51521301269531</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.24025964736938</v>
+        <v>2.24025940895081</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>2.56165099143982</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.28162121772766</v>
+        <v>2.28162097930908</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.56792688369751</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.28721117973328</v>
+        <v>2.2872109413147</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>2.37715196609497</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.11729097366333</v>
+        <v>2.11729073524475</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.58047795295715</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.29838991165161</v>
+        <v>2.29839015007019</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>2.46450710296631</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.19509673118591</v>
+        <v>2.19509649276733</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>2.67335510253906</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.38111400604248</v>
+        <v>2.38111424446106</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>2.86287403106689</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.54991555213928</v>
+        <v>2.54991579055786</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>2.87667989730835</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.56221222877502</v>
+        <v>2.5622124671936</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>2.93943500518799</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.61810731887817</v>
+        <v>2.61810708045959</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>2.87919092178345</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.564448595047</v>
+        <v>2.56444883346558</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>2.84404802322388</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.53314781188965</v>
+        <v>2.53314757347107</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>2.77878308296204</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.47501730918884</v>
+        <v>2.47501707077026</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>2.80262994766235</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.49625730514526</v>
+        <v>2.49625706672668</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>2.79384398460388</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.48843169212341</v>
+        <v>2.48843145370483</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>2.75744605064392</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.45601272583008</v>
+        <v>2.4560124874115</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.43700885772705</v>
+        <v>2.43700909614563</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.84028291702271</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.52979397773743</v>
+        <v>2.52979421615601</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>2.92437410354614</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.6046929359436</v>
+        <v>2.60469269752502</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.73610997200012</v>
       </c>
       <c r="G1605" t="n">
-        <v>2.43700885772705</v>
+        <v>2.43700909614563</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.48509001731873</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.21342945098877</v>
+        <v>2.21342968940735</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>2.53780388832092</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.26038098335266</v>
+        <v>2.26038074493408</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>2.68841600418091</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.39452886581421</v>
+        <v>2.39452862739563</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>2.90680289268494</v>
       </c>
       <c r="G1620" t="n">
-        <v>2.58904242515564</v>
+        <v>2.58904218673706</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>2.97517991065979</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.6499445438385</v>
+        <v>2.64994478225708</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>2.72426104545593</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.42645525932312</v>
+        <v>2.4264554977417</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>2.37423992156982</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.11469721794128</v>
+        <v>2.11469697952271</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>1.96649694442749</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.75152707099915</v>
+        <v>1.75152695178986</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>2.01657509803772</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.79613077640533</v>
+        <v>1.79613089561462</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>2.21557092666626</v>
       </c>
       <c r="G1646" t="n">
-        <v>1.97337329387665</v>
+        <v>1.97337317466736</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>1.73798203468323</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.54799246788025</v>
+        <v>1.54799258708954</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.59776198863983</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.42310070991516</v>
+        <v>1.42310082912445</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>1.24932205677032</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.11275100708008</v>
+        <v>1.11275088787079</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98913478851318</v>
+        <v>2.98913502693176</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.73594284057617</v>
+        <v>1.73594272136688</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.985986948013306</v>
+        <v>0.98598700761795</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.04209995269775</v>
+        <v>1.04210007190704</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.730360686779022</v>
+        <v>0.730360746383667</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>0.71340000629425</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.635413825511932</v>
+        <v>0.635413885116577</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.659106075763702</v>
+        <v>0.659106016159058</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.692061364650726</v>
+        <v>0.692061305046082</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.751737177371979</v>
+        <v>0.751737117767334</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>0.833599984645844</v>
       </c>
       <c r="G1677" t="n">
-        <v>0.74247407913208</v>
+        <v>0.742474019527435</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>0.821799993515015</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.731963992118835</v>
+        <v>0.731963932514191</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>0.762199997901917</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.678879261016846</v>
+        <v>0.678879201412201</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>0.716400027275085</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.638085901737213</v>
+        <v>0.638085961341858</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>0.674600005149841</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.60085529088974</v>
+        <v>0.600855350494385</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>0.697399973869324</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.621162891387939</v>
+        <v>0.621162831783295</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>0.683200001716614</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.608515202999115</v>
+        <v>0.60851514339447</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>0.662199974060059</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.589810848236084</v>
+        <v>0.589810788631439</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>0.64300000667572</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.572709739208221</v>
+        <v>0.572709679603577</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.540645062923431</v>
+        <v>0.540645122528076</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>0.584800004959106</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.520871937274933</v>
+        <v>0.520871877670288</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>0.59280002117157</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.527997374534607</v>
+        <v>0.527997434139252</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>0.597199976444244</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.531916320323944</v>
+        <v>0.531916379928589</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>0.637600004673004</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.567900002002716</v>
+        <v>0.567900061607361</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>0.72759997844696</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.648061513900757</v>
+        <v>0.648061573505402</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.620806694030762</v>
+        <v>0.620806634426117</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.658215343952179</v>
+        <v>0.658215403556824</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>0.758199989795685</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.675316452980042</v>
+        <v>0.675316512584686</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>0.828599989414215</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.738020598888397</v>
+        <v>0.738020658493042</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>0.958599984645844</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.853809535503387</v>
+        <v>0.853809475898743</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.8764328956604</v>
+        <v>0.876432955265045</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.87376081943512</v>
+        <v>0.873760879039764</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.882667660713196</v>
+        <v>0.882667720317841</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.919185698032379</v>
+        <v>0.919185638427734</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.957485198974609</v>
+        <v>0.957485139369965</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>1.09650003910065</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.976634860038757</v>
+        <v>0.976634919643402</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>1.03250002861023</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.919631063938141</v>
+        <v>0.919631123542786</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.921857714653015</v>
+        <v>0.92185777425766</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>1.04649996757507</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.932100653648376</v>
+        <v>0.932100594043732</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.926311135292053</v>
+        <v>0.926311194896698</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>1.04750001430511</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.93299126625061</v>
+        <v>0.932991325855255</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.912950873374939</v>
+        <v>0.912950932979584</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>1.01950001716614</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.908052146434784</v>
+        <v>0.908052206039429</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>1.04449999332428</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.93031919002533</v>
+        <v>0.930319249629974</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>1.00650000572205</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.896473228931427</v>
+        <v>0.896473288536072</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.04949998855591</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.934772729873657</v>
+        <v>0.934772670269012</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>1.10950005054474</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.988213777542114</v>
+        <v>0.988213717937469</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.977970957756042</v>
+        <v>0.977970898151398</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>1.12750005722046</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.00424599647522</v>
+        <v>1.00424611568451</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.05456960201263</v>
+        <v>1.05456972122192</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>1.31149995326996</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.16813182830811</v>
+        <v>1.16813170909882</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.25141072273254</v>
+        <v>1.25141084194183</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.2309250831604</v>
+        <v>1.23092496395111</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.21845555305481</v>
+        <v>1.21845543384552</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.25586414337158</v>
+        <v>1.25586426258087</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>1.40299999713898</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.24962949752808</v>
+        <v>1.24962937831879</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.3146493434906</v>
+        <v>1.31464922428131</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.35116744041443</v>
+        <v>1.35116732120514</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>1.53450000286102</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.36675429344177</v>
+        <v>1.36675441265106</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.31643068790436</v>
+        <v>1.31643080711365</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.35749995708466</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.20910334587097</v>
+        <v>1.20910322666168</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>1.26549994945526</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.12716031074524</v>
+        <v>1.12716042995453</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>1.14049994945526</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.01582491397858</v>
+        <v>1.01582479476929</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>1.23450005054474</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.09954929351807</v>
+        <v>1.09954917430878</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.32550001144409</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.18060147762299</v>
+        <v>1.1806013584137</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.14007532596588</v>
+        <v>1.14007520675659</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>1.38300001621246</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23181581497192</v>
+        <v>1.23181569576263</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>1.25049996376038</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.11380004882812</v>
+        <v>1.11380016803741</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.15076351165771</v>
+        <v>1.150763630867</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.13473129272461</v>
+        <v>1.13473117351532</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.12048017978668</v>
+        <v>1.12048029899597</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.15788900852203</v>
+        <v>1.15788888931274</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>1.25750005245209</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.1200350522995</v>
+        <v>1.12003493309021</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.12226164340973</v>
+        <v>1.12226152420044</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.07416474819183</v>
+        <v>1.07416462898254</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.13473129272461</v>
+        <v>1.13473117351532</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>1.25450003147125</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.11736297607422</v>
+        <v>1.11736285686493</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.08663427829742</v>
+        <v>1.08663439750671</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>1.16250002384186</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.03541994094849</v>
+        <v>1.03542006015778</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.04833495616913</v>
+        <v>1.04833483695984</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.07772743701935</v>
+        <v>1.07772755622864</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.30039846897125</v>
+        <v>1.30039834976196</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.3110865354538</v>
+        <v>1.31108665466309</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.32266557216644</v>
+        <v>1.32266545295715</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>1.43949997425079</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.28213942050934</v>
+        <v>1.28213930130005</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>1.43250000476837</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.27590453624725</v>
+        <v>1.27590465545654</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.30039846897125</v>
+        <v>1.30039834976196</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.328009724617</v>
+        <v>1.32800960540771</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1928" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.3182121515274</v>
+        <v>1.31821203231812</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1930" t="n">
-        <v>1.29683566093445</v>
+        <v>1.29683554172516</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.29327285289764</v>
+        <v>1.29327297210693</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.25586414337158</v>
+        <v>1.25586426258087</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1935" t="n">
-        <v>1.24339461326599</v>
+        <v>1.24339473247528</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.30485188961029</v>
+        <v>1.304851770401</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.33869779109955</v>
+        <v>1.33869791030884</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.32266557216644</v>
+        <v>1.32266545295715</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1951" t="n">
-        <v>1.4019364118576</v>
+        <v>1.40193629264832</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>1.49100005626678</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.328009724617</v>
+        <v>1.32800960540771</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.37566113471985</v>
+        <v>1.37566125392914</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.41975009441376</v>
+        <v>1.41974997520447</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>1.60950005054474</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.43355572223663</v>
+        <v>1.43355560302734</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.40104568004608</v>
+        <v>1.40104556083679</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>1.46249997615814</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.30262517929077</v>
+        <v>1.30262506008148</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.27679538726807</v>
+        <v>1.27679526805878</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.29683566093445</v>
+        <v>1.29683554172516</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>1.41849994659424</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.26343500614166</v>
+        <v>1.26343488693237</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>1.5275000333786</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.36051964759827</v>
+        <v>1.36051952838898</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52031,7 +52031,7 @@
         <v>1.54449999332428</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.37566113471985</v>
+        <v>1.37566125392914</v>
       </c>
       <c r="H1987" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.29015564918518</v>
+        <v>1.29015552997589</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.41449999809265</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.25987231731415</v>
+        <v>1.25987219810486</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.23626923561096</v>
+        <v>1.23626911640167</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.23805046081543</v>
+        <v>1.23805058002472</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G2007" t="n">
-        <v>1.26031756401062</v>
+        <v>1.26031768321991</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>1.44749999046326</v>
       </c>
       <c r="G2012" t="n">
-        <v>1.28926479816437</v>
+        <v>1.28926491737366</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.31019592285156</v>
+        <v>1.31019580364227</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>1.46150004863739</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.30173444747925</v>
+        <v>1.30173456668854</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.24784803390503</v>
+        <v>1.24784815311432</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G2023" t="n">
-        <v>1.24784803390503</v>
+        <v>1.24784815311432</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.22647166252136</v>
+        <v>1.22647154331207</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>1.42050004005432</v>
       </c>
       <c r="G2029" t="n">
-        <v>1.26521635055542</v>
+        <v>1.26521646976471</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.29015564918518</v>
+        <v>1.29015552997589</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>1.44649994373322</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.28837406635284</v>
+        <v>1.28837418556213</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>1.48300004005432</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.3208841085434</v>
+        <v>1.32088422775269</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.30930531024933</v>
+        <v>1.30930519104004</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>1.4889999628067</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.32622814178467</v>
+        <v>1.32622826099396</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>1.50650000572205</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.34181523323059</v>
+        <v>1.3418151140213</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.27679538726807</v>
+        <v>1.27679526805878</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.31643068790436</v>
+        <v>1.31643080711365</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G2055" t="n">
-        <v>1.34315121173859</v>
+        <v>1.34315133094788</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -54189,7 +54189,7 @@
         <v>1.375</v>
       </c>
       <c r="G2070" t="n">
-        <v>1.22469019889832</v>
+        <v>1.2246903181076</v>
       </c>
       <c r="H2070" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>1.38100004196167</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.23003435134888</v>
+        <v>1.23003447055817</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.32979094982147</v>
+        <v>1.32979106903076</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>1.82149994373322</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.6223806142807</v>
+        <v>1.62238049507141</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.72347319126129</v>
+        <v>1.723473072052</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>1.97650003433228</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.76043665409088</v>
+        <v>1.76043653488159</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.87488961219788</v>
+        <v>1.87488949298859</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.88112413883209</v>
+        <v>1.88112425804138</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>2.08699989318848</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.85885715484619</v>
+        <v>1.8588570356369</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.91318881511688</v>
+        <v>1.91318893432617</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -55047,7 +55047,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.98889696598053</v>
+        <v>1.98889708518982</v>
       </c>
       <c r="H2103" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2104" t="n">
-        <v>2.00760126113892</v>
+        <v>2.0076014995575</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G2105" t="n">
-        <v>2.00849199295044</v>
+        <v>2.00849223136902</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.06994915008545</v>
+        <v>2.06994891166687</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>2.3970000743866</v>
       </c>
       <c r="G2109" t="n">
-        <v>2.13496923446655</v>
+        <v>2.13496899604797</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2110" t="n">
-        <v>2.08419990539551</v>
+        <v>2.08420014381409</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.99513185024261</v>
+        <v>1.99513173103333</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.94258141517639</v>
+        <v>1.94258153438568</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.97197389602661</v>
+        <v>1.9719740152359</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.9523788690567</v>
+        <v>1.95237898826599</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2123" t="n">
-        <v>1.94080007076263</v>
+        <v>1.94079983234406</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55645,7 +55645,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G2126" t="n">
-        <v>1.91318881511688</v>
+        <v>1.91318893432617</v>
       </c>
       <c r="H2126" t="s">
         <v>8</v>
@@ -55697,7 +55697,7 @@
         <v>2.13100004196167</v>
       </c>
       <c r="G2128" t="n">
-        <v>1.8980473279953</v>
+        <v>1.89804720878601</v>
       </c>
       <c r="H2128" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G2131" t="n">
-        <v>1.97019255161285</v>
+        <v>1.97019267082214</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G2132" t="n">
-        <v>2.02541494369507</v>
+        <v>2.02541518211365</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -55853,7 +55853,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2134" t="n">
-        <v>2.11359286308289</v>
+        <v>2.11359262466431</v>
       </c>
       <c r="H2134" t="s">
         <v>8</v>
@@ -55957,7 +55957,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2138" t="n">
-        <v>2.12160897254944</v>
+        <v>2.12160873413086</v>
       </c>
       <c r="H2138" t="s">
         <v>8</v>
@@ -55983,7 +55983,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G2139" t="n">
-        <v>2.11359286308289</v>
+        <v>2.11359262466431</v>
       </c>
       <c r="H2139" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2141" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56087,7 +56087,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G2143" t="n">
-        <v>1.98889696598053</v>
+        <v>1.98889708518982</v>
       </c>
       <c r="H2143" t="s">
         <v>8</v>
@@ -56139,7 +56139,7 @@
         <v>2.15300011634827</v>
       </c>
       <c r="G2145" t="n">
-        <v>1.91764235496521</v>
+        <v>1.9176424741745</v>
       </c>
       <c r="H2145" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.9203143119812</v>
+        <v>1.92031419277191</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.93367457389832</v>
+        <v>1.9336746931076</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.83926212787628</v>
+        <v>1.83926224708557</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.86152911186218</v>
+        <v>1.86152923107147</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56399,7 +56399,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2155" t="n">
-        <v>1.86152911186218</v>
+        <v>1.86152923107147</v>
       </c>
       <c r="H2155" t="s">
         <v>8</v>
@@ -56425,7 +56425,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2156" t="n">
-        <v>1.89626574516296</v>
+        <v>1.89626586437225</v>
       </c>
       <c r="H2156" t="s">
         <v>8</v>
@@ -56451,7 +56451,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2157" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2157" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>2.15899991989136</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.92298626899719</v>
+        <v>1.92298638820648</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56503,7 +56503,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.99245965480804</v>
+        <v>1.99245977401733</v>
       </c>
       <c r="H2159" t="s">
         <v>8</v>
@@ -56607,7 +56607,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G2163" t="n">
-        <v>2.1358597278595</v>
+        <v>2.13585996627808</v>
       </c>
       <c r="H2163" t="s">
         <v>8</v>
@@ -56711,7 +56711,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2167" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2167" t="s">
         <v>8</v>
@@ -56789,7 +56789,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G2170" t="n">
-        <v>2.07351183891296</v>
+        <v>2.07351207733154</v>
       </c>
       <c r="H2170" t="s">
         <v>8</v>
@@ -56815,7 +56815,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2171" t="n">
-        <v>2.06371426582336</v>
+        <v>2.06371450424194</v>
       </c>
       <c r="H2171" t="s">
         <v>8</v>
@@ -56841,7 +56841,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G2172" t="n">
-        <v>2.09666991233826</v>
+        <v>2.09666967391968</v>
       </c>
       <c r="H2172" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2174" t="n">
-        <v>2.10913920402527</v>
+        <v>2.10913944244385</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G2175" t="n">
-        <v>2.12339043617249</v>
+        <v>2.12339019775391</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -56945,7 +56945,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G2176" t="n">
-        <v>2.14476656913757</v>
+        <v>2.14476680755615</v>
       </c>
       <c r="H2176" t="s">
         <v>8</v>
@@ -57023,7 +57023,7 @@
         <v>2.41899991035461</v>
       </c>
       <c r="G2179" t="n">
-        <v>2.15456390380859</v>
+        <v>2.15456414222717</v>
       </c>
       <c r="H2179" t="s">
         <v>8</v>
@@ -57075,7 +57075,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G2181" t="n">
-        <v>2.07083988189697</v>
+        <v>2.07084012031555</v>
       </c>
       <c r="H2181" t="s">
         <v>8</v>
@@ -57101,7 +57101,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G2182" t="n">
-        <v>1.98444354534149</v>
+        <v>1.9844434261322</v>
       </c>
       <c r="H2182" t="s">
         <v>8</v>
@@ -57153,7 +57153,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2184" t="n">
-        <v>1.9461442232132</v>
+        <v>1.94614410400391</v>
       </c>
       <c r="H2184" t="s">
         <v>8</v>
@@ -57179,7 +57179,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2185" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2185" t="s">
         <v>8</v>
@@ -57205,7 +57205,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G2186" t="n">
-        <v>1.94080007076263</v>
+        <v>1.94079983234406</v>
       </c>
       <c r="H2186" t="s">
         <v>8</v>
@@ -57309,7 +57309,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G2190" t="n">
-        <v>1.79294645786285</v>
+        <v>1.79294657707214</v>
       </c>
       <c r="H2190" t="s">
         <v>8</v>
@@ -57413,7 +57413,7 @@
         <v>1.98450005054474</v>
       </c>
       <c r="G2194" t="n">
-        <v>1.76756203174591</v>
+        <v>1.7675621509552</v>
       </c>
       <c r="H2194" t="s">
         <v>8</v>
@@ -57543,7 +57543,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G2199" t="n">
-        <v>1.84282493591309</v>
+        <v>1.8428248167038</v>
       </c>
       <c r="H2199" t="s">
         <v>8</v>
@@ -57621,7 +57621,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G2202" t="n">
-        <v>1.84549701213837</v>
+        <v>1.84549689292908</v>
       </c>
       <c r="H2202" t="s">
         <v>8</v>
@@ -57647,7 +57647,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G2203" t="n">
-        <v>1.81521379947662</v>
+        <v>1.81521368026733</v>
       </c>
       <c r="H2203" t="s">
         <v>8</v>
@@ -57725,7 +57725,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2206" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2206" t="s">
         <v>8</v>
@@ -57751,7 +57751,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2207" t="n">
-        <v>1.80185341835022</v>
+        <v>1.80185329914093</v>
       </c>
       <c r="H2207" t="s">
         <v>8</v>
@@ -57777,7 +57777,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2208" t="n">
-        <v>1.67448556423187</v>
+        <v>1.67448568344116</v>
       </c>
       <c r="H2208" t="s">
         <v>8</v>
@@ -57803,7 +57803,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G2209" t="n">
-        <v>1.71189427375793</v>
+        <v>1.71189439296722</v>
       </c>
       <c r="H2209" t="s">
         <v>8</v>
@@ -57907,7 +57907,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G2213" t="n">
-        <v>1.60055887699127</v>
+        <v>1.60055899620056</v>
       </c>
       <c r="H2213" t="s">
         <v>8</v>
@@ -57933,7 +57933,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G2214" t="n">
-        <v>1.6272794008255</v>
+        <v>1.62727928161621</v>
       </c>
       <c r="H2214" t="s">
         <v>8</v>
@@ -58193,7 +58193,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G2224" t="n">
-        <v>1.81343221664429</v>
+        <v>1.81343233585358</v>
       </c>
       <c r="H2224" t="s">
         <v>8</v>
@@ -58401,7 +58401,7 @@
         <v>2.05699992179871</v>
       </c>
       <c r="G2232" t="n">
-        <v>1.83213663101196</v>
+        <v>1.83213651180267</v>
       </c>
       <c r="H2232" t="s">
         <v>8</v>
@@ -58453,7 +58453,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2234" t="n">
-        <v>1.79027438163757</v>
+        <v>1.79027450084686</v>
       </c>
       <c r="H2234" t="s">
         <v>8</v>
@@ -58479,7 +58479,7 @@
         <v>2.02300000190735</v>
       </c>
       <c r="G2235" t="n">
-        <v>1.80185341835022</v>
+        <v>1.80185329914093</v>
       </c>
       <c r="H2235" t="s">
         <v>8</v>
@@ -58635,7 +58635,7 @@
         <v>1.99150002002716</v>
       </c>
       <c r="G2241" t="n">
-        <v>1.773796916008</v>
+        <v>1.77379679679871</v>
       </c>
       <c r="H2241" t="s">
         <v>8</v>
@@ -58687,7 +58687,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G2243" t="n">
-        <v>1.83926212787628</v>
+        <v>1.83926224708557</v>
       </c>
       <c r="H2243" t="s">
         <v>8</v>
@@ -58713,7 +58713,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G2244" t="n">
-        <v>1.80630695819855</v>
+        <v>1.80630683898926</v>
       </c>
       <c r="H2244" t="s">
         <v>8</v>
@@ -58739,7 +58739,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G2245" t="n">
-        <v>1.89003121852875</v>
+        <v>1.89003109931946</v>
       </c>
       <c r="H2245" t="s">
         <v>8</v>
@@ -58765,7 +58765,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G2246" t="n">
-        <v>1.94970679283142</v>
+        <v>1.94970667362213</v>
       </c>
       <c r="H2246" t="s">
         <v>8</v>
@@ -58817,7 +58817,7 @@
         <v>2.16300010681152</v>
       </c>
       <c r="G2248" t="n">
-        <v>1.92654919624329</v>
+        <v>1.92654931545258</v>
       </c>
       <c r="H2248" t="s">
         <v>8</v>
@@ -58843,7 +58843,7 @@
         <v>2.16700005531311</v>
       </c>
       <c r="G2249" t="n">
-        <v>1.93011200428009</v>
+        <v>1.9301118850708</v>
       </c>
       <c r="H2249" t="s">
         <v>8</v>
@@ -58869,7 +58869,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2250" t="n">
-        <v>1.94525361061096</v>
+        <v>1.94525349140167</v>
       </c>
       <c r="H2250" t="s">
         <v>8</v>
@@ -58895,7 +58895,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2251" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2251" t="s">
         <v>8</v>
@@ -58921,7 +58921,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G2252" t="n">
-        <v>1.97909939289093</v>
+        <v>1.97909951210022</v>
       </c>
       <c r="H2252" t="s">
         <v>8</v>
@@ -58973,7 +58973,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2254" t="n">
-        <v>2.00314784049988</v>
+        <v>2.00314807891846</v>
       </c>
       <c r="H2254" t="s">
         <v>8</v>
@@ -59025,7 +59025,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G2256" t="n">
-        <v>2.06994915008545</v>
+        <v>2.06994891166687</v>
       </c>
       <c r="H2256" t="s">
         <v>8</v>
@@ -59103,7 +59103,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2259" t="n">
-        <v>2.05302619934082</v>
+        <v>2.0530264377594</v>
       </c>
       <c r="H2259" t="s">
         <v>8</v>
@@ -59129,7 +59129,7 @@
         <v>2.31699991226196</v>
       </c>
       <c r="G2260" t="n">
-        <v>2.06371426582336</v>
+        <v>2.06371450424194</v>
       </c>
       <c r="H2260" t="s">
         <v>8</v>
@@ -59155,7 +59155,7 @@
         <v>2.33299994468689</v>
       </c>
       <c r="G2261" t="n">
-        <v>2.07796549797058</v>
+        <v>2.077965259552</v>
       </c>
       <c r="H2261" t="s">
         <v>8</v>
@@ -59181,7 +59181,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G2262" t="n">
-        <v>2.10913920402527</v>
+        <v>2.10913944244385</v>
       </c>
       <c r="H2262" t="s">
         <v>8</v>
@@ -59363,7 +59363,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G2269" t="n">
-        <v>2.16525220870972</v>
+        <v>2.1652524471283</v>
       </c>
       <c r="H2269" t="s">
         <v>8</v>
@@ -59493,7 +59493,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G2274" t="n">
-        <v>2.26768088340759</v>
+        <v>2.26768112182617</v>
       </c>
       <c r="H2274" t="s">
         <v>8</v>
@@ -59597,7 +59597,7 @@
         <v>2.48699998855591</v>
       </c>
       <c r="G2278" t="n">
-        <v>2.21513080596924</v>
+        <v>2.21513056755066</v>
       </c>
       <c r="H2278" t="s">
         <v>8</v>
@@ -59675,7 +59675,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G2281" t="n">
-        <v>2.29261994361877</v>
+        <v>2.29262018203735</v>
       </c>
       <c r="H2281" t="s">
         <v>8</v>
@@ -59701,7 +59701,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2282" t="n">
-        <v>2.31577801704407</v>
+        <v>2.31577777862549</v>
       </c>
       <c r="H2282" t="s">
         <v>8</v>
@@ -59779,7 +59779,7 @@
         <v>2.64299988746643</v>
       </c>
       <c r="G2285" t="n">
-        <v>2.35407733917236</v>
+        <v>2.35407710075378</v>
       </c>
       <c r="H2285" t="s">
         <v>8</v>
@@ -59857,7 +59857,7 @@
         <v>2.51099991798401</v>
       </c>
       <c r="G2288" t="n">
-        <v>2.23650693893433</v>
+        <v>2.23650717735291</v>
       </c>
       <c r="H2288" t="s">
         <v>8</v>
@@ -59883,7 +59883,7 @@
         <v>2.5090000629425</v>
       </c>
       <c r="G2289" t="n">
-        <v>2.23472595214844</v>
+        <v>2.23472571372986</v>
       </c>
       <c r="H2289" t="s">
         <v>8</v>
@@ -60039,7 +60039,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G2295" t="n">
-        <v>2.45294332504272</v>
+        <v>2.45294308662415</v>
       </c>
       <c r="H2295" t="s">
         <v>8</v>
@@ -60143,7 +60143,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G2299" t="n">
-        <v>2.31221508979797</v>
+        <v>2.31221532821655</v>
       </c>
       <c r="H2299" t="s">
         <v>8</v>
@@ -60195,7 +60195,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G2301" t="n">
-        <v>2.27658772468567</v>
+        <v>2.27658796310425</v>
       </c>
       <c r="H2301" t="s">
         <v>8</v>
@@ -60221,7 +60221,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G2302" t="n">
-        <v>2.25164866447449</v>
+        <v>2.25164890289307</v>
       </c>
       <c r="H2302" t="s">
         <v>8</v>
@@ -60247,7 +60247,7 @@
         <v>2.51300001144409</v>
       </c>
       <c r="G2303" t="n">
-        <v>2.23828840255737</v>
+        <v>2.23828864097595</v>
       </c>
       <c r="H2303" t="s">
         <v>8</v>
@@ -60299,7 +60299,7 @@
         <v>2.48300004005432</v>
       </c>
       <c r="G2305" t="n">
-        <v>2.21156787872314</v>
+        <v>2.21156811714172</v>
       </c>
       <c r="H2305" t="s">
         <v>8</v>
@@ -60325,7 +60325,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G2306" t="n">
-        <v>2.14832949638367</v>
+        <v>2.14832925796509</v>
       </c>
       <c r="H2306" t="s">
         <v>8</v>
@@ -60351,7 +60351,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G2307" t="n">
-        <v>2.12160897254944</v>
+        <v>2.12160873413086</v>
       </c>
       <c r="H2307" t="s">
         <v>8</v>
@@ -60559,7 +60559,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G2315" t="n">
-        <v>2.04411935806274</v>
+        <v>2.04411959648132</v>
       </c>
       <c r="H2315" t="s">
         <v>8</v>
@@ -60611,7 +60611,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G2317" t="n">
-        <v>2.04768228530884</v>
+        <v>2.04768204689026</v>
       </c>
       <c r="H2317" t="s">
         <v>8</v>
@@ -60741,7 +60741,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G2322" t="n">
-        <v>2.05658912658691</v>
+        <v>2.05658888816833</v>
       </c>
       <c r="H2322" t="s">
         <v>8</v>
@@ -60819,7 +60819,7 @@
         <v>2.28099989891052</v>
       </c>
       <c r="G2325" t="n">
-        <v>2.03164982795715</v>
+        <v>2.03164958953857</v>
       </c>
       <c r="H2325" t="s">
         <v>8</v>
@@ -60845,7 +60845,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G2326" t="n">
-        <v>2.0681676864624</v>
+        <v>2.06816792488098</v>
       </c>
       <c r="H2326" t="s">
         <v>8</v>
@@ -60923,7 +60923,7 @@
         <v>2.20300006866455</v>
       </c>
       <c r="G2329" t="n">
-        <v>1.9621764421463</v>
+        <v>1.96217656135559</v>
       </c>
       <c r="H2329" t="s">
         <v>8</v>
@@ -60949,7 +60949,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G2330" t="n">
-        <v>2.00314784049988</v>
+        <v>2.00314807891846</v>
       </c>
       <c r="H2330" t="s">
         <v>8</v>
@@ -61001,7 +61001,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G2332" t="n">
-        <v>1.91853296756744</v>
+        <v>1.91853308677673</v>
       </c>
       <c r="H2332" t="s">
         <v>8</v>
@@ -61053,7 +61053,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2334" t="n">
-        <v>1.80808806419373</v>
+        <v>1.80808818340302</v>
       </c>
       <c r="H2334" t="s">
         <v>8</v>
@@ -61183,7 +61183,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G2339" t="n">
-        <v>1.85440385341644</v>
+        <v>1.85440373420715</v>
       </c>
       <c r="H2339" t="s">
         <v>8</v>
@@ -61261,7 +61261,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G2342" t="n">
-        <v>1.89626574516296</v>
+        <v>1.89626586437225</v>
       </c>
       <c r="H2342" t="s">
         <v>8</v>
@@ -61287,7 +61287,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2343" t="n">
-        <v>1.93278396129608</v>
+        <v>1.93278384208679</v>
       </c>
       <c r="H2343" t="s">
         <v>8</v>
@@ -61313,7 +61313,7 @@
         <v>2.19700002670288</v>
       </c>
       <c r="G2344" t="n">
-        <v>1.95683228969574</v>
+        <v>1.95683240890503</v>
       </c>
       <c r="H2344" t="s">
         <v>8</v>
@@ -61391,7 +61391,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2347" t="n">
-        <v>1.96841132640839</v>
+        <v>1.9684112071991</v>
       </c>
       <c r="H2347" t="s">
         <v>8</v>
@@ -61417,7 +61417,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G2348" t="n">
-        <v>1.94525361061096</v>
+        <v>1.94525349140167</v>
       </c>
       <c r="H2348" t="s">
         <v>8</v>
@@ -61469,7 +61469,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G2350" t="n">
-        <v>1.9586136341095</v>
+        <v>1.95861351490021</v>
       </c>
       <c r="H2350" t="s">
         <v>8</v>
@@ -61495,7 +61495,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G2351" t="n">
-        <v>1.93367457389832</v>
+        <v>1.9336746931076</v>
       </c>
       <c r="H2351" t="s">
         <v>8</v>
@@ -61573,7 +61573,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G2354" t="n">
-        <v>1.89537537097931</v>
+        <v>1.89537525177002</v>
       </c>
       <c r="H2354" t="s">
         <v>8</v>
@@ -61599,7 +61599,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G2355" t="n">
-        <v>1.72436380386353</v>
+        <v>1.72436392307281</v>
       </c>
       <c r="H2355" t="s">
         <v>8</v>
@@ -61755,7 +61755,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G2361" t="n">
-        <v>1.52128803730011</v>
+        <v>1.52128791809082</v>
       </c>
       <c r="H2361" t="s">
         <v>8</v>
@@ -61781,7 +61781,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G2362" t="n">
-        <v>1.56493139266968</v>
+        <v>1.56493151187897</v>
       </c>
       <c r="H2362" t="s">
         <v>8</v>
@@ -61937,7 +61937,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G2368" t="n">
-        <v>1.74930310249329</v>
+        <v>1.749302983284</v>
       </c>
       <c r="H2368" t="s">
         <v>8</v>
@@ -62015,7 +62015,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2371" t="n">
-        <v>1.82590174674988</v>
+        <v>1.82590186595917</v>
       </c>
       <c r="H2371" t="s">
         <v>8</v>
@@ -62067,7 +62067,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2373" t="n">
-        <v>1.85262227058411</v>
+        <v>1.8526223897934</v>
       </c>
       <c r="H2373" t="s">
         <v>8</v>
@@ -62093,7 +62093,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G2374" t="n">
-        <v>1.83302748203278</v>
+        <v>1.83302736282349</v>
       </c>
       <c r="H2374" t="s">
         <v>8</v>
@@ -62119,7 +62119,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G2375" t="n">
-        <v>1.82768332958221</v>
+        <v>1.82768321037292</v>
       </c>
       <c r="H2375" t="s">
         <v>8</v>
@@ -62145,7 +62145,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G2376" t="n">
-        <v>1.83837139606476</v>
+        <v>1.83837127685547</v>
       </c>
       <c r="H2376" t="s">
         <v>8</v>
@@ -62197,7 +62197,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G2378" t="n">
-        <v>1.9399094581604</v>
+        <v>1.93990933895111</v>
       </c>
       <c r="H2378" t="s">
         <v>8</v>
@@ -69220,6 +69220,32 @@
         <v>4.3289999961853</v>
       </c>
       <c r="H2648" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2649">
+      <c r="A2649" s="1" t="n">
+        <v>46178.2916666667</v>
+      </c>
+      <c r="B2649" t="n">
+        <v>37947533</v>
+      </c>
+      <c r="C2649" t="n">
+        <v>4.53700017929077</v>
+      </c>
+      <c r="D2649" t="n">
+        <v>4.34600019454956</v>
+      </c>
+      <c r="E2649" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="F2649" t="n">
+        <v>4.40399980545044</v>
+      </c>
+      <c r="G2649" t="n">
+        <v>4.40399980545044</v>
+      </c>
+      <c r="H2649" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -473,7 +473,7 @@
         <v>22.3245735168457</v>
       </c>
       <c r="G4" t="n">
-        <v>19.7946090698242</v>
+        <v>19.7946071624756</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>21.3766078948975</v>
       </c>
       <c r="G6" t="n">
-        <v>18.9540748596191</v>
+        <v>18.9540729522705</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>22.1665782928467</v>
       </c>
       <c r="G9" t="n">
-        <v>19.65452003479</v>
+        <v>19.6545181274414</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>19.8440647125244</v>
       </c>
       <c r="G12" t="n">
-        <v>17.5952072143555</v>
+        <v>17.5952091217041</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811977386475</v>
+        <v>17.5811958312988</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460269927979</v>
+        <v>15.7460289001465</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>13.806058883667</v>
       </c>
       <c r="G19" t="n">
-        <v>12.2414665222168</v>
+        <v>12.2414674758911</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>13.5048360824585</v>
       </c>
       <c r="G24" t="n">
-        <v>11.9743814468384</v>
+        <v>11.9743804931641</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617107391357</v>
+        <v>8.16617202758789</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G30" t="n">
-        <v>7.08892250061035</v>
+        <v>7.08892202377319</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G31" t="n">
-        <v>6.70832395553589</v>
+        <v>6.70832347869873</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.87747859954834</v>
+        <v>6.8774790763855</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51181030273438</v>
+        <v>7.51180982589722</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.96546459197998</v>
       </c>
       <c r="G46" t="n">
-        <v>8.83611297607422</v>
+        <v>8.83611392974854</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.0771427154541</v>
+        <v>8.07714366912842</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811292648315</v>
+        <v>7.98811388015747</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G53" t="n">
-        <v>8.29526424407959</v>
+        <v>8.29526329040527</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.26261138916016</v>
       </c>
       <c r="G54" t="n">
-        <v>8.21291255950928</v>
+        <v>8.21291351318359</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.31752109527588</v>
+        <v>8.3175220489502</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G59" t="n">
-        <v>8.2062349319458</v>
+        <v>8.20623397827148</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G60" t="n">
-        <v>7.75218820571899</v>
+        <v>7.75218725204468</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.34487962722778</v>
+        <v>7.3448805809021</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870761871338</v>
+        <v>7.65870809555054</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365779876709</v>
+        <v>7.27365732192993</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.86347341537476</v>
+        <v>7.86347436904907</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09940052032471</v>
+        <v>8.09939956665039</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.87102127075195</v>
       </c>
       <c r="G74" t="n">
-        <v>7.86569976806641</v>
+        <v>7.86570072174072</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.25006008148193</v>
       </c>
       <c r="G79" t="n">
-        <v>8.20178413391113</v>
+        <v>8.20178318023682</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912082672119</v>
+        <v>8.62912178039551</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G86" t="n">
-        <v>8.54009246826172</v>
+        <v>8.54009342193604</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.36803913116455</v>
       </c>
       <c r="G90" t="n">
-        <v>8.30639266967773</v>
+        <v>8.30639171600342</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.20487594604492</v>
       </c>
       <c r="G91" t="n">
-        <v>8.16171932220459</v>
+        <v>8.16172027587891</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.26855373382568</v>
+        <v>8.2685546875</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542102813721</v>
+        <v>8.39542007446289</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588752746582</v>
+        <v>7.98588848114014</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701738357544</v>
+        <v>7.99701642990112</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G103" t="n">
-        <v>8.3976469039917</v>
+        <v>8.39764595031738</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.3303861618042</v>
       </c>
       <c r="G105" t="n">
-        <v>8.27300548553467</v>
+        <v>8.27300643920898</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G106" t="n">
-        <v>8.1884298324585</v>
+        <v>8.18842887878418</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889537811279</v>
+        <v>7.77889633178711</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701738357544</v>
+        <v>7.99701642990112</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G112" t="n">
-        <v>8.85837268829346</v>
+        <v>8.85837173461914</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660707473755</v>
+        <v>7.73660612106323</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808195114136</v>
+        <v>7.96808290481567</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G119" t="n">
-        <v>8.2062349319458</v>
+        <v>8.20623397827148</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.8851375579834</v>
       </c>
       <c r="G122" t="n">
-        <v>8.76488971710205</v>
+        <v>8.76489067077637</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.05933666229248</v>
+        <v>8.0593376159668</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.71147346496582</v>
+        <v>8.7114725112915</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420257568359</v>
+        <v>9.03420352935791</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G141" t="n">
-        <v>9.55947303771973</v>
+        <v>9.55947208404541</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G144" t="n">
-        <v>9.68856430053711</v>
+        <v>9.68856525421143</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>10.6934204101562</v>
       </c>
       <c r="G146" t="n">
-        <v>9.48157215118408</v>
+        <v>9.4815731048584</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.52228736877441</v>
+        <v>8.52228832244873</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>10.3269319534302</v>
       </c>
       <c r="G159" t="n">
-        <v>9.15661811828613</v>
+        <v>9.15661716461182</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.98303604125977</v>
       </c>
       <c r="G164" t="n">
-        <v>8.85169410705566</v>
+        <v>8.85169315338135</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>10.4449110031128</v>
       </c>
       <c r="G165" t="n">
-        <v>9.26122665405273</v>
+        <v>9.26122570037842</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548873901367</v>
+        <v>9.14548778533936</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>10.457462310791</v>
       </c>
       <c r="G174" t="n">
-        <v>9.27235507965088</v>
+        <v>9.2723560333252</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.79224967956543</v>
+        <v>7.79225063323975</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.91871356964111</v>
       </c>
       <c r="G189" t="n">
-        <v>7.90798759460449</v>
+        <v>7.90798664093018</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.7388334274292</v>
+        <v>7.73883247375488</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.063362121582</v>
       </c>
       <c r="G200" t="n">
-        <v>8.92291641235352</v>
+        <v>8.92291736602783</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>10.1662797927856</v>
       </c>
       <c r="G202" t="n">
-        <v>9.01417064666748</v>
+        <v>9.0141716003418</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G207" t="n">
-        <v>9.68856430053711</v>
+        <v>9.68856525421143</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>10.9519701004028</v>
       </c>
       <c r="G208" t="n">
-        <v>9.71082305908203</v>
+        <v>9.71082210540771</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.22244834899902</v>
       </c>
       <c r="G216" t="n">
-        <v>8.17730045318604</v>
+        <v>8.17730140686035</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G220" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G221" t="n">
-        <v>8.73373031616211</v>
+        <v>8.73373126983643</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G232" t="n">
-        <v>9.16329479217529</v>
+        <v>9.16329383850098</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G233" t="n">
-        <v>8.92514228820801</v>
+        <v>8.92514324188232</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.6457271575928</v>
       </c>
       <c r="G236" t="n">
-        <v>9.43928527832031</v>
+        <v>9.439284324646</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.4088249206543</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1159038543701</v>
+        <v>10.1159029006958</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>12.8772878646851</v>
       </c>
       <c r="G253" t="n">
-        <v>11.417950630188</v>
+        <v>11.4179496765137</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>13.0906553268433</v>
       </c>
       <c r="G254" t="n">
-        <v>11.607138633728</v>
+        <v>11.6071376800537</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076108932495</v>
+        <v>11.9076099395752</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>13.9817733764648</v>
       </c>
       <c r="G260" t="n">
-        <v>12.3972682952881</v>
+        <v>12.3972692489624</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619930267334</v>
+        <v>11.1619920730591</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960092544556</v>
+        <v>11.5960083007812</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G280" t="n">
-        <v>10.5276613235474</v>
+        <v>10.5276622772217</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141502380371</v>
+        <v>10.4141492843628</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.3985710144043</v>
+        <v>10.39857006073</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.6874570846558</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3629589080811</v>
+        <v>10.3629579544067</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>10.5754413604736</v>
       </c>
       <c r="G298" t="n">
-        <v>9.37696361541748</v>
+        <v>9.3769645690918</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.6632976531982</v>
       </c>
       <c r="G301" t="n">
-        <v>9.45486450195312</v>
+        <v>9.45486354827881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G313" t="n">
-        <v>9.01639652252197</v>
+        <v>9.01639747619629</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G319" t="n">
-        <v>9.39254379272461</v>
+        <v>9.39254474639893</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77981853485107</v>
+        <v>9.77981948852539</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G325" t="n">
-        <v>9.51050758361816</v>
+        <v>9.51050662994385</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>10.7310733795166</v>
       </c>
       <c r="G326" t="n">
-        <v>9.51495933532715</v>
+        <v>9.51495838165283</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.7671594619751</v>
       </c>
       <c r="G335" t="n">
-        <v>8.66028213500977</v>
+        <v>8.66028118133545</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G342" t="n">
-        <v>8.85837268829346</v>
+        <v>8.85837173461914</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G346" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10.003116607666</v>
       </c>
       <c r="G349" t="n">
-        <v>8.86949825286865</v>
+        <v>8.86949920654297</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.80481243133545</v>
       </c>
       <c r="G354" t="n">
-        <v>8.69366836547852</v>
+        <v>8.6936674118042</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G362" t="n">
-        <v>8.03485488891602</v>
+        <v>8.0348539352417</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G366" t="n">
-        <v>7.66093397140503</v>
+        <v>7.66093349456787</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.13302421569824</v>
       </c>
       <c r="G377" t="n">
-        <v>7.21133661270142</v>
+        <v>7.21133708953857</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G378" t="n">
-        <v>7.18017673492432</v>
+        <v>7.18017721176147</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>8.07779979705811</v>
       </c>
       <c r="G380" t="n">
-        <v>7.16237115859985</v>
+        <v>7.16237163543701</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914266586304</v>
+        <v>7.22914218902588</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817245483398</v>
+        <v>7.31817150115967</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055511474609</v>
+        <v>7.42055559158325</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390846252441</v>
+        <v>7.43390893936157</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.8567967414856</v>
+        <v>7.85679578781128</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>8.52461433410645</v>
       </c>
       <c r="G397" t="n">
-        <v>7.5585503578186</v>
+        <v>7.55854988098145</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842359542847</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G403" t="n">
-        <v>7.59416151046753</v>
+        <v>7.59416103363037</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757919311523</v>
+        <v>7.64757871627808</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G408" t="n">
-        <v>7.5852575302124</v>
+        <v>7.58525800704956</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428636550903</v>
+        <v>7.67428731918335</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.5748176574707</v>
       </c>
       <c r="G411" t="n">
-        <v>7.60306453704834</v>
+        <v>7.60306406021118</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249792098999</v>
+        <v>7.24249744415283</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701210021973</v>
+        <v>7.28701162338257</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G416" t="n">
-        <v>7.26475477218628</v>
+        <v>7.26475429534912</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.61592388153076</v>
       </c>
       <c r="G422" t="n">
-        <v>6.75283861160278</v>
+        <v>6.75283813476562</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>7.68621015548706</v>
       </c>
       <c r="G424" t="n">
-        <v>6.8151593208313</v>
+        <v>6.81515884399414</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.40004777908325</v>
       </c>
       <c r="G426" t="n">
-        <v>6.56142663955688</v>
+        <v>6.56142616271973</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.9397988319397</v>
+        <v>6.93979835510254</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.74645376205444</v>
       </c>
       <c r="G428" t="n">
-        <v>6.86857557296753</v>
+        <v>6.86857604980469</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.76151514053345</v>
       </c>
       <c r="G429" t="n">
-        <v>6.88193035125732</v>
+        <v>6.88192987442017</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G432" t="n">
-        <v>7.22469091415405</v>
+        <v>7.22469139099121</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591369628906</v>
+        <v>7.29591417312622</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409860610962</v>
+        <v>7.55409908294678</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G439" t="n">
-        <v>7.5852575302124</v>
+        <v>7.58525800704956</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538429260254</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.10697937011719</v>
       </c>
       <c r="G444" t="n">
-        <v>8.07491683959961</v>
+        <v>8.07491779327393</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.10195827484131</v>
       </c>
       <c r="G445" t="n">
-        <v>8.07046508789062</v>
+        <v>8.07046604156494</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504360198975</v>
+        <v>8.15504264831543</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G462" t="n">
-        <v>7.38939476013184</v>
+        <v>7.38939523696899</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538429260254</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.49354839324951</v>
       </c>
       <c r="G478" t="n">
-        <v>8.4176778793335</v>
+        <v>8.41767883300781</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757919311523</v>
+        <v>7.64757871627808</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576314926147</v>
+        <v>7.90576219558716</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344244003296</v>
+        <v>7.84344148635864</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>8.60494041442871</v>
       </c>
       <c r="G488" t="n">
-        <v>7.62977266311646</v>
+        <v>7.62977313995361</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.74996280670166</v>
+        <v>7.74996185302734</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>9.34795665740967</v>
       </c>
       <c r="G508" t="n">
-        <v>8.28858661651611</v>
+        <v>8.2885856628418</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.61403846740723</v>
       </c>
       <c r="G510" t="n">
-        <v>8.52451324462891</v>
+        <v>8.52451419830322</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.50225639343262</v>
+        <v>8.5022554397583</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G514" t="n">
-        <v>8.73373031616211</v>
+        <v>8.73373126983643</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G517" t="n">
-        <v>8.7604398727417</v>
+        <v>8.76043891906738</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.76464939117432</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65805625915527</v>
+        <v>8.65805530548096</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>10.1210966110229</v>
       </c>
       <c r="G519" t="n">
-        <v>8.97410869598389</v>
+        <v>8.9741096496582</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>10.1813411712646</v>
       </c>
       <c r="G524" t="n">
-        <v>9.02752590179443</v>
+        <v>9.02752685546875</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G528" t="n">
-        <v>9.16552066802979</v>
+        <v>9.1655216217041</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G529" t="n">
-        <v>9.04088020324707</v>
+        <v>9.04087924957275</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G530" t="n">
-        <v>9.04088020324707</v>
+        <v>9.04087924957275</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833885192871</v>
+        <v>8.83833980560303</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>9.46593570709229</v>
       </c>
       <c r="G533" t="n">
-        <v>8.39319515228271</v>
+        <v>8.3931941986084</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.4199047088623</v>
+        <v>8.41990566253662</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617107391357</v>
+        <v>8.16617202758789</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G538" t="n">
-        <v>8.03485488891602</v>
+        <v>8.0348539352417</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660707473755</v>
+        <v>7.73660612106323</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519557952881</v>
+        <v>7.54519605636597</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G545" t="n">
-        <v>7.66093397140503</v>
+        <v>7.66093349456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G548" t="n">
-        <v>7.60083913803101</v>
+        <v>7.60083866119385</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.76331615447998</v>
+        <v>7.7633171081543</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.52293825149536</v>
+        <v>7.52293872833252</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368829727173</v>
+        <v>7.29368877410889</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.56979656219482</v>
       </c>
       <c r="G558" t="n">
-        <v>7.59861183166504</v>
+        <v>7.5986123085022</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663900375366</v>
+        <v>7.75663805007935</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G560" t="n">
-        <v>7.75218820571899</v>
+        <v>7.75218725204468</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613481521606</v>
+        <v>7.43613433837891</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585079193115</v>
+        <v>7.25585126876831</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.32128810882568</v>
       </c>
       <c r="G567" t="n">
-        <v>7.37826633453369</v>
+        <v>7.37826585769653</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>8.43173694610596</v>
       </c>
       <c r="G568" t="n">
-        <v>7.47619771957397</v>
+        <v>7.47619819641113</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>8.17820739746094</v>
       </c>
       <c r="G570" t="n">
-        <v>7.25139999389648</v>
+        <v>7.25140047073364</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G573" t="n">
-        <v>7.07111692428589</v>
+        <v>7.07111740112305</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G578" t="n">
-        <v>6.98876571655273</v>
+        <v>6.98876523971558</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744714736938</v>
+        <v>6.85744667053223</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G581" t="n">
-        <v>7.08892250061035</v>
+        <v>7.08892202377319</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G583" t="n">
-        <v>7.22469091415405</v>
+        <v>7.22469139099121</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G585" t="n">
-        <v>7.18017673492432</v>
+        <v>7.18017721176147</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G586" t="n">
-        <v>7.4806489944458</v>
+        <v>7.48064947128296</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842359542847</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G589" t="n">
-        <v>7.4806489944458</v>
+        <v>7.48064947128296</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G590" t="n">
-        <v>7.26475477218628</v>
+        <v>7.26475429534912</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G591" t="n">
-        <v>6.98876571655273</v>
+        <v>6.98876523971558</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766731262207</v>
+        <v>6.99766778945923</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>7.92969799041748</v>
       </c>
       <c r="G596" t="n">
-        <v>7.03105354309082</v>
+        <v>7.03105306625366</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.06022834777832</v>
       </c>
       <c r="G599" t="n">
-        <v>7.14679098129272</v>
+        <v>7.14679145812988</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G601" t="n">
-        <v>7.38939476013184</v>
+        <v>7.38939523696899</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.55222606658936</v>
       </c>
       <c r="G603" t="n">
-        <v>7.58303213119507</v>
+        <v>7.58303260803223</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.83242416381836</v>
       </c>
       <c r="G605" t="n">
-        <v>8.71815013885498</v>
+        <v>8.7181510925293</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G607" t="n">
-        <v>8.54009246826172</v>
+        <v>8.54009342193604</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>10.0909738540649</v>
       </c>
       <c r="G609" t="n">
-        <v>8.94740009307861</v>
+        <v>8.9473991394043</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065475463867</v>
+        <v>8.19065380096436</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.31783485412598</v>
       </c>
       <c r="G620" t="n">
-        <v>8.26187801361084</v>
+        <v>8.26187896728516</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>9.85250568389893</v>
       </c>
       <c r="G623" t="n">
-        <v>8.73595523834229</v>
+        <v>8.7359561920166</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G629" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>9.36552906036377</v>
       </c>
       <c r="G630" t="n">
-        <v>8.30416774749756</v>
+        <v>8.30416679382324</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.71147346496582</v>
+        <v>8.7114725112915</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009727478027</v>
+        <v>9.25009632110596</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G646" t="n">
-        <v>9.39254379272461</v>
+        <v>9.39254474639893</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G650" t="n">
-        <v>9.01639652252197</v>
+        <v>9.01639747619629</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G651" t="n">
-        <v>9.05646133422852</v>
+        <v>9.0564603805542</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100505828857</v>
+        <v>9.12100601196289</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>11.200478553772</v>
       </c>
       <c r="G668" t="n">
-        <v>9.93116760253906</v>
+        <v>9.93116855621338</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G671" t="n">
-        <v>9.80652904510498</v>
+        <v>9.80652809143066</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G678" t="n">
-        <v>10.0157461166382</v>
+        <v>10.0157451629639</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G684" t="n">
-        <v>10.334023475647</v>
+        <v>10.3340244293213</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99349021911621</v>
+        <v>9.99348926544189</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694787979126</v>
+        <v>10.2694797515869</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>11.9259252548218</v>
       </c>
       <c r="G689" t="n">
-        <v>10.5744018554688</v>
+        <v>10.5744028091431</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G693" t="n">
-        <v>10.8259077072144</v>
+        <v>10.8259086608887</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.7569122314453</v>
+        <v>10.756911277771</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>13.2086343765259</v>
       </c>
       <c r="G699" t="n">
-        <v>11.7117471694946</v>
+        <v>11.7117462158203</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>13.5500202178955</v>
       </c>
       <c r="G702" t="n">
-        <v>12.0144443511963</v>
+        <v>12.014443397522</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>12.7618188858032</v>
       </c>
       <c r="G709" t="n">
-        <v>11.3155679702759</v>
+        <v>11.3155670166016</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395784378052</v>
+        <v>11.0395774841309</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>12.7065954208374</v>
       </c>
       <c r="G712" t="n">
-        <v>11.2666025161743</v>
+        <v>11.2666015625</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>12.3325757980347</v>
       </c>
       <c r="G714" t="n">
-        <v>10.9349699020386</v>
+        <v>10.9349689483643</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>11.8004150390625</v>
       </c>
       <c r="G715" t="n">
-        <v>10.463116645813</v>
+        <v>10.4631156921387</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364070892334</v>
+        <v>10.4364080429077</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G719" t="n">
-        <v>10.5499200820923</v>
+        <v>10.549919128418</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>11.7979049682617</v>
       </c>
       <c r="G721" t="n">
-        <v>10.4608907699585</v>
+        <v>10.4608898162842</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>11.8857622146606</v>
       </c>
       <c r="G723" t="n">
-        <v>10.5387907028198</v>
+        <v>10.5387916564941</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G724" t="n">
-        <v>10.76136302948</v>
+        <v>10.7613620758057</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>11.7251100540161</v>
       </c>
       <c r="G730" t="n">
-        <v>10.3963451385498</v>
+        <v>10.3963441848755</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G737" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G738" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081249237061</v>
+        <v>8.29081153869629</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889537811279</v>
+        <v>7.77889633178711</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219158172607</v>
+        <v>8.46219253540039</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G750" t="n">
-        <v>8.1884298324585</v>
+        <v>8.18842887878418</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G754" t="n">
-        <v>8.29526424407959</v>
+        <v>8.29526329040527</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G759" t="n">
-        <v>7.59416151046753</v>
+        <v>7.59416103363037</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>8.12800407409668</v>
       </c>
       <c r="G761" t="n">
-        <v>7.20688581466675</v>
+        <v>7.20688629150391</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873331069946</v>
+        <v>6.96873378753662</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576314926147</v>
+        <v>7.90576219558716</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>9.12957000732422</v>
       </c>
       <c r="G767" t="n">
-        <v>8.09494876861572</v>
+        <v>8.09494781494141</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G771" t="n">
-        <v>8.3976469039917</v>
+        <v>8.39764595031738</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>10.2817487716675</v>
       </c>
       <c r="G786" t="n">
-        <v>9.11655426025391</v>
+        <v>9.11655521392822</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>10.4298496246338</v>
       </c>
       <c r="G789" t="n">
-        <v>9.2478723526001</v>
+        <v>9.24787139892578</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>10.7963380813599</v>
       </c>
       <c r="G797" t="n">
-        <v>9.57282638549805</v>
+        <v>9.57282733917236</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>10.8440322875977</v>
       </c>
       <c r="G803" t="n">
-        <v>9.61511707305908</v>
+        <v>9.61511611938477</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G804" t="n">
-        <v>9.69746875762939</v>
+        <v>9.69746780395508</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232986450195</v>
+        <v>9.96232891082764</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496036529541</v>
+        <v>10.3496046066284</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>11.8882722854614</v>
       </c>
       <c r="G809" t="n">
-        <v>10.541015625</v>
+        <v>10.5410165786743</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G812" t="n">
-        <v>10.5276613235474</v>
+        <v>10.5276622772217</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>12.3150053024292</v>
       </c>
       <c r="G815" t="n">
-        <v>10.9193897247314</v>
+        <v>10.9193887710571</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.3350868225098</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9371957778931</v>
+        <v>10.9371948242188</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G820" t="n">
-        <v>10.8259077072144</v>
+        <v>10.8259086608887</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>11.5368452072144</v>
       </c>
       <c r="G822" t="n">
-        <v>10.2294149398804</v>
+        <v>10.2294158935547</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G825" t="n">
-        <v>10.334023475647</v>
+        <v>10.3340244293213</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147811889648</v>
+        <v>10.8147802352905</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>12.2522497177124</v>
       </c>
       <c r="G829" t="n">
-        <v>10.8637456893921</v>
+        <v>10.8637447357178</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G830" t="n">
-        <v>10.76136302948</v>
+        <v>10.7613620758057</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>12.4856977462769</v>
       </c>
       <c r="G831" t="n">
-        <v>11.0707378387451</v>
+        <v>11.0707368850708</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>12.6312885284424</v>
       </c>
       <c r="G832" t="n">
-        <v>11.1998291015625</v>
+        <v>11.1998300552368</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>12.0991277694702</v>
       </c>
       <c r="G834" t="n">
-        <v>10.7279767990112</v>
+        <v>10.7279777526855</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G835" t="n">
-        <v>10.4386329650879</v>
+        <v>10.4386339187622</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295726776123</v>
+        <v>10.3295736312866</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>11.5343351364136</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2271900177002</v>
+        <v>10.2271909713745</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G839" t="n">
-        <v>10.4386329650879</v>
+        <v>10.4386339187622</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G842" t="n">
-        <v>10.5499200820923</v>
+        <v>10.549919128418</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>11.3912544250488</v>
       </c>
       <c r="G844" t="n">
-        <v>10.1003246307373</v>
+        <v>10.100323677063</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>10.836501121521</v>
       </c>
       <c r="G849" t="n">
-        <v>9.60843944549561</v>
+        <v>9.60843849182129</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G858" t="n">
-        <v>9.27012920379639</v>
+        <v>9.2701301574707</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G859" t="n">
-        <v>9.16329479217529</v>
+        <v>9.16329383850098</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G867" t="n">
-        <v>8.7604398727417</v>
+        <v>8.76043891906738</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395576477051</v>
+        <v>9.58395671844482</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G878" t="n">
-        <v>9.27012920379639</v>
+        <v>9.2701301574707</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G880" t="n">
-        <v>9.55947303771973</v>
+        <v>9.55947208404541</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G881" t="n">
-        <v>9.60621356964111</v>
+        <v>9.6062126159668</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>11.0699491500854</v>
       </c>
       <c r="G883" t="n">
-        <v>9.81543159484863</v>
+        <v>9.81543064117432</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079113006592</v>
+        <v>9.69079208374023</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.0498676300049</v>
       </c>
       <c r="G887" t="n">
-        <v>9.79762649536133</v>
+        <v>9.79762554168701</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.2431526184082</v>
       </c>
       <c r="G889" t="n">
-        <v>9.9690055847168</v>
+        <v>9.96900653839111</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G890" t="n">
-        <v>9.69746875762939</v>
+        <v>9.69746780395508</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>11.0272760391235</v>
       </c>
       <c r="G893" t="n">
-        <v>9.7775936126709</v>
+        <v>9.77759456634521</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304893493652</v>
+        <v>9.71304798126221</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>11.0423374176025</v>
       </c>
       <c r="G905" t="n">
-        <v>9.79094791412354</v>
+        <v>9.79094886779785</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G906" t="n">
-        <v>10.0157461166382</v>
+        <v>10.0157451629639</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794101715088</v>
+        <v>9.99794006347656</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G916" t="n">
-        <v>8.92514228820801</v>
+        <v>8.92514324188232</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G919" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.9518518447876</v>
+        <v>8.95185089111328</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>10.4474220275879</v>
       </c>
       <c r="G925" t="n">
-        <v>9.26345348358154</v>
+        <v>9.26345252990723</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>10.2842588424683</v>
       </c>
       <c r="G927" t="n">
-        <v>9.1187801361084</v>
+        <v>9.11878108978271</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>10.3545436859131</v>
       </c>
       <c r="G928" t="n">
-        <v>9.1810998916626</v>
+        <v>9.18110084533691</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>10.9092969894409</v>
       </c>
       <c r="G931" t="n">
-        <v>9.6729850769043</v>
+        <v>9.67298603057861</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>10.9067869186401</v>
       </c>
       <c r="G933" t="n">
-        <v>9.6707592010498</v>
+        <v>9.67076015472412</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G937" t="n">
-        <v>9.80652904510498</v>
+        <v>9.80652809143066</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136779785156</v>
+        <v>10.1136770248413</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403865814209</v>
+        <v>10.1403875350952</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230527877808</v>
+        <v>10.4230537414551</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.881685256958</v>
       </c>
       <c r="G948" t="n">
-        <v>9.64850330352783</v>
+        <v>9.64850234985352</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>10.7862977981567</v>
       </c>
       <c r="G949" t="n">
-        <v>9.56392478942871</v>
+        <v>9.56392383575439</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>10.2164840698242</v>
       </c>
       <c r="G954" t="n">
-        <v>9.05868625640869</v>
+        <v>9.05868530273438</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>10.0683822631836</v>
       </c>
       <c r="G955" t="n">
-        <v>8.92736721038818</v>
+        <v>8.9273681640625</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G958" t="n">
-        <v>9.16552066802979</v>
+        <v>9.1655216217041</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>10.3294429779053</v>
       </c>
       <c r="G968" t="n">
-        <v>9.15884399414062</v>
+        <v>9.15884304046631</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>10.2792387008667</v>
       </c>
       <c r="G969" t="n">
-        <v>9.11432933807373</v>
+        <v>9.11433029174805</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G974" t="n">
-        <v>9.51050758361816</v>
+        <v>9.51050662994385</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G978" t="n">
-        <v>9.60621356964111</v>
+        <v>9.6062126159668</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>11.1402349472046</v>
       </c>
       <c r="G982" t="n">
-        <v>9.87775135040283</v>
+        <v>9.87775230407715</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>11.0573978424072</v>
       </c>
       <c r="G983" t="n">
-        <v>9.80430221557617</v>
+        <v>9.80430126190186</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.802077293396</v>
+        <v>9.80207633972168</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812397003174</v>
+        <v>9.40812492370605</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G994" t="n">
-        <v>9.45931625366211</v>
+        <v>9.45931529998779</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G999" t="n">
-        <v>9.05646133422852</v>
+        <v>9.0564603805542</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>10.427339553833</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.24564647674561</v>
+        <v>9.24564552307129</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.39254379272461</v>
+        <v>9.39254474639893</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467674255371</v>
+        <v>9.33467578887939</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G1008" t="n">
-        <v>9.45931625366211</v>
+        <v>9.45931529998779</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>10.7938280105591</v>
       </c>
       <c r="G1009" t="n">
-        <v>9.57060146331787</v>
+        <v>9.57060241699219</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.56169891357422</v>
+        <v>9.5616979598999</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>11.1728668212891</v>
       </c>
       <c r="G1019" t="n">
-        <v>9.9066858291626</v>
+        <v>9.90668487548828</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>11.1678466796875</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.90223503112793</v>
+        <v>9.90223407745361</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.802077293396</v>
+        <v>9.80207633972168</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.2062349319458</v>
+        <v>8.20623397827148</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>9.51362991333008</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.43548393249512</v>
+        <v>8.43548488616943</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754726409912</v>
+        <v>7.62754774093628</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.60083913803101</v>
+        <v>7.60083866119385</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>8.3037166595459</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.36268663406372</v>
+        <v>7.36268615722656</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585079193115</v>
+        <v>7.25585126876831</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.07111692428589</v>
+        <v>7.07111740112305</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.70832395553589</v>
+        <v>6.70832347869873</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>5.16848611831665</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.58275985717773</v>
+        <v>4.58276033401489</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>5.16346597671509</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.57830905914307</v>
+        <v>4.57830858230591</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342178344727</v>
+        <v>5.00342130661011</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.88990926742554</v>
+        <v>4.8899097442627</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>5.8261570930481</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.1658992767334</v>
+        <v>5.16589975357056</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1078" t="n">
-        <v>4.98561525344849</v>
+        <v>4.98561573028564</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1079" t="n">
-        <v>4.98561525344849</v>
+        <v>4.98561573028564</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.06713485717773</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.37956809997559</v>
+        <v>5.37956762313843</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>5.95919704437256</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.28386259078979</v>
+        <v>5.28386211395264</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.0219521522522</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.33950567245483</v>
+        <v>5.33950614929199</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>5.9014630317688</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.23267126083374</v>
+        <v>5.23267078399658</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>6.04956388473511</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.36398839950562</v>
+        <v>5.36398887634277</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>5.47473001480103</v>
       </c>
       <c r="G1089" t="n">
-        <v>4.85429859161377</v>
+        <v>4.85429811477661</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.95445537567139</v>
+        <v>4.95445489883423</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928550720215</v>
+        <v>5.19928503036499</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041345596313</v>
+        <v>5.21041393280029</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470699310303</v>
+        <v>5.11470746994019</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248159408569</v>
+        <v>5.11248207092285</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>5.57513809204102</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.94332695007324</v>
+        <v>4.9433274269104</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -69246,6 +69246,32 @@
         <v>4.40399980545044</v>
       </c>
       <c r="H2649" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2650">
+      <c r="A2650" s="1" t="n">
+        <v>46181.2916666667</v>
+      </c>
+      <c r="B2650" t="n">
+        <v>15852366</v>
+      </c>
+      <c r="C2650" t="n">
+        <v>4.5149998664856</v>
+      </c>
+      <c r="D2650" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="E2650" t="n">
+        <v>4.40999984741211</v>
+      </c>
+      <c r="F2650" t="n">
+        <v>4.44899988174438</v>
+      </c>
+      <c r="G2650" t="n">
+        <v>4.44899988174438</v>
+      </c>
+      <c r="H2650" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -473,7 +473,7 @@
         <v>22.3245735168457</v>
       </c>
       <c r="G4" t="n">
-        <v>19.7946071624756</v>
+        <v>19.7946090698242</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>21.3766078948975</v>
       </c>
       <c r="G6" t="n">
-        <v>18.9540729522705</v>
+        <v>18.9540748596191</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>22.1665782928467</v>
       </c>
       <c r="G9" t="n">
-        <v>19.6545181274414</v>
+        <v>19.65452003479</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>19.8440647125244</v>
       </c>
       <c r="G12" t="n">
-        <v>17.5952091217041</v>
+        <v>17.5952072143555</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811958312988</v>
+        <v>17.5811977386475</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460289001465</v>
+        <v>15.7460269927979</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>13.806058883667</v>
       </c>
       <c r="G19" t="n">
-        <v>12.2414674758911</v>
+        <v>12.2414665222168</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>13.5048360824585</v>
       </c>
       <c r="G24" t="n">
-        <v>11.9743804931641</v>
+        <v>11.9743814468384</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G30" t="n">
-        <v>7.08892202377319</v>
+        <v>7.08892250061035</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G31" t="n">
-        <v>6.70832347869873</v>
+        <v>6.70832395553589</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.8774790763855</v>
+        <v>6.87747859954834</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51180982589722</v>
+        <v>7.51181030273438</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.96546459197998</v>
       </c>
       <c r="G46" t="n">
-        <v>8.83611392974854</v>
+        <v>8.83611297607422</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.07714366912842</v>
+        <v>8.0771427154541</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811388015747</v>
+        <v>7.98811292648315</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G53" t="n">
-        <v>8.29526329040527</v>
+        <v>8.29526424407959</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.26261138916016</v>
       </c>
       <c r="G54" t="n">
-        <v>8.21291351318359</v>
+        <v>8.21291255950928</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.3175220489502</v>
+        <v>8.31752109527588</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G59" t="n">
-        <v>8.20623397827148</v>
+        <v>8.2062349319458</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G60" t="n">
-        <v>7.75218725204468</v>
+        <v>7.75218820571899</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.3448805809021</v>
+        <v>7.34487962722778</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870809555054</v>
+        <v>7.65870761871338</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365732192993</v>
+        <v>7.27365779876709</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.86347436904907</v>
+        <v>7.86347341537476</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09939956665039</v>
+        <v>8.09940052032471</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.87102127075195</v>
       </c>
       <c r="G74" t="n">
-        <v>7.86570072174072</v>
+        <v>7.86569976806641</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.25006008148193</v>
       </c>
       <c r="G79" t="n">
-        <v>8.20178318023682</v>
+        <v>8.20178413391113</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912178039551</v>
+        <v>8.62912082672119</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G86" t="n">
-        <v>8.54009342193604</v>
+        <v>8.54009246826172</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.36803913116455</v>
       </c>
       <c r="G90" t="n">
-        <v>8.30639171600342</v>
+        <v>8.30639266967773</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.20487594604492</v>
       </c>
       <c r="G91" t="n">
-        <v>8.16172027587891</v>
+        <v>8.16171932220459</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.2685546875</v>
+        <v>8.26855373382568</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542007446289</v>
+        <v>8.39542102813721</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588848114014</v>
+        <v>7.98588752746582</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701642990112</v>
+        <v>7.99701738357544</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G103" t="n">
-        <v>8.39764595031738</v>
+        <v>8.3976469039917</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.3303861618042</v>
       </c>
       <c r="G105" t="n">
-        <v>8.27300643920898</v>
+        <v>8.27300548553467</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G106" t="n">
-        <v>8.18842887878418</v>
+        <v>8.1884298324585</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889633178711</v>
+        <v>7.77889537811279</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701642990112</v>
+        <v>7.99701738357544</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G112" t="n">
-        <v>8.85837173461914</v>
+        <v>8.85837268829346</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660612106323</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808290481567</v>
+        <v>7.96808195114136</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G119" t="n">
-        <v>8.20623397827148</v>
+        <v>8.2062349319458</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.8851375579834</v>
       </c>
       <c r="G122" t="n">
-        <v>8.76489067077637</v>
+        <v>8.76488971710205</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.0593376159668</v>
+        <v>8.05933666229248</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.7114725112915</v>
+        <v>8.71147346496582</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420352935791</v>
+        <v>9.03420257568359</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G141" t="n">
-        <v>9.55947208404541</v>
+        <v>9.55947303771973</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G144" t="n">
-        <v>9.68856525421143</v>
+        <v>9.68856430053711</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>10.6934204101562</v>
       </c>
       <c r="G146" t="n">
-        <v>9.4815731048584</v>
+        <v>9.48157215118408</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.52228832244873</v>
+        <v>8.52228736877441</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>10.3269319534302</v>
       </c>
       <c r="G159" t="n">
-        <v>9.15661716461182</v>
+        <v>9.15661811828613</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.98303604125977</v>
       </c>
       <c r="G164" t="n">
-        <v>8.85169315338135</v>
+        <v>8.85169410705566</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>10.4449110031128</v>
       </c>
       <c r="G165" t="n">
-        <v>9.26122570037842</v>
+        <v>9.26122665405273</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548778533936</v>
+        <v>9.14548873901367</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>10.457462310791</v>
       </c>
       <c r="G174" t="n">
-        <v>9.2723560333252</v>
+        <v>9.27235507965088</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.79225063323975</v>
+        <v>7.79224967956543</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.91871356964111</v>
       </c>
       <c r="G189" t="n">
-        <v>7.90798664093018</v>
+        <v>7.90798759460449</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.73883247375488</v>
+        <v>7.7388334274292</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.063362121582</v>
       </c>
       <c r="G200" t="n">
-        <v>8.92291736602783</v>
+        <v>8.92291641235352</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>10.1662797927856</v>
       </c>
       <c r="G202" t="n">
-        <v>9.0141716003418</v>
+        <v>9.01417064666748</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G207" t="n">
-        <v>9.68856525421143</v>
+        <v>9.68856430053711</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>10.9519701004028</v>
       </c>
       <c r="G208" t="n">
-        <v>9.71082210540771</v>
+        <v>9.71082305908203</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.22244834899902</v>
       </c>
       <c r="G216" t="n">
-        <v>8.17730140686035</v>
+        <v>8.17730045318604</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G220" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G221" t="n">
-        <v>8.73373126983643</v>
+        <v>8.73373031616211</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G232" t="n">
-        <v>9.16329383850098</v>
+        <v>9.16329479217529</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G233" t="n">
-        <v>8.92514324188232</v>
+        <v>8.92514228820801</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.6457271575928</v>
       </c>
       <c r="G236" t="n">
-        <v>9.439284324646</v>
+        <v>9.43928527832031</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.4088249206543</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1159029006958</v>
+        <v>10.1159038543701</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>12.8772878646851</v>
       </c>
       <c r="G253" t="n">
-        <v>11.4179496765137</v>
+        <v>11.417950630188</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>13.0906553268433</v>
       </c>
       <c r="G254" t="n">
-        <v>11.6071376800537</v>
+        <v>11.607138633728</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076099395752</v>
+        <v>11.9076108932495</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>13.9817733764648</v>
       </c>
       <c r="G260" t="n">
-        <v>12.3972692489624</v>
+        <v>12.3972682952881</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619920730591</v>
+        <v>11.1619930267334</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960083007812</v>
+        <v>11.5960092544556</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G280" t="n">
-        <v>10.5276622772217</v>
+        <v>10.5276613235474</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141492843628</v>
+        <v>10.4141502380371</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.39857006073</v>
+        <v>10.3985710144043</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.6874570846558</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3629579544067</v>
+        <v>10.3629589080811</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>10.5754413604736</v>
       </c>
       <c r="G298" t="n">
-        <v>9.3769645690918</v>
+        <v>9.37696361541748</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.6632976531982</v>
       </c>
       <c r="G301" t="n">
-        <v>9.45486354827881</v>
+        <v>9.45486450195312</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G313" t="n">
-        <v>9.01639747619629</v>
+        <v>9.01639652252197</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G319" t="n">
-        <v>9.39254474639893</v>
+        <v>9.39254379272461</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77981948852539</v>
+        <v>9.77981853485107</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G325" t="n">
-        <v>9.51050662994385</v>
+        <v>9.51050758361816</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>10.7310733795166</v>
       </c>
       <c r="G326" t="n">
-        <v>9.51495838165283</v>
+        <v>9.51495933532715</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.7671594619751</v>
       </c>
       <c r="G335" t="n">
-        <v>8.66028118133545</v>
+        <v>8.66028213500977</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G342" t="n">
-        <v>8.85837173461914</v>
+        <v>8.85837268829346</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G346" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10.003116607666</v>
       </c>
       <c r="G349" t="n">
-        <v>8.86949920654297</v>
+        <v>8.86949825286865</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.80481243133545</v>
       </c>
       <c r="G354" t="n">
-        <v>8.6936674118042</v>
+        <v>8.69366836547852</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G362" t="n">
-        <v>8.0348539352417</v>
+        <v>8.03485488891602</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G366" t="n">
-        <v>7.66093349456787</v>
+        <v>7.66093397140503</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.13302421569824</v>
       </c>
       <c r="G377" t="n">
-        <v>7.21133708953857</v>
+        <v>7.21133661270142</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G378" t="n">
-        <v>7.18017721176147</v>
+        <v>7.18017673492432</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>8.07779979705811</v>
       </c>
       <c r="G380" t="n">
-        <v>7.16237163543701</v>
+        <v>7.16237115859985</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914218902588</v>
+        <v>7.22914266586304</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817150115967</v>
+        <v>7.31817245483398</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055559158325</v>
+        <v>7.42055511474609</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390893936157</v>
+        <v>7.43390846252441</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.85679578781128</v>
+        <v>7.8567967414856</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>8.52461433410645</v>
       </c>
       <c r="G397" t="n">
-        <v>7.55854988098145</v>
+        <v>7.5585503578186</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842359542847</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G403" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757871627808</v>
+        <v>7.64757919311523</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G408" t="n">
-        <v>7.58525800704956</v>
+        <v>7.5852575302124</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428731918335</v>
+        <v>7.67428636550903</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.5748176574707</v>
       </c>
       <c r="G411" t="n">
-        <v>7.60306406021118</v>
+        <v>7.60306453704834</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249744415283</v>
+        <v>7.24249792098999</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701162338257</v>
+        <v>7.28701210021973</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G416" t="n">
-        <v>7.26475429534912</v>
+        <v>7.26475477218628</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.61592388153076</v>
       </c>
       <c r="G422" t="n">
-        <v>6.75283813476562</v>
+        <v>6.75283861160278</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>7.68621015548706</v>
       </c>
       <c r="G424" t="n">
-        <v>6.81515884399414</v>
+        <v>6.8151593208313</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.40004777908325</v>
       </c>
       <c r="G426" t="n">
-        <v>6.56142616271973</v>
+        <v>6.56142663955688</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.93979835510254</v>
+        <v>6.9397988319397</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.74645376205444</v>
       </c>
       <c r="G428" t="n">
-        <v>6.86857604980469</v>
+        <v>6.86857557296753</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.76151514053345</v>
       </c>
       <c r="G429" t="n">
-        <v>6.88192987442017</v>
+        <v>6.88193035125732</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G432" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591417312622</v>
+        <v>7.29591369628906</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409908294678</v>
+        <v>7.55409860610962</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G439" t="n">
-        <v>7.58525800704956</v>
+        <v>7.5852575302124</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.66538429260254</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.10697937011719</v>
       </c>
       <c r="G444" t="n">
-        <v>8.07491779327393</v>
+        <v>8.07491683959961</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.10195827484131</v>
       </c>
       <c r="G445" t="n">
-        <v>8.07046604156494</v>
+        <v>8.07046508789062</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504264831543</v>
+        <v>8.15504360198975</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G462" t="n">
-        <v>7.38939523696899</v>
+        <v>7.38939476013184</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.66538429260254</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.49354839324951</v>
       </c>
       <c r="G478" t="n">
-        <v>8.41767883300781</v>
+        <v>8.4176778793335</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757871627808</v>
+        <v>7.64757919311523</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576219558716</v>
+        <v>7.90576314926147</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344148635864</v>
+        <v>7.84344244003296</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>8.60494041442871</v>
       </c>
       <c r="G488" t="n">
-        <v>7.62977313995361</v>
+        <v>7.62977266311646</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.74996185302734</v>
+        <v>7.74996280670166</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>9.34795665740967</v>
       </c>
       <c r="G508" t="n">
-        <v>8.2885856628418</v>
+        <v>8.28858661651611</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.61403846740723</v>
       </c>
       <c r="G510" t="n">
-        <v>8.52451419830322</v>
+        <v>8.52451324462891</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.5022554397583</v>
+        <v>8.50225639343262</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G514" t="n">
-        <v>8.73373126983643</v>
+        <v>8.73373031616211</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G517" t="n">
-        <v>8.76043891906738</v>
+        <v>8.7604398727417</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.76464939117432</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65805530548096</v>
+        <v>8.65805625915527</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>10.1210966110229</v>
       </c>
       <c r="G519" t="n">
-        <v>8.9741096496582</v>
+        <v>8.97410869598389</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>10.1813411712646</v>
       </c>
       <c r="G524" t="n">
-        <v>9.02752685546875</v>
+        <v>9.02752590179443</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G528" t="n">
-        <v>9.1655216217041</v>
+        <v>9.16552066802979</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G529" t="n">
-        <v>9.04087924957275</v>
+        <v>9.04088020324707</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G530" t="n">
-        <v>9.04087924957275</v>
+        <v>9.04088020324707</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833980560303</v>
+        <v>8.83833885192871</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>9.46593570709229</v>
       </c>
       <c r="G533" t="n">
-        <v>8.3931941986084</v>
+        <v>8.39319515228271</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.41990566253662</v>
+        <v>8.4199047088623</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G538" t="n">
-        <v>8.0348539352417</v>
+        <v>8.03485488891602</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660612106323</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519605636597</v>
+        <v>7.54519557952881</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G545" t="n">
-        <v>7.66093349456787</v>
+        <v>7.66093397140503</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G548" t="n">
-        <v>7.60083866119385</v>
+        <v>7.60083913803101</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.7633171081543</v>
+        <v>7.76331615447998</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.52293872833252</v>
+        <v>7.52293825149536</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368877410889</v>
+        <v>7.29368829727173</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.56979656219482</v>
       </c>
       <c r="G558" t="n">
-        <v>7.5986123085022</v>
+        <v>7.59861183166504</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663805007935</v>
+        <v>7.75663900375366</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G560" t="n">
-        <v>7.75218725204468</v>
+        <v>7.75218820571899</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613433837891</v>
+        <v>7.43613481521606</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585126876831</v>
+        <v>7.25585079193115</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.32128810882568</v>
       </c>
       <c r="G567" t="n">
-        <v>7.37826585769653</v>
+        <v>7.37826633453369</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>8.43173694610596</v>
       </c>
       <c r="G568" t="n">
-        <v>7.47619819641113</v>
+        <v>7.47619771957397</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>8.17820739746094</v>
       </c>
       <c r="G570" t="n">
-        <v>7.25140047073364</v>
+        <v>7.25139999389648</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G573" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G578" t="n">
-        <v>6.98876523971558</v>
+        <v>6.98876571655273</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744667053223</v>
+        <v>6.85744714736938</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G581" t="n">
-        <v>7.08892202377319</v>
+        <v>7.08892250061035</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G583" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G585" t="n">
-        <v>7.18017721176147</v>
+        <v>7.18017673492432</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G586" t="n">
-        <v>7.48064947128296</v>
+        <v>7.4806489944458</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842359542847</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G589" t="n">
-        <v>7.48064947128296</v>
+        <v>7.4806489944458</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G590" t="n">
-        <v>7.26475429534912</v>
+        <v>7.26475477218628</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G591" t="n">
-        <v>6.98876523971558</v>
+        <v>6.98876571655273</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766778945923</v>
+        <v>6.99766731262207</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>7.92969799041748</v>
       </c>
       <c r="G596" t="n">
-        <v>7.03105306625366</v>
+        <v>7.03105354309082</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.06022834777832</v>
       </c>
       <c r="G599" t="n">
-        <v>7.14679145812988</v>
+        <v>7.14679098129272</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G601" t="n">
-        <v>7.38939523696899</v>
+        <v>7.38939476013184</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.55222606658936</v>
       </c>
       <c r="G603" t="n">
-        <v>7.58303260803223</v>
+        <v>7.58303213119507</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.83242416381836</v>
       </c>
       <c r="G605" t="n">
-        <v>8.7181510925293</v>
+        <v>8.71815013885498</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G607" t="n">
-        <v>8.54009342193604</v>
+        <v>8.54009246826172</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>10.0909738540649</v>
       </c>
       <c r="G609" t="n">
-        <v>8.9473991394043</v>
+        <v>8.94740009307861</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065380096436</v>
+        <v>8.19065475463867</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.31783485412598</v>
       </c>
       <c r="G620" t="n">
-        <v>8.26187896728516</v>
+        <v>8.26187801361084</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>9.85250568389893</v>
       </c>
       <c r="G623" t="n">
-        <v>8.7359561920166</v>
+        <v>8.73595523834229</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G629" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>9.36552906036377</v>
       </c>
       <c r="G630" t="n">
-        <v>8.30416679382324</v>
+        <v>8.30416774749756</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.7114725112915</v>
+        <v>8.71147346496582</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009632110596</v>
+        <v>9.25009727478027</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G646" t="n">
-        <v>9.39254474639893</v>
+        <v>9.39254379272461</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G650" t="n">
-        <v>9.01639747619629</v>
+        <v>9.01639652252197</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G651" t="n">
-        <v>9.0564603805542</v>
+        <v>9.05646133422852</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100601196289</v>
+        <v>9.12100505828857</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>11.200478553772</v>
       </c>
       <c r="G668" t="n">
-        <v>9.93116855621338</v>
+        <v>9.93116760253906</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G671" t="n">
-        <v>9.80652809143066</v>
+        <v>9.80652904510498</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G678" t="n">
-        <v>10.0157451629639</v>
+        <v>10.0157461166382</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G684" t="n">
-        <v>10.3340244293213</v>
+        <v>10.334023475647</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99348926544189</v>
+        <v>9.99349021911621</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694797515869</v>
+        <v>10.2694787979126</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>11.9259252548218</v>
       </c>
       <c r="G689" t="n">
-        <v>10.5744028091431</v>
+        <v>10.5744018554688</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G693" t="n">
-        <v>10.8259086608887</v>
+        <v>10.8259077072144</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.756911277771</v>
+        <v>10.7569122314453</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>13.2086343765259</v>
       </c>
       <c r="G699" t="n">
-        <v>11.7117462158203</v>
+        <v>11.7117471694946</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>13.5500202178955</v>
       </c>
       <c r="G702" t="n">
-        <v>12.014443397522</v>
+        <v>12.0144443511963</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>12.7618188858032</v>
       </c>
       <c r="G709" t="n">
-        <v>11.3155670166016</v>
+        <v>11.3155679702759</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395774841309</v>
+        <v>11.0395784378052</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>12.7065954208374</v>
       </c>
       <c r="G712" t="n">
-        <v>11.2666015625</v>
+        <v>11.2666025161743</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>12.3325757980347</v>
       </c>
       <c r="G714" t="n">
-        <v>10.9349689483643</v>
+        <v>10.9349699020386</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>11.8004150390625</v>
       </c>
       <c r="G715" t="n">
-        <v>10.4631156921387</v>
+        <v>10.463116645813</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364080429077</v>
+        <v>10.4364070892334</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G719" t="n">
-        <v>10.549919128418</v>
+        <v>10.5499200820923</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>11.7979049682617</v>
       </c>
       <c r="G721" t="n">
-        <v>10.4608898162842</v>
+        <v>10.4608907699585</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>11.8857622146606</v>
       </c>
       <c r="G723" t="n">
-        <v>10.5387916564941</v>
+        <v>10.5387907028198</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G724" t="n">
-        <v>10.7613620758057</v>
+        <v>10.76136302948</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449960708618</v>
+        <v>10.2449951171875</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>11.7251100540161</v>
       </c>
       <c r="G730" t="n">
-        <v>10.3963441848755</v>
+        <v>10.3963451385498</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G737" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G738" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081153869629</v>
+        <v>8.29081249237061</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889633178711</v>
+        <v>7.77889537811279</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219253540039</v>
+        <v>8.46219158172607</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G750" t="n">
-        <v>8.18842887878418</v>
+        <v>8.1884298324585</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G754" t="n">
-        <v>8.29526329040527</v>
+        <v>8.29526424407959</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G759" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>8.12800407409668</v>
       </c>
       <c r="G761" t="n">
-        <v>7.20688629150391</v>
+        <v>7.20688581466675</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873378753662</v>
+        <v>6.96873331069946</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576219558716</v>
+        <v>7.90576314926147</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>9.12957000732422</v>
       </c>
       <c r="G767" t="n">
-        <v>8.09494781494141</v>
+        <v>8.09494876861572</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G771" t="n">
-        <v>8.39764595031738</v>
+        <v>8.3976469039917</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>10.2817487716675</v>
       </c>
       <c r="G786" t="n">
-        <v>9.11655521392822</v>
+        <v>9.11655426025391</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>10.4298496246338</v>
       </c>
       <c r="G789" t="n">
-        <v>9.24787139892578</v>
+        <v>9.2478723526001</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>10.7963380813599</v>
       </c>
       <c r="G797" t="n">
-        <v>9.57282733917236</v>
+        <v>9.57282638549805</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>10.8440322875977</v>
       </c>
       <c r="G803" t="n">
-        <v>9.61511611938477</v>
+        <v>9.61511707305908</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G804" t="n">
-        <v>9.69746780395508</v>
+        <v>9.69746875762939</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232891082764</v>
+        <v>9.96232986450195</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496046066284</v>
+        <v>10.3496036529541</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>11.8882722854614</v>
       </c>
       <c r="G809" t="n">
-        <v>10.5410165786743</v>
+        <v>10.541015625</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G812" t="n">
-        <v>10.5276622772217</v>
+        <v>10.5276613235474</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>12.3150053024292</v>
       </c>
       <c r="G815" t="n">
-        <v>10.9193887710571</v>
+        <v>10.9193897247314</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.3350868225098</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9371948242188</v>
+        <v>10.9371957778931</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G820" t="n">
-        <v>10.8259086608887</v>
+        <v>10.8259077072144</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>11.5368452072144</v>
       </c>
       <c r="G822" t="n">
-        <v>10.2294158935547</v>
+        <v>10.2294149398804</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G825" t="n">
-        <v>10.3340244293213</v>
+        <v>10.334023475647</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147802352905</v>
+        <v>10.8147811889648</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>12.2522497177124</v>
       </c>
       <c r="G829" t="n">
-        <v>10.8637447357178</v>
+        <v>10.8637456893921</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G830" t="n">
-        <v>10.7613620758057</v>
+        <v>10.76136302948</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>12.4856977462769</v>
       </c>
       <c r="G831" t="n">
-        <v>11.0707368850708</v>
+        <v>11.0707378387451</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>12.6312885284424</v>
       </c>
       <c r="G832" t="n">
-        <v>11.1998300552368</v>
+        <v>11.1998291015625</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>12.0991277694702</v>
       </c>
       <c r="G834" t="n">
-        <v>10.7279777526855</v>
+        <v>10.7279767990112</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G835" t="n">
-        <v>10.4386339187622</v>
+        <v>10.4386329650879</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295736312866</v>
+        <v>10.3295726776123</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>11.5343351364136</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2271909713745</v>
+        <v>10.2271900177002</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G839" t="n">
-        <v>10.4386339187622</v>
+        <v>10.4386329650879</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G842" t="n">
-        <v>10.549919128418</v>
+        <v>10.5499200820923</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>11.3912544250488</v>
       </c>
       <c r="G844" t="n">
-        <v>10.100323677063</v>
+        <v>10.1003246307373</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>10.836501121521</v>
       </c>
       <c r="G849" t="n">
-        <v>9.60843849182129</v>
+        <v>9.60843944549561</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G858" t="n">
-        <v>9.2701301574707</v>
+        <v>9.27012920379639</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G859" t="n">
-        <v>9.16329383850098</v>
+        <v>9.16329479217529</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G867" t="n">
-        <v>8.76043891906738</v>
+        <v>8.7604398727417</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395671844482</v>
+        <v>9.58395576477051</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G878" t="n">
-        <v>9.2701301574707</v>
+        <v>9.27012920379639</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G880" t="n">
-        <v>9.55947208404541</v>
+        <v>9.55947303771973</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G881" t="n">
-        <v>9.6062126159668</v>
+        <v>9.60621356964111</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>11.0699491500854</v>
       </c>
       <c r="G883" t="n">
-        <v>9.81543064117432</v>
+        <v>9.81543159484863</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079208374023</v>
+        <v>9.69079113006592</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.0498676300049</v>
       </c>
       <c r="G887" t="n">
-        <v>9.79762554168701</v>
+        <v>9.79762649536133</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.2431526184082</v>
       </c>
       <c r="G889" t="n">
-        <v>9.96900653839111</v>
+        <v>9.9690055847168</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G890" t="n">
-        <v>9.69746780395508</v>
+        <v>9.69746875762939</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>11.0272760391235</v>
       </c>
       <c r="G893" t="n">
-        <v>9.77759456634521</v>
+        <v>9.7775936126709</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304798126221</v>
+        <v>9.71304893493652</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>11.0423374176025</v>
       </c>
       <c r="G905" t="n">
-        <v>9.79094886779785</v>
+        <v>9.79094791412354</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G906" t="n">
-        <v>10.0157451629639</v>
+        <v>10.0157461166382</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794006347656</v>
+        <v>9.99794101715088</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G916" t="n">
-        <v>8.92514324188232</v>
+        <v>8.92514228820801</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G919" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.95185089111328</v>
+        <v>8.9518518447876</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>10.4474220275879</v>
       </c>
       <c r="G925" t="n">
-        <v>9.26345252990723</v>
+        <v>9.26345348358154</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>10.2842588424683</v>
       </c>
       <c r="G927" t="n">
-        <v>9.11878108978271</v>
+        <v>9.1187801361084</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>10.3545436859131</v>
       </c>
       <c r="G928" t="n">
-        <v>9.18110084533691</v>
+        <v>9.1810998916626</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>10.9092969894409</v>
       </c>
       <c r="G931" t="n">
-        <v>9.67298603057861</v>
+        <v>9.6729850769043</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>10.9067869186401</v>
       </c>
       <c r="G933" t="n">
-        <v>9.67076015472412</v>
+        <v>9.6707592010498</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G937" t="n">
-        <v>9.80652809143066</v>
+        <v>9.80652904510498</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136770248413</v>
+        <v>10.1136779785156</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403875350952</v>
+        <v>10.1403865814209</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230537414551</v>
+        <v>10.4230527877808</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.881685256958</v>
       </c>
       <c r="G948" t="n">
-        <v>9.64850234985352</v>
+        <v>9.64850330352783</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>10.7862977981567</v>
       </c>
       <c r="G949" t="n">
-        <v>9.56392383575439</v>
+        <v>9.56392478942871</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>10.2164840698242</v>
       </c>
       <c r="G954" t="n">
-        <v>9.05868530273438</v>
+        <v>9.05868625640869</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>10.0683822631836</v>
       </c>
       <c r="G955" t="n">
-        <v>8.9273681640625</v>
+        <v>8.92736721038818</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G958" t="n">
-        <v>9.1655216217041</v>
+        <v>9.16552066802979</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>10.3294429779053</v>
       </c>
       <c r="G968" t="n">
-        <v>9.15884304046631</v>
+        <v>9.15884399414062</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>10.2792387008667</v>
       </c>
       <c r="G969" t="n">
-        <v>9.11433029174805</v>
+        <v>9.11432933807373</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G974" t="n">
-        <v>9.51050662994385</v>
+        <v>9.51050758361816</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G978" t="n">
-        <v>9.6062126159668</v>
+        <v>9.60621356964111</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>11.1402349472046</v>
       </c>
       <c r="G982" t="n">
-        <v>9.87775230407715</v>
+        <v>9.87775135040283</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>11.0573978424072</v>
       </c>
       <c r="G983" t="n">
-        <v>9.80430126190186</v>
+        <v>9.80430221557617</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812492370605</v>
+        <v>9.40812397003174</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G994" t="n">
-        <v>9.45931529998779</v>
+        <v>9.45931625366211</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G999" t="n">
-        <v>9.0564603805542</v>
+        <v>9.05646133422852</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>10.427339553833</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.24564552307129</v>
+        <v>9.24564647674561</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.39254474639893</v>
+        <v>9.39254379272461</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467578887939</v>
+        <v>9.33467674255371</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G1008" t="n">
-        <v>9.45931529998779</v>
+        <v>9.45931625366211</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>10.7938280105591</v>
       </c>
       <c r="G1009" t="n">
-        <v>9.57060241699219</v>
+        <v>9.57060146331787</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821880340576</v>
+        <v>9.46821784973145</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.5616979598999</v>
+        <v>9.56169891357422</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85771942138672</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>11.1728668212891</v>
       </c>
       <c r="G1019" t="n">
-        <v>9.90668487548828</v>
+        <v>9.9066858291626</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>11.1678466796875</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.90223407745361</v>
+        <v>9.90223503112793</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.80207633972168</v>
+        <v>9.802077293396</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.9028844833374</v>
+        <v>8.90288543701172</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.20623397827148</v>
+        <v>8.2062349319458</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>9.51362991333008</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.43548488616943</v>
+        <v>8.43548393249512</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754774093628</v>
+        <v>7.62754726409912</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.60083866119385</v>
+        <v>7.60083913803101</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>8.3037166595459</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.36268615722656</v>
+        <v>7.36268663406372</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585126876831</v>
+        <v>7.25585079193115</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.70832347869873</v>
+        <v>6.70832395553589</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>5.16848611831665</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.58276033401489</v>
+        <v>4.58275985717773</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>5.16346597671509</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.57830858230591</v>
+        <v>4.57830905914307</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342130661011</v>
+        <v>5.00342178344727</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.8899097442627</v>
+        <v>4.88990926742554</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>5.8261570930481</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.16589975357056</v>
+        <v>5.1658992767334</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1078" t="n">
-        <v>4.98561573028564</v>
+        <v>4.98561525344849</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1079" t="n">
-        <v>4.98561573028564</v>
+        <v>4.98561525344849</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.06713485717773</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.37956762313843</v>
+        <v>5.37956809997559</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>5.95919704437256</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.28386211395264</v>
+        <v>5.28386259078979</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.0219521522522</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.33950614929199</v>
+        <v>5.33950567245483</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>5.9014630317688</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.23267078399658</v>
+        <v>5.23267126083374</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>6.04956388473511</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.36398887634277</v>
+        <v>5.36398839950562</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>5.47473001480103</v>
       </c>
       <c r="G1089" t="n">
-        <v>4.85429811477661</v>
+        <v>4.85429859161377</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.95445489883423</v>
+        <v>4.95445537567139</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871793746948</v>
+        <v>4.83871746063232</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928503036499</v>
+        <v>5.19928550720215</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041393280029</v>
+        <v>5.21041345596313</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470746994019</v>
+        <v>5.11470699310303</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248207092285</v>
+        <v>5.11248159408569</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>5.57513809204102</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.9433274269104</v>
+        <v>4.94332695007324</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -69272,6 +69272,32 @@
         <v>4.44899988174438</v>
       </c>
       <c r="H2650" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2651">
+      <c r="A2651" s="1" t="n">
+        <v>46182.2916666667</v>
+      </c>
+      <c r="B2651" t="n">
+        <v>18077322</v>
+      </c>
+      <c r="C2651" t="n">
+        <v>4.51599979400635</v>
+      </c>
+      <c r="D2651" t="n">
+        <v>4.39599990844727</v>
+      </c>
+      <c r="E2651" t="n">
+        <v>4.45599985122681</v>
+      </c>
+      <c r="F2651" t="n">
+        <v>4.40500020980835</v>
+      </c>
+      <c r="G2651" t="n">
+        <v>4.40500020980835</v>
+      </c>
+      <c r="H2651" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -473,7 +473,7 @@
         <v>22.3245735168457</v>
       </c>
       <c r="G4" t="n">
-        <v>19.7946090698242</v>
+        <v>19.7946071624756</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>21.3766078948975</v>
       </c>
       <c r="G6" t="n">
-        <v>18.9540748596191</v>
+        <v>18.9540729522705</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>22.1665782928467</v>
       </c>
       <c r="G9" t="n">
-        <v>19.65452003479</v>
+        <v>19.6545181274414</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>19.8440647125244</v>
       </c>
       <c r="G12" t="n">
-        <v>17.5952072143555</v>
+        <v>17.5952091217041</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811977386475</v>
+        <v>17.5811958312988</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460269927979</v>
+        <v>15.7460289001465</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>13.806058883667</v>
       </c>
       <c r="G19" t="n">
-        <v>12.2414665222168</v>
+        <v>12.2414674758911</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>13.5048360824585</v>
       </c>
       <c r="G24" t="n">
-        <v>11.9743814468384</v>
+        <v>11.9743804931641</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617107391357</v>
+        <v>8.16617202758789</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G30" t="n">
-        <v>7.08892250061035</v>
+        <v>7.08892202377319</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G31" t="n">
-        <v>6.70832395553589</v>
+        <v>6.70832347869873</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.87747859954834</v>
+        <v>6.8774790763855</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51181030273438</v>
+        <v>7.51180982589722</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.96546459197998</v>
       </c>
       <c r="G46" t="n">
-        <v>8.83611297607422</v>
+        <v>8.83611392974854</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.0771427154541</v>
+        <v>8.07714366912842</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811292648315</v>
+        <v>7.98811388015747</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G53" t="n">
-        <v>8.29526424407959</v>
+        <v>8.29526329040527</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.26261138916016</v>
       </c>
       <c r="G54" t="n">
-        <v>8.21291255950928</v>
+        <v>8.21291351318359</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.31752109527588</v>
+        <v>8.3175220489502</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G59" t="n">
-        <v>8.2062349319458</v>
+        <v>8.20623397827148</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G60" t="n">
-        <v>7.75218820571899</v>
+        <v>7.75218725204468</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.34487962722778</v>
+        <v>7.3448805809021</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870761871338</v>
+        <v>7.65870809555054</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365779876709</v>
+        <v>7.27365732192993</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.86347341537476</v>
+        <v>7.86347436904907</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09940052032471</v>
+        <v>8.09939956665039</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.87102127075195</v>
       </c>
       <c r="G74" t="n">
-        <v>7.86569976806641</v>
+        <v>7.86570072174072</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.25006008148193</v>
       </c>
       <c r="G79" t="n">
-        <v>8.20178413391113</v>
+        <v>8.20178318023682</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912082672119</v>
+        <v>8.62912178039551</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G86" t="n">
-        <v>8.54009246826172</v>
+        <v>8.54009342193604</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.36803913116455</v>
       </c>
       <c r="G90" t="n">
-        <v>8.30639266967773</v>
+        <v>8.30639171600342</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.20487594604492</v>
       </c>
       <c r="G91" t="n">
-        <v>8.16171932220459</v>
+        <v>8.16172027587891</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.26855373382568</v>
+        <v>8.2685546875</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542102813721</v>
+        <v>8.39542007446289</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588752746582</v>
+        <v>7.98588848114014</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701738357544</v>
+        <v>7.99701642990112</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G103" t="n">
-        <v>8.3976469039917</v>
+        <v>8.39764595031738</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.3303861618042</v>
       </c>
       <c r="G105" t="n">
-        <v>8.27300548553467</v>
+        <v>8.27300643920898</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G106" t="n">
-        <v>8.1884298324585</v>
+        <v>8.18842887878418</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889537811279</v>
+        <v>7.77889633178711</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701738357544</v>
+        <v>7.99701642990112</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G112" t="n">
-        <v>8.85837268829346</v>
+        <v>8.85837173461914</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660707473755</v>
+        <v>7.73660612106323</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808195114136</v>
+        <v>7.96808290481567</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G119" t="n">
-        <v>8.2062349319458</v>
+        <v>8.20623397827148</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.8851375579834</v>
       </c>
       <c r="G122" t="n">
-        <v>8.76488971710205</v>
+        <v>8.76489067077637</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.05933666229248</v>
+        <v>8.0593376159668</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.71147346496582</v>
+        <v>8.7114725112915</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420257568359</v>
+        <v>9.03420352935791</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G141" t="n">
-        <v>9.55947303771973</v>
+        <v>9.55947208404541</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G144" t="n">
-        <v>9.68856430053711</v>
+        <v>9.68856525421143</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>10.6934204101562</v>
       </c>
       <c r="G146" t="n">
-        <v>9.48157215118408</v>
+        <v>9.4815731048584</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.52228736877441</v>
+        <v>8.52228832244873</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>10.3269319534302</v>
       </c>
       <c r="G159" t="n">
-        <v>9.15661811828613</v>
+        <v>9.15661716461182</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.98303604125977</v>
       </c>
       <c r="G164" t="n">
-        <v>8.85169410705566</v>
+        <v>8.85169315338135</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>10.4449110031128</v>
       </c>
       <c r="G165" t="n">
-        <v>9.26122665405273</v>
+        <v>9.26122570037842</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548873901367</v>
+        <v>9.14548778533936</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>10.457462310791</v>
       </c>
       <c r="G174" t="n">
-        <v>9.27235507965088</v>
+        <v>9.2723560333252</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.78818416595459</v>
       </c>
       <c r="G185" t="n">
-        <v>7.79224967956543</v>
+        <v>7.79225063323975</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.91871356964111</v>
       </c>
       <c r="G189" t="n">
-        <v>7.90798759460449</v>
+        <v>7.90798664093018</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.7388334274292</v>
+        <v>7.73883247375488</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.063362121582</v>
       </c>
       <c r="G200" t="n">
-        <v>8.92291641235352</v>
+        <v>8.92291736602783</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>10.1662797927856</v>
       </c>
       <c r="G202" t="n">
-        <v>9.01417064666748</v>
+        <v>9.0141716003418</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.9268684387207</v>
       </c>
       <c r="G207" t="n">
-        <v>9.68856430053711</v>
+        <v>9.68856525421143</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>10.9519701004028</v>
       </c>
       <c r="G208" t="n">
-        <v>9.71082305908203</v>
+        <v>9.71082210540771</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.22244834899902</v>
       </c>
       <c r="G216" t="n">
-        <v>8.17730045318604</v>
+        <v>8.17730140686035</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G220" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G221" t="n">
-        <v>8.73373031616211</v>
+        <v>8.73373126983643</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G232" t="n">
-        <v>9.16329479217529</v>
+        <v>9.16329383850098</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G233" t="n">
-        <v>8.92514228820801</v>
+        <v>8.92514324188232</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.6457271575928</v>
       </c>
       <c r="G236" t="n">
-        <v>9.43928527832031</v>
+        <v>9.439284324646</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.4088249206543</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1159038543701</v>
+        <v>10.1159029006958</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>12.8772878646851</v>
       </c>
       <c r="G253" t="n">
-        <v>11.417950630188</v>
+        <v>11.4179496765137</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>13.0906553268433</v>
       </c>
       <c r="G254" t="n">
-        <v>11.607138633728</v>
+        <v>11.6071376800537</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076108932495</v>
+        <v>11.9076099395752</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>13.9817733764648</v>
       </c>
       <c r="G260" t="n">
-        <v>12.3972682952881</v>
+        <v>12.3972692489624</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619930267334</v>
+        <v>11.1619920730591</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960092544556</v>
+        <v>11.5960083007812</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G280" t="n">
-        <v>10.5276613235474</v>
+        <v>10.5276622772217</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141502380371</v>
+        <v>10.4141492843628</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.3985710144043</v>
+        <v>10.39857006073</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.6874570846558</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3629589080811</v>
+        <v>10.3629579544067</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>10.5754413604736</v>
       </c>
       <c r="G298" t="n">
-        <v>9.37696361541748</v>
+        <v>9.3769645690918</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.6632976531982</v>
       </c>
       <c r="G301" t="n">
-        <v>9.45486450195312</v>
+        <v>9.45486354827881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G313" t="n">
-        <v>9.01639652252197</v>
+        <v>9.01639747619629</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G319" t="n">
-        <v>9.39254379272461</v>
+        <v>9.39254474639893</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77981853485107</v>
+        <v>9.77981948852539</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G325" t="n">
-        <v>9.51050758361816</v>
+        <v>9.51050662994385</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>10.7310733795166</v>
       </c>
       <c r="G326" t="n">
-        <v>9.51495933532715</v>
+        <v>9.51495838165283</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.7671594619751</v>
       </c>
       <c r="G335" t="n">
-        <v>8.66028213500977</v>
+        <v>8.66028118133545</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.99056720733643</v>
       </c>
       <c r="G342" t="n">
-        <v>8.85837268829346</v>
+        <v>8.85837173461914</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G346" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10.003116607666</v>
       </c>
       <c r="G349" t="n">
-        <v>8.86949825286865</v>
+        <v>8.86949920654297</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.80481243133545</v>
       </c>
       <c r="G354" t="n">
-        <v>8.69366836547852</v>
+        <v>8.6936674118042</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.2930383682251</v>
+        <v>8.29303741455078</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G362" t="n">
-        <v>8.03485488891602</v>
+        <v>8.0348539352417</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G366" t="n">
-        <v>7.66093397140503</v>
+        <v>7.66093349456787</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.13302421569824</v>
       </c>
       <c r="G377" t="n">
-        <v>7.21133661270142</v>
+        <v>7.21133708953857</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G378" t="n">
-        <v>7.18017673492432</v>
+        <v>7.18017721176147</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>8.07779979705811</v>
       </c>
       <c r="G380" t="n">
-        <v>7.16237115859985</v>
+        <v>7.16237163543701</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914266586304</v>
+        <v>7.22914218902588</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817245483398</v>
+        <v>7.31817150115967</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055511474609</v>
+        <v>7.42055559158325</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390846252441</v>
+        <v>7.43390893936157</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.8567967414856</v>
+        <v>7.85679578781128</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>8.52461433410645</v>
       </c>
       <c r="G397" t="n">
-        <v>7.5585503578186</v>
+        <v>7.55854988098145</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842359542847</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G403" t="n">
-        <v>7.59416151046753</v>
+        <v>7.59416103363037</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757919311523</v>
+        <v>7.64757871627808</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G408" t="n">
-        <v>7.5852575302124</v>
+        <v>7.58525800704956</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428636550903</v>
+        <v>7.67428731918335</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.5748176574707</v>
       </c>
       <c r="G411" t="n">
-        <v>7.60306453704834</v>
+        <v>7.60306406021118</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249792098999</v>
+        <v>7.24249744415283</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701210021973</v>
+        <v>7.28701162338257</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G416" t="n">
-        <v>7.26475477218628</v>
+        <v>7.26475429534912</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.61592388153076</v>
       </c>
       <c r="G422" t="n">
-        <v>6.75283861160278</v>
+        <v>6.75283813476562</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>7.68621015548706</v>
       </c>
       <c r="G424" t="n">
-        <v>6.8151593208313</v>
+        <v>6.81515884399414</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.40004777908325</v>
       </c>
       <c r="G426" t="n">
-        <v>6.56142663955688</v>
+        <v>6.56142616271973</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.9397988319397</v>
+        <v>6.93979835510254</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.74645376205444</v>
       </c>
       <c r="G428" t="n">
-        <v>6.86857557296753</v>
+        <v>6.86857604980469</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.76151514053345</v>
       </c>
       <c r="G429" t="n">
-        <v>6.88193035125732</v>
+        <v>6.88192987442017</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G432" t="n">
-        <v>7.22469091415405</v>
+        <v>7.22469139099121</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.2284107208252</v>
       </c>
       <c r="G434" t="n">
-        <v>7.29591369628906</v>
+        <v>7.29591417312622</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409860610962</v>
+        <v>7.55409908294678</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.55473613739014</v>
       </c>
       <c r="G439" t="n">
-        <v>7.5852575302124</v>
+        <v>7.58525800704956</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538429260254</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.10697937011719</v>
       </c>
       <c r="G444" t="n">
-        <v>8.07491683959961</v>
+        <v>8.07491779327393</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.10195827484131</v>
       </c>
       <c r="G445" t="n">
-        <v>8.07046508789062</v>
+        <v>8.07046604156494</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504360198975</v>
+        <v>8.15504264831543</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G462" t="n">
-        <v>7.38939476013184</v>
+        <v>7.38939523696899</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.6653847694397</v>
+        <v>7.66538429260254</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.49354839324951</v>
       </c>
       <c r="G478" t="n">
-        <v>8.4176778793335</v>
+        <v>8.41767883300781</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757919311523</v>
+        <v>7.64757871627808</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576314926147</v>
+        <v>7.90576219558716</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344244003296</v>
+        <v>7.84344148635864</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>8.60494041442871</v>
       </c>
       <c r="G488" t="n">
-        <v>7.62977266311646</v>
+        <v>7.62977313995361</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.74996280670166</v>
+        <v>7.74996185302734</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>9.34795665740967</v>
       </c>
       <c r="G508" t="n">
-        <v>8.28858661651611</v>
+        <v>8.2885856628418</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.61403846740723</v>
       </c>
       <c r="G510" t="n">
-        <v>8.52451324462891</v>
+        <v>8.52451419830322</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.50225639343262</v>
+        <v>8.5022554397583</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G514" t="n">
-        <v>8.73373031616211</v>
+        <v>8.73373126983643</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G517" t="n">
-        <v>8.7604398727417</v>
+        <v>8.76043891906738</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.76464939117432</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65805625915527</v>
+        <v>8.65805530548096</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>10.1210966110229</v>
       </c>
       <c r="G519" t="n">
-        <v>8.97410869598389</v>
+        <v>8.9741096496582</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>10.1813411712646</v>
       </c>
       <c r="G524" t="n">
-        <v>9.02752590179443</v>
+        <v>9.02752685546875</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G528" t="n">
-        <v>9.16552066802979</v>
+        <v>9.1655216217041</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G529" t="n">
-        <v>9.04088020324707</v>
+        <v>9.04087924957275</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>10.1964015960693</v>
       </c>
       <c r="G530" t="n">
-        <v>9.04088020324707</v>
+        <v>9.04087924957275</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833885192871</v>
+        <v>8.83833980560303</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>9.46593570709229</v>
       </c>
       <c r="G533" t="n">
-        <v>8.39319515228271</v>
+        <v>8.3931941986084</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.4199047088623</v>
+        <v>8.41990566253662</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617107391357</v>
+        <v>8.16617202758789</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.06179523468018</v>
       </c>
       <c r="G538" t="n">
-        <v>8.03485488891602</v>
+        <v>8.0348539352417</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660707473755</v>
+        <v>7.73660612106323</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519557952881</v>
+        <v>7.54519605636597</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.64008331298828</v>
       </c>
       <c r="G545" t="n">
-        <v>7.66093397140503</v>
+        <v>7.66093349456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G548" t="n">
-        <v>7.60083913803101</v>
+        <v>7.60083866119385</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.76331615447998</v>
+        <v>7.7633171081543</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.52293825149536</v>
+        <v>7.52293872833252</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368829727173</v>
+        <v>7.29368877410889</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.56979656219482</v>
       </c>
       <c r="G558" t="n">
-        <v>7.59861183166504</v>
+        <v>7.5986123085022</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663900375366</v>
+        <v>7.75663805007935</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G560" t="n">
-        <v>7.75218820571899</v>
+        <v>7.75218725204468</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613481521606</v>
+        <v>7.43613433837891</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G566" t="n">
-        <v>7.25585079193115</v>
+        <v>7.25585126876831</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.32128810882568</v>
       </c>
       <c r="G567" t="n">
-        <v>7.37826633453369</v>
+        <v>7.37826585769653</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>8.43173694610596</v>
       </c>
       <c r="G568" t="n">
-        <v>7.47619771957397</v>
+        <v>7.47619819641113</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>8.17820739746094</v>
       </c>
       <c r="G570" t="n">
-        <v>7.25139999389648</v>
+        <v>7.25140047073364</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G573" t="n">
-        <v>7.07111692428589</v>
+        <v>7.07111740112305</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224582672119</v>
+        <v>7.08224534988403</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G578" t="n">
-        <v>6.98876571655273</v>
+        <v>6.98876523971558</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744714736938</v>
+        <v>6.85744667053223</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G581" t="n">
-        <v>7.08892250061035</v>
+        <v>7.08892202377319</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G583" t="n">
-        <v>7.22469091415405</v>
+        <v>7.22469139099121</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G585" t="n">
-        <v>7.18017673492432</v>
+        <v>7.18017721176147</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G586" t="n">
-        <v>7.4806489944458</v>
+        <v>7.48064947128296</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842359542847</v>
+        <v>7.47842407226562</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.43675708770752</v>
       </c>
       <c r="G589" t="n">
-        <v>7.4806489944458</v>
+        <v>7.48064947128296</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G590" t="n">
-        <v>7.26475477218628</v>
+        <v>7.26475429534912</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G591" t="n">
-        <v>6.98876571655273</v>
+        <v>6.98876523971558</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766731262207</v>
+        <v>6.99766778945923</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>7.92969799041748</v>
       </c>
       <c r="G596" t="n">
-        <v>7.03105354309082</v>
+        <v>7.03105306625366</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.06022834777832</v>
       </c>
       <c r="G599" t="n">
-        <v>7.14679098129272</v>
+        <v>7.14679145812988</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G601" t="n">
-        <v>7.38939476013184</v>
+        <v>7.38939523696899</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.55222606658936</v>
       </c>
       <c r="G603" t="n">
-        <v>7.58303213119507</v>
+        <v>7.58303260803223</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.83242416381836</v>
       </c>
       <c r="G605" t="n">
-        <v>8.71815013885498</v>
+        <v>8.7181510925293</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.82275867462158</v>
+        <v>8.8227596282959</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G607" t="n">
-        <v>8.54009246826172</v>
+        <v>8.54009342193604</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>10.0909738540649</v>
       </c>
       <c r="G609" t="n">
-        <v>8.94740009307861</v>
+        <v>8.9473991394043</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065475463867</v>
+        <v>8.19065380096436</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.31783485412598</v>
       </c>
       <c r="G620" t="n">
-        <v>8.26187801361084</v>
+        <v>8.26187896728516</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>9.85250568389893</v>
       </c>
       <c r="G623" t="n">
-        <v>8.73595523834229</v>
+        <v>8.7359561920166</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G629" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>9.36552906036377</v>
       </c>
       <c r="G630" t="n">
-        <v>8.30416774749756</v>
+        <v>8.30416679382324</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G641" t="n">
-        <v>8.71147346496582</v>
+        <v>8.7114725112915</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.4323596954346</v>
       </c>
       <c r="G645" t="n">
-        <v>9.25009727478027</v>
+        <v>9.25009632110596</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G646" t="n">
-        <v>9.39254379272461</v>
+        <v>9.39254474639893</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G650" t="n">
-        <v>9.01639652252197</v>
+        <v>9.01639747619629</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G651" t="n">
-        <v>9.05646133422852</v>
+        <v>9.0564603805542</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10.286768913269</v>
       </c>
       <c r="G652" t="n">
-        <v>9.12100505828857</v>
+        <v>9.12100601196289</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>11.200478553772</v>
       </c>
       <c r="G668" t="n">
-        <v>9.93116760253906</v>
+        <v>9.93116855621338</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G671" t="n">
-        <v>9.80652904510498</v>
+        <v>9.80652809143066</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G677" t="n">
-        <v>10.2939624786377</v>
+        <v>10.2939615249634</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G678" t="n">
-        <v>10.0157461166382</v>
+        <v>10.0157451629639</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G681" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G684" t="n">
-        <v>10.334023475647</v>
+        <v>10.3340244293213</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>11.2707653045654</v>
       </c>
       <c r="G685" t="n">
-        <v>9.99349021911621</v>
+        <v>9.99348926544189</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>11.5820293426514</v>
       </c>
       <c r="G687" t="n">
-        <v>10.2694787979126</v>
+        <v>10.2694797515869</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>11.9259252548218</v>
       </c>
       <c r="G689" t="n">
-        <v>10.5744018554688</v>
+        <v>10.5744028091431</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G693" t="n">
-        <v>10.8259077072144</v>
+        <v>10.8259086608887</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>12.131760597229</v>
       </c>
       <c r="G695" t="n">
-        <v>10.7569122314453</v>
+        <v>10.756911277771</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>13.2086343765259</v>
       </c>
       <c r="G699" t="n">
-        <v>11.7117471694946</v>
+        <v>11.7117462158203</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>13.5500202178955</v>
       </c>
       <c r="G702" t="n">
-        <v>12.0144443511963</v>
+        <v>12.014443397522</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>12.7618188858032</v>
       </c>
       <c r="G709" t="n">
-        <v>11.3155679702759</v>
+        <v>11.3155670166016</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.4505548477173</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0395784378052</v>
+        <v>11.0395774841309</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>12.7065954208374</v>
       </c>
       <c r="G712" t="n">
-        <v>11.2666025161743</v>
+        <v>11.2666015625</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>12.3325757980347</v>
       </c>
       <c r="G714" t="n">
-        <v>10.9349699020386</v>
+        <v>10.9349689483643</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>11.8004150390625</v>
       </c>
       <c r="G715" t="n">
-        <v>10.463116645813</v>
+        <v>10.4631156921387</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>11.7702932357788</v>
       </c>
       <c r="G717" t="n">
-        <v>10.4364070892334</v>
+        <v>10.4364080429077</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G719" t="n">
-        <v>10.5499200820923</v>
+        <v>10.549919128418</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>11.7979049682617</v>
       </c>
       <c r="G721" t="n">
-        <v>10.4608907699585</v>
+        <v>10.4608898162842</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>11.8857622146606</v>
       </c>
       <c r="G723" t="n">
-        <v>10.5387907028198</v>
+        <v>10.5387916564941</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G724" t="n">
-        <v>10.76136302948</v>
+        <v>10.7613620758057</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>11.5544166564941</v>
       </c>
       <c r="G726" t="n">
-        <v>10.2449951171875</v>
+        <v>10.2449960708618</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>11.7251100540161</v>
       </c>
       <c r="G730" t="n">
-        <v>10.3963451385498</v>
+        <v>10.3963441848755</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G737" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G738" t="n">
-        <v>8.25965213775635</v>
+        <v>8.25965118408203</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.35046672821045</v>
       </c>
       <c r="G739" t="n">
-        <v>8.29081249237061</v>
+        <v>8.29081153869629</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G741" t="n">
-        <v>7.77889537811279</v>
+        <v>7.77889633178711</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.54375171661377</v>
       </c>
       <c r="G743" t="n">
-        <v>8.46219158172607</v>
+        <v>8.46219253540039</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.23499870300293</v>
       </c>
       <c r="G750" t="n">
-        <v>8.1884298324585</v>
+        <v>8.18842887878418</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.35548782348633</v>
       </c>
       <c r="G754" t="n">
-        <v>8.29526424407959</v>
+        <v>8.29526329040527</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G759" t="n">
-        <v>7.59416151046753</v>
+        <v>7.59416103363037</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>8.12800407409668</v>
       </c>
       <c r="G761" t="n">
-        <v>7.20688581466675</v>
+        <v>7.20688629150391</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.85941314697266</v>
       </c>
       <c r="G762" t="n">
-        <v>6.96873331069946</v>
+        <v>6.96873378753662</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G766" t="n">
-        <v>7.90576314926147</v>
+        <v>7.90576219558716</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>9.12957000732422</v>
       </c>
       <c r="G767" t="n">
-        <v>8.09494876861572</v>
+        <v>8.09494781494141</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G771" t="n">
-        <v>8.3976469039917</v>
+        <v>8.39764595031738</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G774" t="n">
-        <v>8.59128475189209</v>
+        <v>8.59128379821777</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>10.2817487716675</v>
       </c>
       <c r="G786" t="n">
-        <v>9.11655426025391</v>
+        <v>9.11655521392822</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>10.4298496246338</v>
       </c>
       <c r="G789" t="n">
-        <v>9.2478723526001</v>
+        <v>9.24787139892578</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>10.7963380813599</v>
       </c>
       <c r="G797" t="n">
-        <v>9.57282638549805</v>
+        <v>9.57282733917236</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>10.8440322875977</v>
       </c>
       <c r="G803" t="n">
-        <v>9.61511707305908</v>
+        <v>9.61511611938477</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G804" t="n">
-        <v>9.69746875762939</v>
+        <v>9.69746780395508</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.2356224060059</v>
       </c>
       <c r="G806" t="n">
-        <v>9.96232986450195</v>
+        <v>9.96232891082764</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.6723957061768</v>
       </c>
       <c r="G808" t="n">
-        <v>10.3496036529541</v>
+        <v>10.3496046066284</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>11.8882722854614</v>
       </c>
       <c r="G809" t="n">
-        <v>10.541015625</v>
+        <v>10.5410165786743</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>11.8732109069824</v>
       </c>
       <c r="G812" t="n">
-        <v>10.5276613235474</v>
+        <v>10.5276622772217</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>12.3150053024292</v>
       </c>
       <c r="G815" t="n">
-        <v>10.9193897247314</v>
+        <v>10.9193887710571</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.3350868225098</v>
       </c>
       <c r="G818" t="n">
-        <v>10.9371957778931</v>
+        <v>10.9371948242188</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>12.2095766067505</v>
       </c>
       <c r="G820" t="n">
-        <v>10.8259077072144</v>
+        <v>10.8259086608887</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>11.5368452072144</v>
       </c>
       <c r="G822" t="n">
-        <v>10.2294149398804</v>
+        <v>10.2294158935547</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>11.654824256897</v>
       </c>
       <c r="G825" t="n">
-        <v>10.334023475647</v>
+        <v>10.3340244293213</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>12.1970262527466</v>
       </c>
       <c r="G828" t="n">
-        <v>10.8147811889648</v>
+        <v>10.8147802352905</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>12.2522497177124</v>
       </c>
       <c r="G829" t="n">
-        <v>10.8637456893921</v>
+        <v>10.8637447357178</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>12.1367807388306</v>
       </c>
       <c r="G830" t="n">
-        <v>10.76136302948</v>
+        <v>10.7613620758057</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>12.4856977462769</v>
       </c>
       <c r="G831" t="n">
-        <v>11.0707378387451</v>
+        <v>11.0707368850708</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>12.6312885284424</v>
       </c>
       <c r="G832" t="n">
-        <v>11.1998291015625</v>
+        <v>11.1998300552368</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>12.0991277694702</v>
       </c>
       <c r="G834" t="n">
-        <v>10.7279767990112</v>
+        <v>10.7279777526855</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G835" t="n">
-        <v>10.4386329650879</v>
+        <v>10.4386339187622</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>11.6498041152954</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3295726776123</v>
+        <v>10.3295736312866</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>11.5343351364136</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2271900177002</v>
+        <v>10.2271909713745</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>11.7728033065796</v>
       </c>
       <c r="G839" t="n">
-        <v>10.4386329650879</v>
+        <v>10.4386339187622</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>11.8983125686646</v>
       </c>
       <c r="G842" t="n">
-        <v>10.5499200820923</v>
+        <v>10.549919128418</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>11.3912544250488</v>
       </c>
       <c r="G844" t="n">
-        <v>10.1003246307373</v>
+        <v>10.100323677063</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>10.836501121521</v>
       </c>
       <c r="G849" t="n">
-        <v>9.60843944549561</v>
+        <v>9.60843849182129</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G850" t="n">
-        <v>9.21448516845703</v>
+        <v>9.21448612213135</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G858" t="n">
-        <v>9.27012920379639</v>
+        <v>9.2701301574707</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G859" t="n">
-        <v>9.16329479217529</v>
+        <v>9.16329383850098</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>9.88011837005615</v>
       </c>
       <c r="G867" t="n">
-        <v>8.7604398727417</v>
+        <v>8.76043891906738</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10.8088893890381</v>
       </c>
       <c r="G875" t="n">
-        <v>9.58395576477051</v>
+        <v>9.58395671844482</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>10.4549522399902</v>
       </c>
       <c r="G878" t="n">
-        <v>9.27012920379639</v>
+        <v>9.2701301574707</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G880" t="n">
-        <v>9.55947303771973</v>
+        <v>9.55947208404541</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G881" t="n">
-        <v>9.60621356964111</v>
+        <v>9.6062126159668</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>11.0699491500854</v>
       </c>
       <c r="G883" t="n">
-        <v>9.81543159484863</v>
+        <v>9.81543064117432</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.9293794631958</v>
       </c>
       <c r="G884" t="n">
-        <v>9.69079113006592</v>
+        <v>9.69079208374023</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.0498676300049</v>
       </c>
       <c r="G887" t="n">
-        <v>9.79762649536133</v>
+        <v>9.79762554168701</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.2431526184082</v>
       </c>
       <c r="G889" t="n">
-        <v>9.9690055847168</v>
+        <v>9.96900653839111</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.9369087219238</v>
       </c>
       <c r="G890" t="n">
-        <v>9.69746875762939</v>
+        <v>9.69746780395508</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>11.0272760391235</v>
       </c>
       <c r="G893" t="n">
-        <v>9.7775936126709</v>
+        <v>9.77759456634521</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.9544811248779</v>
       </c>
       <c r="G902" t="n">
-        <v>9.71304893493652</v>
+        <v>9.71304798126221</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G903" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>11.0423374176025</v>
       </c>
       <c r="G905" t="n">
-        <v>9.79094791412354</v>
+        <v>9.79094886779785</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>11.2958669662476</v>
       </c>
       <c r="G906" t="n">
-        <v>10.0157461166382</v>
+        <v>10.0157451629639</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.275785446167</v>
       </c>
       <c r="G911" t="n">
-        <v>9.99794101715088</v>
+        <v>9.99794006347656</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G916" t="n">
-        <v>8.92514228820801</v>
+        <v>8.92514324188232</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G919" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.0959949493408</v>
       </c>
       <c r="G922" t="n">
-        <v>8.9518518447876</v>
+        <v>8.95185089111328</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>10.4474220275879</v>
       </c>
       <c r="G925" t="n">
-        <v>9.26345348358154</v>
+        <v>9.26345252990723</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>10.2842588424683</v>
       </c>
       <c r="G927" t="n">
-        <v>9.1187801361084</v>
+        <v>9.11878108978271</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>10.3545436859131</v>
       </c>
       <c r="G928" t="n">
-        <v>9.1810998916626</v>
+        <v>9.18110084533691</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>10.9092969894409</v>
       </c>
       <c r="G931" t="n">
-        <v>9.6729850769043</v>
+        <v>9.67298603057861</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>10.9067869186401</v>
       </c>
       <c r="G933" t="n">
-        <v>9.6707592010498</v>
+        <v>9.67076015472412</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>11.0599088668823</v>
       </c>
       <c r="G937" t="n">
-        <v>9.80652904510498</v>
+        <v>9.80652809143066</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.4063148498535</v>
       </c>
       <c r="G941" t="n">
-        <v>10.1136779785156</v>
+        <v>10.1136770248413</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.4364376068115</v>
       </c>
       <c r="G942" t="n">
-        <v>10.1403865814209</v>
+        <v>10.1403875350952</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>11.7552318572998</v>
       </c>
       <c r="G943" t="n">
-        <v>10.4230527877808</v>
+        <v>10.4230537414551</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.881685256958</v>
       </c>
       <c r="G948" t="n">
-        <v>9.64850330352783</v>
+        <v>9.64850234985352</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>10.7862977981567</v>
       </c>
       <c r="G949" t="n">
-        <v>9.56392478942871</v>
+        <v>9.56392383575439</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>10.2164840698242</v>
       </c>
       <c r="G954" t="n">
-        <v>9.05868625640869</v>
+        <v>9.05868530273438</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>10.0683822631836</v>
       </c>
       <c r="G955" t="n">
-        <v>8.92736721038818</v>
+        <v>8.9273681640625</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G958" t="n">
-        <v>9.16552066802979</v>
+        <v>9.1655216217041</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>10.3294429779053</v>
       </c>
       <c r="G968" t="n">
-        <v>9.15884399414062</v>
+        <v>9.15884304046631</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>10.2792387008667</v>
       </c>
       <c r="G969" t="n">
-        <v>9.11432933807373</v>
+        <v>9.11433029174805</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G974" t="n">
-        <v>9.51050758361816</v>
+        <v>9.51050662994385</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>10.8339910507202</v>
       </c>
       <c r="G978" t="n">
-        <v>9.60621356964111</v>
+        <v>9.6062126159668</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G980" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>11.1402349472046</v>
       </c>
       <c r="G982" t="n">
-        <v>9.87775135040283</v>
+        <v>9.87775230407715</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>11.0573978424072</v>
       </c>
       <c r="G983" t="n">
-        <v>9.80430221557617</v>
+        <v>9.80430126190186</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G987" t="n">
-        <v>9.802077293396</v>
+        <v>9.80207633972168</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>10.6105842590332</v>
       </c>
       <c r="G989" t="n">
-        <v>9.40812397003174</v>
+        <v>9.40812492370605</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G994" t="n">
-        <v>9.45931625366211</v>
+        <v>9.45931529998779</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>10.2139739990234</v>
       </c>
       <c r="G999" t="n">
-        <v>9.05646133422852</v>
+        <v>9.0564603805542</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>10.427339553833</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.24564647674561</v>
+        <v>9.24564552307129</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.39254379272461</v>
+        <v>9.39254474639893</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>10.5277481079102</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.33467674255371</v>
+        <v>9.33467578887939</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>10.6683187484741</v>
       </c>
       <c r="G1008" t="n">
-        <v>9.45931625366211</v>
+        <v>9.45931529998779</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>10.7938280105591</v>
       </c>
       <c r="G1009" t="n">
-        <v>9.57060146331787</v>
+        <v>9.57060241699219</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>10.6783590316772</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.46821784973145</v>
+        <v>9.46821880340576</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>10.7837867736816</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.56169891357422</v>
+        <v>9.5616979598999</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>11.1176433563232</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>11.1728668212891</v>
       </c>
       <c r="G1019" t="n">
-        <v>9.9066858291626</v>
+        <v>9.90668487548828</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>11.1678466796875</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.90223503112793</v>
+        <v>9.90223407745361</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.0548877716064</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.802077293396</v>
+        <v>9.80207633972168</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>10.0407695770264</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.90288543701172</v>
+        <v>8.9028844833374</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.2062349319458</v>
+        <v>8.20623397827148</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>9.51362991333008</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.43548393249512</v>
+        <v>8.43548488616943</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>8.60243034362793</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.62754726409912</v>
+        <v>7.62754774093628</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.57230758666992</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.60083913803101</v>
+        <v>7.60083866119385</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>8.3037166595459</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.36268663406372</v>
+        <v>7.36268615722656</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.1832275390625</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.25585079193115</v>
+        <v>7.25585126876831</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.07111692428589</v>
+        <v>7.07111740112305</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.70832395553589</v>
+        <v>6.70832347869873</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>5.16848611831665</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.58275985717773</v>
+        <v>4.58276033401489</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>5.16346597671509</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.57830905914307</v>
+        <v>4.57830858230591</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>5.64291286468506</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.00342178344727</v>
+        <v>5.00342130661011</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.51489305496216</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.88990926742554</v>
+        <v>4.8899097442627</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>5.8261570930481</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.1658992767334</v>
+        <v>5.16589975357056</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1078" t="n">
-        <v>4.98561525344849</v>
+        <v>4.98561573028564</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>5.62283086776733</v>
       </c>
       <c r="G1079" t="n">
-        <v>4.98561525344849</v>
+        <v>4.98561573028564</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.06713485717773</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.37956809997559</v>
+        <v>5.37956762313843</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>5.95919704437256</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.28386259078979</v>
+        <v>5.28386211395264</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.0219521522522</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.33950567245483</v>
+        <v>5.33950614929199</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>5.9014630317688</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.23267126083374</v>
+        <v>5.23267078399658</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>6.04956388473511</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.36398839950562</v>
+        <v>5.36398887634277</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>5.47473001480103</v>
       </c>
       <c r="G1089" t="n">
-        <v>4.85429859161377</v>
+        <v>4.85429811477661</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>5.58768796920776</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.95445537567139</v>
+        <v>4.95445489883423</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>5.45715808868408</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.83871746063232</v>
+        <v>4.83871793746948</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>5.86381006240845</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.19928550720215</v>
+        <v>5.19928503036499</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>5.87636089324951</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.21041345596313</v>
+        <v>5.21041393280029</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.76842212677002</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.11470699310303</v>
+        <v>5.11470746994019</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>5.76591205596924</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.11248159408569</v>
+        <v>5.11248207092285</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>5.57513809204102</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.94332695007324</v>
+        <v>4.9433274269104</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -69298,6 +69298,32 @@
         <v>4.40500020980835</v>
       </c>
       <c r="H2651" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2652">
+      <c r="A2652" s="1" t="n">
+        <v>46183.2916666667</v>
+      </c>
+      <c r="B2652" t="n">
+        <v>11727497</v>
+      </c>
+      <c r="C2652" t="n">
+        <v>4.46600008010864</v>
+      </c>
+      <c r="D2652" t="n">
+        <v>4.36600017547607</v>
+      </c>
+      <c r="E2652" t="n">
+        <v>4.39300012588501</v>
+      </c>
+      <c r="F2652" t="n">
+        <v>4.42500019073486</v>
+      </c>
+      <c r="G2652" t="n">
+        <v>4.42500019073486</v>
+      </c>
+      <c r="H2652" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SPM.MI.xlsx
+++ b/data/SPM.MI.xlsx
@@ -473,7 +473,7 @@
         <v>22.3245735168457</v>
       </c>
       <c r="G4" t="n">
-        <v>19.7946071624756</v>
+        <v>19.7946090698242</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>22.4193687438965</v>
       </c>
       <c r="G8" t="n">
-        <v>19.878662109375</v>
+        <v>19.8786602020264</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>22.1665782928467</v>
       </c>
       <c r="G9" t="n">
-        <v>19.6545181274414</v>
+        <v>19.65452003479</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>22.1823787689209</v>
       </c>
       <c r="G10" t="n">
-        <v>19.668529510498</v>
+        <v>19.6685276031494</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>20.9184246063232</v>
       </c>
       <c r="G11" t="n">
-        <v>18.5478134155273</v>
+        <v>18.547815322876</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>19.8440647125244</v>
       </c>
       <c r="G12" t="n">
-        <v>17.5952091217041</v>
+        <v>17.5952072143555</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>19.8282642364502</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5811958312988</v>
+        <v>17.5811977386475</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.7585411071777</v>
       </c>
       <c r="G14" t="n">
-        <v>15.7460289001465</v>
+        <v>15.7460279464722</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>16.7157802581787</v>
       </c>
       <c r="G15" t="n">
-        <v>14.821439743042</v>
+        <v>14.8214406967163</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>15.7389078140259</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9552726745605</v>
+        <v>13.9552736282349</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14.2202405929565</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6087112426758</v>
+        <v>12.6087121963501</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.0530023574829</v>
       </c>
       <c r="G26" t="n">
-        <v>11.573751449585</v>
+        <v>11.5737524032593</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G28" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G30" t="n">
-        <v>7.08892202377319</v>
+        <v>7.08892250061035</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.56572008132935</v>
       </c>
       <c r="G31" t="n">
-        <v>6.70832347869873</v>
+        <v>6.70832395553589</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.60588312149048</v>
       </c>
       <c r="G32" t="n">
-        <v>6.74393558502197</v>
+        <v>6.74393510818481</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.75649499893188</v>
       </c>
       <c r="G33" t="n">
-        <v>6.8774790763855</v>
+        <v>6.87747859954834</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.47189998626709</v>
       </c>
       <c r="G34" t="n">
-        <v>7.51180982589722</v>
+        <v>7.51181030273438</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.30120658874512</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36046028137207</v>
+        <v>7.36045980453491</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.92373466491699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.91243934631348</v>
+        <v>7.91243886947632</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G40" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G43" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>10.6884002685547</v>
       </c>
       <c r="G47" t="n">
-        <v>9.47712135314941</v>
+        <v>9.47712230682373</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.10948944091797</v>
       </c>
       <c r="G48" t="n">
-        <v>8.07714366912842</v>
+        <v>8.0771427154541</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.00908088684082</v>
       </c>
       <c r="G50" t="n">
-        <v>7.98811388015747</v>
+        <v>7.98811340332031</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.68432331085205</v>
       </c>
       <c r="G52" t="n">
-        <v>8.58683300018311</v>
+        <v>8.58683204650879</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.26261138916016</v>
       </c>
       <c r="G54" t="n">
-        <v>8.21291351318359</v>
+        <v>8.21291255950928</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.38059043884277</v>
       </c>
       <c r="G55" t="n">
-        <v>8.3175220489502</v>
+        <v>8.31752109527588</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G59" t="n">
-        <v>8.20623397827148</v>
+        <v>8.2062349319458</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G60" t="n">
-        <v>7.75218725204468</v>
+        <v>7.75218820571899</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.28363513946533</v>
       </c>
       <c r="G61" t="n">
-        <v>7.3448805809021</v>
+        <v>7.34488010406494</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.6375732421875</v>
       </c>
       <c r="G64" t="n">
-        <v>7.65870809555054</v>
+        <v>7.65870714187622</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.78159713745117</v>
       </c>
       <c r="G66" t="n">
-        <v>6.89973640441895</v>
+        <v>6.89973592758179</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.61341381072998</v>
       </c>
       <c r="G68" t="n">
-        <v>6.75061273574829</v>
+        <v>6.75061225891113</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.20330905914307</v>
       </c>
       <c r="G69" t="n">
-        <v>7.27365732192993</v>
+        <v>7.27365779876709</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G70" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G71" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.86851024627686</v>
       </c>
       <c r="G72" t="n">
-        <v>7.86347436904907</v>
+        <v>7.8634729385376</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.1345911026001</v>
       </c>
       <c r="G73" t="n">
-        <v>8.09939956665039</v>
+        <v>8.09940052032471</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.87102127075195</v>
       </c>
       <c r="G74" t="n">
-        <v>7.86570072174072</v>
+        <v>7.86569976806641</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G76" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.39816093444824</v>
       </c>
       <c r="G80" t="n">
-        <v>8.33310127258301</v>
+        <v>8.33310031890869</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.73201656341553</v>
       </c>
       <c r="G82" t="n">
-        <v>8.62912178039551</v>
+        <v>8.62912082672119</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>10.4926052093506</v>
       </c>
       <c r="G84" t="n">
-        <v>9.30351448059082</v>
+        <v>9.30351543426514</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G85" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G86" t="n">
-        <v>8.54009342193604</v>
+        <v>8.54009246826172</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G87" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G88" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G89" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.36803913116455</v>
       </c>
       <c r="G90" t="n">
-        <v>8.30639171600342</v>
+        <v>8.30639266967773</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G93" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.32536506652832</v>
       </c>
       <c r="G94" t="n">
-        <v>8.2685546875</v>
+        <v>8.26855373382568</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.46844577789307</v>
       </c>
       <c r="G95" t="n">
-        <v>8.39542007446289</v>
+        <v>8.39542102813721</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G97" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.00657081604004</v>
       </c>
       <c r="G98" t="n">
-        <v>7.98588848114014</v>
+        <v>7.98588752746582</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G99" t="n">
-        <v>7.99701642990112</v>
+        <v>7.99701690673828</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.53873157501221</v>
       </c>
       <c r="G102" t="n">
-        <v>8.45774078369141</v>
+        <v>8.45774173736572</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.47095680236816</v>
       </c>
       <c r="G103" t="n">
-        <v>8.39764595031738</v>
+        <v>8.3976469039917</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.77312278747559</v>
       </c>
       <c r="G109" t="n">
-        <v>7.77889633178711</v>
+        <v>7.77889585494995</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.01912212371826</v>
       </c>
       <c r="G110" t="n">
-        <v>7.99701642990112</v>
+        <v>7.99701690673828</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G113" t="n">
-        <v>8.6736364364624</v>
+        <v>8.67363548278809</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.71036815643311</v>
       </c>
       <c r="G115" t="n">
-        <v>7.72325372695923</v>
+        <v>7.72325325012207</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G116" t="n">
-        <v>7.73660612106323</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.98648929595947</v>
       </c>
       <c r="G117" t="n">
-        <v>7.96808290481567</v>
+        <v>7.96808242797852</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.2550802230835</v>
       </c>
       <c r="G119" t="n">
-        <v>8.20623397827148</v>
+        <v>8.2062349319458</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.8851375579834</v>
       </c>
       <c r="G122" t="n">
-        <v>8.76489067077637</v>
+        <v>8.76488971710205</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.08940696716309</v>
       </c>
       <c r="G124" t="n">
-        <v>8.0593376159668</v>
+        <v>8.05933666229248</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.5622673034668</v>
       </c>
       <c r="G125" t="n">
-        <v>7.59193563461304</v>
+        <v>7.5919361114502</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78557348251343</v>
+        <v>7.78557395935059</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.86349010467529</v>
       </c>
       <c r="G127" t="n">
-        <v>7.85902214050293</v>
+        <v>7.85902261734009</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.60650730133057</v>
       </c>
       <c r="G130" t="n">
-        <v>8.51783561706543</v>
+        <v>8.51783657073975</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.82489395141602</v>
       </c>
       <c r="G135" t="n">
-        <v>8.7114725112915</v>
+        <v>8.71147441864014</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.1888723373413</v>
       </c>
       <c r="G136" t="n">
-        <v>9.03420352935791</v>
+        <v>9.03420257568359</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>10.3771362304688</v>
       </c>
       <c r="G139" t="n">
-        <v>9.20113277435303</v>
+        <v>9.20113182067871</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>10.5679111480713</v>
       </c>
       <c r="G140" t="n">
-        <v>9.37028694152832</v>
+        <v>9.37028789520264</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>10.7812767028809</v>
       </c>
       <c r="G141" t="n">
-        <v>9.55947208404541</v>
+        <v>9.55947303771973</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>10.6934204101562</v>
       </c>
       <c r="G146" t="n">
-        <v>9.4815731048584</v>
+        <v>9.48157215118408</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.0348072052002</v>
       </c>
       <c r="G147" t="n">
-        <v>9.78427124023438</v>
+        <v>9.78427219390869</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.95542430877686</v>
       </c>
       <c r="G148" t="n">
-        <v>8.82721138000488</v>
+        <v>8.8272123336792</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G149" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.37807941436768</v>
       </c>
       <c r="G153" t="n">
-        <v>8.31529521942139</v>
+        <v>8.31529426574707</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.61152744293213</v>
       </c>
       <c r="G154" t="n">
-        <v>8.52228832244873</v>
+        <v>8.52228736877441</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G160" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G163" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.98303604125977</v>
       </c>
       <c r="G164" t="n">
-        <v>8.85169315338135</v>
+        <v>8.85169410705566</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>10.4449110031128</v>
       </c>
       <c r="G165" t="n">
-        <v>9.26122570037842</v>
+        <v>9.26122665405273</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>10.3947076797485</v>
       </c>
       <c r="G166" t="n">
-        <v>9.21671199798584</v>
+        <v>9.21671295166016</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>10.442400932312</v>
       </c>
       <c r="G168" t="n">
-        <v>9.25900077819824</v>
+        <v>9.25899982452393</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.314380645752</v>
       </c>
       <c r="G171" t="n">
-        <v>9.14548778533936</v>
+        <v>9.14548873901367</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>10.457462310791</v>
       </c>
       <c r="G174" t="n">
-        <v>9.2723560333252</v>
+        <v>9.27235507965088</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>10.4147891998291</v>
       </c>
       <c r="G177" t="n">
-        <v>9.23451900482178</v>
+        <v>9.23451805114746</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>10.3168916702271</v>
       </c>
       <c r="G178" t="n">
-        <v>9.14771556854248</v>
+        <v>9.14771461486816</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G182" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.95887660980225</v>
       </c>
       <c r="G183" t="n">
-        <v>7.94359827041626</v>
+        <v>7.94359874725342</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.90365314483643</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89463329315186</v>
+        <v>7.89463376998901</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.91871356964111</v>
       </c>
       <c r="G189" t="n">
-        <v>7.90798664093018</v>
+        <v>7.90798759460449</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.72793960571289</v>
       </c>
       <c r="G191" t="n">
-        <v>7.73883247375488</v>
+        <v>7.7388334274292</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G193" t="n">
-        <v>8.38429260253906</v>
+        <v>8.38429164886475</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G196" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.77217960357666</v>
       </c>
       <c r="G198" t="n">
-        <v>8.66473388671875</v>
+        <v>8.66473293304443</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>10.4047479629517</v>
       </c>
       <c r="G203" t="n">
-        <v>9.22561550140381</v>
+        <v>9.22561454772949</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10.3696060180664</v>
       </c>
       <c r="G204" t="n">
-        <v>9.19445514678955</v>
+        <v>9.19445610046387</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G205" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.5051555633545</v>
       </c>
       <c r="G210" t="n">
-        <v>9.31464385986328</v>
+        <v>9.31464290618896</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G211" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G213" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.45589542388916</v>
       </c>
       <c r="G219" t="n">
-        <v>8.38429260253906</v>
+        <v>8.38429164886475</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.3153247833252</v>
       </c>
       <c r="G220" t="n">
-        <v>8.25965118408203</v>
+        <v>8.25965213775635</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G221" t="n">
-        <v>8.73373126983643</v>
+        <v>8.73373031616211</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G224" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.0834436416626</v>
       </c>
       <c r="G226" t="n">
-        <v>8.94072341918945</v>
+        <v>8.94072246551514</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.7822208404541</v>
       </c>
       <c r="G228" t="n">
-        <v>8.6736364364624</v>
+        <v>8.67363548278809</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.0884637832642</v>
       </c>
       <c r="G230" t="n">
-        <v>8.94517421722412</v>
+        <v>8.9451732635498</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.3344631195068</v>
       </c>
       <c r="G232" t="n">
-        <v>9.16329383850098</v>
+        <v>9.16329479217529</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.0658721923828</v>
       </c>
       <c r="G233" t="n">
-        <v>8.92514324188232</v>
+        <v>8.92514228820801</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>9.81234264373779</v>
       </c>
       <c r="G234" t="n">
-        <v>8.70034503936768</v>
+        <v>8.70034408569336</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.9695415496826</v>
       </c>
       <c r="G237" t="n">
-        <v>9.72640323638916</v>
+        <v>9.72640228271484</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>11.484130859375</v>
       </c>
       <c r="G240" t="n">
-        <v>10.1826753616333</v>
+        <v>10.182674407959</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.4088249206543</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1159029006958</v>
+        <v>10.1159038543701</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.8230066299438</v>
       </c>
       <c r="G245" t="n">
-        <v>10.4831466674805</v>
+        <v>10.4831476211548</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.9309453964233</v>
       </c>
       <c r="G247" t="n">
-        <v>10.5788545608521</v>
+        <v>10.5788536071777</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>12.3928213119507</v>
       </c>
       <c r="G251" t="n">
-        <v>10.9883861541748</v>
+        <v>10.9883871078491</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G252" t="n">
-        <v>11.2844076156616</v>
+        <v>11.2844085693359</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>12.8772878646851</v>
       </c>
       <c r="G253" t="n">
-        <v>11.4179496765137</v>
+        <v>11.417950630188</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>13.2287149429321</v>
       </c>
       <c r="G255" t="n">
-        <v>11.7295522689819</v>
+        <v>11.7295513153076</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>13.4295310974121</v>
       </c>
       <c r="G257" t="n">
-        <v>11.9076099395752</v>
+        <v>11.9076108932495</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>13.9817733764648</v>
       </c>
       <c r="G260" t="n">
-        <v>12.3972692489624</v>
+        <v>12.3972682952881</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>14.006875038147</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4195251464844</v>
+        <v>12.4195261001587</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>13.7433052062988</v>
       </c>
       <c r="G262" t="n">
-        <v>12.1858253479004</v>
+        <v>12.1858243942261</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>12.8647365570068</v>
       </c>
       <c r="G267" t="n">
-        <v>11.4068222045898</v>
+        <v>11.4068212509155</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>12.726676940918</v>
       </c>
       <c r="G270" t="n">
-        <v>11.2844076156616</v>
+        <v>11.2844085693359</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>12.5886163711548</v>
       </c>
       <c r="G271" t="n">
-        <v>11.1619920730591</v>
+        <v>11.1619939804077</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>12.4455347061157</v>
       </c>
       <c r="G273" t="n">
-        <v>11.0351266860962</v>
+        <v>11.0351257324219</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>13.3040208816528</v>
       </c>
       <c r="G275" t="n">
-        <v>11.7963237762451</v>
+        <v>11.7963228225708</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>13.078104019165</v>
       </c>
       <c r="G277" t="n">
-        <v>11.5960083007812</v>
+        <v>11.5960092544556</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>11.5468864440918</v>
       </c>
       <c r="G281" t="n">
-        <v>10.2383184432983</v>
+        <v>10.2383193969727</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>11.7451906204224</v>
       </c>
       <c r="G282" t="n">
-        <v>10.4141492843628</v>
+        <v>10.4141502380371</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>11.5619468688965</v>
       </c>
       <c r="G283" t="n">
-        <v>10.2516717910767</v>
+        <v>10.251672744751</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.7276201248169</v>
       </c>
       <c r="G286" t="n">
-        <v>10.39857006073</v>
+        <v>10.3985710144043</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.6899671554565</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3651847839355</v>
+        <v>10.3651838302612</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.6096410751343</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2939615249634</v>
+        <v>10.2939624786377</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.6874570846558</v>
       </c>
       <c r="G294" t="n">
-        <v>10.3629579544067</v>
+        <v>10.3629589080811</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>10.5754413604736</v>
       </c>
       <c r="G298" t="n">
-        <v>9.3769645690918</v>
+        <v>9.37696361541748</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.6632976531982</v>
       </c>
       <c r="G301" t="n">
-        <v>9.45486354827881</v>
+        <v>9.45486450195312</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10.6984405517578</v>
       </c>
       <c r="G302" t="n">
-        <v>9.48602390289307</v>
+        <v>9.48602485656738</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10.4675025939941</v>
       </c>
       <c r="G304" t="n">
-        <v>9.28125762939453</v>
+        <v>9.28125858306885</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.1110563278198</v>
       </c>
       <c r="G309" t="n">
-        <v>8.96520709991455</v>
+        <v>8.96520614624023</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10.218994140625</v>
       </c>
       <c r="G310" t="n">
-        <v>9.06091213226318</v>
+        <v>9.06091117858887</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10.1687898635864</v>
       </c>
       <c r="G313" t="n">
-        <v>9.01639747619629</v>
+        <v>9.01639652252197</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.2466058731079</v>
       </c>
       <c r="G314" t="n">
-        <v>9.08539485931396</v>
+        <v>9.08539390563965</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.1336479187012</v>
       </c>
       <c r="G315" t="n">
-        <v>8.98523712158203</v>
+        <v>8.98523807525635</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G318" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>10.5930128097534</v>
       </c>
       <c r="G319" t="n">
-        <v>9.39254474639893</v>
+        <v>9.39254379272461</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>10.6708288192749</v>
       </c>
       <c r="G320" t="n">
-        <v>9.4615421295166</v>
+        <v>9.46154117584229</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.0297861099243</v>
       </c>
       <c r="G323" t="n">
-        <v>9.77981948852539</v>
+        <v>9.77981853485107</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>10.7034606933594</v>
       </c>
       <c r="G324" t="n">
-        <v>9.49047565460205</v>
+        <v>9.49047470092773</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>10.726053237915</v>
       </c>
       <c r="G325" t="n">
-        <v>9.51050662994385</v>
+        <v>9.51050758361816</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>10.7310733795166</v>
       </c>
       <c r="G326" t="n">
-        <v>9.51495838165283</v>
+        <v>9.51495933532715</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>10.5227270126343</v>
       </c>
       <c r="G328" t="n">
-        <v>9.33022403717041</v>
+        <v>9.33022308349609</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.3921966552734</v>
       </c>
       <c r="G329" t="n">
-        <v>9.21448612213135</v>
+        <v>9.21448516845703</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G330" t="n">
-        <v>9.12990856170654</v>
+        <v>9.12990951538086</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.7671594619751</v>
       </c>
       <c r="G335" t="n">
-        <v>8.66028118133545</v>
+        <v>8.66028213500977</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>10.3796463012695</v>
       </c>
       <c r="G338" t="n">
-        <v>9.2033576965332</v>
+        <v>9.20335865020752</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G353" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.80481243133545</v>
       </c>
       <c r="G354" t="n">
-        <v>8.6936674118042</v>
+        <v>8.69366836547852</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G356" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>9.86505699157715</v>
       </c>
       <c r="G357" t="n">
-        <v>8.74708461761475</v>
+        <v>8.74708557128906</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.35297775268555</v>
       </c>
       <c r="G360" t="n">
-        <v>8.29303741455078</v>
+        <v>8.2930383682251</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.0115909576416</v>
       </c>
       <c r="G363" t="n">
-        <v>7.9903392791748</v>
+        <v>7.99033975601196</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.72040939331055</v>
       </c>
       <c r="G367" t="n">
-        <v>7.73215627670288</v>
+        <v>7.73215579986572</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G368" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>8.88106060028076</v>
       </c>
       <c r="G372" t="n">
-        <v>7.87460136413574</v>
+        <v>7.8746018409729</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G373" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G378" t="n">
-        <v>7.18017721176147</v>
+        <v>7.18017673492432</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G379" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>8.07779979705811</v>
       </c>
       <c r="G380" t="n">
-        <v>7.16237163543701</v>
+        <v>7.16237115859985</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.15310478210449</v>
       </c>
       <c r="G381" t="n">
-        <v>7.22914218902588</v>
+        <v>7.22914266586304</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8.25351333618164</v>
       </c>
       <c r="G382" t="n">
-        <v>7.31817150115967</v>
+        <v>7.31817245483398</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G383" t="n">
-        <v>7.23804521560669</v>
+        <v>7.23804569244385</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.36898231506348</v>
       </c>
       <c r="G385" t="n">
-        <v>7.42055559158325</v>
+        <v>7.42055463790894</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.68024635314941</v>
       </c>
       <c r="G386" t="n">
-        <v>7.69654512405396</v>
+        <v>7.6965446472168</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.44428825378418</v>
       </c>
       <c r="G387" t="n">
-        <v>7.48732709884644</v>
+        <v>7.48732662200928</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.38404273986816</v>
       </c>
       <c r="G391" t="n">
-        <v>7.43390893936157</v>
+        <v>7.43390846252441</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>8.66016387939453</v>
       </c>
       <c r="G392" t="n">
-        <v>7.67873811721802</v>
+        <v>7.67873859405518</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G393" t="n">
-        <v>7.74551010131836</v>
+        <v>7.7455096244812</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.86098003387451</v>
       </c>
       <c r="G395" t="n">
-        <v>7.85679578781128</v>
+        <v>7.85679721832275</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G396" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.514573097229</v>
       </c>
       <c r="G398" t="n">
-        <v>7.54964685440063</v>
+        <v>7.54964637756348</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G399" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842311859131</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G400" t="n">
-        <v>7.61196708679199</v>
+        <v>7.61196756362915</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.56477737426758</v>
       </c>
       <c r="G403" t="n">
-        <v>7.59416103363037</v>
+        <v>7.59416151046753</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>8.6953067779541</v>
       </c>
       <c r="G404" t="n">
-        <v>7.70989894866943</v>
+        <v>7.70989847183228</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G406" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G407" t="n">
-        <v>7.64757871627808</v>
+        <v>7.64757966995239</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.65514373779297</v>
       </c>
       <c r="G410" t="n">
-        <v>7.67428731918335</v>
+        <v>7.67428636550903</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.16816711425781</v>
       </c>
       <c r="G414" t="n">
-        <v>7.24249744415283</v>
+        <v>7.24249792098999</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.21837043762207</v>
       </c>
       <c r="G415" t="n">
-        <v>7.28701162338257</v>
+        <v>7.28701210021973</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G416" t="n">
-        <v>7.26475429534912</v>
+        <v>7.26475477218628</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>8.08281993865967</v>
       </c>
       <c r="G419" t="n">
-        <v>7.16682243347168</v>
+        <v>7.16682195663452</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>7.84184217453003</v>
       </c>
       <c r="G421" t="n">
-        <v>6.95315408706665</v>
+        <v>6.95315361022949</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.61592388153076</v>
       </c>
       <c r="G422" t="n">
-        <v>6.75283813476562</v>
+        <v>6.75283861160278</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>7.70127105712891</v>
       </c>
       <c r="G423" t="n">
-        <v>6.82851314544678</v>
+        <v>6.82851362228394</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>7.68621015548706</v>
       </c>
       <c r="G424" t="n">
-        <v>6.81515884399414</v>
+        <v>6.8151593208313</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.40004777908325</v>
       </c>
       <c r="G426" t="n">
-        <v>6.56142616271973</v>
+        <v>6.56142663955688</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.82677984237671</v>
       </c>
       <c r="G427" t="n">
-        <v>6.93979835510254</v>
+        <v>6.9397988319397</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.74645376205444</v>
       </c>
       <c r="G428" t="n">
-        <v>6.86857604980469</v>
+        <v>6.86857557296753</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G432" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.96233081817627</v>
       </c>
       <c r="G433" t="n">
-        <v>7.05998802185059</v>
+        <v>7.05998849868774</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.51959419250488</v>
       </c>
       <c r="G437" t="n">
-        <v>7.55409908294678</v>
+        <v>7.55409860610962</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.42922687530518</v>
       </c>
       <c r="G438" t="n">
-        <v>7.47397232055664</v>
+        <v>7.4739727973938</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G440" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G441" t="n">
-        <v>7.66538429260254</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.95134735107422</v>
       </c>
       <c r="G451" t="n">
-        <v>7.93692302703857</v>
+        <v>7.93692350387573</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.19734573364258</v>
       </c>
       <c r="G452" t="n">
-        <v>8.15504264831543</v>
+        <v>8.15504360198975</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G462" t="n">
-        <v>7.38939523696899</v>
+        <v>7.38939476013184</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.3790225982666</v>
       </c>
       <c r="G463" t="n">
-        <v>7.42945766448975</v>
+        <v>7.42945718765259</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.16314601898193</v>
       </c>
       <c r="G464" t="n">
-        <v>7.23804521560669</v>
+        <v>7.23804569244385</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G466" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.64510345458984</v>
       </c>
       <c r="G467" t="n">
-        <v>7.66538429260254</v>
+        <v>7.6653847694397</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.01661205291748</v>
       </c>
       <c r="G469" t="n">
-        <v>7.99479103088379</v>
+        <v>7.99479198455811</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.63914012908936</v>
       </c>
       <c r="G472" t="n">
-        <v>8.5467700958252</v>
+        <v>8.54677104949951</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G474" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G475" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G476" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.49354839324951</v>
       </c>
       <c r="G478" t="n">
-        <v>8.41767883300781</v>
+        <v>8.4176778793335</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.78065395355225</v>
       </c>
       <c r="G480" t="n">
-        <v>7.78557348251343</v>
+        <v>7.78557395935059</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.62502193450928</v>
       </c>
       <c r="G481" t="n">
-        <v>7.64757871627808</v>
+        <v>7.64757966995239</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G482" t="n">
-        <v>7.62532186508179</v>
+        <v>7.62532234191895</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>8.59992027282715</v>
       </c>
       <c r="G483" t="n">
-        <v>7.62532186508179</v>
+        <v>7.62532234191895</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>8.67522621154785</v>
       </c>
       <c r="G484" t="n">
-        <v>7.69209384918213</v>
+        <v>7.69209432601929</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>8.91620445251465</v>
       </c>
       <c r="G486" t="n">
-        <v>7.90576219558716</v>
+        <v>7.90576267242432</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>8.84591865539551</v>
       </c>
       <c r="G487" t="n">
-        <v>7.84344148635864</v>
+        <v>7.84344244003296</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>8.60494041442871</v>
       </c>
       <c r="G488" t="n">
-        <v>7.62977313995361</v>
+        <v>7.62977266311646</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G490" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>8.73546981811523</v>
       </c>
       <c r="G491" t="n">
-        <v>7.74551010131836</v>
+        <v>7.7455096244812</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G494" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G495" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>8.60996055603027</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63422441482544</v>
+        <v>7.6342248916626</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>8.55975723266602</v>
       </c>
       <c r="G501" t="n">
-        <v>7.5897102355957</v>
+        <v>7.58971071243286</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.74049091339111</v>
       </c>
       <c r="G504" t="n">
-        <v>7.74996185302734</v>
+        <v>7.74996280670166</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>9.33791637420654</v>
       </c>
       <c r="G507" t="n">
-        <v>8.27968406677246</v>
+        <v>8.27968311309814</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.68934345245361</v>
       </c>
       <c r="G509" t="n">
-        <v>8.59128379821777</v>
+        <v>8.59128475189209</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.61403846740723</v>
       </c>
       <c r="G510" t="n">
-        <v>8.52451419830322</v>
+        <v>8.52451324462891</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.55379295349121</v>
       </c>
       <c r="G511" t="n">
-        <v>8.47109603881836</v>
+        <v>8.47109508514404</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9.59395599365234</v>
       </c>
       <c r="G512" t="n">
-        <v>8.50670719146729</v>
+        <v>8.50670623779297</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.58893585205078</v>
       </c>
       <c r="G513" t="n">
-        <v>8.5022554397583</v>
+        <v>8.50225639343262</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.84999561309814</v>
       </c>
       <c r="G514" t="n">
-        <v>8.73373126983643</v>
+        <v>8.73373031616211</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.81485271453857</v>
       </c>
       <c r="G515" t="n">
-        <v>8.70256996154785</v>
+        <v>8.70257091522217</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.76464939117432</v>
       </c>
       <c r="G518" t="n">
-        <v>8.65805530548096</v>
+        <v>8.65805625915527</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>10.1210966110229</v>
       </c>
       <c r="G519" t="n">
-        <v>8.9741096496582</v>
+        <v>8.97410869598389</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>10.2968101501465</v>
       </c>
       <c r="G522" t="n">
-        <v>9.12990856170654</v>
+        <v>9.12990951538086</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>10.1913824081421</v>
       </c>
       <c r="G523" t="n">
-        <v>9.0364294052124</v>
+        <v>9.03643035888672</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>10.1813411712646</v>
       </c>
       <c r="G524" t="n">
-        <v>9.02752685546875</v>
+        <v>9.02752590179443</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>10.4172992706299</v>
       </c>
       <c r="G527" t="n">
-        <v>9.23674392700195</v>
+        <v>9.23674297332764</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>10.3369731903076</v>
       </c>
       <c r="G528" t="n">
-        <v>9.1655216217041</v>
+        <v>9.16552066802979</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.96797466278076</v>
       </c>
       <c r="G531" t="n">
-        <v>8.83833980560303</v>
+        <v>8.83833885192871</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>9.46593570709229</v>
       </c>
       <c r="G533" t="n">
-        <v>8.3931941986084</v>
+        <v>8.39319515228271</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.49605941772461</v>
       </c>
       <c r="G534" t="n">
-        <v>8.41990566253662</v>
+        <v>8.41990375518799</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>9.30277442932129</v>
       </c>
       <c r="G535" t="n">
-        <v>8.2485237121582</v>
+        <v>8.24852466583252</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.2098970413208</v>
       </c>
       <c r="G536" t="n">
-        <v>8.16617202758789</v>
+        <v>8.16617107391357</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.72542858123779</v>
       </c>
       <c r="G539" t="n">
-        <v>7.73660612106323</v>
+        <v>7.73660707473755</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>8.58485889434814</v>
       </c>
       <c r="G540" t="n">
-        <v>7.61196708679199</v>
+        <v>7.61196756362915</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.50955295562744</v>
       </c>
       <c r="G541" t="n">
-        <v>7.54519605636597</v>
+        <v>7.54519510269165</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>8.4543285369873</v>
       </c>
       <c r="G543" t="n">
-        <v>7.49622964859009</v>
+        <v>7.49623012542725</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.70032691955566</v>
       </c>
       <c r="G547" t="n">
-        <v>7.71435022354126</v>
+        <v>7.7143497467041</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.83587837219238</v>
       </c>
       <c r="G550" t="n">
-        <v>7.83453989028931</v>
+        <v>7.83453893661499</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.75555229187012</v>
       </c>
       <c r="G551" t="n">
-        <v>7.7633171081543</v>
+        <v>7.76331663131714</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.65012359619141</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66983556747437</v>
+        <v>7.66983604431152</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G553" t="n">
-        <v>7.50068092346191</v>
+        <v>7.50068044662476</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.48445129394531</v>
       </c>
       <c r="G554" t="n">
-        <v>7.52293872833252</v>
+        <v>7.5229377746582</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.22590065002441</v>
       </c>
       <c r="G555" t="n">
-        <v>7.29368877410889</v>
+        <v>7.29368829727173</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.45934867858887</v>
       </c>
       <c r="G557" t="n">
-        <v>7.50068092346191</v>
+        <v>7.50068044662476</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.56979656219482</v>
       </c>
       <c r="G558" t="n">
-        <v>7.5986123085022</v>
+        <v>7.59861183166504</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.74802112579346</v>
       </c>
       <c r="G559" t="n">
-        <v>7.75663805007935</v>
+        <v>7.75663948059082</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.74300098419189</v>
       </c>
       <c r="G560" t="n">
-        <v>7.75218725204468</v>
+        <v>7.75218820571899</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.31124782562256</v>
       </c>
       <c r="G564" t="n">
-        <v>7.36936378479004</v>
+        <v>7.36936330795288</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.38655281066895</v>
       </c>
       <c r="G565" t="n">
-        <v>7.43613433837891</v>
+        <v>7.43613481521606</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8.32128810882568</v>
       </c>
       <c r="G567" t="n">
-        <v>7.37826585769653</v>
+        <v>7.37826633453369</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>8.17820739746094</v>
       </c>
       <c r="G570" t="n">
-        <v>7.25140047073364</v>
+        <v>7.25139999389648</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.97488212585449</v>
       </c>
       <c r="G573" t="n">
-        <v>7.07111740112305</v>
+        <v>7.07111692428589</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.98743295669556</v>
       </c>
       <c r="G574" t="n">
-        <v>7.08224534988403</v>
+        <v>7.08224582672119</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G578" t="n">
-        <v>6.98876523971558</v>
+        <v>6.98876571655273</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.73390293121338</v>
       </c>
       <c r="G579" t="n">
-        <v>6.85744667053223</v>
+        <v>6.85744762420654</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>7.9949631690979</v>
       </c>
       <c r="G581" t="n">
-        <v>7.08892202377319</v>
+        <v>7.08892250061035</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.14808464050293</v>
       </c>
       <c r="G583" t="n">
-        <v>7.22469139099121</v>
+        <v>7.22469091415405</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>8.1079216003418</v>
       </c>
       <c r="G584" t="n">
-        <v>7.18907976150513</v>
+        <v>7.18907928466797</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.09788131713867</v>
       </c>
       <c r="G585" t="n">
-        <v>7.18017721176147</v>
+        <v>7.18017673492432</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.43424701690674</v>
       </c>
       <c r="G587" t="n">
-        <v>7.47842407226562</v>
+        <v>7.47842311859131</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.36396217346191</v>
       </c>
       <c r="G588" t="n">
-        <v>7.41610383987427</v>
+        <v>7.41610431671143</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.19326877593994</v>
       </c>
       <c r="G590" t="n">
-        <v>7.26475429534912</v>
+        <v>7.26475477218628</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>7.88200521469116</v>
       </c>
       <c r="G591" t="n">
-        <v>6.98876523971558</v>
+        <v>6.98876571655273</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.89204502105713</v>
       </c>
       <c r="G592" t="n">
-        <v>6.99766778945923</v>
+        <v>6.99766731262207</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>7.96735095977783</v>
       </c>
       <c r="G594" t="n">
-        <v>7.06443881988525</v>
+        <v>7.06443929672241</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>7.92969799041748</v>
       </c>
       <c r="G596" t="n">
-        <v>7.03105306625366</v>
+        <v>7.03105354309082</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G600" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.33383941650391</v>
       </c>
       <c r="G601" t="n">
-        <v>7.38939523696899</v>
+        <v>7.38939476013184</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.53465461730957</v>
       </c>
       <c r="G602" t="n">
-        <v>7.5674524307251</v>
+        <v>7.56745290756226</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.83242416381836</v>
       </c>
       <c r="G605" t="n">
-        <v>8.7181510925293</v>
+        <v>8.71815013885498</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.95040321350098</v>
       </c>
       <c r="G606" t="n">
-        <v>8.8227596282959</v>
+        <v>8.82275867462158</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.6316089630127</v>
       </c>
       <c r="G607" t="n">
-        <v>8.54009342193604</v>
+        <v>8.54009246826172</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>9.83995532989502</v>
       </c>
       <c r="G608" t="n">
-        <v>8.72482776641846</v>
+        <v>8.72482872009277</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>10.0909738540649</v>
       </c>
       <c r="G609" t="n">
-        <v>8.9473991394043</v>
+        <v>8.94740009307861</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.44585514068604</v>
       </c>
       <c r="G611" t="n">
-        <v>8.37539005279541</v>
+        <v>8.37538909912109</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.23750877380371</v>
       </c>
       <c r="G612" t="n">
-        <v>8.19065380096436</v>
+        <v>8.19065475463867</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>8.79822540283203</v>
       </c>
       <c r="G613" t="n">
-        <v>7.80115365982056</v>
+        <v>7.80115413665771</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.68181324005127</v>
       </c>
       <c r="G617" t="n">
-        <v>8.58460807800293</v>
+        <v>8.58460712432861</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.31783485412598</v>
       </c>
       <c r="G620" t="n">
-        <v>8.26187896728516</v>
+        <v>8.26187801361084</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.78975105285645</v>
       </c>
       <c r="G621" t="n">
-        <v>8.68031406402588</v>
+        <v>8.68031311035156</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>9.72448635101318</v>
       </c>
       <c r="G622" t="n">
-        <v>8.62244510650635</v>
+        <v>8.62244415283203</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>9.85250568389893</v>
       </c>
       <c r="G623" t="n">
-        <v>8.7359561920166</v>
+        <v>8.73595523834229</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.66424083709717</v>
       </c>
       <c r="G624" t="n">
-        <v>8.56902694702148</v>
+        <v>8.5690259933471